--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="1950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="1949">
   <si>
     <t>ID</t>
   </si>
@@ -3966,9 +3966,6 @@
     <t>04.112.864/0001-56</t>
   </si>
   <si>
-    <t>86 %</t>
-  </si>
-  <si>
     <t>724</t>
   </si>
   <si>
@@ -4488,9 +4485,6 @@
     <t>879</t>
   </si>
   <si>
-    <t>89 %</t>
-  </si>
-  <si>
     <t>880</t>
   </si>
   <si>
@@ -5772,6 +5766,9 @@
     <t>1178</t>
   </si>
   <si>
+    <t>80 %</t>
+  </si>
+  <si>
     <t>1179</t>
   </si>
   <si>
@@ -5784,13 +5781,13 @@
     <t>1182</t>
   </si>
   <si>
-    <t>46 %</t>
+    <t>65 %</t>
   </si>
   <si>
     <t>1183</t>
   </si>
   <si>
-    <t>7 %</t>
+    <t>19 %</t>
   </si>
   <si>
     <t>1184</t>
@@ -5811,9 +5808,6 @@
     <t>1188</t>
   </si>
   <si>
-    <t>15 %</t>
-  </si>
-  <si>
     <t>1189</t>
   </si>
   <si>
@@ -5863,6 +5857,9 @@
   </si>
   <si>
     <t>1197</t>
+  </si>
+  <si>
+    <t>1198</t>
   </si>
 </sst>
 </file>
@@ -6056,7 +6053,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V964"/>
+  <dimension ref="A1:V965"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -38598,13 +38595,13 @@
         <v>23</v>
       </c>
       <c r="E561" s="8" t="s">
-        <v>1317</v>
+        <v>24</v>
       </c>
       <c r="F561" s="9" t="s">
         <v>235</v>
       </c>
       <c r="G561" s="9" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H561" s="10" t="n">
         <v>46122</v>
@@ -38636,7 +38633,7 @@
         <v>242444.07</v>
       </c>
       <c r="S561" s="12" t="n">
-        <v>207620.82</v>
+        <v>242444.07</v>
       </c>
       <c r="T561" s="9" t="s">
         <v>32</v>
@@ -38659,10 +38656,10 @@
         <v>24</v>
       </c>
       <c r="F562" s="4" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G562" s="4" t="s">
         <v>1319</v>
-      </c>
-      <c r="G562" s="4" t="s">
-        <v>1320</v>
       </c>
       <c r="H562" s="5" t="n">
         <v>46122</v>
@@ -38717,22 +38714,22 @@
         <v>24</v>
       </c>
       <c r="F563" s="9" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G563" s="9" t="s">
         <v>1321</v>
-      </c>
-      <c r="G563" s="9" t="s">
-        <v>1322</v>
       </c>
       <c r="H563" s="10" t="n">
         <v>46125</v>
       </c>
       <c r="I563" s="9" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="J563" s="9" t="s">
+        <v>1322</v>
+      </c>
+      <c r="K563" s="9" t="s">
         <v>1323</v>
-      </c>
-      <c r="K563" s="9" t="s">
-        <v>1324</v>
       </c>
       <c r="L563" s="10"/>
       <c r="M563" s="10"/>
@@ -38778,7 +38775,7 @@
         <v>1289</v>
       </c>
       <c r="G564" s="4" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H564" s="5" t="n">
         <v>46125</v>
@@ -38833,10 +38830,10 @@
         <v>24</v>
       </c>
       <c r="F565" s="9" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G565" s="9" t="s">
         <v>1326</v>
-      </c>
-      <c r="G565" s="9" t="s">
-        <v>1327</v>
       </c>
       <c r="H565" s="10" t="n">
         <v>46126</v>
@@ -38894,7 +38891,7 @@
         <v>355</v>
       </c>
       <c r="G566" s="4" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H566" s="5" t="n">
         <v>46126</v>
@@ -38949,22 +38946,22 @@
         <v>24</v>
       </c>
       <c r="F567" s="9" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G567" s="9" t="s">
         <v>1329</v>
-      </c>
-      <c r="G567" s="9" t="s">
-        <v>1330</v>
       </c>
       <c r="H567" s="10" t="n">
         <v>46126</v>
       </c>
       <c r="I567" s="9" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="J567" s="9" t="s">
+        <v>1330</v>
+      </c>
+      <c r="K567" s="9" t="s">
         <v>1331</v>
-      </c>
-      <c r="K567" s="9" t="s">
-        <v>1332</v>
       </c>
       <c r="L567" s="10"/>
       <c r="M567" s="10"/>
@@ -39010,7 +39007,7 @@
         <v>945</v>
       </c>
       <c r="G568" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H568" s="5" t="n">
         <v>46127</v>
@@ -39068,7 +39065,7 @@
         <v>945</v>
       </c>
       <c r="G569" s="9" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H569" s="10" t="n">
         <v>46127</v>
@@ -39126,7 +39123,7 @@
         <v>194</v>
       </c>
       <c r="G570" s="4" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H570" s="5" t="n">
         <v>46127</v>
@@ -39184,7 +39181,7 @@
         <v>103</v>
       </c>
       <c r="G571" s="9" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H571" s="10" t="n">
         <v>46127</v>
@@ -39242,7 +39239,7 @@
         <v>103</v>
       </c>
       <c r="G572" s="4" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H572" s="5" t="n">
         <v>46127</v>
@@ -39300,7 +39297,7 @@
         <v>75</v>
       </c>
       <c r="G573" s="9" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H573" s="10" t="n">
         <v>46127</v>
@@ -39355,22 +39352,22 @@
         <v>24</v>
       </c>
       <c r="F574" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G574" s="4" t="s">
         <v>1339</v>
-      </c>
-      <c r="G574" s="4" t="s">
-        <v>1340</v>
       </c>
       <c r="H574" s="5" t="n">
         <v>46127</v>
       </c>
       <c r="I574" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="J574" s="4" t="s">
+        <v>1340</v>
+      </c>
+      <c r="K574" s="4" t="s">
         <v>1341</v>
-      </c>
-      <c r="K574" s="4" t="s">
-        <v>1342</v>
       </c>
       <c r="L574" s="5"/>
       <c r="M574" s="5"/>
@@ -39416,7 +39413,7 @@
         <v>332</v>
       </c>
       <c r="G575" s="9" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H575" s="10" t="n">
         <v>46128</v>
@@ -39471,10 +39468,10 @@
         <v>24</v>
       </c>
       <c r="F576" s="4" t="s">
+        <v>1343</v>
+      </c>
+      <c r="G576" s="4" t="s">
         <v>1344</v>
-      </c>
-      <c r="G576" s="4" t="s">
-        <v>1345</v>
       </c>
       <c r="H576" s="5" t="n">
         <v>46128</v>
@@ -39532,7 +39529,7 @@
         <v>955</v>
       </c>
       <c r="G577" s="9" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H577" s="10" t="n">
         <v>46128</v>
@@ -39587,10 +39584,10 @@
         <v>24</v>
       </c>
       <c r="F578" s="4" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G578" s="4" t="s">
         <v>1347</v>
-      </c>
-      <c r="G578" s="4" t="s">
-        <v>1348</v>
       </c>
       <c r="H578" s="5" t="n">
         <v>46128</v>
@@ -39648,7 +39645,7 @@
         <v>194</v>
       </c>
       <c r="G579" s="9" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H579" s="10" t="n">
         <v>46128</v>
@@ -39706,7 +39703,7 @@
         <v>276</v>
       </c>
       <c r="G580" s="4" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H580" s="5" t="n">
         <v>46129</v>
@@ -39764,7 +39761,7 @@
         <v>1289</v>
       </c>
       <c r="G581" s="9" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H581" s="10" t="n">
         <v>46132</v>
@@ -39822,7 +39819,7 @@
         <v>436</v>
       </c>
       <c r="G582" s="4" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H582" s="5" t="n">
         <v>46132</v>
@@ -39880,7 +39877,7 @@
         <v>945</v>
       </c>
       <c r="G583" s="9" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H583" s="10" t="n">
         <v>46132</v>
@@ -39938,7 +39935,7 @@
         <v>945</v>
       </c>
       <c r="G584" s="4" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H584" s="5" t="n">
         <v>46132</v>
@@ -39993,10 +39990,10 @@
         <v>24</v>
       </c>
       <c r="F585" s="9" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G585" s="9" t="s">
         <v>1355</v>
-      </c>
-      <c r="G585" s="9" t="s">
-        <v>1356</v>
       </c>
       <c r="H585" s="10" t="n">
         <v>46132</v>
@@ -40054,7 +40051,7 @@
         <v>1077</v>
       </c>
       <c r="G586" s="4" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H586" s="5" t="n">
         <v>46132</v>
@@ -40112,7 +40109,7 @@
         <v>400</v>
       </c>
       <c r="G587" s="9" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H587" s="10" t="n">
         <v>46132</v>
@@ -40170,7 +40167,7 @@
         <v>168</v>
       </c>
       <c r="G588" s="4" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H588" s="5" t="n">
         <v>46132</v>
@@ -40228,7 +40225,7 @@
         <v>1097</v>
       </c>
       <c r="G589" s="9" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H589" s="10" t="n">
         <v>46132</v>
@@ -40286,7 +40283,7 @@
         <v>1241</v>
       </c>
       <c r="G590" s="4" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H590" s="5" t="n">
         <v>46132</v>
@@ -40344,7 +40341,7 @@
         <v>168</v>
       </c>
       <c r="G591" s="9" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H591" s="10" t="n">
         <v>46132</v>
@@ -40402,7 +40399,7 @@
         <v>945</v>
       </c>
       <c r="G592" s="4" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H592" s="5" t="n">
         <v>46132</v>
@@ -40460,7 +40457,7 @@
         <v>945</v>
       </c>
       <c r="G593" s="9" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H593" s="10" t="n">
         <v>46132</v>
@@ -40518,7 +40515,7 @@
         <v>581</v>
       </c>
       <c r="G594" s="4" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H594" s="5" t="n">
         <v>46132</v>
@@ -40573,10 +40570,10 @@
         <v>24</v>
       </c>
       <c r="F595" s="9" t="s">
+        <v>1365</v>
+      </c>
+      <c r="G595" s="9" t="s">
         <v>1366</v>
-      </c>
-      <c r="G595" s="9" t="s">
-        <v>1367</v>
       </c>
       <c r="H595" s="10" t="n">
         <v>46132</v>
@@ -40631,22 +40628,22 @@
         <v>24</v>
       </c>
       <c r="F596" s="4" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G596" s="4" t="s">
         <v>1368</v>
-      </c>
-      <c r="G596" s="4" t="s">
-        <v>1369</v>
       </c>
       <c r="H596" s="5" t="n">
         <v>46134</v>
       </c>
       <c r="I596" s="4" t="s">
+        <v>1369</v>
+      </c>
+      <c r="J596" s="4" t="s">
         <v>1370</v>
       </c>
-      <c r="J596" s="4" t="s">
+      <c r="K596" s="4" t="s">
         <v>1371</v>
-      </c>
-      <c r="K596" s="4" t="s">
-        <v>1372</v>
       </c>
       <c r="L596" s="5"/>
       <c r="M596" s="5"/>
@@ -40692,7 +40689,7 @@
         <v>33</v>
       </c>
       <c r="G597" s="9" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H597" s="10" t="n">
         <v>46134</v>
@@ -40747,10 +40744,10 @@
         <v>24</v>
       </c>
       <c r="F598" s="4" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G598" s="4" t="s">
         <v>1374</v>
-      </c>
-      <c r="G598" s="4" t="s">
-        <v>1375</v>
       </c>
       <c r="H598" s="5" t="n">
         <v>46134</v>
@@ -40808,7 +40805,7 @@
         <v>1264</v>
       </c>
       <c r="G599" s="9" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H599" s="10" t="n">
         <v>46134</v>
@@ -40866,7 +40863,7 @@
         <v>157</v>
       </c>
       <c r="G600" s="4" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H600" s="5" t="n">
         <v>46135</v>
@@ -40924,7 +40921,7 @@
         <v>77</v>
       </c>
       <c r="G601" s="9" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H601" s="10" t="n">
         <v>46135</v>
@@ -40979,10 +40976,10 @@
         <v>24</v>
       </c>
       <c r="F602" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G602" s="4" t="s">
         <v>1379</v>
-      </c>
-      <c r="G602" s="4" t="s">
-        <v>1380</v>
       </c>
       <c r="H602" s="5" t="n">
         <v>46135</v>
@@ -41040,7 +41037,7 @@
         <v>1102</v>
       </c>
       <c r="G603" s="9" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H603" s="10" t="n">
         <v>46135</v>
@@ -41098,7 +41095,7 @@
         <v>589</v>
       </c>
       <c r="G604" s="4" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H604" s="5" t="n">
         <v>46135</v>
@@ -41156,7 +41153,7 @@
         <v>75</v>
       </c>
       <c r="G605" s="9" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H605" s="10" t="n">
         <v>46136</v>
@@ -41214,7 +41211,7 @@
         <v>1075</v>
       </c>
       <c r="G606" s="4" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H606" s="5" t="n">
         <v>46139</v>
@@ -41272,7 +41269,7 @@
         <v>484</v>
       </c>
       <c r="G607" s="9" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H607" s="10" t="n">
         <v>46139</v>
@@ -41330,7 +41327,7 @@
         <v>75</v>
       </c>
       <c r="G608" s="4" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H608" s="5" t="n">
         <v>46139</v>
@@ -41388,7 +41385,7 @@
         <v>191</v>
       </c>
       <c r="G609" s="9" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H609" s="10" t="n">
         <v>46139</v>
@@ -41446,7 +41443,7 @@
         <v>552</v>
       </c>
       <c r="G610" s="4" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H610" s="5" t="n">
         <v>46139</v>
@@ -41504,7 +41501,7 @@
         <v>49</v>
       </c>
       <c r="G611" s="9" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H611" s="10" t="n">
         <v>46139</v>
@@ -41562,7 +41559,7 @@
         <v>75</v>
       </c>
       <c r="G612" s="4" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H612" s="5" t="n">
         <v>46139</v>
@@ -41620,7 +41617,7 @@
         <v>272</v>
       </c>
       <c r="G613" s="9" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H613" s="10" t="n">
         <v>46139</v>
@@ -41678,7 +41675,7 @@
         <v>945</v>
       </c>
       <c r="G614" s="4" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H614" s="5" t="n">
         <v>46140</v>
@@ -41733,22 +41730,22 @@
         <v>24</v>
       </c>
       <c r="F615" s="9" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G615" s="9" t="s">
         <v>1393</v>
-      </c>
-      <c r="G615" s="9" t="s">
-        <v>1394</v>
       </c>
       <c r="H615" s="10" t="n">
         <v>46141</v>
       </c>
       <c r="I615" s="9" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J615" s="9" t="s">
+        <v>1394</v>
+      </c>
+      <c r="K615" s="9" t="s">
         <v>1395</v>
-      </c>
-      <c r="K615" s="9" t="s">
-        <v>1396</v>
       </c>
       <c r="L615" s="10"/>
       <c r="M615" s="10"/>
@@ -41794,7 +41791,7 @@
         <v>561</v>
       </c>
       <c r="G616" s="4" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H616" s="5" t="n">
         <v>46141</v>
@@ -41849,10 +41846,10 @@
         <v>24</v>
       </c>
       <c r="F617" s="9" t="s">
+        <v>1397</v>
+      </c>
+      <c r="G617" s="9" t="s">
         <v>1398</v>
-      </c>
-      <c r="G617" s="9" t="s">
-        <v>1399</v>
       </c>
       <c r="H617" s="10" t="n">
         <v>46141</v>
@@ -41904,13 +41901,13 @@
         <v>23</v>
       </c>
       <c r="E618" s="3" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F618" s="4" t="s">
         <v>945</v>
       </c>
       <c r="G618" s="4" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H618" s="5" t="n">
         <v>46141</v>
@@ -41968,7 +41965,7 @@
         <v>945</v>
       </c>
       <c r="G619" s="9" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H619" s="10" t="n">
         <v>46141</v>
@@ -42023,10 +42020,10 @@
         <v>24</v>
       </c>
       <c r="F620" s="4" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="G620" s="4" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H620" s="5" t="n">
         <v>46141</v>
@@ -42084,7 +42081,7 @@
         <v>295</v>
       </c>
       <c r="G621" s="9" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H621" s="10" t="n">
         <v>46141</v>
@@ -42142,7 +42139,7 @@
         <v>1196</v>
       </c>
       <c r="G622" s="4" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H622" s="5" t="n">
         <v>46141</v>
@@ -42200,7 +42197,7 @@
         <v>310</v>
       </c>
       <c r="G623" s="9" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H623" s="10" t="n">
         <v>46141</v>
@@ -42258,7 +42255,7 @@
         <v>742</v>
       </c>
       <c r="G624" s="4" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H624" s="5" t="n">
         <v>46141</v>
@@ -42316,7 +42313,7 @@
         <v>249</v>
       </c>
       <c r="G625" s="9" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H625" s="10" t="n">
         <v>46141</v>
@@ -42374,7 +42371,7 @@
         <v>157</v>
       </c>
       <c r="G626" s="4" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H626" s="5" t="n">
         <v>46141</v>
@@ -42432,7 +42429,7 @@
         <v>1298</v>
       </c>
       <c r="G627" s="9" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H627" s="10" t="n">
         <v>46142</v>
@@ -42490,7 +42487,7 @@
         <v>194</v>
       </c>
       <c r="G628" s="4" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H628" s="5" t="n">
         <v>46142</v>
@@ -42545,10 +42542,10 @@
         <v>24</v>
       </c>
       <c r="F629" s="9" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G629" s="9" t="s">
         <v>1412</v>
-      </c>
-      <c r="G629" s="9" t="s">
-        <v>1413</v>
       </c>
       <c r="H629" s="10" t="n">
         <v>46142</v>
@@ -42606,7 +42603,7 @@
         <v>38</v>
       </c>
       <c r="G630" s="4" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H630" s="5" t="n">
         <v>46142</v>
@@ -42664,7 +42661,7 @@
         <v>194</v>
       </c>
       <c r="G631" s="9" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H631" s="10" t="n">
         <v>46147</v>
@@ -42722,7 +42719,7 @@
         <v>1143</v>
       </c>
       <c r="G632" s="4" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H632" s="5" t="n">
         <v>46147</v>
@@ -42777,22 +42774,22 @@
         <v>24</v>
       </c>
       <c r="F633" s="9" t="s">
+        <v>1416</v>
+      </c>
+      <c r="G633" s="9" t="s">
         <v>1417</v>
-      </c>
-      <c r="G633" s="9" t="s">
-        <v>1418</v>
       </c>
       <c r="H633" s="10" t="n">
         <v>46147</v>
       </c>
       <c r="I633" s="9" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J633" s="9" t="s">
         <v>1419</v>
       </c>
-      <c r="J633" s="9" t="s">
+      <c r="K633" s="9" t="s">
         <v>1420</v>
-      </c>
-      <c r="K633" s="9" t="s">
-        <v>1421</v>
       </c>
       <c r="L633" s="10"/>
       <c r="M633" s="10"/>
@@ -42835,22 +42832,22 @@
         <v>24</v>
       </c>
       <c r="F634" s="4" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G634" s="4" t="s">
         <v>1422</v>
-      </c>
-      <c r="G634" s="4" t="s">
-        <v>1423</v>
       </c>
       <c r="H634" s="5" t="n">
         <v>46147</v>
       </c>
       <c r="I634" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="J634" s="4" t="s">
         <v>1424</v>
       </c>
-      <c r="J634" s="4" t="s">
+      <c r="K634" s="4" t="s">
         <v>1425</v>
-      </c>
-      <c r="K634" s="4" t="s">
-        <v>1426</v>
       </c>
       <c r="L634" s="5"/>
       <c r="M634" s="5"/>
@@ -42896,7 +42893,7 @@
         <v>461</v>
       </c>
       <c r="G635" s="9" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H635" s="10" t="n">
         <v>46147</v>
@@ -42951,22 +42948,22 @@
         <v>24</v>
       </c>
       <c r="F636" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G636" s="4" t="s">
         <v>1428</v>
-      </c>
-      <c r="G636" s="4" t="s">
-        <v>1429</v>
       </c>
       <c r="H636" s="5" t="n">
         <v>46147</v>
       </c>
       <c r="I636" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J636" s="4" t="s">
         <v>1430</v>
       </c>
-      <c r="J636" s="4" t="s">
+      <c r="K636" s="4" t="s">
         <v>1431</v>
-      </c>
-      <c r="K636" s="4" t="s">
-        <v>1432</v>
       </c>
       <c r="L636" s="5"/>
       <c r="M636" s="5"/>
@@ -43012,7 +43009,7 @@
         <v>328</v>
       </c>
       <c r="G637" s="9" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H637" s="10" t="n">
         <v>46147</v>
@@ -43070,7 +43067,7 @@
         <v>1003</v>
       </c>
       <c r="G638" s="4" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H638" s="5" t="n">
         <v>46147</v>
@@ -43128,7 +43125,7 @@
         <v>38</v>
       </c>
       <c r="G639" s="9" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H639" s="10" t="n">
         <v>46147</v>
@@ -43183,10 +43180,10 @@
         <v>24</v>
       </c>
       <c r="F640" s="4" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G640" s="4" t="s">
         <v>1436</v>
-      </c>
-      <c r="G640" s="4" t="s">
-        <v>1437</v>
       </c>
       <c r="H640" s="5" t="n">
         <v>46147</v>
@@ -43244,7 +43241,7 @@
         <v>698</v>
       </c>
       <c r="G641" s="9" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H641" s="10" t="n">
         <v>46147</v>
@@ -43302,7 +43299,7 @@
         <v>490</v>
       </c>
       <c r="G642" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H642" s="5" t="n">
         <v>46147</v>
@@ -43360,7 +43357,7 @@
         <v>355</v>
       </c>
       <c r="G643" s="9" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H643" s="10" t="n">
         <v>46147</v>
@@ -43418,7 +43415,7 @@
         <v>1016</v>
       </c>
       <c r="G644" s="4" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H644" s="5" t="n">
         <v>46147</v>
@@ -43476,7 +43473,7 @@
         <v>896</v>
       </c>
       <c r="G645" s="9" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H645" s="10" t="n">
         <v>46147</v>
@@ -43534,7 +43531,7 @@
         <v>698</v>
       </c>
       <c r="G646" s="4" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H646" s="5" t="n">
         <v>46147</v>
@@ -43592,7 +43589,7 @@
         <v>1019</v>
       </c>
       <c r="G647" s="9" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H647" s="10" t="n">
         <v>46148</v>
@@ -43650,7 +43647,7 @@
         <v>276</v>
       </c>
       <c r="G648" s="4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H648" s="5" t="n">
         <v>46148</v>
@@ -43708,7 +43705,7 @@
         <v>288</v>
       </c>
       <c r="G649" s="9" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H649" s="10" t="n">
         <v>46148</v>
@@ -43766,7 +43763,7 @@
         <v>223</v>
       </c>
       <c r="G650" s="4" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H650" s="5" t="n">
         <v>46150</v>
@@ -43824,7 +43821,7 @@
         <v>1008</v>
       </c>
       <c r="G651" s="9" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H651" s="10" t="n">
         <v>46150</v>
@@ -43884,7 +43881,7 @@
         <v>75</v>
       </c>
       <c r="G652" s="4" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H652" s="5" t="n">
         <v>46150</v>
@@ -43942,7 +43939,7 @@
         <v>665</v>
       </c>
       <c r="G653" s="9" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H653" s="10" t="n">
         <v>46153</v>
@@ -44000,7 +43997,7 @@
         <v>203</v>
       </c>
       <c r="G654" s="4" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H654" s="5" t="n">
         <v>46153</v>
@@ -44055,22 +44052,22 @@
         <v>24</v>
       </c>
       <c r="F655" s="9" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G655" s="9" t="s">
         <v>1452</v>
-      </c>
-      <c r="G655" s="9" t="s">
-        <v>1453</v>
       </c>
       <c r="H655" s="10" t="n">
         <v>46154</v>
       </c>
       <c r="I655" s="9" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="J655" s="9" t="s">
+        <v>1453</v>
+      </c>
+      <c r="K655" s="9" t="s">
         <v>1454</v>
-      </c>
-      <c r="K655" s="9" t="s">
-        <v>1455</v>
       </c>
       <c r="L655" s="10"/>
       <c r="M655" s="10"/>
@@ -44081,7 +44078,7 @@
         <v>46154.67827662</v>
       </c>
       <c r="P655" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q655" s="9" t="s">
         <v>47</v>
@@ -44116,7 +44113,7 @@
         <v>75</v>
       </c>
       <c r="G656" s="4" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H656" s="5" t="n">
         <v>46154</v>
@@ -44139,7 +44136,7 @@
         <v>46154.684005243</v>
       </c>
       <c r="P656" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q656" s="4" t="s">
         <v>31</v>
@@ -44168,13 +44165,13 @@
         <v>23</v>
       </c>
       <c r="E657" s="8" t="s">
-        <v>952</v>
+        <v>24</v>
       </c>
       <c r="F657" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G657" s="9" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H657" s="10" t="n">
         <v>46156</v>
@@ -44191,13 +44188,13 @@
       <c r="L657" s="10"/>
       <c r="M657" s="10"/>
       <c r="N657" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O657" s="11" t="n">
         <v>46156.334980556</v>
       </c>
       <c r="P657" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q657" s="9" t="s">
         <v>31</v>
@@ -44206,7 +44203,7 @@
         <v>288792.7</v>
       </c>
       <c r="S657" s="12" t="n">
-        <v>275670.1</v>
+        <v>288780.1</v>
       </c>
       <c r="T657" s="9" t="s">
         <v>32</v>
@@ -44232,7 +44229,7 @@
         <v>698</v>
       </c>
       <c r="G658" s="4" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H658" s="5" t="n">
         <v>46156</v>
@@ -44255,7 +44252,7 @@
         <v>46156.347628623</v>
       </c>
       <c r="P658" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q658" s="4" t="s">
         <v>47</v>
@@ -44287,22 +44284,22 @@
         <v>24</v>
       </c>
       <c r="F659" s="9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="G659" s="9" t="s">
         <v>1460</v>
-      </c>
-      <c r="G659" s="9" t="s">
-        <v>1461</v>
       </c>
       <c r="H659" s="10" t="n">
         <v>46156</v>
       </c>
       <c r="I659" s="9" t="s">
+        <v>1461</v>
+      </c>
+      <c r="J659" s="9" t="s">
         <v>1462</v>
       </c>
-      <c r="J659" s="9" t="s">
+      <c r="K659" s="9" t="s">
         <v>1463</v>
-      </c>
-      <c r="K659" s="9" t="s">
-        <v>1464</v>
       </c>
       <c r="L659" s="10"/>
       <c r="M659" s="10"/>
@@ -44313,7 +44310,7 @@
         <v>46156.350939965</v>
       </c>
       <c r="P659" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q659" s="9" t="s">
         <v>47</v>
@@ -44348,7 +44345,7 @@
         <v>328</v>
       </c>
       <c r="G660" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H660" s="5" t="n">
         <v>46156</v>
@@ -44371,7 +44368,7 @@
         <v>46156.458845602</v>
       </c>
       <c r="P660" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q660" s="4" t="s">
         <v>31</v>
@@ -44406,7 +44403,7 @@
         <v>38</v>
       </c>
       <c r="G661" s="9" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H661" s="10" t="n">
         <v>46156</v>
@@ -44429,7 +44426,7 @@
         <v>46156.4653311</v>
       </c>
       <c r="P661" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q661" s="9" t="s">
         <v>31</v>
@@ -44464,7 +44461,7 @@
         <v>945</v>
       </c>
       <c r="G662" s="4" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H662" s="5" t="n">
         <v>46156</v>
@@ -44487,7 +44484,7 @@
         <v>46156.467329317</v>
       </c>
       <c r="P662" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q662" s="4" t="s">
         <v>31</v>
@@ -44522,7 +44519,7 @@
         <v>945</v>
       </c>
       <c r="G663" s="9" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H663" s="10" t="n">
         <v>46156</v>
@@ -44545,7 +44542,7 @@
         <v>46156.469836343</v>
       </c>
       <c r="P663" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q663" s="9" t="s">
         <v>31</v>
@@ -44577,10 +44574,10 @@
         <v>24</v>
       </c>
       <c r="F664" s="4" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="G664" s="4" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H664" s="5" t="n">
         <v>46156</v>
@@ -44603,7 +44600,7 @@
         <v>46156.475388391</v>
       </c>
       <c r="P664" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q664" s="4" t="s">
         <v>31</v>
@@ -44635,10 +44632,10 @@
         <v>24</v>
       </c>
       <c r="F665" s="9" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G665" s="9" t="s">
         <v>1470</v>
-      </c>
-      <c r="G665" s="9" t="s">
-        <v>1471</v>
       </c>
       <c r="H665" s="10" t="n">
         <v>46156</v>
@@ -44661,7 +44658,7 @@
         <v>46156.479976157</v>
       </c>
       <c r="P665" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q665" s="9" t="s">
         <v>31</v>
@@ -44693,10 +44690,10 @@
         <v>24</v>
       </c>
       <c r="F666" s="4" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G666" s="4" t="s">
         <v>1472</v>
-      </c>
-      <c r="G666" s="4" t="s">
-        <v>1473</v>
       </c>
       <c r="H666" s="5" t="n">
         <v>46157</v>
@@ -44719,7 +44716,7 @@
         <v>46157.634608368</v>
       </c>
       <c r="P666" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q666" s="4" t="s">
         <v>474</v>
@@ -44751,10 +44748,10 @@
         <v>24</v>
       </c>
       <c r="F667" s="9" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G667" s="9" t="s">
         <v>1474</v>
-      </c>
-      <c r="G667" s="9" t="s">
-        <v>1475</v>
       </c>
       <c r="H667" s="10" t="n">
         <v>46157</v>
@@ -44777,7 +44774,7 @@
         <v>46157.644521759</v>
       </c>
       <c r="P667" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q667" s="9" t="s">
         <v>31</v>
@@ -44809,22 +44806,22 @@
         <v>24</v>
       </c>
       <c r="F668" s="4" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G668" s="4" t="s">
         <v>1476</v>
-      </c>
-      <c r="G668" s="4" t="s">
-        <v>1477</v>
       </c>
       <c r="H668" s="5" t="n">
         <v>46157</v>
       </c>
       <c r="I668" s="4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="J668" s="4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="K668" s="4" t="s">
         <v>1478</v>
-      </c>
-      <c r="J668" s="4" t="s">
-        <v>1478</v>
-      </c>
-      <c r="K668" s="4" t="s">
-        <v>1479</v>
       </c>
       <c r="L668" s="5"/>
       <c r="M668" s="5"/>
@@ -44835,7 +44832,7 @@
         <v>46157.65773287</v>
       </c>
       <c r="P668" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q668" s="4" t="s">
         <v>74</v>
@@ -44867,10 +44864,10 @@
         <v>24</v>
       </c>
       <c r="F669" s="9" t="s">
+        <v>1479</v>
+      </c>
+      <c r="G669" s="9" t="s">
         <v>1480</v>
-      </c>
-      <c r="G669" s="9" t="s">
-        <v>1481</v>
       </c>
       <c r="H669" s="10" t="n">
         <v>46160</v>
@@ -44893,7 +44890,7 @@
         <v>46160.585927546</v>
       </c>
       <c r="P669" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q669" s="9" t="s">
         <v>37</v>
@@ -44928,7 +44925,7 @@
         <v>1241</v>
       </c>
       <c r="G670" s="4" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H670" s="5" t="n">
         <v>46161</v>
@@ -44951,7 +44948,7 @@
         <v>46161.504839271</v>
       </c>
       <c r="P670" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q670" s="4" t="s">
         <v>747</v>
@@ -44983,22 +44980,22 @@
         <v>24</v>
       </c>
       <c r="F671" s="9" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G671" s="9" t="s">
         <v>1483</v>
-      </c>
-      <c r="G671" s="9" t="s">
-        <v>1484</v>
       </c>
       <c r="H671" s="10" t="n">
         <v>46161</v>
       </c>
       <c r="I671" s="9" t="s">
+        <v>1484</v>
+      </c>
+      <c r="J671" s="9" t="s">
+        <v>1484</v>
+      </c>
+      <c r="K671" s="9" t="s">
         <v>1485</v>
-      </c>
-      <c r="J671" s="9" t="s">
-        <v>1485</v>
-      </c>
-      <c r="K671" s="9" t="s">
-        <v>1486</v>
       </c>
       <c r="L671" s="10"/>
       <c r="M671" s="10"/>
@@ -45009,7 +45006,7 @@
         <v>46161.506482257</v>
       </c>
       <c r="P671" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q671" s="9" t="s">
         <v>797</v>
@@ -45044,7 +45041,7 @@
         <v>328</v>
       </c>
       <c r="G672" s="4" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H672" s="5" t="n">
         <v>46161</v>
@@ -45067,7 +45064,7 @@
         <v>46161.507248808</v>
       </c>
       <c r="P672" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q672" s="4" t="s">
         <v>31</v>
@@ -45102,7 +45099,7 @@
         <v>511</v>
       </c>
       <c r="G673" s="9" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H673" s="10" t="n">
         <v>46161</v>
@@ -45125,7 +45122,7 @@
         <v>46161.512865741</v>
       </c>
       <c r="P673" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q673" s="9" t="s">
         <v>74</v>
@@ -45157,10 +45154,10 @@
         <v>24</v>
       </c>
       <c r="F674" s="4" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G674" s="4" t="s">
         <v>1489</v>
-      </c>
-      <c r="G674" s="4" t="s">
-        <v>1490</v>
       </c>
       <c r="H674" s="5" t="n">
         <v>46162</v>
@@ -45183,7 +45180,7 @@
         <v>46162.641798495</v>
       </c>
       <c r="P674" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q674" s="4" t="s">
         <v>134</v>
@@ -45212,13 +45209,13 @@
         <v>23</v>
       </c>
       <c r="E675" s="8" t="s">
-        <v>1491</v>
+        <v>952</v>
       </c>
       <c r="F675" s="9" t="s">
         <v>945</v>
       </c>
       <c r="G675" s="9" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="H675" s="10" t="n">
         <v>46162</v>
@@ -45241,7 +45238,7 @@
         <v>46162.643832442</v>
       </c>
       <c r="P675" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q675" s="9" t="s">
         <v>31</v>
@@ -45250,7 +45247,7 @@
         <v>205156.58</v>
       </c>
       <c r="S675" s="12" t="n">
-        <v>182526.98</v>
+        <v>194380.58</v>
       </c>
       <c r="T675" s="9" t="s">
         <v>32</v>
@@ -45276,7 +45273,7 @@
         <v>453</v>
       </c>
       <c r="G676" s="4" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="H676" s="5" t="n">
         <v>46162</v>
@@ -45299,7 +45296,7 @@
         <v>46162.654836111</v>
       </c>
       <c r="P676" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q676" s="4" t="s">
         <v>142</v>
@@ -45328,13 +45325,13 @@
         <v>23</v>
       </c>
       <c r="E677" s="8" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="F677" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G677" s="9" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="H677" s="10" t="n">
         <v>46163</v>
@@ -45357,7 +45354,7 @@
         <v>46163.698247801</v>
       </c>
       <c r="P677" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q677" s="9" t="s">
         <v>31</v>
@@ -45389,10 +45386,10 @@
         <v>24</v>
       </c>
       <c r="F678" s="4" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="G678" s="4" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="H678" s="5" t="n">
         <v>46163</v>
@@ -45415,7 +45412,7 @@
         <v>46163.700571493</v>
       </c>
       <c r="P678" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q678" s="4" t="s">
         <v>47</v>
@@ -45447,10 +45444,10 @@
         <v>24</v>
       </c>
       <c r="F679" s="9" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="G679" s="9" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="H679" s="10" t="n">
         <v>46164</v>
@@ -45473,7 +45470,7 @@
         <v>46164.630094676</v>
       </c>
       <c r="P679" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q679" s="9" t="s">
         <v>31</v>
@@ -45505,10 +45502,10 @@
         <v>24</v>
       </c>
       <c r="F680" s="4" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G680" s="4" t="s">
         <v>1498</v>
-      </c>
-      <c r="G680" s="4" t="s">
-        <v>1500</v>
       </c>
       <c r="H680" s="5" t="n">
         <v>46164</v>
@@ -45531,7 +45528,7 @@
         <v>46164.638035104</v>
       </c>
       <c r="P680" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q680" s="4" t="s">
         <v>31</v>
@@ -45566,7 +45563,7 @@
         <v>521</v>
       </c>
       <c r="G681" s="9" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="H681" s="10" t="n">
         <v>46164</v>
@@ -45589,7 +45586,7 @@
         <v>46164.672004826</v>
       </c>
       <c r="P681" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q681" s="9" t="s">
         <v>31</v>
@@ -45624,7 +45621,7 @@
         <v>619</v>
       </c>
       <c r="G682" s="4" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="H682" s="5" t="n">
         <v>46164</v>
@@ -45647,7 +45644,7 @@
         <v>46164.674161574</v>
       </c>
       <c r="P682" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q682" s="4" t="s">
         <v>31</v>
@@ -45679,10 +45676,10 @@
         <v>24</v>
       </c>
       <c r="F683" s="9" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="G683" s="9" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="H683" s="10" t="n">
         <v>46164</v>
@@ -45705,7 +45702,7 @@
         <v>46164.676046991</v>
       </c>
       <c r="P683" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q683" s="9" t="s">
         <v>31</v>
@@ -45740,7 +45737,7 @@
         <v>276</v>
       </c>
       <c r="G684" s="4" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="H684" s="5" t="n">
         <v>46164</v>
@@ -45763,7 +45760,7 @@
         <v>46164.677312002</v>
       </c>
       <c r="P684" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q684" s="4" t="s">
         <v>68</v>
@@ -45798,7 +45795,7 @@
         <v>1056</v>
       </c>
       <c r="G685" s="9" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="H685" s="10" t="n">
         <v>46164</v>
@@ -45821,7 +45818,7 @@
         <v>46164.678607176</v>
       </c>
       <c r="P685" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q685" s="9" t="s">
         <v>134</v>
@@ -45853,22 +45850,22 @@
         <v>24</v>
       </c>
       <c r="F686" s="4" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="G686" s="4" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="H686" s="5" t="n">
         <v>46164</v>
       </c>
       <c r="I686" s="4" t="s">
+        <v>1505</v>
+      </c>
+      <c r="J686" s="4" t="s">
         <v>1507</v>
       </c>
-      <c r="J686" s="4" t="s">
-        <v>1509</v>
-      </c>
       <c r="K686" s="4" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="L686" s="5"/>
       <c r="M686" s="5"/>
@@ -45879,7 +45876,7 @@
         <v>46164.679870336</v>
       </c>
       <c r="P686" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q686" s="4" t="s">
         <v>31</v>
@@ -45914,7 +45911,7 @@
         <v>124</v>
       </c>
       <c r="G687" s="9" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="H687" s="10" t="n">
         <v>46164</v>
@@ -45937,7 +45934,7 @@
         <v>46164.681622569</v>
       </c>
       <c r="P687" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q687" s="9" t="s">
         <v>31</v>
@@ -45972,7 +45969,7 @@
         <v>351</v>
       </c>
       <c r="G688" s="4" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="H688" s="5" t="n">
         <v>46164</v>
@@ -45995,7 +45992,7 @@
         <v>46164.683332211</v>
       </c>
       <c r="P688" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q688" s="4" t="s">
         <v>31</v>
@@ -46027,10 +46024,10 @@
         <v>24</v>
       </c>
       <c r="F689" s="9" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="G689" s="9" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="H689" s="10" t="n">
         <v>46167</v>
@@ -46053,7 +46050,7 @@
         <v>46167.595417396</v>
       </c>
       <c r="P689" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q689" s="9" t="s">
         <v>747</v>
@@ -46085,10 +46082,10 @@
         <v>24</v>
       </c>
       <c r="F690" s="4" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G690" s="4" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="H690" s="5" t="n">
         <v>46167</v>
@@ -46111,7 +46108,7 @@
         <v>46167.599102894</v>
       </c>
       <c r="P690" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q690" s="4" t="s">
         <v>31</v>
@@ -46146,7 +46143,7 @@
         <v>581</v>
       </c>
       <c r="G691" s="9" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="H691" s="10" t="n">
         <v>46167</v>
@@ -46169,7 +46166,7 @@
         <v>46167.601793021</v>
       </c>
       <c r="P691" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q691" s="9" t="s">
         <v>31</v>
@@ -46204,7 +46201,7 @@
         <v>1016</v>
       </c>
       <c r="G692" s="4" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="H692" s="5" t="n">
         <v>46167</v>
@@ -46227,7 +46224,7 @@
         <v>46167.614190127</v>
       </c>
       <c r="P692" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q692" s="4" t="s">
         <v>37</v>
@@ -46259,10 +46256,10 @@
         <v>24</v>
       </c>
       <c r="F693" s="9" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="G693" s="9" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="H693" s="10" t="n">
         <v>46167</v>
@@ -46285,7 +46282,7 @@
         <v>46167.616605984</v>
       </c>
       <c r="P693" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q693" s="9" t="s">
         <v>134</v>
@@ -46314,13 +46311,13 @@
         <v>23</v>
       </c>
       <c r="E694" s="3" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="F694" s="4" t="s">
         <v>75</v>
       </c>
       <c r="G694" s="4" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="H694" s="5" t="n">
         <v>46167</v>
@@ -46343,7 +46340,7 @@
         <v>46167.620332986</v>
       </c>
       <c r="P694" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q694" s="4" t="s">
         <v>31</v>
@@ -46378,7 +46375,7 @@
         <v>490</v>
       </c>
       <c r="G695" s="9" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="H695" s="10" t="n">
         <v>46168</v>
@@ -46401,7 +46398,7 @@
         <v>46168.376790544</v>
       </c>
       <c r="P695" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q695" s="9" t="s">
         <v>47</v>
@@ -46433,10 +46430,10 @@
         <v>24</v>
       </c>
       <c r="F696" s="4" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="G696" s="4" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="H696" s="5" t="n">
         <v>46168</v>
@@ -46459,7 +46456,7 @@
         <v>46168.593096181</v>
       </c>
       <c r="P696" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q696" s="4" t="s">
         <v>31</v>
@@ -46491,10 +46488,10 @@
         <v>24</v>
       </c>
       <c r="F697" s="9" t="s">
+        <v>1521</v>
+      </c>
+      <c r="G697" s="9" t="s">
         <v>1523</v>
-      </c>
-      <c r="G697" s="9" t="s">
-        <v>1525</v>
       </c>
       <c r="H697" s="10" t="n">
         <v>46168</v>
@@ -46517,7 +46514,7 @@
         <v>46168.594570174</v>
       </c>
       <c r="P697" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q697" s="9" t="s">
         <v>31</v>
@@ -46552,7 +46549,7 @@
         <v>502</v>
       </c>
       <c r="G698" s="4" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="H698" s="5" t="n">
         <v>46169</v>
@@ -46575,7 +46572,7 @@
         <v>46170.317637731</v>
       </c>
       <c r="P698" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q698" s="4" t="s">
         <v>1234</v>
@@ -46610,7 +46607,7 @@
         <v>75</v>
       </c>
       <c r="G699" s="9" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="H699" s="10" t="n">
         <v>46168</v>
@@ -46633,7 +46630,7 @@
         <v>46170.324846991</v>
       </c>
       <c r="P699" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q699" s="9" t="s">
         <v>31</v>
@@ -46668,7 +46665,7 @@
         <v>75</v>
       </c>
       <c r="G700" s="4" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="H700" s="5" t="n">
         <v>46168</v>
@@ -46691,7 +46688,7 @@
         <v>46170.326156447</v>
       </c>
       <c r="P700" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q700" s="4" t="s">
         <v>31</v>
@@ -46723,10 +46720,10 @@
         <v>24</v>
       </c>
       <c r="F701" s="9" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="G701" s="9" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="H701" s="10" t="n">
         <v>46167</v>
@@ -46749,7 +46746,7 @@
         <v>46170.329556829</v>
       </c>
       <c r="P701" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q701" s="9" t="s">
         <v>37</v>
@@ -46784,7 +46781,7 @@
         <v>988</v>
       </c>
       <c r="G702" s="4" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="H702" s="5" t="n">
         <v>46169</v>
@@ -46807,7 +46804,7 @@
         <v>46170.333476933</v>
       </c>
       <c r="P702" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q702" s="4" t="s">
         <v>74</v>
@@ -46842,7 +46839,7 @@
         <v>505</v>
       </c>
       <c r="G703" s="9" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="H703" s="10" t="n">
         <v>46168</v>
@@ -46865,7 +46862,7 @@
         <v>46170.335349653</v>
       </c>
       <c r="P703" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q703" s="9" t="s">
         <v>74</v>
@@ -46900,7 +46897,7 @@
         <v>592</v>
       </c>
       <c r="G704" s="4" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="H704" s="5" t="n">
         <v>46169</v>
@@ -46923,7 +46920,7 @@
         <v>46170.338192743</v>
       </c>
       <c r="P704" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q704" s="4" t="s">
         <v>47</v>
@@ -46958,7 +46955,7 @@
         <v>347</v>
       </c>
       <c r="G705" s="9" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="H705" s="10" t="n">
         <v>46168</v>
@@ -46981,7 +46978,7 @@
         <v>46170.340080984</v>
       </c>
       <c r="P705" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q705" s="9" t="s">
         <v>74</v>
@@ -47016,7 +47013,7 @@
         <v>671</v>
       </c>
       <c r="G706" s="4" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="H706" s="5" t="n">
         <v>46168</v>
@@ -47039,7 +47036,7 @@
         <v>46170.341493715</v>
       </c>
       <c r="P706" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q706" s="4" t="s">
         <v>31</v>
@@ -47074,7 +47071,7 @@
         <v>203</v>
       </c>
       <c r="G707" s="9" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="H707" s="10" t="n">
         <v>46168</v>
@@ -47097,7 +47094,7 @@
         <v>46170.346237002</v>
       </c>
       <c r="P707" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q707" s="9" t="s">
         <v>74</v>
@@ -47132,7 +47129,7 @@
         <v>262</v>
       </c>
       <c r="G708" s="4" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="H708" s="5" t="n">
         <v>46168</v>
@@ -47155,7 +47152,7 @@
         <v>46170.347851238</v>
       </c>
       <c r="P708" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q708" s="4" t="s">
         <v>31</v>
@@ -47190,7 +47187,7 @@
         <v>152</v>
       </c>
       <c r="G709" s="9" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="H709" s="10" t="n">
         <v>46167</v>
@@ -47213,7 +47210,7 @@
         <v>46170.34928912</v>
       </c>
       <c r="P709" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q709" s="9" t="s">
         <v>47</v>
@@ -47248,7 +47245,7 @@
         <v>58</v>
       </c>
       <c r="G710" s="4" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="H710" s="5" t="n">
         <v>46167</v>
@@ -47271,7 +47268,7 @@
         <v>46170.350719213</v>
       </c>
       <c r="P710" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q710" s="4" t="s">
         <v>47</v>
@@ -47306,7 +47303,7 @@
         <v>310</v>
       </c>
       <c r="G711" s="9" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="H711" s="10" t="n">
         <v>46167</v>
@@ -47329,7 +47326,7 @@
         <v>46170.351649456</v>
       </c>
       <c r="P711" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q711" s="9" t="s">
         <v>134</v>
@@ -47361,10 +47358,10 @@
         <v>24</v>
       </c>
       <c r="F712" s="4" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="G712" s="4" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H712" s="5" t="n">
         <v>46167</v>
@@ -47387,7 +47384,7 @@
         <v>46170.352928009</v>
       </c>
       <c r="P712" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q712" s="4" t="s">
         <v>474</v>
@@ -47422,7 +47419,7 @@
         <v>328</v>
       </c>
       <c r="G713" s="9" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="H713" s="10" t="n">
         <v>46167</v>
@@ -47445,7 +47442,7 @@
         <v>46170.354495255</v>
       </c>
       <c r="P713" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q713" s="9" t="s">
         <v>31</v>
@@ -47477,10 +47474,10 @@
         <v>24</v>
       </c>
       <c r="F714" s="4" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="G714" s="4" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="H714" s="5" t="n">
         <v>46168</v>
@@ -47503,7 +47500,7 @@
         <v>46171.347414236</v>
       </c>
       <c r="P714" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q714" s="4" t="s">
         <v>74</v>
@@ -47535,10 +47532,10 @@
         <v>24</v>
       </c>
       <c r="F715" s="9" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="G715" s="9" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="H715" s="10" t="n">
         <v>46169</v>
@@ -47561,7 +47558,7 @@
         <v>46171.351338692</v>
       </c>
       <c r="P715" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q715" s="9" t="s">
         <v>31</v>
@@ -47596,7 +47593,7 @@
         <v>675</v>
       </c>
       <c r="G716" s="4" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="H716" s="5" t="n">
         <v>46170</v>
@@ -47619,7 +47616,7 @@
         <v>46171.3540086</v>
       </c>
       <c r="P716" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q716" s="4" t="s">
         <v>134</v>
@@ -47651,10 +47648,10 @@
         <v>24</v>
       </c>
       <c r="F717" s="9" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="G717" s="9" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="H717" s="10" t="n">
         <v>46169</v>
@@ -47677,7 +47674,7 @@
         <v>46171.35535787</v>
       </c>
       <c r="P717" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q717" s="9" t="s">
         <v>31</v>
@@ -47712,7 +47709,7 @@
         <v>909</v>
       </c>
       <c r="G718" s="4" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="H718" s="5" t="n">
         <v>46170</v>
@@ -47735,7 +47732,7 @@
         <v>46171.357065544</v>
       </c>
       <c r="P718" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q718" s="4" t="s">
         <v>913</v>
@@ -47767,22 +47764,22 @@
         <v>24</v>
       </c>
       <c r="F719" s="9" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="G719" s="9" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="H719" s="10" t="n">
         <v>46174</v>
       </c>
       <c r="I719" s="9" t="s">
+        <v>1550</v>
+      </c>
+      <c r="J719" s="9" t="s">
         <v>1552</v>
       </c>
-      <c r="J719" s="9" t="s">
-        <v>1554</v>
-      </c>
       <c r="K719" s="9" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="L719" s="10"/>
       <c r="M719" s="10"/>
@@ -47793,7 +47790,7 @@
         <v>46174.329489502</v>
       </c>
       <c r="P719" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q719" s="9" t="s">
         <v>134</v>
@@ -47828,7 +47825,7 @@
         <v>969</v>
       </c>
       <c r="G720" s="4" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="H720" s="5" t="n">
         <v>46170</v>
@@ -47851,7 +47848,7 @@
         <v>46174.331686262</v>
       </c>
       <c r="P720" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q720" s="4" t="s">
         <v>134</v>
@@ -47883,22 +47880,22 @@
         <v>24</v>
       </c>
       <c r="F721" s="9" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G721" s="9" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="H721" s="10" t="n">
         <v>46169</v>
       </c>
       <c r="I721" s="9" t="s">
+        <v>1461</v>
+      </c>
+      <c r="J721" s="9" t="s">
         <v>1462</v>
       </c>
-      <c r="J721" s="9" t="s">
+      <c r="K721" s="9" t="s">
         <v>1463</v>
-      </c>
-      <c r="K721" s="9" t="s">
-        <v>1464</v>
       </c>
       <c r="L721" s="10"/>
       <c r="M721" s="10"/>
@@ -47909,7 +47906,7 @@
         <v>46174.338220984</v>
       </c>
       <c r="P721" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q721" s="9" t="s">
         <v>47</v>
@@ -47944,7 +47941,7 @@
         <v>820</v>
       </c>
       <c r="G722" s="4" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="H722" s="5" t="n">
         <v>46169</v>
@@ -47967,7 +47964,7 @@
         <v>46174.341687766</v>
       </c>
       <c r="P722" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q722" s="4" t="s">
         <v>74</v>
@@ -48002,7 +47999,7 @@
         <v>1012</v>
       </c>
       <c r="G723" s="9" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="H723" s="10" t="n">
         <v>46169</v>
@@ -48025,7 +48022,7 @@
         <v>46174.344054317</v>
       </c>
       <c r="P723" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q723" s="9" t="s">
         <v>142</v>
@@ -48057,22 +48054,22 @@
         <v>24</v>
       </c>
       <c r="F724" s="4" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="G724" s="4" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="H724" s="5" t="n">
         <v>46169</v>
       </c>
       <c r="I724" s="4" t="s">
+        <v>1560</v>
+      </c>
+      <c r="J724" s="4" t="s">
+        <v>1561</v>
+      </c>
+      <c r="K724" s="4" t="s">
         <v>1562</v>
-      </c>
-      <c r="J724" s="4" t="s">
-        <v>1563</v>
-      </c>
-      <c r="K724" s="4" t="s">
-        <v>1564</v>
       </c>
       <c r="L724" s="5"/>
       <c r="M724" s="5"/>
@@ -48083,7 +48080,7 @@
         <v>46174.350288889</v>
       </c>
       <c r="P724" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q724" s="4" t="s">
         <v>142</v>
@@ -48118,7 +48115,7 @@
         <v>1102</v>
       </c>
       <c r="G725" s="9" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="H725" s="10" t="n">
         <v>46170</v>
@@ -48141,7 +48138,7 @@
         <v>46174.352334606</v>
       </c>
       <c r="P725" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q725" s="9" t="s">
         <v>74</v>
@@ -48176,7 +48173,7 @@
         <v>592</v>
       </c>
       <c r="G726" s="4" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="H726" s="5" t="n">
         <v>46170</v>
@@ -48199,7 +48196,7 @@
         <v>46174.354713576</v>
       </c>
       <c r="P726" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q726" s="4" t="s">
         <v>47</v>
@@ -48234,7 +48231,7 @@
         <v>461</v>
       </c>
       <c r="G727" s="9" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="H727" s="10" t="n">
         <v>46170</v>
@@ -48257,7 +48254,7 @@
         <v>46174.356615278</v>
       </c>
       <c r="P727" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q727" s="9" t="s">
         <v>31</v>
@@ -48292,7 +48289,7 @@
         <v>1292</v>
       </c>
       <c r="G728" s="4" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="H728" s="5" t="n">
         <v>46171</v>
@@ -48315,7 +48312,7 @@
         <v>46175.31323272</v>
       </c>
       <c r="P728" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q728" s="4" t="s">
         <v>31</v>
@@ -48347,22 +48344,22 @@
         <v>24</v>
       </c>
       <c r="F729" s="9" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G729" s="9" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="H729" s="10" t="n">
         <v>46175</v>
       </c>
       <c r="I729" s="9" t="s">
+        <v>1461</v>
+      </c>
+      <c r="J729" s="9" t="s">
         <v>1462</v>
       </c>
-      <c r="J729" s="9" t="s">
+      <c r="K729" s="9" t="s">
         <v>1463</v>
-      </c>
-      <c r="K729" s="9" t="s">
-        <v>1464</v>
       </c>
       <c r="L729" s="10"/>
       <c r="M729" s="10"/>
@@ -48373,7 +48370,7 @@
         <v>46175.584908137</v>
       </c>
       <c r="P729" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q729" s="9" t="s">
         <v>47</v>
@@ -48408,7 +48405,7 @@
         <v>1062</v>
       </c>
       <c r="G730" s="4" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="H730" s="5" t="n">
         <v>46175</v>
@@ -48431,7 +48428,7 @@
         <v>46176.649429086</v>
       </c>
       <c r="P730" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q730" s="4" t="s">
         <v>74</v>
@@ -48466,7 +48463,7 @@
         <v>696</v>
       </c>
       <c r="G731" s="9" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="H731" s="10" t="n">
         <v>46175</v>
@@ -48489,7 +48486,7 @@
         <v>46176.652511308</v>
       </c>
       <c r="P731" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q731" s="9" t="s">
         <v>47</v>
@@ -48521,10 +48518,10 @@
         <v>24</v>
       </c>
       <c r="F732" s="4" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="G732" s="4" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="H732" s="5" t="n">
         <v>46176</v>
@@ -48547,7 +48544,7 @@
         <v>46177.701994792</v>
       </c>
       <c r="P732" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q732" s="4" t="s">
         <v>47</v>
@@ -48582,7 +48579,7 @@
         <v>103</v>
       </c>
       <c r="G733" s="9" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="H733" s="10" t="n">
         <v>46176</v>
@@ -48599,13 +48596,13 @@
       <c r="L733" s="10"/>
       <c r="M733" s="10"/>
       <c r="N733" s="9" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="O733" s="11" t="n">
         <v>46178.475498414</v>
       </c>
       <c r="P733" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q733" s="9" t="s">
         <v>47</v>
@@ -48637,10 +48634,10 @@
         <v>24</v>
       </c>
       <c r="F734" s="4" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="G734" s="4" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="H734" s="5" t="n">
         <v>46176</v>
@@ -48663,7 +48660,7 @@
         <v>46178.477565625</v>
       </c>
       <c r="P734" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q734" s="4" t="s">
         <v>47</v>
@@ -48695,10 +48692,10 @@
         <v>24</v>
       </c>
       <c r="F735" s="9" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="G735" s="9" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="H735" s="10" t="n">
         <v>46176</v>
@@ -48721,7 +48718,7 @@
         <v>46178.492351007</v>
       </c>
       <c r="P735" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q735" s="9" t="s">
         <v>47</v>
@@ -48756,7 +48753,7 @@
         <v>143</v>
       </c>
       <c r="G736" s="4" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H736" s="5" t="n">
         <v>46181</v>
@@ -48779,7 +48776,7 @@
         <v>46182.602910648</v>
       </c>
       <c r="P736" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q736" s="4" t="s">
         <v>74</v>
@@ -48814,7 +48811,7 @@
         <v>447</v>
       </c>
       <c r="G737" s="9" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="H737" s="10" t="n">
         <v>46182</v>
@@ -48837,7 +48834,7 @@
         <v>46182.605711655</v>
       </c>
       <c r="P737" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q737" s="9" t="s">
         <v>134</v>
@@ -48872,7 +48869,7 @@
         <v>143</v>
       </c>
       <c r="G738" s="4" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="H738" s="5" t="n">
         <v>46182</v>
@@ -48895,7 +48892,7 @@
         <v>46183.582611458</v>
       </c>
       <c r="P738" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q738" s="4" t="s">
         <v>74</v>
@@ -48927,10 +48924,10 @@
         <v>24</v>
       </c>
       <c r="F739" s="9" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="G739" s="9" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="H739" s="10" t="n">
         <v>46182</v>
@@ -48953,7 +48950,7 @@
         <v>46183.587275463</v>
       </c>
       <c r="P739" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q739" s="9" t="s">
         <v>31</v>
@@ -48985,22 +48982,22 @@
         <v>24</v>
       </c>
       <c r="F740" s="4" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="G740" s="4" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="H740" s="5" t="n">
         <v>46181</v>
       </c>
       <c r="I740" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="J740" s="4" t="s">
         <v>1424</v>
       </c>
-      <c r="J740" s="4" t="s">
+      <c r="K740" s="4" t="s">
         <v>1425</v>
-      </c>
-      <c r="K740" s="4" t="s">
-        <v>1426</v>
       </c>
       <c r="L740" s="5"/>
       <c r="M740" s="5"/>
@@ -49011,7 +49008,7 @@
         <v>46184.706767708</v>
       </c>
       <c r="P740" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q740" s="4" t="s">
         <v>1158</v>
@@ -49043,22 +49040,22 @@
         <v>24</v>
       </c>
       <c r="F741" s="9" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="G741" s="9" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="H741" s="10" t="n">
         <v>46183</v>
       </c>
       <c r="I741" s="9" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="J741" s="9" t="s">
+        <v>1453</v>
+      </c>
+      <c r="K741" s="9" t="s">
         <v>1454</v>
-      </c>
-      <c r="K741" s="9" t="s">
-        <v>1455</v>
       </c>
       <c r="L741" s="10"/>
       <c r="M741" s="10"/>
@@ -49069,7 +49066,7 @@
         <v>46185.32546956</v>
       </c>
       <c r="P741" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q741" s="9" t="s">
         <v>47</v>
@@ -49101,10 +49098,10 @@
         <v>24</v>
       </c>
       <c r="F742" s="4" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="G742" s="4" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="H742" s="5" t="n">
         <v>46184</v>
@@ -49127,7 +49124,7 @@
         <v>46185.328011227</v>
       </c>
       <c r="P742" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q742" s="4" t="s">
         <v>47</v>
@@ -49161,10 +49158,10 @@
         <v>24</v>
       </c>
       <c r="F743" s="9" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="G743" s="9" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="H743" s="10" t="n">
         <v>46183</v>
@@ -49187,7 +49184,7 @@
         <v>46185.331006285</v>
       </c>
       <c r="P743" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q743" s="9" t="s">
         <v>134</v>
@@ -49219,22 +49216,22 @@
         <v>24</v>
       </c>
       <c r="F744" s="4" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="G744" s="4" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="H744" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="I744" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="J744" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="K744" s="4" t="s">
         <v>1592</v>
-      </c>
-      <c r="J744" s="4" t="s">
-        <v>1593</v>
-      </c>
-      <c r="K744" s="4" t="s">
-        <v>1594</v>
       </c>
       <c r="L744" s="5"/>
       <c r="M744" s="5"/>
@@ -49245,7 +49242,7 @@
         <v>46185.47253669</v>
       </c>
       <c r="P744" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q744" s="4" t="s">
         <v>31</v>
@@ -49280,7 +49277,7 @@
         <v>272</v>
       </c>
       <c r="G745" s="9" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="H745" s="10" t="n">
         <v>46184</v>
@@ -49303,7 +49300,7 @@
         <v>46185.473653738</v>
       </c>
       <c r="P745" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q745" s="9" t="s">
         <v>134</v>
@@ -49338,7 +49335,7 @@
         <v>519</v>
       </c>
       <c r="G746" s="4" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="H746" s="5" t="n">
         <v>46184</v>
@@ -49361,7 +49358,7 @@
         <v>46185.474852928</v>
       </c>
       <c r="P746" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q746" s="4" t="s">
         <v>31</v>
@@ -49393,10 +49390,10 @@
         <v>24</v>
       </c>
       <c r="F747" s="9" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="G747" s="9" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="H747" s="10" t="n">
         <v>46185</v>
@@ -49419,7 +49416,7 @@
         <v>46188.60344934</v>
       </c>
       <c r="P747" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q747" s="9" t="s">
         <v>747</v>
@@ -49451,10 +49448,10 @@
         <v>24</v>
       </c>
       <c r="F748" s="4" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="G748" s="4" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="H748" s="5" t="n">
         <v>46185</v>
@@ -49477,7 +49474,7 @@
         <v>46188.608977199</v>
       </c>
       <c r="P748" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q748" s="4" t="s">
         <v>31</v>
@@ -49512,7 +49509,7 @@
         <v>704</v>
       </c>
       <c r="G749" s="9" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="H749" s="10" t="n">
         <v>46188</v>
@@ -49535,7 +49532,7 @@
         <v>46189.62425309</v>
       </c>
       <c r="P749" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q749" s="9" t="s">
         <v>47</v>
@@ -49567,10 +49564,10 @@
         <v>24</v>
       </c>
       <c r="F750" s="4" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="G750" s="4" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="H750" s="5" t="n">
         <v>46188</v>
@@ -49593,7 +49590,7 @@
         <v>46189.626049572</v>
       </c>
       <c r="P750" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q750" s="4" t="s">
         <v>747</v>
@@ -49628,7 +49625,7 @@
         <v>228</v>
       </c>
       <c r="G751" s="9" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="H751" s="10" t="n">
         <v>46188</v>
@@ -49651,7 +49648,7 @@
         <v>46189.629395752</v>
       </c>
       <c r="P751" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q751" s="9" t="s">
         <v>142</v>
@@ -49686,7 +49683,7 @@
         <v>228</v>
       </c>
       <c r="G752" s="4" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="H752" s="5" t="n">
         <v>46188</v>
@@ -49709,7 +49706,7 @@
         <v>46189.632741817</v>
       </c>
       <c r="P752" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q752" s="4" t="s">
         <v>142</v>
@@ -49744,7 +49741,7 @@
         <v>589</v>
       </c>
       <c r="G753" s="9" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="H753" s="10" t="n">
         <v>46189</v>
@@ -49767,7 +49764,7 @@
         <v>46189.634861921</v>
       </c>
       <c r="P753" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q753" s="9" t="s">
         <v>134</v>
@@ -49799,22 +49796,22 @@
         <v>24</v>
       </c>
       <c r="F754" s="4" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="G754" s="4" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="H754" s="5" t="n">
         <v>46188</v>
       </c>
       <c r="I754" s="4" t="s">
+        <v>1606</v>
+      </c>
+      <c r="J754" s="4" t="s">
+        <v>1607</v>
+      </c>
+      <c r="K754" s="4" t="s">
         <v>1608</v>
-      </c>
-      <c r="J754" s="4" t="s">
-        <v>1609</v>
-      </c>
-      <c r="K754" s="4" t="s">
-        <v>1610</v>
       </c>
       <c r="L754" s="5"/>
       <c r="M754" s="5"/>
@@ -49825,7 +49822,7 @@
         <v>46189.637001968</v>
       </c>
       <c r="P754" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q754" s="4" t="s">
         <v>142</v>
@@ -49860,7 +49857,7 @@
         <v>1298</v>
       </c>
       <c r="G755" s="9" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="H755" s="10" t="n">
         <v>46188</v>
@@ -49883,7 +49880,7 @@
         <v>46190.390420405</v>
       </c>
       <c r="P755" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q755" s="9" t="s">
         <v>142</v>
@@ -49918,7 +49915,7 @@
         <v>152</v>
       </c>
       <c r="G756" s="4" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="H756" s="5" t="n">
         <v>46189</v>
@@ -49941,7 +49938,7 @@
         <v>46190.626894363</v>
       </c>
       <c r="P756" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q756" s="4" t="s">
         <v>47</v>
@@ -49976,7 +49973,7 @@
         <v>1296</v>
       </c>
       <c r="G757" s="9" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="H757" s="10" t="n">
         <v>46189</v>
@@ -49999,7 +49996,7 @@
         <v>46190.628310764</v>
       </c>
       <c r="P757" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q757" s="9" t="s">
         <v>31</v>
@@ -50034,7 +50031,7 @@
         <v>1296</v>
       </c>
       <c r="G758" s="4" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="H758" s="5" t="n">
         <v>46189</v>
@@ -50057,7 +50054,7 @@
         <v>46190.632363808</v>
       </c>
       <c r="P758" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q758" s="4" t="s">
         <v>31</v>
@@ -50092,7 +50089,7 @@
         <v>402</v>
       </c>
       <c r="G759" s="9" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="H759" s="10" t="n">
         <v>46190</v>
@@ -50115,7 +50112,7 @@
         <v>46190.646078588</v>
       </c>
       <c r="P759" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q759" s="9" t="s">
         <v>47</v>
@@ -50147,22 +50144,22 @@
         <v>24</v>
       </c>
       <c r="F760" s="4" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="G760" s="4" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="H760" s="5" t="n">
         <v>46189</v>
       </c>
       <c r="I760" s="4" t="s">
+        <v>1616</v>
+      </c>
+      <c r="J760" s="4" t="s">
+        <v>1617</v>
+      </c>
+      <c r="K760" s="4" t="s">
         <v>1618</v>
-      </c>
-      <c r="J760" s="4" t="s">
-        <v>1619</v>
-      </c>
-      <c r="K760" s="4" t="s">
-        <v>1620</v>
       </c>
       <c r="L760" s="5"/>
       <c r="M760" s="5"/>
@@ -50173,10 +50170,10 @@
         <v>46191.463827164</v>
       </c>
       <c r="P760" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q760" s="4" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="R760" s="7" t="n">
         <v>2230.4</v>
@@ -50208,7 +50205,7 @@
         <v>157</v>
       </c>
       <c r="G761" s="9" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="H761" s="10" t="n">
         <v>46189</v>
@@ -50231,7 +50228,7 @@
         <v>46192.346937535</v>
       </c>
       <c r="P761" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q761" s="9" t="s">
         <v>134</v>
@@ -50263,22 +50260,22 @@
         <v>24</v>
       </c>
       <c r="F762" s="4" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="G762" s="4" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="H762" s="5" t="n">
         <v>46191</v>
       </c>
       <c r="I762" s="4" t="s">
+        <v>1623</v>
+      </c>
+      <c r="J762" s="4" t="s">
+        <v>1624</v>
+      </c>
+      <c r="K762" s="4" t="s">
         <v>1625</v>
-      </c>
-      <c r="J762" s="4" t="s">
-        <v>1626</v>
-      </c>
-      <c r="K762" s="4" t="s">
-        <v>1627</v>
       </c>
       <c r="L762" s="5"/>
       <c r="M762" s="5"/>
@@ -50289,7 +50286,7 @@
         <v>46192.353690312</v>
       </c>
       <c r="P762" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q762" s="4" t="s">
         <v>913</v>
@@ -50324,7 +50321,7 @@
         <v>892</v>
       </c>
       <c r="G763" s="9" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="H763" s="10" t="n">
         <v>46191</v>
@@ -50347,7 +50344,7 @@
         <v>46192.368715706</v>
       </c>
       <c r="P763" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q763" s="9" t="s">
         <v>31</v>
@@ -50382,7 +50379,7 @@
         <v>502</v>
       </c>
       <c r="G764" s="4" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="H764" s="5" t="n">
         <v>46190</v>
@@ -50405,7 +50402,7 @@
         <v>46192.370965162</v>
       </c>
       <c r="P764" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q764" s="4" t="s">
         <v>1234</v>
@@ -50440,7 +50437,7 @@
         <v>322</v>
       </c>
       <c r="G765" s="9" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="H765" s="10" t="n">
         <v>46190</v>
@@ -50463,7 +50460,7 @@
         <v>46192.374241169</v>
       </c>
       <c r="P765" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q765" s="9" t="s">
         <v>142</v>
@@ -50495,10 +50492,10 @@
         <v>24</v>
       </c>
       <c r="F766" s="4" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="G766" s="4" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="H766" s="5" t="n">
         <v>46192</v>
@@ -50521,7 +50518,7 @@
         <v>46195.351359225</v>
       </c>
       <c r="P766" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q766" s="4" t="s">
         <v>134</v>
@@ -50556,7 +50553,7 @@
         <v>249</v>
       </c>
       <c r="G767" s="9" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="H767" s="10" t="n">
         <v>46191</v>
@@ -50579,7 +50576,7 @@
         <v>46195.353954248</v>
       </c>
       <c r="P767" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q767" s="9" t="s">
         <v>74</v>
@@ -50611,10 +50608,10 @@
         <v>24</v>
       </c>
       <c r="F768" s="4" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="G768" s="4" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="H768" s="5" t="n">
         <v>46191</v>
@@ -50637,7 +50634,7 @@
         <v>46195.366646644</v>
       </c>
       <c r="P768" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q768" s="4" t="s">
         <v>31</v>
@@ -50669,10 +50666,10 @@
         <v>24</v>
       </c>
       <c r="F769" s="9" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="G769" s="9" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="H769" s="11" t="n">
         <v>46196.641111111</v>
@@ -50695,7 +50692,7 @@
         <v>46198.434918947</v>
       </c>
       <c r="P769" s="9" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="Q769" s="9" t="s">
         <v>74</v>
@@ -50730,7 +50727,7 @@
         <v>904</v>
       </c>
       <c r="G770" s="4" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="H770" s="5" t="n">
         <v>46195</v>
@@ -50753,7 +50750,7 @@
         <v>46198.448793519</v>
       </c>
       <c r="P770" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q770" s="4" t="s">
         <v>142</v>
@@ -50788,7 +50785,7 @@
         <v>888</v>
       </c>
       <c r="G771" s="9" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="H771" s="10" t="n">
         <v>46192</v>
@@ -50811,7 +50808,7 @@
         <v>46198.452410104</v>
       </c>
       <c r="P771" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q771" s="9" t="s">
         <v>747</v>
@@ -50840,13 +50837,13 @@
         <v>23</v>
       </c>
       <c r="E772" s="3" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="F772" s="4" t="s">
         <v>997</v>
       </c>
       <c r="G772" s="4" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="H772" s="5" t="n">
         <v>46198</v>
@@ -50869,7 +50866,7 @@
         <v>46198.454084525</v>
       </c>
       <c r="P772" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q772" s="4" t="s">
         <v>142</v>
@@ -50904,7 +50901,7 @@
         <v>276</v>
       </c>
       <c r="G773" s="9" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="H773" s="10" t="n">
         <v>46198</v>
@@ -50927,7 +50924,7 @@
         <v>46199.347961262</v>
       </c>
       <c r="P773" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q773" s="9" t="s">
         <v>31</v>
@@ -50956,13 +50953,13 @@
         <v>23</v>
       </c>
       <c r="E774" s="3" t="s">
+        <v>1641</v>
+      </c>
+      <c r="F774" s="4" t="s">
+        <v>1642</v>
+      </c>
+      <c r="G774" s="4" t="s">
         <v>1643</v>
-      </c>
-      <c r="F774" s="4" t="s">
-        <v>1644</v>
-      </c>
-      <c r="G774" s="4" t="s">
-        <v>1645</v>
       </c>
       <c r="H774" s="5" t="n">
         <v>46198</v>
@@ -50985,7 +50982,7 @@
         <v>46199.356272685</v>
       </c>
       <c r="P774" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q774" s="4" t="s">
         <v>68</v>
@@ -51020,7 +51017,7 @@
         <v>1271</v>
       </c>
       <c r="G775" s="9" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="H775" s="10" t="n">
         <v>46196</v>
@@ -51043,7 +51040,7 @@
         <v>46199.376881748</v>
       </c>
       <c r="P775" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q775" s="9" t="s">
         <v>37</v>
@@ -51078,7 +51075,7 @@
         <v>1264</v>
       </c>
       <c r="G776" s="4" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="H776" s="5" t="n">
         <v>46195</v>
@@ -51101,7 +51098,7 @@
         <v>46199.38206412</v>
       </c>
       <c r="P776" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q776" s="4" t="s">
         <v>74</v>
@@ -51136,7 +51133,7 @@
         <v>496</v>
       </c>
       <c r="G777" s="9" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="H777" s="10" t="n">
         <v>46198</v>
@@ -51159,7 +51156,7 @@
         <v>46202.328502049</v>
       </c>
       <c r="P777" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q777" s="9" t="s">
         <v>74</v>
@@ -51194,7 +51191,7 @@
         <v>1075</v>
       </c>
       <c r="G778" s="4" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="H778" s="5" t="n">
         <v>46198</v>
@@ -51217,7 +51214,7 @@
         <v>46202.330392593</v>
       </c>
       <c r="P778" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q778" s="4" t="s">
         <v>31</v>
@@ -51252,7 +51249,7 @@
         <v>945</v>
       </c>
       <c r="G779" s="9" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="H779" s="10" t="n">
         <v>46198</v>
@@ -51275,7 +51272,7 @@
         <v>46202.331869711</v>
       </c>
       <c r="P779" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q779" s="9" t="s">
         <v>31</v>
@@ -51307,22 +51304,22 @@
         <v>24</v>
       </c>
       <c r="F780" s="4" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G780" s="4" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="H780" s="5" t="n">
         <v>46198</v>
       </c>
       <c r="I780" s="4" t="s">
+        <v>1461</v>
+      </c>
+      <c r="J780" s="4" t="s">
         <v>1462</v>
       </c>
-      <c r="J780" s="4" t="s">
+      <c r="K780" s="4" t="s">
         <v>1463</v>
-      </c>
-      <c r="K780" s="4" t="s">
-        <v>1464</v>
       </c>
       <c r="L780" s="5"/>
       <c r="M780" s="5"/>
@@ -51333,7 +51330,7 @@
         <v>46202.334358333</v>
       </c>
       <c r="P780" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q780" s="4" t="s">
         <v>47</v>
@@ -51365,10 +51362,10 @@
         <v>24</v>
       </c>
       <c r="F781" s="9" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="G781" s="9" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="H781" s="10" t="n">
         <v>46198</v>
@@ -51391,7 +51388,7 @@
         <v>46202.336277234</v>
       </c>
       <c r="P781" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q781" s="9" t="s">
         <v>74</v>
@@ -51426,7 +51423,7 @@
         <v>191</v>
       </c>
       <c r="G782" s="4" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="H782" s="5" t="n">
         <v>46198</v>
@@ -51449,7 +51446,7 @@
         <v>46202.339326123</v>
       </c>
       <c r="P782" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q782" s="4" t="s">
         <v>31</v>
@@ -51478,13 +51475,13 @@
         <v>23</v>
       </c>
       <c r="E783" s="8" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F783" s="9" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G783" s="9" t="s">
         <v>1655</v>
-      </c>
-      <c r="F783" s="9" t="s">
-        <v>1656</v>
-      </c>
-      <c r="G783" s="9" t="s">
-        <v>1657</v>
       </c>
       <c r="H783" s="10" t="n">
         <v>46197</v>
@@ -51507,7 +51504,7 @@
         <v>46202.342017975</v>
       </c>
       <c r="P783" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q783" s="9" t="s">
         <v>142</v>
@@ -51542,7 +51539,7 @@
         <v>124</v>
       </c>
       <c r="G784" s="4" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="H784" s="5" t="n">
         <v>46198</v>
@@ -51565,7 +51562,7 @@
         <v>46202.343938194</v>
       </c>
       <c r="P784" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q784" s="4" t="s">
         <v>31</v>
@@ -51600,7 +51597,7 @@
         <v>75</v>
       </c>
       <c r="G785" s="9" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="H785" s="10" t="n">
         <v>46199</v>
@@ -51623,7 +51620,7 @@
         <v>46202.474389039</v>
       </c>
       <c r="P785" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q785" s="9" t="s">
         <v>31</v>
@@ -51658,7 +51655,7 @@
         <v>332</v>
       </c>
       <c r="G786" s="4" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="H786" s="5" t="n">
         <v>46199</v>
@@ -51681,7 +51678,7 @@
         <v>46202.531873067</v>
       </c>
       <c r="P786" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q786" s="4" t="s">
         <v>31</v>
@@ -51713,10 +51710,10 @@
         <v>24</v>
       </c>
       <c r="F787" s="9" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G787" s="9" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="H787" s="11" t="n">
         <v>46202.697662037</v>
@@ -51739,7 +51736,7 @@
         <v>46203.433667593</v>
       </c>
       <c r="P787" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q787" s="9" t="s">
         <v>31</v>
@@ -51774,7 +51771,7 @@
         <v>249</v>
       </c>
       <c r="G788" s="4" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="H788" s="6" t="n">
         <v>46203.350740741</v>
@@ -51797,7 +51794,7 @@
         <v>46203.434054016</v>
       </c>
       <c r="P788" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q788" s="4" t="s">
         <v>74</v>
@@ -51832,7 +51829,7 @@
         <v>1102</v>
       </c>
       <c r="G789" s="9" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="H789" s="11" t="n">
         <v>46203.360023148</v>
@@ -51855,7 +51852,7 @@
         <v>46203.434466007</v>
       </c>
       <c r="P789" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q789" s="9" t="s">
         <v>74</v>
@@ -51890,7 +51887,7 @@
         <v>295</v>
       </c>
       <c r="G790" s="4" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="H790" s="6" t="n">
         <v>46199.437291667</v>
@@ -51913,7 +51910,7 @@
         <v>46203.434983565</v>
       </c>
       <c r="P790" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q790" s="4" t="s">
         <v>31</v>
@@ -51948,7 +51945,7 @@
         <v>262</v>
       </c>
       <c r="G791" s="9" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="H791" s="11" t="n">
         <v>46199.61</v>
@@ -51971,7 +51968,7 @@
         <v>46203.435316435</v>
       </c>
       <c r="P791" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q791" s="9" t="s">
         <v>31</v>
@@ -52006,7 +52003,7 @@
         <v>58</v>
       </c>
       <c r="G792" s="4" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="H792" s="5" t="n">
         <v>46203</v>
@@ -52029,7 +52026,7 @@
         <v>46203.435921991</v>
       </c>
       <c r="P792" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q792" s="4" t="s">
         <v>47</v>
@@ -52064,7 +52061,7 @@
         <v>1099</v>
       </c>
       <c r="G793" s="9" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="H793" s="10" t="n">
         <v>46199</v>
@@ -52087,7 +52084,7 @@
         <v>46203.437449456</v>
       </c>
       <c r="P793" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q793" s="9" t="s">
         <v>37</v>
@@ -52119,10 +52116,10 @@
         <v>24</v>
       </c>
       <c r="F794" s="4" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="G794" s="4" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="H794" s="5" t="n">
         <v>46203</v>
@@ -52145,7 +52142,7 @@
         <v>46205.382749456</v>
       </c>
       <c r="P794" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q794" s="4" t="s">
         <v>134</v>
@@ -52177,10 +52174,10 @@
         <v>24</v>
       </c>
       <c r="F795" s="9" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="G795" s="9" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="H795" s="11" t="n">
         <v>46203.499918981</v>
@@ -52203,7 +52200,7 @@
         <v>46205.385711806</v>
       </c>
       <c r="P795" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q795" s="9" t="s">
         <v>31</v>
@@ -52238,7 +52235,7 @@
         <v>357</v>
       </c>
       <c r="G796" s="4" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="H796" s="5" t="n">
         <v>46203</v>
@@ -52261,7 +52258,7 @@
         <v>46205.391037234</v>
       </c>
       <c r="P796" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q796" s="4" t="s">
         <v>134</v>
@@ -52296,7 +52293,7 @@
         <v>955</v>
       </c>
       <c r="G797" s="9" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="H797" s="11" t="n">
         <v>46204.462268519</v>
@@ -52319,7 +52316,7 @@
         <v>46205.393357326</v>
       </c>
       <c r="P797" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q797" s="9" t="s">
         <v>37</v>
@@ -52348,13 +52345,13 @@
         <v>23</v>
       </c>
       <c r="E798" s="3" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F798" s="4" t="s">
         <v>1298</v>
       </c>
       <c r="G798" s="4" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="H798" s="5" t="n">
         <v>46205</v>
@@ -52377,7 +52374,7 @@
         <v>46205.617754861</v>
       </c>
       <c r="P798" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q798" s="4" t="s">
         <v>142</v>
@@ -52409,22 +52406,22 @@
         <v>24</v>
       </c>
       <c r="F799" s="9" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="G799" s="9" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="H799" s="10" t="n">
         <v>46205</v>
       </c>
       <c r="I799" s="9" t="s">
+        <v>1616</v>
+      </c>
+      <c r="J799" s="9" t="s">
+        <v>1617</v>
+      </c>
+      <c r="K799" s="9" t="s">
         <v>1618</v>
-      </c>
-      <c r="J799" s="9" t="s">
-        <v>1619</v>
-      </c>
-      <c r="K799" s="9" t="s">
-        <v>1620</v>
       </c>
       <c r="L799" s="10"/>
       <c r="M799" s="10"/>
@@ -52435,10 +52432,10 @@
         <v>46205.678818519</v>
       </c>
       <c r="P799" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q799" s="9" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="R799" s="12" t="n">
         <v>5000</v>
@@ -52467,22 +52464,22 @@
         <v>24</v>
       </c>
       <c r="F800" s="4" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="G800" s="4" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="H800" s="6" t="n">
         <v>46205.688020833</v>
       </c>
       <c r="I800" s="4" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="J800" s="4" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="K800" s="4" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="L800" s="5"/>
       <c r="M800" s="5"/>
@@ -52493,7 +52490,7 @@
         <v>46206.558645486</v>
       </c>
       <c r="P800" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q800" s="4" t="s">
         <v>47</v>
@@ -52525,22 +52522,22 @@
         <v>24</v>
       </c>
       <c r="F801" s="9" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="G801" s="9" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="H801" s="11" t="n">
         <v>46205.676435185</v>
       </c>
       <c r="I801" s="9" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J801" s="9" t="s">
         <v>1430</v>
       </c>
-      <c r="J801" s="9" t="s">
+      <c r="K801" s="9" t="s">
         <v>1431</v>
-      </c>
-      <c r="K801" s="9" t="s">
-        <v>1432</v>
       </c>
       <c r="L801" s="10"/>
       <c r="M801" s="10"/>
@@ -52551,7 +52548,7 @@
         <v>46206.55882338</v>
       </c>
       <c r="P801" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q801" s="9" t="s">
         <v>47</v>
@@ -52583,10 +52580,10 @@
         <v>24</v>
       </c>
       <c r="F802" s="4" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="G802" s="4" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="H802" s="5" t="n">
         <v>46206</v>
@@ -52609,7 +52606,7 @@
         <v>46209.623041354</v>
       </c>
       <c r="P802" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q802" s="4" t="s">
         <v>47</v>
@@ -52641,10 +52638,10 @@
         <v>24</v>
       </c>
       <c r="F803" s="9" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="G803" s="9" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="H803" s="10" t="n">
         <v>46206</v>
@@ -52667,7 +52664,7 @@
         <v>46209.624799225</v>
       </c>
       <c r="P803" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q803" s="9" t="s">
         <v>47</v>
@@ -52702,7 +52699,7 @@
         <v>366</v>
       </c>
       <c r="G804" s="4" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="H804" s="5" t="n">
         <v>46209</v>
@@ -52725,7 +52722,7 @@
         <v>46211.346130637</v>
       </c>
       <c r="P804" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q804" s="4" t="s">
         <v>134</v>
@@ -52760,7 +52757,7 @@
         <v>829</v>
       </c>
       <c r="G805" s="9" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="H805" s="11" t="n">
         <v>46210.393460648</v>
@@ -52783,7 +52780,7 @@
         <v>46211.347523762</v>
       </c>
       <c r="P805" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q805" s="9" t="s">
         <v>142</v>
@@ -52815,10 +52812,10 @@
         <v>24</v>
       </c>
       <c r="F806" s="4" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="G806" s="4" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="H806" s="5" t="n">
         <v>46210</v>
@@ -52841,7 +52838,7 @@
         <v>46211.600125579</v>
       </c>
       <c r="P806" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q806" s="4" t="s">
         <v>47</v>
@@ -52870,25 +52867,25 @@
         <v>23</v>
       </c>
       <c r="E807" s="8" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F807" s="9" t="s">
+        <v>1687</v>
+      </c>
+      <c r="G807" s="9" t="s">
         <v>1688</v>
-      </c>
-      <c r="F807" s="9" t="s">
-        <v>1689</v>
-      </c>
-      <c r="G807" s="9" t="s">
-        <v>1690</v>
       </c>
       <c r="H807" s="10" t="n">
         <v>46209</v>
       </c>
       <c r="I807" s="9" t="s">
+        <v>1689</v>
+      </c>
+      <c r="J807" s="9" t="s">
+        <v>1690</v>
+      </c>
+      <c r="K807" s="9" t="s">
         <v>1691</v>
-      </c>
-      <c r="J807" s="9" t="s">
-        <v>1692</v>
-      </c>
-      <c r="K807" s="9" t="s">
-        <v>1693</v>
       </c>
       <c r="L807" s="10"/>
       <c r="M807" s="10"/>
@@ -52899,10 +52896,10 @@
         <v>46212.601001123</v>
       </c>
       <c r="P807" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q807" s="9" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="R807" s="12" t="n">
         <v>57832.4</v>
@@ -52911,7 +52908,7 @@
         <v>44782.4</v>
       </c>
       <c r="T807" s="9" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="U807" s="9"/>
       <c r="V807" s="9"/>
@@ -52931,10 +52928,10 @@
         <v>24</v>
       </c>
       <c r="F808" s="4" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="G808" s="4" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="H808" s="5" t="n">
         <v>46212</v>
@@ -52957,7 +52954,7 @@
         <v>46216.331953704</v>
       </c>
       <c r="P808" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q808" s="4" t="s">
         <v>134</v>
@@ -52989,22 +52986,22 @@
         <v>24</v>
       </c>
       <c r="F809" s="9" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="G809" s="9" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="H809" s="10" t="n">
         <v>46209</v>
       </c>
       <c r="I809" s="9" t="s">
+        <v>1695</v>
+      </c>
+      <c r="J809" s="9" t="s">
         <v>1697</v>
       </c>
-      <c r="J809" s="9" t="s">
-        <v>1699</v>
-      </c>
       <c r="K809" s="9" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="L809" s="10"/>
       <c r="M809" s="10"/>
@@ -53015,10 +53012,10 @@
         <v>46216.335014549</v>
       </c>
       <c r="P809" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q809" s="9" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="R809" s="12" t="n">
         <v>12246.14</v>
@@ -53027,7 +53024,7 @@
         <v>12246.14</v>
       </c>
       <c r="T809" s="9" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="U809" s="9"/>
       <c r="V809" s="9"/>
@@ -53047,22 +53044,22 @@
         <v>24</v>
       </c>
       <c r="F810" s="4" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="G810" s="4" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="H810" s="5" t="n">
         <v>46209</v>
       </c>
       <c r="I810" s="4" t="s">
+        <v>1701</v>
+      </c>
+      <c r="J810" s="4" t="s">
+        <v>1702</v>
+      </c>
+      <c r="K810" s="4" t="s">
         <v>1703</v>
-      </c>
-      <c r="J810" s="4" t="s">
-        <v>1704</v>
-      </c>
-      <c r="K810" s="4" t="s">
-        <v>1705</v>
       </c>
       <c r="L810" s="5"/>
       <c r="M810" s="5"/>
@@ -53073,10 +53070,10 @@
         <v>46216.348499687</v>
       </c>
       <c r="P810" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q810" s="4" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="R810" s="7" t="n">
         <v>12246.14</v>
@@ -53085,7 +53082,7 @@
         <v>12246.14</v>
       </c>
       <c r="T810" s="4" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="U810" s="4"/>
       <c r="V810" s="4"/>
@@ -53105,22 +53102,22 @@
         <v>24</v>
       </c>
       <c r="F811" s="9" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="G811" s="9" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="H811" s="10" t="n">
         <v>46212</v>
       </c>
       <c r="I811" s="9" t="s">
+        <v>1706</v>
+      </c>
+      <c r="J811" s="9" t="s">
+        <v>1707</v>
+      </c>
+      <c r="K811" s="9" t="s">
         <v>1708</v>
-      </c>
-      <c r="J811" s="9" t="s">
-        <v>1709</v>
-      </c>
-      <c r="K811" s="9" t="s">
-        <v>1710</v>
       </c>
       <c r="L811" s="10"/>
       <c r="M811" s="10"/>
@@ -53131,10 +53128,10 @@
         <v>46216.352796065</v>
       </c>
       <c r="P811" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q811" s="9" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="R811" s="12" t="n">
         <v>46556.88</v>
@@ -53143,7 +53140,7 @@
         <v>46556.88</v>
       </c>
       <c r="T811" s="9" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="U811" s="9"/>
       <c r="V811" s="9"/>
@@ -53163,10 +53160,10 @@
         <v>24</v>
       </c>
       <c r="F812" s="4" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="G812" s="4" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="H812" s="6" t="n">
         <v>46212.609872685</v>
@@ -53189,7 +53186,7 @@
         <v>46216.402183252</v>
       </c>
       <c r="P812" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q812" s="4" t="s">
         <v>31</v>
@@ -53221,10 +53218,10 @@
         <v>24</v>
       </c>
       <c r="F813" s="9" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="G813" s="9" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="H813" s="11" t="n">
         <v>46212.603854167</v>
@@ -53247,7 +53244,7 @@
         <v>46216.403755752</v>
       </c>
       <c r="P813" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q813" s="9" t="s">
         <v>31</v>
@@ -53282,7 +53279,7 @@
         <v>328</v>
       </c>
       <c r="G814" s="4" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="H814" s="6" t="n">
         <v>46212.706458333</v>
@@ -53305,7 +53302,7 @@
         <v>46216.404863773</v>
       </c>
       <c r="P814" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q814" s="4" t="s">
         <v>31</v>
@@ -53340,7 +53337,7 @@
         <v>75</v>
       </c>
       <c r="G815" s="9" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="H815" s="11" t="n">
         <v>46216.38931713</v>
@@ -53363,7 +53360,7 @@
         <v>46217.339997303</v>
       </c>
       <c r="P815" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q815" s="9" t="s">
         <v>31</v>
@@ -53398,7 +53395,7 @@
         <v>389</v>
       </c>
       <c r="G816" s="4" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="H816" s="6" t="n">
         <v>46213.494444444</v>
@@ -53421,7 +53418,7 @@
         <v>46217.340197257</v>
       </c>
       <c r="P816" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q816" s="4" t="s">
         <v>31</v>
@@ -53456,7 +53453,7 @@
         <v>249</v>
       </c>
       <c r="G817" s="9" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="H817" s="11" t="n">
         <v>46216.315104167</v>
@@ -53479,7 +53476,7 @@
         <v>46217.34034853</v>
       </c>
       <c r="P817" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q817" s="9" t="s">
         <v>74</v>
@@ -53511,10 +53508,10 @@
         <v>24</v>
       </c>
       <c r="F818" s="4" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="G818" s="4" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="H818" s="6" t="n">
         <v>46216.636458333</v>
@@ -53537,7 +53534,7 @@
         <v>46217.663376042</v>
       </c>
       <c r="P818" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q818" s="4" t="s">
         <v>31</v>
@@ -53569,10 +53566,10 @@
         <v>24</v>
       </c>
       <c r="F819" s="9" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="G819" s="9" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="H819" s="11" t="n">
         <v>46216.752118056</v>
@@ -53595,7 +53592,7 @@
         <v>46218.335123958</v>
       </c>
       <c r="P819" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q819" s="9" t="s">
         <v>31</v>
@@ -53630,7 +53627,7 @@
         <v>164</v>
       </c>
       <c r="G820" s="4" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="H820" s="6" t="n">
         <v>46216.772175926</v>
@@ -53653,7 +53650,7 @@
         <v>46218.335351736</v>
       </c>
       <c r="P820" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q820" s="4" t="s">
         <v>47</v>
@@ -53685,10 +53682,10 @@
         <v>24</v>
       </c>
       <c r="F821" s="9" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="G821" s="9" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="H821" s="10" t="n">
         <v>46217</v>
@@ -53711,7 +53708,7 @@
         <v>46218.336172257</v>
       </c>
       <c r="P821" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q821" s="9" t="s">
         <v>134</v>
@@ -53743,10 +53740,10 @@
         <v>24</v>
       </c>
       <c r="F822" s="4" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="G822" s="4" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="H822" s="6" t="n">
         <v>46217.426458333</v>
@@ -53769,7 +53766,7 @@
         <v>46219.374058368</v>
       </c>
       <c r="P822" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q822" s="4" t="s">
         <v>31</v>
@@ -53801,10 +53798,10 @@
         <v>24</v>
       </c>
       <c r="F823" s="9" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="G823" s="9" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="H823" s="10" t="n">
         <v>46217</v>
@@ -53827,7 +53824,7 @@
         <v>46219.37489309</v>
       </c>
       <c r="P823" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q823" s="9" t="s">
         <v>134</v>
@@ -53859,10 +53856,10 @@
         <v>24</v>
       </c>
       <c r="F824" s="4" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="G824" s="4" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="H824" s="5" t="n">
         <v>46219</v>
@@ -53885,7 +53882,7 @@
         <v>46219.485821296</v>
       </c>
       <c r="P824" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q824" s="4" t="s">
         <v>68</v>
@@ -53917,10 +53914,10 @@
         <v>24</v>
       </c>
       <c r="F825" s="9" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="G825" s="9" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="H825" s="10" t="n">
         <v>46219</v>
@@ -53943,7 +53940,7 @@
         <v>46219.573011921</v>
       </c>
       <c r="P825" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q825" s="9" t="s">
         <v>474</v>
@@ -53975,10 +53972,10 @@
         <v>24</v>
       </c>
       <c r="F826" s="4" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="G826" s="4" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="H826" s="5" t="n">
         <v>46219</v>
@@ -54001,7 +53998,7 @@
         <v>46219.578629896</v>
       </c>
       <c r="P826" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q826" s="4" t="s">
         <v>474</v>
@@ -54036,7 +54033,7 @@
         <v>332</v>
       </c>
       <c r="G827" s="9" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="H827" s="11" t="n">
         <v>46218.657847222</v>
@@ -54059,7 +54056,7 @@
         <v>46219.581437072</v>
       </c>
       <c r="P827" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q827" s="9" t="s">
         <v>31</v>
@@ -54091,10 +54088,10 @@
         <v>24</v>
       </c>
       <c r="F828" s="4" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="G828" s="4" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="H828" s="6" t="n">
         <v>46218.558854167</v>
@@ -54117,7 +54114,7 @@
         <v>46219.582433252</v>
       </c>
       <c r="P828" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q828" s="4" t="s">
         <v>1158</v>
@@ -54152,7 +54149,7 @@
         <v>484</v>
       </c>
       <c r="G829" s="9" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="H829" s="11" t="n">
         <v>46218.501886574</v>
@@ -54175,7 +54172,7 @@
         <v>46219.587382442</v>
       </c>
       <c r="P829" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q829" s="9" t="s">
         <v>31</v>
@@ -54204,13 +54201,13 @@
         <v>23</v>
       </c>
       <c r="E830" s="3" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="F830" s="4" t="s">
         <v>1264</v>
       </c>
       <c r="G830" s="4" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="H830" s="5" t="n">
         <v>46219</v>
@@ -54233,7 +54230,7 @@
         <v>46219.675766285</v>
       </c>
       <c r="P830" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q830" s="4" t="s">
         <v>74</v>
@@ -54268,7 +54265,7 @@
         <v>310</v>
       </c>
       <c r="G831" s="9" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="H831" s="10" t="n">
         <v>46219</v>
@@ -54291,7 +54288,7 @@
         <v>46223.33606316</v>
       </c>
       <c r="P831" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q831" s="9" t="s">
         <v>134</v>
@@ -54326,7 +54323,7 @@
         <v>969</v>
       </c>
       <c r="G832" s="4" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="H832" s="5" t="n">
         <v>46219</v>
@@ -54349,7 +54346,7 @@
         <v>46223.337611771</v>
       </c>
       <c r="P832" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q832" s="4" t="s">
         <v>134</v>
@@ -54381,22 +54378,22 @@
         <v>24</v>
       </c>
       <c r="F833" s="9" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="G833" s="9" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="H833" s="11" t="n">
         <v>46219.727233796</v>
       </c>
       <c r="I833" s="9" t="s">
+        <v>1737</v>
+      </c>
+      <c r="J833" s="9" t="s">
+        <v>1738</v>
+      </c>
+      <c r="K833" s="9" t="s">
         <v>1739</v>
-      </c>
-      <c r="J833" s="9" t="s">
-        <v>1740</v>
-      </c>
-      <c r="K833" s="9" t="s">
-        <v>1741</v>
       </c>
       <c r="L833" s="10"/>
       <c r="M833" s="10"/>
@@ -54407,7 +54404,7 @@
         <v>46223.340685683</v>
       </c>
       <c r="P833" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q833" s="9" t="s">
         <v>31</v>
@@ -54439,22 +54436,22 @@
         <v>24</v>
       </c>
       <c r="F834" s="4" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="G834" s="4" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="H834" s="5" t="n">
         <v>46220</v>
       </c>
       <c r="I834" s="4" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="J834" s="4" t="s">
+        <v>1330</v>
+      </c>
+      <c r="K834" s="4" t="s">
         <v>1331</v>
-      </c>
-      <c r="K834" s="4" t="s">
-        <v>1332</v>
       </c>
       <c r="L834" s="5"/>
       <c r="M834" s="5"/>
@@ -54465,7 +54462,7 @@
         <v>46224.377425313</v>
       </c>
       <c r="P834" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q834" s="4" t="s">
         <v>747</v>
@@ -54497,10 +54494,10 @@
         <v>24</v>
       </c>
       <c r="F835" s="9" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="G835" s="9" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="H835" s="10" t="n">
         <v>46223</v>
@@ -54523,7 +54520,7 @@
         <v>46224.382978241</v>
       </c>
       <c r="P835" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q835" s="9" t="s">
         <v>37</v>
@@ -54555,10 +54552,10 @@
         <v>24</v>
       </c>
       <c r="F836" s="4" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="G836" s="4" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="H836" s="5" t="n">
         <v>46224</v>
@@ -54581,7 +54578,7 @@
         <v>46225.461194792</v>
       </c>
       <c r="P836" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q836" s="4" t="s">
         <v>68</v>
@@ -54613,10 +54610,10 @@
         <v>24</v>
       </c>
       <c r="F837" s="9" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="G837" s="9" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="H837" s="10" t="n">
         <v>46225</v>
@@ -54639,7 +54636,7 @@
         <v>46225.704363924</v>
       </c>
       <c r="P837" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q837" s="9" t="s">
         <v>747</v>
@@ -54674,7 +54671,7 @@
         <v>1264</v>
       </c>
       <c r="G838" s="4" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="H838" s="5" t="n">
         <v>46224</v>
@@ -54697,7 +54694,7 @@
         <v>46226.328184606</v>
       </c>
       <c r="P838" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q838" s="4" t="s">
         <v>74</v>
@@ -54732,7 +54729,7 @@
         <v>203</v>
       </c>
       <c r="G839" s="9" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="H839" s="10" t="n">
         <v>46224</v>
@@ -54755,7 +54752,7 @@
         <v>46226.334652975</v>
       </c>
       <c r="P839" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q839" s="9" t="s">
         <v>74</v>
@@ -54790,7 +54787,7 @@
         <v>310</v>
       </c>
       <c r="G840" s="4" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="H840" s="5" t="n">
         <v>46224</v>
@@ -54813,7 +54810,7 @@
         <v>46226.339257789</v>
       </c>
       <c r="P840" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q840" s="4" t="s">
         <v>134</v>
@@ -54845,10 +54842,10 @@
         <v>24</v>
       </c>
       <c r="F841" s="9" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="G841" s="9" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="H841" s="10" t="n">
         <v>46224</v>
@@ -54871,7 +54868,7 @@
         <v>46226.341217442</v>
       </c>
       <c r="P841" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q841" s="9" t="s">
         <v>134</v>
@@ -54903,10 +54900,10 @@
         <v>24</v>
       </c>
       <c r="F842" s="4" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="G842" s="4" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="H842" s="5" t="n">
         <v>46224</v>
@@ -54929,7 +54926,7 @@
         <v>46226.404616667</v>
       </c>
       <c r="P842" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q842" s="4" t="s">
         <v>142</v>
@@ -54961,10 +54958,10 @@
         <v>24</v>
       </c>
       <c r="F843" s="9" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="G843" s="9" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="H843" s="10" t="n">
         <v>46224</v>
@@ -54987,7 +54984,7 @@
         <v>46226.406921447</v>
       </c>
       <c r="P843" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q843" s="9" t="s">
         <v>142</v>
@@ -55019,10 +55016,10 @@
         <v>24</v>
       </c>
       <c r="F844" s="4" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="G844" s="4" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="H844" s="5" t="n">
         <v>46225</v>
@@ -55045,7 +55042,7 @@
         <v>46226.655716748</v>
       </c>
       <c r="P844" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q844" s="4" t="s">
         <v>31</v>
@@ -55077,22 +55074,22 @@
         <v>24</v>
       </c>
       <c r="F845" s="9" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="G845" s="9" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="H845" s="10" t="n">
         <v>46225</v>
       </c>
       <c r="I845" s="9" t="s">
+        <v>1757</v>
+      </c>
+      <c r="J845" s="9" t="s">
         <v>1759</v>
       </c>
-      <c r="J845" s="9" t="s">
-        <v>1761</v>
-      </c>
       <c r="K845" s="9" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="L845" s="10"/>
       <c r="M845" s="10"/>
@@ -55103,7 +55100,7 @@
         <v>46226.658852465</v>
       </c>
       <c r="P845" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q845" s="9" t="s">
         <v>47</v>
@@ -55135,22 +55132,22 @@
         <v>24</v>
       </c>
       <c r="F846" s="4" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="G846" s="4" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="H846" s="5" t="n">
         <v>46226</v>
       </c>
       <c r="I846" s="4" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="J846" s="4" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="K846" s="4" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="L846" s="5"/>
       <c r="M846" s="5"/>
@@ -55161,7 +55158,7 @@
         <v>46226.67444309</v>
       </c>
       <c r="P846" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q846" s="4" t="s">
         <v>134</v>
@@ -55196,7 +55193,7 @@
         <v>592</v>
       </c>
       <c r="G847" s="9" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="H847" s="10" t="n">
         <v>46226</v>
@@ -55219,7 +55216,7 @@
         <v>46230.339660648</v>
       </c>
       <c r="P847" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q847" s="9" t="s">
         <v>47</v>
@@ -55254,7 +55251,7 @@
         <v>1179</v>
       </c>
       <c r="G848" s="4" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="H848" s="5" t="n">
         <v>46227</v>
@@ -55277,7 +55274,7 @@
         <v>46230.341659178</v>
       </c>
       <c r="P848" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q848" s="4" t="s">
         <v>1158</v>
@@ -55312,7 +55309,7 @@
         <v>623</v>
       </c>
       <c r="G849" s="9" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="H849" s="10" t="n">
         <v>46225</v>
@@ -55335,7 +55332,7 @@
         <v>46230.347240081</v>
       </c>
       <c r="P849" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q849" s="9" t="s">
         <v>31</v>
@@ -55370,7 +55367,7 @@
         <v>310</v>
       </c>
       <c r="G850" s="4" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="H850" s="5" t="n">
         <v>46226</v>
@@ -55393,7 +55390,7 @@
         <v>46230.353483947</v>
       </c>
       <c r="P850" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q850" s="4" t="s">
         <v>134</v>
@@ -55425,10 +55422,10 @@
         <v>24</v>
       </c>
       <c r="F851" s="9" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="G851" s="9" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="H851" s="10" t="n">
         <v>46225</v>
@@ -55451,7 +55448,7 @@
         <v>46230.356930174</v>
       </c>
       <c r="P851" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q851" s="9" t="s">
         <v>747</v>
@@ -55486,7 +55483,7 @@
         <v>581</v>
       </c>
       <c r="G852" s="4" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="H852" s="5" t="n">
         <v>46224</v>
@@ -55509,7 +55506,7 @@
         <v>46230.375244792</v>
       </c>
       <c r="P852" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q852" s="4" t="s">
         <v>31</v>
@@ -55541,10 +55538,10 @@
         <v>24</v>
       </c>
       <c r="F853" s="9" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="G853" s="9" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="H853" s="10" t="n">
         <v>46230</v>
@@ -55567,7 +55564,7 @@
         <v>46230.663143785</v>
       </c>
       <c r="P853" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q853" s="9" t="s">
         <v>134</v>
@@ -55599,22 +55596,22 @@
         <v>24</v>
       </c>
       <c r="F854" s="4" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="G854" s="4" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="H854" s="5" t="n">
         <v>46227</v>
       </c>
       <c r="I854" s="4" t="s">
+        <v>1772</v>
+      </c>
+      <c r="J854" s="4" t="s">
         <v>1774</v>
       </c>
-      <c r="J854" s="4" t="s">
-        <v>1776</v>
-      </c>
       <c r="K854" s="4" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="L854" s="5"/>
       <c r="M854" s="5"/>
@@ -55625,7 +55622,7 @@
         <v>46230.665892211</v>
       </c>
       <c r="P854" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q854" s="4" t="s">
         <v>747</v>
@@ -55654,25 +55651,25 @@
         <v>23</v>
       </c>
       <c r="E855" s="8" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F855" s="9" t="s">
+        <v>1777</v>
+      </c>
+      <c r="G855" s="9" t="s">
         <v>1778</v>
-      </c>
-      <c r="F855" s="9" t="s">
-        <v>1779</v>
-      </c>
-      <c r="G855" s="9" t="s">
-        <v>1780</v>
       </c>
       <c r="H855" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I855" s="9" t="s">
+        <v>1777</v>
+      </c>
+      <c r="J855" s="9" t="s">
         <v>1779</v>
       </c>
-      <c r="J855" s="9" t="s">
-        <v>1781</v>
-      </c>
       <c r="K855" s="9" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="L855" s="10"/>
       <c r="M855" s="10"/>
@@ -55683,10 +55680,10 @@
         <v>46231.629427465</v>
       </c>
       <c r="P855" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q855" s="9" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="R855" s="12" t="n">
         <v>176352</v>
@@ -55718,7 +55715,7 @@
         <v>276</v>
       </c>
       <c r="G856" s="4" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="H856" s="5" t="n">
         <v>46230</v>
@@ -55741,7 +55738,7 @@
         <v>46232.365431516</v>
       </c>
       <c r="P856" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q856" s="4" t="s">
         <v>31</v>
@@ -55776,7 +55773,7 @@
         <v>1280</v>
       </c>
       <c r="G857" s="9" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="H857" s="10" t="n">
         <v>46231</v>
@@ -55799,7 +55796,7 @@
         <v>46232.37670934</v>
       </c>
       <c r="P857" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q857" s="9" t="s">
         <v>47</v>
@@ -55834,7 +55831,7 @@
         <v>592</v>
       </c>
       <c r="G858" s="4" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="H858" s="5" t="n">
         <v>46230</v>
@@ -55857,7 +55854,7 @@
         <v>46232.379035069</v>
       </c>
       <c r="P858" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q858" s="4" t="s">
         <v>47</v>
@@ -55892,7 +55889,7 @@
         <v>1264</v>
       </c>
       <c r="G859" s="9" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="H859" s="10" t="n">
         <v>46231</v>
@@ -55915,7 +55912,7 @@
         <v>46232.382735336</v>
       </c>
       <c r="P859" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q859" s="9" t="s">
         <v>74</v>
@@ -55947,10 +55944,10 @@
         <v>24</v>
       </c>
       <c r="F860" s="4" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="G860" s="4" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="H860" s="5" t="n">
         <v>46230</v>
@@ -55973,7 +55970,7 @@
         <v>46232.394575081</v>
       </c>
       <c r="P860" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q860" s="4" t="s">
         <v>31</v>
@@ -56002,25 +55999,25 @@
         <v>23</v>
       </c>
       <c r="E861" s="8" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F861" s="9" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G861" s="9" t="s">
         <v>1789</v>
-      </c>
-      <c r="F861" s="9" t="s">
-        <v>1790</v>
-      </c>
-      <c r="G861" s="9" t="s">
-        <v>1791</v>
       </c>
       <c r="H861" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I861" s="9" t="s">
+        <v>1790</v>
+      </c>
+      <c r="J861" s="9" t="s">
+        <v>1791</v>
+      </c>
+      <c r="K861" s="9" t="s">
         <v>1792</v>
-      </c>
-      <c r="J861" s="9" t="s">
-        <v>1793</v>
-      </c>
-      <c r="K861" s="9" t="s">
-        <v>1794</v>
       </c>
       <c r="L861" s="10"/>
       <c r="M861" s="10"/>
@@ -56031,10 +56028,10 @@
         <v>46232.396937037</v>
       </c>
       <c r="P861" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q861" s="9" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="R861" s="12" t="n">
         <v>39463.12</v>
@@ -56043,7 +56040,7 @@
         <v>16215.2</v>
       </c>
       <c r="T861" s="9" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="U861" s="9"/>
       <c r="V861" s="9"/>
@@ -56063,22 +56060,22 @@
         <v>24</v>
       </c>
       <c r="F862" s="4" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="G862" s="4" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="H862" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="I862" s="4" t="s">
+        <v>1793</v>
+      </c>
+      <c r="J862" s="4" t="s">
         <v>1795</v>
       </c>
-      <c r="J862" s="4" t="s">
-        <v>1797</v>
-      </c>
       <c r="K862" s="4" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="L862" s="5"/>
       <c r="M862" s="5"/>
@@ -56089,7 +56086,7 @@
         <v>46232.405220521</v>
       </c>
       <c r="P862" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q862" s="4" t="s">
         <v>1158</v>
@@ -56124,7 +56121,7 @@
         <v>859</v>
       </c>
       <c r="G863" s="9" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="H863" s="10" t="n">
         <v>46230</v>
@@ -56147,7 +56144,7 @@
         <v>46232.407563194</v>
       </c>
       <c r="P863" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q863" s="9" t="s">
         <v>31</v>
@@ -56182,7 +56179,7 @@
         <v>262</v>
       </c>
       <c r="G864" s="4" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="H864" s="5" t="n">
         <v>46230</v>
@@ -56205,7 +56202,7 @@
         <v>46232.409892789</v>
       </c>
       <c r="P864" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q864" s="4" t="s">
         <v>31</v>
@@ -56237,22 +56234,22 @@
         <v>24</v>
       </c>
       <c r="F865" s="9" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="G865" s="9" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="H865" s="10" t="n">
         <v>46230</v>
       </c>
       <c r="I865" s="9" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="J865" s="9" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="K865" s="9" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="L865" s="10"/>
       <c r="M865" s="10"/>
@@ -56263,7 +56260,7 @@
         <v>46232.411495914</v>
       </c>
       <c r="P865" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q865" s="9" t="s">
         <v>134</v>
@@ -56298,7 +56295,7 @@
         <v>490</v>
       </c>
       <c r="G866" s="4" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="H866" s="5" t="n">
         <v>46231</v>
@@ -56321,7 +56318,7 @@
         <v>46232.457877465</v>
       </c>
       <c r="P866" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q866" s="4" t="s">
         <v>47</v>
@@ -56356,7 +56353,7 @@
         <v>521</v>
       </c>
       <c r="G867" s="9" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="H867" s="10" t="n">
         <v>46232</v>
@@ -56379,7 +56376,7 @@
         <v>46233.652091435</v>
       </c>
       <c r="P867" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q867" s="9" t="s">
         <v>31</v>
@@ -56411,10 +56408,10 @@
         <v>24</v>
       </c>
       <c r="F868" s="4" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="G868" s="4" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="H868" s="5" t="n">
         <v>46231</v>
@@ -56437,7 +56434,7 @@
         <v>46233.653612153</v>
       </c>
       <c r="P868" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q868" s="4" t="s">
         <v>31</v>
@@ -56472,7 +56469,7 @@
         <v>1133</v>
       </c>
       <c r="G869" s="9" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="H869" s="10" t="n">
         <v>46233</v>
@@ -56495,7 +56492,7 @@
         <v>46233.656732905</v>
       </c>
       <c r="P869" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q869" s="9" t="s">
         <v>37</v>
@@ -56527,10 +56524,10 @@
         <v>24</v>
       </c>
       <c r="F870" s="4" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="G870" s="4" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="H870" s="5" t="n">
         <v>46232</v>
@@ -56553,7 +56550,7 @@
         <v>46233.658307292</v>
       </c>
       <c r="P870" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q870" s="4" t="s">
         <v>31</v>
@@ -56588,7 +56585,7 @@
         <v>355</v>
       </c>
       <c r="G871" s="9" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="H871" s="10" t="n">
         <v>46232</v>
@@ -56611,7 +56608,7 @@
         <v>46233.660123229</v>
       </c>
       <c r="P871" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q871" s="9" t="s">
         <v>134</v>
@@ -56646,7 +56643,7 @@
         <v>351</v>
       </c>
       <c r="G872" s="4" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="H872" s="5" t="n">
         <v>46232</v>
@@ -56669,7 +56666,7 @@
         <v>46233.661470567</v>
       </c>
       <c r="P872" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q872" s="4" t="s">
         <v>31</v>
@@ -56704,7 +56701,7 @@
         <v>945</v>
       </c>
       <c r="G873" s="9" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="H873" s="10" t="n">
         <v>46232</v>
@@ -56727,7 +56724,7 @@
         <v>46233.66313897</v>
       </c>
       <c r="P873" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q873" s="9" t="s">
         <v>31</v>
@@ -56762,7 +56759,7 @@
         <v>262</v>
       </c>
       <c r="G874" s="4" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="H874" s="5" t="n">
         <v>46231</v>
@@ -56785,7 +56782,7 @@
         <v>46233.666216817</v>
       </c>
       <c r="P874" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q874" s="4" t="s">
         <v>31</v>
@@ -56820,7 +56817,7 @@
         <v>1264</v>
       </c>
       <c r="G875" s="9" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="H875" s="10" t="n">
         <v>46232</v>
@@ -56843,7 +56840,7 @@
         <v>46233.668326042</v>
       </c>
       <c r="P875" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q875" s="9" t="s">
         <v>74</v>
@@ -56872,13 +56869,13 @@
         <v>23</v>
       </c>
       <c r="E876" s="3" t="s">
+        <v>1814</v>
+      </c>
+      <c r="F876" s="4" t="s">
+        <v>1815</v>
+      </c>
+      <c r="G876" s="4" t="s">
         <v>1816</v>
-      </c>
-      <c r="F876" s="4" t="s">
-        <v>1817</v>
-      </c>
-      <c r="G876" s="4" t="s">
-        <v>1818</v>
       </c>
       <c r="H876" s="5" t="n">
         <v>46232</v>
@@ -56901,7 +56898,7 @@
         <v>46233.672459873</v>
       </c>
       <c r="P876" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q876" s="4" t="s">
         <v>74</v>
@@ -56936,7 +56933,7 @@
         <v>75</v>
       </c>
       <c r="G877" s="9" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="H877" s="10" t="n">
         <v>46232</v>
@@ -56959,7 +56956,7 @@
         <v>46233.673794873</v>
       </c>
       <c r="P877" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q877" s="9" t="s">
         <v>31</v>
@@ -56994,7 +56991,7 @@
         <v>408</v>
       </c>
       <c r="G878" s="4" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="H878" s="5" t="n">
         <v>46232</v>
@@ -57011,13 +57008,13 @@
       <c r="L878" s="5"/>
       <c r="M878" s="5"/>
       <c r="N878" s="4" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="O878" s="6" t="n">
         <v>46233.675736539</v>
       </c>
       <c r="P878" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q878" s="4" t="s">
         <v>31</v>
@@ -57049,10 +57046,10 @@
         <v>24</v>
       </c>
       <c r="F879" s="9" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G879" s="9" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="H879" s="10" t="n">
         <v>46232</v>
@@ -57075,7 +57072,7 @@
         <v>46233.677147419</v>
       </c>
       <c r="P879" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q879" s="9" t="s">
         <v>31</v>
@@ -57107,22 +57104,22 @@
         <v>24</v>
       </c>
       <c r="F880" s="4" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="G880" s="4" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="H880" s="5" t="n">
         <v>46233</v>
       </c>
       <c r="I880" s="4" t="s">
+        <v>1822</v>
+      </c>
+      <c r="J880" s="4" t="s">
+        <v>1823</v>
+      </c>
+      <c r="K880" s="4" t="s">
         <v>1824</v>
-      </c>
-      <c r="J880" s="4" t="s">
-        <v>1825</v>
-      </c>
-      <c r="K880" s="4" t="s">
-        <v>1826</v>
       </c>
       <c r="L880" s="5"/>
       <c r="M880" s="5"/>
@@ -57133,7 +57130,7 @@
         <v>46234.349953044</v>
       </c>
       <c r="P880" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q880" s="4" t="s">
         <v>747</v>
@@ -57168,7 +57165,7 @@
         <v>276</v>
       </c>
       <c r="G881" s="9" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="H881" s="10" t="n">
         <v>46234</v>
@@ -57191,7 +57188,7 @@
         <v>46234.504198461</v>
       </c>
       <c r="P881" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q881" s="9" t="s">
         <v>31</v>
@@ -57226,7 +57223,7 @@
         <v>1298</v>
       </c>
       <c r="G882" s="4" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="H882" s="5" t="n">
         <v>46233</v>
@@ -57249,7 +57246,7 @@
         <v>46237.439774109</v>
       </c>
       <c r="P882" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q882" s="4" t="s">
         <v>142</v>
@@ -57281,10 +57278,10 @@
         <v>24</v>
       </c>
       <c r="F883" s="9" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="G883" s="9" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="H883" s="10" t="n">
         <v>46234</v>
@@ -57307,7 +57304,7 @@
         <v>46237.444415822</v>
       </c>
       <c r="P883" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q883" s="9" t="s">
         <v>47</v>
@@ -57336,13 +57333,13 @@
         <v>23</v>
       </c>
       <c r="E884" s="3" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="F884" s="4" t="s">
         <v>888</v>
       </c>
       <c r="G884" s="4" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="H884" s="5" t="n">
         <v>46234</v>
@@ -57365,7 +57362,7 @@
         <v>46237.450804167</v>
       </c>
       <c r="P884" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q884" s="4" t="s">
         <v>747</v>
@@ -57397,10 +57394,10 @@
         <v>24</v>
       </c>
       <c r="F885" s="9" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="G885" s="9" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="H885" s="10" t="n">
         <v>46234</v>
@@ -57423,7 +57420,7 @@
         <v>46237.453498843</v>
       </c>
       <c r="P885" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q885" s="9" t="s">
         <v>31</v>
@@ -57455,10 +57452,10 @@
         <v>24</v>
       </c>
       <c r="F886" s="4" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="G886" s="4" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="H886" s="5" t="n">
         <v>46234</v>
@@ -57481,7 +57478,7 @@
         <v>46237.455918553</v>
       </c>
       <c r="P886" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q886" s="4" t="s">
         <v>74</v>
@@ -57513,22 +57510,22 @@
         <v>24</v>
       </c>
       <c r="F887" s="9" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="G887" s="9" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="H887" s="10" t="n">
         <v>46233</v>
       </c>
       <c r="I887" s="9" t="s">
+        <v>1606</v>
+      </c>
+      <c r="J887" s="9" t="s">
+        <v>1607</v>
+      </c>
+      <c r="K887" s="9" t="s">
         <v>1608</v>
-      </c>
-      <c r="J887" s="9" t="s">
-        <v>1609</v>
-      </c>
-      <c r="K887" s="9" t="s">
-        <v>1610</v>
       </c>
       <c r="L887" s="10"/>
       <c r="M887" s="10"/>
@@ -57539,7 +57536,7 @@
         <v>46237.457760648</v>
       </c>
       <c r="P887" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q887" s="9" t="s">
         <v>142</v>
@@ -57571,22 +57568,22 @@
         <v>24</v>
       </c>
       <c r="F888" s="4" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="G888" s="4" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="H888" s="5" t="n">
         <v>46234</v>
       </c>
       <c r="I888" s="4" t="s">
+        <v>1737</v>
+      </c>
+      <c r="J888" s="4" t="s">
+        <v>1738</v>
+      </c>
+      <c r="K888" s="4" t="s">
         <v>1739</v>
-      </c>
-      <c r="J888" s="4" t="s">
-        <v>1740</v>
-      </c>
-      <c r="K888" s="4" t="s">
-        <v>1741</v>
       </c>
       <c r="L888" s="5"/>
       <c r="M888" s="5"/>
@@ -57597,7 +57594,7 @@
         <v>46237.460359178</v>
       </c>
       <c r="P888" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q888" s="4" t="s">
         <v>31</v>
@@ -57632,7 +57629,7 @@
         <v>143</v>
       </c>
       <c r="G889" s="9" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="H889" s="10" t="n">
         <v>46238</v>
@@ -57655,7 +57652,7 @@
         <v>46240.69323044</v>
       </c>
       <c r="P889" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q889" s="9" t="s">
         <v>74</v>
@@ -57690,7 +57687,7 @@
         <v>402</v>
       </c>
       <c r="G890" s="4" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="H890" s="5" t="n">
         <v>46238</v>
@@ -57713,7 +57710,7 @@
         <v>46240.695117627</v>
       </c>
       <c r="P890" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q890" s="4" t="s">
         <v>47</v>
@@ -57748,7 +57745,7 @@
         <v>698</v>
       </c>
       <c r="G891" s="9" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="H891" s="10" t="n">
         <v>46238</v>
@@ -57771,7 +57768,7 @@
         <v>46240.69812191</v>
       </c>
       <c r="P891" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q891" s="9" t="s">
         <v>47</v>
@@ -57806,7 +57803,7 @@
         <v>328</v>
       </c>
       <c r="G892" s="4" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="H892" s="5" t="n">
         <v>46238</v>
@@ -57829,7 +57826,7 @@
         <v>46240.702751539</v>
       </c>
       <c r="P892" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q892" s="4" t="s">
         <v>31</v>
@@ -57864,7 +57861,7 @@
         <v>1264</v>
       </c>
       <c r="G893" s="9" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="H893" s="10" t="n">
         <v>46240</v>
@@ -57887,7 +57884,7 @@
         <v>46240.705916053</v>
       </c>
       <c r="P893" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q893" s="9" t="s">
         <v>74</v>
@@ -57922,7 +57919,7 @@
         <v>203</v>
       </c>
       <c r="G894" s="4" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="H894" s="5" t="n">
         <v>46240</v>
@@ -57945,7 +57942,7 @@
         <v>46244.33139294</v>
       </c>
       <c r="P894" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q894" s="4" t="s">
         <v>74</v>
@@ -57980,7 +57977,7 @@
         <v>829</v>
       </c>
       <c r="G895" s="9" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="H895" s="10" t="n">
         <v>46240</v>
@@ -58003,7 +58000,7 @@
         <v>46244.333240625</v>
       </c>
       <c r="P895" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q895" s="9" t="s">
         <v>142</v>
@@ -58035,22 +58032,22 @@
         <v>24</v>
       </c>
       <c r="F896" s="4" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="G896" s="4" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="H896" s="5" t="n">
         <v>46240</v>
       </c>
       <c r="I896" s="4" t="s">
+        <v>1843</v>
+      </c>
+      <c r="J896" s="4" t="s">
+        <v>1844</v>
+      </c>
+      <c r="K896" s="4" t="s">
         <v>1845</v>
-      </c>
-      <c r="J896" s="4" t="s">
-        <v>1846</v>
-      </c>
-      <c r="K896" s="4" t="s">
-        <v>1847</v>
       </c>
       <c r="L896" s="5"/>
       <c r="M896" s="5"/>
@@ -58061,7 +58058,7 @@
         <v>46244.335539086</v>
       </c>
       <c r="P896" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q896" s="4" t="s">
         <v>31</v>
@@ -58073,7 +58070,7 @@
         <v>7411.2</v>
       </c>
       <c r="T896" s="4" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="U896" s="4"/>
       <c r="V896" s="4"/>
@@ -58093,22 +58090,22 @@
         <v>24</v>
       </c>
       <c r="F897" s="9" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="G897" s="9" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="H897" s="10" t="n">
         <v>46240</v>
       </c>
       <c r="I897" s="9" t="s">
+        <v>1843</v>
+      </c>
+      <c r="J897" s="9" t="s">
+        <v>1844</v>
+      </c>
+      <c r="K897" s="9" t="s">
         <v>1845</v>
-      </c>
-      <c r="J897" s="9" t="s">
-        <v>1846</v>
-      </c>
-      <c r="K897" s="9" t="s">
-        <v>1847</v>
       </c>
       <c r="L897" s="10"/>
       <c r="M897" s="10"/>
@@ -58119,7 +58116,7 @@
         <v>46244.338932292</v>
       </c>
       <c r="P897" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q897" s="9" t="s">
         <v>31</v>
@@ -58131,7 +58128,7 @@
         <v>6860.4</v>
       </c>
       <c r="T897" s="9" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="U897" s="9"/>
       <c r="V897" s="9"/>
@@ -58154,7 +58151,7 @@
         <v>75</v>
       </c>
       <c r="G898" s="4" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="H898" s="5" t="n">
         <v>46241</v>
@@ -58177,7 +58174,7 @@
         <v>46244.34290066</v>
       </c>
       <c r="P898" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q898" s="4" t="s">
         <v>31</v>
@@ -58212,7 +58209,7 @@
         <v>1056</v>
       </c>
       <c r="G899" s="9" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="H899" s="10" t="n">
         <v>46244</v>
@@ -58235,7 +58232,7 @@
         <v>46244.653839468</v>
       </c>
       <c r="P899" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q899" s="9" t="s">
         <v>134</v>
@@ -58267,10 +58264,10 @@
         <v>24</v>
       </c>
       <c r="F900" s="4" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="G900" s="4" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="H900" s="5" t="n">
         <v>46244</v>
@@ -58293,7 +58290,7 @@
         <v>46245.341406134</v>
       </c>
       <c r="P900" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q900" s="4" t="s">
         <v>134</v>
@@ -58328,7 +58325,7 @@
         <v>1264</v>
       </c>
       <c r="G901" s="9" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="H901" s="11" t="n">
         <v>46244.693715278</v>
@@ -58351,7 +58348,7 @@
         <v>46245.708180093</v>
       </c>
       <c r="P901" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q901" s="9" t="s">
         <v>74</v>
@@ -58386,7 +58383,7 @@
         <v>904</v>
       </c>
       <c r="G902" s="4" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="H902" s="6" t="n">
         <v>46244.646689815</v>
@@ -58409,7 +58406,7 @@
         <v>46246.342438542</v>
       </c>
       <c r="P902" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q902" s="4" t="s">
         <v>142</v>
@@ -58441,22 +58438,22 @@
         <v>24</v>
       </c>
       <c r="F903" s="9" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="G903" s="9" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="H903" s="11" t="n">
         <v>46244.891539352</v>
       </c>
       <c r="I903" s="9" t="s">
+        <v>1853</v>
+      </c>
+      <c r="J903" s="9" t="s">
         <v>1855</v>
       </c>
-      <c r="J903" s="9" t="s">
-        <v>1857</v>
-      </c>
       <c r="K903" s="9" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="L903" s="10"/>
       <c r="M903" s="10"/>
@@ -58467,7 +58464,7 @@
         <v>46246.342689815</v>
       </c>
       <c r="P903" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q903" s="9" t="s">
         <v>74</v>
@@ -58502,7 +58499,7 @@
         <v>592</v>
       </c>
       <c r="G904" s="4" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="H904" s="6" t="n">
         <v>46244.846145833</v>
@@ -58525,7 +58522,7 @@
         <v>46246.342835995</v>
       </c>
       <c r="P904" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q904" s="4" t="s">
         <v>47</v>
@@ -58560,7 +58557,7 @@
         <v>75</v>
       </c>
       <c r="G905" s="9" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="H905" s="11" t="n">
         <v>46244.704305556</v>
@@ -58583,7 +58580,7 @@
         <v>46246.342990046</v>
       </c>
       <c r="P905" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q905" s="9" t="s">
         <v>31</v>
@@ -58618,7 +58615,7 @@
         <v>58</v>
       </c>
       <c r="G906" s="4" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="H906" s="6" t="n">
         <v>46245.52099537</v>
@@ -58641,7 +58638,7 @@
         <v>46246.415708102</v>
       </c>
       <c r="P906" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q906" s="4" t="s">
         <v>47</v>
@@ -58676,7 +58673,7 @@
         <v>152</v>
       </c>
       <c r="G907" s="9" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="H907" s="11" t="n">
         <v>46245.60755787</v>
@@ -58699,7 +58696,7 @@
         <v>46246.415864271</v>
       </c>
       <c r="P907" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q907" s="9" t="s">
         <v>47</v>
@@ -58734,7 +58731,7 @@
         <v>295</v>
       </c>
       <c r="G908" s="4" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="H908" s="6" t="n">
         <v>46245.672013889</v>
@@ -58757,7 +58754,7 @@
         <v>46246.418621875</v>
       </c>
       <c r="P908" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q908" s="4" t="s">
         <v>31</v>
@@ -58792,7 +58789,7 @@
         <v>249</v>
       </c>
       <c r="G909" s="9" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="H909" s="10" t="n">
         <v>46247</v>
@@ -58815,7 +58812,7 @@
         <v>46248.402886111</v>
       </c>
       <c r="P909" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q909" s="9" t="s">
         <v>74</v>
@@ -58850,7 +58847,7 @@
         <v>249</v>
       </c>
       <c r="G910" s="4" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="H910" s="6" t="n">
         <v>46247.371365741</v>
@@ -58873,7 +58870,7 @@
         <v>46248.404624456</v>
       </c>
       <c r="P910" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q910" s="4" t="s">
         <v>74</v>
@@ -58908,7 +58905,7 @@
         <v>988</v>
       </c>
       <c r="G911" s="9" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="H911" s="11" t="n">
         <v>46247.461736111</v>
@@ -58931,7 +58928,7 @@
         <v>46248.406403391</v>
       </c>
       <c r="P911" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q911" s="9" t="s">
         <v>74</v>
@@ -58963,22 +58960,22 @@
         <v>24</v>
       </c>
       <c r="F912" s="4" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="G912" s="4" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="H912" s="6" t="n">
         <v>46246.935729167</v>
       </c>
       <c r="I912" s="4" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="J912" s="4" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="K912" s="4" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="L912" s="5"/>
       <c r="M912" s="5"/>
@@ -58989,7 +58986,7 @@
         <v>46248.406544294</v>
       </c>
       <c r="P912" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q912" s="4" t="s">
         <v>47</v>
@@ -59018,25 +59015,25 @@
         <v>23</v>
       </c>
       <c r="E913" s="8" t="s">
+        <v>1866</v>
+      </c>
+      <c r="F913" s="9" t="s">
+        <v>1867</v>
+      </c>
+      <c r="G913" s="9" t="s">
         <v>1868</v>
-      </c>
-      <c r="F913" s="9" t="s">
-        <v>1869</v>
-      </c>
-      <c r="G913" s="9" t="s">
-        <v>1870</v>
       </c>
       <c r="H913" s="11" t="n">
         <v>46246.852106481</v>
       </c>
       <c r="I913" s="9" t="s">
+        <v>1867</v>
+      </c>
+      <c r="J913" s="9" t="s">
         <v>1869</v>
       </c>
-      <c r="J913" s="9" t="s">
-        <v>1871</v>
-      </c>
       <c r="K913" s="9" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="L913" s="10"/>
       <c r="M913" s="10"/>
@@ -59047,7 +59044,7 @@
         <v>46248.406686076</v>
       </c>
       <c r="P913" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q913" s="9" t="s">
         <v>1095</v>
@@ -59082,7 +59079,7 @@
         <v>332</v>
       </c>
       <c r="G914" s="4" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="H914" s="6" t="n">
         <v>46246.467384259</v>
@@ -59105,7 +59102,7 @@
         <v>46248.406833877</v>
       </c>
       <c r="P914" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q914" s="4" t="s">
         <v>31</v>
@@ -59140,7 +59137,7 @@
         <v>328</v>
       </c>
       <c r="G915" s="9" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="H915" s="11" t="n">
         <v>46247.693402778</v>
@@ -59163,7 +59160,7 @@
         <v>46248.407092593</v>
       </c>
       <c r="P915" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q915" s="9" t="s">
         <v>31</v>
@@ -59195,22 +59192,22 @@
         <v>24</v>
       </c>
       <c r="F916" s="4" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="G916" s="4" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="H916" s="6" t="n">
         <v>46247.72962963</v>
       </c>
       <c r="I916" s="4" t="s">
+        <v>1505</v>
+      </c>
+      <c r="J916" s="4" t="s">
         <v>1507</v>
       </c>
-      <c r="J916" s="4" t="s">
-        <v>1509</v>
-      </c>
       <c r="K916" s="4" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="L916" s="5"/>
       <c r="M916" s="5"/>
@@ -59221,7 +59218,7 @@
         <v>46248.40725316</v>
       </c>
       <c r="P916" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q916" s="4" t="s">
         <v>31</v>
@@ -59253,10 +59250,10 @@
         <v>24</v>
       </c>
       <c r="F917" s="9" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="G917" s="9" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="H917" s="11" t="n">
         <v>46247.621585648</v>
@@ -59279,7 +59276,7 @@
         <v>46248.407440046</v>
       </c>
       <c r="P917" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q917" s="9" t="s">
         <v>31</v>
@@ -59314,7 +59311,7 @@
         <v>75</v>
       </c>
       <c r="G918" s="4" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="H918" s="6" t="n">
         <v>46248.419988426</v>
@@ -59337,7 +59334,7 @@
         <v>46248.450811725</v>
       </c>
       <c r="P918" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q918" s="4" t="s">
         <v>31</v>
@@ -59372,7 +59369,7 @@
         <v>328</v>
       </c>
       <c r="G919" s="9" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="H919" s="11" t="n">
         <v>46248.451365741</v>
@@ -59395,7 +59392,7 @@
         <v>46248.478451655</v>
       </c>
       <c r="P919" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q919" s="9" t="s">
         <v>31</v>
@@ -59430,7 +59427,7 @@
         <v>272</v>
       </c>
       <c r="G920" s="4" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="H920" s="5" t="n">
         <v>46248</v>
@@ -59453,7 +59450,7 @@
         <v>46252.328676273</v>
       </c>
       <c r="P920" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q920" s="4" t="s">
         <v>134</v>
@@ -59488,7 +59485,7 @@
         <v>1060</v>
       </c>
       <c r="G921" s="9" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="H921" s="11" t="n">
         <v>46251.721273148</v>
@@ -59511,7 +59508,7 @@
         <v>46252.424934491</v>
       </c>
       <c r="P921" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q921" s="9" t="s">
         <v>31</v>
@@ -59546,7 +59543,7 @@
         <v>262</v>
       </c>
       <c r="G922" s="4" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="H922" s="6" t="n">
         <v>46251.698263889</v>
@@ -59569,7 +59566,7 @@
         <v>46252.425033912</v>
       </c>
       <c r="P922" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q922" s="4" t="s">
         <v>31</v>
@@ -59601,22 +59598,22 @@
         <v>24</v>
       </c>
       <c r="F923" s="9" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="G923" s="9" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="H923" s="11" t="n">
         <v>46253.493287037</v>
       </c>
       <c r="I923" s="9" t="s">
+        <v>1880</v>
+      </c>
+      <c r="J923" s="9" t="s">
         <v>1882</v>
       </c>
-      <c r="J923" s="9" t="s">
-        <v>1884</v>
-      </c>
       <c r="K923" s="9" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="L923" s="10"/>
       <c r="M923" s="10"/>
@@ -59627,7 +59624,7 @@
         <v>46253.471141667</v>
       </c>
       <c r="P923" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q923" s="9" t="s">
         <v>47</v>
@@ -59662,7 +59659,7 @@
         <v>461</v>
       </c>
       <c r="G924" s="4" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="H924" s="6" t="n">
         <v>46252.750821759</v>
@@ -59685,7 +59682,7 @@
         <v>46253.471281215</v>
       </c>
       <c r="P924" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q924" s="4" t="s">
         <v>31</v>
@@ -59717,22 +59714,22 @@
         <v>24</v>
       </c>
       <c r="F925" s="9" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="G925" s="9" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="H925" s="11" t="n">
         <v>46252.487453704</v>
       </c>
       <c r="I925" s="9" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J925" s="9" t="s">
         <v>1430</v>
       </c>
-      <c r="J925" s="9" t="s">
+      <c r="K925" s="9" t="s">
         <v>1431</v>
-      </c>
-      <c r="K925" s="9" t="s">
-        <v>1432</v>
       </c>
       <c r="L925" s="10"/>
       <c r="M925" s="10"/>
@@ -59743,7 +59740,7 @@
         <v>46253.471405405</v>
       </c>
       <c r="P925" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q925" s="9" t="s">
         <v>47</v>
@@ -59778,7 +59775,7 @@
         <v>75</v>
       </c>
       <c r="G926" s="4" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="H926" s="6" t="n">
         <v>46253.626689815</v>
@@ -59801,7 +59798,7 @@
         <v>46254.553285961</v>
       </c>
       <c r="P926" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q926" s="4" t="s">
         <v>31</v>
@@ -59836,7 +59833,7 @@
         <v>589</v>
       </c>
       <c r="G927" s="9" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="H927" s="10" t="n">
         <v>46255</v>
@@ -59859,7 +59856,7 @@
         <v>46255.558190197</v>
       </c>
       <c r="P927" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q927" s="9" t="s">
         <v>134</v>
@@ -59894,7 +59891,7 @@
         <v>355</v>
       </c>
       <c r="G928" s="4" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="H928" s="5" t="n">
         <v>46255</v>
@@ -59917,7 +59914,7 @@
         <v>46255.559634954</v>
       </c>
       <c r="P928" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q928" s="4" t="s">
         <v>134</v>
@@ -59949,22 +59946,22 @@
         <v>24</v>
       </c>
       <c r="F929" s="9" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="G929" s="9" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="H929" s="10" t="n">
         <v>46254</v>
       </c>
       <c r="I929" s="9" t="s">
+        <v>1889</v>
+      </c>
+      <c r="J929" s="9" t="s">
         <v>1891</v>
       </c>
-      <c r="J929" s="9" t="s">
-        <v>1893</v>
-      </c>
       <c r="K929" s="9" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="L929" s="10"/>
       <c r="M929" s="10"/>
@@ -59975,10 +59972,10 @@
         <v>46255.566605324</v>
       </c>
       <c r="P929" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q929" s="9" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="R929" s="12" t="n">
         <v>116127.08</v>
@@ -60010,7 +60007,7 @@
         <v>698</v>
       </c>
       <c r="G930" s="4" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="H930" s="6" t="n">
         <v>46258.645081019</v>
@@ -60033,7 +60030,7 @@
         <v>46259.63694375</v>
       </c>
       <c r="P930" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q930" s="4" t="s">
         <v>47</v>
@@ -60062,13 +60059,13 @@
         <v>23</v>
       </c>
       <c r="E931" s="8" t="s">
-        <v>285</v>
+        <v>1219</v>
       </c>
       <c r="F931" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G931" s="9" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="H931" s="11" t="n">
         <v>46258.652638889</v>
@@ -60085,22 +60082,22 @@
       <c r="L931" s="10"/>
       <c r="M931" s="10"/>
       <c r="N931" s="9" t="s">
-        <v>1575</v>
+        <v>1288</v>
       </c>
       <c r="O931" s="11" t="n">
         <v>46259.637292558</v>
       </c>
       <c r="P931" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q931" s="9" t="s">
         <v>47</v>
       </c>
       <c r="R931" s="12" t="n">
-        <v>56288</v>
+        <v>56696</v>
       </c>
       <c r="S931" s="12" t="n">
-        <v>0</v>
+        <v>41096</v>
       </c>
       <c r="T931" s="9" t="s">
         <v>32</v>
@@ -60126,7 +60123,7 @@
         <v>888</v>
       </c>
       <c r="G932" s="4" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="H932" s="6" t="n">
         <v>46258.672395833</v>
@@ -60149,7 +60146,7 @@
         <v>46259.637395023</v>
       </c>
       <c r="P932" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q932" s="4" t="s">
         <v>747</v>
@@ -60181,33 +60178,33 @@
         <v>285</v>
       </c>
       <c r="F933" s="9" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G933" s="9" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="H933" s="11" t="n">
         <v>46259.638611111</v>
       </c>
       <c r="I933" s="9" t="s">
+        <v>1461</v>
+      </c>
+      <c r="J933" s="9" t="s">
         <v>1462</v>
       </c>
-      <c r="J933" s="9" t="s">
+      <c r="K933" s="9" t="s">
         <v>1463</v>
-      </c>
-      <c r="K933" s="9" t="s">
-        <v>1464</v>
       </c>
       <c r="L933" s="10"/>
       <c r="M933" s="10"/>
       <c r="N933" s="9" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="O933" s="11" t="n">
         <v>46260.463491435</v>
       </c>
       <c r="P933" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q933" s="9" t="s">
         <v>47</v>
@@ -60236,25 +60233,25 @@
         <v>23</v>
       </c>
       <c r="E934" s="3" t="s">
+        <v>1898</v>
+      </c>
+      <c r="F934" s="4" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G934" s="4" t="s">
         <v>1900</v>
-      </c>
-      <c r="F934" s="4" t="s">
-        <v>1901</v>
-      </c>
-      <c r="G934" s="4" t="s">
-        <v>1902</v>
       </c>
       <c r="H934" s="6" t="n">
         <v>46259.473958333</v>
       </c>
       <c r="I934" s="4" t="s">
+        <v>1899</v>
+      </c>
+      <c r="J934" s="4" t="s">
         <v>1901</v>
       </c>
-      <c r="J934" s="4" t="s">
-        <v>1903</v>
-      </c>
       <c r="K934" s="4" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="L934" s="5"/>
       <c r="M934" s="5"/>
@@ -60265,7 +60262,7 @@
         <v>46260.465283762</v>
       </c>
       <c r="P934" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q934" s="4" t="s">
         <v>1095</v>
@@ -60300,7 +60297,7 @@
         <v>1060</v>
       </c>
       <c r="G935" s="9" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="H935" s="11" t="n">
         <v>46259.50275463</v>
@@ -60323,7 +60320,7 @@
         <v>46260.472780787</v>
       </c>
       <c r="P935" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q935" s="9" t="s">
         <v>31</v>
@@ -60355,22 +60352,22 @@
         <v>24</v>
       </c>
       <c r="F936" s="4" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="G936" s="4" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="H936" s="5" t="n">
         <v>46259</v>
       </c>
       <c r="I936" s="4" t="s">
+        <v>1906</v>
+      </c>
+      <c r="J936" s="4" t="s">
+        <v>1907</v>
+      </c>
+      <c r="K936" s="4" t="s">
         <v>1908</v>
-      </c>
-      <c r="J936" s="4" t="s">
-        <v>1909</v>
-      </c>
-      <c r="K936" s="4" t="s">
-        <v>1910</v>
       </c>
       <c r="L936" s="5"/>
       <c r="M936" s="5"/>
@@ -60381,10 +60378,10 @@
         <v>46260.475690625</v>
       </c>
       <c r="P936" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q936" s="4" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="R936" s="7" t="n">
         <v>42572</v>
@@ -60416,7 +60413,7 @@
         <v>698</v>
       </c>
       <c r="G937" s="9" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="H937" s="11" t="n">
         <v>46259.659039352</v>
@@ -60439,7 +60436,7 @@
         <v>46260.478625231</v>
       </c>
       <c r="P937" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q937" s="9" t="s">
         <v>47</v>
@@ -60474,7 +60471,7 @@
         <v>262</v>
       </c>
       <c r="G938" s="4" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="H938" s="6" t="n">
         <v>46259.757233796</v>
@@ -60497,7 +60494,7 @@
         <v>46260.481702546</v>
       </c>
       <c r="P938" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q938" s="4" t="s">
         <v>31</v>
@@ -60532,7 +60529,7 @@
         <v>945</v>
       </c>
       <c r="G939" s="9" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="H939" s="11" t="n">
         <v>46259.670231481</v>
@@ -60555,7 +60552,7 @@
         <v>46260.610262269</v>
       </c>
       <c r="P939" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q939" s="9" t="s">
         <v>31</v>
@@ -60584,13 +60581,13 @@
         <v>23</v>
       </c>
       <c r="E940" s="3" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="F940" s="4" t="s">
         <v>408</v>
       </c>
       <c r="G940" s="4" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="H940" s="6" t="n">
         <v>46261.456944444</v>
@@ -60613,7 +60610,7 @@
         <v>46261.555533102</v>
       </c>
       <c r="P940" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q940" s="4" t="s">
         <v>31</v>
@@ -60645,10 +60642,10 @@
         <v>24</v>
       </c>
       <c r="F941" s="9" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="G941" s="9" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="H941" s="11" t="n">
         <v>46260.641412037</v>
@@ -60671,7 +60668,7 @@
         <v>46261.563297998</v>
       </c>
       <c r="P941" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q941" s="9" t="s">
         <v>31</v>
@@ -60706,7 +60703,7 @@
         <v>1280</v>
       </c>
       <c r="G942" s="4" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="H942" s="6" t="n">
         <v>46261.627002315</v>
@@ -60729,7 +60726,7 @@
         <v>46262.58220772</v>
       </c>
       <c r="P942" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q942" s="4" t="s">
         <v>47</v>
@@ -60764,7 +60761,7 @@
         <v>75</v>
       </c>
       <c r="G943" s="9" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="H943" s="11" t="n">
         <v>46261.674166667</v>
@@ -60781,13 +60778,13 @@
       <c r="L943" s="10"/>
       <c r="M943" s="10"/>
       <c r="N943" s="9" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="O943" s="11" t="n">
         <v>46262.58240625</v>
       </c>
       <c r="P943" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q943" s="9" t="s">
         <v>31</v>
@@ -60816,13 +60813,13 @@
         <v>23</v>
       </c>
       <c r="E944" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F944" s="4" t="s">
         <v>211</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="H944" s="6" t="n">
         <v>46261.624131944</v>
@@ -60839,13 +60836,13 @@
       <c r="L944" s="5"/>
       <c r="M944" s="5"/>
       <c r="N944" s="4" t="s">
-        <v>1575</v>
+        <v>29</v>
       </c>
       <c r="O944" s="6" t="n">
         <v>46262.582538507</v>
       </c>
       <c r="P944" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q944" s="4" t="s">
         <v>47</v>
@@ -60854,7 +60851,7 @@
         <v>44352</v>
       </c>
       <c r="S944" s="7" t="n">
-        <v>0</v>
+        <v>44352</v>
       </c>
       <c r="T944" s="4" t="s">
         <v>32</v>
@@ -60874,13 +60871,13 @@
         <v>23</v>
       </c>
       <c r="E945" s="8" t="s">
-        <v>285</v>
+        <v>1917</v>
       </c>
       <c r="F945" s="9" t="s">
         <v>521</v>
       </c>
       <c r="G945" s="9" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="H945" s="11" t="n">
         <v>46261.626898148</v>
@@ -60897,13 +60894,13 @@
       <c r="L945" s="10"/>
       <c r="M945" s="10"/>
       <c r="N945" s="9" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="O945" s="11" t="n">
         <v>46262.582696609</v>
       </c>
       <c r="P945" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q945" s="9" t="s">
         <v>31</v>
@@ -60912,7 +60909,7 @@
         <v>5972</v>
       </c>
       <c r="S945" s="12" t="n">
-        <v>0</v>
+        <v>4806</v>
       </c>
       <c r="T945" s="9" t="s">
         <v>32</v>
@@ -60938,7 +60935,7 @@
         <v>1056</v>
       </c>
       <c r="G946" s="4" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H946" s="5" t="n">
         <v>46262</v>
@@ -60961,7 +60958,7 @@
         <v>46262.59088912</v>
       </c>
       <c r="P946" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q946" s="4" t="s">
         <v>134</v>
@@ -60996,7 +60993,7 @@
         <v>1019</v>
       </c>
       <c r="G947" s="9" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="H947" s="10" t="n">
         <v>46261</v>
@@ -61019,7 +61016,7 @@
         <v>46262.592242708</v>
       </c>
       <c r="P947" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q947" s="9" t="s">
         <v>134</v>
@@ -61054,7 +61051,7 @@
         <v>38</v>
       </c>
       <c r="G948" s="4" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="H948" s="6" t="n">
         <v>46262.683993056</v>
@@ -61077,7 +61074,7 @@
         <v>46265.653780324</v>
       </c>
       <c r="P948" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q948" s="4" t="s">
         <v>31</v>
@@ -61106,25 +61103,25 @@
         <v>23</v>
       </c>
       <c r="E949" s="8" t="s">
+        <v>1922</v>
+      </c>
+      <c r="F949" s="9" t="s">
+        <v>1737</v>
+      </c>
+      <c r="G949" s="9" t="s">
         <v>1923</v>
-      </c>
-      <c r="F949" s="9" t="s">
-        <v>1739</v>
-      </c>
-      <c r="G949" s="9" t="s">
-        <v>1924</v>
       </c>
       <c r="H949" s="10" t="n">
         <v>46265</v>
       </c>
       <c r="I949" s="9" t="s">
+        <v>1737</v>
+      </c>
+      <c r="J949" s="9" t="s">
+        <v>1738</v>
+      </c>
+      <c r="K949" s="9" t="s">
         <v>1739</v>
-      </c>
-      <c r="J949" s="9" t="s">
-        <v>1740</v>
-      </c>
-      <c r="K949" s="9" t="s">
-        <v>1741</v>
       </c>
       <c r="L949" s="10"/>
       <c r="M949" s="10"/>
@@ -61135,7 +61132,7 @@
         <v>46265.656787882</v>
       </c>
       <c r="P949" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q949" s="9" t="s">
         <v>31</v>
@@ -61144,7 +61141,7 @@
         <v>201401</v>
       </c>
       <c r="S949" s="12" t="n">
-        <v>93000</v>
+        <v>130260</v>
       </c>
       <c r="T949" s="9" t="s">
         <v>32</v>
@@ -61164,13 +61161,13 @@
         <v>23</v>
       </c>
       <c r="E950" s="3" t="s">
+        <v>1924</v>
+      </c>
+      <c r="F950" s="4" t="s">
+        <v>1642</v>
+      </c>
+      <c r="G950" s="4" t="s">
         <v>1925</v>
-      </c>
-      <c r="F950" s="4" t="s">
-        <v>1644</v>
-      </c>
-      <c r="G950" s="4" t="s">
-        <v>1926</v>
       </c>
       <c r="H950" s="5" t="n">
         <v>46265</v>
@@ -61193,7 +61190,7 @@
         <v>46266.3342289</v>
       </c>
       <c r="P950" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q950" s="4" t="s">
         <v>68</v>
@@ -61202,7 +61199,7 @@
         <v>63150.72</v>
       </c>
       <c r="S950" s="7" t="n">
-        <v>4224.96</v>
+        <v>11970.72</v>
       </c>
       <c r="T950" s="4" t="s">
         <v>32</v>
@@ -61222,13 +61219,13 @@
         <v>23</v>
       </c>
       <c r="E951" s="8" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="F951" s="9" t="s">
         <v>619</v>
       </c>
       <c r="G951" s="9" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H951" s="11" t="n">
         <v>46265.756805556</v>
@@ -61251,7 +61248,7 @@
         <v>46266.686144444</v>
       </c>
       <c r="P951" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q951" s="9" t="s">
         <v>31</v>
@@ -61286,7 +61283,7 @@
         <v>103</v>
       </c>
       <c r="G952" s="4" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H952" s="6" t="n">
         <v>46262.6721875</v>
@@ -61303,13 +61300,13 @@
       <c r="L952" s="5"/>
       <c r="M952" s="5"/>
       <c r="N952" s="4" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="O952" s="6" t="n">
         <v>46266.68744059</v>
       </c>
       <c r="P952" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q952" s="4" t="s">
         <v>47</v>
@@ -61344,7 +61341,7 @@
         <v>814</v>
       </c>
       <c r="G953" s="9" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H953" s="11" t="n">
         <v>46265.738773148</v>
@@ -61361,19 +61358,19 @@
       <c r="L953" s="10"/>
       <c r="M953" s="10"/>
       <c r="N953" s="9" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="O953" s="11" t="n">
         <v>46266.688499306</v>
       </c>
       <c r="P953" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q953" s="9" t="s">
         <v>142</v>
       </c>
       <c r="R953" s="12" t="n">
-        <v>26895.14</v>
+        <v>27007.74</v>
       </c>
       <c r="S953" s="12" t="n">
         <v>0</v>
@@ -61402,7 +61399,7 @@
         <v>484</v>
       </c>
       <c r="G954" s="4" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H954" s="6" t="n">
         <v>46265.406400463</v>
@@ -61425,7 +61422,7 @@
         <v>46266.689224306</v>
       </c>
       <c r="P954" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q954" s="4" t="s">
         <v>31</v>
@@ -61454,13 +61451,13 @@
         <v>23</v>
       </c>
       <c r="E955" s="8" t="s">
-        <v>1932</v>
+        <v>24</v>
       </c>
       <c r="F955" s="9" t="s">
         <v>482</v>
       </c>
       <c r="G955" s="9" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="H955" s="11" t="n">
         <v>46262.643506944</v>
@@ -61477,13 +61474,13 @@
       <c r="L955" s="10"/>
       <c r="M955" s="10"/>
       <c r="N955" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O955" s="11" t="n">
         <v>46266.690371215</v>
       </c>
       <c r="P955" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q955" s="9" t="s">
         <v>31</v>
@@ -61492,7 +61489,7 @@
         <v>33757.34</v>
       </c>
       <c r="S955" s="12" t="n">
-        <v>4959.12</v>
+        <v>33757.34</v>
       </c>
       <c r="T955" s="9" t="s">
         <v>32</v>
@@ -61518,7 +61515,7 @@
         <v>744</v>
       </c>
       <c r="G956" s="4" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="H956" s="6" t="n">
         <v>46262.644305556</v>
@@ -61541,7 +61538,7 @@
         <v>46266.691768252</v>
       </c>
       <c r="P956" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q956" s="4" t="s">
         <v>747</v>
@@ -61576,7 +61573,7 @@
         <v>1179</v>
       </c>
       <c r="G957" s="9" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="H957" s="11" t="n">
         <v>46262.617488426</v>
@@ -61593,13 +61590,13 @@
       <c r="L957" s="10"/>
       <c r="M957" s="10"/>
       <c r="N957" s="9" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="O957" s="11" t="n">
         <v>46266.693244294</v>
       </c>
       <c r="P957" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q957" s="9" t="s">
         <v>1158</v>
@@ -61631,10 +61628,10 @@
         <v>24</v>
       </c>
       <c r="F958" s="4" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="G958" s="4" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="H958" s="6" t="n">
         <v>46262.337835648</v>
@@ -61657,7 +61654,7 @@
         <v>46266.694431794</v>
       </c>
       <c r="P958" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q958" s="4" t="s">
         <v>37</v>
@@ -61689,10 +61686,10 @@
         <v>24</v>
       </c>
       <c r="F959" s="9" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="G959" s="9" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="H959" s="10" t="n">
         <v>46266</v>
@@ -61715,7 +61712,7 @@
         <v>46266.695900926</v>
       </c>
       <c r="P959" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q959" s="9" t="s">
         <v>134</v>
@@ -61747,10 +61744,10 @@
         <v>24</v>
       </c>
       <c r="F960" s="4" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="G960" s="4" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="H960" s="5" t="n">
         <v>46265</v>
@@ -61773,7 +61770,7 @@
         <v>46266.697281597</v>
       </c>
       <c r="P960" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q960" s="4" t="s">
         <v>134</v>
@@ -61802,45 +61799,45 @@
         <v>23</v>
       </c>
       <c r="E961" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F961" s="9" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="G961" s="9" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="H961" s="10" t="n">
         <v>46266</v>
       </c>
       <c r="I961" s="9" t="s">
+        <v>1938</v>
+      </c>
+      <c r="J961" s="9" t="s">
         <v>1940</v>
       </c>
-      <c r="J961" s="9" t="s">
-        <v>1942</v>
-      </c>
       <c r="K961" s="9" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="L961" s="10"/>
       <c r="M961" s="10"/>
       <c r="N961" s="9" t="s">
-        <v>1575</v>
+        <v>29</v>
       </c>
       <c r="O961" s="11" t="n">
         <v>46266.698305127</v>
       </c>
       <c r="P961" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q961" s="9" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="R961" s="12" t="n">
         <v>17437.2</v>
       </c>
       <c r="S961" s="12" t="n">
-        <v>0</v>
+        <v>17437.2</v>
       </c>
       <c r="T961" s="9" t="s">
         <v>88</v>
@@ -61860,45 +61857,45 @@
         <v>23</v>
       </c>
       <c r="E962" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F962" s="4" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="G962" s="4" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="H962" s="5" t="n">
         <v>46265</v>
       </c>
       <c r="I962" s="4" t="s">
+        <v>1944</v>
+      </c>
+      <c r="J962" s="4" t="s">
+        <v>1945</v>
+      </c>
+      <c r="K962" s="4" t="s">
         <v>1946</v>
-      </c>
-      <c r="J962" s="4" t="s">
-        <v>1947</v>
-      </c>
-      <c r="K962" s="4" t="s">
-        <v>1948</v>
       </c>
       <c r="L962" s="5"/>
       <c r="M962" s="5"/>
       <c r="N962" s="4" t="s">
-        <v>1575</v>
+        <v>29</v>
       </c>
       <c r="O962" s="6" t="n">
         <v>46266.700271262</v>
       </c>
       <c r="P962" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q962" s="4" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="R962" s="7" t="n">
         <v>10074</v>
       </c>
       <c r="S962" s="7" t="n">
-        <v>0</v>
+        <v>10074</v>
       </c>
       <c r="T962" s="4" t="s">
         <v>88</v>
@@ -61924,7 +61921,7 @@
         <v>945</v>
       </c>
       <c r="G963" s="9" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="H963" s="11" t="n">
         <v>46267.438217593</v>
@@ -61941,13 +61938,13 @@
       <c r="L963" s="10"/>
       <c r="M963" s="10"/>
       <c r="N963" s="9" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="O963" s="11" t="n">
         <v>46267.661274965</v>
       </c>
       <c r="P963" s="9" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="Q963" s="9" t="s">
         <v>31</v>
@@ -61964,35 +61961,93 @@
       <c r="U963" s="9"/>
       <c r="V963" s="9"/>
     </row>
-    <row r="964" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A964" s="13" t="n">
-        <v>962</v>
-      </c>
-      <c r="B964" s="14"/>
-      <c r="C964" s="14"/>
-      <c r="D964" s="14"/>
-      <c r="E964" s="14"/>
-      <c r="F964" s="14"/>
-      <c r="G964" s="14"/>
-      <c r="H964" s="14"/>
-      <c r="I964" s="14"/>
-      <c r="J964" s="14"/>
-      <c r="K964" s="14"/>
-      <c r="L964" s="14"/>
-      <c r="M964" s="14"/>
-      <c r="N964" s="14"/>
-      <c r="O964" s="14"/>
-      <c r="P964" s="14"/>
-      <c r="Q964" s="14"/>
-      <c r="R964" s="15" t="n">
-        <v>58094105.5826</v>
-      </c>
-      <c r="S964" s="15" t="n">
-        <v>56822675.4926</v>
-      </c>
-      <c r="T964" s="14"/>
-      <c r="U964" s="14"/>
-      <c r="V964" s="16"/>
+    <row r="964" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A964" s="3" t="n">
+        <v>1033</v>
+      </c>
+      <c r="B964" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C964" s="4"/>
+      <c r="D964" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E964" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F964" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="G964" s="4" t="s">
+        <v>1948</v>
+      </c>
+      <c r="H964" s="5" t="n">
+        <v>46269</v>
+      </c>
+      <c r="I964" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J964" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K964" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L964" s="5"/>
+      <c r="M964" s="5"/>
+      <c r="N964" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O964" s="6" t="n">
+        <v>46269.606936921</v>
+      </c>
+      <c r="P964" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q964" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="R964" s="7" t="n">
+        <v>840</v>
+      </c>
+      <c r="S964" s="7" t="n">
+        <v>840</v>
+      </c>
+      <c r="T964" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U964" s="4"/>
+      <c r="V964" s="4"/>
+    </row>
+    <row r="965" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A965" s="13" t="n">
+        <v>963</v>
+      </c>
+      <c r="B965" s="14"/>
+      <c r="C965" s="14"/>
+      <c r="D965" s="14"/>
+      <c r="E965" s="14"/>
+      <c r="F965" s="14"/>
+      <c r="G965" s="14"/>
+      <c r="H965" s="14"/>
+      <c r="I965" s="14"/>
+      <c r="J965" s="14"/>
+      <c r="K965" s="14"/>
+      <c r="L965" s="14"/>
+      <c r="M965" s="14"/>
+      <c r="N965" s="14"/>
+      <c r="O965" s="14"/>
+      <c r="P965" s="14"/>
+      <c r="Q965" s="14"/>
+      <c r="R965" s="15" t="n">
+        <v>58095466.1826</v>
+      </c>
+      <c r="S965" s="15" t="n">
+        <v>57074871.5226</v>
+      </c>
+      <c r="T965" s="14"/>
+      <c r="U965" s="14"/>
+      <c r="V965" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="1949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="1969">
   <si>
     <t>ID</t>
   </si>
@@ -4734,744 +4734,744 @@
     <t>945</t>
   </si>
   <si>
+    <t>VAL MED PRODUTOS E EQUIP.</t>
+  </si>
+  <si>
+    <t>946</t>
+  </si>
+  <si>
+    <t>947</t>
+  </si>
+  <si>
+    <t>948</t>
+  </si>
+  <si>
+    <t>949</t>
+  </si>
+  <si>
+    <t>950</t>
+  </si>
+  <si>
+    <t>D. ARAUJO COMERCIO</t>
+  </si>
+  <si>
+    <t>951</t>
+  </si>
+  <si>
+    <t>953</t>
+  </si>
+  <si>
+    <t>MERCANTE DISTRIBUIDOR HOSP.</t>
+  </si>
+  <si>
+    <t>954</t>
+  </si>
+  <si>
+    <t>MONTALVAO COMERCIAL</t>
+  </si>
+  <si>
+    <t>955</t>
+  </si>
+  <si>
+    <t>956</t>
+  </si>
+  <si>
+    <t>BANDEIRANTES LAB</t>
+  </si>
+  <si>
+    <t>957</t>
+  </si>
+  <si>
+    <t>LABAND</t>
+  </si>
+  <si>
+    <t>BANDEIRANTES LAB PROD FARMACEUTICOS E HOSPITALARES</t>
+  </si>
+  <si>
+    <t>70.027.479/0001-35</t>
+  </si>
+  <si>
+    <t>958</t>
+  </si>
+  <si>
+    <t>959</t>
+  </si>
+  <si>
+    <t>JFB DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>960</t>
+  </si>
+  <si>
+    <t>L G PRODUTOS HOSP</t>
+  </si>
+  <si>
+    <t>963</t>
+  </si>
+  <si>
+    <t>964</t>
+  </si>
+  <si>
+    <t>965</t>
+  </si>
+  <si>
+    <t>966</t>
+  </si>
+  <si>
+    <t>967</t>
+  </si>
+  <si>
+    <t>968</t>
+  </si>
+  <si>
+    <t>HOSPMED - PIAUI</t>
+  </si>
+  <si>
+    <t>969</t>
+  </si>
+  <si>
+    <t>HOSPMED DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>HOSPMED LTDA</t>
+  </si>
+  <si>
+    <t>00.156.820/0001-77</t>
+  </si>
+  <si>
+    <t>970</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>972</t>
+  </si>
+  <si>
+    <t>973</t>
+  </si>
+  <si>
+    <t>974</t>
+  </si>
+  <si>
+    <t>UNI-RIM UNIDADE</t>
+  </si>
+  <si>
+    <t>975</t>
+  </si>
+  <si>
+    <t>UNI-RIM UNIDADE DE DOENCAS RENAIS</t>
+  </si>
+  <si>
+    <t>MARCELO BARBOSA LEITE</t>
+  </si>
+  <si>
+    <t>02.553.837/0001-93</t>
+  </si>
+  <si>
+    <t>ULTRA TEXTIL</t>
+  </si>
+  <si>
+    <t>976</t>
+  </si>
+  <si>
+    <t>ALYNE FARMA</t>
+  </si>
+  <si>
+    <t>977</t>
+  </si>
+  <si>
+    <t>FARMACIAS CLARA POPULAR</t>
+  </si>
+  <si>
+    <t>ALYNE FARMA LTDA</t>
+  </si>
+  <si>
+    <t>14.674.114/0001-21</t>
+  </si>
+  <si>
+    <t>978</t>
+  </si>
+  <si>
+    <t>979</t>
+  </si>
+  <si>
+    <t>980</t>
+  </si>
+  <si>
+    <t>981</t>
+  </si>
+  <si>
+    <t>982</t>
+  </si>
+  <si>
+    <t>MED &amp; FARMA DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>983</t>
+  </si>
+  <si>
+    <t>J LAERCIO</t>
+  </si>
+  <si>
+    <t>984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabio     </t>
+  </si>
+  <si>
+    <t>985</t>
+  </si>
+  <si>
+    <t>986</t>
+  </si>
+  <si>
+    <t>47 %</t>
+  </si>
+  <si>
+    <t>987</t>
+  </si>
+  <si>
+    <t>989</t>
+  </si>
+  <si>
+    <t>91 %</t>
+  </si>
+  <si>
+    <t>EXPRESS DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>990</t>
+  </si>
+  <si>
+    <t>991</t>
+  </si>
+  <si>
+    <t>992</t>
+  </si>
+  <si>
+    <t>996</t>
+  </si>
+  <si>
+    <t>997</t>
+  </si>
+  <si>
+    <t>998</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
+    <t>T S DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>43 %</t>
+  </si>
+  <si>
+    <t>M. A. M COMERCIO</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>1008</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>PB MED</t>
+  </si>
+  <si>
+    <t>1017</t>
+  </si>
+  <si>
+    <t>1018</t>
+  </si>
+  <si>
+    <t>1020</t>
+  </si>
+  <si>
+    <t>39 %</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>1022</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>14.416.886/0001-63</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>GM FARMA COMERCIAL</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>1027</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>C G FARMA DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1029</t>
+  </si>
+  <si>
+    <t>77 %</t>
+  </si>
+  <si>
+    <t>ALTAMED DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1030</t>
+  </si>
+  <si>
+    <t>ALTAMED</t>
+  </si>
+  <si>
+    <t>ALTAMED DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>21.581.445/0001-82</t>
+  </si>
+  <si>
+    <t>ALINE CERBINO - PA</t>
+  </si>
+  <si>
+    <t>Região03</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>FERMATA</t>
+  </si>
+  <si>
+    <t>1035</t>
+  </si>
+  <si>
+    <t>FERMATA LTDA</t>
+  </si>
+  <si>
+    <t>66.175.139/0001-84</t>
+  </si>
+  <si>
+    <t>RC HOSPITALAR</t>
+  </si>
+  <si>
+    <t>1036</t>
+  </si>
+  <si>
+    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR</t>
+  </si>
+  <si>
+    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>26.147.597/0001-95</t>
+  </si>
+  <si>
+    <t>CRISTALFARMA</t>
+  </si>
+  <si>
+    <t>1037</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA CRISTALFARMA</t>
+  </si>
+  <si>
+    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
+  </si>
+  <si>
+    <t>05.003.408/0001-30</t>
+  </si>
+  <si>
+    <t>PLENA DIST - RN</t>
+  </si>
+  <si>
+    <t>1038</t>
+  </si>
+  <si>
+    <t>PLENA DIST - PE</t>
+  </si>
+  <si>
+    <t>1039</t>
+  </si>
+  <si>
+    <t>1040</t>
+  </si>
+  <si>
+    <t>1041</t>
+  </si>
+  <si>
+    <t>1042</t>
+  </si>
+  <si>
+    <t>1043</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>1046</t>
+  </si>
+  <si>
+    <t>1047</t>
+  </si>
+  <si>
+    <t>1048</t>
+  </si>
+  <si>
+    <t>1049</t>
+  </si>
+  <si>
+    <t>1050</t>
+  </si>
+  <si>
+    <t>CIRURGICA SHALOM</t>
+  </si>
+  <si>
+    <t>1051</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>1053</t>
+  </si>
+  <si>
+    <t>MP COMERCIO</t>
+  </si>
+  <si>
+    <t>1055</t>
+  </si>
+  <si>
+    <t>1056</t>
+  </si>
+  <si>
+    <t>84 %</t>
+  </si>
+  <si>
+    <t>1057</t>
+  </si>
+  <si>
+    <t>1058</t>
+  </si>
+  <si>
+    <t>1059</t>
+  </si>
+  <si>
+    <t>CIRURGICA MONTEBELLO</t>
+  </si>
+  <si>
+    <t>1060</t>
+  </si>
+  <si>
+    <t>MONTEBELLO</t>
+  </si>
+  <si>
+    <t>CIRURGICA MONTEBELLO LTDA</t>
+  </si>
+  <si>
+    <t>08.674.752/0001-40</t>
+  </si>
+  <si>
+    <t>1062</t>
+  </si>
+  <si>
+    <t>D FARIAS LIMA</t>
+  </si>
+  <si>
+    <t>1063</t>
+  </si>
+  <si>
+    <t>EXPRESS DIST.</t>
+  </si>
+  <si>
+    <t>1064</t>
+  </si>
+  <si>
+    <t>1065</t>
+  </si>
+  <si>
+    <t>1066</t>
+  </si>
+  <si>
+    <t>1067</t>
+  </si>
+  <si>
+    <t>1068</t>
+  </si>
+  <si>
+    <t>LS MATERIAIS (HELDER WALNER)</t>
+  </si>
+  <si>
+    <t>1069</t>
+  </si>
+  <si>
+    <t>A M FARMA - MA</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>A M FARMA - PI</t>
+  </si>
+  <si>
+    <t>1071</t>
+  </si>
+  <si>
+    <t>F MELO MATERIAL MEDICO</t>
+  </si>
+  <si>
+    <t>1072</t>
+  </si>
+  <si>
+    <t>JT COSTA COMERCIAL</t>
+  </si>
+  <si>
+    <t>1073</t>
+  </si>
+  <si>
+    <t>JT COSTA COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>64.190.875/0001-86</t>
+  </si>
+  <si>
+    <t>CAMPINA SAUDE</t>
+  </si>
+  <si>
+    <t>1074</t>
+  </si>
+  <si>
+    <t>CAMPINA SAUDE CENTER COM. DE ART. MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>39.324.410/0001-23</t>
+  </si>
+  <si>
+    <t>1075</t>
+  </si>
+  <si>
+    <t>1076</t>
+  </si>
+  <si>
+    <t>1077</t>
+  </si>
+  <si>
+    <t>1078</t>
+  </si>
+  <si>
+    <t>1079</t>
+  </si>
+  <si>
+    <t>1080</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>NOVA BAHIA MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>1083</t>
+  </si>
+  <si>
+    <t>NOVA BAHIA MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>32.658.023/0001-84</t>
+  </si>
+  <si>
+    <t>71 %</t>
+  </si>
+  <si>
+    <t>CONQUISTA MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>1084</t>
+  </si>
+  <si>
+    <t>CONQUISTA DISTRIBUIDORA DE MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>12.418.191/0001-95</t>
+  </si>
+  <si>
+    <t>1085</t>
+  </si>
+  <si>
+    <t>1086</t>
+  </si>
+  <si>
+    <t>1087</t>
+  </si>
+  <si>
+    <t>1088</t>
+  </si>
+  <si>
+    <t>F MELO</t>
+  </si>
+  <si>
+    <t>1089</t>
+  </si>
+  <si>
+    <t>41 %</t>
+  </si>
+  <si>
+    <t>C J A PARENTE</t>
+  </si>
+  <si>
+    <t>1090</t>
+  </si>
+  <si>
+    <t>C J A PARENTE COMERCIO</t>
+  </si>
+  <si>
+    <t>C J A PARENTE COMERCIO DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>83.646.307/0001-91</t>
+  </si>
+  <si>
+    <t>NORTE GREEN</t>
+  </si>
+  <si>
+    <t>1091</t>
+  </si>
+  <si>
+    <t>NORTE GREEN COMERCIO DE PROD FARM E HOSP LTDA</t>
+  </si>
+  <si>
+    <t>24.218.223/0001-98</t>
+  </si>
+  <si>
+    <t>1092</t>
+  </si>
+  <si>
+    <t>1093</t>
+  </si>
+  <si>
+    <t>CDMED HOSPITALAR</t>
+  </si>
+  <si>
+    <t>1094</t>
+  </si>
+  <si>
+    <t>CDMED HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>46.359.681/0001-80</t>
+  </si>
+  <si>
+    <t>1095</t>
+  </si>
+  <si>
+    <t>1096</t>
+  </si>
+  <si>
+    <t>1097</t>
+  </si>
+  <si>
+    <t>1098</t>
+  </si>
+  <si>
+    <t>F MELO MATERIAL</t>
+  </si>
+  <si>
+    <t>1099</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>58 %</t>
+  </si>
+  <si>
+    <t>RC DISTRIBUIDORA DE MED.</t>
+  </si>
+  <si>
+    <t>1105</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
     <t>A INICIAR</t>
   </si>
   <si>
-    <t>VAL MED PRODUTOS E EQUIP.</t>
-  </si>
-  <si>
-    <t>946</t>
-  </si>
-  <si>
-    <t>947</t>
-  </si>
-  <si>
-    <t>948</t>
-  </si>
-  <si>
-    <t>949</t>
-  </si>
-  <si>
-    <t>950</t>
-  </si>
-  <si>
-    <t>D. ARAUJO COMERCIO</t>
-  </si>
-  <si>
-    <t>951</t>
-  </si>
-  <si>
-    <t>953</t>
-  </si>
-  <si>
-    <t>MERCANTE DISTRIBUIDOR HOSP.</t>
-  </si>
-  <si>
-    <t>954</t>
-  </si>
-  <si>
-    <t>MONTALVAO COMERCIAL</t>
-  </si>
-  <si>
-    <t>955</t>
-  </si>
-  <si>
-    <t>956</t>
-  </si>
-  <si>
-    <t>BANDEIRANTES LAB</t>
-  </si>
-  <si>
-    <t>957</t>
-  </si>
-  <si>
-    <t>LABAND</t>
-  </si>
-  <si>
-    <t>BANDEIRANTES LAB PROD FARMACEUTICOS E HOSPITALARES</t>
-  </si>
-  <si>
-    <t>70.027.479/0001-35</t>
-  </si>
-  <si>
-    <t>958</t>
-  </si>
-  <si>
-    <t>959</t>
-  </si>
-  <si>
-    <t>JFB DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>960</t>
-  </si>
-  <si>
-    <t>L G PRODUTOS HOSP</t>
-  </si>
-  <si>
-    <t>963</t>
-  </si>
-  <si>
-    <t>964</t>
-  </si>
-  <si>
-    <t>965</t>
-  </si>
-  <si>
-    <t>966</t>
-  </si>
-  <si>
-    <t>967</t>
-  </si>
-  <si>
-    <t>968</t>
-  </si>
-  <si>
-    <t>HOSPMED - PIAUI</t>
-  </si>
-  <si>
-    <t>969</t>
-  </si>
-  <si>
-    <t>HOSPMED DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>HOSPMED LTDA</t>
-  </si>
-  <si>
-    <t>00.156.820/0001-77</t>
-  </si>
-  <si>
-    <t>970</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>972</t>
-  </si>
-  <si>
-    <t>973</t>
-  </si>
-  <si>
-    <t>974</t>
-  </si>
-  <si>
-    <t>UNI-RIM UNIDADE</t>
-  </si>
-  <si>
-    <t>975</t>
-  </si>
-  <si>
-    <t>UNI-RIM UNIDADE DE DOENCAS RENAIS</t>
-  </si>
-  <si>
-    <t>MARCELO BARBOSA LEITE</t>
-  </si>
-  <si>
-    <t>02.553.837/0001-93</t>
-  </si>
-  <si>
-    <t>ULTRA TEXTIL</t>
-  </si>
-  <si>
-    <t>976</t>
-  </si>
-  <si>
-    <t>ALYNE FARMA</t>
-  </si>
-  <si>
-    <t>977</t>
-  </si>
-  <si>
-    <t>FARMACIAS CLARA POPULAR</t>
-  </si>
-  <si>
-    <t>ALYNE FARMA LTDA</t>
-  </si>
-  <si>
-    <t>14.674.114/0001-21</t>
-  </si>
-  <si>
-    <t>978</t>
-  </si>
-  <si>
-    <t>979</t>
-  </si>
-  <si>
-    <t>980</t>
-  </si>
-  <si>
-    <t>981</t>
-  </si>
-  <si>
-    <t>982</t>
-  </si>
-  <si>
-    <t>MED &amp; FARMA DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>983</t>
-  </si>
-  <si>
-    <t>J LAERCIO</t>
-  </si>
-  <si>
-    <t>984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabio     </t>
-  </si>
-  <si>
-    <t>985</t>
-  </si>
-  <si>
-    <t>986</t>
-  </si>
-  <si>
-    <t>47 %</t>
-  </si>
-  <si>
-    <t>987</t>
-  </si>
-  <si>
-    <t>989</t>
-  </si>
-  <si>
-    <t>91 %</t>
-  </si>
-  <si>
-    <t>EXPRESS DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>990</t>
-  </si>
-  <si>
-    <t>991</t>
-  </si>
-  <si>
-    <t>992</t>
-  </si>
-  <si>
-    <t>996</t>
-  </si>
-  <si>
-    <t>997</t>
-  </si>
-  <si>
-    <t>998</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>T S DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>43 %</t>
-  </si>
-  <si>
-    <t>M. A. M COMERCIO</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>1006</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>1013</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>1015</t>
-  </si>
-  <si>
-    <t>PB MED</t>
-  </si>
-  <si>
-    <t>1017</t>
-  </si>
-  <si>
-    <t>1018</t>
-  </si>
-  <si>
-    <t>1020</t>
-  </si>
-  <si>
-    <t>39 %</t>
-  </si>
-  <si>
-    <t>1021</t>
-  </si>
-  <si>
-    <t>1022</t>
-  </si>
-  <si>
-    <t>COBERMED COMERCIO</t>
-  </si>
-  <si>
-    <t>1023</t>
-  </si>
-  <si>
-    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>14.416.886/0001-63</t>
-  </si>
-  <si>
-    <t>1024</t>
-  </si>
-  <si>
-    <t>GM FARMA COMERCIAL</t>
-  </si>
-  <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>1026</t>
-  </si>
-  <si>
-    <t>1027</t>
-  </si>
-  <si>
-    <t>1028</t>
-  </si>
-  <si>
-    <t>C G FARMA DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1029</t>
-  </si>
-  <si>
-    <t>77 %</t>
-  </si>
-  <si>
-    <t>ALTAMED DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1030</t>
-  </si>
-  <si>
-    <t>ALTAMED</t>
-  </si>
-  <si>
-    <t>ALTAMED DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>21.581.445/0001-82</t>
-  </si>
-  <si>
-    <t>ALINE CERBINO - PA</t>
-  </si>
-  <si>
-    <t>Região03</t>
-  </si>
-  <si>
-    <t>1033</t>
-  </si>
-  <si>
-    <t>FERMATA</t>
-  </si>
-  <si>
-    <t>1035</t>
-  </si>
-  <si>
-    <t>FERMATA LTDA</t>
-  </si>
-  <si>
-    <t>66.175.139/0001-84</t>
-  </si>
-  <si>
-    <t>RC HOSPITALAR</t>
-  </si>
-  <si>
-    <t>1036</t>
-  </si>
-  <si>
-    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR</t>
-  </si>
-  <si>
-    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>26.147.597/0001-95</t>
-  </si>
-  <si>
-    <t>CRISTALFARMA</t>
-  </si>
-  <si>
-    <t>1037</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA CRISTALFARMA</t>
-  </si>
-  <si>
-    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
-  </si>
-  <si>
-    <t>05.003.408/0001-30</t>
-  </si>
-  <si>
-    <t>PLENA DIST - RN</t>
-  </si>
-  <si>
-    <t>1038</t>
-  </si>
-  <si>
-    <t>PLENA DIST - PE</t>
-  </si>
-  <si>
-    <t>1039</t>
-  </si>
-  <si>
-    <t>1040</t>
-  </si>
-  <si>
-    <t>1041</t>
-  </si>
-  <si>
-    <t>1042</t>
-  </si>
-  <si>
-    <t>1043</t>
-  </si>
-  <si>
-    <t>1044</t>
-  </si>
-  <si>
-    <t>1045</t>
-  </si>
-  <si>
-    <t>1046</t>
-  </si>
-  <si>
-    <t>1047</t>
-  </si>
-  <si>
-    <t>1048</t>
-  </si>
-  <si>
-    <t>1049</t>
-  </si>
-  <si>
-    <t>1050</t>
-  </si>
-  <si>
-    <t>CIRURGICA SHALOM</t>
-  </si>
-  <si>
-    <t>1051</t>
-  </si>
-  <si>
-    <t>1052</t>
-  </si>
-  <si>
-    <t>1053</t>
-  </si>
-  <si>
-    <t>MP COMERCIO</t>
-  </si>
-  <si>
-    <t>1055</t>
-  </si>
-  <si>
-    <t>1056</t>
-  </si>
-  <si>
-    <t>84 %</t>
-  </si>
-  <si>
-    <t>1057</t>
-  </si>
-  <si>
-    <t>1058</t>
-  </si>
-  <si>
-    <t>1059</t>
-  </si>
-  <si>
-    <t>CIRURGICA MONTEBELLO</t>
-  </si>
-  <si>
-    <t>1060</t>
-  </si>
-  <si>
-    <t>MONTEBELLO</t>
-  </si>
-  <si>
-    <t>CIRURGICA MONTEBELLO LTDA</t>
-  </si>
-  <si>
-    <t>08.674.752/0001-40</t>
-  </si>
-  <si>
-    <t>1062</t>
-  </si>
-  <si>
-    <t>D FARIAS LIMA</t>
-  </si>
-  <si>
-    <t>1063</t>
-  </si>
-  <si>
-    <t>EXPRESS DIST.</t>
-  </si>
-  <si>
-    <t>1064</t>
-  </si>
-  <si>
-    <t>1065</t>
-  </si>
-  <si>
-    <t>1066</t>
-  </si>
-  <si>
-    <t>1067</t>
-  </si>
-  <si>
-    <t>1068</t>
-  </si>
-  <si>
-    <t>LS MATERIAIS (HELDER WALNER)</t>
-  </si>
-  <si>
-    <t>1069</t>
-  </si>
-  <si>
-    <t>A M FARMA - MA</t>
-  </si>
-  <si>
-    <t>1070</t>
-  </si>
-  <si>
-    <t>A M FARMA - PI</t>
-  </si>
-  <si>
-    <t>1071</t>
-  </si>
-  <si>
-    <t>F MELO MATERIAL MEDICO</t>
-  </si>
-  <si>
-    <t>1072</t>
-  </si>
-  <si>
-    <t>JT COSTA COMERCIAL</t>
-  </si>
-  <si>
-    <t>1073</t>
-  </si>
-  <si>
-    <t>JT COSTA COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>64.190.875/0001-86</t>
-  </si>
-  <si>
-    <t>CAMPINA SAUDE</t>
-  </si>
-  <si>
-    <t>1074</t>
-  </si>
-  <si>
-    <t>CAMPINA SAUDE CENTER COM. DE ART. MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>39.324.410/0001-23</t>
-  </si>
-  <si>
-    <t>1075</t>
-  </si>
-  <si>
-    <t>1076</t>
-  </si>
-  <si>
-    <t>1077</t>
-  </si>
-  <si>
-    <t>1078</t>
-  </si>
-  <si>
-    <t>1079</t>
-  </si>
-  <si>
-    <t>1080</t>
-  </si>
-  <si>
-    <t>1082</t>
-  </si>
-  <si>
-    <t>NOVA BAHIA MEDICAMENTOS</t>
-  </si>
-  <si>
-    <t>1083</t>
-  </si>
-  <si>
-    <t>NOVA BAHIA MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>32.658.023/0001-84</t>
-  </si>
-  <si>
-    <t>71 %</t>
-  </si>
-  <si>
-    <t>CONQUISTA MEDICAMENTOS</t>
-  </si>
-  <si>
-    <t>1084</t>
-  </si>
-  <si>
-    <t>CONQUISTA DISTRIBUIDORA DE MEDICAMENTOS</t>
-  </si>
-  <si>
-    <t>12.418.191/0001-95</t>
-  </si>
-  <si>
-    <t>1085</t>
-  </si>
-  <si>
-    <t>1086</t>
-  </si>
-  <si>
-    <t>1087</t>
-  </si>
-  <si>
-    <t>1088</t>
-  </si>
-  <si>
-    <t>F MELO</t>
-  </si>
-  <si>
-    <t>1089</t>
-  </si>
-  <si>
-    <t>41 %</t>
-  </si>
-  <si>
-    <t>C J A PARENTE</t>
-  </si>
-  <si>
-    <t>1090</t>
-  </si>
-  <si>
-    <t>C J A PARENTE COMERCIO</t>
-  </si>
-  <si>
-    <t>C J A PARENTE COMERCIO DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>83.646.307/0001-91</t>
-  </si>
-  <si>
-    <t>NORTE GREEN</t>
-  </si>
-  <si>
-    <t>1091</t>
-  </si>
-  <si>
-    <t>NORTE GREEN COMERCIO DE PROD FARM E HOSP LTDA</t>
-  </si>
-  <si>
-    <t>24.218.223/0001-98</t>
-  </si>
-  <si>
-    <t>1092</t>
-  </si>
-  <si>
-    <t>1093</t>
-  </si>
-  <si>
-    <t>CDMED HOSPITALAR</t>
-  </si>
-  <si>
-    <t>1094</t>
-  </si>
-  <si>
-    <t>CDMED HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>46.359.681/0001-80</t>
-  </si>
-  <si>
-    <t>1095</t>
-  </si>
-  <si>
-    <t>1096</t>
-  </si>
-  <si>
-    <t>1097</t>
-  </si>
-  <si>
-    <t>1098</t>
-  </si>
-  <si>
-    <t>F MELO MATERIAL</t>
-  </si>
-  <si>
-    <t>1099</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>1102</t>
-  </si>
-  <si>
-    <t>1103</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>58 %</t>
-  </si>
-  <si>
-    <t>RC DISTRIBUIDORA DE MED.</t>
-  </si>
-  <si>
-    <t>1105</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
     <t>1108</t>
   </si>
   <si>
@@ -5763,12 +5763,12 @@
     <t>1177</t>
   </si>
   <si>
+    <t>50 %</t>
+  </si>
+  <si>
     <t>1178</t>
   </si>
   <si>
-    <t>80 %</t>
-  </si>
-  <si>
     <t>1179</t>
   </si>
   <si>
@@ -5781,13 +5781,10 @@
     <t>1182</t>
   </si>
   <si>
-    <t>65 %</t>
-  </si>
-  <si>
     <t>1183</t>
   </si>
   <si>
-    <t>19 %</t>
+    <t>34 %</t>
   </si>
   <si>
     <t>1184</t>
@@ -5860,6 +5857,69 @@
   </si>
   <si>
     <t>1198</t>
+  </si>
+  <si>
+    <t>1199</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>33 %</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>1204</t>
+  </si>
+  <si>
+    <t>ATECNOMED ASSISTENCIA</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>1206</t>
+  </si>
+  <si>
+    <t>1207</t>
+  </si>
+  <si>
+    <t>CONTROLE MEDLAB</t>
+  </si>
+  <si>
+    <t>1208</t>
+  </si>
+  <si>
+    <t>CONTROLE MEDLAB COMERCIO DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>31.059.333/0001-10</t>
+  </si>
+  <si>
+    <t>1209</t>
+  </si>
+  <si>
+    <t>DISMED DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1210</t>
+  </si>
+  <si>
+    <t>UNI RIM</t>
+  </si>
+  <si>
+    <t>1211</t>
+  </si>
+  <si>
+    <t>1212</t>
   </si>
 </sst>
 </file>
@@ -6053,7 +6113,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V965"/>
+  <dimension ref="A1:V979"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -48573,7 +48633,7 @@
         <v>23</v>
       </c>
       <c r="E733" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F733" s="9" t="s">
         <v>103</v>
@@ -48596,7 +48656,7 @@
       <c r="L733" s="10"/>
       <c r="M733" s="10"/>
       <c r="N733" s="9" t="s">
-        <v>1573</v>
+        <v>29</v>
       </c>
       <c r="O733" s="11" t="n">
         <v>46178.475498414</v>
@@ -48611,7 +48671,7 @@
         <v>25500</v>
       </c>
       <c r="S733" s="12" t="n">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="T733" s="9" t="s">
         <v>32</v>
@@ -48634,10 +48694,10 @@
         <v>24</v>
       </c>
       <c r="F734" s="4" t="s">
+        <v>1573</v>
+      </c>
+      <c r="G734" s="4" t="s">
         <v>1574</v>
-      </c>
-      <c r="G734" s="4" t="s">
-        <v>1575</v>
       </c>
       <c r="H734" s="5" t="n">
         <v>46176</v>
@@ -48695,7 +48755,7 @@
         <v>1570</v>
       </c>
       <c r="G735" s="9" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H735" s="10" t="n">
         <v>46176</v>
@@ -48753,7 +48813,7 @@
         <v>143</v>
       </c>
       <c r="G736" s="4" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H736" s="5" t="n">
         <v>46181</v>
@@ -48811,7 +48871,7 @@
         <v>447</v>
       </c>
       <c r="G737" s="9" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H737" s="10" t="n">
         <v>46182</v>
@@ -48869,7 +48929,7 @@
         <v>143</v>
       </c>
       <c r="G738" s="4" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H738" s="5" t="n">
         <v>46182</v>
@@ -48924,10 +48984,10 @@
         <v>24</v>
       </c>
       <c r="F739" s="9" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G739" s="9" t="s">
         <v>1580</v>
-      </c>
-      <c r="G739" s="9" t="s">
-        <v>1581</v>
       </c>
       <c r="H739" s="10" t="n">
         <v>46182</v>
@@ -48985,7 +49045,7 @@
         <v>1421</v>
       </c>
       <c r="G740" s="4" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H740" s="5" t="n">
         <v>46181</v>
@@ -49040,10 +49100,10 @@
         <v>24</v>
       </c>
       <c r="F741" s="9" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G741" s="9" t="s">
         <v>1583</v>
-      </c>
-      <c r="G741" s="9" t="s">
-        <v>1584</v>
       </c>
       <c r="H741" s="10" t="n">
         <v>46183</v>
@@ -49098,10 +49158,10 @@
         <v>24</v>
       </c>
       <c r="F742" s="4" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G742" s="4" t="s">
         <v>1585</v>
-      </c>
-      <c r="G742" s="4" t="s">
-        <v>1586</v>
       </c>
       <c r="H742" s="5" t="n">
         <v>46184</v>
@@ -49161,7 +49221,7 @@
         <v>1488</v>
       </c>
       <c r="G743" s="9" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H743" s="10" t="n">
         <v>46183</v>
@@ -49216,22 +49276,22 @@
         <v>24</v>
       </c>
       <c r="F744" s="4" t="s">
+        <v>1587</v>
+      </c>
+      <c r="G744" s="4" t="s">
         <v>1588</v>
-      </c>
-      <c r="G744" s="4" t="s">
-        <v>1589</v>
       </c>
       <c r="H744" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="I744" s="4" t="s">
+        <v>1589</v>
+      </c>
+      <c r="J744" s="4" t="s">
         <v>1590</v>
       </c>
-      <c r="J744" s="4" t="s">
+      <c r="K744" s="4" t="s">
         <v>1591</v>
-      </c>
-      <c r="K744" s="4" t="s">
-        <v>1592</v>
       </c>
       <c r="L744" s="5"/>
       <c r="M744" s="5"/>
@@ -49277,7 +49337,7 @@
         <v>272</v>
       </c>
       <c r="G745" s="9" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H745" s="10" t="n">
         <v>46184</v>
@@ -49335,7 +49395,7 @@
         <v>519</v>
       </c>
       <c r="G746" s="4" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H746" s="5" t="n">
         <v>46184</v>
@@ -49390,10 +49450,10 @@
         <v>24</v>
       </c>
       <c r="F747" s="9" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G747" s="9" t="s">
         <v>1595</v>
-      </c>
-      <c r="G747" s="9" t="s">
-        <v>1596</v>
       </c>
       <c r="H747" s="10" t="n">
         <v>46185</v>
@@ -49448,10 +49508,10 @@
         <v>24</v>
       </c>
       <c r="F748" s="4" t="s">
+        <v>1596</v>
+      </c>
+      <c r="G748" s="4" t="s">
         <v>1597</v>
-      </c>
-      <c r="G748" s="4" t="s">
-        <v>1598</v>
       </c>
       <c r="H748" s="5" t="n">
         <v>46185</v>
@@ -49509,7 +49569,7 @@
         <v>704</v>
       </c>
       <c r="G749" s="9" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H749" s="10" t="n">
         <v>46188</v>
@@ -49564,10 +49624,10 @@
         <v>24</v>
       </c>
       <c r="F750" s="4" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G750" s="4" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H750" s="5" t="n">
         <v>46188</v>
@@ -49625,7 +49685,7 @@
         <v>228</v>
       </c>
       <c r="G751" s="9" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H751" s="10" t="n">
         <v>46188</v>
@@ -49683,7 +49743,7 @@
         <v>228</v>
       </c>
       <c r="G752" s="4" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H752" s="5" t="n">
         <v>46188</v>
@@ -49741,7 +49801,7 @@
         <v>589</v>
       </c>
       <c r="G753" s="9" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H753" s="10" t="n">
         <v>46189</v>
@@ -49796,22 +49856,22 @@
         <v>24</v>
       </c>
       <c r="F754" s="4" t="s">
+        <v>1603</v>
+      </c>
+      <c r="G754" s="4" t="s">
         <v>1604</v>
-      </c>
-      <c r="G754" s="4" t="s">
-        <v>1605</v>
       </c>
       <c r="H754" s="5" t="n">
         <v>46188</v>
       </c>
       <c r="I754" s="4" t="s">
+        <v>1605</v>
+      </c>
+      <c r="J754" s="4" t="s">
         <v>1606</v>
       </c>
-      <c r="J754" s="4" t="s">
+      <c r="K754" s="4" t="s">
         <v>1607</v>
-      </c>
-      <c r="K754" s="4" t="s">
-        <v>1608</v>
       </c>
       <c r="L754" s="5"/>
       <c r="M754" s="5"/>
@@ -49857,7 +49917,7 @@
         <v>1298</v>
       </c>
       <c r="G755" s="9" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H755" s="10" t="n">
         <v>46188</v>
@@ -49915,7 +49975,7 @@
         <v>152</v>
       </c>
       <c r="G756" s="4" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H756" s="5" t="n">
         <v>46189</v>
@@ -49973,7 +50033,7 @@
         <v>1296</v>
       </c>
       <c r="G757" s="9" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H757" s="10" t="n">
         <v>46189</v>
@@ -50031,7 +50091,7 @@
         <v>1296</v>
       </c>
       <c r="G758" s="4" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H758" s="5" t="n">
         <v>46189</v>
@@ -50089,7 +50149,7 @@
         <v>402</v>
       </c>
       <c r="G759" s="9" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H759" s="10" t="n">
         <v>46190</v>
@@ -50144,22 +50204,22 @@
         <v>24</v>
       </c>
       <c r="F760" s="4" t="s">
+        <v>1613</v>
+      </c>
+      <c r="G760" s="4" t="s">
         <v>1614</v>
-      </c>
-      <c r="G760" s="4" t="s">
-        <v>1615</v>
       </c>
       <c r="H760" s="5" t="n">
         <v>46189</v>
       </c>
       <c r="I760" s="4" t="s">
+        <v>1615</v>
+      </c>
+      <c r="J760" s="4" t="s">
         <v>1616</v>
       </c>
-      <c r="J760" s="4" t="s">
+      <c r="K760" s="4" t="s">
         <v>1617</v>
-      </c>
-      <c r="K760" s="4" t="s">
-        <v>1618</v>
       </c>
       <c r="L760" s="5"/>
       <c r="M760" s="5"/>
@@ -50173,7 +50233,7 @@
         <v>1455</v>
       </c>
       <c r="Q760" s="4" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="R760" s="7" t="n">
         <v>2230.4</v>
@@ -50205,7 +50265,7 @@
         <v>157</v>
       </c>
       <c r="G761" s="9" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H761" s="10" t="n">
         <v>46189</v>
@@ -50260,22 +50320,22 @@
         <v>24</v>
       </c>
       <c r="F762" s="4" t="s">
+        <v>1620</v>
+      </c>
+      <c r="G762" s="4" t="s">
         <v>1621</v>
-      </c>
-      <c r="G762" s="4" t="s">
-        <v>1622</v>
       </c>
       <c r="H762" s="5" t="n">
         <v>46191</v>
       </c>
       <c r="I762" s="4" t="s">
+        <v>1622</v>
+      </c>
+      <c r="J762" s="4" t="s">
         <v>1623</v>
       </c>
-      <c r="J762" s="4" t="s">
+      <c r="K762" s="4" t="s">
         <v>1624</v>
-      </c>
-      <c r="K762" s="4" t="s">
-        <v>1625</v>
       </c>
       <c r="L762" s="5"/>
       <c r="M762" s="5"/>
@@ -50321,7 +50381,7 @@
         <v>892</v>
       </c>
       <c r="G763" s="9" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H763" s="10" t="n">
         <v>46191</v>
@@ -50379,7 +50439,7 @@
         <v>502</v>
       </c>
       <c r="G764" s="4" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H764" s="5" t="n">
         <v>46190</v>
@@ -50437,7 +50497,7 @@
         <v>322</v>
       </c>
       <c r="G765" s="9" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H765" s="10" t="n">
         <v>46190</v>
@@ -50495,7 +50555,7 @@
         <v>1488</v>
       </c>
       <c r="G766" s="4" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H766" s="5" t="n">
         <v>46192</v>
@@ -50553,7 +50613,7 @@
         <v>249</v>
       </c>
       <c r="G767" s="9" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H767" s="10" t="n">
         <v>46191</v>
@@ -50608,10 +50668,10 @@
         <v>24</v>
       </c>
       <c r="F768" s="4" t="s">
+        <v>1630</v>
+      </c>
+      <c r="G768" s="4" t="s">
         <v>1631</v>
-      </c>
-      <c r="G768" s="4" t="s">
-        <v>1632</v>
       </c>
       <c r="H768" s="5" t="n">
         <v>46191</v>
@@ -50666,10 +50726,10 @@
         <v>24</v>
       </c>
       <c r="F769" s="9" t="s">
+        <v>1632</v>
+      </c>
+      <c r="G769" s="9" t="s">
         <v>1633</v>
-      </c>
-      <c r="G769" s="9" t="s">
-        <v>1634</v>
       </c>
       <c r="H769" s="11" t="n">
         <v>46196.641111111</v>
@@ -50692,7 +50752,7 @@
         <v>46198.434918947</v>
       </c>
       <c r="P769" s="9" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="Q769" s="9" t="s">
         <v>74</v>
@@ -50727,7 +50787,7 @@
         <v>904</v>
       </c>
       <c r="G770" s="4" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H770" s="5" t="n">
         <v>46195</v>
@@ -50785,7 +50845,7 @@
         <v>888</v>
       </c>
       <c r="G771" s="9" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H771" s="10" t="n">
         <v>46192</v>
@@ -50837,13 +50897,13 @@
         <v>23</v>
       </c>
       <c r="E772" s="3" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="F772" s="4" t="s">
         <v>997</v>
       </c>
       <c r="G772" s="4" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H772" s="5" t="n">
         <v>46198</v>
@@ -50901,7 +50961,7 @@
         <v>276</v>
       </c>
       <c r="G773" s="9" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H773" s="10" t="n">
         <v>46198</v>
@@ -50953,13 +51013,13 @@
         <v>23</v>
       </c>
       <c r="E774" s="3" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F774" s="4" t="s">
         <v>1641</v>
       </c>
-      <c r="F774" s="4" t="s">
+      <c r="G774" s="4" t="s">
         <v>1642</v>
-      </c>
-      <c r="G774" s="4" t="s">
-        <v>1643</v>
       </c>
       <c r="H774" s="5" t="n">
         <v>46198</v>
@@ -51017,7 +51077,7 @@
         <v>1271</v>
       </c>
       <c r="G775" s="9" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H775" s="10" t="n">
         <v>46196</v>
@@ -51075,7 +51135,7 @@
         <v>1264</v>
       </c>
       <c r="G776" s="4" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H776" s="5" t="n">
         <v>46195</v>
@@ -51133,7 +51193,7 @@
         <v>496</v>
       </c>
       <c r="G777" s="9" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H777" s="10" t="n">
         <v>46198</v>
@@ -51191,7 +51251,7 @@
         <v>1075</v>
       </c>
       <c r="G778" s="4" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H778" s="5" t="n">
         <v>46198</v>
@@ -51249,7 +51309,7 @@
         <v>945</v>
       </c>
       <c r="G779" s="9" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H779" s="10" t="n">
         <v>46198</v>
@@ -51307,7 +51367,7 @@
         <v>1459</v>
       </c>
       <c r="G780" s="4" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H780" s="5" t="n">
         <v>46198</v>
@@ -51362,10 +51422,10 @@
         <v>24</v>
       </c>
       <c r="F781" s="9" t="s">
+        <v>1649</v>
+      </c>
+      <c r="G781" s="9" t="s">
         <v>1650</v>
-      </c>
-      <c r="G781" s="9" t="s">
-        <v>1651</v>
       </c>
       <c r="H781" s="10" t="n">
         <v>46198</v>
@@ -51423,7 +51483,7 @@
         <v>191</v>
       </c>
       <c r="G782" s="4" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H782" s="5" t="n">
         <v>46198</v>
@@ -51475,13 +51535,13 @@
         <v>23</v>
       </c>
       <c r="E783" s="8" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F783" s="9" t="s">
         <v>1653</v>
       </c>
-      <c r="F783" s="9" t="s">
+      <c r="G783" s="9" t="s">
         <v>1654</v>
-      </c>
-      <c r="G783" s="9" t="s">
-        <v>1655</v>
       </c>
       <c r="H783" s="10" t="n">
         <v>46197</v>
@@ -51539,7 +51599,7 @@
         <v>124</v>
       </c>
       <c r="G784" s="4" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H784" s="5" t="n">
         <v>46198</v>
@@ -51597,7 +51657,7 @@
         <v>75</v>
       </c>
       <c r="G785" s="9" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H785" s="10" t="n">
         <v>46199</v>
@@ -51655,7 +51715,7 @@
         <v>332</v>
       </c>
       <c r="G786" s="4" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H786" s="5" t="n">
         <v>46199</v>
@@ -51713,7 +51773,7 @@
         <v>1473</v>
       </c>
       <c r="G787" s="9" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H787" s="11" t="n">
         <v>46202.697662037</v>
@@ -51771,7 +51831,7 @@
         <v>249</v>
       </c>
       <c r="G788" s="4" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H788" s="6" t="n">
         <v>46203.350740741</v>
@@ -51829,7 +51889,7 @@
         <v>1102</v>
       </c>
       <c r="G789" s="9" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H789" s="11" t="n">
         <v>46203.360023148</v>
@@ -51887,7 +51947,7 @@
         <v>295</v>
       </c>
       <c r="G790" s="4" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H790" s="6" t="n">
         <v>46199.437291667</v>
@@ -51945,7 +52005,7 @@
         <v>262</v>
       </c>
       <c r="G791" s="9" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H791" s="11" t="n">
         <v>46199.61</v>
@@ -52003,7 +52063,7 @@
         <v>58</v>
       </c>
       <c r="G792" s="4" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H792" s="5" t="n">
         <v>46203</v>
@@ -52061,7 +52121,7 @@
         <v>1099</v>
       </c>
       <c r="G793" s="9" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H793" s="10" t="n">
         <v>46199</v>
@@ -52119,7 +52179,7 @@
         <v>1516</v>
       </c>
       <c r="G794" s="4" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H794" s="5" t="n">
         <v>46203</v>
@@ -52174,10 +52234,10 @@
         <v>24</v>
       </c>
       <c r="F795" s="9" t="s">
+        <v>1666</v>
+      </c>
+      <c r="G795" s="9" t="s">
         <v>1667</v>
-      </c>
-      <c r="G795" s="9" t="s">
-        <v>1668</v>
       </c>
       <c r="H795" s="11" t="n">
         <v>46203.499918981</v>
@@ -52235,7 +52295,7 @@
         <v>357</v>
       </c>
       <c r="G796" s="4" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H796" s="5" t="n">
         <v>46203</v>
@@ -52293,7 +52353,7 @@
         <v>955</v>
       </c>
       <c r="G797" s="9" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H797" s="11" t="n">
         <v>46204.462268519</v>
@@ -52345,13 +52405,13 @@
         <v>23</v>
       </c>
       <c r="E798" s="3" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="F798" s="4" t="s">
         <v>1298</v>
       </c>
       <c r="G798" s="4" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H798" s="5" t="n">
         <v>46205</v>
@@ -52406,22 +52466,22 @@
         <v>24</v>
       </c>
       <c r="F799" s="9" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="G799" s="9" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H799" s="10" t="n">
         <v>46205</v>
       </c>
       <c r="I799" s="9" t="s">
+        <v>1615</v>
+      </c>
+      <c r="J799" s="9" t="s">
         <v>1616</v>
       </c>
-      <c r="J799" s="9" t="s">
+      <c r="K799" s="9" t="s">
         <v>1617</v>
-      </c>
-      <c r="K799" s="9" t="s">
-        <v>1618</v>
       </c>
       <c r="L799" s="10"/>
       <c r="M799" s="10"/>
@@ -52435,7 +52495,7 @@
         <v>1455</v>
       </c>
       <c r="Q799" s="9" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="R799" s="12" t="n">
         <v>5000</v>
@@ -52464,22 +52524,22 @@
         <v>24</v>
       </c>
       <c r="F800" s="4" t="s">
+        <v>1673</v>
+      </c>
+      <c r="G800" s="4" t="s">
         <v>1674</v>
-      </c>
-      <c r="G800" s="4" t="s">
-        <v>1675</v>
       </c>
       <c r="H800" s="6" t="n">
         <v>46205.688020833</v>
       </c>
       <c r="I800" s="4" t="s">
+        <v>1675</v>
+      </c>
+      <c r="J800" s="4" t="s">
+        <v>1675</v>
+      </c>
+      <c r="K800" s="4" t="s">
         <v>1676</v>
-      </c>
-      <c r="J800" s="4" t="s">
-        <v>1676</v>
-      </c>
-      <c r="K800" s="4" t="s">
-        <v>1677</v>
       </c>
       <c r="L800" s="5"/>
       <c r="M800" s="5"/>
@@ -52525,7 +52585,7 @@
         <v>1427</v>
       </c>
       <c r="G801" s="9" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H801" s="11" t="n">
         <v>46205.676435185</v>
@@ -52580,10 +52640,10 @@
         <v>24</v>
       </c>
       <c r="F802" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G802" s="4" t="s">
         <v>1679</v>
-      </c>
-      <c r="G802" s="4" t="s">
-        <v>1680</v>
       </c>
       <c r="H802" s="5" t="n">
         <v>46206</v>
@@ -52641,7 +52701,7 @@
         <v>1570</v>
       </c>
       <c r="G803" s="9" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H803" s="10" t="n">
         <v>46206</v>
@@ -52699,7 +52759,7 @@
         <v>366</v>
       </c>
       <c r="G804" s="4" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H804" s="5" t="n">
         <v>46209</v>
@@ -52757,7 +52817,7 @@
         <v>829</v>
       </c>
       <c r="G805" s="9" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H805" s="11" t="n">
         <v>46210.393460648</v>
@@ -52812,10 +52872,10 @@
         <v>24</v>
       </c>
       <c r="F806" s="4" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G806" s="4" t="s">
         <v>1684</v>
-      </c>
-      <c r="G806" s="4" t="s">
-        <v>1685</v>
       </c>
       <c r="H806" s="5" t="n">
         <v>46210</v>
@@ -52867,25 +52927,25 @@
         <v>23</v>
       </c>
       <c r="E807" s="8" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F807" s="9" t="s">
         <v>1686</v>
       </c>
-      <c r="F807" s="9" t="s">
+      <c r="G807" s="9" t="s">
         <v>1687</v>
-      </c>
-      <c r="G807" s="9" t="s">
-        <v>1688</v>
       </c>
       <c r="H807" s="10" t="n">
         <v>46209</v>
       </c>
       <c r="I807" s="9" t="s">
+        <v>1688</v>
+      </c>
+      <c r="J807" s="9" t="s">
         <v>1689</v>
       </c>
-      <c r="J807" s="9" t="s">
+      <c r="K807" s="9" t="s">
         <v>1690</v>
-      </c>
-      <c r="K807" s="9" t="s">
-        <v>1691</v>
       </c>
       <c r="L807" s="10"/>
       <c r="M807" s="10"/>
@@ -52899,7 +52959,7 @@
         <v>1455</v>
       </c>
       <c r="Q807" s="9" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="R807" s="12" t="n">
         <v>57832.4</v>
@@ -52908,7 +52968,7 @@
         <v>44782.4</v>
       </c>
       <c r="T807" s="9" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="U807" s="9"/>
       <c r="V807" s="9"/>
@@ -52931,7 +52991,7 @@
         <v>1516</v>
       </c>
       <c r="G808" s="4" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H808" s="5" t="n">
         <v>46212</v>
@@ -52986,22 +53046,22 @@
         <v>24</v>
       </c>
       <c r="F809" s="9" t="s">
+        <v>1694</v>
+      </c>
+      <c r="G809" s="9" t="s">
         <v>1695</v>
-      </c>
-      <c r="G809" s="9" t="s">
-        <v>1696</v>
       </c>
       <c r="H809" s="10" t="n">
         <v>46209</v>
       </c>
       <c r="I809" s="9" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="J809" s="9" t="s">
+        <v>1696</v>
+      </c>
+      <c r="K809" s="9" t="s">
         <v>1697</v>
-      </c>
-      <c r="K809" s="9" t="s">
-        <v>1698</v>
       </c>
       <c r="L809" s="10"/>
       <c r="M809" s="10"/>
@@ -53015,7 +53075,7 @@
         <v>1455</v>
       </c>
       <c r="Q809" s="9" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="R809" s="12" t="n">
         <v>12246.14</v>
@@ -53024,7 +53084,7 @@
         <v>12246.14</v>
       </c>
       <c r="T809" s="9" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="U809" s="9"/>
       <c r="V809" s="9"/>
@@ -53044,22 +53104,22 @@
         <v>24</v>
       </c>
       <c r="F810" s="4" t="s">
+        <v>1698</v>
+      </c>
+      <c r="G810" s="4" t="s">
         <v>1699</v>
-      </c>
-      <c r="G810" s="4" t="s">
-        <v>1700</v>
       </c>
       <c r="H810" s="5" t="n">
         <v>46209</v>
       </c>
       <c r="I810" s="4" t="s">
+        <v>1700</v>
+      </c>
+      <c r="J810" s="4" t="s">
         <v>1701</v>
       </c>
-      <c r="J810" s="4" t="s">
+      <c r="K810" s="4" t="s">
         <v>1702</v>
-      </c>
-      <c r="K810" s="4" t="s">
-        <v>1703</v>
       </c>
       <c r="L810" s="5"/>
       <c r="M810" s="5"/>
@@ -53073,7 +53133,7 @@
         <v>1455</v>
       </c>
       <c r="Q810" s="4" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="R810" s="7" t="n">
         <v>12246.14</v>
@@ -53082,7 +53142,7 @@
         <v>12246.14</v>
       </c>
       <c r="T810" s="4" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="U810" s="4"/>
       <c r="V810" s="4"/>
@@ -53102,22 +53162,22 @@
         <v>24</v>
       </c>
       <c r="F811" s="9" t="s">
+        <v>1703</v>
+      </c>
+      <c r="G811" s="9" t="s">
         <v>1704</v>
-      </c>
-      <c r="G811" s="9" t="s">
-        <v>1705</v>
       </c>
       <c r="H811" s="10" t="n">
         <v>46212</v>
       </c>
       <c r="I811" s="9" t="s">
+        <v>1705</v>
+      </c>
+      <c r="J811" s="9" t="s">
         <v>1706</v>
       </c>
-      <c r="J811" s="9" t="s">
+      <c r="K811" s="9" t="s">
         <v>1707</v>
-      </c>
-      <c r="K811" s="9" t="s">
-        <v>1708</v>
       </c>
       <c r="L811" s="10"/>
       <c r="M811" s="10"/>
@@ -53131,7 +53191,7 @@
         <v>1455</v>
       </c>
       <c r="Q811" s="9" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="R811" s="12" t="n">
         <v>46556.88</v>
@@ -53140,7 +53200,7 @@
         <v>46556.88</v>
       </c>
       <c r="T811" s="9" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="U811" s="9"/>
       <c r="V811" s="9"/>
@@ -53160,10 +53220,10 @@
         <v>24</v>
       </c>
       <c r="F812" s="4" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G812" s="4" t="s">
         <v>1709</v>
-      </c>
-      <c r="G812" s="4" t="s">
-        <v>1710</v>
       </c>
       <c r="H812" s="6" t="n">
         <v>46212.609872685</v>
@@ -53218,10 +53278,10 @@
         <v>24</v>
       </c>
       <c r="F813" s="9" t="s">
+        <v>1710</v>
+      </c>
+      <c r="G813" s="9" t="s">
         <v>1711</v>
-      </c>
-      <c r="G813" s="9" t="s">
-        <v>1712</v>
       </c>
       <c r="H813" s="11" t="n">
         <v>46212.603854167</v>
@@ -53279,7 +53339,7 @@
         <v>328</v>
       </c>
       <c r="G814" s="4" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H814" s="6" t="n">
         <v>46212.706458333</v>
@@ -53337,7 +53397,7 @@
         <v>75</v>
       </c>
       <c r="G815" s="9" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H815" s="11" t="n">
         <v>46216.38931713</v>
@@ -53395,7 +53455,7 @@
         <v>389</v>
       </c>
       <c r="G816" s="4" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H816" s="6" t="n">
         <v>46213.494444444</v>
@@ -53453,7 +53513,7 @@
         <v>249</v>
       </c>
       <c r="G817" s="9" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H817" s="11" t="n">
         <v>46216.315104167</v>
@@ -53511,7 +53571,7 @@
         <v>1547</v>
       </c>
       <c r="G818" s="4" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H818" s="6" t="n">
         <v>46216.636458333</v>
@@ -53569,7 +53629,7 @@
         <v>1411</v>
       </c>
       <c r="G819" s="9" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H819" s="11" t="n">
         <v>46216.752118056</v>
@@ -53627,7 +53687,7 @@
         <v>164</v>
       </c>
       <c r="G820" s="4" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H820" s="6" t="n">
         <v>46216.772175926</v>
@@ -53685,7 +53745,7 @@
         <v>1488</v>
       </c>
       <c r="G821" s="9" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H821" s="10" t="n">
         <v>46217</v>
@@ -53743,7 +53803,7 @@
         <v>1547</v>
       </c>
       <c r="G822" s="4" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H822" s="6" t="n">
         <v>46217.426458333</v>
@@ -53801,7 +53861,7 @@
         <v>1373</v>
       </c>
       <c r="G823" s="9" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H823" s="10" t="n">
         <v>46217</v>
@@ -53856,10 +53916,10 @@
         <v>24</v>
       </c>
       <c r="F824" s="4" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="G824" s="4" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H824" s="5" t="n">
         <v>46219</v>
@@ -53914,10 +53974,10 @@
         <v>24</v>
       </c>
       <c r="F825" s="9" t="s">
+        <v>1723</v>
+      </c>
+      <c r="G825" s="9" t="s">
         <v>1724</v>
-      </c>
-      <c r="G825" s="9" t="s">
-        <v>1725</v>
       </c>
       <c r="H825" s="10" t="n">
         <v>46219</v>
@@ -53975,7 +54035,7 @@
         <v>1471</v>
       </c>
       <c r="G826" s="4" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H826" s="5" t="n">
         <v>46219</v>
@@ -54033,7 +54093,7 @@
         <v>332</v>
       </c>
       <c r="G827" s="9" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H827" s="11" t="n">
         <v>46218.657847222</v>
@@ -54088,10 +54148,10 @@
         <v>24</v>
       </c>
       <c r="F828" s="4" t="s">
+        <v>1727</v>
+      </c>
+      <c r="G828" s="4" t="s">
         <v>1728</v>
-      </c>
-      <c r="G828" s="4" t="s">
-        <v>1729</v>
       </c>
       <c r="H828" s="6" t="n">
         <v>46218.558854167</v>
@@ -54149,7 +54209,7 @@
         <v>484</v>
       </c>
       <c r="G829" s="9" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H829" s="11" t="n">
         <v>46218.501886574</v>
@@ -54201,13 +54261,13 @@
         <v>23</v>
       </c>
       <c r="E830" s="3" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="F830" s="4" t="s">
         <v>1264</v>
       </c>
       <c r="G830" s="4" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H830" s="5" t="n">
         <v>46219</v>
@@ -54265,7 +54325,7 @@
         <v>310</v>
       </c>
       <c r="G831" s="9" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H831" s="10" t="n">
         <v>46219</v>
@@ -54323,7 +54383,7 @@
         <v>969</v>
       </c>
       <c r="G832" s="4" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H832" s="5" t="n">
         <v>46219</v>
@@ -54378,22 +54438,22 @@
         <v>24</v>
       </c>
       <c r="F833" s="9" t="s">
+        <v>1734</v>
+      </c>
+      <c r="G833" s="9" t="s">
         <v>1735</v>
-      </c>
-      <c r="G833" s="9" t="s">
-        <v>1736</v>
       </c>
       <c r="H833" s="11" t="n">
         <v>46219.727233796</v>
       </c>
       <c r="I833" s="9" t="s">
+        <v>1736</v>
+      </c>
+      <c r="J833" s="9" t="s">
         <v>1737</v>
       </c>
-      <c r="J833" s="9" t="s">
+      <c r="K833" s="9" t="s">
         <v>1738</v>
-      </c>
-      <c r="K833" s="9" t="s">
-        <v>1739</v>
       </c>
       <c r="L833" s="10"/>
       <c r="M833" s="10"/>
@@ -54439,7 +54499,7 @@
         <v>1328</v>
       </c>
       <c r="G834" s="4" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H834" s="5" t="n">
         <v>46220</v>
@@ -54494,10 +54554,10 @@
         <v>24</v>
       </c>
       <c r="F835" s="9" t="s">
+        <v>1740</v>
+      </c>
+      <c r="G835" s="9" t="s">
         <v>1741</v>
-      </c>
-      <c r="G835" s="9" t="s">
-        <v>1742</v>
       </c>
       <c r="H835" s="10" t="n">
         <v>46223</v>
@@ -54552,10 +54612,10 @@
         <v>24</v>
       </c>
       <c r="F836" s="4" t="s">
+        <v>1742</v>
+      </c>
+      <c r="G836" s="4" t="s">
         <v>1743</v>
-      </c>
-      <c r="G836" s="4" t="s">
-        <v>1744</v>
       </c>
       <c r="H836" s="5" t="n">
         <v>46224</v>
@@ -54610,10 +54670,10 @@
         <v>24</v>
       </c>
       <c r="F837" s="9" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G837" s="9" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H837" s="10" t="n">
         <v>46225</v>
@@ -54671,7 +54731,7 @@
         <v>1264</v>
       </c>
       <c r="G838" s="4" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H838" s="5" t="n">
         <v>46224</v>
@@ -54729,7 +54789,7 @@
         <v>203</v>
       </c>
       <c r="G839" s="9" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H839" s="10" t="n">
         <v>46224</v>
@@ -54787,7 +54847,7 @@
         <v>310</v>
       </c>
       <c r="G840" s="4" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H840" s="5" t="n">
         <v>46224</v>
@@ -54842,10 +54902,10 @@
         <v>24</v>
       </c>
       <c r="F841" s="9" t="s">
+        <v>1748</v>
+      </c>
+      <c r="G841" s="9" t="s">
         <v>1749</v>
-      </c>
-      <c r="G841" s="9" t="s">
-        <v>1750</v>
       </c>
       <c r="H841" s="10" t="n">
         <v>46224</v>
@@ -54900,10 +54960,10 @@
         <v>24</v>
       </c>
       <c r="F842" s="4" t="s">
+        <v>1750</v>
+      </c>
+      <c r="G842" s="4" t="s">
         <v>1751</v>
-      </c>
-      <c r="G842" s="4" t="s">
-        <v>1752</v>
       </c>
       <c r="H842" s="5" t="n">
         <v>46224</v>
@@ -54958,10 +55018,10 @@
         <v>24</v>
       </c>
       <c r="F843" s="9" t="s">
+        <v>1752</v>
+      </c>
+      <c r="G843" s="9" t="s">
         <v>1753</v>
-      </c>
-      <c r="G843" s="9" t="s">
-        <v>1754</v>
       </c>
       <c r="H843" s="10" t="n">
         <v>46224</v>
@@ -55016,10 +55076,10 @@
         <v>24</v>
       </c>
       <c r="F844" s="4" t="s">
+        <v>1754</v>
+      </c>
+      <c r="G844" s="4" t="s">
         <v>1755</v>
-      </c>
-      <c r="G844" s="4" t="s">
-        <v>1756</v>
       </c>
       <c r="H844" s="5" t="n">
         <v>46225</v>
@@ -55074,22 +55134,22 @@
         <v>24</v>
       </c>
       <c r="F845" s="9" t="s">
+        <v>1756</v>
+      </c>
+      <c r="G845" s="9" t="s">
         <v>1757</v>
-      </c>
-      <c r="G845" s="9" t="s">
-        <v>1758</v>
       </c>
       <c r="H845" s="10" t="n">
         <v>46225</v>
       </c>
       <c r="I845" s="9" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="J845" s="9" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K845" s="9" t="s">
         <v>1759</v>
-      </c>
-      <c r="K845" s="9" t="s">
-        <v>1760</v>
       </c>
       <c r="L845" s="10"/>
       <c r="M845" s="10"/>
@@ -55132,22 +55192,22 @@
         <v>24</v>
       </c>
       <c r="F846" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G846" s="4" t="s">
         <v>1761</v>
-      </c>
-      <c r="G846" s="4" t="s">
-        <v>1762</v>
       </c>
       <c r="H846" s="5" t="n">
         <v>46226</v>
       </c>
       <c r="I846" s="4" t="s">
+        <v>1762</v>
+      </c>
+      <c r="J846" s="4" t="s">
+        <v>1762</v>
+      </c>
+      <c r="K846" s="4" t="s">
         <v>1763</v>
-      </c>
-      <c r="J846" s="4" t="s">
-        <v>1763</v>
-      </c>
-      <c r="K846" s="4" t="s">
-        <v>1764</v>
       </c>
       <c r="L846" s="5"/>
       <c r="M846" s="5"/>
@@ -55193,7 +55253,7 @@
         <v>592</v>
       </c>
       <c r="G847" s="9" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H847" s="10" t="n">
         <v>46226</v>
@@ -55251,7 +55311,7 @@
         <v>1179</v>
       </c>
       <c r="G848" s="4" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H848" s="5" t="n">
         <v>46227</v>
@@ -55309,7 +55369,7 @@
         <v>623</v>
       </c>
       <c r="G849" s="9" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H849" s="10" t="n">
         <v>46225</v>
@@ -55367,7 +55427,7 @@
         <v>310</v>
       </c>
       <c r="G850" s="4" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H850" s="5" t="n">
         <v>46226</v>
@@ -55422,10 +55482,10 @@
         <v>24</v>
       </c>
       <c r="F851" s="9" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G851" s="9" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H851" s="10" t="n">
         <v>46225</v>
@@ -55483,7 +55543,7 @@
         <v>581</v>
       </c>
       <c r="G852" s="4" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H852" s="5" t="n">
         <v>46224</v>
@@ -55541,7 +55601,7 @@
         <v>1516</v>
       </c>
       <c r="G853" s="9" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H853" s="10" t="n">
         <v>46230</v>
@@ -55596,22 +55656,22 @@
         <v>24</v>
       </c>
       <c r="F854" s="4" t="s">
+        <v>1771</v>
+      </c>
+      <c r="G854" s="4" t="s">
         <v>1772</v>
-      </c>
-      <c r="G854" s="4" t="s">
-        <v>1773</v>
       </c>
       <c r="H854" s="5" t="n">
         <v>46227</v>
       </c>
       <c r="I854" s="4" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="J854" s="4" t="s">
+        <v>1773</v>
+      </c>
+      <c r="K854" s="4" t="s">
         <v>1774</v>
-      </c>
-      <c r="K854" s="4" t="s">
-        <v>1775</v>
       </c>
       <c r="L854" s="5"/>
       <c r="M854" s="5"/>
@@ -55651,25 +55711,25 @@
         <v>23</v>
       </c>
       <c r="E855" s="8" t="s">
+        <v>1775</v>
+      </c>
+      <c r="F855" s="9" t="s">
         <v>1776</v>
       </c>
-      <c r="F855" s="9" t="s">
+      <c r="G855" s="9" t="s">
         <v>1777</v>
-      </c>
-      <c r="G855" s="9" t="s">
-        <v>1778</v>
       </c>
       <c r="H855" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I855" s="9" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="J855" s="9" t="s">
+        <v>1778</v>
+      </c>
+      <c r="K855" s="9" t="s">
         <v>1779</v>
-      </c>
-      <c r="K855" s="9" t="s">
-        <v>1780</v>
       </c>
       <c r="L855" s="10"/>
       <c r="M855" s="10"/>
@@ -55683,7 +55743,7 @@
         <v>1455</v>
       </c>
       <c r="Q855" s="9" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="R855" s="12" t="n">
         <v>176352</v>
@@ -55715,7 +55775,7 @@
         <v>276</v>
       </c>
       <c r="G856" s="4" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H856" s="5" t="n">
         <v>46230</v>
@@ -55773,7 +55833,7 @@
         <v>1280</v>
       </c>
       <c r="G857" s="9" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H857" s="10" t="n">
         <v>46231</v>
@@ -55831,7 +55891,7 @@
         <v>592</v>
       </c>
       <c r="G858" s="4" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H858" s="5" t="n">
         <v>46230</v>
@@ -55889,7 +55949,7 @@
         <v>1264</v>
       </c>
       <c r="G859" s="9" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H859" s="10" t="n">
         <v>46231</v>
@@ -55944,10 +56004,10 @@
         <v>24</v>
       </c>
       <c r="F860" s="4" t="s">
+        <v>1784</v>
+      </c>
+      <c r="G860" s="4" t="s">
         <v>1785</v>
-      </c>
-      <c r="G860" s="4" t="s">
-        <v>1786</v>
       </c>
       <c r="H860" s="5" t="n">
         <v>46230</v>
@@ -55999,25 +56059,25 @@
         <v>23</v>
       </c>
       <c r="E861" s="8" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F861" s="9" t="s">
         <v>1787</v>
       </c>
-      <c r="F861" s="9" t="s">
+      <c r="G861" s="9" t="s">
         <v>1788</v>
-      </c>
-      <c r="G861" s="9" t="s">
-        <v>1789</v>
       </c>
       <c r="H861" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I861" s="9" t="s">
+        <v>1789</v>
+      </c>
+      <c r="J861" s="9" t="s">
         <v>1790</v>
       </c>
-      <c r="J861" s="9" t="s">
+      <c r="K861" s="9" t="s">
         <v>1791</v>
-      </c>
-      <c r="K861" s="9" t="s">
-        <v>1792</v>
       </c>
       <c r="L861" s="10"/>
       <c r="M861" s="10"/>
@@ -56031,7 +56091,7 @@
         <v>1455</v>
       </c>
       <c r="Q861" s="9" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="R861" s="12" t="n">
         <v>39463.12</v>
@@ -56040,7 +56100,7 @@
         <v>16215.2</v>
       </c>
       <c r="T861" s="9" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="U861" s="9"/>
       <c r="V861" s="9"/>
@@ -56060,22 +56120,22 @@
         <v>24</v>
       </c>
       <c r="F862" s="4" t="s">
+        <v>1792</v>
+      </c>
+      <c r="G862" s="4" t="s">
         <v>1793</v>
-      </c>
-      <c r="G862" s="4" t="s">
-        <v>1794</v>
       </c>
       <c r="H862" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="I862" s="4" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="J862" s="4" t="s">
+        <v>1794</v>
+      </c>
+      <c r="K862" s="4" t="s">
         <v>1795</v>
-      </c>
-      <c r="K862" s="4" t="s">
-        <v>1796</v>
       </c>
       <c r="L862" s="5"/>
       <c r="M862" s="5"/>
@@ -56121,7 +56181,7 @@
         <v>859</v>
       </c>
       <c r="G863" s="9" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H863" s="10" t="n">
         <v>46230</v>
@@ -56179,7 +56239,7 @@
         <v>262</v>
       </c>
       <c r="G864" s="4" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H864" s="5" t="n">
         <v>46230</v>
@@ -56234,22 +56294,22 @@
         <v>24</v>
       </c>
       <c r="F865" s="9" t="s">
+        <v>1798</v>
+      </c>
+      <c r="G865" s="9" t="s">
         <v>1799</v>
-      </c>
-      <c r="G865" s="9" t="s">
-        <v>1800</v>
       </c>
       <c r="H865" s="10" t="n">
         <v>46230</v>
       </c>
       <c r="I865" s="9" t="s">
+        <v>1800</v>
+      </c>
+      <c r="J865" s="9" t="s">
+        <v>1800</v>
+      </c>
+      <c r="K865" s="9" t="s">
         <v>1801</v>
-      </c>
-      <c r="J865" s="9" t="s">
-        <v>1801</v>
-      </c>
-      <c r="K865" s="9" t="s">
-        <v>1802</v>
       </c>
       <c r="L865" s="10"/>
       <c r="M865" s="10"/>
@@ -56295,7 +56355,7 @@
         <v>490</v>
       </c>
       <c r="G866" s="4" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H866" s="5" t="n">
         <v>46231</v>
@@ -56353,7 +56413,7 @@
         <v>521</v>
       </c>
       <c r="G867" s="9" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H867" s="10" t="n">
         <v>46232</v>
@@ -56411,7 +56471,7 @@
         <v>1547</v>
       </c>
       <c r="G868" s="4" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="H868" s="5" t="n">
         <v>46231</v>
@@ -56469,7 +56529,7 @@
         <v>1133</v>
       </c>
       <c r="G869" s="9" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="H869" s="10" t="n">
         <v>46233</v>
@@ -56524,10 +56584,10 @@
         <v>24</v>
       </c>
       <c r="F870" s="4" t="s">
+        <v>1806</v>
+      </c>
+      <c r="G870" s="4" t="s">
         <v>1807</v>
-      </c>
-      <c r="G870" s="4" t="s">
-        <v>1808</v>
       </c>
       <c r="H870" s="5" t="n">
         <v>46232</v>
@@ -56585,7 +56645,7 @@
         <v>355</v>
       </c>
       <c r="G871" s="9" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H871" s="10" t="n">
         <v>46232</v>
@@ -56643,7 +56703,7 @@
         <v>351</v>
       </c>
       <c r="G872" s="4" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="H872" s="5" t="n">
         <v>46232</v>
@@ -56701,7 +56761,7 @@
         <v>945</v>
       </c>
       <c r="G873" s="9" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H873" s="10" t="n">
         <v>46232</v>
@@ -56759,7 +56819,7 @@
         <v>262</v>
       </c>
       <c r="G874" s="4" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H874" s="5" t="n">
         <v>46231</v>
@@ -56817,7 +56877,7 @@
         <v>1264</v>
       </c>
       <c r="G875" s="9" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H875" s="10" t="n">
         <v>46232</v>
@@ -56869,13 +56929,13 @@
         <v>23</v>
       </c>
       <c r="E876" s="3" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F876" s="4" t="s">
         <v>1814</v>
       </c>
-      <c r="F876" s="4" t="s">
+      <c r="G876" s="4" t="s">
         <v>1815</v>
-      </c>
-      <c r="G876" s="4" t="s">
-        <v>1816</v>
       </c>
       <c r="H876" s="5" t="n">
         <v>46232</v>
@@ -56933,7 +56993,7 @@
         <v>75</v>
       </c>
       <c r="G877" s="9" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H877" s="10" t="n">
         <v>46232</v>
@@ -56991,7 +57051,7 @@
         <v>408</v>
       </c>
       <c r="G878" s="4" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="H878" s="5" t="n">
         <v>46232</v>
@@ -57008,7 +57068,7 @@
       <c r="L878" s="5"/>
       <c r="M878" s="5"/>
       <c r="N878" s="4" t="s">
-        <v>1573</v>
+        <v>1818</v>
       </c>
       <c r="O878" s="6" t="n">
         <v>46233.675736539</v>
@@ -57394,7 +57454,7 @@
         <v>24</v>
       </c>
       <c r="F885" s="9" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="G885" s="9" t="s">
         <v>1830</v>
@@ -57510,7 +57570,7 @@
         <v>24</v>
       </c>
       <c r="F887" s="9" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="G887" s="9" t="s">
         <v>1832</v>
@@ -57519,13 +57579,13 @@
         <v>46233</v>
       </c>
       <c r="I887" s="9" t="s">
+        <v>1605</v>
+      </c>
+      <c r="J887" s="9" t="s">
         <v>1606</v>
       </c>
-      <c r="J887" s="9" t="s">
+      <c r="K887" s="9" t="s">
         <v>1607</v>
-      </c>
-      <c r="K887" s="9" t="s">
-        <v>1608</v>
       </c>
       <c r="L887" s="10"/>
       <c r="M887" s="10"/>
@@ -57568,7 +57628,7 @@
         <v>24</v>
       </c>
       <c r="F888" s="4" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="G888" s="4" t="s">
         <v>1833</v>
@@ -57577,13 +57637,13 @@
         <v>46234</v>
       </c>
       <c r="I888" s="4" t="s">
+        <v>1736</v>
+      </c>
+      <c r="J888" s="4" t="s">
         <v>1737</v>
       </c>
-      <c r="J888" s="4" t="s">
+      <c r="K888" s="4" t="s">
         <v>1738</v>
-      </c>
-      <c r="K888" s="4" t="s">
-        <v>1739</v>
       </c>
       <c r="L888" s="5"/>
       <c r="M888" s="5"/>
@@ -58960,7 +59020,7 @@
         <v>24</v>
       </c>
       <c r="F912" s="4" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="G912" s="4" t="s">
         <v>1865</v>
@@ -58969,13 +59029,13 @@
         <v>46246.935729167</v>
       </c>
       <c r="I912" s="4" t="s">
+        <v>1675</v>
+      </c>
+      <c r="J912" s="4" t="s">
+        <v>1675</v>
+      </c>
+      <c r="K912" s="4" t="s">
         <v>1676</v>
-      </c>
-      <c r="J912" s="4" t="s">
-        <v>1676</v>
-      </c>
-      <c r="K912" s="4" t="s">
-        <v>1677</v>
       </c>
       <c r="L912" s="5"/>
       <c r="M912" s="5"/>
@@ -60198,7 +60258,7 @@
       <c r="L933" s="10"/>
       <c r="M933" s="10"/>
       <c r="N933" s="9" t="s">
-        <v>1573</v>
+        <v>1818</v>
       </c>
       <c r="O933" s="11" t="n">
         <v>46260.463491435</v>
@@ -60581,7 +60641,7 @@
         <v>23</v>
       </c>
       <c r="E940" s="3" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="F940" s="4" t="s">
         <v>408</v>
@@ -60778,7 +60838,7 @@
       <c r="L943" s="10"/>
       <c r="M943" s="10"/>
       <c r="N943" s="9" t="s">
-        <v>1573</v>
+        <v>1818</v>
       </c>
       <c r="O943" s="11" t="n">
         <v>46262.58240625</v>
@@ -60813,13 +60873,13 @@
         <v>23</v>
       </c>
       <c r="E944" s="3" t="s">
-        <v>24</v>
+        <v>1916</v>
       </c>
       <c r="F944" s="4" t="s">
         <v>211</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="H944" s="6" t="n">
         <v>46261.624131944</v>
@@ -60836,7 +60896,7 @@
       <c r="L944" s="5"/>
       <c r="M944" s="5"/>
       <c r="N944" s="4" t="s">
-        <v>29</v>
+        <v>1288</v>
       </c>
       <c r="O944" s="6" t="n">
         <v>46262.582538507</v>
@@ -60851,7 +60911,7 @@
         <v>44352</v>
       </c>
       <c r="S944" s="7" t="n">
-        <v>44352</v>
+        <v>22176</v>
       </c>
       <c r="T944" s="4" t="s">
         <v>32</v>
@@ -60871,7 +60931,7 @@
         <v>23</v>
       </c>
       <c r="E945" s="8" t="s">
-        <v>1917</v>
+        <v>24</v>
       </c>
       <c r="F945" s="9" t="s">
         <v>521</v>
@@ -60894,7 +60954,7 @@
       <c r="L945" s="10"/>
       <c r="M945" s="10"/>
       <c r="N945" s="9" t="s">
-        <v>1573</v>
+        <v>29</v>
       </c>
       <c r="O945" s="11" t="n">
         <v>46262.582696609</v>
@@ -60909,7 +60969,7 @@
         <v>5972</v>
       </c>
       <c r="S945" s="12" t="n">
-        <v>4806</v>
+        <v>5972</v>
       </c>
       <c r="T945" s="9" t="s">
         <v>32</v>
@@ -61103,30 +61163,30 @@
         <v>23</v>
       </c>
       <c r="E949" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F949" s="9" t="s">
+        <v>1736</v>
+      </c>
+      <c r="G949" s="9" t="s">
         <v>1922</v>
-      </c>
-      <c r="F949" s="9" t="s">
-        <v>1737</v>
-      </c>
-      <c r="G949" s="9" t="s">
-        <v>1923</v>
       </c>
       <c r="H949" s="10" t="n">
         <v>46265</v>
       </c>
       <c r="I949" s="9" t="s">
+        <v>1736</v>
+      </c>
+      <c r="J949" s="9" t="s">
         <v>1737</v>
       </c>
-      <c r="J949" s="9" t="s">
+      <c r="K949" s="9" t="s">
         <v>1738</v>
-      </c>
-      <c r="K949" s="9" t="s">
-        <v>1739</v>
       </c>
       <c r="L949" s="10"/>
       <c r="M949" s="10"/>
       <c r="N949" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O949" s="11" t="n">
         <v>46265.656787882</v>
@@ -61141,7 +61201,7 @@
         <v>201401</v>
       </c>
       <c r="S949" s="12" t="n">
-        <v>130260</v>
+        <v>201401</v>
       </c>
       <c r="T949" s="9" t="s">
         <v>32</v>
@@ -61161,13 +61221,13 @@
         <v>23</v>
       </c>
       <c r="E950" s="3" t="s">
+        <v>1923</v>
+      </c>
+      <c r="F950" s="4" t="s">
+        <v>1641</v>
+      </c>
+      <c r="G950" s="4" t="s">
         <v>1924</v>
-      </c>
-      <c r="F950" s="4" t="s">
-        <v>1642</v>
-      </c>
-      <c r="G950" s="4" t="s">
-        <v>1925</v>
       </c>
       <c r="H950" s="5" t="n">
         <v>46265</v>
@@ -61199,7 +61259,7 @@
         <v>63150.72</v>
       </c>
       <c r="S950" s="7" t="n">
-        <v>11970.72</v>
+        <v>21570.72</v>
       </c>
       <c r="T950" s="4" t="s">
         <v>32</v>
@@ -61219,13 +61279,13 @@
         <v>23</v>
       </c>
       <c r="E951" s="8" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F951" s="9" t="s">
         <v>619</v>
       </c>
       <c r="G951" s="9" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H951" s="11" t="n">
         <v>46265.756805556</v>
@@ -61277,13 +61337,13 @@
         <v>23</v>
       </c>
       <c r="E952" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F952" s="4" t="s">
         <v>103</v>
       </c>
       <c r="G952" s="4" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H952" s="6" t="n">
         <v>46262.6721875</v>
@@ -61300,7 +61360,7 @@
       <c r="L952" s="5"/>
       <c r="M952" s="5"/>
       <c r="N952" s="4" t="s">
-        <v>1573</v>
+        <v>1818</v>
       </c>
       <c r="O952" s="6" t="n">
         <v>46266.68744059</v>
@@ -61315,7 +61375,7 @@
         <v>44000</v>
       </c>
       <c r="S952" s="7" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T952" s="4" t="s">
         <v>32</v>
@@ -61335,13 +61395,13 @@
         <v>23</v>
       </c>
       <c r="E953" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F953" s="9" t="s">
         <v>814</v>
       </c>
       <c r="G953" s="9" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H953" s="11" t="n">
         <v>46265.738773148</v>
@@ -61358,7 +61418,7 @@
       <c r="L953" s="10"/>
       <c r="M953" s="10"/>
       <c r="N953" s="9" t="s">
-        <v>1573</v>
+        <v>29</v>
       </c>
       <c r="O953" s="11" t="n">
         <v>46266.688499306</v>
@@ -61370,10 +61430,10 @@
         <v>142</v>
       </c>
       <c r="R953" s="12" t="n">
-        <v>27007.74</v>
+        <v>27379.32</v>
       </c>
       <c r="S953" s="12" t="n">
-        <v>0</v>
+        <v>27379.32</v>
       </c>
       <c r="T953" s="9" t="s">
         <v>32</v>
@@ -61399,7 +61459,7 @@
         <v>484</v>
       </c>
       <c r="G954" s="4" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H954" s="6" t="n">
         <v>46265.406400463</v>
@@ -61457,7 +61517,7 @@
         <v>482</v>
       </c>
       <c r="G955" s="9" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H955" s="11" t="n">
         <v>46262.643506944</v>
@@ -61515,7 +61575,7 @@
         <v>744</v>
       </c>
       <c r="G956" s="4" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="H956" s="6" t="n">
         <v>46262.644305556</v>
@@ -61567,13 +61627,13 @@
         <v>23</v>
       </c>
       <c r="E957" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F957" s="9" t="s">
         <v>1179</v>
       </c>
       <c r="G957" s="9" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="H957" s="11" t="n">
         <v>46262.617488426</v>
@@ -61590,7 +61650,7 @@
       <c r="L957" s="10"/>
       <c r="M957" s="10"/>
       <c r="N957" s="9" t="s">
-        <v>1573</v>
+        <v>29</v>
       </c>
       <c r="O957" s="11" t="n">
         <v>46266.693244294</v>
@@ -61605,7 +61665,7 @@
         <v>32787.96</v>
       </c>
       <c r="S957" s="12" t="n">
-        <v>0</v>
+        <v>32787.96</v>
       </c>
       <c r="T957" s="9" t="s">
         <v>88</v>
@@ -61631,7 +61691,7 @@
         <v>1527</v>
       </c>
       <c r="G958" s="4" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="H958" s="6" t="n">
         <v>46262.337835648</v>
@@ -61689,7 +61749,7 @@
         <v>1516</v>
       </c>
       <c r="G959" s="9" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="H959" s="10" t="n">
         <v>46266</v>
@@ -61744,10 +61804,10 @@
         <v>24</v>
       </c>
       <c r="F960" s="4" t="s">
+        <v>1935</v>
+      </c>
+      <c r="G960" s="4" t="s">
         <v>1936</v>
-      </c>
-      <c r="G960" s="4" t="s">
-        <v>1937</v>
       </c>
       <c r="H960" s="5" t="n">
         <v>46265</v>
@@ -61802,22 +61862,22 @@
         <v>24</v>
       </c>
       <c r="F961" s="9" t="s">
+        <v>1937</v>
+      </c>
+      <c r="G961" s="9" t="s">
         <v>1938</v>
-      </c>
-      <c r="G961" s="9" t="s">
-        <v>1939</v>
       </c>
       <c r="H961" s="10" t="n">
         <v>46266</v>
       </c>
       <c r="I961" s="9" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="J961" s="9" t="s">
+        <v>1939</v>
+      </c>
+      <c r="K961" s="9" t="s">
         <v>1940</v>
-      </c>
-      <c r="K961" s="9" t="s">
-        <v>1941</v>
       </c>
       <c r="L961" s="10"/>
       <c r="M961" s="10"/>
@@ -61860,22 +61920,22 @@
         <v>24</v>
       </c>
       <c r="F962" s="4" t="s">
+        <v>1941</v>
+      </c>
+      <c r="G962" s="4" t="s">
         <v>1942</v>
-      </c>
-      <c r="G962" s="4" t="s">
-        <v>1943</v>
       </c>
       <c r="H962" s="5" t="n">
         <v>46265</v>
       </c>
       <c r="I962" s="4" t="s">
+        <v>1943</v>
+      </c>
+      <c r="J962" s="4" t="s">
         <v>1944</v>
       </c>
-      <c r="J962" s="4" t="s">
+      <c r="K962" s="4" t="s">
         <v>1945</v>
-      </c>
-      <c r="K962" s="4" t="s">
-        <v>1946</v>
       </c>
       <c r="L962" s="5"/>
       <c r="M962" s="5"/>
@@ -61915,13 +61975,13 @@
         <v>23</v>
       </c>
       <c r="E963" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F963" s="9" t="s">
         <v>945</v>
       </c>
       <c r="G963" s="9" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="H963" s="11" t="n">
         <v>46267.438217593</v>
@@ -61938,7 +61998,7 @@
       <c r="L963" s="10"/>
       <c r="M963" s="10"/>
       <c r="N963" s="9" t="s">
-        <v>1573</v>
+        <v>29</v>
       </c>
       <c r="O963" s="11" t="n">
         <v>46267.661274965</v>
@@ -61953,7 +62013,7 @@
         <v>14178</v>
       </c>
       <c r="S963" s="12" t="n">
-        <v>0</v>
+        <v>14178</v>
       </c>
       <c r="T963" s="9" t="s">
         <v>32</v>
@@ -61979,7 +62039,7 @@
         <v>310</v>
       </c>
       <c r="G964" s="4" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="H964" s="5" t="n">
         <v>46269</v>
@@ -62019,35 +62079,847 @@
       <c r="U964" s="4"/>
       <c r="V964" s="4"/>
     </row>
-    <row r="965" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A965" s="13" t="n">
-        <v>963</v>
-      </c>
-      <c r="B965" s="14"/>
-      <c r="C965" s="14"/>
-      <c r="D965" s="14"/>
-      <c r="E965" s="14"/>
-      <c r="F965" s="14"/>
-      <c r="G965" s="14"/>
-      <c r="H965" s="14"/>
-      <c r="I965" s="14"/>
-      <c r="J965" s="14"/>
-      <c r="K965" s="14"/>
-      <c r="L965" s="14"/>
-      <c r="M965" s="14"/>
-      <c r="N965" s="14"/>
-      <c r="O965" s="14"/>
-      <c r="P965" s="14"/>
-      <c r="Q965" s="14"/>
-      <c r="R965" s="15" t="n">
-        <v>58095466.1826</v>
-      </c>
-      <c r="S965" s="15" t="n">
-        <v>57074871.5226</v>
-      </c>
-      <c r="T965" s="14"/>
-      <c r="U965" s="14"/>
-      <c r="V965" s="16"/>
+    <row r="965" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A965" s="8" t="n">
+        <v>1034</v>
+      </c>
+      <c r="B965" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C965" s="9"/>
+      <c r="D965" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E965" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F965" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G965" s="9" t="s">
+        <v>1948</v>
+      </c>
+      <c r="H965" s="11" t="n">
+        <v>46269.745752315</v>
+      </c>
+      <c r="I965" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="J965" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="K965" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="L965" s="10"/>
+      <c r="M965" s="10"/>
+      <c r="N965" s="9" t="s">
+        <v>1818</v>
+      </c>
+      <c r="O965" s="11" t="n">
+        <v>46274.36010478</v>
+      </c>
+      <c r="P965" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q965" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R965" s="12" t="n">
+        <v>37380</v>
+      </c>
+      <c r="S965" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T965" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U965" s="9"/>
+      <c r="V965" s="9"/>
+    </row>
+    <row r="966" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A966" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="B966" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C966" s="4"/>
+      <c r="D966" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E966" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F966" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="G966" s="4" t="s">
+        <v>1949</v>
+      </c>
+      <c r="H966" s="6" t="n">
+        <v>46269.693969907</v>
+      </c>
+      <c r="I966" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="J966" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="K966" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="L966" s="5"/>
+      <c r="M966" s="5"/>
+      <c r="N966" s="4" t="s">
+        <v>1818</v>
+      </c>
+      <c r="O966" s="6" t="n">
+        <v>46274.360279861</v>
+      </c>
+      <c r="P966" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q966" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="R966" s="7" t="n">
+        <v>9591</v>
+      </c>
+      <c r="S966" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T966" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U966" s="4"/>
+      <c r="V966" s="4"/>
+    </row>
+    <row r="967" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A967" s="8" t="n">
+        <v>1036</v>
+      </c>
+      <c r="B967" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C967" s="9"/>
+      <c r="D967" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E967" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F967" s="9" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G967" s="9" t="s">
+        <v>1950</v>
+      </c>
+      <c r="H967" s="11" t="n">
+        <v>46269.459189815</v>
+      </c>
+      <c r="I967" s="9" t="s">
+        <v>1079</v>
+      </c>
+      <c r="J967" s="9" t="s">
+        <v>1080</v>
+      </c>
+      <c r="K967" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="L967" s="10"/>
+      <c r="M967" s="10"/>
+      <c r="N967" s="9" t="s">
+        <v>1818</v>
+      </c>
+      <c r="O967" s="11" t="n">
+        <v>46274.360427546</v>
+      </c>
+      <c r="P967" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q967" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R967" s="12" t="n">
+        <v>18393</v>
+      </c>
+      <c r="S967" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T967" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U967" s="9"/>
+      <c r="V967" s="9"/>
+    </row>
+    <row r="968" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A968" s="3" t="n">
+        <v>1037</v>
+      </c>
+      <c r="B968" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C968" s="4"/>
+      <c r="D968" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E968" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F968" s="4" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G968" s="4" t="s">
+        <v>1951</v>
+      </c>
+      <c r="H968" s="6" t="n">
+        <v>46268.442615741</v>
+      </c>
+      <c r="I968" s="4" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J968" s="4" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K968" s="4" t="s">
+        <v>1231</v>
+      </c>
+      <c r="L968" s="5"/>
+      <c r="M968" s="5"/>
+      <c r="N968" s="4" t="s">
+        <v>1818</v>
+      </c>
+      <c r="O968" s="6" t="n">
+        <v>46274.360582905</v>
+      </c>
+      <c r="P968" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q968" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R968" s="7" t="n">
+        <v>59790</v>
+      </c>
+      <c r="S968" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T968" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U968" s="4"/>
+      <c r="V968" s="4"/>
+    </row>
+    <row r="969" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A969" s="8" t="n">
+        <v>1038</v>
+      </c>
+      <c r="B969" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C969" s="9"/>
+      <c r="D969" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E969" s="8" t="s">
+        <v>1952</v>
+      </c>
+      <c r="F969" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G969" s="9" t="s">
+        <v>1953</v>
+      </c>
+      <c r="H969" s="10" t="n">
+        <v>46268</v>
+      </c>
+      <c r="I969" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J969" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="K969" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="L969" s="10"/>
+      <c r="M969" s="10"/>
+      <c r="N969" s="9" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O969" s="11" t="n">
+        <v>46274.365774919</v>
+      </c>
+      <c r="P969" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q969" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="R969" s="12" t="n">
+        <v>3326.18</v>
+      </c>
+      <c r="S969" s="12" t="n">
+        <v>1081.68</v>
+      </c>
+      <c r="T969" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U969" s="9"/>
+      <c r="V969" s="9"/>
+    </row>
+    <row r="970" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A970" s="3" t="n">
+        <v>1039</v>
+      </c>
+      <c r="B970" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C970" s="4"/>
+      <c r="D970" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E970" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F970" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="G970" s="4" t="s">
+        <v>1954</v>
+      </c>
+      <c r="H970" s="5" t="n">
+        <v>46268</v>
+      </c>
+      <c r="I970" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="J970" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="K970" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="L970" s="5"/>
+      <c r="M970" s="5"/>
+      <c r="N970" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O970" s="6" t="n">
+        <v>46274.369346678</v>
+      </c>
+      <c r="P970" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q970" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="R970" s="7" t="n">
+        <v>5818.84</v>
+      </c>
+      <c r="S970" s="7" t="n">
+        <v>5818.84</v>
+      </c>
+      <c r="T970" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U970" s="4"/>
+      <c r="V970" s="4"/>
+    </row>
+    <row r="971" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A971" s="8" t="n">
+        <v>1040</v>
+      </c>
+      <c r="B971" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C971" s="9"/>
+      <c r="D971" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E971" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F971" s="9" t="s">
+        <v>1955</v>
+      </c>
+      <c r="G971" s="9" t="s">
+        <v>1956</v>
+      </c>
+      <c r="H971" s="10" t="n">
+        <v>46273</v>
+      </c>
+      <c r="I971" s="9" t="s">
+        <v>1306</v>
+      </c>
+      <c r="J971" s="9" t="s">
+        <v>1307</v>
+      </c>
+      <c r="K971" s="9" t="s">
+        <v>1308</v>
+      </c>
+      <c r="L971" s="10"/>
+      <c r="M971" s="10"/>
+      <c r="N971" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O971" s="11" t="n">
+        <v>46274.372697454</v>
+      </c>
+      <c r="P971" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q971" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="R971" s="12" t="n">
+        <v>18939.52</v>
+      </c>
+      <c r="S971" s="12" t="n">
+        <v>18939.52</v>
+      </c>
+      <c r="T971" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="U971" s="9"/>
+      <c r="V971" s="9"/>
+    </row>
+    <row r="972" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A972" s="3" t="n">
+        <v>1041</v>
+      </c>
+      <c r="B972" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C972" s="4"/>
+      <c r="D972" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E972" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F972" s="4" t="s">
+        <v>1264</v>
+      </c>
+      <c r="G972" s="4" t="s">
+        <v>1957</v>
+      </c>
+      <c r="H972" s="5" t="n">
+        <v>46273</v>
+      </c>
+      <c r="I972" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="J972" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="K972" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="L972" s="5"/>
+      <c r="M972" s="5"/>
+      <c r="N972" s="4" t="s">
+        <v>1818</v>
+      </c>
+      <c r="O972" s="6" t="n">
+        <v>46274.466218981</v>
+      </c>
+      <c r="P972" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q972" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="R972" s="7" t="n">
+        <v>127920.76</v>
+      </c>
+      <c r="S972" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T972" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U972" s="4"/>
+      <c r="V972" s="4"/>
+    </row>
+    <row r="973" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A973" s="8" t="n">
+        <v>1042</v>
+      </c>
+      <c r="B973" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C973" s="9"/>
+      <c r="D973" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E973" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F973" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="G973" s="9" t="s">
+        <v>1958</v>
+      </c>
+      <c r="H973" s="11" t="n">
+        <v>46273.758136574</v>
+      </c>
+      <c r="I973" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="J973" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="K973" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="L973" s="10"/>
+      <c r="M973" s="10"/>
+      <c r="N973" s="9" t="s">
+        <v>1818</v>
+      </c>
+      <c r="O973" s="11" t="n">
+        <v>46274.621396412</v>
+      </c>
+      <c r="P973" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q973" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R973" s="12" t="n">
+        <v>193050</v>
+      </c>
+      <c r="S973" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T973" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U973" s="9"/>
+      <c r="V973" s="9"/>
+    </row>
+    <row r="974" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A974" s="3" t="n">
+        <v>1043</v>
+      </c>
+      <c r="B974" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C974" s="4"/>
+      <c r="D974" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E974" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F974" s="4" t="s">
+        <v>1959</v>
+      </c>
+      <c r="G974" s="4" t="s">
+        <v>1960</v>
+      </c>
+      <c r="H974" s="6" t="n">
+        <v>46273.740416667</v>
+      </c>
+      <c r="I974" s="4" t="s">
+        <v>1959</v>
+      </c>
+      <c r="J974" s="4" t="s">
+        <v>1961</v>
+      </c>
+      <c r="K974" s="4" t="s">
+        <v>1962</v>
+      </c>
+      <c r="L974" s="5"/>
+      <c r="M974" s="5"/>
+      <c r="N974" s="4" t="s">
+        <v>1818</v>
+      </c>
+      <c r="O974" s="6" t="n">
+        <v>46274.621603935</v>
+      </c>
+      <c r="P974" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q974" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R974" s="7" t="n">
+        <v>1602</v>
+      </c>
+      <c r="S974" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T974" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U974" s="4"/>
+      <c r="V974" s="4"/>
+    </row>
+    <row r="975" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A975" s="8" t="n">
+        <v>1044</v>
+      </c>
+      <c r="B975" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C975" s="9"/>
+      <c r="D975" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E975" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F975" s="9" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G975" s="9" t="s">
+        <v>1963</v>
+      </c>
+      <c r="H975" s="11" t="n">
+        <v>46273.780162037</v>
+      </c>
+      <c r="I975" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="J975" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="K975" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="L975" s="10"/>
+      <c r="M975" s="10"/>
+      <c r="N975" s="9" t="s">
+        <v>1818</v>
+      </c>
+      <c r="O975" s="11" t="n">
+        <v>46274.62173441</v>
+      </c>
+      <c r="P975" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q975" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R975" s="12" t="n">
+        <v>2293.2</v>
+      </c>
+      <c r="S975" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T975" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U975" s="9"/>
+      <c r="V975" s="9"/>
+    </row>
+    <row r="976" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A976" s="3" t="n">
+        <v>1045</v>
+      </c>
+      <c r="B976" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C976" s="4"/>
+      <c r="D976" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E976" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F976" s="4" t="s">
+        <v>1964</v>
+      </c>
+      <c r="G976" s="4" t="s">
+        <v>1965</v>
+      </c>
+      <c r="H976" s="6" t="n">
+        <v>46274.442685185</v>
+      </c>
+      <c r="I976" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J976" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K976" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="L976" s="5"/>
+      <c r="M976" s="5"/>
+      <c r="N976" s="4" t="s">
+        <v>1818</v>
+      </c>
+      <c r="O976" s="6" t="n">
+        <v>46274.622029167</v>
+      </c>
+      <c r="P976" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q976" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R976" s="7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="S976" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T976" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U976" s="4"/>
+      <c r="V976" s="4"/>
+    </row>
+    <row r="977" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A977" s="8" t="n">
+        <v>1046</v>
+      </c>
+      <c r="B977" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C977" s="9"/>
+      <c r="D977" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E977" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F977" s="9" t="s">
+        <v>1966</v>
+      </c>
+      <c r="G977" s="9" t="s">
+        <v>1967</v>
+      </c>
+      <c r="H977" s="10" t="n">
+        <v>46273</v>
+      </c>
+      <c r="I977" s="9" t="s">
+        <v>1615</v>
+      </c>
+      <c r="J977" s="9" t="s">
+        <v>1616</v>
+      </c>
+      <c r="K977" s="9" t="s">
+        <v>1617</v>
+      </c>
+      <c r="L977" s="10"/>
+      <c r="M977" s="10"/>
+      <c r="N977" s="9" t="s">
+        <v>1818</v>
+      </c>
+      <c r="O977" s="11" t="n">
+        <v>46274.637010382</v>
+      </c>
+      <c r="P977" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q977" s="9" t="s">
+        <v>1618</v>
+      </c>
+      <c r="R977" s="12" t="n">
+        <v>12500</v>
+      </c>
+      <c r="S977" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T977" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U977" s="9"/>
+      <c r="V977" s="9"/>
+    </row>
+    <row r="978" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A978" s="3" t="n">
+        <v>1047</v>
+      </c>
+      <c r="B978" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C978" s="4"/>
+      <c r="D978" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E978" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F978" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="G978" s="4" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H978" s="5" t="n">
+        <v>46274</v>
+      </c>
+      <c r="I978" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="J978" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="K978" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="L978" s="5"/>
+      <c r="M978" s="5"/>
+      <c r="N978" s="4" t="s">
+        <v>1818</v>
+      </c>
+      <c r="O978" s="6" t="n">
+        <v>46274.638265822</v>
+      </c>
+      <c r="P978" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q978" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="R978" s="7" t="n">
+        <v>2298</v>
+      </c>
+      <c r="S978" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T978" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U978" s="4"/>
+      <c r="V978" s="4"/>
+    </row>
+    <row r="979" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A979" s="13" t="n">
+        <v>977</v>
+      </c>
+      <c r="B979" s="14"/>
+      <c r="C979" s="14"/>
+      <c r="D979" s="14"/>
+      <c r="E979" s="14"/>
+      <c r="F979" s="14"/>
+      <c r="G979" s="14"/>
+      <c r="H979" s="14"/>
+      <c r="I979" s="14"/>
+      <c r="J979" s="14"/>
+      <c r="K979" s="14"/>
+      <c r="L979" s="14"/>
+      <c r="M979" s="14"/>
+      <c r="N979" s="14"/>
+      <c r="O979" s="14"/>
+      <c r="P979" s="14"/>
+      <c r="Q979" s="14"/>
+      <c r="R979" s="15" t="n">
+        <v>58606740.2626</v>
+      </c>
+      <c r="S979" s="15" t="n">
+        <v>57304287.8426</v>
+      </c>
+      <c r="T979" s="14"/>
+      <c r="U979" s="14"/>
+      <c r="V979" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="1969">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="1974">
   <si>
     <t>ID</t>
   </si>
@@ -3663,10 +3663,10 @@
     <t>657</t>
   </si>
   <si>
-    <t>BELIFE INDUSTRIA COM. IMPORTACAO E EXP. DE MAT. HOSP.</t>
-  </si>
-  <si>
-    <t>BELIFE IND. COMER. IMPORT E EXPORT. DE MAT. HOSP.</t>
+    <t>BELIFE INDUSTRIA COM. IMPORT E EXP</t>
+  </si>
+  <si>
+    <t>BELIFE IND. COM. IMPORT E EXP</t>
   </si>
   <si>
     <t>26.402.053/0001-22</t>
@@ -4569,9 +4569,6 @@
     <t>903</t>
   </si>
   <si>
-    <t>97 %</t>
-  </si>
-  <si>
     <t>904</t>
   </si>
   <si>
@@ -4935,822 +4932,807 @@
     <t>989</t>
   </si>
   <si>
+    <t>EXPRESS DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>990</t>
+  </si>
+  <si>
+    <t>991</t>
+  </si>
+  <si>
+    <t>992</t>
+  </si>
+  <si>
+    <t>996</t>
+  </si>
+  <si>
+    <t>997</t>
+  </si>
+  <si>
+    <t>998</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
+    <t>T S DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>M. A. M COMERCIO</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>1008</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>1012</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>1014</t>
+  </si>
+  <si>
+    <t>1015</t>
+  </si>
+  <si>
+    <t>PB MED</t>
+  </si>
+  <si>
+    <t>1017</t>
+  </si>
+  <si>
+    <t>1018</t>
+  </si>
+  <si>
+    <t>1020</t>
+  </si>
+  <si>
+    <t>1021</t>
+  </si>
+  <si>
+    <t>1022</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
+    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>14.416.886/0001-63</t>
+  </si>
+  <si>
+    <t>1024</t>
+  </si>
+  <si>
+    <t>GM FARMA COMERCIAL</t>
+  </si>
+  <si>
+    <t>1025</t>
+  </si>
+  <si>
+    <t>1026</t>
+  </si>
+  <si>
+    <t>1027</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>C G FARMA DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1029</t>
+  </si>
+  <si>
+    <t>77 %</t>
+  </si>
+  <si>
+    <t>ALTAMED DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1030</t>
+  </si>
+  <si>
+    <t>ALTAMED</t>
+  </si>
+  <si>
+    <t>ALTAMED DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>21.581.445/0001-82</t>
+  </si>
+  <si>
+    <t>ALINE CERBINO - PA</t>
+  </si>
+  <si>
+    <t>Região03</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>FERMATA</t>
+  </si>
+  <si>
+    <t>1035</t>
+  </si>
+  <si>
+    <t>FERMATA LTDA</t>
+  </si>
+  <si>
+    <t>66.175.139/0001-84</t>
+  </si>
+  <si>
+    <t>RC HOSPITALAR</t>
+  </si>
+  <si>
+    <t>1036</t>
+  </si>
+  <si>
+    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR</t>
+  </si>
+  <si>
+    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>26.147.597/0001-95</t>
+  </si>
+  <si>
+    <t>CRISTALFARMA</t>
+  </si>
+  <si>
+    <t>1037</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA CRISTALFARMA</t>
+  </si>
+  <si>
+    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
+  </si>
+  <si>
+    <t>05.003.408/0001-30</t>
+  </si>
+  <si>
+    <t>PLENA DIST - RN</t>
+  </si>
+  <si>
+    <t>1038</t>
+  </si>
+  <si>
+    <t>PLENA DIST - PE</t>
+  </si>
+  <si>
+    <t>1039</t>
+  </si>
+  <si>
+    <t>1040</t>
+  </si>
+  <si>
+    <t>1041</t>
+  </si>
+  <si>
+    <t>1042</t>
+  </si>
+  <si>
+    <t>1043</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>1046</t>
+  </si>
+  <si>
+    <t>1047</t>
+  </si>
+  <si>
+    <t>1048</t>
+  </si>
+  <si>
+    <t>1049</t>
+  </si>
+  <si>
+    <t>1050</t>
+  </si>
+  <si>
+    <t>CIRURGICA SHALOM</t>
+  </si>
+  <si>
+    <t>1051</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>1053</t>
+  </si>
+  <si>
+    <t>MP COMERCIO</t>
+  </si>
+  <si>
+    <t>1055</t>
+  </si>
+  <si>
+    <t>1056</t>
+  </si>
+  <si>
+    <t>1057</t>
+  </si>
+  <si>
+    <t>1058</t>
+  </si>
+  <si>
+    <t>1059</t>
+  </si>
+  <si>
+    <t>CIRURGICA MONTEBELLO</t>
+  </si>
+  <si>
+    <t>1060</t>
+  </si>
+  <si>
+    <t>MONTEBELLO</t>
+  </si>
+  <si>
+    <t>CIRURGICA MONTEBELLO LTDA</t>
+  </si>
+  <si>
+    <t>08.674.752/0001-40</t>
+  </si>
+  <si>
+    <t>1062</t>
+  </si>
+  <si>
+    <t>D FARIAS LIMA</t>
+  </si>
+  <si>
+    <t>1063</t>
+  </si>
+  <si>
+    <t>EXPRESS DIST.</t>
+  </si>
+  <si>
+    <t>1064</t>
+  </si>
+  <si>
+    <t>1065</t>
+  </si>
+  <si>
+    <t>1066</t>
+  </si>
+  <si>
+    <t>1067</t>
+  </si>
+  <si>
+    <t>1068</t>
+  </si>
+  <si>
+    <t>LS MATERIAIS (HELDER WALNER)</t>
+  </si>
+  <si>
+    <t>1069</t>
+  </si>
+  <si>
+    <t>A M FARMA - MA</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>A M FARMA - PI</t>
+  </si>
+  <si>
+    <t>1071</t>
+  </si>
+  <si>
+    <t>F MELO MATERIAL MEDICO</t>
+  </si>
+  <si>
+    <t>1072</t>
+  </si>
+  <si>
+    <t>JT COSTA COMERCIAL</t>
+  </si>
+  <si>
+    <t>1073</t>
+  </si>
+  <si>
+    <t>JT COSTA COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>64.190.875/0001-86</t>
+  </si>
+  <si>
+    <t>CAMPINA SAUDE</t>
+  </si>
+  <si>
+    <t>1074</t>
+  </si>
+  <si>
+    <t>CAMPINA SAUDE CENTER COM. DE ART. MEDICOS LTDA</t>
+  </si>
+  <si>
+    <t>39.324.410/0001-23</t>
+  </si>
+  <si>
+    <t>1075</t>
+  </si>
+  <si>
+    <t>1076</t>
+  </si>
+  <si>
+    <t>1077</t>
+  </si>
+  <si>
+    <t>1078</t>
+  </si>
+  <si>
+    <t>1079</t>
+  </si>
+  <si>
+    <t>1080</t>
+  </si>
+  <si>
+    <t>1082</t>
+  </si>
+  <si>
+    <t>NOVA BAHIA MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>1083</t>
+  </si>
+  <si>
+    <t>NOVA BAHIA MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>32.658.023/0001-84</t>
+  </si>
+  <si>
+    <t>71 %</t>
+  </si>
+  <si>
+    <t>CONQUISTA MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>1084</t>
+  </si>
+  <si>
+    <t>CONQUISTA DISTRIBUIDORA DE MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>12.418.191/0001-95</t>
+  </si>
+  <si>
+    <t>1085</t>
+  </si>
+  <si>
+    <t>1086</t>
+  </si>
+  <si>
+    <t>1087</t>
+  </si>
+  <si>
+    <t>1088</t>
+  </si>
+  <si>
+    <t>F MELO</t>
+  </si>
+  <si>
+    <t>1089</t>
+  </si>
+  <si>
+    <t>41 %</t>
+  </si>
+  <si>
+    <t>C J A PARENTE</t>
+  </si>
+  <si>
+    <t>1090</t>
+  </si>
+  <si>
+    <t>C J A PARENTE COMERCIO</t>
+  </si>
+  <si>
+    <t>C J A PARENTE COMERCIO DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>83.646.307/0001-91</t>
+  </si>
+  <si>
+    <t>NORTE GREEN</t>
+  </si>
+  <si>
+    <t>1091</t>
+  </si>
+  <si>
+    <t>NORTE GREEN COMERCIO DE PROD FARM E HOSP LTDA</t>
+  </si>
+  <si>
+    <t>24.218.223/0001-98</t>
+  </si>
+  <si>
+    <t>1092</t>
+  </si>
+  <si>
+    <t>1093</t>
+  </si>
+  <si>
+    <t>CDMED HOSPITALAR</t>
+  </si>
+  <si>
+    <t>1094</t>
+  </si>
+  <si>
+    <t>CDMED HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>46.359.681/0001-80</t>
+  </si>
+  <si>
+    <t>1095</t>
+  </si>
+  <si>
+    <t>1096</t>
+  </si>
+  <si>
+    <t>1097</t>
+  </si>
+  <si>
+    <t>1098</t>
+  </si>
+  <si>
+    <t>F MELO MATERIAL</t>
+  </si>
+  <si>
+    <t>1099</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>58 %</t>
+  </si>
+  <si>
+    <t>RC DISTRIBUIDORA DE MED.</t>
+  </si>
+  <si>
+    <t>1105</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>A INICIAR</t>
+  </si>
+  <si>
+    <t>1108</t>
+  </si>
+  <si>
+    <t>LICIMASTER DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LICIMASTER DISTRIBUIDORA DE MEDICAMENTOS E PRODUTOS MEDICO HOSPITALAR </t>
+  </si>
+  <si>
+    <t>LICIMASTER DIST. DE MED. E PRODUTOS MEDICO</t>
+  </si>
+  <si>
+    <t>20.001.049/0001-76</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>64 %</t>
+  </si>
+  <si>
+    <t>1114</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>1119</t>
+  </si>
+  <si>
+    <t>1120</t>
+  </si>
+  <si>
+    <t>1121</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>1123</t>
+  </si>
+  <si>
+    <t>1124</t>
+  </si>
+  <si>
+    <t>1125</t>
+  </si>
+  <si>
+    <t>ARTMED COMERCIAL</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>ARTMED FARMA</t>
+  </si>
+  <si>
+    <t>ARTMED COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>04.361.467/0001-18</t>
+  </si>
+  <si>
+    <t>GERAL</t>
+  </si>
+  <si>
+    <t>1127</t>
+  </si>
+  <si>
+    <t>1128</t>
+  </si>
+  <si>
+    <t>1129</t>
+  </si>
+  <si>
+    <t>1130</t>
+  </si>
+  <si>
+    <t>1132</t>
+  </si>
+  <si>
+    <t>1134</t>
+  </si>
+  <si>
+    <t>OMNIELMASTER HEMOMED</t>
+  </si>
+  <si>
+    <t>1135</t>
+  </si>
+  <si>
+    <t>OMNIELMASTER HEMOMED REPRESENTACAO</t>
+  </si>
+  <si>
+    <t>05.578.020/0001-68</t>
+  </si>
+  <si>
+    <t>1136</t>
+  </si>
+  <si>
+    <t>1137</t>
+  </si>
+  <si>
+    <t>1139</t>
+  </si>
+  <si>
+    <t>1140</t>
+  </si>
+  <si>
+    <t>1141</t>
+  </si>
+  <si>
+    <t>1142</t>
+  </si>
+  <si>
+    <t>1143</t>
+  </si>
+  <si>
+    <t>1144</t>
+  </si>
+  <si>
+    <t>1145</t>
+  </si>
+  <si>
+    <t>HRX COMERCIAL</t>
+  </si>
+  <si>
+    <t>1146</t>
+  </si>
+  <si>
+    <t>HRX PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>11.634.742/0002-76</t>
+  </si>
+  <si>
+    <t>1147</t>
+  </si>
+  <si>
+    <t>1148</t>
+  </si>
+  <si>
+    <t>1149</t>
+  </si>
+  <si>
+    <t>1150</t>
+  </si>
+  <si>
+    <t>1151</t>
+  </si>
+  <si>
+    <t>1152</t>
+  </si>
+  <si>
+    <t>1153</t>
+  </si>
+  <si>
+    <t>1154</t>
+  </si>
+  <si>
+    <t>1155</t>
+  </si>
+  <si>
+    <t>MASTER DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1156</t>
+  </si>
+  <si>
+    <t>MASTER DISTRIBUIDORA E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>55.076.740/0001-01</t>
+  </si>
+  <si>
+    <t>1157</t>
+  </si>
+  <si>
+    <t>1158</t>
+  </si>
+  <si>
+    <t>1159</t>
+  </si>
+  <si>
+    <t>1160</t>
+  </si>
+  <si>
+    <t>1161</t>
+  </si>
+  <si>
+    <t>FAMA DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1162</t>
+  </si>
+  <si>
+    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>03.250.803/0001-92</t>
+  </si>
+  <si>
+    <t>FELIPE AQUINO - MT</t>
+  </si>
+  <si>
+    <t>1163</t>
+  </si>
+  <si>
+    <t>1164</t>
+  </si>
+  <si>
+    <t>1165</t>
+  </si>
+  <si>
+    <t>1166</t>
+  </si>
+  <si>
+    <t>MEDKA HOSPITALAR</t>
+  </si>
+  <si>
+    <t>1167</t>
+  </si>
+  <si>
+    <t>MEDKA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>36.958.637/0001-32</t>
+  </si>
+  <si>
+    <t>1168</t>
+  </si>
+  <si>
+    <t>DAZ MEDIC</t>
+  </si>
+  <si>
+    <t>1169</t>
+  </si>
+  <si>
+    <t>DAZ DISTRIBUIDORA HOSPITALAR</t>
+  </si>
+  <si>
+    <t>DAZ MEDIC DISTRIBUIDOR HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>33.744.332/0001-30</t>
+  </si>
+  <si>
+    <t>1170</t>
+  </si>
+  <si>
+    <t>1171</t>
+  </si>
+  <si>
+    <t>1173</t>
+  </si>
+  <si>
     <t>91 %</t>
   </si>
   <si>
-    <t>EXPRESS DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>990</t>
-  </si>
-  <si>
-    <t>991</t>
-  </si>
-  <si>
-    <t>992</t>
-  </si>
-  <si>
-    <t>996</t>
-  </si>
-  <si>
-    <t>997</t>
-  </si>
-  <si>
-    <t>998</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>T S DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>43 %</t>
-  </si>
-  <si>
-    <t>M. A. M COMERCIO</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>1006</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>1012</t>
-  </si>
-  <si>
-    <t>1013</t>
-  </si>
-  <si>
-    <t>1014</t>
-  </si>
-  <si>
-    <t>1015</t>
-  </si>
-  <si>
-    <t>PB MED</t>
-  </si>
-  <si>
-    <t>1017</t>
-  </si>
-  <si>
-    <t>1018</t>
-  </si>
-  <si>
-    <t>1020</t>
-  </si>
-  <si>
-    <t>39 %</t>
-  </si>
-  <si>
-    <t>1021</t>
-  </si>
-  <si>
-    <t>1022</t>
-  </si>
-  <si>
-    <t>COBERMED COMERCIO</t>
-  </si>
-  <si>
-    <t>1023</t>
-  </si>
-  <si>
-    <t>COBERMED COMERCIO DE MATERIAIS MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>14.416.886/0001-63</t>
-  </si>
-  <si>
-    <t>1024</t>
-  </si>
-  <si>
-    <t>GM FARMA COMERCIAL</t>
-  </si>
-  <si>
-    <t>1025</t>
-  </si>
-  <si>
-    <t>1026</t>
-  </si>
-  <si>
-    <t>1027</t>
-  </si>
-  <si>
-    <t>1028</t>
-  </si>
-  <si>
-    <t>C G FARMA DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1029</t>
-  </si>
-  <si>
-    <t>77 %</t>
-  </si>
-  <si>
-    <t>ALTAMED DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1030</t>
-  </si>
-  <si>
-    <t>ALTAMED</t>
-  </si>
-  <si>
-    <t>ALTAMED DISTRIBUIDORA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>21.581.445/0001-82</t>
-  </si>
-  <si>
-    <t>ALINE CERBINO - PA</t>
-  </si>
-  <si>
-    <t>Região03</t>
-  </si>
-  <si>
-    <t>1033</t>
-  </si>
-  <si>
-    <t>FERMATA</t>
-  </si>
-  <si>
-    <t>1035</t>
-  </si>
-  <si>
-    <t>FERMATA LTDA</t>
-  </si>
-  <si>
-    <t>66.175.139/0001-84</t>
-  </si>
-  <si>
-    <t>RC HOSPITALAR</t>
-  </si>
-  <si>
-    <t>1036</t>
-  </si>
-  <si>
-    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR</t>
-  </si>
-  <si>
-    <t>RC DISTRIBUIDORA FARMA E HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>26.147.597/0001-95</t>
-  </si>
-  <si>
-    <t>CRISTALFARMA</t>
-  </si>
-  <si>
-    <t>1037</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA CRISTALFARMA</t>
-  </si>
-  <si>
-    <t>CRISTALFARMA COMERCIO IMPORT E EXPORT LTDA</t>
-  </si>
-  <si>
-    <t>05.003.408/0001-30</t>
-  </si>
-  <si>
-    <t>PLENA DIST - RN</t>
-  </si>
-  <si>
-    <t>1038</t>
-  </si>
-  <si>
-    <t>PLENA DIST - PE</t>
-  </si>
-  <si>
-    <t>1039</t>
-  </si>
-  <si>
-    <t>1040</t>
-  </si>
-  <si>
-    <t>1041</t>
-  </si>
-  <si>
-    <t>1042</t>
-  </si>
-  <si>
-    <t>1043</t>
-  </si>
-  <si>
-    <t>1044</t>
-  </si>
-  <si>
-    <t>1045</t>
-  </si>
-  <si>
-    <t>1046</t>
-  </si>
-  <si>
-    <t>1047</t>
-  </si>
-  <si>
-    <t>1048</t>
-  </si>
-  <si>
-    <t>1049</t>
-  </si>
-  <si>
-    <t>1050</t>
-  </si>
-  <si>
-    <t>CIRURGICA SHALOM</t>
-  </si>
-  <si>
-    <t>1051</t>
-  </si>
-  <si>
-    <t>1052</t>
-  </si>
-  <si>
-    <t>1053</t>
-  </si>
-  <si>
-    <t>MP COMERCIO</t>
-  </si>
-  <si>
-    <t>1055</t>
-  </si>
-  <si>
-    <t>1056</t>
-  </si>
-  <si>
-    <t>84 %</t>
-  </si>
-  <si>
-    <t>1057</t>
-  </si>
-  <si>
-    <t>1058</t>
-  </si>
-  <si>
-    <t>1059</t>
-  </si>
-  <si>
-    <t>CIRURGICA MONTEBELLO</t>
-  </si>
-  <si>
-    <t>1060</t>
-  </si>
-  <si>
-    <t>MONTEBELLO</t>
-  </si>
-  <si>
-    <t>CIRURGICA MONTEBELLO LTDA</t>
-  </si>
-  <si>
-    <t>08.674.752/0001-40</t>
-  </si>
-  <si>
-    <t>1062</t>
-  </si>
-  <si>
-    <t>D FARIAS LIMA</t>
-  </si>
-  <si>
-    <t>1063</t>
-  </si>
-  <si>
-    <t>EXPRESS DIST.</t>
-  </si>
-  <si>
-    <t>1064</t>
-  </si>
-  <si>
-    <t>1065</t>
-  </si>
-  <si>
-    <t>1066</t>
-  </si>
-  <si>
-    <t>1067</t>
-  </si>
-  <si>
-    <t>1068</t>
-  </si>
-  <si>
-    <t>LS MATERIAIS (HELDER WALNER)</t>
-  </si>
-  <si>
-    <t>1069</t>
-  </si>
-  <si>
-    <t>A M FARMA - MA</t>
-  </si>
-  <si>
-    <t>1070</t>
-  </si>
-  <si>
-    <t>A M FARMA - PI</t>
-  </si>
-  <si>
-    <t>1071</t>
-  </si>
-  <si>
-    <t>F MELO MATERIAL MEDICO</t>
-  </si>
-  <si>
-    <t>1072</t>
-  </si>
-  <si>
-    <t>JT COSTA COMERCIAL</t>
-  </si>
-  <si>
-    <t>1073</t>
-  </si>
-  <si>
-    <t>JT COSTA COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>64.190.875/0001-86</t>
-  </si>
-  <si>
-    <t>CAMPINA SAUDE</t>
-  </si>
-  <si>
-    <t>1074</t>
-  </si>
-  <si>
-    <t>CAMPINA SAUDE CENTER COM. DE ART. MEDICOS LTDA</t>
-  </si>
-  <si>
-    <t>39.324.410/0001-23</t>
-  </si>
-  <si>
-    <t>1075</t>
-  </si>
-  <si>
-    <t>1076</t>
-  </si>
-  <si>
-    <t>1077</t>
-  </si>
-  <si>
-    <t>1078</t>
-  </si>
-  <si>
-    <t>1079</t>
-  </si>
-  <si>
-    <t>1080</t>
-  </si>
-  <si>
-    <t>1082</t>
-  </si>
-  <si>
-    <t>NOVA BAHIA MEDICAMENTOS</t>
-  </si>
-  <si>
-    <t>1083</t>
-  </si>
-  <si>
-    <t>NOVA BAHIA MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>32.658.023/0001-84</t>
-  </si>
-  <si>
-    <t>71 %</t>
-  </si>
-  <si>
-    <t>CONQUISTA MEDICAMENTOS</t>
-  </si>
-  <si>
-    <t>1084</t>
-  </si>
-  <si>
-    <t>CONQUISTA DISTRIBUIDORA DE MEDICAMENTOS</t>
-  </si>
-  <si>
-    <t>12.418.191/0001-95</t>
-  </si>
-  <si>
-    <t>1085</t>
-  </si>
-  <si>
-    <t>1086</t>
-  </si>
-  <si>
-    <t>1087</t>
-  </si>
-  <si>
-    <t>1088</t>
-  </si>
-  <si>
-    <t>F MELO</t>
-  </si>
-  <si>
-    <t>1089</t>
-  </si>
-  <si>
-    <t>41 %</t>
-  </si>
-  <si>
-    <t>C J A PARENTE</t>
-  </si>
-  <si>
-    <t>1090</t>
-  </si>
-  <si>
-    <t>C J A PARENTE COMERCIO</t>
-  </si>
-  <si>
-    <t>C J A PARENTE COMERCIO DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>83.646.307/0001-91</t>
-  </si>
-  <si>
-    <t>NORTE GREEN</t>
-  </si>
-  <si>
-    <t>1091</t>
-  </si>
-  <si>
-    <t>NORTE GREEN COMERCIO DE PROD FARM E HOSP LTDA</t>
-  </si>
-  <si>
-    <t>24.218.223/0001-98</t>
-  </si>
-  <si>
-    <t>1092</t>
-  </si>
-  <si>
-    <t>1093</t>
-  </si>
-  <si>
-    <t>CDMED HOSPITALAR</t>
-  </si>
-  <si>
-    <t>1094</t>
-  </si>
-  <si>
-    <t>CDMED HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>46.359.681/0001-80</t>
-  </si>
-  <si>
-    <t>1095</t>
-  </si>
-  <si>
-    <t>1096</t>
-  </si>
-  <si>
-    <t>1097</t>
-  </si>
-  <si>
-    <t>1098</t>
-  </si>
-  <si>
-    <t>F MELO MATERIAL</t>
-  </si>
-  <si>
-    <t>1099</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>1102</t>
-  </si>
-  <si>
-    <t>1103</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>58 %</t>
-  </si>
-  <si>
-    <t>RC DISTRIBUIDORA DE MED.</t>
-  </si>
-  <si>
-    <t>1105</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
-    <t>A INICIAR</t>
-  </si>
-  <si>
-    <t>1108</t>
-  </si>
-  <si>
-    <t>LICIMASTER DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LICIMASTER DISTRIBUIDORA DE MEDICAMENTOS E PRODUTOS MEDICO HOSPITALAR </t>
-  </si>
-  <si>
-    <t>LICIMASTER DIST. DE MED. E PRODUTOS MEDICO</t>
-  </si>
-  <si>
-    <t>20.001.049/0001-76</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>1112</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>64 %</t>
-  </si>
-  <si>
-    <t>1114</t>
-  </si>
-  <si>
-    <t>1115</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>1117</t>
-  </si>
-  <si>
-    <t>1118</t>
-  </si>
-  <si>
-    <t>1119</t>
-  </si>
-  <si>
-    <t>1120</t>
-  </si>
-  <si>
-    <t>1121</t>
-  </si>
-  <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>1123</t>
-  </si>
-  <si>
-    <t>1124</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>ARTMED COMERCIAL</t>
-  </si>
-  <si>
-    <t>1126</t>
-  </si>
-  <si>
-    <t>ARTMED FARMA</t>
-  </si>
-  <si>
-    <t>ARTMED COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>04.361.467/0001-18</t>
-  </si>
-  <si>
-    <t>GERAL</t>
-  </si>
-  <si>
-    <t>1127</t>
-  </si>
-  <si>
-    <t>1128</t>
-  </si>
-  <si>
-    <t>1129</t>
-  </si>
-  <si>
-    <t>1130</t>
-  </si>
-  <si>
-    <t>1132</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>OMNIELMASTER HEMOMED</t>
-  </si>
-  <si>
-    <t>1135</t>
-  </si>
-  <si>
-    <t>OMNIELMASTER HEMOMED REPRESENTACAO</t>
-  </si>
-  <si>
-    <t>05.578.020/0001-68</t>
-  </si>
-  <si>
-    <t>1136</t>
-  </si>
-  <si>
-    <t>1137</t>
-  </si>
-  <si>
-    <t>1139</t>
-  </si>
-  <si>
-    <t>1140</t>
-  </si>
-  <si>
-    <t>1141</t>
-  </si>
-  <si>
-    <t>1142</t>
-  </si>
-  <si>
-    <t>1143</t>
-  </si>
-  <si>
-    <t>1144</t>
-  </si>
-  <si>
-    <t>1145</t>
-  </si>
-  <si>
-    <t>60 %</t>
-  </si>
-  <si>
-    <t>HRX COMERCIAL</t>
-  </si>
-  <si>
-    <t>1146</t>
-  </si>
-  <si>
-    <t>HRX PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>11.634.742/0002-76</t>
-  </si>
-  <si>
-    <t>1147</t>
-  </si>
-  <si>
-    <t>1148</t>
-  </si>
-  <si>
-    <t>1149</t>
-  </si>
-  <si>
-    <t>1150</t>
-  </si>
-  <si>
-    <t>1151</t>
-  </si>
-  <si>
-    <t>1152</t>
-  </si>
-  <si>
-    <t>1153</t>
-  </si>
-  <si>
-    <t>1154</t>
-  </si>
-  <si>
-    <t>1155</t>
-  </si>
-  <si>
-    <t>MASTER DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1156</t>
-  </si>
-  <si>
-    <t>MASTER DISTRIBUIDORA E SERVICOS LTDA</t>
-  </si>
-  <si>
-    <t>55.076.740/0001-01</t>
-  </si>
-  <si>
-    <t>1157</t>
-  </si>
-  <si>
-    <t>1158</t>
-  </si>
-  <si>
-    <t>1159</t>
-  </si>
-  <si>
-    <t>1160</t>
-  </si>
-  <si>
-    <t>1161</t>
-  </si>
-  <si>
-    <t>FAMA DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1162</t>
-  </si>
-  <si>
-    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>03.250.803/0001-92</t>
-  </si>
-  <si>
-    <t>FELIPE AQUINO - MT</t>
-  </si>
-  <si>
-    <t>1163</t>
-  </si>
-  <si>
-    <t>1164</t>
-  </si>
-  <si>
-    <t>1165</t>
-  </si>
-  <si>
-    <t>1166</t>
-  </si>
-  <si>
-    <t>54 %</t>
-  </si>
-  <si>
-    <t>MEDKA HOSPITALAR</t>
-  </si>
-  <si>
-    <t>1167</t>
-  </si>
-  <si>
-    <t>MEDKA DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>36.958.637/0001-32</t>
-  </si>
-  <si>
-    <t>1168</t>
-  </si>
-  <si>
-    <t>DAZ MEDIC</t>
-  </si>
-  <si>
-    <t>1169</t>
-  </si>
-  <si>
-    <t>DAZ DISTRIBUIDORA HOSPITALAR</t>
-  </si>
-  <si>
-    <t>DAZ MEDIC DISTRIBUIDOR HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>33.744.332/0001-30</t>
-  </si>
-  <si>
-    <t>1170</t>
-  </si>
-  <si>
-    <t>1171</t>
-  </si>
-  <si>
-    <t>1173</t>
-  </si>
-  <si>
     <t>1174</t>
   </si>
   <si>
@@ -5760,12 +5742,12 @@
     <t>1176</t>
   </si>
   <si>
+    <t>29 %</t>
+  </si>
+  <si>
     <t>1177</t>
   </si>
   <si>
-    <t>50 %</t>
-  </si>
-  <si>
     <t>1178</t>
   </si>
   <si>
@@ -5781,6 +5763,9 @@
     <t>1182</t>
   </si>
   <si>
+    <t>46 %</t>
+  </si>
+  <si>
     <t>1183</t>
   </si>
   <si>
@@ -5868,6 +5853,9 @@
     <t>1201</t>
   </si>
   <si>
+    <t>25 %</t>
+  </si>
+  <si>
     <t>1202</t>
   </si>
   <si>
@@ -5889,6 +5877,9 @@
     <t>1206</t>
   </si>
   <si>
+    <t>53 %</t>
+  </si>
+  <si>
     <t>1207</t>
   </si>
   <si>
@@ -5920,6 +5911,30 @@
   </si>
   <si>
     <t>1212</t>
+  </si>
+  <si>
+    <t>1213</t>
+  </si>
+  <si>
+    <t>1214</t>
+  </si>
+  <si>
+    <t>1215</t>
+  </si>
+  <si>
+    <t>1216</t>
+  </si>
+  <si>
+    <t>1217</t>
+  </si>
+  <si>
+    <t>1218</t>
+  </si>
+  <si>
+    <t>1219</t>
+  </si>
+  <si>
+    <t>1220</t>
   </si>
 </sst>
 </file>
@@ -6113,7 +6128,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V979"/>
+  <dimension ref="A1:V987"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -46371,13 +46386,13 @@
         <v>23</v>
       </c>
       <c r="E694" s="3" t="s">
-        <v>1518</v>
+        <v>24</v>
       </c>
       <c r="F694" s="4" t="s">
         <v>75</v>
       </c>
       <c r="G694" s="4" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H694" s="5" t="n">
         <v>46167</v>
@@ -46394,7 +46409,7 @@
       <c r="L694" s="5"/>
       <c r="M694" s="5"/>
       <c r="N694" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O694" s="6" t="n">
         <v>46167.620332986</v>
@@ -46409,7 +46424,7 @@
         <v>156029.6</v>
       </c>
       <c r="S694" s="7" t="n">
-        <v>151061.6</v>
+        <v>156029.6</v>
       </c>
       <c r="T694" s="4" t="s">
         <v>32</v>
@@ -46435,7 +46450,7 @@
         <v>490</v>
       </c>
       <c r="G695" s="9" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H695" s="10" t="n">
         <v>46168</v>
@@ -46490,10 +46505,10 @@
         <v>24</v>
       </c>
       <c r="F696" s="4" t="s">
+        <v>1520</v>
+      </c>
+      <c r="G696" s="4" t="s">
         <v>1521</v>
-      </c>
-      <c r="G696" s="4" t="s">
-        <v>1522</v>
       </c>
       <c r="H696" s="5" t="n">
         <v>46168</v>
@@ -46548,10 +46563,10 @@
         <v>24</v>
       </c>
       <c r="F697" s="9" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G697" s="9" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H697" s="10" t="n">
         <v>46168</v>
@@ -46609,7 +46624,7 @@
         <v>502</v>
       </c>
       <c r="G698" s="4" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H698" s="5" t="n">
         <v>46169</v>
@@ -46667,7 +46682,7 @@
         <v>75</v>
       </c>
       <c r="G699" s="9" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H699" s="10" t="n">
         <v>46168</v>
@@ -46725,7 +46740,7 @@
         <v>75</v>
       </c>
       <c r="G700" s="4" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H700" s="5" t="n">
         <v>46168</v>
@@ -46780,10 +46795,10 @@
         <v>24</v>
       </c>
       <c r="F701" s="9" t="s">
+        <v>1526</v>
+      </c>
+      <c r="G701" s="9" t="s">
         <v>1527</v>
-      </c>
-      <c r="G701" s="9" t="s">
-        <v>1528</v>
       </c>
       <c r="H701" s="10" t="n">
         <v>46167</v>
@@ -46841,7 +46856,7 @@
         <v>988</v>
       </c>
       <c r="G702" s="4" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H702" s="5" t="n">
         <v>46169</v>
@@ -46899,7 +46914,7 @@
         <v>505</v>
       </c>
       <c r="G703" s="9" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H703" s="10" t="n">
         <v>46168</v>
@@ -46957,7 +46972,7 @@
         <v>592</v>
       </c>
       <c r="G704" s="4" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H704" s="5" t="n">
         <v>46169</v>
@@ -47015,7 +47030,7 @@
         <v>347</v>
       </c>
       <c r="G705" s="9" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H705" s="10" t="n">
         <v>46168</v>
@@ -47073,7 +47088,7 @@
         <v>671</v>
       </c>
       <c r="G706" s="4" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H706" s="5" t="n">
         <v>46168</v>
@@ -47131,7 +47146,7 @@
         <v>203</v>
       </c>
       <c r="G707" s="9" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H707" s="10" t="n">
         <v>46168</v>
@@ -47189,7 +47204,7 @@
         <v>262</v>
       </c>
       <c r="G708" s="4" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H708" s="5" t="n">
         <v>46168</v>
@@ -47247,7 +47262,7 @@
         <v>152</v>
       </c>
       <c r="G709" s="9" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H709" s="10" t="n">
         <v>46167</v>
@@ -47305,7 +47320,7 @@
         <v>58</v>
       </c>
       <c r="G710" s="4" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H710" s="5" t="n">
         <v>46167</v>
@@ -47363,7 +47378,7 @@
         <v>310</v>
       </c>
       <c r="G711" s="9" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H711" s="10" t="n">
         <v>46167</v>
@@ -47418,10 +47433,10 @@
         <v>24</v>
       </c>
       <c r="F712" s="4" t="s">
+        <v>1538</v>
+      </c>
+      <c r="G712" s="4" t="s">
         <v>1539</v>
-      </c>
-      <c r="G712" s="4" t="s">
-        <v>1540</v>
       </c>
       <c r="H712" s="5" t="n">
         <v>46167</v>
@@ -47479,7 +47494,7 @@
         <v>328</v>
       </c>
       <c r="G713" s="9" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H713" s="10" t="n">
         <v>46167</v>
@@ -47534,10 +47549,10 @@
         <v>24</v>
       </c>
       <c r="F714" s="4" t="s">
+        <v>1541</v>
+      </c>
+      <c r="G714" s="4" t="s">
         <v>1542</v>
-      </c>
-      <c r="G714" s="4" t="s">
-        <v>1543</v>
       </c>
       <c r="H714" s="5" t="n">
         <v>46168</v>
@@ -47592,10 +47607,10 @@
         <v>24</v>
       </c>
       <c r="F715" s="9" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G715" s="9" t="s">
         <v>1544</v>
-      </c>
-      <c r="G715" s="9" t="s">
-        <v>1545</v>
       </c>
       <c r="H715" s="10" t="n">
         <v>46169</v>
@@ -47653,7 +47668,7 @@
         <v>675</v>
       </c>
       <c r="G716" s="4" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H716" s="5" t="n">
         <v>46170</v>
@@ -47708,10 +47723,10 @@
         <v>24</v>
       </c>
       <c r="F717" s="9" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G717" s="9" t="s">
         <v>1547</v>
-      </c>
-      <c r="G717" s="9" t="s">
-        <v>1548</v>
       </c>
       <c r="H717" s="10" t="n">
         <v>46169</v>
@@ -47769,7 +47784,7 @@
         <v>909</v>
       </c>
       <c r="G718" s="4" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H718" s="5" t="n">
         <v>46170</v>
@@ -47824,22 +47839,22 @@
         <v>24</v>
       </c>
       <c r="F719" s="9" t="s">
+        <v>1549</v>
+      </c>
+      <c r="G719" s="9" t="s">
         <v>1550</v>
-      </c>
-      <c r="G719" s="9" t="s">
-        <v>1551</v>
       </c>
       <c r="H719" s="10" t="n">
         <v>46174</v>
       </c>
       <c r="I719" s="9" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="J719" s="9" t="s">
+        <v>1551</v>
+      </c>
+      <c r="K719" s="9" t="s">
         <v>1552</v>
-      </c>
-      <c r="K719" s="9" t="s">
-        <v>1553</v>
       </c>
       <c r="L719" s="10"/>
       <c r="M719" s="10"/>
@@ -47885,7 +47900,7 @@
         <v>969</v>
       </c>
       <c r="G720" s="4" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H720" s="5" t="n">
         <v>46170</v>
@@ -47943,7 +47958,7 @@
         <v>1459</v>
       </c>
       <c r="G721" s="9" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H721" s="10" t="n">
         <v>46169</v>
@@ -48001,7 +48016,7 @@
         <v>820</v>
       </c>
       <c r="G722" s="4" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H722" s="5" t="n">
         <v>46169</v>
@@ -48059,7 +48074,7 @@
         <v>1012</v>
       </c>
       <c r="G723" s="9" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H723" s="10" t="n">
         <v>46169</v>
@@ -48114,22 +48129,22 @@
         <v>24</v>
       </c>
       <c r="F724" s="4" t="s">
+        <v>1557</v>
+      </c>
+      <c r="G724" s="4" t="s">
         <v>1558</v>
-      </c>
-      <c r="G724" s="4" t="s">
-        <v>1559</v>
       </c>
       <c r="H724" s="5" t="n">
         <v>46169</v>
       </c>
       <c r="I724" s="4" t="s">
+        <v>1559</v>
+      </c>
+      <c r="J724" s="4" t="s">
         <v>1560</v>
       </c>
-      <c r="J724" s="4" t="s">
+      <c r="K724" s="4" t="s">
         <v>1561</v>
-      </c>
-      <c r="K724" s="4" t="s">
-        <v>1562</v>
       </c>
       <c r="L724" s="5"/>
       <c r="M724" s="5"/>
@@ -48175,7 +48190,7 @@
         <v>1102</v>
       </c>
       <c r="G725" s="9" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H725" s="10" t="n">
         <v>46170</v>
@@ -48233,7 +48248,7 @@
         <v>592</v>
       </c>
       <c r="G726" s="4" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H726" s="5" t="n">
         <v>46170</v>
@@ -48291,7 +48306,7 @@
         <v>461</v>
       </c>
       <c r="G727" s="9" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H727" s="10" t="n">
         <v>46170</v>
@@ -48349,7 +48364,7 @@
         <v>1292</v>
       </c>
       <c r="G728" s="4" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H728" s="5" t="n">
         <v>46171</v>
@@ -48407,7 +48422,7 @@
         <v>1459</v>
       </c>
       <c r="G729" s="9" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H729" s="10" t="n">
         <v>46175</v>
@@ -48465,7 +48480,7 @@
         <v>1062</v>
       </c>
       <c r="G730" s="4" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H730" s="5" t="n">
         <v>46175</v>
@@ -48523,7 +48538,7 @@
         <v>696</v>
       </c>
       <c r="G731" s="9" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H731" s="10" t="n">
         <v>46175</v>
@@ -48578,10 +48593,10 @@
         <v>24</v>
       </c>
       <c r="F732" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="G732" s="4" t="s">
         <v>1570</v>
-      </c>
-      <c r="G732" s="4" t="s">
-        <v>1571</v>
       </c>
       <c r="H732" s="5" t="n">
         <v>46176</v>
@@ -48639,7 +48654,7 @@
         <v>103</v>
       </c>
       <c r="G733" s="9" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H733" s="10" t="n">
         <v>46176</v>
@@ -48694,10 +48709,10 @@
         <v>24</v>
       </c>
       <c r="F734" s="4" t="s">
+        <v>1572</v>
+      </c>
+      <c r="G734" s="4" t="s">
         <v>1573</v>
-      </c>
-      <c r="G734" s="4" t="s">
-        <v>1574</v>
       </c>
       <c r="H734" s="5" t="n">
         <v>46176</v>
@@ -48752,10 +48767,10 @@
         <v>24</v>
       </c>
       <c r="F735" s="9" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="G735" s="9" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H735" s="10" t="n">
         <v>46176</v>
@@ -48813,7 +48828,7 @@
         <v>143</v>
       </c>
       <c r="G736" s="4" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H736" s="5" t="n">
         <v>46181</v>
@@ -48871,7 +48886,7 @@
         <v>447</v>
       </c>
       <c r="G737" s="9" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H737" s="10" t="n">
         <v>46182</v>
@@ -48929,7 +48944,7 @@
         <v>143</v>
       </c>
       <c r="G738" s="4" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H738" s="5" t="n">
         <v>46182</v>
@@ -48984,10 +48999,10 @@
         <v>24</v>
       </c>
       <c r="F739" s="9" t="s">
+        <v>1578</v>
+      </c>
+      <c r="G739" s="9" t="s">
         <v>1579</v>
-      </c>
-      <c r="G739" s="9" t="s">
-        <v>1580</v>
       </c>
       <c r="H739" s="10" t="n">
         <v>46182</v>
@@ -49045,7 +49060,7 @@
         <v>1421</v>
       </c>
       <c r="G740" s="4" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H740" s="5" t="n">
         <v>46181</v>
@@ -49100,10 +49115,10 @@
         <v>24</v>
       </c>
       <c r="F741" s="9" t="s">
+        <v>1581</v>
+      </c>
+      <c r="G741" s="9" t="s">
         <v>1582</v>
-      </c>
-      <c r="G741" s="9" t="s">
-        <v>1583</v>
       </c>
       <c r="H741" s="10" t="n">
         <v>46183</v>
@@ -49158,10 +49173,10 @@
         <v>24</v>
       </c>
       <c r="F742" s="4" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G742" s="4" t="s">
         <v>1584</v>
-      </c>
-      <c r="G742" s="4" t="s">
-        <v>1585</v>
       </c>
       <c r="H742" s="5" t="n">
         <v>46184</v>
@@ -49221,7 +49236,7 @@
         <v>1488</v>
       </c>
       <c r="G743" s="9" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H743" s="10" t="n">
         <v>46183</v>
@@ -49276,22 +49291,22 @@
         <v>24</v>
       </c>
       <c r="F744" s="4" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G744" s="4" t="s">
         <v>1587</v>
-      </c>
-      <c r="G744" s="4" t="s">
-        <v>1588</v>
       </c>
       <c r="H744" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="I744" s="4" t="s">
+        <v>1588</v>
+      </c>
+      <c r="J744" s="4" t="s">
         <v>1589</v>
       </c>
-      <c r="J744" s="4" t="s">
+      <c r="K744" s="4" t="s">
         <v>1590</v>
-      </c>
-      <c r="K744" s="4" t="s">
-        <v>1591</v>
       </c>
       <c r="L744" s="5"/>
       <c r="M744" s="5"/>
@@ -49337,7 +49352,7 @@
         <v>272</v>
       </c>
       <c r="G745" s="9" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H745" s="10" t="n">
         <v>46184</v>
@@ -49395,7 +49410,7 @@
         <v>519</v>
       </c>
       <c r="G746" s="4" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H746" s="5" t="n">
         <v>46184</v>
@@ -49450,10 +49465,10 @@
         <v>24</v>
       </c>
       <c r="F747" s="9" t="s">
+        <v>1593</v>
+      </c>
+      <c r="G747" s="9" t="s">
         <v>1594</v>
-      </c>
-      <c r="G747" s="9" t="s">
-        <v>1595</v>
       </c>
       <c r="H747" s="10" t="n">
         <v>46185</v>
@@ -49508,10 +49523,10 @@
         <v>24</v>
       </c>
       <c r="F748" s="4" t="s">
+        <v>1595</v>
+      </c>
+      <c r="G748" s="4" t="s">
         <v>1596</v>
-      </c>
-      <c r="G748" s="4" t="s">
-        <v>1597</v>
       </c>
       <c r="H748" s="5" t="n">
         <v>46185</v>
@@ -49569,7 +49584,7 @@
         <v>704</v>
       </c>
       <c r="G749" s="9" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H749" s="10" t="n">
         <v>46188</v>
@@ -49624,10 +49639,10 @@
         <v>24</v>
       </c>
       <c r="F750" s="4" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G750" s="4" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H750" s="5" t="n">
         <v>46188</v>
@@ -49685,7 +49700,7 @@
         <v>228</v>
       </c>
       <c r="G751" s="9" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H751" s="10" t="n">
         <v>46188</v>
@@ -49743,7 +49758,7 @@
         <v>228</v>
       </c>
       <c r="G752" s="4" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H752" s="5" t="n">
         <v>46188</v>
@@ -49801,7 +49816,7 @@
         <v>589</v>
       </c>
       <c r="G753" s="9" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H753" s="10" t="n">
         <v>46189</v>
@@ -49856,22 +49871,22 @@
         <v>24</v>
       </c>
       <c r="F754" s="4" t="s">
+        <v>1602</v>
+      </c>
+      <c r="G754" s="4" t="s">
         <v>1603</v>
-      </c>
-      <c r="G754" s="4" t="s">
-        <v>1604</v>
       </c>
       <c r="H754" s="5" t="n">
         <v>46188</v>
       </c>
       <c r="I754" s="4" t="s">
+        <v>1604</v>
+      </c>
+      <c r="J754" s="4" t="s">
         <v>1605</v>
       </c>
-      <c r="J754" s="4" t="s">
+      <c r="K754" s="4" t="s">
         <v>1606</v>
-      </c>
-      <c r="K754" s="4" t="s">
-        <v>1607</v>
       </c>
       <c r="L754" s="5"/>
       <c r="M754" s="5"/>
@@ -49917,7 +49932,7 @@
         <v>1298</v>
       </c>
       <c r="G755" s="9" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H755" s="10" t="n">
         <v>46188</v>
@@ -49975,7 +49990,7 @@
         <v>152</v>
       </c>
       <c r="G756" s="4" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H756" s="5" t="n">
         <v>46189</v>
@@ -50033,7 +50048,7 @@
         <v>1296</v>
       </c>
       <c r="G757" s="9" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H757" s="10" t="n">
         <v>46189</v>
@@ -50091,7 +50106,7 @@
         <v>1296</v>
       </c>
       <c r="G758" s="4" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H758" s="5" t="n">
         <v>46189</v>
@@ -50149,7 +50164,7 @@
         <v>402</v>
       </c>
       <c r="G759" s="9" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H759" s="10" t="n">
         <v>46190</v>
@@ -50204,22 +50219,22 @@
         <v>24</v>
       </c>
       <c r="F760" s="4" t="s">
+        <v>1612</v>
+      </c>
+      <c r="G760" s="4" t="s">
         <v>1613</v>
-      </c>
-      <c r="G760" s="4" t="s">
-        <v>1614</v>
       </c>
       <c r="H760" s="5" t="n">
         <v>46189</v>
       </c>
       <c r="I760" s="4" t="s">
+        <v>1614</v>
+      </c>
+      <c r="J760" s="4" t="s">
         <v>1615</v>
       </c>
-      <c r="J760" s="4" t="s">
+      <c r="K760" s="4" t="s">
         <v>1616</v>
-      </c>
-      <c r="K760" s="4" t="s">
-        <v>1617</v>
       </c>
       <c r="L760" s="5"/>
       <c r="M760" s="5"/>
@@ -50233,7 +50248,7 @@
         <v>1455</v>
       </c>
       <c r="Q760" s="4" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="R760" s="7" t="n">
         <v>2230.4</v>
@@ -50265,7 +50280,7 @@
         <v>157</v>
       </c>
       <c r="G761" s="9" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H761" s="10" t="n">
         <v>46189</v>
@@ -50320,22 +50335,22 @@
         <v>24</v>
       </c>
       <c r="F762" s="4" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G762" s="4" t="s">
         <v>1620</v>
-      </c>
-      <c r="G762" s="4" t="s">
-        <v>1621</v>
       </c>
       <c r="H762" s="5" t="n">
         <v>46191</v>
       </c>
       <c r="I762" s="4" t="s">
+        <v>1621</v>
+      </c>
+      <c r="J762" s="4" t="s">
         <v>1622</v>
       </c>
-      <c r="J762" s="4" t="s">
+      <c r="K762" s="4" t="s">
         <v>1623</v>
-      </c>
-      <c r="K762" s="4" t="s">
-        <v>1624</v>
       </c>
       <c r="L762" s="5"/>
       <c r="M762" s="5"/>
@@ -50381,7 +50396,7 @@
         <v>892</v>
       </c>
       <c r="G763" s="9" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H763" s="10" t="n">
         <v>46191</v>
@@ -50439,7 +50454,7 @@
         <v>502</v>
       </c>
       <c r="G764" s="4" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H764" s="5" t="n">
         <v>46190</v>
@@ -50497,7 +50512,7 @@
         <v>322</v>
       </c>
       <c r="G765" s="9" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H765" s="10" t="n">
         <v>46190</v>
@@ -50555,7 +50570,7 @@
         <v>1488</v>
       </c>
       <c r="G766" s="4" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H766" s="5" t="n">
         <v>46192</v>
@@ -50613,7 +50628,7 @@
         <v>249</v>
       </c>
       <c r="G767" s="9" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H767" s="10" t="n">
         <v>46191</v>
@@ -50668,10 +50683,10 @@
         <v>24</v>
       </c>
       <c r="F768" s="4" t="s">
+        <v>1629</v>
+      </c>
+      <c r="G768" s="4" t="s">
         <v>1630</v>
-      </c>
-      <c r="G768" s="4" t="s">
-        <v>1631</v>
       </c>
       <c r="H768" s="5" t="n">
         <v>46191</v>
@@ -50726,10 +50741,10 @@
         <v>24</v>
       </c>
       <c r="F769" s="9" t="s">
+        <v>1631</v>
+      </c>
+      <c r="G769" s="9" t="s">
         <v>1632</v>
-      </c>
-      <c r="G769" s="9" t="s">
-        <v>1633</v>
       </c>
       <c r="H769" s="11" t="n">
         <v>46196.641111111</v>
@@ -50752,7 +50767,7 @@
         <v>46198.434918947</v>
       </c>
       <c r="P769" s="9" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="Q769" s="9" t="s">
         <v>74</v>
@@ -50787,7 +50802,7 @@
         <v>904</v>
       </c>
       <c r="G770" s="4" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H770" s="5" t="n">
         <v>46195</v>
@@ -50845,7 +50860,7 @@
         <v>888</v>
       </c>
       <c r="G771" s="9" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H771" s="10" t="n">
         <v>46192</v>
@@ -50897,13 +50912,13 @@
         <v>23</v>
       </c>
       <c r="E772" s="3" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="F772" s="4" t="s">
         <v>997</v>
       </c>
       <c r="G772" s="4" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H772" s="5" t="n">
         <v>46198</v>
@@ -50961,7 +50976,7 @@
         <v>276</v>
       </c>
       <c r="G773" s="9" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H773" s="10" t="n">
         <v>46198</v>
@@ -51013,13 +51028,13 @@
         <v>23</v>
       </c>
       <c r="E774" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F774" s="4" t="s">
+        <v>1639</v>
+      </c>
+      <c r="G774" s="4" t="s">
         <v>1640</v>
-      </c>
-      <c r="F774" s="4" t="s">
-        <v>1641</v>
-      </c>
-      <c r="G774" s="4" t="s">
-        <v>1642</v>
       </c>
       <c r="H774" s="5" t="n">
         <v>46198</v>
@@ -51036,7 +51051,7 @@
       <c r="L774" s="5"/>
       <c r="M774" s="5"/>
       <c r="N774" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O774" s="6" t="n">
         <v>46199.356272685</v>
@@ -51048,10 +51063,10 @@
         <v>68</v>
       </c>
       <c r="R774" s="7" t="n">
-        <v>96792.892</v>
+        <v>97657.108</v>
       </c>
       <c r="S774" s="7" t="n">
-        <v>87836.912</v>
+        <v>97723.108</v>
       </c>
       <c r="T774" s="4" t="s">
         <v>32</v>
@@ -51077,7 +51092,7 @@
         <v>1271</v>
       </c>
       <c r="G775" s="9" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="H775" s="10" t="n">
         <v>46196</v>
@@ -51135,7 +51150,7 @@
         <v>1264</v>
       </c>
       <c r="G776" s="4" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="H776" s="5" t="n">
         <v>46195</v>
@@ -51193,7 +51208,7 @@
         <v>496</v>
       </c>
       <c r="G777" s="9" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="H777" s="10" t="n">
         <v>46198</v>
@@ -51251,7 +51266,7 @@
         <v>1075</v>
       </c>
       <c r="G778" s="4" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="H778" s="5" t="n">
         <v>46198</v>
@@ -51309,7 +51324,7 @@
         <v>945</v>
       </c>
       <c r="G779" s="9" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="H779" s="10" t="n">
         <v>46198</v>
@@ -51367,7 +51382,7 @@
         <v>1459</v>
       </c>
       <c r="G780" s="4" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="H780" s="5" t="n">
         <v>46198</v>
@@ -51422,10 +51437,10 @@
         <v>24</v>
       </c>
       <c r="F781" s="9" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="G781" s="9" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="H781" s="10" t="n">
         <v>46198</v>
@@ -51483,7 +51498,7 @@
         <v>191</v>
       </c>
       <c r="G782" s="4" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="H782" s="5" t="n">
         <v>46198</v>
@@ -51535,13 +51550,13 @@
         <v>23</v>
       </c>
       <c r="E783" s="8" t="s">
-        <v>1652</v>
+        <v>24</v>
       </c>
       <c r="F783" s="9" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="G783" s="9" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="H783" s="10" t="n">
         <v>46197</v>
@@ -51558,7 +51573,7 @@
       <c r="L783" s="10"/>
       <c r="M783" s="10"/>
       <c r="N783" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O783" s="11" t="n">
         <v>46202.342017975</v>
@@ -51573,7 +51588,7 @@
         <v>47317.36</v>
       </c>
       <c r="S783" s="12" t="n">
-        <v>20519.76</v>
+        <v>47317.36</v>
       </c>
       <c r="T783" s="9" t="s">
         <v>32</v>
@@ -51599,7 +51614,7 @@
         <v>124</v>
       </c>
       <c r="G784" s="4" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="H784" s="5" t="n">
         <v>46198</v>
@@ -51657,7 +51672,7 @@
         <v>75</v>
       </c>
       <c r="G785" s="9" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
       <c r="H785" s="10" t="n">
         <v>46199</v>
@@ -51715,7 +51730,7 @@
         <v>332</v>
       </c>
       <c r="G786" s="4" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
       <c r="H786" s="5" t="n">
         <v>46199</v>
@@ -51773,7 +51788,7 @@
         <v>1473</v>
       </c>
       <c r="G787" s="9" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
       <c r="H787" s="11" t="n">
         <v>46202.697662037</v>
@@ -51831,7 +51846,7 @@
         <v>249</v>
       </c>
       <c r="G788" s="4" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
       <c r="H788" s="6" t="n">
         <v>46203.350740741</v>
@@ -51889,7 +51904,7 @@
         <v>1102</v>
       </c>
       <c r="G789" s="9" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
       <c r="H789" s="11" t="n">
         <v>46203.360023148</v>
@@ -51947,7 +51962,7 @@
         <v>295</v>
       </c>
       <c r="G790" s="4" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="H790" s="6" t="n">
         <v>46199.437291667</v>
@@ -52005,7 +52020,7 @@
         <v>262</v>
       </c>
       <c r="G791" s="9" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
       <c r="H791" s="11" t="n">
         <v>46199.61</v>
@@ -52063,7 +52078,7 @@
         <v>58</v>
       </c>
       <c r="G792" s="4" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="H792" s="5" t="n">
         <v>46203</v>
@@ -52121,7 +52136,7 @@
         <v>1099</v>
       </c>
       <c r="G793" s="9" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="H793" s="10" t="n">
         <v>46199</v>
@@ -52179,7 +52194,7 @@
         <v>1516</v>
       </c>
       <c r="G794" s="4" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="H794" s="5" t="n">
         <v>46203</v>
@@ -52234,10 +52249,10 @@
         <v>24</v>
       </c>
       <c r="F795" s="9" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="G795" s="9" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="H795" s="11" t="n">
         <v>46203.499918981</v>
@@ -52295,7 +52310,7 @@
         <v>357</v>
       </c>
       <c r="G796" s="4" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="H796" s="5" t="n">
         <v>46203</v>
@@ -52353,7 +52368,7 @@
         <v>955</v>
       </c>
       <c r="G797" s="9" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="H797" s="11" t="n">
         <v>46204.462268519</v>
@@ -52405,13 +52420,13 @@
         <v>23</v>
       </c>
       <c r="E798" s="3" t="s">
-        <v>1670</v>
+        <v>24</v>
       </c>
       <c r="F798" s="4" t="s">
         <v>1298</v>
       </c>
       <c r="G798" s="4" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="H798" s="5" t="n">
         <v>46205</v>
@@ -52428,7 +52443,7 @@
       <c r="L798" s="5"/>
       <c r="M798" s="5"/>
       <c r="N798" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O798" s="6" t="n">
         <v>46205.617754861</v>
@@ -52443,7 +52458,7 @@
         <v>47102.9</v>
       </c>
       <c r="S798" s="7" t="n">
-        <v>18465.5</v>
+        <v>47102.9</v>
       </c>
       <c r="T798" s="4" t="s">
         <v>32</v>
@@ -52466,22 +52481,22 @@
         <v>24</v>
       </c>
       <c r="F799" s="9" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="G799" s="9" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="H799" s="10" t="n">
         <v>46205</v>
       </c>
       <c r="I799" s="9" t="s">
+        <v>1614</v>
+      </c>
+      <c r="J799" s="9" t="s">
         <v>1615</v>
       </c>
-      <c r="J799" s="9" t="s">
+      <c r="K799" s="9" t="s">
         <v>1616</v>
-      </c>
-      <c r="K799" s="9" t="s">
-        <v>1617</v>
       </c>
       <c r="L799" s="10"/>
       <c r="M799" s="10"/>
@@ -52495,7 +52510,7 @@
         <v>1455</v>
       </c>
       <c r="Q799" s="9" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="R799" s="12" t="n">
         <v>5000</v>
@@ -52524,22 +52539,22 @@
         <v>24</v>
       </c>
       <c r="F800" s="4" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="G800" s="4" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="H800" s="6" t="n">
         <v>46205.688020833</v>
       </c>
       <c r="I800" s="4" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="J800" s="4" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="K800" s="4" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="L800" s="5"/>
       <c r="M800" s="5"/>
@@ -52585,7 +52600,7 @@
         <v>1427</v>
       </c>
       <c r="G801" s="9" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="H801" s="11" t="n">
         <v>46205.676435185</v>
@@ -52640,10 +52655,10 @@
         <v>24</v>
       </c>
       <c r="F802" s="4" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="G802" s="4" t="s">
-        <v>1679</v>
+        <v>1675</v>
       </c>
       <c r="H802" s="5" t="n">
         <v>46206</v>
@@ -52698,10 +52713,10 @@
         <v>24</v>
       </c>
       <c r="F803" s="9" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="G803" s="9" t="s">
-        <v>1680</v>
+        <v>1676</v>
       </c>
       <c r="H803" s="10" t="n">
         <v>46206</v>
@@ -52759,7 +52774,7 @@
         <v>366</v>
       </c>
       <c r="G804" s="4" t="s">
-        <v>1681</v>
+        <v>1677</v>
       </c>
       <c r="H804" s="5" t="n">
         <v>46209</v>
@@ -52817,7 +52832,7 @@
         <v>829</v>
       </c>
       <c r="G805" s="9" t="s">
-        <v>1682</v>
+        <v>1678</v>
       </c>
       <c r="H805" s="11" t="n">
         <v>46210.393460648</v>
@@ -52872,10 +52887,10 @@
         <v>24</v>
       </c>
       <c r="F806" s="4" t="s">
-        <v>1683</v>
+        <v>1679</v>
       </c>
       <c r="G806" s="4" t="s">
-        <v>1684</v>
+        <v>1680</v>
       </c>
       <c r="H806" s="5" t="n">
         <v>46210</v>
@@ -52927,25 +52942,25 @@
         <v>23</v>
       </c>
       <c r="E807" s="8" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
       <c r="F807" s="9" t="s">
-        <v>1686</v>
+        <v>1682</v>
       </c>
       <c r="G807" s="9" t="s">
-        <v>1687</v>
+        <v>1683</v>
       </c>
       <c r="H807" s="10" t="n">
         <v>46209</v>
       </c>
       <c r="I807" s="9" t="s">
-        <v>1688</v>
+        <v>1684</v>
       </c>
       <c r="J807" s="9" t="s">
-        <v>1689</v>
+        <v>1685</v>
       </c>
       <c r="K807" s="9" t="s">
-        <v>1690</v>
+        <v>1686</v>
       </c>
       <c r="L807" s="10"/>
       <c r="M807" s="10"/>
@@ -52959,7 +52974,7 @@
         <v>1455</v>
       </c>
       <c r="Q807" s="9" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="R807" s="12" t="n">
         <v>57832.4</v>
@@ -52968,7 +52983,7 @@
         <v>44782.4</v>
       </c>
       <c r="T807" s="9" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="U807" s="9"/>
       <c r="V807" s="9"/>
@@ -52991,7 +53006,7 @@
         <v>1516</v>
       </c>
       <c r="G808" s="4" t="s">
-        <v>1693</v>
+        <v>1689</v>
       </c>
       <c r="H808" s="5" t="n">
         <v>46212</v>
@@ -53046,22 +53061,22 @@
         <v>24</v>
       </c>
       <c r="F809" s="9" t="s">
-        <v>1694</v>
+        <v>1690</v>
       </c>
       <c r="G809" s="9" t="s">
-        <v>1695</v>
+        <v>1691</v>
       </c>
       <c r="H809" s="10" t="n">
         <v>46209</v>
       </c>
       <c r="I809" s="9" t="s">
-        <v>1694</v>
+        <v>1690</v>
       </c>
       <c r="J809" s="9" t="s">
-        <v>1696</v>
+        <v>1692</v>
       </c>
       <c r="K809" s="9" t="s">
-        <v>1697</v>
+        <v>1693</v>
       </c>
       <c r="L809" s="10"/>
       <c r="M809" s="10"/>
@@ -53075,7 +53090,7 @@
         <v>1455</v>
       </c>
       <c r="Q809" s="9" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="R809" s="12" t="n">
         <v>12246.14</v>
@@ -53084,7 +53099,7 @@
         <v>12246.14</v>
       </c>
       <c r="T809" s="9" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="U809" s="9"/>
       <c r="V809" s="9"/>
@@ -53104,22 +53119,22 @@
         <v>24</v>
       </c>
       <c r="F810" s="4" t="s">
-        <v>1698</v>
+        <v>1694</v>
       </c>
       <c r="G810" s="4" t="s">
-        <v>1699</v>
+        <v>1695</v>
       </c>
       <c r="H810" s="5" t="n">
         <v>46209</v>
       </c>
       <c r="I810" s="4" t="s">
-        <v>1700</v>
+        <v>1696</v>
       </c>
       <c r="J810" s="4" t="s">
-        <v>1701</v>
+        <v>1697</v>
       </c>
       <c r="K810" s="4" t="s">
-        <v>1702</v>
+        <v>1698</v>
       </c>
       <c r="L810" s="5"/>
       <c r="M810" s="5"/>
@@ -53133,7 +53148,7 @@
         <v>1455</v>
       </c>
       <c r="Q810" s="4" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="R810" s="7" t="n">
         <v>12246.14</v>
@@ -53142,7 +53157,7 @@
         <v>12246.14</v>
       </c>
       <c r="T810" s="4" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="U810" s="4"/>
       <c r="V810" s="4"/>
@@ -53162,22 +53177,22 @@
         <v>24</v>
       </c>
       <c r="F811" s="9" t="s">
-        <v>1703</v>
+        <v>1699</v>
       </c>
       <c r="G811" s="9" t="s">
-        <v>1704</v>
+        <v>1700</v>
       </c>
       <c r="H811" s="10" t="n">
         <v>46212</v>
       </c>
       <c r="I811" s="9" t="s">
-        <v>1705</v>
+        <v>1701</v>
       </c>
       <c r="J811" s="9" t="s">
-        <v>1706</v>
+        <v>1702</v>
       </c>
       <c r="K811" s="9" t="s">
-        <v>1707</v>
+        <v>1703</v>
       </c>
       <c r="L811" s="10"/>
       <c r="M811" s="10"/>
@@ -53191,7 +53206,7 @@
         <v>1455</v>
       </c>
       <c r="Q811" s="9" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="R811" s="12" t="n">
         <v>46556.88</v>
@@ -53200,7 +53215,7 @@
         <v>46556.88</v>
       </c>
       <c r="T811" s="9" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="U811" s="9"/>
       <c r="V811" s="9"/>
@@ -53220,10 +53235,10 @@
         <v>24</v>
       </c>
       <c r="F812" s="4" t="s">
-        <v>1708</v>
+        <v>1704</v>
       </c>
       <c r="G812" s="4" t="s">
-        <v>1709</v>
+        <v>1705</v>
       </c>
       <c r="H812" s="6" t="n">
         <v>46212.609872685</v>
@@ -53278,10 +53293,10 @@
         <v>24</v>
       </c>
       <c r="F813" s="9" t="s">
-        <v>1710</v>
+        <v>1706</v>
       </c>
       <c r="G813" s="9" t="s">
-        <v>1711</v>
+        <v>1707</v>
       </c>
       <c r="H813" s="11" t="n">
         <v>46212.603854167</v>
@@ -53339,7 +53354,7 @@
         <v>328</v>
       </c>
       <c r="G814" s="4" t="s">
-        <v>1712</v>
+        <v>1708</v>
       </c>
       <c r="H814" s="6" t="n">
         <v>46212.706458333</v>
@@ -53397,7 +53412,7 @@
         <v>75</v>
       </c>
       <c r="G815" s="9" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
       <c r="H815" s="11" t="n">
         <v>46216.38931713</v>
@@ -53455,7 +53470,7 @@
         <v>389</v>
       </c>
       <c r="G816" s="4" t="s">
-        <v>1714</v>
+        <v>1710</v>
       </c>
       <c r="H816" s="6" t="n">
         <v>46213.494444444</v>
@@ -53513,7 +53528,7 @@
         <v>249</v>
       </c>
       <c r="G817" s="9" t="s">
-        <v>1715</v>
+        <v>1711</v>
       </c>
       <c r="H817" s="11" t="n">
         <v>46216.315104167</v>
@@ -53568,10 +53583,10 @@
         <v>24</v>
       </c>
       <c r="F818" s="4" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="G818" s="4" t="s">
-        <v>1716</v>
+        <v>1712</v>
       </c>
       <c r="H818" s="6" t="n">
         <v>46216.636458333</v>
@@ -53629,7 +53644,7 @@
         <v>1411</v>
       </c>
       <c r="G819" s="9" t="s">
-        <v>1717</v>
+        <v>1713</v>
       </c>
       <c r="H819" s="11" t="n">
         <v>46216.752118056</v>
@@ -53687,7 +53702,7 @@
         <v>164</v>
       </c>
       <c r="G820" s="4" t="s">
-        <v>1718</v>
+        <v>1714</v>
       </c>
       <c r="H820" s="6" t="n">
         <v>46216.772175926</v>
@@ -53745,7 +53760,7 @@
         <v>1488</v>
       </c>
       <c r="G821" s="9" t="s">
-        <v>1719</v>
+        <v>1715</v>
       </c>
       <c r="H821" s="10" t="n">
         <v>46217</v>
@@ -53800,10 +53815,10 @@
         <v>24</v>
       </c>
       <c r="F822" s="4" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="G822" s="4" t="s">
-        <v>1720</v>
+        <v>1716</v>
       </c>
       <c r="H822" s="6" t="n">
         <v>46217.426458333</v>
@@ -53861,7 +53876,7 @@
         <v>1373</v>
       </c>
       <c r="G823" s="9" t="s">
-        <v>1721</v>
+        <v>1717</v>
       </c>
       <c r="H823" s="10" t="n">
         <v>46217</v>
@@ -53916,10 +53931,10 @@
         <v>24</v>
       </c>
       <c r="F824" s="4" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="G824" s="4" t="s">
-        <v>1722</v>
+        <v>1718</v>
       </c>
       <c r="H824" s="5" t="n">
         <v>46219</v>
@@ -53974,10 +53989,10 @@
         <v>24</v>
       </c>
       <c r="F825" s="9" t="s">
-        <v>1723</v>
+        <v>1719</v>
       </c>
       <c r="G825" s="9" t="s">
-        <v>1724</v>
+        <v>1720</v>
       </c>
       <c r="H825" s="10" t="n">
         <v>46219</v>
@@ -54035,7 +54050,7 @@
         <v>1471</v>
       </c>
       <c r="G826" s="4" t="s">
-        <v>1725</v>
+        <v>1721</v>
       </c>
       <c r="H826" s="5" t="n">
         <v>46219</v>
@@ -54093,7 +54108,7 @@
         <v>332</v>
       </c>
       <c r="G827" s="9" t="s">
-        <v>1726</v>
+        <v>1722</v>
       </c>
       <c r="H827" s="11" t="n">
         <v>46218.657847222</v>
@@ -54148,10 +54163,10 @@
         <v>24</v>
       </c>
       <c r="F828" s="4" t="s">
-        <v>1727</v>
+        <v>1723</v>
       </c>
       <c r="G828" s="4" t="s">
-        <v>1728</v>
+        <v>1724</v>
       </c>
       <c r="H828" s="6" t="n">
         <v>46218.558854167</v>
@@ -54209,7 +54224,7 @@
         <v>484</v>
       </c>
       <c r="G829" s="9" t="s">
-        <v>1729</v>
+        <v>1725</v>
       </c>
       <c r="H829" s="11" t="n">
         <v>46218.501886574</v>
@@ -54261,13 +54276,13 @@
         <v>23</v>
       </c>
       <c r="E830" s="3" t="s">
-        <v>1730</v>
+        <v>24</v>
       </c>
       <c r="F830" s="4" t="s">
         <v>1264</v>
       </c>
       <c r="G830" s="4" t="s">
-        <v>1731</v>
+        <v>1726</v>
       </c>
       <c r="H830" s="5" t="n">
         <v>46219</v>
@@ -54284,7 +54299,7 @@
       <c r="L830" s="5"/>
       <c r="M830" s="5"/>
       <c r="N830" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O830" s="6" t="n">
         <v>46219.675766285</v>
@@ -54299,7 +54314,7 @@
         <v>102750</v>
       </c>
       <c r="S830" s="7" t="n">
-        <v>85899</v>
+        <v>102750</v>
       </c>
       <c r="T830" s="4" t="s">
         <v>32</v>
@@ -54325,7 +54340,7 @@
         <v>310</v>
       </c>
       <c r="G831" s="9" t="s">
-        <v>1732</v>
+        <v>1727</v>
       </c>
       <c r="H831" s="10" t="n">
         <v>46219</v>
@@ -54383,7 +54398,7 @@
         <v>969</v>
       </c>
       <c r="G832" s="4" t="s">
-        <v>1733</v>
+        <v>1728</v>
       </c>
       <c r="H832" s="5" t="n">
         <v>46219</v>
@@ -54438,22 +54453,22 @@
         <v>24</v>
       </c>
       <c r="F833" s="9" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="G833" s="9" t="s">
-        <v>1735</v>
+        <v>1730</v>
       </c>
       <c r="H833" s="11" t="n">
         <v>46219.727233796</v>
       </c>
       <c r="I833" s="9" t="s">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="J833" s="9" t="s">
-        <v>1737</v>
+        <v>1732</v>
       </c>
       <c r="K833" s="9" t="s">
-        <v>1738</v>
+        <v>1733</v>
       </c>
       <c r="L833" s="10"/>
       <c r="M833" s="10"/>
@@ -54499,7 +54514,7 @@
         <v>1328</v>
       </c>
       <c r="G834" s="4" t="s">
-        <v>1739</v>
+        <v>1734</v>
       </c>
       <c r="H834" s="5" t="n">
         <v>46220</v>
@@ -54554,10 +54569,10 @@
         <v>24</v>
       </c>
       <c r="F835" s="9" t="s">
-        <v>1740</v>
+        <v>1735</v>
       </c>
       <c r="G835" s="9" t="s">
-        <v>1741</v>
+        <v>1736</v>
       </c>
       <c r="H835" s="10" t="n">
         <v>46223</v>
@@ -54612,10 +54627,10 @@
         <v>24</v>
       </c>
       <c r="F836" s="4" t="s">
-        <v>1742</v>
+        <v>1737</v>
       </c>
       <c r="G836" s="4" t="s">
-        <v>1743</v>
+        <v>1738</v>
       </c>
       <c r="H836" s="5" t="n">
         <v>46224</v>
@@ -54670,10 +54685,10 @@
         <v>24</v>
       </c>
       <c r="F837" s="9" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G837" s="9" t="s">
-        <v>1744</v>
+        <v>1739</v>
       </c>
       <c r="H837" s="10" t="n">
         <v>46225</v>
@@ -54731,7 +54746,7 @@
         <v>1264</v>
       </c>
       <c r="G838" s="4" t="s">
-        <v>1745</v>
+        <v>1740</v>
       </c>
       <c r="H838" s="5" t="n">
         <v>46224</v>
@@ -54789,7 +54804,7 @@
         <v>203</v>
       </c>
       <c r="G839" s="9" t="s">
-        <v>1746</v>
+        <v>1741</v>
       </c>
       <c r="H839" s="10" t="n">
         <v>46224</v>
@@ -54847,7 +54862,7 @@
         <v>310</v>
       </c>
       <c r="G840" s="4" t="s">
-        <v>1747</v>
+        <v>1742</v>
       </c>
       <c r="H840" s="5" t="n">
         <v>46224</v>
@@ -54902,10 +54917,10 @@
         <v>24</v>
       </c>
       <c r="F841" s="9" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="G841" s="9" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="H841" s="10" t="n">
         <v>46224</v>
@@ -54960,10 +54975,10 @@
         <v>24</v>
       </c>
       <c r="F842" s="4" t="s">
-        <v>1750</v>
+        <v>1745</v>
       </c>
       <c r="G842" s="4" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="H842" s="5" t="n">
         <v>46224</v>
@@ -55018,10 +55033,10 @@
         <v>24</v>
       </c>
       <c r="F843" s="9" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="G843" s="9" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="H843" s="10" t="n">
         <v>46224</v>
@@ -55076,10 +55091,10 @@
         <v>24</v>
       </c>
       <c r="F844" s="4" t="s">
-        <v>1754</v>
+        <v>1749</v>
       </c>
       <c r="G844" s="4" t="s">
-        <v>1755</v>
+        <v>1750</v>
       </c>
       <c r="H844" s="5" t="n">
         <v>46225</v>
@@ -55134,22 +55149,22 @@
         <v>24</v>
       </c>
       <c r="F845" s="9" t="s">
-        <v>1756</v>
+        <v>1751</v>
       </c>
       <c r="G845" s="9" t="s">
-        <v>1757</v>
+        <v>1752</v>
       </c>
       <c r="H845" s="10" t="n">
         <v>46225</v>
       </c>
       <c r="I845" s="9" t="s">
-        <v>1756</v>
+        <v>1751</v>
       </c>
       <c r="J845" s="9" t="s">
-        <v>1758</v>
+        <v>1753</v>
       </c>
       <c r="K845" s="9" t="s">
-        <v>1759</v>
+        <v>1754</v>
       </c>
       <c r="L845" s="10"/>
       <c r="M845" s="10"/>
@@ -55192,22 +55207,22 @@
         <v>24</v>
       </c>
       <c r="F846" s="4" t="s">
-        <v>1760</v>
+        <v>1755</v>
       </c>
       <c r="G846" s="4" t="s">
-        <v>1761</v>
+        <v>1756</v>
       </c>
       <c r="H846" s="5" t="n">
         <v>46226</v>
       </c>
       <c r="I846" s="4" t="s">
-        <v>1762</v>
+        <v>1757</v>
       </c>
       <c r="J846" s="4" t="s">
-        <v>1762</v>
+        <v>1757</v>
       </c>
       <c r="K846" s="4" t="s">
-        <v>1763</v>
+        <v>1758</v>
       </c>
       <c r="L846" s="5"/>
       <c r="M846" s="5"/>
@@ -55253,7 +55268,7 @@
         <v>592</v>
       </c>
       <c r="G847" s="9" t="s">
-        <v>1764</v>
+        <v>1759</v>
       </c>
       <c r="H847" s="10" t="n">
         <v>46226</v>
@@ -55311,7 +55326,7 @@
         <v>1179</v>
       </c>
       <c r="G848" s="4" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="H848" s="5" t="n">
         <v>46227</v>
@@ -55369,7 +55384,7 @@
         <v>623</v>
       </c>
       <c r="G849" s="9" t="s">
-        <v>1766</v>
+        <v>1761</v>
       </c>
       <c r="H849" s="10" t="n">
         <v>46225</v>
@@ -55427,7 +55442,7 @@
         <v>310</v>
       </c>
       <c r="G850" s="4" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
       <c r="H850" s="5" t="n">
         <v>46226</v>
@@ -55482,10 +55497,10 @@
         <v>24</v>
       </c>
       <c r="F851" s="9" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G851" s="9" t="s">
-        <v>1768</v>
+        <v>1763</v>
       </c>
       <c r="H851" s="10" t="n">
         <v>46225</v>
@@ -55543,7 +55558,7 @@
         <v>581</v>
       </c>
       <c r="G852" s="4" t="s">
-        <v>1769</v>
+        <v>1764</v>
       </c>
       <c r="H852" s="5" t="n">
         <v>46224</v>
@@ -55601,7 +55616,7 @@
         <v>1516</v>
       </c>
       <c r="G853" s="9" t="s">
-        <v>1770</v>
+        <v>1765</v>
       </c>
       <c r="H853" s="10" t="n">
         <v>46230</v>
@@ -55656,22 +55671,22 @@
         <v>24</v>
       </c>
       <c r="F854" s="4" t="s">
-        <v>1771</v>
+        <v>1766</v>
       </c>
       <c r="G854" s="4" t="s">
-        <v>1772</v>
+        <v>1767</v>
       </c>
       <c r="H854" s="5" t="n">
         <v>46227</v>
       </c>
       <c r="I854" s="4" t="s">
-        <v>1771</v>
+        <v>1766</v>
       </c>
       <c r="J854" s="4" t="s">
-        <v>1773</v>
+        <v>1768</v>
       </c>
       <c r="K854" s="4" t="s">
-        <v>1774</v>
+        <v>1769</v>
       </c>
       <c r="L854" s="5"/>
       <c r="M854" s="5"/>
@@ -55711,25 +55726,25 @@
         <v>23</v>
       </c>
       <c r="E855" s="8" t="s">
-        <v>1775</v>
+        <v>1770</v>
       </c>
       <c r="F855" s="9" t="s">
-        <v>1776</v>
+        <v>1771</v>
       </c>
       <c r="G855" s="9" t="s">
-        <v>1777</v>
+        <v>1772</v>
       </c>
       <c r="H855" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I855" s="9" t="s">
-        <v>1776</v>
+        <v>1771</v>
       </c>
       <c r="J855" s="9" t="s">
-        <v>1778</v>
+        <v>1773</v>
       </c>
       <c r="K855" s="9" t="s">
-        <v>1779</v>
+        <v>1774</v>
       </c>
       <c r="L855" s="10"/>
       <c r="M855" s="10"/>
@@ -55743,7 +55758,7 @@
         <v>1455</v>
       </c>
       <c r="Q855" s="9" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="R855" s="12" t="n">
         <v>176352</v>
@@ -55775,7 +55790,7 @@
         <v>276</v>
       </c>
       <c r="G856" s="4" t="s">
-        <v>1780</v>
+        <v>1775</v>
       </c>
       <c r="H856" s="5" t="n">
         <v>46230</v>
@@ -55833,7 +55848,7 @@
         <v>1280</v>
       </c>
       <c r="G857" s="9" t="s">
-        <v>1781</v>
+        <v>1776</v>
       </c>
       <c r="H857" s="10" t="n">
         <v>46231</v>
@@ -55891,7 +55906,7 @@
         <v>592</v>
       </c>
       <c r="G858" s="4" t="s">
-        <v>1782</v>
+        <v>1777</v>
       </c>
       <c r="H858" s="5" t="n">
         <v>46230</v>
@@ -55949,7 +55964,7 @@
         <v>1264</v>
       </c>
       <c r="G859" s="9" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="H859" s="10" t="n">
         <v>46231</v>
@@ -56004,10 +56019,10 @@
         <v>24</v>
       </c>
       <c r="F860" s="4" t="s">
-        <v>1784</v>
+        <v>1779</v>
       </c>
       <c r="G860" s="4" t="s">
-        <v>1785</v>
+        <v>1780</v>
       </c>
       <c r="H860" s="5" t="n">
         <v>46230</v>
@@ -56059,25 +56074,25 @@
         <v>23</v>
       </c>
       <c r="E861" s="8" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="F861" s="9" t="s">
-        <v>1787</v>
+        <v>1782</v>
       </c>
       <c r="G861" s="9" t="s">
-        <v>1788</v>
+        <v>1783</v>
       </c>
       <c r="H861" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I861" s="9" t="s">
-        <v>1789</v>
+        <v>1784</v>
       </c>
       <c r="J861" s="9" t="s">
-        <v>1790</v>
+        <v>1785</v>
       </c>
       <c r="K861" s="9" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="L861" s="10"/>
       <c r="M861" s="10"/>
@@ -56091,7 +56106,7 @@
         <v>1455</v>
       </c>
       <c r="Q861" s="9" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="R861" s="12" t="n">
         <v>39463.12</v>
@@ -56100,7 +56115,7 @@
         <v>16215.2</v>
       </c>
       <c r="T861" s="9" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="U861" s="9"/>
       <c r="V861" s="9"/>
@@ -56120,22 +56135,22 @@
         <v>24</v>
       </c>
       <c r="F862" s="4" t="s">
-        <v>1792</v>
+        <v>1787</v>
       </c>
       <c r="G862" s="4" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="H862" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="I862" s="4" t="s">
-        <v>1792</v>
+        <v>1787</v>
       </c>
       <c r="J862" s="4" t="s">
-        <v>1794</v>
+        <v>1789</v>
       </c>
       <c r="K862" s="4" t="s">
-        <v>1795</v>
+        <v>1790</v>
       </c>
       <c r="L862" s="5"/>
       <c r="M862" s="5"/>
@@ -56181,7 +56196,7 @@
         <v>859</v>
       </c>
       <c r="G863" s="9" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="H863" s="10" t="n">
         <v>46230</v>
@@ -56239,7 +56254,7 @@
         <v>262</v>
       </c>
       <c r="G864" s="4" t="s">
-        <v>1797</v>
+        <v>1792</v>
       </c>
       <c r="H864" s="5" t="n">
         <v>46230</v>
@@ -56294,22 +56309,22 @@
         <v>24</v>
       </c>
       <c r="F865" s="9" t="s">
-        <v>1798</v>
+        <v>1793</v>
       </c>
       <c r="G865" s="9" t="s">
-        <v>1799</v>
+        <v>1794</v>
       </c>
       <c r="H865" s="10" t="n">
         <v>46230</v>
       </c>
       <c r="I865" s="9" t="s">
-        <v>1800</v>
+        <v>1795</v>
       </c>
       <c r="J865" s="9" t="s">
-        <v>1800</v>
+        <v>1795</v>
       </c>
       <c r="K865" s="9" t="s">
-        <v>1801</v>
+        <v>1796</v>
       </c>
       <c r="L865" s="10"/>
       <c r="M865" s="10"/>
@@ -56355,7 +56370,7 @@
         <v>490</v>
       </c>
       <c r="G866" s="4" t="s">
-        <v>1802</v>
+        <v>1797</v>
       </c>
       <c r="H866" s="5" t="n">
         <v>46231</v>
@@ -56413,7 +56428,7 @@
         <v>521</v>
       </c>
       <c r="G867" s="9" t="s">
-        <v>1803</v>
+        <v>1798</v>
       </c>
       <c r="H867" s="10" t="n">
         <v>46232</v>
@@ -56468,10 +56483,10 @@
         <v>24</v>
       </c>
       <c r="F868" s="4" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="G868" s="4" t="s">
-        <v>1804</v>
+        <v>1799</v>
       </c>
       <c r="H868" s="5" t="n">
         <v>46231</v>
@@ -56529,7 +56544,7 @@
         <v>1133</v>
       </c>
       <c r="G869" s="9" t="s">
-        <v>1805</v>
+        <v>1800</v>
       </c>
       <c r="H869" s="10" t="n">
         <v>46233</v>
@@ -56584,10 +56599,10 @@
         <v>24</v>
       </c>
       <c r="F870" s="4" t="s">
-        <v>1806</v>
+        <v>1801</v>
       </c>
       <c r="G870" s="4" t="s">
-        <v>1807</v>
+        <v>1802</v>
       </c>
       <c r="H870" s="5" t="n">
         <v>46232</v>
@@ -56645,7 +56660,7 @@
         <v>355</v>
       </c>
       <c r="G871" s="9" t="s">
-        <v>1808</v>
+        <v>1803</v>
       </c>
       <c r="H871" s="10" t="n">
         <v>46232</v>
@@ -56703,7 +56718,7 @@
         <v>351</v>
       </c>
       <c r="G872" s="4" t="s">
-        <v>1809</v>
+        <v>1804</v>
       </c>
       <c r="H872" s="5" t="n">
         <v>46232</v>
@@ -56761,7 +56776,7 @@
         <v>945</v>
       </c>
       <c r="G873" s="9" t="s">
-        <v>1810</v>
+        <v>1805</v>
       </c>
       <c r="H873" s="10" t="n">
         <v>46232</v>
@@ -56819,7 +56834,7 @@
         <v>262</v>
       </c>
       <c r="G874" s="4" t="s">
-        <v>1811</v>
+        <v>1806</v>
       </c>
       <c r="H874" s="5" t="n">
         <v>46231</v>
@@ -56871,13 +56886,13 @@
         <v>23</v>
       </c>
       <c r="E875" s="8" t="s">
-        <v>952</v>
+        <v>24</v>
       </c>
       <c r="F875" s="9" t="s">
         <v>1264</v>
       </c>
       <c r="G875" s="9" t="s">
-        <v>1812</v>
+        <v>1807</v>
       </c>
       <c r="H875" s="10" t="n">
         <v>46232</v>
@@ -56909,7 +56924,7 @@
         <v>145422.56</v>
       </c>
       <c r="S875" s="12" t="n">
-        <v>138072.44</v>
+        <v>145422.56</v>
       </c>
       <c r="T875" s="9" t="s">
         <v>32</v>
@@ -56929,13 +56944,13 @@
         <v>23</v>
       </c>
       <c r="E876" s="3" t="s">
-        <v>1813</v>
+        <v>1808</v>
       </c>
       <c r="F876" s="4" t="s">
-        <v>1814</v>
+        <v>1809</v>
       </c>
       <c r="G876" s="4" t="s">
-        <v>1815</v>
+        <v>1810</v>
       </c>
       <c r="H876" s="5" t="n">
         <v>46232</v>
@@ -56993,7 +57008,7 @@
         <v>75</v>
       </c>
       <c r="G877" s="9" t="s">
-        <v>1816</v>
+        <v>1811</v>
       </c>
       <c r="H877" s="10" t="n">
         <v>46232</v>
@@ -57051,7 +57066,7 @@
         <v>408</v>
       </c>
       <c r="G878" s="4" t="s">
-        <v>1817</v>
+        <v>1812</v>
       </c>
       <c r="H878" s="5" t="n">
         <v>46232</v>
@@ -57068,7 +57083,7 @@
       <c r="L878" s="5"/>
       <c r="M878" s="5"/>
       <c r="N878" s="4" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="O878" s="6" t="n">
         <v>46233.675736539</v>
@@ -57109,7 +57124,7 @@
         <v>1473</v>
       </c>
       <c r="G879" s="9" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="H879" s="10" t="n">
         <v>46232</v>
@@ -57164,22 +57179,22 @@
         <v>24</v>
       </c>
       <c r="F880" s="4" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="G880" s="4" t="s">
-        <v>1821</v>
+        <v>1816</v>
       </c>
       <c r="H880" s="5" t="n">
         <v>46233</v>
       </c>
       <c r="I880" s="4" t="s">
-        <v>1822</v>
+        <v>1817</v>
       </c>
       <c r="J880" s="4" t="s">
-        <v>1823</v>
+        <v>1818</v>
       </c>
       <c r="K880" s="4" t="s">
-        <v>1824</v>
+        <v>1819</v>
       </c>
       <c r="L880" s="5"/>
       <c r="M880" s="5"/>
@@ -57219,13 +57234,13 @@
         <v>23</v>
       </c>
       <c r="E881" s="8" t="s">
-        <v>1285</v>
+        <v>24</v>
       </c>
       <c r="F881" s="9" t="s">
         <v>276</v>
       </c>
       <c r="G881" s="9" t="s">
-        <v>1825</v>
+        <v>1820</v>
       </c>
       <c r="H881" s="10" t="n">
         <v>46234</v>
@@ -57242,7 +57257,7 @@
       <c r="L881" s="10"/>
       <c r="M881" s="10"/>
       <c r="N881" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O881" s="11" t="n">
         <v>46234.504198461</v>
@@ -57257,7 +57272,7 @@
         <v>73636</v>
       </c>
       <c r="S881" s="12" t="n">
-        <v>54778</v>
+        <v>73636</v>
       </c>
       <c r="T881" s="9" t="s">
         <v>32</v>
@@ -57283,7 +57298,7 @@
         <v>1298</v>
       </c>
       <c r="G882" s="4" t="s">
-        <v>1826</v>
+        <v>1821</v>
       </c>
       <c r="H882" s="5" t="n">
         <v>46233</v>
@@ -57341,7 +57356,7 @@
         <v>1494</v>
       </c>
       <c r="G883" s="9" t="s">
-        <v>1827</v>
+        <v>1822</v>
       </c>
       <c r="H883" s="10" t="n">
         <v>46234</v>
@@ -57393,13 +57408,13 @@
         <v>23</v>
       </c>
       <c r="E884" s="3" t="s">
-        <v>1828</v>
+        <v>1823</v>
       </c>
       <c r="F884" s="4" t="s">
         <v>888</v>
       </c>
       <c r="G884" s="4" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="H884" s="5" t="n">
         <v>46234</v>
@@ -57454,10 +57469,10 @@
         <v>24</v>
       </c>
       <c r="F885" s="9" t="s">
-        <v>1806</v>
+        <v>1801</v>
       </c>
       <c r="G885" s="9" t="s">
-        <v>1830</v>
+        <v>1825</v>
       </c>
       <c r="H885" s="10" t="n">
         <v>46234</v>
@@ -57515,7 +57530,7 @@
         <v>1378</v>
       </c>
       <c r="G886" s="4" t="s">
-        <v>1831</v>
+        <v>1826</v>
       </c>
       <c r="H886" s="5" t="n">
         <v>46234</v>
@@ -57570,22 +57585,22 @@
         <v>24</v>
       </c>
       <c r="F887" s="9" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="G887" s="9" t="s">
-        <v>1832</v>
+        <v>1827</v>
       </c>
       <c r="H887" s="10" t="n">
         <v>46233</v>
       </c>
       <c r="I887" s="9" t="s">
+        <v>1604</v>
+      </c>
+      <c r="J887" s="9" t="s">
         <v>1605</v>
       </c>
-      <c r="J887" s="9" t="s">
+      <c r="K887" s="9" t="s">
         <v>1606</v>
-      </c>
-      <c r="K887" s="9" t="s">
-        <v>1607</v>
       </c>
       <c r="L887" s="10"/>
       <c r="M887" s="10"/>
@@ -57628,22 +57643,22 @@
         <v>24</v>
       </c>
       <c r="F888" s="4" t="s">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="G888" s="4" t="s">
-        <v>1833</v>
+        <v>1828</v>
       </c>
       <c r="H888" s="5" t="n">
         <v>46234</v>
       </c>
       <c r="I888" s="4" t="s">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="J888" s="4" t="s">
-        <v>1737</v>
+        <v>1732</v>
       </c>
       <c r="K888" s="4" t="s">
-        <v>1738</v>
+        <v>1733</v>
       </c>
       <c r="L888" s="5"/>
       <c r="M888" s="5"/>
@@ -57689,7 +57704,7 @@
         <v>143</v>
       </c>
       <c r="G889" s="9" t="s">
-        <v>1834</v>
+        <v>1829</v>
       </c>
       <c r="H889" s="10" t="n">
         <v>46238</v>
@@ -57747,7 +57762,7 @@
         <v>402</v>
       </c>
       <c r="G890" s="4" t="s">
-        <v>1835</v>
+        <v>1830</v>
       </c>
       <c r="H890" s="5" t="n">
         <v>46238</v>
@@ -57805,7 +57820,7 @@
         <v>698</v>
       </c>
       <c r="G891" s="9" t="s">
-        <v>1836</v>
+        <v>1831</v>
       </c>
       <c r="H891" s="10" t="n">
         <v>46238</v>
@@ -57863,7 +57878,7 @@
         <v>328</v>
       </c>
       <c r="G892" s="4" t="s">
-        <v>1837</v>
+        <v>1832</v>
       </c>
       <c r="H892" s="5" t="n">
         <v>46238</v>
@@ -57921,7 +57936,7 @@
         <v>1264</v>
       </c>
       <c r="G893" s="9" t="s">
-        <v>1838</v>
+        <v>1833</v>
       </c>
       <c r="H893" s="10" t="n">
         <v>46240</v>
@@ -57979,7 +57994,7 @@
         <v>203</v>
       </c>
       <c r="G894" s="4" t="s">
-        <v>1839</v>
+        <v>1834</v>
       </c>
       <c r="H894" s="5" t="n">
         <v>46240</v>
@@ -58037,7 +58052,7 @@
         <v>829</v>
       </c>
       <c r="G895" s="9" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="H895" s="10" t="n">
         <v>46240</v>
@@ -58092,22 +58107,22 @@
         <v>24</v>
       </c>
       <c r="F896" s="4" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="G896" s="4" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="H896" s="5" t="n">
         <v>46240</v>
       </c>
       <c r="I896" s="4" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="J896" s="4" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K896" s="4" t="s">
-        <v>1845</v>
+        <v>1840</v>
       </c>
       <c r="L896" s="5"/>
       <c r="M896" s="5"/>
@@ -58130,7 +58145,7 @@
         <v>7411.2</v>
       </c>
       <c r="T896" s="4" t="s">
-        <v>1846</v>
+        <v>1841</v>
       </c>
       <c r="U896" s="4"/>
       <c r="V896" s="4"/>
@@ -58150,22 +58165,22 @@
         <v>24</v>
       </c>
       <c r="F897" s="9" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="G897" s="9" t="s">
-        <v>1847</v>
+        <v>1842</v>
       </c>
       <c r="H897" s="10" t="n">
         <v>46240</v>
       </c>
       <c r="I897" s="9" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="J897" s="9" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="K897" s="9" t="s">
-        <v>1845</v>
+        <v>1840</v>
       </c>
       <c r="L897" s="10"/>
       <c r="M897" s="10"/>
@@ -58188,7 +58203,7 @@
         <v>6860.4</v>
       </c>
       <c r="T897" s="9" t="s">
-        <v>1846</v>
+        <v>1841</v>
       </c>
       <c r="U897" s="9"/>
       <c r="V897" s="9"/>
@@ -58211,7 +58226,7 @@
         <v>75</v>
       </c>
       <c r="G898" s="4" t="s">
-        <v>1848</v>
+        <v>1843</v>
       </c>
       <c r="H898" s="5" t="n">
         <v>46241</v>
@@ -58269,7 +58284,7 @@
         <v>1056</v>
       </c>
       <c r="G899" s="9" t="s">
-        <v>1849</v>
+        <v>1844</v>
       </c>
       <c r="H899" s="10" t="n">
         <v>46244</v>
@@ -58327,7 +58342,7 @@
         <v>1488</v>
       </c>
       <c r="G900" s="4" t="s">
-        <v>1850</v>
+        <v>1845</v>
       </c>
       <c r="H900" s="5" t="n">
         <v>46244</v>
@@ -58385,7 +58400,7 @@
         <v>1264</v>
       </c>
       <c r="G901" s="9" t="s">
-        <v>1851</v>
+        <v>1846</v>
       </c>
       <c r="H901" s="11" t="n">
         <v>46244.693715278</v>
@@ -58443,7 +58458,7 @@
         <v>904</v>
       </c>
       <c r="G902" s="4" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="H902" s="6" t="n">
         <v>46244.646689815</v>
@@ -58498,22 +58513,22 @@
         <v>24</v>
       </c>
       <c r="F903" s="9" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
       <c r="G903" s="9" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="H903" s="11" t="n">
         <v>46244.891539352</v>
       </c>
       <c r="I903" s="9" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
       <c r="J903" s="9" t="s">
-        <v>1855</v>
+        <v>1850</v>
       </c>
       <c r="K903" s="9" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="L903" s="10"/>
       <c r="M903" s="10"/>
@@ -58559,7 +58574,7 @@
         <v>592</v>
       </c>
       <c r="G904" s="4" t="s">
-        <v>1857</v>
+        <v>1852</v>
       </c>
       <c r="H904" s="6" t="n">
         <v>46244.846145833</v>
@@ -58617,7 +58632,7 @@
         <v>75</v>
       </c>
       <c r="G905" s="9" t="s">
-        <v>1858</v>
+        <v>1853</v>
       </c>
       <c r="H905" s="11" t="n">
         <v>46244.704305556</v>
@@ -58675,7 +58690,7 @@
         <v>58</v>
       </c>
       <c r="G906" s="4" t="s">
-        <v>1859</v>
+        <v>1854</v>
       </c>
       <c r="H906" s="6" t="n">
         <v>46245.52099537</v>
@@ -58733,7 +58748,7 @@
         <v>152</v>
       </c>
       <c r="G907" s="9" t="s">
-        <v>1860</v>
+        <v>1855</v>
       </c>
       <c r="H907" s="11" t="n">
         <v>46245.60755787</v>
@@ -58791,7 +58806,7 @@
         <v>295</v>
       </c>
       <c r="G908" s="4" t="s">
-        <v>1861</v>
+        <v>1856</v>
       </c>
       <c r="H908" s="6" t="n">
         <v>46245.672013889</v>
@@ -58849,7 +58864,7 @@
         <v>249</v>
       </c>
       <c r="G909" s="9" t="s">
-        <v>1862</v>
+        <v>1857</v>
       </c>
       <c r="H909" s="10" t="n">
         <v>46247</v>
@@ -58907,7 +58922,7 @@
         <v>249</v>
       </c>
       <c r="G910" s="4" t="s">
-        <v>1863</v>
+        <v>1858</v>
       </c>
       <c r="H910" s="6" t="n">
         <v>46247.371365741</v>
@@ -58965,7 +58980,7 @@
         <v>988</v>
       </c>
       <c r="G911" s="9" t="s">
-        <v>1864</v>
+        <v>1859</v>
       </c>
       <c r="H911" s="11" t="n">
         <v>46247.461736111</v>
@@ -59020,22 +59035,22 @@
         <v>24</v>
       </c>
       <c r="F912" s="4" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="G912" s="4" t="s">
-        <v>1865</v>
+        <v>1860</v>
       </c>
       <c r="H912" s="6" t="n">
         <v>46246.935729167</v>
       </c>
       <c r="I912" s="4" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="J912" s="4" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="K912" s="4" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="L912" s="5"/>
       <c r="M912" s="5"/>
@@ -59075,30 +59090,30 @@
         <v>23</v>
       </c>
       <c r="E913" s="8" t="s">
-        <v>1866</v>
+        <v>24</v>
       </c>
       <c r="F913" s="9" t="s">
-        <v>1867</v>
+        <v>1861</v>
       </c>
       <c r="G913" s="9" t="s">
-        <v>1868</v>
+        <v>1862</v>
       </c>
       <c r="H913" s="11" t="n">
         <v>46246.852106481</v>
       </c>
       <c r="I913" s="9" t="s">
-        <v>1867</v>
+        <v>1861</v>
       </c>
       <c r="J913" s="9" t="s">
-        <v>1869</v>
+        <v>1863</v>
       </c>
       <c r="K913" s="9" t="s">
-        <v>1870</v>
+        <v>1864</v>
       </c>
       <c r="L913" s="10"/>
       <c r="M913" s="10"/>
       <c r="N913" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O913" s="11" t="n">
         <v>46248.406686076</v>
@@ -59113,7 +59128,7 @@
         <v>76180</v>
       </c>
       <c r="S913" s="12" t="n">
-        <v>45948</v>
+        <v>76180</v>
       </c>
       <c r="T913" s="9" t="s">
         <v>571</v>
@@ -59139,7 +59154,7 @@
         <v>332</v>
       </c>
       <c r="G914" s="4" t="s">
-        <v>1871</v>
+        <v>1865</v>
       </c>
       <c r="H914" s="6" t="n">
         <v>46246.467384259</v>
@@ -59197,7 +59212,7 @@
         <v>328</v>
       </c>
       <c r="G915" s="9" t="s">
-        <v>1872</v>
+        <v>1866</v>
       </c>
       <c r="H915" s="11" t="n">
         <v>46247.693402778</v>
@@ -59255,7 +59270,7 @@
         <v>1505</v>
       </c>
       <c r="G916" s="4" t="s">
-        <v>1873</v>
+        <v>1867</v>
       </c>
       <c r="H916" s="6" t="n">
         <v>46247.72962963</v>
@@ -59313,7 +59328,7 @@
         <v>1473</v>
       </c>
       <c r="G917" s="9" t="s">
-        <v>1874</v>
+        <v>1868</v>
       </c>
       <c r="H917" s="11" t="n">
         <v>46247.621585648</v>
@@ -59371,7 +59386,7 @@
         <v>75</v>
       </c>
       <c r="G918" s="4" t="s">
-        <v>1875</v>
+        <v>1869</v>
       </c>
       <c r="H918" s="6" t="n">
         <v>46248.419988426</v>
@@ -59429,7 +59444,7 @@
         <v>328</v>
       </c>
       <c r="G919" s="9" t="s">
-        <v>1876</v>
+        <v>1870</v>
       </c>
       <c r="H919" s="11" t="n">
         <v>46248.451365741</v>
@@ -59487,7 +59502,7 @@
         <v>272</v>
       </c>
       <c r="G920" s="4" t="s">
-        <v>1877</v>
+        <v>1871</v>
       </c>
       <c r="H920" s="5" t="n">
         <v>46248</v>
@@ -59545,7 +59560,7 @@
         <v>1060</v>
       </c>
       <c r="G921" s="9" t="s">
-        <v>1878</v>
+        <v>1872</v>
       </c>
       <c r="H921" s="11" t="n">
         <v>46251.721273148</v>
@@ -59603,7 +59618,7 @@
         <v>262</v>
       </c>
       <c r="G922" s="4" t="s">
-        <v>1879</v>
+        <v>1873</v>
       </c>
       <c r="H922" s="6" t="n">
         <v>46251.698263889</v>
@@ -59658,22 +59673,22 @@
         <v>24</v>
       </c>
       <c r="F923" s="9" t="s">
-        <v>1880</v>
+        <v>1874</v>
       </c>
       <c r="G923" s="9" t="s">
-        <v>1881</v>
+        <v>1875</v>
       </c>
       <c r="H923" s="11" t="n">
         <v>46253.493287037</v>
       </c>
       <c r="I923" s="9" t="s">
-        <v>1880</v>
+        <v>1874</v>
       </c>
       <c r="J923" s="9" t="s">
-        <v>1882</v>
+        <v>1876</v>
       </c>
       <c r="K923" s="9" t="s">
-        <v>1883</v>
+        <v>1877</v>
       </c>
       <c r="L923" s="10"/>
       <c r="M923" s="10"/>
@@ -59719,7 +59734,7 @@
         <v>461</v>
       </c>
       <c r="G924" s="4" t="s">
-        <v>1884</v>
+        <v>1878</v>
       </c>
       <c r="H924" s="6" t="n">
         <v>46252.750821759</v>
@@ -59777,7 +59792,7 @@
         <v>1427</v>
       </c>
       <c r="G925" s="9" t="s">
-        <v>1885</v>
+        <v>1879</v>
       </c>
       <c r="H925" s="11" t="n">
         <v>46252.487453704</v>
@@ -59835,7 +59850,7 @@
         <v>75</v>
       </c>
       <c r="G926" s="4" t="s">
-        <v>1886</v>
+        <v>1880</v>
       </c>
       <c r="H926" s="6" t="n">
         <v>46253.626689815</v>
@@ -59893,7 +59908,7 @@
         <v>589</v>
       </c>
       <c r="G927" s="9" t="s">
-        <v>1887</v>
+        <v>1881</v>
       </c>
       <c r="H927" s="10" t="n">
         <v>46255</v>
@@ -59951,7 +59966,7 @@
         <v>355</v>
       </c>
       <c r="G928" s="4" t="s">
-        <v>1888</v>
+        <v>1882</v>
       </c>
       <c r="H928" s="5" t="n">
         <v>46255</v>
@@ -60006,22 +60021,22 @@
         <v>24</v>
       </c>
       <c r="F929" s="9" t="s">
-        <v>1889</v>
+        <v>1883</v>
       </c>
       <c r="G929" s="9" t="s">
-        <v>1890</v>
+        <v>1884</v>
       </c>
       <c r="H929" s="10" t="n">
         <v>46254</v>
       </c>
       <c r="I929" s="9" t="s">
-        <v>1889</v>
+        <v>1883</v>
       </c>
       <c r="J929" s="9" t="s">
-        <v>1891</v>
+        <v>1885</v>
       </c>
       <c r="K929" s="9" t="s">
-        <v>1892</v>
+        <v>1886</v>
       </c>
       <c r="L929" s="10"/>
       <c r="M929" s="10"/>
@@ -60035,7 +60050,7 @@
         <v>1455</v>
       </c>
       <c r="Q929" s="9" t="s">
-        <v>1893</v>
+        <v>1887</v>
       </c>
       <c r="R929" s="12" t="n">
         <v>116127.08</v>
@@ -60067,7 +60082,7 @@
         <v>698</v>
       </c>
       <c r="G930" s="4" t="s">
-        <v>1894</v>
+        <v>1888</v>
       </c>
       <c r="H930" s="6" t="n">
         <v>46258.645081019</v>
@@ -60119,13 +60134,13 @@
         <v>23</v>
       </c>
       <c r="E931" s="8" t="s">
-        <v>1219</v>
+        <v>24</v>
       </c>
       <c r="F931" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G931" s="9" t="s">
-        <v>1895</v>
+        <v>1889</v>
       </c>
       <c r="H931" s="11" t="n">
         <v>46258.652638889</v>
@@ -60142,7 +60157,7 @@
       <c r="L931" s="10"/>
       <c r="M931" s="10"/>
       <c r="N931" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O931" s="11" t="n">
         <v>46259.637292558</v>
@@ -60157,7 +60172,7 @@
         <v>56696</v>
       </c>
       <c r="S931" s="12" t="n">
-        <v>41096</v>
+        <v>56696</v>
       </c>
       <c r="T931" s="9" t="s">
         <v>32</v>
@@ -60183,7 +60198,7 @@
         <v>888</v>
       </c>
       <c r="G932" s="4" t="s">
-        <v>1896</v>
+        <v>1890</v>
       </c>
       <c r="H932" s="6" t="n">
         <v>46258.672395833</v>
@@ -60235,13 +60250,13 @@
         <v>23</v>
       </c>
       <c r="E933" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F933" s="9" t="s">
         <v>1459</v>
       </c>
       <c r="G933" s="9" t="s">
-        <v>1897</v>
+        <v>1891</v>
       </c>
       <c r="H933" s="11" t="n">
         <v>46259.638611111</v>
@@ -60258,7 +60273,7 @@
       <c r="L933" s="10"/>
       <c r="M933" s="10"/>
       <c r="N933" s="9" t="s">
-        <v>1818</v>
+        <v>29</v>
       </c>
       <c r="O933" s="11" t="n">
         <v>46260.463491435</v>
@@ -60273,7 +60288,7 @@
         <v>27030</v>
       </c>
       <c r="S933" s="12" t="n">
-        <v>0</v>
+        <v>27030</v>
       </c>
       <c r="T933" s="9" t="s">
         <v>32</v>
@@ -60293,30 +60308,30 @@
         <v>23</v>
       </c>
       <c r="E934" s="3" t="s">
-        <v>1898</v>
+        <v>24</v>
       </c>
       <c r="F934" s="4" t="s">
-        <v>1899</v>
+        <v>1892</v>
       </c>
       <c r="G934" s="4" t="s">
-        <v>1900</v>
+        <v>1893</v>
       </c>
       <c r="H934" s="6" t="n">
         <v>46259.473958333</v>
       </c>
       <c r="I934" s="4" t="s">
-        <v>1899</v>
+        <v>1892</v>
       </c>
       <c r="J934" s="4" t="s">
-        <v>1901</v>
+        <v>1894</v>
       </c>
       <c r="K934" s="4" t="s">
-        <v>1902</v>
+        <v>1895</v>
       </c>
       <c r="L934" s="5"/>
       <c r="M934" s="5"/>
       <c r="N934" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O934" s="6" t="n">
         <v>46260.465283762</v>
@@ -60331,7 +60346,7 @@
         <v>66983</v>
       </c>
       <c r="S934" s="7" t="n">
-        <v>35894</v>
+        <v>66983</v>
       </c>
       <c r="T934" s="4" t="s">
         <v>571</v>
@@ -60357,7 +60372,7 @@
         <v>1060</v>
       </c>
       <c r="G935" s="9" t="s">
-        <v>1903</v>
+        <v>1896</v>
       </c>
       <c r="H935" s="11" t="n">
         <v>46259.50275463</v>
@@ -60412,22 +60427,22 @@
         <v>24</v>
       </c>
       <c r="F936" s="4" t="s">
-        <v>1904</v>
+        <v>1897</v>
       </c>
       <c r="G936" s="4" t="s">
-        <v>1905</v>
+        <v>1898</v>
       </c>
       <c r="H936" s="5" t="n">
         <v>46259</v>
       </c>
       <c r="I936" s="4" t="s">
-        <v>1906</v>
+        <v>1899</v>
       </c>
       <c r="J936" s="4" t="s">
-        <v>1907</v>
+        <v>1900</v>
       </c>
       <c r="K936" s="4" t="s">
-        <v>1908</v>
+        <v>1901</v>
       </c>
       <c r="L936" s="5"/>
       <c r="M936" s="5"/>
@@ -60441,7 +60456,7 @@
         <v>1455</v>
       </c>
       <c r="Q936" s="4" t="s">
-        <v>1893</v>
+        <v>1887</v>
       </c>
       <c r="R936" s="7" t="n">
         <v>42572</v>
@@ -60473,7 +60488,7 @@
         <v>698</v>
       </c>
       <c r="G937" s="9" t="s">
-        <v>1909</v>
+        <v>1902</v>
       </c>
       <c r="H937" s="11" t="n">
         <v>46259.659039352</v>
@@ -60531,7 +60546,7 @@
         <v>262</v>
       </c>
       <c r="G938" s="4" t="s">
-        <v>1910</v>
+        <v>1903</v>
       </c>
       <c r="H938" s="6" t="n">
         <v>46259.757233796</v>
@@ -60589,7 +60604,7 @@
         <v>945</v>
       </c>
       <c r="G939" s="9" t="s">
-        <v>1911</v>
+        <v>1904</v>
       </c>
       <c r="H939" s="11" t="n">
         <v>46259.670231481</v>
@@ -60641,13 +60656,13 @@
         <v>23</v>
       </c>
       <c r="E940" s="3" t="s">
-        <v>1640</v>
+        <v>1905</v>
       </c>
       <c r="F940" s="4" t="s">
         <v>408</v>
       </c>
       <c r="G940" s="4" t="s">
-        <v>1912</v>
+        <v>1906</v>
       </c>
       <c r="H940" s="6" t="n">
         <v>46261.456944444</v>
@@ -60702,10 +60717,10 @@
         <v>24</v>
       </c>
       <c r="F941" s="9" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="G941" s="9" t="s">
-        <v>1913</v>
+        <v>1907</v>
       </c>
       <c r="H941" s="11" t="n">
         <v>46260.641412037</v>
@@ -60763,7 +60778,7 @@
         <v>1280</v>
       </c>
       <c r="G942" s="4" t="s">
-        <v>1914</v>
+        <v>1908</v>
       </c>
       <c r="H942" s="6" t="n">
         <v>46261.627002315</v>
@@ -60815,13 +60830,13 @@
         <v>23</v>
       </c>
       <c r="E943" s="8" t="s">
-        <v>285</v>
+        <v>1909</v>
       </c>
       <c r="F943" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G943" s="9" t="s">
-        <v>1915</v>
+        <v>1910</v>
       </c>
       <c r="H943" s="11" t="n">
         <v>46261.674166667</v>
@@ -60838,7 +60853,7 @@
       <c r="L943" s="10"/>
       <c r="M943" s="10"/>
       <c r="N943" s="9" t="s">
-        <v>1818</v>
+        <v>1288</v>
       </c>
       <c r="O943" s="11" t="n">
         <v>46262.58240625</v>
@@ -60853,7 +60868,7 @@
         <v>42336</v>
       </c>
       <c r="S943" s="12" t="n">
-        <v>0</v>
+        <v>12096</v>
       </c>
       <c r="T943" s="9" t="s">
         <v>32</v>
@@ -60873,13 +60888,13 @@
         <v>23</v>
       </c>
       <c r="E944" s="3" t="s">
-        <v>1916</v>
+        <v>24</v>
       </c>
       <c r="F944" s="4" t="s">
         <v>211</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1917</v>
+        <v>1911</v>
       </c>
       <c r="H944" s="6" t="n">
         <v>46261.624131944</v>
@@ -60896,7 +60911,7 @@
       <c r="L944" s="5"/>
       <c r="M944" s="5"/>
       <c r="N944" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O944" s="6" t="n">
         <v>46262.582538507</v>
@@ -60911,7 +60926,7 @@
         <v>44352</v>
       </c>
       <c r="S944" s="7" t="n">
-        <v>22176</v>
+        <v>44352</v>
       </c>
       <c r="T944" s="4" t="s">
         <v>32</v>
@@ -60937,7 +60952,7 @@
         <v>521</v>
       </c>
       <c r="G945" s="9" t="s">
-        <v>1918</v>
+        <v>1912</v>
       </c>
       <c r="H945" s="11" t="n">
         <v>46261.626898148</v>
@@ -60995,7 +61010,7 @@
         <v>1056</v>
       </c>
       <c r="G946" s="4" t="s">
-        <v>1919</v>
+        <v>1913</v>
       </c>
       <c r="H946" s="5" t="n">
         <v>46262</v>
@@ -61053,7 +61068,7 @@
         <v>1019</v>
       </c>
       <c r="G947" s="9" t="s">
-        <v>1920</v>
+        <v>1914</v>
       </c>
       <c r="H947" s="10" t="n">
         <v>46261</v>
@@ -61111,7 +61126,7 @@
         <v>38</v>
       </c>
       <c r="G948" s="4" t="s">
-        <v>1921</v>
+        <v>1915</v>
       </c>
       <c r="H948" s="6" t="n">
         <v>46262.683993056</v>
@@ -61163,25 +61178,25 @@
         <v>23</v>
       </c>
       <c r="E949" s="8" t="s">
-        <v>24</v>
+        <v>1916</v>
       </c>
       <c r="F949" s="9" t="s">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="G949" s="9" t="s">
-        <v>1922</v>
+        <v>1917</v>
       </c>
       <c r="H949" s="10" t="n">
         <v>46265</v>
       </c>
       <c r="I949" s="9" t="s">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="J949" s="9" t="s">
-        <v>1737</v>
+        <v>1732</v>
       </c>
       <c r="K949" s="9" t="s">
-        <v>1738</v>
+        <v>1733</v>
       </c>
       <c r="L949" s="10"/>
       <c r="M949" s="10"/>
@@ -61201,7 +61216,7 @@
         <v>201401</v>
       </c>
       <c r="S949" s="12" t="n">
-        <v>201401</v>
+        <v>93000</v>
       </c>
       <c r="T949" s="9" t="s">
         <v>32</v>
@@ -61221,13 +61236,13 @@
         <v>23</v>
       </c>
       <c r="E950" s="3" t="s">
-        <v>1923</v>
+        <v>1918</v>
       </c>
       <c r="F950" s="4" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="G950" s="4" t="s">
-        <v>1924</v>
+        <v>1919</v>
       </c>
       <c r="H950" s="5" t="n">
         <v>46265</v>
@@ -61279,13 +61294,13 @@
         <v>23</v>
       </c>
       <c r="E951" s="8" t="s">
-        <v>1925</v>
+        <v>1920</v>
       </c>
       <c r="F951" s="9" t="s">
         <v>619</v>
       </c>
       <c r="G951" s="9" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="H951" s="11" t="n">
         <v>46265.756805556</v>
@@ -61343,7 +61358,7 @@
         <v>103</v>
       </c>
       <c r="G952" s="4" t="s">
-        <v>1927</v>
+        <v>1922</v>
       </c>
       <c r="H952" s="6" t="n">
         <v>46262.6721875</v>
@@ -61360,7 +61375,7 @@
       <c r="L952" s="5"/>
       <c r="M952" s="5"/>
       <c r="N952" s="4" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="O952" s="6" t="n">
         <v>46266.68744059</v>
@@ -61401,7 +61416,7 @@
         <v>814</v>
       </c>
       <c r="G953" s="9" t="s">
-        <v>1928</v>
+        <v>1923</v>
       </c>
       <c r="H953" s="11" t="n">
         <v>46265.738773148</v>
@@ -61459,7 +61474,7 @@
         <v>484</v>
       </c>
       <c r="G954" s="4" t="s">
-        <v>1929</v>
+        <v>1924</v>
       </c>
       <c r="H954" s="6" t="n">
         <v>46265.406400463</v>
@@ -61517,7 +61532,7 @@
         <v>482</v>
       </c>
       <c r="G955" s="9" t="s">
-        <v>1930</v>
+        <v>1925</v>
       </c>
       <c r="H955" s="11" t="n">
         <v>46262.643506944</v>
@@ -61575,7 +61590,7 @@
         <v>744</v>
       </c>
       <c r="G956" s="4" t="s">
-        <v>1931</v>
+        <v>1926</v>
       </c>
       <c r="H956" s="6" t="n">
         <v>46262.644305556</v>
@@ -61633,7 +61648,7 @@
         <v>1179</v>
       </c>
       <c r="G957" s="9" t="s">
-        <v>1932</v>
+        <v>1927</v>
       </c>
       <c r="H957" s="11" t="n">
         <v>46262.617488426</v>
@@ -61688,10 +61703,10 @@
         <v>24</v>
       </c>
       <c r="F958" s="4" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G958" s="4" t="s">
-        <v>1933</v>
+        <v>1928</v>
       </c>
       <c r="H958" s="6" t="n">
         <v>46262.337835648</v>
@@ -61749,7 +61764,7 @@
         <v>1516</v>
       </c>
       <c r="G959" s="9" t="s">
-        <v>1934</v>
+        <v>1929</v>
       </c>
       <c r="H959" s="10" t="n">
         <v>46266</v>
@@ -61804,10 +61819,10 @@
         <v>24</v>
       </c>
       <c r="F960" s="4" t="s">
-        <v>1935</v>
+        <v>1930</v>
       </c>
       <c r="G960" s="4" t="s">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="H960" s="5" t="n">
         <v>46265</v>
@@ -61862,22 +61877,22 @@
         <v>24</v>
       </c>
       <c r="F961" s="9" t="s">
-        <v>1937</v>
+        <v>1932</v>
       </c>
       <c r="G961" s="9" t="s">
-        <v>1938</v>
+        <v>1933</v>
       </c>
       <c r="H961" s="10" t="n">
         <v>46266</v>
       </c>
       <c r="I961" s="9" t="s">
-        <v>1937</v>
+        <v>1932</v>
       </c>
       <c r="J961" s="9" t="s">
-        <v>1939</v>
+        <v>1934</v>
       </c>
       <c r="K961" s="9" t="s">
-        <v>1940</v>
+        <v>1935</v>
       </c>
       <c r="L961" s="10"/>
       <c r="M961" s="10"/>
@@ -61891,7 +61906,7 @@
         <v>1455</v>
       </c>
       <c r="Q961" s="9" t="s">
-        <v>1893</v>
+        <v>1887</v>
       </c>
       <c r="R961" s="12" t="n">
         <v>17437.2</v>
@@ -61920,22 +61935,22 @@
         <v>24</v>
       </c>
       <c r="F962" s="4" t="s">
-        <v>1941</v>
+        <v>1936</v>
       </c>
       <c r="G962" s="4" t="s">
-        <v>1942</v>
+        <v>1937</v>
       </c>
       <c r="H962" s="5" t="n">
         <v>46265</v>
       </c>
       <c r="I962" s="4" t="s">
-        <v>1943</v>
+        <v>1938</v>
       </c>
       <c r="J962" s="4" t="s">
-        <v>1944</v>
+        <v>1939</v>
       </c>
       <c r="K962" s="4" t="s">
-        <v>1945</v>
+        <v>1940</v>
       </c>
       <c r="L962" s="5"/>
       <c r="M962" s="5"/>
@@ -61949,7 +61964,7 @@
         <v>1455</v>
       </c>
       <c r="Q962" s="4" t="s">
-        <v>1893</v>
+        <v>1887</v>
       </c>
       <c r="R962" s="7" t="n">
         <v>10074</v>
@@ -61981,7 +61996,7 @@
         <v>945</v>
       </c>
       <c r="G963" s="9" t="s">
-        <v>1946</v>
+        <v>1941</v>
       </c>
       <c r="H963" s="11" t="n">
         <v>46267.438217593</v>
@@ -62039,7 +62054,7 @@
         <v>310</v>
       </c>
       <c r="G964" s="4" t="s">
-        <v>1947</v>
+        <v>1942</v>
       </c>
       <c r="H964" s="5" t="n">
         <v>46269</v>
@@ -62091,13 +62106,13 @@
         <v>23</v>
       </c>
       <c r="E965" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F965" s="9" t="s">
         <v>402</v>
       </c>
       <c r="G965" s="9" t="s">
-        <v>1948</v>
+        <v>1943</v>
       </c>
       <c r="H965" s="11" t="n">
         <v>46269.745752315</v>
@@ -62114,7 +62129,7 @@
       <c r="L965" s="10"/>
       <c r="M965" s="10"/>
       <c r="N965" s="9" t="s">
-        <v>1818</v>
+        <v>29</v>
       </c>
       <c r="O965" s="11" t="n">
         <v>46274.36010478</v>
@@ -62129,7 +62144,7 @@
         <v>37380</v>
       </c>
       <c r="S965" s="12" t="n">
-        <v>0</v>
+        <v>37380</v>
       </c>
       <c r="T965" s="9" t="s">
         <v>32</v>
@@ -62155,7 +62170,7 @@
         <v>988</v>
       </c>
       <c r="G966" s="4" t="s">
-        <v>1949</v>
+        <v>1944</v>
       </c>
       <c r="H966" s="6" t="n">
         <v>46269.693969907</v>
@@ -62172,7 +62187,7 @@
       <c r="L966" s="5"/>
       <c r="M966" s="5"/>
       <c r="N966" s="4" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="O966" s="6" t="n">
         <v>46274.360279861</v>
@@ -62207,13 +62222,13 @@
         <v>23</v>
       </c>
       <c r="E967" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F967" s="9" t="s">
         <v>1079</v>
       </c>
       <c r="G967" s="9" t="s">
-        <v>1950</v>
+        <v>1945</v>
       </c>
       <c r="H967" s="11" t="n">
         <v>46269.459189815</v>
@@ -62230,7 +62245,7 @@
       <c r="L967" s="10"/>
       <c r="M967" s="10"/>
       <c r="N967" s="9" t="s">
-        <v>1818</v>
+        <v>29</v>
       </c>
       <c r="O967" s="11" t="n">
         <v>46274.360427546</v>
@@ -62245,7 +62260,7 @@
         <v>18393</v>
       </c>
       <c r="S967" s="12" t="n">
-        <v>0</v>
+        <v>18393</v>
       </c>
       <c r="T967" s="9" t="s">
         <v>32</v>
@@ -62265,13 +62280,13 @@
         <v>23</v>
       </c>
       <c r="E968" s="3" t="s">
-        <v>285</v>
+        <v>1946</v>
       </c>
       <c r="F968" s="4" t="s">
         <v>1496</v>
       </c>
       <c r="G968" s="4" t="s">
-        <v>1951</v>
+        <v>1947</v>
       </c>
       <c r="H968" s="6" t="n">
         <v>46268.442615741</v>
@@ -62288,7 +62303,7 @@
       <c r="L968" s="5"/>
       <c r="M968" s="5"/>
       <c r="N968" s="4" t="s">
-        <v>1818</v>
+        <v>1288</v>
       </c>
       <c r="O968" s="6" t="n">
         <v>46274.360582905</v>
@@ -62303,7 +62318,7 @@
         <v>59790</v>
       </c>
       <c r="S968" s="7" t="n">
-        <v>0</v>
+        <v>14850</v>
       </c>
       <c r="T968" s="4" t="s">
         <v>32</v>
@@ -62323,13 +62338,13 @@
         <v>23</v>
       </c>
       <c r="E969" s="8" t="s">
-        <v>1952</v>
+        <v>1948</v>
       </c>
       <c r="F969" s="9" t="s">
         <v>157</v>
       </c>
       <c r="G969" s="9" t="s">
-        <v>1953</v>
+        <v>1949</v>
       </c>
       <c r="H969" s="10" t="n">
         <v>46268</v>
@@ -62387,7 +62402,7 @@
         <v>969</v>
       </c>
       <c r="G970" s="4" t="s">
-        <v>1954</v>
+        <v>1950</v>
       </c>
       <c r="H970" s="5" t="n">
         <v>46268</v>
@@ -62442,10 +62457,10 @@
         <v>24</v>
       </c>
       <c r="F971" s="9" t="s">
-        <v>1955</v>
+        <v>1951</v>
       </c>
       <c r="G971" s="9" t="s">
-        <v>1956</v>
+        <v>1952</v>
       </c>
       <c r="H971" s="10" t="n">
         <v>46273</v>
@@ -62497,13 +62512,13 @@
         <v>23</v>
       </c>
       <c r="E972" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F972" s="4" t="s">
         <v>1264</v>
       </c>
       <c r="G972" s="4" t="s">
-        <v>1957</v>
+        <v>1953</v>
       </c>
       <c r="H972" s="5" t="n">
         <v>46273</v>
@@ -62520,7 +62535,7 @@
       <c r="L972" s="5"/>
       <c r="M972" s="5"/>
       <c r="N972" s="4" t="s">
-        <v>1818</v>
+        <v>29</v>
       </c>
       <c r="O972" s="6" t="n">
         <v>46274.466218981</v>
@@ -62532,10 +62547,10 @@
         <v>74</v>
       </c>
       <c r="R972" s="7" t="n">
-        <v>127920.76</v>
+        <v>128234.16</v>
       </c>
       <c r="S972" s="7" t="n">
-        <v>0</v>
+        <v>128234.16</v>
       </c>
       <c r="T972" s="4" t="s">
         <v>32</v>
@@ -62555,13 +62570,13 @@
         <v>23</v>
       </c>
       <c r="E973" s="8" t="s">
-        <v>285</v>
+        <v>1954</v>
       </c>
       <c r="F973" s="9" t="s">
         <v>152</v>
       </c>
       <c r="G973" s="9" t="s">
-        <v>1958</v>
+        <v>1955</v>
       </c>
       <c r="H973" s="11" t="n">
         <v>46273.758136574</v>
@@ -62578,7 +62593,7 @@
       <c r="L973" s="10"/>
       <c r="M973" s="10"/>
       <c r="N973" s="9" t="s">
-        <v>1818</v>
+        <v>1288</v>
       </c>
       <c r="O973" s="11" t="n">
         <v>46274.621396412</v>
@@ -62593,7 +62608,7 @@
         <v>193050</v>
       </c>
       <c r="S973" s="12" t="n">
-        <v>0</v>
+        <v>101400</v>
       </c>
       <c r="T973" s="9" t="s">
         <v>32</v>
@@ -62613,30 +62628,30 @@
         <v>23</v>
       </c>
       <c r="E974" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F974" s="4" t="s">
-        <v>1959</v>
+        <v>1956</v>
       </c>
       <c r="G974" s="4" t="s">
-        <v>1960</v>
+        <v>1957</v>
       </c>
       <c r="H974" s="6" t="n">
         <v>46273.740416667</v>
       </c>
       <c r="I974" s="4" t="s">
+        <v>1956</v>
+      </c>
+      <c r="J974" s="4" t="s">
+        <v>1958</v>
+      </c>
+      <c r="K974" s="4" t="s">
         <v>1959</v>
-      </c>
-      <c r="J974" s="4" t="s">
-        <v>1961</v>
-      </c>
-      <c r="K974" s="4" t="s">
-        <v>1962</v>
       </c>
       <c r="L974" s="5"/>
       <c r="M974" s="5"/>
       <c r="N974" s="4" t="s">
-        <v>1818</v>
+        <v>29</v>
       </c>
       <c r="O974" s="6" t="n">
         <v>46274.621603935</v>
@@ -62651,7 +62666,7 @@
         <v>1602</v>
       </c>
       <c r="S974" s="7" t="n">
-        <v>0</v>
+        <v>1602</v>
       </c>
       <c r="T974" s="4" t="s">
         <v>32</v>
@@ -62671,13 +62686,13 @@
         <v>23</v>
       </c>
       <c r="E975" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F975" s="9" t="s">
         <v>1411</v>
       </c>
       <c r="G975" s="9" t="s">
-        <v>1963</v>
+        <v>1960</v>
       </c>
       <c r="H975" s="11" t="n">
         <v>46273.780162037</v>
@@ -62694,7 +62709,7 @@
       <c r="L975" s="10"/>
       <c r="M975" s="10"/>
       <c r="N975" s="9" t="s">
-        <v>1818</v>
+        <v>29</v>
       </c>
       <c r="O975" s="11" t="n">
         <v>46274.62173441</v>
@@ -62709,7 +62724,7 @@
         <v>2293.2</v>
       </c>
       <c r="S975" s="12" t="n">
-        <v>0</v>
+        <v>2293.2</v>
       </c>
       <c r="T975" s="9" t="s">
         <v>32</v>
@@ -62732,10 +62747,10 @@
         <v>285</v>
       </c>
       <c r="F976" s="4" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="G976" s="4" t="s">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="H976" s="6" t="n">
         <v>46274.442685185</v>
@@ -62752,7 +62767,7 @@
       <c r="L976" s="5"/>
       <c r="M976" s="5"/>
       <c r="N976" s="4" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="O976" s="6" t="n">
         <v>46274.622029167</v>
@@ -62787,30 +62802,30 @@
         <v>23</v>
       </c>
       <c r="E977" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F977" s="9" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="G977" s="9" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="H977" s="10" t="n">
         <v>46273</v>
       </c>
       <c r="I977" s="9" t="s">
+        <v>1614</v>
+      </c>
+      <c r="J977" s="9" t="s">
         <v>1615</v>
       </c>
-      <c r="J977" s="9" t="s">
+      <c r="K977" s="9" t="s">
         <v>1616</v>
-      </c>
-      <c r="K977" s="9" t="s">
-        <v>1617</v>
       </c>
       <c r="L977" s="10"/>
       <c r="M977" s="10"/>
       <c r="N977" s="9" t="s">
-        <v>1818</v>
+        <v>29</v>
       </c>
       <c r="O977" s="11" t="n">
         <v>46274.637010382</v>
@@ -62819,13 +62834,13 @@
         <v>1455</v>
       </c>
       <c r="Q977" s="9" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="R977" s="12" t="n">
         <v>12500</v>
       </c>
       <c r="S977" s="12" t="n">
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="T977" s="9" t="s">
         <v>32</v>
@@ -62842,16 +62857,16 @@
       </c>
       <c r="C978" s="4"/>
       <c r="D978" s="4" t="s">
-        <v>284</v>
+        <v>23</v>
       </c>
       <c r="E978" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F978" s="4" t="s">
         <v>355</v>
       </c>
       <c r="G978" s="4" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="H978" s="5" t="n">
         <v>46274</v>
@@ -62868,7 +62883,7 @@
       <c r="L978" s="5"/>
       <c r="M978" s="5"/>
       <c r="N978" s="4" t="s">
-        <v>1818</v>
+        <v>29</v>
       </c>
       <c r="O978" s="6" t="n">
         <v>46274.638265822</v>
@@ -62880,10 +62895,10 @@
         <v>134</v>
       </c>
       <c r="R978" s="7" t="n">
-        <v>2298</v>
+        <v>3648</v>
       </c>
       <c r="S978" s="7" t="n">
-        <v>0</v>
+        <v>3648</v>
       </c>
       <c r="T978" s="4" t="s">
         <v>32</v>
@@ -62891,35 +62906,499 @@
       <c r="U978" s="4"/>
       <c r="V978" s="4"/>
     </row>
-    <row r="979" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A979" s="13" t="n">
-        <v>977</v>
-      </c>
-      <c r="B979" s="14"/>
-      <c r="C979" s="14"/>
-      <c r="D979" s="14"/>
-      <c r="E979" s="14"/>
-      <c r="F979" s="14"/>
-      <c r="G979" s="14"/>
-      <c r="H979" s="14"/>
-      <c r="I979" s="14"/>
-      <c r="J979" s="14"/>
-      <c r="K979" s="14"/>
-      <c r="L979" s="14"/>
-      <c r="M979" s="14"/>
-      <c r="N979" s="14"/>
-      <c r="O979" s="14"/>
-      <c r="P979" s="14"/>
-      <c r="Q979" s="14"/>
-      <c r="R979" s="15" t="n">
-        <v>58606740.2626</v>
-      </c>
-      <c r="S979" s="15" t="n">
-        <v>57304287.8426</v>
-      </c>
-      <c r="T979" s="14"/>
-      <c r="U979" s="14"/>
-      <c r="V979" s="16"/>
+    <row r="979" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A979" s="8" t="n">
+        <v>1048</v>
+      </c>
+      <c r="B979" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C979" s="9"/>
+      <c r="D979" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E979" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F979" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="G979" s="9" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H979" s="10" t="n">
+        <v>46273</v>
+      </c>
+      <c r="I979" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="J979" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="K979" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="L979" s="10"/>
+      <c r="M979" s="10"/>
+      <c r="N979" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O979" s="11" t="n">
+        <v>46274.640229861</v>
+      </c>
+      <c r="P979" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q979" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R979" s="12" t="n">
+        <v>1950</v>
+      </c>
+      <c r="S979" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T979" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U979" s="9"/>
+      <c r="V979" s="9"/>
+    </row>
+    <row r="980" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A980" s="3" t="n">
+        <v>1049</v>
+      </c>
+      <c r="B980" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C980" s="4"/>
+      <c r="D980" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E980" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F980" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G980" s="4" t="s">
+        <v>1967</v>
+      </c>
+      <c r="H980" s="5" t="n">
+        <v>46275</v>
+      </c>
+      <c r="I980" s="4" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J980" s="4" t="s">
+        <v>1217</v>
+      </c>
+      <c r="K980" s="4" t="s">
+        <v>1218</v>
+      </c>
+      <c r="L980" s="5"/>
+      <c r="M980" s="5"/>
+      <c r="N980" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O980" s="6" t="n">
+        <v>46275.621564583</v>
+      </c>
+      <c r="P980" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q980" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R980" s="7" t="n">
+        <v>70875</v>
+      </c>
+      <c r="S980" s="7" t="n">
+        <v>70875</v>
+      </c>
+      <c r="T980" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U980" s="4"/>
+      <c r="V980" s="4"/>
+    </row>
+    <row r="981" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A981" s="8" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B981" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C981" s="9"/>
+      <c r="D981" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E981" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F981" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="G981" s="9" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H981" s="10" t="n">
+        <v>46275</v>
+      </c>
+      <c r="I981" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="J981" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="K981" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="L981" s="10"/>
+      <c r="M981" s="10"/>
+      <c r="N981" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O981" s="11" t="n">
+        <v>46275.6269689</v>
+      </c>
+      <c r="P981" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q981" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R981" s="12" t="n">
+        <v>78750</v>
+      </c>
+      <c r="S981" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T981" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U981" s="9"/>
+      <c r="V981" s="9"/>
+    </row>
+    <row r="982" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A982" s="3" t="n">
+        <v>1051</v>
+      </c>
+      <c r="B982" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C982" s="4"/>
+      <c r="D982" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E982" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F982" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="G982" s="4" t="s">
+        <v>1969</v>
+      </c>
+      <c r="H982" s="6" t="n">
+        <v>46274.972708333</v>
+      </c>
+      <c r="I982" s="4" t="s">
+        <v>1461</v>
+      </c>
+      <c r="J982" s="4" t="s">
+        <v>1462</v>
+      </c>
+      <c r="K982" s="4" t="s">
+        <v>1463</v>
+      </c>
+      <c r="L982" s="5"/>
+      <c r="M982" s="5"/>
+      <c r="N982" s="4" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O982" s="6" t="n">
+        <v>46275.62822434</v>
+      </c>
+      <c r="P982" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q982" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R982" s="7" t="n">
+        <v>11420</v>
+      </c>
+      <c r="S982" s="7" t="n">
+        <v>11420</v>
+      </c>
+      <c r="T982" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U982" s="4"/>
+      <c r="V982" s="4"/>
+    </row>
+    <row r="983" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A983" s="8" t="n">
+        <v>1052</v>
+      </c>
+      <c r="B983" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C983" s="9"/>
+      <c r="D983" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E983" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F983" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G983" s="9" t="s">
+        <v>1970</v>
+      </c>
+      <c r="H983" s="11" t="n">
+        <v>46274.976979167</v>
+      </c>
+      <c r="I983" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="J983" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K983" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="L983" s="10"/>
+      <c r="M983" s="10"/>
+      <c r="N983" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O983" s="11" t="n">
+        <v>46275.628351887</v>
+      </c>
+      <c r="P983" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q983" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R983" s="12" t="n">
+        <v>94000</v>
+      </c>
+      <c r="S983" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T983" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U983" s="9"/>
+      <c r="V983" s="9"/>
+    </row>
+    <row r="984" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A984" s="3" t="n">
+        <v>1053</v>
+      </c>
+      <c r="B984" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C984" s="4"/>
+      <c r="D984" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E984" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F984" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G984" s="4" t="s">
+        <v>1971</v>
+      </c>
+      <c r="H984" s="6" t="n">
+        <v>46274.703055556</v>
+      </c>
+      <c r="I984" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="J984" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K984" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="L984" s="5"/>
+      <c r="M984" s="5"/>
+      <c r="N984" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O984" s="6" t="n">
+        <v>46275.628472454</v>
+      </c>
+      <c r="P984" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q984" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R984" s="7" t="n">
+        <v>4785</v>
+      </c>
+      <c r="S984" s="7" t="n">
+        <v>4785</v>
+      </c>
+      <c r="T984" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U984" s="4"/>
+      <c r="V984" s="4"/>
+    </row>
+    <row r="985" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A985" s="8" t="n">
+        <v>1054</v>
+      </c>
+      <c r="B985" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C985" s="9"/>
+      <c r="D985" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E985" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F985" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G985" s="9" t="s">
+        <v>1972</v>
+      </c>
+      <c r="H985" s="11" t="n">
+        <v>46274.682534722</v>
+      </c>
+      <c r="I985" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J985" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K985" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="L985" s="10"/>
+      <c r="M985" s="10"/>
+      <c r="N985" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O985" s="11" t="n">
+        <v>46275.62857581</v>
+      </c>
+      <c r="P985" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q985" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R985" s="12" t="n">
+        <v>22230</v>
+      </c>
+      <c r="S985" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T985" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U985" s="9"/>
+      <c r="V985" s="9"/>
+    </row>
+    <row r="986" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A986" s="3" t="n">
+        <v>1055</v>
+      </c>
+      <c r="B986" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C986" s="4"/>
+      <c r="D986" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E986" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F986" s="4" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G986" s="4" t="s">
+        <v>1973</v>
+      </c>
+      <c r="H986" s="6" t="n">
+        <v>46275.472800926</v>
+      </c>
+      <c r="I986" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="J986" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="K986" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="L986" s="5"/>
+      <c r="M986" s="5"/>
+      <c r="N986" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O986" s="6" t="n">
+        <v>46275.628670833</v>
+      </c>
+      <c r="P986" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q986" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R986" s="7" t="n">
+        <v>12121.08</v>
+      </c>
+      <c r="S986" s="7" t="n">
+        <v>12121.08</v>
+      </c>
+      <c r="T986" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U986" s="4"/>
+      <c r="V986" s="4"/>
+    </row>
+    <row r="987" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A987" s="13" t="n">
+        <v>985</v>
+      </c>
+      <c r="B987" s="14"/>
+      <c r="C987" s="14"/>
+      <c r="D987" s="14"/>
+      <c r="E987" s="14"/>
+      <c r="F987" s="14"/>
+      <c r="G987" s="14"/>
+      <c r="H987" s="14"/>
+      <c r="I987" s="14"/>
+      <c r="J987" s="14"/>
+      <c r="K987" s="14"/>
+      <c r="L987" s="14"/>
+      <c r="M987" s="14"/>
+      <c r="N987" s="14"/>
+      <c r="O987" s="14"/>
+      <c r="P987" s="14"/>
+      <c r="Q987" s="14"/>
+      <c r="R987" s="15" t="n">
+        <v>58905398.9586</v>
+      </c>
+      <c r="S987" s="15" t="n">
+        <v>57866959.5986</v>
+      </c>
+      <c r="T987" s="14"/>
+      <c r="U987" s="14"/>
+      <c r="V987" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="1974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="1985">
   <si>
     <t>ID</t>
   </si>
@@ -5935,6 +5935,39 @@
   </si>
   <si>
     <t>1220</t>
+  </si>
+  <si>
+    <t>1221</t>
+  </si>
+  <si>
+    <t>1222</t>
+  </si>
+  <si>
+    <t>1223</t>
+  </si>
+  <si>
+    <t>1224</t>
+  </si>
+  <si>
+    <t>1225</t>
+  </si>
+  <si>
+    <t>1226</t>
+  </si>
+  <si>
+    <t>1227</t>
+  </si>
+  <si>
+    <t>1228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPECIFARMA COM DE MEDICAMENTOS </t>
+  </si>
+  <si>
+    <t>00.085.822/0001-12</t>
+  </si>
+  <si>
+    <t>1229</t>
   </si>
 </sst>
 </file>
@@ -6128,7 +6161,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V987"/>
+  <dimension ref="A1:V996"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -62164,7 +62197,7 @@
         <v>23</v>
       </c>
       <c r="E966" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F966" s="4" t="s">
         <v>988</v>
@@ -62187,7 +62220,7 @@
       <c r="L966" s="5"/>
       <c r="M966" s="5"/>
       <c r="N966" s="4" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O966" s="6" t="n">
         <v>46274.360279861</v>
@@ -62202,7 +62235,7 @@
         <v>9591</v>
       </c>
       <c r="S966" s="7" t="n">
-        <v>0</v>
+        <v>9591</v>
       </c>
       <c r="T966" s="4" t="s">
         <v>32</v>
@@ -63370,35 +63403,557 @@
       <c r="U986" s="4"/>
       <c r="V986" s="4"/>
     </row>
-    <row r="987" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A987" s="13" t="n">
-        <v>985</v>
-      </c>
-      <c r="B987" s="14"/>
-      <c r="C987" s="14"/>
-      <c r="D987" s="14"/>
-      <c r="E987" s="14"/>
-      <c r="F987" s="14"/>
-      <c r="G987" s="14"/>
-      <c r="H987" s="14"/>
-      <c r="I987" s="14"/>
-      <c r="J987" s="14"/>
-      <c r="K987" s="14"/>
-      <c r="L987" s="14"/>
-      <c r="M987" s="14"/>
-      <c r="N987" s="14"/>
-      <c r="O987" s="14"/>
-      <c r="P987" s="14"/>
-      <c r="Q987" s="14"/>
-      <c r="R987" s="15" t="n">
-        <v>58905398.9586</v>
-      </c>
-      <c r="S987" s="15" t="n">
-        <v>57866959.5986</v>
-      </c>
-      <c r="T987" s="14"/>
-      <c r="U987" s="14"/>
-      <c r="V987" s="16"/>
+    <row r="987" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A987" s="8" t="n">
+        <v>1056</v>
+      </c>
+      <c r="B987" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C987" s="9"/>
+      <c r="D987" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E987" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F987" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G987" s="9" t="s">
+        <v>1974</v>
+      </c>
+      <c r="H987" s="11" t="n">
+        <v>46276.641041667</v>
+      </c>
+      <c r="I987" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="J987" s="9" t="s">
+        <v>1119</v>
+      </c>
+      <c r="K987" s="9" t="s">
+        <v>1120</v>
+      </c>
+      <c r="L987" s="10"/>
+      <c r="M987" s="10"/>
+      <c r="N987" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O987" s="11" t="n">
+        <v>46279.583453507</v>
+      </c>
+      <c r="P987" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q987" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="R987" s="12" t="n">
+        <v>43201</v>
+      </c>
+      <c r="S987" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T987" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U987" s="9"/>
+      <c r="V987" s="9"/>
+    </row>
+    <row r="988" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A988" s="3" t="n">
+        <v>1057</v>
+      </c>
+      <c r="B988" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C988" s="4"/>
+      <c r="D988" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E988" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F988" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="G988" s="4" t="s">
+        <v>1975</v>
+      </c>
+      <c r="H988" s="6" t="n">
+        <v>46276.445613426</v>
+      </c>
+      <c r="I988" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J988" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K988" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="L988" s="5"/>
+      <c r="M988" s="5"/>
+      <c r="N988" s="4" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O988" s="6" t="n">
+        <v>46279.583654942</v>
+      </c>
+      <c r="P988" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q988" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R988" s="7" t="n">
+        <v>39000</v>
+      </c>
+      <c r="S988" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T988" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U988" s="4"/>
+      <c r="V988" s="4"/>
+    </row>
+    <row r="989" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A989" s="8" t="n">
+        <v>1058</v>
+      </c>
+      <c r="B989" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C989" s="9"/>
+      <c r="D989" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E989" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F989" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="G989" s="9" t="s">
+        <v>1976</v>
+      </c>
+      <c r="H989" s="11" t="n">
+        <v>46275.859097222</v>
+      </c>
+      <c r="I989" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="J989" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="K989" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="L989" s="10"/>
+      <c r="M989" s="10"/>
+      <c r="N989" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O989" s="11" t="n">
+        <v>46279.583951817</v>
+      </c>
+      <c r="P989" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q989" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="R989" s="12" t="n">
+        <v>14826</v>
+      </c>
+      <c r="S989" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T989" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U989" s="9"/>
+      <c r="V989" s="9"/>
+    </row>
+    <row r="990" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A990" s="3" t="n">
+        <v>1059</v>
+      </c>
+      <c r="B990" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C990" s="4"/>
+      <c r="D990" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E990" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F990" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="G990" s="4" t="s">
+        <v>1977</v>
+      </c>
+      <c r="H990" s="6" t="n">
+        <v>46276.36244213</v>
+      </c>
+      <c r="I990" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="J990" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="K990" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="L990" s="5"/>
+      <c r="M990" s="5"/>
+      <c r="N990" s="4" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O990" s="6" t="n">
+        <v>46279.584095637</v>
+      </c>
+      <c r="P990" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q990" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="R990" s="7" t="n">
+        <v>17343.86</v>
+      </c>
+      <c r="S990" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T990" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U990" s="4"/>
+      <c r="V990" s="4"/>
+    </row>
+    <row r="991" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A991" s="8" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B991" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C991" s="9"/>
+      <c r="D991" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E991" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F991" s="9" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G991" s="9" t="s">
+        <v>1978</v>
+      </c>
+      <c r="H991" s="11" t="n">
+        <v>46276.780416667</v>
+      </c>
+      <c r="I991" s="9" t="s">
+        <v>1429</v>
+      </c>
+      <c r="J991" s="9" t="s">
+        <v>1430</v>
+      </c>
+      <c r="K991" s="9" t="s">
+        <v>1431</v>
+      </c>
+      <c r="L991" s="10"/>
+      <c r="M991" s="10"/>
+      <c r="N991" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O991" s="11" t="n">
+        <v>46279.584272454</v>
+      </c>
+      <c r="P991" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q991" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R991" s="12" t="n">
+        <v>42000</v>
+      </c>
+      <c r="S991" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T991" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U991" s="9"/>
+      <c r="V991" s="9"/>
+    </row>
+    <row r="992" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A992" s="3" t="n">
+        <v>1061</v>
+      </c>
+      <c r="B992" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C992" s="4"/>
+      <c r="D992" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E992" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F992" s="4" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G992" s="4" t="s">
+        <v>1979</v>
+      </c>
+      <c r="H992" s="6" t="n">
+        <v>46276.750868056</v>
+      </c>
+      <c r="I992" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="J992" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="K992" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="L992" s="5"/>
+      <c r="M992" s="5"/>
+      <c r="N992" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O992" s="6" t="n">
+        <v>46279.584542326</v>
+      </c>
+      <c r="P992" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q992" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R992" s="7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S992" s="7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T992" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U992" s="4"/>
+      <c r="V992" s="4"/>
+    </row>
+    <row r="993" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A993" s="8" t="n">
+        <v>1062</v>
+      </c>
+      <c r="B993" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C993" s="9"/>
+      <c r="D993" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E993" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F993" s="9" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G993" s="9" t="s">
+        <v>1980</v>
+      </c>
+      <c r="H993" s="11" t="n">
+        <v>46276.782905093</v>
+      </c>
+      <c r="I993" s="9" t="s">
+        <v>1671</v>
+      </c>
+      <c r="J993" s="9" t="s">
+        <v>1671</v>
+      </c>
+      <c r="K993" s="9" t="s">
+        <v>1672</v>
+      </c>
+      <c r="L993" s="10"/>
+      <c r="M993" s="10"/>
+      <c r="N993" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O993" s="11" t="n">
+        <v>46279.584654942</v>
+      </c>
+      <c r="P993" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q993" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R993" s="12" t="n">
+        <v>18795</v>
+      </c>
+      <c r="S993" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T993" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U993" s="9"/>
+      <c r="V993" s="9"/>
+    </row>
+    <row r="994" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A994" s="3" t="n">
+        <v>1063</v>
+      </c>
+      <c r="B994" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C994" s="4"/>
+      <c r="D994" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E994" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F994" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G994" s="4" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H994" s="5" t="n">
+        <v>46276</v>
+      </c>
+      <c r="I994" s="4" t="s">
+        <v>1982</v>
+      </c>
+      <c r="J994" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="K994" s="4" t="s">
+        <v>1983</v>
+      </c>
+      <c r="L994" s="5"/>
+      <c r="M994" s="5"/>
+      <c r="N994" s="4" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O994" s="6" t="n">
+        <v>46279.599731713</v>
+      </c>
+      <c r="P994" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q994" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="R994" s="7" t="n">
+        <v>58266</v>
+      </c>
+      <c r="S994" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T994" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="U994" s="4"/>
+      <c r="V994" s="4"/>
+    </row>
+    <row r="995" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A995" s="8" t="n">
+        <v>1064</v>
+      </c>
+      <c r="B995" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C995" s="9"/>
+      <c r="D995" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E995" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F995" s="9" t="s">
+        <v>1930</v>
+      </c>
+      <c r="G995" s="9" t="s">
+        <v>1984</v>
+      </c>
+      <c r="H995" s="10" t="n">
+        <v>46276</v>
+      </c>
+      <c r="I995" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J995" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="K995" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L995" s="10"/>
+      <c r="M995" s="10"/>
+      <c r="N995" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O995" s="11" t="n">
+        <v>46279.617387963</v>
+      </c>
+      <c r="P995" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q995" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="R995" s="12" t="n">
+        <v>3157.44</v>
+      </c>
+      <c r="S995" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T995" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U995" s="9"/>
+      <c r="V995" s="9"/>
+    </row>
+    <row r="996" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A996" s="13" t="n">
+        <v>994</v>
+      </c>
+      <c r="B996" s="14"/>
+      <c r="C996" s="14"/>
+      <c r="D996" s="14"/>
+      <c r="E996" s="14"/>
+      <c r="F996" s="14"/>
+      <c r="G996" s="14"/>
+      <c r="H996" s="14"/>
+      <c r="I996" s="14"/>
+      <c r="J996" s="14"/>
+      <c r="K996" s="14"/>
+      <c r="L996" s="14"/>
+      <c r="M996" s="14"/>
+      <c r="N996" s="14"/>
+      <c r="O996" s="14"/>
+      <c r="P996" s="14"/>
+      <c r="Q996" s="14"/>
+      <c r="R996" s="15" t="n">
+        <v>59149988.2586</v>
+      </c>
+      <c r="S996" s="15" t="n">
+        <v>57884550.5986</v>
+      </c>
+      <c r="T996" s="14"/>
+      <c r="U996" s="14"/>
+      <c r="V996" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1985" uniqueCount="1985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1986" uniqueCount="1986">
   <si>
     <t>ID</t>
   </si>
@@ -5748,6 +5748,9 @@
     <t>1177</t>
   </si>
   <si>
+    <t>70 %</t>
+  </si>
+  <si>
     <t>1178</t>
   </si>
   <si>
@@ -5775,9 +5778,6 @@
     <t>1184</t>
   </si>
   <si>
-    <t>48 %</t>
-  </si>
-  <si>
     <t>1185</t>
   </si>
   <si>
@@ -5842,6 +5842,9 @@
   </si>
   <si>
     <t>1198</t>
+  </si>
+  <si>
+    <t>35 %</t>
   </si>
   <si>
     <t>1199</t>
@@ -54309,7 +54312,7 @@
         <v>23</v>
       </c>
       <c r="E830" s="3" t="s">
-        <v>24</v>
+        <v>1125</v>
       </c>
       <c r="F830" s="4" t="s">
         <v>1264</v>
@@ -54332,7 +54335,7 @@
       <c r="L830" s="5"/>
       <c r="M830" s="5"/>
       <c r="N830" s="4" t="s">
-        <v>29</v>
+        <v>1288</v>
       </c>
       <c r="O830" s="6" t="n">
         <v>46219.675766285</v>
@@ -54347,7 +54350,7 @@
         <v>102750</v>
       </c>
       <c r="S830" s="7" t="n">
-        <v>102750</v>
+        <v>101722.5</v>
       </c>
       <c r="T830" s="4" t="s">
         <v>32</v>
@@ -60921,13 +60924,13 @@
         <v>23</v>
       </c>
       <c r="E944" s="3" t="s">
-        <v>24</v>
+        <v>1911</v>
       </c>
       <c r="F944" s="4" t="s">
         <v>211</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="H944" s="6" t="n">
         <v>46261.624131944</v>
@@ -60944,7 +60947,7 @@
       <c r="L944" s="5"/>
       <c r="M944" s="5"/>
       <c r="N944" s="4" t="s">
-        <v>29</v>
+        <v>1288</v>
       </c>
       <c r="O944" s="6" t="n">
         <v>46262.582538507</v>
@@ -60959,7 +60962,7 @@
         <v>44352</v>
       </c>
       <c r="S944" s="7" t="n">
-        <v>44352</v>
+        <v>31152</v>
       </c>
       <c r="T944" s="4" t="s">
         <v>32</v>
@@ -60985,7 +60988,7 @@
         <v>521</v>
       </c>
       <c r="G945" s="9" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="H945" s="11" t="n">
         <v>46261.626898148</v>
@@ -61043,7 +61046,7 @@
         <v>1056</v>
       </c>
       <c r="G946" s="4" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="H946" s="5" t="n">
         <v>46262</v>
@@ -61101,7 +61104,7 @@
         <v>1019</v>
       </c>
       <c r="G947" s="9" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="H947" s="10" t="n">
         <v>46261</v>
@@ -61159,7 +61162,7 @@
         <v>38</v>
       </c>
       <c r="G948" s="4" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="H948" s="6" t="n">
         <v>46262.683993056</v>
@@ -61211,13 +61214,13 @@
         <v>23</v>
       </c>
       <c r="E949" s="8" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="F949" s="9" t="s">
         <v>1731</v>
       </c>
       <c r="G949" s="9" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="H949" s="10" t="n">
         <v>46265</v>
@@ -61234,7 +61237,7 @@
       <c r="L949" s="10"/>
       <c r="M949" s="10"/>
       <c r="N949" s="9" t="s">
-        <v>29</v>
+        <v>1288</v>
       </c>
       <c r="O949" s="11" t="n">
         <v>46265.656787882</v>
@@ -61269,13 +61272,13 @@
         <v>23</v>
       </c>
       <c r="E950" s="3" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="F950" s="4" t="s">
         <v>1639</v>
       </c>
       <c r="G950" s="4" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="H950" s="5" t="n">
         <v>46265</v>
@@ -61327,7 +61330,7 @@
         <v>23</v>
       </c>
       <c r="E951" s="8" t="s">
-        <v>1920</v>
+        <v>24</v>
       </c>
       <c r="F951" s="9" t="s">
         <v>619</v>
@@ -61350,7 +61353,7 @@
       <c r="L951" s="10"/>
       <c r="M951" s="10"/>
       <c r="N951" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O951" s="11" t="n">
         <v>46266.686144444</v>
@@ -61365,7 +61368,7 @@
         <v>16743.84</v>
       </c>
       <c r="S951" s="12" t="n">
-        <v>8000</v>
+        <v>16743.84</v>
       </c>
       <c r="T951" s="9" t="s">
         <v>32</v>
@@ -62139,13 +62142,13 @@
         <v>23</v>
       </c>
       <c r="E965" s="8" t="s">
-        <v>24</v>
+        <v>1943</v>
       </c>
       <c r="F965" s="9" t="s">
         <v>402</v>
       </c>
       <c r="G965" s="9" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="H965" s="11" t="n">
         <v>46269.745752315</v>
@@ -62162,7 +62165,7 @@
       <c r="L965" s="10"/>
       <c r="M965" s="10"/>
       <c r="N965" s="9" t="s">
-        <v>29</v>
+        <v>1288</v>
       </c>
       <c r="O965" s="11" t="n">
         <v>46274.36010478</v>
@@ -62177,7 +62180,7 @@
         <v>37380</v>
       </c>
       <c r="S965" s="12" t="n">
-        <v>37380</v>
+        <v>12900</v>
       </c>
       <c r="T965" s="9" t="s">
         <v>32</v>
@@ -62203,7 +62206,7 @@
         <v>988</v>
       </c>
       <c r="G966" s="4" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="H966" s="6" t="n">
         <v>46269.693969907</v>
@@ -62261,7 +62264,7 @@
         <v>1079</v>
       </c>
       <c r="G967" s="9" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="H967" s="11" t="n">
         <v>46269.459189815</v>
@@ -62313,13 +62316,13 @@
         <v>23</v>
       </c>
       <c r="E968" s="3" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="F968" s="4" t="s">
         <v>1496</v>
       </c>
       <c r="G968" s="4" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="H968" s="6" t="n">
         <v>46268.442615741</v>
@@ -62371,13 +62374,13 @@
         <v>23</v>
       </c>
       <c r="E969" s="8" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="F969" s="9" t="s">
         <v>157</v>
       </c>
       <c r="G969" s="9" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="H969" s="10" t="n">
         <v>46268</v>
@@ -62435,7 +62438,7 @@
         <v>969</v>
       </c>
       <c r="G970" s="4" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="H970" s="5" t="n">
         <v>46268</v>
@@ -62490,10 +62493,10 @@
         <v>24</v>
       </c>
       <c r="F971" s="9" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="G971" s="9" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="H971" s="10" t="n">
         <v>46273</v>
@@ -62545,13 +62548,13 @@
         <v>23</v>
       </c>
       <c r="E972" s="3" t="s">
-        <v>24</v>
+        <v>1285</v>
       </c>
       <c r="F972" s="4" t="s">
         <v>1264</v>
       </c>
       <c r="G972" s="4" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="H972" s="5" t="n">
         <v>46273</v>
@@ -62568,7 +62571,7 @@
       <c r="L972" s="5"/>
       <c r="M972" s="5"/>
       <c r="N972" s="4" t="s">
-        <v>29</v>
+        <v>1288</v>
       </c>
       <c r="O972" s="6" t="n">
         <v>46274.466218981</v>
@@ -62583,7 +62586,7 @@
         <v>128234.16</v>
       </c>
       <c r="S972" s="7" t="n">
-        <v>128234.16</v>
+        <v>94394.16</v>
       </c>
       <c r="T972" s="4" t="s">
         <v>32</v>
@@ -62603,13 +62606,13 @@
         <v>23</v>
       </c>
       <c r="E973" s="8" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="F973" s="9" t="s">
         <v>152</v>
       </c>
       <c r="G973" s="9" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="H973" s="11" t="n">
         <v>46273.758136574</v>
@@ -62664,22 +62667,22 @@
         <v>24</v>
       </c>
       <c r="F974" s="4" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="G974" s="4" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="H974" s="6" t="n">
         <v>46273.740416667</v>
       </c>
       <c r="I974" s="4" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="J974" s="4" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="K974" s="4" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="L974" s="5"/>
       <c r="M974" s="5"/>
@@ -62725,7 +62728,7 @@
         <v>1411</v>
       </c>
       <c r="G975" s="9" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H975" s="11" t="n">
         <v>46273.780162037</v>
@@ -62780,10 +62783,10 @@
         <v>285</v>
       </c>
       <c r="F976" s="4" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="G976" s="4" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H976" s="6" t="n">
         <v>46274.442685185</v>
@@ -62838,10 +62841,10 @@
         <v>24</v>
       </c>
       <c r="F977" s="9" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="G977" s="9" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H977" s="10" t="n">
         <v>46273</v>
@@ -62899,7 +62902,7 @@
         <v>355</v>
       </c>
       <c r="G978" s="4" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H978" s="5" t="n">
         <v>46274</v>
@@ -62957,7 +62960,7 @@
         <v>152</v>
       </c>
       <c r="G979" s="9" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H979" s="10" t="n">
         <v>46273</v>
@@ -63015,7 +63018,7 @@
         <v>1214</v>
       </c>
       <c r="G980" s="4" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H980" s="5" t="n">
         <v>46275</v>
@@ -63073,7 +63076,7 @@
         <v>215</v>
       </c>
       <c r="G981" s="9" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H981" s="10" t="n">
         <v>46275</v>
@@ -63131,7 +63134,7 @@
         <v>1459</v>
       </c>
       <c r="G982" s="4" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H982" s="6" t="n">
         <v>46274.972708333</v>
@@ -63189,7 +63192,7 @@
         <v>103</v>
       </c>
       <c r="G983" s="9" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H983" s="11" t="n">
         <v>46274.976979167</v>
@@ -63247,7 +63250,7 @@
         <v>276</v>
       </c>
       <c r="G984" s="4" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H984" s="6" t="n">
         <v>46274.703055556</v>
@@ -63305,7 +63308,7 @@
         <v>75</v>
       </c>
       <c r="G985" s="9" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H985" s="11" t="n">
         <v>46274.682534722</v>
@@ -63363,7 +63366,7 @@
         <v>1196</v>
       </c>
       <c r="G986" s="4" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H986" s="6" t="n">
         <v>46275.472800926</v>
@@ -63421,7 +63424,7 @@
         <v>1118</v>
       </c>
       <c r="G987" s="9" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H987" s="11" t="n">
         <v>46276.641041667</v>
@@ -63473,13 +63476,13 @@
         <v>23</v>
       </c>
       <c r="E988" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F988" s="4" t="s">
         <v>1296</v>
       </c>
       <c r="G988" s="4" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H988" s="6" t="n">
         <v>46276.445613426</v>
@@ -63496,7 +63499,7 @@
       <c r="L988" s="5"/>
       <c r="M988" s="5"/>
       <c r="N988" s="4" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O988" s="6" t="n">
         <v>46279.583654942</v>
@@ -63511,7 +63514,7 @@
         <v>39000</v>
       </c>
       <c r="S988" s="7" t="n">
-        <v>0</v>
+        <v>39000</v>
       </c>
       <c r="T988" s="4" t="s">
         <v>32</v>
@@ -63537,7 +63540,7 @@
         <v>478</v>
       </c>
       <c r="G989" s="9" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H989" s="11" t="n">
         <v>46275.859097222</v>
@@ -63589,13 +63592,13 @@
         <v>23</v>
       </c>
       <c r="E990" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F990" s="4" t="s">
         <v>496</v>
       </c>
       <c r="G990" s="4" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H990" s="6" t="n">
         <v>46276.36244213</v>
@@ -63612,7 +63615,7 @@
       <c r="L990" s="5"/>
       <c r="M990" s="5"/>
       <c r="N990" s="4" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O990" s="6" t="n">
         <v>46279.584095637</v>
@@ -63627,7 +63630,7 @@
         <v>17343.86</v>
       </c>
       <c r="S990" s="7" t="n">
-        <v>0</v>
+        <v>17343.86</v>
       </c>
       <c r="T990" s="4" t="s">
         <v>32</v>
@@ -63653,7 +63656,7 @@
         <v>1427</v>
       </c>
       <c r="G991" s="9" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H991" s="11" t="n">
         <v>46276.780416667</v>
@@ -63711,7 +63714,7 @@
         <v>1292</v>
       </c>
       <c r="G992" s="4" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H992" s="6" t="n">
         <v>46276.750868056</v>
@@ -63769,7 +63772,7 @@
         <v>1669</v>
       </c>
       <c r="G993" s="9" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H993" s="11" t="n">
         <v>46276.782905093</v>
@@ -63827,19 +63830,19 @@
         <v>1162</v>
       </c>
       <c r="G994" s="4" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H994" s="5" t="n">
         <v>46276</v>
       </c>
       <c r="I994" s="4" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="J994" s="4" t="s">
         <v>1165</v>
       </c>
       <c r="K994" s="4" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="L994" s="5"/>
       <c r="M994" s="5"/>
@@ -63879,13 +63882,13 @@
         <v>23</v>
       </c>
       <c r="E995" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F995" s="9" t="s">
         <v>1930</v>
       </c>
       <c r="G995" s="9" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H995" s="10" t="n">
         <v>46276</v>
@@ -63902,7 +63905,7 @@
       <c r="L995" s="10"/>
       <c r="M995" s="10"/>
       <c r="N995" s="9" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O995" s="11" t="n">
         <v>46279.617387963</v>
@@ -63917,7 +63920,7 @@
         <v>3157.44</v>
       </c>
       <c r="S995" s="12" t="n">
-        <v>0</v>
+        <v>3157.44</v>
       </c>
       <c r="T995" s="9" t="s">
         <v>32</v>
@@ -63949,7 +63952,7 @@
         <v>59149988.2586</v>
       </c>
       <c r="S996" s="15" t="n">
-        <v>57884550.5986</v>
+        <v>57880248.2386</v>
       </c>
       <c r="T996" s="14"/>
       <c r="U996" s="14"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1986" uniqueCount="1986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="1992">
   <si>
     <t>ID</t>
   </si>
@@ -4491,7 +4491,7 @@
     <t>881</t>
   </si>
   <si>
-    <t>44 %</t>
+    <t>61 %</t>
   </si>
   <si>
     <t>884</t>
@@ -5748,9 +5748,6 @@
     <t>1177</t>
   </si>
   <si>
-    <t>70 %</t>
-  </si>
-  <si>
     <t>1178</t>
   </si>
   <si>
@@ -5844,9 +5841,6 @@
     <t>1198</t>
   </si>
   <si>
-    <t>35 %</t>
-  </si>
-  <si>
     <t>1199</t>
   </si>
   <si>
@@ -5877,12 +5871,12 @@
     <t>1205</t>
   </si>
   <si>
+    <t>83 %</t>
+  </si>
+  <si>
     <t>1206</t>
   </si>
   <si>
-    <t>53 %</t>
-  </si>
-  <si>
     <t>1207</t>
   </si>
   <si>
@@ -5971,6 +5965,30 @@
   </si>
   <si>
     <t>1229</t>
+  </si>
+  <si>
+    <t>1230</t>
+  </si>
+  <si>
+    <t>55 %</t>
+  </si>
+  <si>
+    <t>1231</t>
+  </si>
+  <si>
+    <t>1232</t>
+  </si>
+  <si>
+    <t>1233</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>1235</t>
+  </si>
+  <si>
+    <t>1236</t>
   </si>
 </sst>
 </file>
@@ -6164,7 +6182,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V996"/>
+  <dimension ref="A1:V1003"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -45474,7 +45492,7 @@
         <v>226301.7</v>
       </c>
       <c r="S677" s="12" t="n">
-        <v>100277.4</v>
+        <v>138220.2</v>
       </c>
       <c r="T677" s="9" t="s">
         <v>32</v>
@@ -56145,7 +56163,7 @@
         <v>1687</v>
       </c>
       <c r="R861" s="12" t="n">
-        <v>39463.12</v>
+        <v>39446.2</v>
       </c>
       <c r="S861" s="12" t="n">
         <v>16215.2</v>
@@ -57015,7 +57033,7 @@
         <v>74</v>
       </c>
       <c r="R876" s="7" t="n">
-        <v>24200</v>
+        <v>24258.9</v>
       </c>
       <c r="S876" s="7" t="n">
         <v>14064</v>
@@ -60924,13 +60942,13 @@
         <v>23</v>
       </c>
       <c r="E944" s="3" t="s">
-        <v>1911</v>
+        <v>24</v>
       </c>
       <c r="F944" s="4" t="s">
         <v>211</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H944" s="6" t="n">
         <v>46261.624131944</v>
@@ -60947,7 +60965,7 @@
       <c r="L944" s="5"/>
       <c r="M944" s="5"/>
       <c r="N944" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O944" s="6" t="n">
         <v>46262.582538507</v>
@@ -60962,7 +60980,7 @@
         <v>44352</v>
       </c>
       <c r="S944" s="7" t="n">
-        <v>31152</v>
+        <v>44352</v>
       </c>
       <c r="T944" s="4" t="s">
         <v>32</v>
@@ -60988,7 +61006,7 @@
         <v>521</v>
       </c>
       <c r="G945" s="9" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H945" s="11" t="n">
         <v>46261.626898148</v>
@@ -61046,7 +61064,7 @@
         <v>1056</v>
       </c>
       <c r="G946" s="4" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="H946" s="5" t="n">
         <v>46262</v>
@@ -61104,7 +61122,7 @@
         <v>1019</v>
       </c>
       <c r="G947" s="9" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H947" s="10" t="n">
         <v>46261</v>
@@ -61162,7 +61180,7 @@
         <v>38</v>
       </c>
       <c r="G948" s="4" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H948" s="6" t="n">
         <v>46262.683993056</v>
@@ -61214,13 +61232,13 @@
         <v>23</v>
       </c>
       <c r="E949" s="8" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="F949" s="9" t="s">
         <v>1731</v>
       </c>
       <c r="G949" s="9" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="H949" s="10" t="n">
         <v>46265</v>
@@ -61272,13 +61290,13 @@
         <v>23</v>
       </c>
       <c r="E950" s="3" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="F950" s="4" t="s">
         <v>1639</v>
       </c>
       <c r="G950" s="4" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H950" s="5" t="n">
         <v>46265</v>
@@ -61336,7 +61354,7 @@
         <v>619</v>
       </c>
       <c r="G951" s="9" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="H951" s="11" t="n">
         <v>46265.756805556</v>
@@ -61394,7 +61412,7 @@
         <v>103</v>
       </c>
       <c r="G952" s="4" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="H952" s="6" t="n">
         <v>46262.6721875</v>
@@ -61452,7 +61470,7 @@
         <v>814</v>
       </c>
       <c r="G953" s="9" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H953" s="11" t="n">
         <v>46265.738773148</v>
@@ -61510,7 +61528,7 @@
         <v>484</v>
       </c>
       <c r="G954" s="4" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="H954" s="6" t="n">
         <v>46265.406400463</v>
@@ -61568,7 +61586,7 @@
         <v>482</v>
       </c>
       <c r="G955" s="9" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="H955" s="11" t="n">
         <v>46262.643506944</v>
@@ -61626,7 +61644,7 @@
         <v>744</v>
       </c>
       <c r="G956" s="4" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="H956" s="6" t="n">
         <v>46262.644305556</v>
@@ -61684,7 +61702,7 @@
         <v>1179</v>
       </c>
       <c r="G957" s="9" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H957" s="11" t="n">
         <v>46262.617488426</v>
@@ -61742,7 +61760,7 @@
         <v>1526</v>
       </c>
       <c r="G958" s="4" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H958" s="6" t="n">
         <v>46262.337835648</v>
@@ -61800,7 +61818,7 @@
         <v>1516</v>
       </c>
       <c r="G959" s="9" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H959" s="10" t="n">
         <v>46266</v>
@@ -61855,10 +61873,10 @@
         <v>24</v>
       </c>
       <c r="F960" s="4" t="s">
+        <v>1929</v>
+      </c>
+      <c r="G960" s="4" t="s">
         <v>1930</v>
-      </c>
-      <c r="G960" s="4" t="s">
-        <v>1931</v>
       </c>
       <c r="H960" s="5" t="n">
         <v>46265</v>
@@ -61913,22 +61931,22 @@
         <v>24</v>
       </c>
       <c r="F961" s="9" t="s">
+        <v>1931</v>
+      </c>
+      <c r="G961" s="9" t="s">
         <v>1932</v>
-      </c>
-      <c r="G961" s="9" t="s">
-        <v>1933</v>
       </c>
       <c r="H961" s="10" t="n">
         <v>46266</v>
       </c>
       <c r="I961" s="9" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="J961" s="9" t="s">
+        <v>1933</v>
+      </c>
+      <c r="K961" s="9" t="s">
         <v>1934</v>
-      </c>
-      <c r="K961" s="9" t="s">
-        <v>1935</v>
       </c>
       <c r="L961" s="10"/>
       <c r="M961" s="10"/>
@@ -61971,22 +61989,22 @@
         <v>24</v>
       </c>
       <c r="F962" s="4" t="s">
+        <v>1935</v>
+      </c>
+      <c r="G962" s="4" t="s">
         <v>1936</v>
-      </c>
-      <c r="G962" s="4" t="s">
-        <v>1937</v>
       </c>
       <c r="H962" s="5" t="n">
         <v>46265</v>
       </c>
       <c r="I962" s="4" t="s">
+        <v>1937</v>
+      </c>
+      <c r="J962" s="4" t="s">
         <v>1938</v>
       </c>
-      <c r="J962" s="4" t="s">
+      <c r="K962" s="4" t="s">
         <v>1939</v>
-      </c>
-      <c r="K962" s="4" t="s">
-        <v>1940</v>
       </c>
       <c r="L962" s="5"/>
       <c r="M962" s="5"/>
@@ -62032,7 +62050,7 @@
         <v>945</v>
       </c>
       <c r="G963" s="9" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="H963" s="11" t="n">
         <v>46267.438217593</v>
@@ -62090,7 +62108,7 @@
         <v>310</v>
       </c>
       <c r="G964" s="4" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="H964" s="5" t="n">
         <v>46269</v>
@@ -62142,13 +62160,13 @@
         <v>23</v>
       </c>
       <c r="E965" s="8" t="s">
-        <v>1943</v>
+        <v>24</v>
       </c>
       <c r="F965" s="9" t="s">
         <v>402</v>
       </c>
       <c r="G965" s="9" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="H965" s="11" t="n">
         <v>46269.745752315</v>
@@ -62180,7 +62198,7 @@
         <v>37380</v>
       </c>
       <c r="S965" s="12" t="n">
-        <v>12900</v>
+        <v>37380</v>
       </c>
       <c r="T965" s="9" t="s">
         <v>32</v>
@@ -62206,7 +62224,7 @@
         <v>988</v>
       </c>
       <c r="G966" s="4" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="H966" s="6" t="n">
         <v>46269.693969907</v>
@@ -62264,7 +62282,7 @@
         <v>1079</v>
       </c>
       <c r="G967" s="9" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="H967" s="11" t="n">
         <v>46269.459189815</v>
@@ -62316,13 +62334,13 @@
         <v>23</v>
       </c>
       <c r="E968" s="3" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="F968" s="4" t="s">
         <v>1496</v>
       </c>
       <c r="G968" s="4" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="H968" s="6" t="n">
         <v>46268.442615741</v>
@@ -62374,13 +62392,13 @@
         <v>23</v>
       </c>
       <c r="E969" s="8" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="F969" s="9" t="s">
         <v>157</v>
       </c>
       <c r="G969" s="9" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="H969" s="10" t="n">
         <v>46268</v>
@@ -62438,7 +62456,7 @@
         <v>969</v>
       </c>
       <c r="G970" s="4" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="H970" s="5" t="n">
         <v>46268</v>
@@ -62493,10 +62511,10 @@
         <v>24</v>
       </c>
       <c r="F971" s="9" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="G971" s="9" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="H971" s="10" t="n">
         <v>46273</v>
@@ -62548,13 +62566,13 @@
         <v>23</v>
       </c>
       <c r="E972" s="3" t="s">
-        <v>1285</v>
+        <v>1952</v>
       </c>
       <c r="F972" s="4" t="s">
         <v>1264</v>
       </c>
       <c r="G972" s="4" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="H972" s="5" t="n">
         <v>46273</v>
@@ -62586,7 +62604,7 @@
         <v>128234.16</v>
       </c>
       <c r="S972" s="7" t="n">
-        <v>94394.16</v>
+        <v>106436.7</v>
       </c>
       <c r="T972" s="4" t="s">
         <v>32</v>
@@ -62606,13 +62624,13 @@
         <v>23</v>
       </c>
       <c r="E973" s="8" t="s">
-        <v>1955</v>
+        <v>24</v>
       </c>
       <c r="F973" s="9" t="s">
         <v>152</v>
       </c>
       <c r="G973" s="9" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="H973" s="11" t="n">
         <v>46273.758136574</v>
@@ -62629,7 +62647,7 @@
       <c r="L973" s="10"/>
       <c r="M973" s="10"/>
       <c r="N973" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O973" s="11" t="n">
         <v>46274.621396412</v>
@@ -62644,7 +62662,7 @@
         <v>193050</v>
       </c>
       <c r="S973" s="12" t="n">
-        <v>101400</v>
+        <v>193050</v>
       </c>
       <c r="T973" s="9" t="s">
         <v>32</v>
@@ -62667,22 +62685,22 @@
         <v>24</v>
       </c>
       <c r="F974" s="4" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="G974" s="4" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="H974" s="6" t="n">
         <v>46273.740416667</v>
       </c>
       <c r="I974" s="4" t="s">
+        <v>1955</v>
+      </c>
+      <c r="J974" s="4" t="s">
         <v>1957</v>
       </c>
-      <c r="J974" s="4" t="s">
-        <v>1959</v>
-      </c>
       <c r="K974" s="4" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="L974" s="5"/>
       <c r="M974" s="5"/>
@@ -62728,7 +62746,7 @@
         <v>1411</v>
       </c>
       <c r="G975" s="9" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="H975" s="11" t="n">
         <v>46273.780162037</v>
@@ -62783,10 +62801,10 @@
         <v>285</v>
       </c>
       <c r="F976" s="4" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="G976" s="4" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="H976" s="6" t="n">
         <v>46274.442685185</v>
@@ -62841,10 +62859,10 @@
         <v>24</v>
       </c>
       <c r="F977" s="9" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="G977" s="9" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="H977" s="10" t="n">
         <v>46273</v>
@@ -62902,7 +62920,7 @@
         <v>355</v>
       </c>
       <c r="G978" s="4" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="H978" s="5" t="n">
         <v>46274</v>
@@ -62954,13 +62972,13 @@
         <v>23</v>
       </c>
       <c r="E979" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F979" s="9" t="s">
         <v>152</v>
       </c>
       <c r="G979" s="9" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="H979" s="10" t="n">
         <v>46273</v>
@@ -62977,7 +62995,7 @@
       <c r="L979" s="10"/>
       <c r="M979" s="10"/>
       <c r="N979" s="9" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O979" s="11" t="n">
         <v>46274.640229861</v>
@@ -62992,7 +63010,7 @@
         <v>1950</v>
       </c>
       <c r="S979" s="12" t="n">
-        <v>0</v>
+        <v>1950</v>
       </c>
       <c r="T979" s="9" t="s">
         <v>32</v>
@@ -63018,7 +63036,7 @@
         <v>1214</v>
       </c>
       <c r="G980" s="4" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="H980" s="5" t="n">
         <v>46275</v>
@@ -63070,13 +63088,13 @@
         <v>23</v>
       </c>
       <c r="E981" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F981" s="9" t="s">
         <v>215</v>
       </c>
       <c r="G981" s="9" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="H981" s="10" t="n">
         <v>46275</v>
@@ -63093,7 +63111,7 @@
       <c r="L981" s="10"/>
       <c r="M981" s="10"/>
       <c r="N981" s="9" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O981" s="11" t="n">
         <v>46275.6269689</v>
@@ -63108,7 +63126,7 @@
         <v>78750</v>
       </c>
       <c r="S981" s="12" t="n">
-        <v>0</v>
+        <v>78750</v>
       </c>
       <c r="T981" s="9" t="s">
         <v>32</v>
@@ -63134,7 +63152,7 @@
         <v>1459</v>
       </c>
       <c r="G982" s="4" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="H982" s="6" t="n">
         <v>46274.972708333</v>
@@ -63192,7 +63210,7 @@
         <v>103</v>
       </c>
       <c r="G983" s="9" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="H983" s="11" t="n">
         <v>46274.976979167</v>
@@ -63250,7 +63268,7 @@
         <v>276</v>
       </c>
       <c r="G984" s="4" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="H984" s="6" t="n">
         <v>46274.703055556</v>
@@ -63302,13 +63320,13 @@
         <v>23</v>
       </c>
       <c r="E985" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F985" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G985" s="9" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="H985" s="11" t="n">
         <v>46274.682534722</v>
@@ -63325,7 +63343,7 @@
       <c r="L985" s="10"/>
       <c r="M985" s="10"/>
       <c r="N985" s="9" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O985" s="11" t="n">
         <v>46275.62857581</v>
@@ -63340,7 +63358,7 @@
         <v>22230</v>
       </c>
       <c r="S985" s="12" t="n">
-        <v>0</v>
+        <v>22230</v>
       </c>
       <c r="T985" s="9" t="s">
         <v>32</v>
@@ -63366,7 +63384,7 @@
         <v>1196</v>
       </c>
       <c r="G986" s="4" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="H986" s="6" t="n">
         <v>46275.472800926</v>
@@ -63424,7 +63442,7 @@
         <v>1118</v>
       </c>
       <c r="G987" s="9" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="H987" s="11" t="n">
         <v>46276.641041667</v>
@@ -63482,7 +63500,7 @@
         <v>1296</v>
       </c>
       <c r="G988" s="4" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="H988" s="6" t="n">
         <v>46276.445613426</v>
@@ -63540,7 +63558,7 @@
         <v>478</v>
       </c>
       <c r="G989" s="9" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="H989" s="11" t="n">
         <v>46275.859097222</v>
@@ -63598,7 +63616,7 @@
         <v>496</v>
       </c>
       <c r="G990" s="4" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="H990" s="6" t="n">
         <v>46276.36244213</v>
@@ -63656,7 +63674,7 @@
         <v>1427</v>
       </c>
       <c r="G991" s="9" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="H991" s="11" t="n">
         <v>46276.780416667</v>
@@ -63714,7 +63732,7 @@
         <v>1292</v>
       </c>
       <c r="G992" s="4" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="H992" s="6" t="n">
         <v>46276.750868056</v>
@@ -63766,13 +63784,13 @@
         <v>23</v>
       </c>
       <c r="E993" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F993" s="9" t="s">
         <v>1669</v>
       </c>
       <c r="G993" s="9" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="H993" s="11" t="n">
         <v>46276.782905093</v>
@@ -63789,7 +63807,7 @@
       <c r="L993" s="10"/>
       <c r="M993" s="10"/>
       <c r="N993" s="9" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O993" s="11" t="n">
         <v>46279.584654942</v>
@@ -63804,7 +63822,7 @@
         <v>18795</v>
       </c>
       <c r="S993" s="12" t="n">
-        <v>0</v>
+        <v>18795</v>
       </c>
       <c r="T993" s="9" t="s">
         <v>32</v>
@@ -63830,19 +63848,19 @@
         <v>1162</v>
       </c>
       <c r="G994" s="4" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="H994" s="5" t="n">
         <v>46276</v>
       </c>
       <c r="I994" s="4" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="J994" s="4" t="s">
         <v>1165</v>
       </c>
       <c r="K994" s="4" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="L994" s="5"/>
       <c r="M994" s="5"/>
@@ -63885,10 +63903,10 @@
         <v>24</v>
       </c>
       <c r="F995" s="9" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="G995" s="9" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="H995" s="10" t="n">
         <v>46276</v>
@@ -63928,35 +63946,441 @@
       <c r="U995" s="9"/>
       <c r="V995" s="9"/>
     </row>
-    <row r="996" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A996" s="13" t="n">
-        <v>994</v>
-      </c>
-      <c r="B996" s="14"/>
-      <c r="C996" s="14"/>
-      <c r="D996" s="14"/>
-      <c r="E996" s="14"/>
-      <c r="F996" s="14"/>
-      <c r="G996" s="14"/>
-      <c r="H996" s="14"/>
-      <c r="I996" s="14"/>
-      <c r="J996" s="14"/>
-      <c r="K996" s="14"/>
-      <c r="L996" s="14"/>
-      <c r="M996" s="14"/>
-      <c r="N996" s="14"/>
-      <c r="O996" s="14"/>
-      <c r="P996" s="14"/>
-      <c r="Q996" s="14"/>
-      <c r="R996" s="15" t="n">
-        <v>59149988.2586</v>
-      </c>
-      <c r="S996" s="15" t="n">
-        <v>57880248.2386</v>
-      </c>
-      <c r="T996" s="14"/>
-      <c r="U996" s="14"/>
-      <c r="V996" s="16"/>
+    <row r="996" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A996" s="3" t="n">
+        <v>1065</v>
+      </c>
+      <c r="B996" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C996" s="4"/>
+      <c r="D996" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E996" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F996" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="G996" s="4" t="s">
+        <v>1984</v>
+      </c>
+      <c r="H996" s="6" t="n">
+        <v>46279.943194444</v>
+      </c>
+      <c r="I996" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="J996" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="K996" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="L996" s="5"/>
+      <c r="M996" s="5"/>
+      <c r="N996" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O996" s="6" t="n">
+        <v>46281.567899306</v>
+      </c>
+      <c r="P996" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q996" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R996" s="7" t="n">
+        <v>22176</v>
+      </c>
+      <c r="S996" s="7" t="n">
+        <v>22176</v>
+      </c>
+      <c r="T996" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U996" s="4"/>
+      <c r="V996" s="4"/>
+    </row>
+    <row r="997" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A997" s="8" t="n">
+        <v>1066</v>
+      </c>
+      <c r="B997" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C997" s="9"/>
+      <c r="D997" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E997" s="8" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F997" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="G997" s="9" t="s">
+        <v>1986</v>
+      </c>
+      <c r="H997" s="11" t="n">
+        <v>46280.741736111</v>
+      </c>
+      <c r="I997" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="J997" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="K997" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="L997" s="10"/>
+      <c r="M997" s="10"/>
+      <c r="N997" s="9" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O997" s="11" t="n">
+        <v>46281.618698843</v>
+      </c>
+      <c r="P997" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q997" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R997" s="12" t="n">
+        <v>49800</v>
+      </c>
+      <c r="S997" s="12" t="n">
+        <v>27300</v>
+      </c>
+      <c r="T997" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U997" s="9"/>
+      <c r="V997" s="9"/>
+    </row>
+    <row r="998" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A998" s="3" t="n">
+        <v>1067</v>
+      </c>
+      <c r="B998" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C998" s="4"/>
+      <c r="D998" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E998" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F998" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G998" s="4" t="s">
+        <v>1987</v>
+      </c>
+      <c r="H998" s="5" t="n">
+        <v>46279</v>
+      </c>
+      <c r="I998" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="J998" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="K998" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="L998" s="5"/>
+      <c r="M998" s="5"/>
+      <c r="N998" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O998" s="6" t="n">
+        <v>46281.660576192</v>
+      </c>
+      <c r="P998" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q998" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="R998" s="7" t="n">
+        <v>12900</v>
+      </c>
+      <c r="S998" s="7" t="n">
+        <v>12900</v>
+      </c>
+      <c r="T998" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U998" s="4"/>
+      <c r="V998" s="4"/>
+    </row>
+    <row r="999" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A999" s="8" t="n">
+        <v>1068</v>
+      </c>
+      <c r="B999" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C999" s="9"/>
+      <c r="D999" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E999" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F999" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="G999" s="9" t="s">
+        <v>1988</v>
+      </c>
+      <c r="H999" s="11" t="n">
+        <v>46280.714386574</v>
+      </c>
+      <c r="I999" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="J999" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="K999" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="L999" s="10"/>
+      <c r="M999" s="10"/>
+      <c r="N999" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O999" s="11" t="n">
+        <v>46281.66226184</v>
+      </c>
+      <c r="P999" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q999" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R999" s="12" t="n">
+        <v>9198</v>
+      </c>
+      <c r="S999" s="12" t="n">
+        <v>9198</v>
+      </c>
+      <c r="T999" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U999" s="9"/>
+      <c r="V999" s="9"/>
+    </row>
+    <row r="1000" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1000" s="3" t="n">
+        <v>1069</v>
+      </c>
+      <c r="B1000" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1000" s="4"/>
+      <c r="D1000" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1000" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1000" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1000" s="4" t="s">
+        <v>1989</v>
+      </c>
+      <c r="H1000" s="6" t="n">
+        <v>46280.693761574</v>
+      </c>
+      <c r="I1000" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1000" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1000" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1000" s="5"/>
+      <c r="M1000" s="5"/>
+      <c r="N1000" s="4" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O1000" s="6" t="n">
+        <v>46281.662435336</v>
+      </c>
+      <c r="P1000" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1000" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1000" s="7" t="n">
+        <v>882756</v>
+      </c>
+      <c r="S1000" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1000" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1000" s="4"/>
+      <c r="V1000" s="4"/>
+    </row>
+    <row r="1001" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1001" s="8" t="n">
+        <v>1070</v>
+      </c>
+      <c r="B1001" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1001" s="9"/>
+      <c r="D1001" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1001" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1001" s="9" t="s">
+        <v>965</v>
+      </c>
+      <c r="G1001" s="9" t="s">
+        <v>1990</v>
+      </c>
+      <c r="H1001" s="11" t="n">
+        <v>46280.868599537</v>
+      </c>
+      <c r="I1001" s="9" t="s">
+        <v>965</v>
+      </c>
+      <c r="J1001" s="9" t="s">
+        <v>967</v>
+      </c>
+      <c r="K1001" s="9" t="s">
+        <v>968</v>
+      </c>
+      <c r="L1001" s="10"/>
+      <c r="M1001" s="10"/>
+      <c r="N1001" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O1001" s="11" t="n">
+        <v>46281.662679248</v>
+      </c>
+      <c r="P1001" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1001" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1001" s="12" t="n">
+        <v>26033.86</v>
+      </c>
+      <c r="S1001" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1001" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1001" s="9"/>
+      <c r="V1001" s="9"/>
+    </row>
+    <row r="1002" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1002" s="3" t="n">
+        <v>1071</v>
+      </c>
+      <c r="B1002" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1002" s="4"/>
+      <c r="D1002" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1002" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1002" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="G1002" s="4" t="s">
+        <v>1991</v>
+      </c>
+      <c r="H1002" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="I1002" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="J1002" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="K1002" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="L1002" s="5"/>
+      <c r="M1002" s="5"/>
+      <c r="N1002" s="4" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O1002" s="6" t="n">
+        <v>46281.670784028</v>
+      </c>
+      <c r="P1002" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1002" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1002" s="7" t="n">
+        <v>20400</v>
+      </c>
+      <c r="S1002" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1002" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1002" s="4"/>
+      <c r="V1002" s="4"/>
+    </row>
+    <row r="1003" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A1003" s="13" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B1003" s="14"/>
+      <c r="C1003" s="14"/>
+      <c r="D1003" s="14"/>
+      <c r="E1003" s="14"/>
+      <c r="F1003" s="14"/>
+      <c r="G1003" s="14"/>
+      <c r="H1003" s="14"/>
+      <c r="I1003" s="14"/>
+      <c r="J1003" s="14"/>
+      <c r="K1003" s="14"/>
+      <c r="L1003" s="14"/>
+      <c r="M1003" s="14"/>
+      <c r="N1003" s="14"/>
+      <c r="O1003" s="14"/>
+      <c r="P1003" s="14"/>
+      <c r="Q1003" s="14"/>
+      <c r="R1003" s="15" t="n">
+        <v>60173294.0986</v>
+      </c>
+      <c r="S1003" s="15" t="n">
+        <v>58252862.5786</v>
+      </c>
+      <c r="T1003" s="14"/>
+      <c r="U1003" s="14"/>
+      <c r="V1003" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="1992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="2009">
   <si>
     <t>ID</t>
   </si>
@@ -5989,6 +5989,57 @@
   </si>
   <si>
     <t>1236</t>
+  </si>
+  <si>
+    <t>ZILFARMA PRODUTOS</t>
+  </si>
+  <si>
+    <t>1237</t>
+  </si>
+  <si>
+    <t>ZILFARMA PRODUTOS FARMACEUTICOS E IMPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t>06.046.371/0001-90</t>
+  </si>
+  <si>
+    <t>1238</t>
+  </si>
+  <si>
+    <t>1239</t>
+  </si>
+  <si>
+    <t>1240</t>
+  </si>
+  <si>
+    <t>MEDCARE DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1241</t>
+  </si>
+  <si>
+    <t>DISNOMED</t>
+  </si>
+  <si>
+    <t>1242</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA NOGUEIRA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>03.315.618/0001-39</t>
+  </si>
+  <si>
+    <t>OBRA PRIVADA - INTERNA</t>
+  </si>
+  <si>
+    <t>Orçamento 274</t>
+  </si>
+  <si>
+    <t>1243</t>
+  </si>
+  <si>
+    <t>EM ANDAMENTO</t>
   </si>
 </sst>
 </file>
@@ -6182,7 +6233,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V1003"/>
+  <dimension ref="A1:V1010"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -56963,7 +57014,7 @@
       <c r="L875" s="10"/>
       <c r="M875" s="10"/>
       <c r="N875" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O875" s="11" t="n">
         <v>46233.668326042</v>
@@ -61429,7 +61480,7 @@
       <c r="L952" s="5"/>
       <c r="M952" s="5"/>
       <c r="N952" s="4" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O952" s="6" t="n">
         <v>46266.68744059</v>
@@ -63007,10 +63058,10 @@
         <v>47</v>
       </c>
       <c r="R979" s="12" t="n">
-        <v>1950</v>
+        <v>4950</v>
       </c>
       <c r="S979" s="12" t="n">
-        <v>1950</v>
+        <v>4950</v>
       </c>
       <c r="T979" s="9" t="s">
         <v>32</v>
@@ -63169,7 +63220,7 @@
       <c r="L982" s="5"/>
       <c r="M982" s="5"/>
       <c r="N982" s="4" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O982" s="6" t="n">
         <v>46275.62822434</v>
@@ -64248,7 +64299,7 @@
         <v>23</v>
       </c>
       <c r="E1001" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1001" s="9" t="s">
         <v>965</v>
@@ -64271,7 +64322,7 @@
       <c r="L1001" s="10"/>
       <c r="M1001" s="10"/>
       <c r="N1001" s="9" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O1001" s="11" t="n">
         <v>46281.662679248</v>
@@ -64286,7 +64337,7 @@
         <v>26033.86</v>
       </c>
       <c r="S1001" s="12" t="n">
-        <v>0</v>
+        <v>26033.86</v>
       </c>
       <c r="T1001" s="9" t="s">
         <v>32</v>
@@ -64352,35 +64403,441 @@
       <c r="U1002" s="4"/>
       <c r="V1002" s="4"/>
     </row>
-    <row r="1003" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A1003" s="13" t="n">
-        <v>1001</v>
-      </c>
-      <c r="B1003" s="14"/>
-      <c r="C1003" s="14"/>
-      <c r="D1003" s="14"/>
-      <c r="E1003" s="14"/>
-      <c r="F1003" s="14"/>
-      <c r="G1003" s="14"/>
-      <c r="H1003" s="14"/>
-      <c r="I1003" s="14"/>
-      <c r="J1003" s="14"/>
-      <c r="K1003" s="14"/>
-      <c r="L1003" s="14"/>
-      <c r="M1003" s="14"/>
-      <c r="N1003" s="14"/>
-      <c r="O1003" s="14"/>
-      <c r="P1003" s="14"/>
-      <c r="Q1003" s="14"/>
-      <c r="R1003" s="15" t="n">
-        <v>60173294.0986</v>
-      </c>
-      <c r="S1003" s="15" t="n">
-        <v>58252862.5786</v>
-      </c>
-      <c r="T1003" s="14"/>
-      <c r="U1003" s="14"/>
-      <c r="V1003" s="16"/>
+    <row r="1003" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1003" s="8" t="n">
+        <v>1072</v>
+      </c>
+      <c r="B1003" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1003" s="9"/>
+      <c r="D1003" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1003" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1003" s="9" t="s">
+        <v>1992</v>
+      </c>
+      <c r="G1003" s="9" t="s">
+        <v>1993</v>
+      </c>
+      <c r="H1003" s="11" t="n">
+        <v>46281.483981481</v>
+      </c>
+      <c r="I1003" s="9" t="s">
+        <v>1994</v>
+      </c>
+      <c r="J1003" s="9" t="s">
+        <v>1994</v>
+      </c>
+      <c r="K1003" s="9" t="s">
+        <v>1995</v>
+      </c>
+      <c r="L1003" s="10"/>
+      <c r="M1003" s="10"/>
+      <c r="N1003" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O1003" s="11" t="n">
+        <v>46282.652243715</v>
+      </c>
+      <c r="P1003" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1003" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1003" s="12" t="n">
+        <v>13822.8</v>
+      </c>
+      <c r="S1003" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1003" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1003" s="9"/>
+      <c r="V1003" s="9"/>
+    </row>
+    <row r="1004" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1004" s="3" t="n">
+        <v>1073</v>
+      </c>
+      <c r="B1004" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1004" s="4"/>
+      <c r="D1004" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1004" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1004" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="G1004" s="4" t="s">
+        <v>1996</v>
+      </c>
+      <c r="H1004" s="6" t="n">
+        <v>46281.591608796</v>
+      </c>
+      <c r="I1004" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="J1004" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="K1004" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="L1004" s="5"/>
+      <c r="M1004" s="5"/>
+      <c r="N1004" s="4" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O1004" s="6" t="n">
+        <v>46282.65346184</v>
+      </c>
+      <c r="P1004" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1004" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1004" s="7" t="n">
+        <v>23652</v>
+      </c>
+      <c r="S1004" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1004" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1004" s="4"/>
+      <c r="V1004" s="4"/>
+    </row>
+    <row r="1005" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1005" s="8" t="n">
+        <v>1074</v>
+      </c>
+      <c r="B1005" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1005" s="9"/>
+      <c r="D1005" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1005" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1005" s="9" t="s">
+        <v>1538</v>
+      </c>
+      <c r="G1005" s="9" t="s">
+        <v>1997</v>
+      </c>
+      <c r="H1005" s="10" t="n">
+        <v>46282</v>
+      </c>
+      <c r="I1005" s="9" t="s">
+        <v>1032</v>
+      </c>
+      <c r="J1005" s="9" t="s">
+        <v>1032</v>
+      </c>
+      <c r="K1005" s="9" t="s">
+        <v>1033</v>
+      </c>
+      <c r="L1005" s="10"/>
+      <c r="M1005" s="10"/>
+      <c r="N1005" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1005" s="11" t="n">
+        <v>46282.655471875</v>
+      </c>
+      <c r="P1005" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1005" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="R1005" s="12" t="n">
+        <v>2353.9</v>
+      </c>
+      <c r="S1005" s="12" t="n">
+        <v>2353.9</v>
+      </c>
+      <c r="T1005" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1005" s="9"/>
+      <c r="V1005" s="9"/>
+    </row>
+    <row r="1006" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1006" s="3" t="n">
+        <v>1075</v>
+      </c>
+      <c r="B1006" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1006" s="4"/>
+      <c r="D1006" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1006" s="3" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F1006" s="4" t="s">
+        <v>1639</v>
+      </c>
+      <c r="G1006" s="4" t="s">
+        <v>1998</v>
+      </c>
+      <c r="H1006" s="5" t="n">
+        <v>46282</v>
+      </c>
+      <c r="I1006" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1006" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K1006" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="L1006" s="5"/>
+      <c r="M1006" s="5"/>
+      <c r="N1006" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1006" s="6" t="n">
+        <v>46282.659586458</v>
+      </c>
+      <c r="P1006" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1006" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="R1006" s="7" t="n">
+        <v>29027.712</v>
+      </c>
+      <c r="S1006" s="7" t="n">
+        <v>22258.992</v>
+      </c>
+      <c r="T1006" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1006" s="4"/>
+      <c r="V1006" s="4"/>
+    </row>
+    <row r="1007" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1007" s="8" t="n">
+        <v>1076</v>
+      </c>
+      <c r="B1007" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1007" s="9"/>
+      <c r="D1007" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1007" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1007" s="9" t="s">
+        <v>1999</v>
+      </c>
+      <c r="G1007" s="9" t="s">
+        <v>2000</v>
+      </c>
+      <c r="H1007" s="11" t="n">
+        <v>46282.690821759</v>
+      </c>
+      <c r="I1007" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="J1007" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="K1007" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="L1007" s="10"/>
+      <c r="M1007" s="10"/>
+      <c r="N1007" s="9" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O1007" s="11" t="n">
+        <v>46286.373205243</v>
+      </c>
+      <c r="P1007" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1007" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1007" s="12" t="n">
+        <v>89187</v>
+      </c>
+      <c r="S1007" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1007" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1007" s="9"/>
+      <c r="V1007" s="9"/>
+    </row>
+    <row r="1008" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1008" s="3" t="n">
+        <v>1077</v>
+      </c>
+      <c r="B1008" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1008" s="4"/>
+      <c r="D1008" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E1008" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1008" s="4" t="s">
+        <v>2001</v>
+      </c>
+      <c r="G1008" s="4" t="s">
+        <v>2002</v>
+      </c>
+      <c r="H1008" s="6" t="n">
+        <v>46283.62880787</v>
+      </c>
+      <c r="I1008" s="4" t="s">
+        <v>2001</v>
+      </c>
+      <c r="J1008" s="4" t="s">
+        <v>2003</v>
+      </c>
+      <c r="K1008" s="4" t="s">
+        <v>2004</v>
+      </c>
+      <c r="L1008" s="5"/>
+      <c r="M1008" s="5"/>
+      <c r="N1008" s="4" t="s">
+        <v>1813</v>
+      </c>
+      <c r="O1008" s="6" t="n">
+        <v>46286.37336088</v>
+      </c>
+      <c r="P1008" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1008" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1008" s="7" t="n">
+        <v>17281.04</v>
+      </c>
+      <c r="S1008" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1008" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1008" s="4"/>
+      <c r="V1008" s="4"/>
+    </row>
+    <row r="1009" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1009" s="8" t="n">
+        <v>1078</v>
+      </c>
+      <c r="B1009" s="9" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C1009" s="9"/>
+      <c r="D1009" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="E1009" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1009" s="9" t="s">
+        <v>2006</v>
+      </c>
+      <c r="G1009" s="9" t="s">
+        <v>2007</v>
+      </c>
+      <c r="H1009" s="11" t="n">
+        <v>46282.73755787</v>
+      </c>
+      <c r="I1009" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J1009" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="K1009" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="L1009" s="10"/>
+      <c r="M1009" s="10"/>
+      <c r="N1009" s="9" t="s">
+        <v>2008</v>
+      </c>
+      <c r="O1009" s="11" t="n">
+        <v>46286.373498264</v>
+      </c>
+      <c r="P1009" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1009" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1009" s="12" t="n">
+        <v>25800</v>
+      </c>
+      <c r="S1009" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1009" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1009" s="9"/>
+      <c r="V1009" s="9"/>
+    </row>
+    <row r="1010" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A1010" s="13" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B1010" s="14"/>
+      <c r="C1010" s="14"/>
+      <c r="D1010" s="14"/>
+      <c r="E1010" s="14"/>
+      <c r="F1010" s="14"/>
+      <c r="G1010" s="14"/>
+      <c r="H1010" s="14"/>
+      <c r="I1010" s="14"/>
+      <c r="J1010" s="14"/>
+      <c r="K1010" s="14"/>
+      <c r="L1010" s="14"/>
+      <c r="M1010" s="14"/>
+      <c r="N1010" s="14"/>
+      <c r="O1010" s="14"/>
+      <c r="P1010" s="14"/>
+      <c r="Q1010" s="14"/>
+      <c r="R1010" s="15" t="n">
+        <v>60377418.5506</v>
+      </c>
+      <c r="S1010" s="15" t="n">
+        <v>58306509.3306</v>
+      </c>
+      <c r="T1010" s="14"/>
+      <c r="U1010" s="14"/>
+      <c r="V1010" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="2009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="2030">
   <si>
     <t>ID</t>
   </si>
@@ -3870,7 +3870,7 @@
     <t>703</t>
   </si>
   <si>
-    <t>74 %</t>
+    <t>81 %</t>
   </si>
   <si>
     <t>DBV</t>
@@ -4491,9 +4491,6 @@
     <t>881</t>
   </si>
   <si>
-    <t>61 %</t>
-  </si>
-  <si>
     <t>884</t>
   </si>
   <si>
@@ -5058,9 +5055,6 @@
     <t>1029</t>
   </si>
   <si>
-    <t>77 %</t>
-  </si>
-  <si>
     <t>ALTAMED DISTRIBUIDORA</t>
   </si>
   <si>
@@ -5325,9 +5319,6 @@
     <t>32.658.023/0001-84</t>
   </si>
   <si>
-    <t>71 %</t>
-  </si>
-  <si>
     <t>CONQUISTA MEDICAMENTOS</t>
   </si>
   <si>
@@ -5850,15 +5841,9 @@
     <t>1201</t>
   </si>
   <si>
-    <t>25 %</t>
-  </si>
-  <si>
     <t>1202</t>
   </si>
   <si>
-    <t>33 %</t>
-  </si>
-  <si>
     <t>1203</t>
   </si>
   <si>
@@ -5922,6 +5907,9 @@
     <t>1216</t>
   </si>
   <si>
+    <t>60 %</t>
+  </si>
+  <si>
     <t>1217</t>
   </si>
   <si>
@@ -5970,9 +5958,6 @@
     <t>1230</t>
   </si>
   <si>
-    <t>55 %</t>
-  </si>
-  <si>
     <t>1231</t>
   </si>
   <si>
@@ -6030,16 +6015,94 @@
     <t>03.315.618/0001-39</t>
   </si>
   <si>
-    <t>OBRA PRIVADA - INTERNA</t>
-  </si>
-  <si>
-    <t>Orçamento 274</t>
-  </si>
-  <si>
     <t>1243</t>
   </si>
   <si>
-    <t>EM ANDAMENTO</t>
+    <t>1244</t>
+  </si>
+  <si>
+    <t>UNI-RIM</t>
+  </si>
+  <si>
+    <t>1245</t>
+  </si>
+  <si>
+    <t>1246</t>
+  </si>
+  <si>
+    <t>1247</t>
+  </si>
+  <si>
+    <t>1248</t>
+  </si>
+  <si>
+    <t>1249</t>
+  </si>
+  <si>
+    <t>1250</t>
+  </si>
+  <si>
+    <t>1251</t>
+  </si>
+  <si>
+    <t>REC HOSPITALAR</t>
+  </si>
+  <si>
+    <t>1252</t>
+  </si>
+  <si>
+    <t>REC DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>39.500.546/0001-47</t>
+  </si>
+  <si>
+    <t>1253</t>
+  </si>
+  <si>
+    <t>1254</t>
+  </si>
+  <si>
+    <t>1255</t>
+  </si>
+  <si>
+    <t>1256</t>
+  </si>
+  <si>
+    <t>1257</t>
+  </si>
+  <si>
+    <t>50 %</t>
+  </si>
+  <si>
+    <t>1258</t>
+  </si>
+  <si>
+    <t>21 %</t>
+  </si>
+  <si>
+    <t>1259</t>
+  </si>
+  <si>
+    <t>1260</t>
+  </si>
+  <si>
+    <t>1261</t>
+  </si>
+  <si>
+    <t>MEDFASP SERVICOS</t>
+  </si>
+  <si>
+    <t>1262</t>
+  </si>
+  <si>
+    <t>1263</t>
+  </si>
+  <si>
+    <t>42 %</t>
+  </si>
+  <si>
+    <t>1264</t>
   </si>
 </sst>
 </file>
@@ -6233,7 +6296,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V1010"/>
+  <dimension ref="A1:V1031"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -37943,7 +38006,7 @@
         <v>820410</v>
       </c>
       <c r="S546" s="7" t="n">
-        <v>604545</v>
+        <v>666045</v>
       </c>
       <c r="T546" s="4" t="s">
         <v>571</v>
@@ -45505,13 +45568,13 @@
         <v>23</v>
       </c>
       <c r="E677" s="8" t="s">
-        <v>1492</v>
+        <v>24</v>
       </c>
       <c r="F677" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G677" s="9" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H677" s="10" t="n">
         <v>46163</v>
@@ -45528,7 +45591,7 @@
       <c r="L677" s="10"/>
       <c r="M677" s="10"/>
       <c r="N677" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O677" s="11" t="n">
         <v>46163.698247801</v>
@@ -45540,10 +45603,10 @@
         <v>31</v>
       </c>
       <c r="R677" s="12" t="n">
-        <v>226301.7</v>
+        <v>222913.95</v>
       </c>
       <c r="S677" s="12" t="n">
-        <v>138220.2</v>
+        <v>222913.95</v>
       </c>
       <c r="T677" s="9" t="s">
         <v>32</v>
@@ -45566,10 +45629,10 @@
         <v>24</v>
       </c>
       <c r="F678" s="4" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G678" s="4" t="s">
         <v>1494</v>
-      </c>
-      <c r="G678" s="4" t="s">
-        <v>1495</v>
       </c>
       <c r="H678" s="5" t="n">
         <v>46163</v>
@@ -45624,10 +45687,10 @@
         <v>24</v>
       </c>
       <c r="F679" s="9" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G679" s="9" t="s">
         <v>1496</v>
-      </c>
-      <c r="G679" s="9" t="s">
-        <v>1497</v>
       </c>
       <c r="H679" s="10" t="n">
         <v>46164</v>
@@ -45682,10 +45745,10 @@
         <v>24</v>
       </c>
       <c r="F680" s="4" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G680" s="4" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H680" s="5" t="n">
         <v>46164</v>
@@ -45743,7 +45806,7 @@
         <v>521</v>
       </c>
       <c r="G681" s="9" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H681" s="10" t="n">
         <v>46164</v>
@@ -45801,7 +45864,7 @@
         <v>619</v>
       </c>
       <c r="G682" s="4" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H682" s="5" t="n">
         <v>46164</v>
@@ -45856,10 +45919,10 @@
         <v>24</v>
       </c>
       <c r="F683" s="9" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G683" s="9" t="s">
         <v>1501</v>
-      </c>
-      <c r="G683" s="9" t="s">
-        <v>1502</v>
       </c>
       <c r="H683" s="10" t="n">
         <v>46164</v>
@@ -45917,7 +45980,7 @@
         <v>276</v>
       </c>
       <c r="G684" s="4" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H684" s="5" t="n">
         <v>46164</v>
@@ -45975,7 +46038,7 @@
         <v>1056</v>
       </c>
       <c r="G685" s="9" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H685" s="10" t="n">
         <v>46164</v>
@@ -46030,22 +46093,22 @@
         <v>24</v>
       </c>
       <c r="F686" s="4" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G686" s="4" t="s">
         <v>1505</v>
-      </c>
-      <c r="G686" s="4" t="s">
-        <v>1506</v>
       </c>
       <c r="H686" s="5" t="n">
         <v>46164</v>
       </c>
       <c r="I686" s="4" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="J686" s="4" t="s">
+        <v>1506</v>
+      </c>
+      <c r="K686" s="4" t="s">
         <v>1507</v>
-      </c>
-      <c r="K686" s="4" t="s">
-        <v>1508</v>
       </c>
       <c r="L686" s="5"/>
       <c r="M686" s="5"/>
@@ -46091,7 +46154,7 @@
         <v>124</v>
       </c>
       <c r="G687" s="9" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="H687" s="10" t="n">
         <v>46164</v>
@@ -46149,7 +46212,7 @@
         <v>351</v>
       </c>
       <c r="G688" s="4" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H688" s="5" t="n">
         <v>46164</v>
@@ -46204,10 +46267,10 @@
         <v>24</v>
       </c>
       <c r="F689" s="9" t="s">
+        <v>1510</v>
+      </c>
+      <c r="G689" s="9" t="s">
         <v>1511</v>
-      </c>
-      <c r="G689" s="9" t="s">
-        <v>1512</v>
       </c>
       <c r="H689" s="10" t="n">
         <v>46167</v>
@@ -46265,7 +46328,7 @@
         <v>1473</v>
       </c>
       <c r="G690" s="4" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H690" s="5" t="n">
         <v>46167</v>
@@ -46323,7 +46386,7 @@
         <v>581</v>
       </c>
       <c r="G691" s="9" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H691" s="10" t="n">
         <v>46167</v>
@@ -46381,7 +46444,7 @@
         <v>1016</v>
       </c>
       <c r="G692" s="4" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H692" s="5" t="n">
         <v>46167</v>
@@ -46436,10 +46499,10 @@
         <v>24</v>
       </c>
       <c r="F693" s="9" t="s">
+        <v>1515</v>
+      </c>
+      <c r="G693" s="9" t="s">
         <v>1516</v>
-      </c>
-      <c r="G693" s="9" t="s">
-        <v>1517</v>
       </c>
       <c r="H693" s="10" t="n">
         <v>46167</v>
@@ -46497,7 +46560,7 @@
         <v>75</v>
       </c>
       <c r="G694" s="4" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H694" s="5" t="n">
         <v>46167</v>
@@ -46555,7 +46618,7 @@
         <v>490</v>
       </c>
       <c r="G695" s="9" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H695" s="10" t="n">
         <v>46168</v>
@@ -46610,10 +46673,10 @@
         <v>24</v>
       </c>
       <c r="F696" s="4" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G696" s="4" t="s">
         <v>1520</v>
-      </c>
-      <c r="G696" s="4" t="s">
-        <v>1521</v>
       </c>
       <c r="H696" s="5" t="n">
         <v>46168</v>
@@ -46668,10 +46731,10 @@
         <v>24</v>
       </c>
       <c r="F697" s="9" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="G697" s="9" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H697" s="10" t="n">
         <v>46168</v>
@@ -46729,7 +46792,7 @@
         <v>502</v>
       </c>
       <c r="G698" s="4" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H698" s="5" t="n">
         <v>46169</v>
@@ -46787,7 +46850,7 @@
         <v>75</v>
       </c>
       <c r="G699" s="9" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H699" s="10" t="n">
         <v>46168</v>
@@ -46845,7 +46908,7 @@
         <v>75</v>
       </c>
       <c r="G700" s="4" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H700" s="5" t="n">
         <v>46168</v>
@@ -46900,10 +46963,10 @@
         <v>24</v>
       </c>
       <c r="F701" s="9" t="s">
+        <v>1525</v>
+      </c>
+      <c r="G701" s="9" t="s">
         <v>1526</v>
-      </c>
-      <c r="G701" s="9" t="s">
-        <v>1527</v>
       </c>
       <c r="H701" s="10" t="n">
         <v>46167</v>
@@ -46961,7 +47024,7 @@
         <v>988</v>
       </c>
       <c r="G702" s="4" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H702" s="5" t="n">
         <v>46169</v>
@@ -47019,7 +47082,7 @@
         <v>505</v>
       </c>
       <c r="G703" s="9" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H703" s="10" t="n">
         <v>46168</v>
@@ -47077,7 +47140,7 @@
         <v>592</v>
       </c>
       <c r="G704" s="4" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H704" s="5" t="n">
         <v>46169</v>
@@ -47135,7 +47198,7 @@
         <v>347</v>
       </c>
       <c r="G705" s="9" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H705" s="10" t="n">
         <v>46168</v>
@@ -47193,7 +47256,7 @@
         <v>671</v>
       </c>
       <c r="G706" s="4" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H706" s="5" t="n">
         <v>46168</v>
@@ -47251,7 +47314,7 @@
         <v>203</v>
       </c>
       <c r="G707" s="9" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H707" s="10" t="n">
         <v>46168</v>
@@ -47309,7 +47372,7 @@
         <v>262</v>
       </c>
       <c r="G708" s="4" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H708" s="5" t="n">
         <v>46168</v>
@@ -47367,7 +47430,7 @@
         <v>152</v>
       </c>
       <c r="G709" s="9" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H709" s="10" t="n">
         <v>46167</v>
@@ -47425,7 +47488,7 @@
         <v>58</v>
       </c>
       <c r="G710" s="4" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H710" s="5" t="n">
         <v>46167</v>
@@ -47483,7 +47546,7 @@
         <v>310</v>
       </c>
       <c r="G711" s="9" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H711" s="10" t="n">
         <v>46167</v>
@@ -47538,10 +47601,10 @@
         <v>24</v>
       </c>
       <c r="F712" s="4" t="s">
+        <v>1537</v>
+      </c>
+      <c r="G712" s="4" t="s">
         <v>1538</v>
-      </c>
-      <c r="G712" s="4" t="s">
-        <v>1539</v>
       </c>
       <c r="H712" s="5" t="n">
         <v>46167</v>
@@ -47599,7 +47662,7 @@
         <v>328</v>
       </c>
       <c r="G713" s="9" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H713" s="10" t="n">
         <v>46167</v>
@@ -47654,10 +47717,10 @@
         <v>24</v>
       </c>
       <c r="F714" s="4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="G714" s="4" t="s">
         <v>1541</v>
-      </c>
-      <c r="G714" s="4" t="s">
-        <v>1542</v>
       </c>
       <c r="H714" s="5" t="n">
         <v>46168</v>
@@ -47712,10 +47775,10 @@
         <v>24</v>
       </c>
       <c r="F715" s="9" t="s">
+        <v>1542</v>
+      </c>
+      <c r="G715" s="9" t="s">
         <v>1543</v>
-      </c>
-      <c r="G715" s="9" t="s">
-        <v>1544</v>
       </c>
       <c r="H715" s="10" t="n">
         <v>46169</v>
@@ -47773,7 +47836,7 @@
         <v>675</v>
       </c>
       <c r="G716" s="4" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H716" s="5" t="n">
         <v>46170</v>
@@ -47828,10 +47891,10 @@
         <v>24</v>
       </c>
       <c r="F717" s="9" t="s">
+        <v>1545</v>
+      </c>
+      <c r="G717" s="9" t="s">
         <v>1546</v>
-      </c>
-      <c r="G717" s="9" t="s">
-        <v>1547</v>
       </c>
       <c r="H717" s="10" t="n">
         <v>46169</v>
@@ -47889,7 +47952,7 @@
         <v>909</v>
       </c>
       <c r="G718" s="4" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H718" s="5" t="n">
         <v>46170</v>
@@ -47944,22 +48007,22 @@
         <v>24</v>
       </c>
       <c r="F719" s="9" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G719" s="9" t="s">
         <v>1549</v>
-      </c>
-      <c r="G719" s="9" t="s">
-        <v>1550</v>
       </c>
       <c r="H719" s="10" t="n">
         <v>46174</v>
       </c>
       <c r="I719" s="9" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="J719" s="9" t="s">
+        <v>1550</v>
+      </c>
+      <c r="K719" s="9" t="s">
         <v>1551</v>
-      </c>
-      <c r="K719" s="9" t="s">
-        <v>1552</v>
       </c>
       <c r="L719" s="10"/>
       <c r="M719" s="10"/>
@@ -48005,7 +48068,7 @@
         <v>969</v>
       </c>
       <c r="G720" s="4" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H720" s="5" t="n">
         <v>46170</v>
@@ -48063,7 +48126,7 @@
         <v>1459</v>
       </c>
       <c r="G721" s="9" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H721" s="10" t="n">
         <v>46169</v>
@@ -48121,7 +48184,7 @@
         <v>820</v>
       </c>
       <c r="G722" s="4" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H722" s="5" t="n">
         <v>46169</v>
@@ -48179,7 +48242,7 @@
         <v>1012</v>
       </c>
       <c r="G723" s="9" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H723" s="10" t="n">
         <v>46169</v>
@@ -48234,22 +48297,22 @@
         <v>24</v>
       </c>
       <c r="F724" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G724" s="4" t="s">
         <v>1557</v>
-      </c>
-      <c r="G724" s="4" t="s">
-        <v>1558</v>
       </c>
       <c r="H724" s="5" t="n">
         <v>46169</v>
       </c>
       <c r="I724" s="4" t="s">
+        <v>1558</v>
+      </c>
+      <c r="J724" s="4" t="s">
         <v>1559</v>
       </c>
-      <c r="J724" s="4" t="s">
+      <c r="K724" s="4" t="s">
         <v>1560</v>
-      </c>
-      <c r="K724" s="4" t="s">
-        <v>1561</v>
       </c>
       <c r="L724" s="5"/>
       <c r="M724" s="5"/>
@@ -48295,7 +48358,7 @@
         <v>1102</v>
       </c>
       <c r="G725" s="9" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H725" s="10" t="n">
         <v>46170</v>
@@ -48353,7 +48416,7 @@
         <v>592</v>
       </c>
       <c r="G726" s="4" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H726" s="5" t="n">
         <v>46170</v>
@@ -48411,7 +48474,7 @@
         <v>461</v>
       </c>
       <c r="G727" s="9" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H727" s="10" t="n">
         <v>46170</v>
@@ -48469,7 +48532,7 @@
         <v>1292</v>
       </c>
       <c r="G728" s="4" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H728" s="5" t="n">
         <v>46171</v>
@@ -48527,7 +48590,7 @@
         <v>1459</v>
       </c>
       <c r="G729" s="9" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H729" s="10" t="n">
         <v>46175</v>
@@ -48585,7 +48648,7 @@
         <v>1062</v>
       </c>
       <c r="G730" s="4" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H730" s="5" t="n">
         <v>46175</v>
@@ -48643,7 +48706,7 @@
         <v>696</v>
       </c>
       <c r="G731" s="9" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H731" s="10" t="n">
         <v>46175</v>
@@ -48698,10 +48761,10 @@
         <v>24</v>
       </c>
       <c r="F732" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G732" s="4" t="s">
         <v>1569</v>
-      </c>
-      <c r="G732" s="4" t="s">
-        <v>1570</v>
       </c>
       <c r="H732" s="5" t="n">
         <v>46176</v>
@@ -48759,7 +48822,7 @@
         <v>103</v>
       </c>
       <c r="G733" s="9" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H733" s="10" t="n">
         <v>46176</v>
@@ -48814,10 +48877,10 @@
         <v>24</v>
       </c>
       <c r="F734" s="4" t="s">
+        <v>1571</v>
+      </c>
+      <c r="G734" s="4" t="s">
         <v>1572</v>
-      </c>
-      <c r="G734" s="4" t="s">
-        <v>1573</v>
       </c>
       <c r="H734" s="5" t="n">
         <v>46176</v>
@@ -48872,10 +48935,10 @@
         <v>24</v>
       </c>
       <c r="F735" s="9" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="G735" s="9" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H735" s="10" t="n">
         <v>46176</v>
@@ -48933,7 +48996,7 @@
         <v>143</v>
       </c>
       <c r="G736" s="4" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H736" s="5" t="n">
         <v>46181</v>
@@ -48991,7 +49054,7 @@
         <v>447</v>
       </c>
       <c r="G737" s="9" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H737" s="10" t="n">
         <v>46182</v>
@@ -49049,7 +49112,7 @@
         <v>143</v>
       </c>
       <c r="G738" s="4" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H738" s="5" t="n">
         <v>46182</v>
@@ -49104,10 +49167,10 @@
         <v>24</v>
       </c>
       <c r="F739" s="9" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G739" s="9" t="s">
         <v>1578</v>
-      </c>
-      <c r="G739" s="9" t="s">
-        <v>1579</v>
       </c>
       <c r="H739" s="10" t="n">
         <v>46182</v>
@@ -49165,7 +49228,7 @@
         <v>1421</v>
       </c>
       <c r="G740" s="4" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H740" s="5" t="n">
         <v>46181</v>
@@ -49220,10 +49283,10 @@
         <v>24</v>
       </c>
       <c r="F741" s="9" t="s">
+        <v>1580</v>
+      </c>
+      <c r="G741" s="9" t="s">
         <v>1581</v>
-      </c>
-      <c r="G741" s="9" t="s">
-        <v>1582</v>
       </c>
       <c r="H741" s="10" t="n">
         <v>46183</v>
@@ -49278,10 +49341,10 @@
         <v>24</v>
       </c>
       <c r="F742" s="4" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G742" s="4" t="s">
         <v>1583</v>
-      </c>
-      <c r="G742" s="4" t="s">
-        <v>1584</v>
       </c>
       <c r="H742" s="5" t="n">
         <v>46184</v>
@@ -49341,7 +49404,7 @@
         <v>1488</v>
       </c>
       <c r="G743" s="9" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H743" s="10" t="n">
         <v>46183</v>
@@ -49396,22 +49459,22 @@
         <v>24</v>
       </c>
       <c r="F744" s="4" t="s">
+        <v>1585</v>
+      </c>
+      <c r="G744" s="4" t="s">
         <v>1586</v>
-      </c>
-      <c r="G744" s="4" t="s">
-        <v>1587</v>
       </c>
       <c r="H744" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="I744" s="4" t="s">
+        <v>1587</v>
+      </c>
+      <c r="J744" s="4" t="s">
         <v>1588</v>
       </c>
-      <c r="J744" s="4" t="s">
+      <c r="K744" s="4" t="s">
         <v>1589</v>
-      </c>
-      <c r="K744" s="4" t="s">
-        <v>1590</v>
       </c>
       <c r="L744" s="5"/>
       <c r="M744" s="5"/>
@@ -49457,7 +49520,7 @@
         <v>272</v>
       </c>
       <c r="G745" s="9" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H745" s="10" t="n">
         <v>46184</v>
@@ -49515,7 +49578,7 @@
         <v>519</v>
       </c>
       <c r="G746" s="4" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H746" s="5" t="n">
         <v>46184</v>
@@ -49570,10 +49633,10 @@
         <v>24</v>
       </c>
       <c r="F747" s="9" t="s">
+        <v>1592</v>
+      </c>
+      <c r="G747" s="9" t="s">
         <v>1593</v>
-      </c>
-      <c r="G747" s="9" t="s">
-        <v>1594</v>
       </c>
       <c r="H747" s="10" t="n">
         <v>46185</v>
@@ -49628,10 +49691,10 @@
         <v>24</v>
       </c>
       <c r="F748" s="4" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G748" s="4" t="s">
         <v>1595</v>
-      </c>
-      <c r="G748" s="4" t="s">
-        <v>1596</v>
       </c>
       <c r="H748" s="5" t="n">
         <v>46185</v>
@@ -49689,7 +49752,7 @@
         <v>704</v>
       </c>
       <c r="G749" s="9" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H749" s="10" t="n">
         <v>46188</v>
@@ -49744,10 +49807,10 @@
         <v>24</v>
       </c>
       <c r="F750" s="4" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="G750" s="4" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H750" s="5" t="n">
         <v>46188</v>
@@ -49805,7 +49868,7 @@
         <v>228</v>
       </c>
       <c r="G751" s="9" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H751" s="10" t="n">
         <v>46188</v>
@@ -49863,7 +49926,7 @@
         <v>228</v>
       </c>
       <c r="G752" s="4" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H752" s="5" t="n">
         <v>46188</v>
@@ -49921,7 +49984,7 @@
         <v>589</v>
       </c>
       <c r="G753" s="9" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H753" s="10" t="n">
         <v>46189</v>
@@ -49976,22 +50039,22 @@
         <v>24</v>
       </c>
       <c r="F754" s="4" t="s">
+        <v>1601</v>
+      </c>
+      <c r="G754" s="4" t="s">
         <v>1602</v>
-      </c>
-      <c r="G754" s="4" t="s">
-        <v>1603</v>
       </c>
       <c r="H754" s="5" t="n">
         <v>46188</v>
       </c>
       <c r="I754" s="4" t="s">
+        <v>1603</v>
+      </c>
+      <c r="J754" s="4" t="s">
         <v>1604</v>
       </c>
-      <c r="J754" s="4" t="s">
+      <c r="K754" s="4" t="s">
         <v>1605</v>
-      </c>
-      <c r="K754" s="4" t="s">
-        <v>1606</v>
       </c>
       <c r="L754" s="5"/>
       <c r="M754" s="5"/>
@@ -50037,7 +50100,7 @@
         <v>1298</v>
       </c>
       <c r="G755" s="9" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H755" s="10" t="n">
         <v>46188</v>
@@ -50095,7 +50158,7 @@
         <v>152</v>
       </c>
       <c r="G756" s="4" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H756" s="5" t="n">
         <v>46189</v>
@@ -50153,7 +50216,7 @@
         <v>1296</v>
       </c>
       <c r="G757" s="9" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H757" s="10" t="n">
         <v>46189</v>
@@ -50211,7 +50274,7 @@
         <v>1296</v>
       </c>
       <c r="G758" s="4" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H758" s="5" t="n">
         <v>46189</v>
@@ -50269,7 +50332,7 @@
         <v>402</v>
       </c>
       <c r="G759" s="9" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H759" s="10" t="n">
         <v>46190</v>
@@ -50324,22 +50387,22 @@
         <v>24</v>
       </c>
       <c r="F760" s="4" t="s">
+        <v>1611</v>
+      </c>
+      <c r="G760" s="4" t="s">
         <v>1612</v>
-      </c>
-      <c r="G760" s="4" t="s">
-        <v>1613</v>
       </c>
       <c r="H760" s="5" t="n">
         <v>46189</v>
       </c>
       <c r="I760" s="4" t="s">
+        <v>1613</v>
+      </c>
+      <c r="J760" s="4" t="s">
         <v>1614</v>
       </c>
-      <c r="J760" s="4" t="s">
+      <c r="K760" s="4" t="s">
         <v>1615</v>
-      </c>
-      <c r="K760" s="4" t="s">
-        <v>1616</v>
       </c>
       <c r="L760" s="5"/>
       <c r="M760" s="5"/>
@@ -50353,7 +50416,7 @@
         <v>1455</v>
       </c>
       <c r="Q760" s="4" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="R760" s="7" t="n">
         <v>2230.4</v>
@@ -50385,7 +50448,7 @@
         <v>157</v>
       </c>
       <c r="G761" s="9" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H761" s="10" t="n">
         <v>46189</v>
@@ -50440,22 +50503,22 @@
         <v>24</v>
       </c>
       <c r="F762" s="4" t="s">
+        <v>1618</v>
+      </c>
+      <c r="G762" s="4" t="s">
         <v>1619</v>
-      </c>
-      <c r="G762" s="4" t="s">
-        <v>1620</v>
       </c>
       <c r="H762" s="5" t="n">
         <v>46191</v>
       </c>
       <c r="I762" s="4" t="s">
+        <v>1620</v>
+      </c>
+      <c r="J762" s="4" t="s">
         <v>1621</v>
       </c>
-      <c r="J762" s="4" t="s">
+      <c r="K762" s="4" t="s">
         <v>1622</v>
-      </c>
-      <c r="K762" s="4" t="s">
-        <v>1623</v>
       </c>
       <c r="L762" s="5"/>
       <c r="M762" s="5"/>
@@ -50501,7 +50564,7 @@
         <v>892</v>
       </c>
       <c r="G763" s="9" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H763" s="10" t="n">
         <v>46191</v>
@@ -50559,7 +50622,7 @@
         <v>502</v>
       </c>
       <c r="G764" s="4" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H764" s="5" t="n">
         <v>46190</v>
@@ -50617,7 +50680,7 @@
         <v>322</v>
       </c>
       <c r="G765" s="9" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H765" s="10" t="n">
         <v>46190</v>
@@ -50675,7 +50738,7 @@
         <v>1488</v>
       </c>
       <c r="G766" s="4" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H766" s="5" t="n">
         <v>46192</v>
@@ -50733,7 +50796,7 @@
         <v>249</v>
       </c>
       <c r="G767" s="9" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H767" s="10" t="n">
         <v>46191</v>
@@ -50788,10 +50851,10 @@
         <v>24</v>
       </c>
       <c r="F768" s="4" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G768" s="4" t="s">
         <v>1629</v>
-      </c>
-      <c r="G768" s="4" t="s">
-        <v>1630</v>
       </c>
       <c r="H768" s="5" t="n">
         <v>46191</v>
@@ -50846,10 +50909,10 @@
         <v>24</v>
       </c>
       <c r="F769" s="9" t="s">
+        <v>1630</v>
+      </c>
+      <c r="G769" s="9" t="s">
         <v>1631</v>
-      </c>
-      <c r="G769" s="9" t="s">
-        <v>1632</v>
       </c>
       <c r="H769" s="11" t="n">
         <v>46196.641111111</v>
@@ -50872,7 +50935,7 @@
         <v>46198.434918947</v>
       </c>
       <c r="P769" s="9" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="Q769" s="9" t="s">
         <v>74</v>
@@ -50907,7 +50970,7 @@
         <v>904</v>
       </c>
       <c r="G770" s="4" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H770" s="5" t="n">
         <v>46195</v>
@@ -50965,7 +51028,7 @@
         <v>888</v>
       </c>
       <c r="G771" s="9" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H771" s="10" t="n">
         <v>46192</v>
@@ -51017,13 +51080,13 @@
         <v>23</v>
       </c>
       <c r="E772" s="3" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="F772" s="4" t="s">
         <v>997</v>
       </c>
       <c r="G772" s="4" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H772" s="5" t="n">
         <v>46198</v>
@@ -51081,7 +51144,7 @@
         <v>276</v>
       </c>
       <c r="G773" s="9" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H773" s="10" t="n">
         <v>46198</v>
@@ -51136,10 +51199,10 @@
         <v>24</v>
       </c>
       <c r="F774" s="4" t="s">
+        <v>1638</v>
+      </c>
+      <c r="G774" s="4" t="s">
         <v>1639</v>
-      </c>
-      <c r="G774" s="4" t="s">
-        <v>1640</v>
       </c>
       <c r="H774" s="5" t="n">
         <v>46198</v>
@@ -51197,7 +51260,7 @@
         <v>1271</v>
       </c>
       <c r="G775" s="9" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H775" s="10" t="n">
         <v>46196</v>
@@ -51255,7 +51318,7 @@
         <v>1264</v>
       </c>
       <c r="G776" s="4" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H776" s="5" t="n">
         <v>46195</v>
@@ -51313,7 +51376,7 @@
         <v>496</v>
       </c>
       <c r="G777" s="9" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H777" s="10" t="n">
         <v>46198</v>
@@ -51371,7 +51434,7 @@
         <v>1075</v>
       </c>
       <c r="G778" s="4" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H778" s="5" t="n">
         <v>46198</v>
@@ -51429,7 +51492,7 @@
         <v>945</v>
       </c>
       <c r="G779" s="9" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H779" s="10" t="n">
         <v>46198</v>
@@ -51487,7 +51550,7 @@
         <v>1459</v>
       </c>
       <c r="G780" s="4" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H780" s="5" t="n">
         <v>46198</v>
@@ -51542,10 +51605,10 @@
         <v>24</v>
       </c>
       <c r="F781" s="9" t="s">
+        <v>1646</v>
+      </c>
+      <c r="G781" s="9" t="s">
         <v>1647</v>
-      </c>
-      <c r="G781" s="9" t="s">
-        <v>1648</v>
       </c>
       <c r="H781" s="10" t="n">
         <v>46198</v>
@@ -51603,7 +51666,7 @@
         <v>191</v>
       </c>
       <c r="G782" s="4" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H782" s="5" t="n">
         <v>46198</v>
@@ -51658,10 +51721,10 @@
         <v>24</v>
       </c>
       <c r="F783" s="9" t="s">
+        <v>1649</v>
+      </c>
+      <c r="G783" s="9" t="s">
         <v>1650</v>
-      </c>
-      <c r="G783" s="9" t="s">
-        <v>1651</v>
       </c>
       <c r="H783" s="10" t="n">
         <v>46197</v>
@@ -51719,7 +51782,7 @@
         <v>124</v>
       </c>
       <c r="G784" s="4" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H784" s="5" t="n">
         <v>46198</v>
@@ -51777,7 +51840,7 @@
         <v>75</v>
       </c>
       <c r="G785" s="9" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H785" s="10" t="n">
         <v>46199</v>
@@ -51835,7 +51898,7 @@
         <v>332</v>
       </c>
       <c r="G786" s="4" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H786" s="5" t="n">
         <v>46199</v>
@@ -51893,7 +51956,7 @@
         <v>1473</v>
       </c>
       <c r="G787" s="9" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H787" s="11" t="n">
         <v>46202.697662037</v>
@@ -51951,7 +52014,7 @@
         <v>249</v>
       </c>
       <c r="G788" s="4" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H788" s="6" t="n">
         <v>46203.350740741</v>
@@ -52009,7 +52072,7 @@
         <v>1102</v>
       </c>
       <c r="G789" s="9" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H789" s="11" t="n">
         <v>46203.360023148</v>
@@ -52067,7 +52130,7 @@
         <v>295</v>
       </c>
       <c r="G790" s="4" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H790" s="6" t="n">
         <v>46199.437291667</v>
@@ -52125,7 +52188,7 @@
         <v>262</v>
       </c>
       <c r="G791" s="9" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H791" s="11" t="n">
         <v>46199.61</v>
@@ -52183,7 +52246,7 @@
         <v>58</v>
       </c>
       <c r="G792" s="4" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H792" s="5" t="n">
         <v>46203</v>
@@ -52241,7 +52304,7 @@
         <v>1099</v>
       </c>
       <c r="G793" s="9" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H793" s="10" t="n">
         <v>46199</v>
@@ -52296,10 +52359,10 @@
         <v>24</v>
       </c>
       <c r="F794" s="4" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="G794" s="4" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H794" s="5" t="n">
         <v>46203</v>
@@ -52354,10 +52417,10 @@
         <v>24</v>
       </c>
       <c r="F795" s="9" t="s">
+        <v>1662</v>
+      </c>
+      <c r="G795" s="9" t="s">
         <v>1663</v>
-      </c>
-      <c r="G795" s="9" t="s">
-        <v>1664</v>
       </c>
       <c r="H795" s="11" t="n">
         <v>46203.499918981</v>
@@ -52415,7 +52478,7 @@
         <v>357</v>
       </c>
       <c r="G796" s="4" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H796" s="5" t="n">
         <v>46203</v>
@@ -52473,7 +52536,7 @@
         <v>955</v>
       </c>
       <c r="G797" s="9" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H797" s="11" t="n">
         <v>46204.462268519</v>
@@ -52531,7 +52594,7 @@
         <v>1298</v>
       </c>
       <c r="G798" s="4" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H798" s="5" t="n">
         <v>46205</v>
@@ -52586,22 +52649,22 @@
         <v>24</v>
       </c>
       <c r="F799" s="9" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="G799" s="9" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H799" s="10" t="n">
         <v>46205</v>
       </c>
       <c r="I799" s="9" t="s">
+        <v>1613</v>
+      </c>
+      <c r="J799" s="9" t="s">
         <v>1614</v>
       </c>
-      <c r="J799" s="9" t="s">
+      <c r="K799" s="9" t="s">
         <v>1615</v>
-      </c>
-      <c r="K799" s="9" t="s">
-        <v>1616</v>
       </c>
       <c r="L799" s="10"/>
       <c r="M799" s="10"/>
@@ -52615,7 +52678,7 @@
         <v>1455</v>
       </c>
       <c r="Q799" s="9" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="R799" s="12" t="n">
         <v>5000</v>
@@ -52644,22 +52707,22 @@
         <v>24</v>
       </c>
       <c r="F800" s="4" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G800" s="4" t="s">
         <v>1669</v>
-      </c>
-      <c r="G800" s="4" t="s">
-        <v>1670</v>
       </c>
       <c r="H800" s="6" t="n">
         <v>46205.688020833</v>
       </c>
       <c r="I800" s="4" t="s">
+        <v>1670</v>
+      </c>
+      <c r="J800" s="4" t="s">
+        <v>1670</v>
+      </c>
+      <c r="K800" s="4" t="s">
         <v>1671</v>
-      </c>
-      <c r="J800" s="4" t="s">
-        <v>1671</v>
-      </c>
-      <c r="K800" s="4" t="s">
-        <v>1672</v>
       </c>
       <c r="L800" s="5"/>
       <c r="M800" s="5"/>
@@ -52705,7 +52768,7 @@
         <v>1427</v>
       </c>
       <c r="G801" s="9" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H801" s="11" t="n">
         <v>46205.676435185</v>
@@ -52760,10 +52823,10 @@
         <v>24</v>
       </c>
       <c r="F802" s="4" t="s">
+        <v>1673</v>
+      </c>
+      <c r="G802" s="4" t="s">
         <v>1674</v>
-      </c>
-      <c r="G802" s="4" t="s">
-        <v>1675</v>
       </c>
       <c r="H802" s="5" t="n">
         <v>46206</v>
@@ -52818,10 +52881,10 @@
         <v>24</v>
       </c>
       <c r="F803" s="9" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="G803" s="9" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H803" s="10" t="n">
         <v>46206</v>
@@ -52879,7 +52942,7 @@
         <v>366</v>
       </c>
       <c r="G804" s="4" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H804" s="5" t="n">
         <v>46209</v>
@@ -52937,7 +53000,7 @@
         <v>829</v>
       </c>
       <c r="G805" s="9" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H805" s="11" t="n">
         <v>46210.393460648</v>
@@ -52992,10 +53055,10 @@
         <v>24</v>
       </c>
       <c r="F806" s="4" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G806" s="4" t="s">
         <v>1679</v>
-      </c>
-      <c r="G806" s="4" t="s">
-        <v>1680</v>
       </c>
       <c r="H806" s="5" t="n">
         <v>46210</v>
@@ -53047,30 +53110,30 @@
         <v>23</v>
       </c>
       <c r="E807" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F807" s="9" t="s">
+        <v>1680</v>
+      </c>
+      <c r="G807" s="9" t="s">
         <v>1681</v>
-      </c>
-      <c r="F807" s="9" t="s">
-        <v>1682</v>
-      </c>
-      <c r="G807" s="9" t="s">
-        <v>1683</v>
       </c>
       <c r="H807" s="10" t="n">
         <v>46209</v>
       </c>
       <c r="I807" s="9" t="s">
+        <v>1682</v>
+      </c>
+      <c r="J807" s="9" t="s">
+        <v>1683</v>
+      </c>
+      <c r="K807" s="9" t="s">
         <v>1684</v>
-      </c>
-      <c r="J807" s="9" t="s">
-        <v>1685</v>
-      </c>
-      <c r="K807" s="9" t="s">
-        <v>1686</v>
       </c>
       <c r="L807" s="10"/>
       <c r="M807" s="10"/>
       <c r="N807" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O807" s="11" t="n">
         <v>46212.601001123</v>
@@ -53079,16 +53142,16 @@
         <v>1455</v>
       </c>
       <c r="Q807" s="9" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="R807" s="12" t="n">
         <v>57832.4</v>
       </c>
       <c r="S807" s="12" t="n">
-        <v>44782.4</v>
+        <v>57832.4</v>
       </c>
       <c r="T807" s="9" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="U807" s="9"/>
       <c r="V807" s="9"/>
@@ -53108,10 +53171,10 @@
         <v>24</v>
       </c>
       <c r="F808" s="4" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="G808" s="4" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="H808" s="5" t="n">
         <v>46212</v>
@@ -53166,22 +53229,22 @@
         <v>24</v>
       </c>
       <c r="F809" s="9" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="G809" s="9" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="H809" s="10" t="n">
         <v>46209</v>
       </c>
       <c r="I809" s="9" t="s">
+        <v>1688</v>
+      </c>
+      <c r="J809" s="9" t="s">
         <v>1690</v>
       </c>
-      <c r="J809" s="9" t="s">
-        <v>1692</v>
-      </c>
       <c r="K809" s="9" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="L809" s="10"/>
       <c r="M809" s="10"/>
@@ -53195,7 +53258,7 @@
         <v>1455</v>
       </c>
       <c r="Q809" s="9" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="R809" s="12" t="n">
         <v>12246.14</v>
@@ -53204,7 +53267,7 @@
         <v>12246.14</v>
       </c>
       <c r="T809" s="9" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="U809" s="9"/>
       <c r="V809" s="9"/>
@@ -53224,22 +53287,22 @@
         <v>24</v>
       </c>
       <c r="F810" s="4" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="G810" s="4" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="H810" s="5" t="n">
         <v>46209</v>
       </c>
       <c r="I810" s="4" t="s">
+        <v>1694</v>
+      </c>
+      <c r="J810" s="4" t="s">
+        <v>1695</v>
+      </c>
+      <c r="K810" s="4" t="s">
         <v>1696</v>
-      </c>
-      <c r="J810" s="4" t="s">
-        <v>1697</v>
-      </c>
-      <c r="K810" s="4" t="s">
-        <v>1698</v>
       </c>
       <c r="L810" s="5"/>
       <c r="M810" s="5"/>
@@ -53253,7 +53316,7 @@
         <v>1455</v>
       </c>
       <c r="Q810" s="4" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="R810" s="7" t="n">
         <v>12246.14</v>
@@ -53262,7 +53325,7 @@
         <v>12246.14</v>
       </c>
       <c r="T810" s="4" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="U810" s="4"/>
       <c r="V810" s="4"/>
@@ -53282,22 +53345,22 @@
         <v>24</v>
       </c>
       <c r="F811" s="9" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="G811" s="9" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="H811" s="10" t="n">
         <v>46212</v>
       </c>
       <c r="I811" s="9" t="s">
+        <v>1699</v>
+      </c>
+      <c r="J811" s="9" t="s">
+        <v>1700</v>
+      </c>
+      <c r="K811" s="9" t="s">
         <v>1701</v>
-      </c>
-      <c r="J811" s="9" t="s">
-        <v>1702</v>
-      </c>
-      <c r="K811" s="9" t="s">
-        <v>1703</v>
       </c>
       <c r="L811" s="10"/>
       <c r="M811" s="10"/>
@@ -53311,7 +53374,7 @@
         <v>1455</v>
       </c>
       <c r="Q811" s="9" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="R811" s="12" t="n">
         <v>46556.88</v>
@@ -53320,7 +53383,7 @@
         <v>46556.88</v>
       </c>
       <c r="T811" s="9" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="U811" s="9"/>
       <c r="V811" s="9"/>
@@ -53340,10 +53403,10 @@
         <v>24</v>
       </c>
       <c r="F812" s="4" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="G812" s="4" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="H812" s="6" t="n">
         <v>46212.609872685</v>
@@ -53398,10 +53461,10 @@
         <v>24</v>
       </c>
       <c r="F813" s="9" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="G813" s="9" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="H813" s="11" t="n">
         <v>46212.603854167</v>
@@ -53459,7 +53522,7 @@
         <v>328</v>
       </c>
       <c r="G814" s="4" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="H814" s="6" t="n">
         <v>46212.706458333</v>
@@ -53517,7 +53580,7 @@
         <v>75</v>
       </c>
       <c r="G815" s="9" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="H815" s="11" t="n">
         <v>46216.38931713</v>
@@ -53575,7 +53638,7 @@
         <v>389</v>
       </c>
       <c r="G816" s="4" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="H816" s="6" t="n">
         <v>46213.494444444</v>
@@ -53633,7 +53696,7 @@
         <v>249</v>
       </c>
       <c r="G817" s="9" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="H817" s="11" t="n">
         <v>46216.315104167</v>
@@ -53688,10 +53751,10 @@
         <v>24</v>
       </c>
       <c r="F818" s="4" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="G818" s="4" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="H818" s="6" t="n">
         <v>46216.636458333</v>
@@ -53749,7 +53812,7 @@
         <v>1411</v>
       </c>
       <c r="G819" s="9" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="H819" s="11" t="n">
         <v>46216.752118056</v>
@@ -53807,7 +53870,7 @@
         <v>164</v>
       </c>
       <c r="G820" s="4" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="H820" s="6" t="n">
         <v>46216.772175926</v>
@@ -53865,7 +53928,7 @@
         <v>1488</v>
       </c>
       <c r="G821" s="9" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="H821" s="10" t="n">
         <v>46217</v>
@@ -53920,10 +53983,10 @@
         <v>24</v>
       </c>
       <c r="F822" s="4" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="G822" s="4" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="H822" s="6" t="n">
         <v>46217.426458333</v>
@@ -53981,7 +54044,7 @@
         <v>1373</v>
       </c>
       <c r="G823" s="9" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="H823" s="10" t="n">
         <v>46217</v>
@@ -54036,10 +54099,10 @@
         <v>24</v>
       </c>
       <c r="F824" s="4" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="G824" s="4" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="H824" s="5" t="n">
         <v>46219</v>
@@ -54094,10 +54157,10 @@
         <v>24</v>
       </c>
       <c r="F825" s="9" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="G825" s="9" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="H825" s="10" t="n">
         <v>46219</v>
@@ -54155,7 +54218,7 @@
         <v>1471</v>
       </c>
       <c r="G826" s="4" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="H826" s="5" t="n">
         <v>46219</v>
@@ -54213,7 +54276,7 @@
         <v>332</v>
       </c>
       <c r="G827" s="9" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="H827" s="11" t="n">
         <v>46218.657847222</v>
@@ -54268,10 +54331,10 @@
         <v>24</v>
       </c>
       <c r="F828" s="4" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="G828" s="4" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="H828" s="6" t="n">
         <v>46218.558854167</v>
@@ -54329,7 +54392,7 @@
         <v>484</v>
       </c>
       <c r="G829" s="9" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="H829" s="11" t="n">
         <v>46218.501886574</v>
@@ -54387,7 +54450,7 @@
         <v>1264</v>
       </c>
       <c r="G830" s="4" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="H830" s="5" t="n">
         <v>46219</v>
@@ -54445,7 +54508,7 @@
         <v>310</v>
       </c>
       <c r="G831" s="9" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="H831" s="10" t="n">
         <v>46219</v>
@@ -54503,7 +54566,7 @@
         <v>969</v>
       </c>
       <c r="G832" s="4" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="H832" s="5" t="n">
         <v>46219</v>
@@ -54558,22 +54621,22 @@
         <v>24</v>
       </c>
       <c r="F833" s="9" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="G833" s="9" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="H833" s="11" t="n">
         <v>46219.727233796</v>
       </c>
       <c r="I833" s="9" t="s">
+        <v>1729</v>
+      </c>
+      <c r="J833" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="K833" s="9" t="s">
         <v>1731</v>
-      </c>
-      <c r="J833" s="9" t="s">
-        <v>1732</v>
-      </c>
-      <c r="K833" s="9" t="s">
-        <v>1733</v>
       </c>
       <c r="L833" s="10"/>
       <c r="M833" s="10"/>
@@ -54619,7 +54682,7 @@
         <v>1328</v>
       </c>
       <c r="G834" s="4" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="H834" s="5" t="n">
         <v>46220</v>
@@ -54674,10 +54737,10 @@
         <v>24</v>
       </c>
       <c r="F835" s="9" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="G835" s="9" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="H835" s="10" t="n">
         <v>46223</v>
@@ -54732,10 +54795,10 @@
         <v>24</v>
       </c>
       <c r="F836" s="4" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="G836" s="4" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="H836" s="5" t="n">
         <v>46224</v>
@@ -54790,10 +54853,10 @@
         <v>24</v>
       </c>
       <c r="F837" s="9" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="G837" s="9" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="H837" s="10" t="n">
         <v>46225</v>
@@ -54851,7 +54914,7 @@
         <v>1264</v>
       </c>
       <c r="G838" s="4" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="H838" s="5" t="n">
         <v>46224</v>
@@ -54909,7 +54972,7 @@
         <v>203</v>
       </c>
       <c r="G839" s="9" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="H839" s="10" t="n">
         <v>46224</v>
@@ -54967,7 +55030,7 @@
         <v>310</v>
       </c>
       <c r="G840" s="4" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="H840" s="5" t="n">
         <v>46224</v>
@@ -55022,10 +55085,10 @@
         <v>24</v>
       </c>
       <c r="F841" s="9" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="G841" s="9" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="H841" s="10" t="n">
         <v>46224</v>
@@ -55080,10 +55143,10 @@
         <v>24</v>
       </c>
       <c r="F842" s="4" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="G842" s="4" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="H842" s="5" t="n">
         <v>46224</v>
@@ -55138,10 +55201,10 @@
         <v>24</v>
       </c>
       <c r="F843" s="9" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="G843" s="9" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="H843" s="10" t="n">
         <v>46224</v>
@@ -55196,10 +55259,10 @@
         <v>24</v>
       </c>
       <c r="F844" s="4" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="G844" s="4" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="H844" s="5" t="n">
         <v>46225</v>
@@ -55254,22 +55317,22 @@
         <v>24</v>
       </c>
       <c r="F845" s="9" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="G845" s="9" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="H845" s="10" t="n">
         <v>46225</v>
       </c>
       <c r="I845" s="9" t="s">
+        <v>1749</v>
+      </c>
+      <c r="J845" s="9" t="s">
         <v>1751</v>
       </c>
-      <c r="J845" s="9" t="s">
-        <v>1753</v>
-      </c>
       <c r="K845" s="9" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="L845" s="10"/>
       <c r="M845" s="10"/>
@@ -55312,22 +55375,22 @@
         <v>24</v>
       </c>
       <c r="F846" s="4" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="G846" s="4" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="H846" s="5" t="n">
         <v>46226</v>
       </c>
       <c r="I846" s="4" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="J846" s="4" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="K846" s="4" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="L846" s="5"/>
       <c r="M846" s="5"/>
@@ -55373,7 +55436,7 @@
         <v>592</v>
       </c>
       <c r="G847" s="9" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="H847" s="10" t="n">
         <v>46226</v>
@@ -55431,7 +55494,7 @@
         <v>1179</v>
       </c>
       <c r="G848" s="4" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="H848" s="5" t="n">
         <v>46227</v>
@@ -55489,7 +55552,7 @@
         <v>623</v>
       </c>
       <c r="G849" s="9" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="H849" s="10" t="n">
         <v>46225</v>
@@ -55547,7 +55610,7 @@
         <v>310</v>
       </c>
       <c r="G850" s="4" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="H850" s="5" t="n">
         <v>46226</v>
@@ -55602,10 +55665,10 @@
         <v>24</v>
       </c>
       <c r="F851" s="9" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="G851" s="9" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="H851" s="10" t="n">
         <v>46225</v>
@@ -55663,7 +55726,7 @@
         <v>581</v>
       </c>
       <c r="G852" s="4" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="H852" s="5" t="n">
         <v>46224</v>
@@ -55718,10 +55781,10 @@
         <v>24</v>
       </c>
       <c r="F853" s="9" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="G853" s="9" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="H853" s="10" t="n">
         <v>46230</v>
@@ -55776,22 +55839,22 @@
         <v>24</v>
       </c>
       <c r="F854" s="4" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="G854" s="4" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="H854" s="5" t="n">
         <v>46227</v>
       </c>
       <c r="I854" s="4" t="s">
+        <v>1764</v>
+      </c>
+      <c r="J854" s="4" t="s">
         <v>1766</v>
       </c>
-      <c r="J854" s="4" t="s">
-        <v>1768</v>
-      </c>
       <c r="K854" s="4" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="L854" s="5"/>
       <c r="M854" s="5"/>
@@ -55831,30 +55894,30 @@
         <v>23</v>
       </c>
       <c r="E855" s="8" t="s">
-        <v>1770</v>
+        <v>24</v>
       </c>
       <c r="F855" s="9" t="s">
-        <v>1771</v>
+        <v>1768</v>
       </c>
       <c r="G855" s="9" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
       <c r="H855" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I855" s="9" t="s">
+        <v>1768</v>
+      </c>
+      <c r="J855" s="9" t="s">
+        <v>1770</v>
+      </c>
+      <c r="K855" s="9" t="s">
         <v>1771</v>
-      </c>
-      <c r="J855" s="9" t="s">
-        <v>1773</v>
-      </c>
-      <c r="K855" s="9" t="s">
-        <v>1774</v>
       </c>
       <c r="L855" s="10"/>
       <c r="M855" s="10"/>
       <c r="N855" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O855" s="11" t="n">
         <v>46231.629427465</v>
@@ -55863,13 +55926,13 @@
         <v>1455</v>
       </c>
       <c r="Q855" s="9" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="R855" s="12" t="n">
         <v>176352</v>
       </c>
       <c r="S855" s="12" t="n">
-        <v>125664</v>
+        <v>176352</v>
       </c>
       <c r="T855" s="9" t="s">
         <v>571</v>
@@ -55895,7 +55958,7 @@
         <v>276</v>
       </c>
       <c r="G856" s="4" t="s">
-        <v>1775</v>
+        <v>1772</v>
       </c>
       <c r="H856" s="5" t="n">
         <v>46230</v>
@@ -55953,7 +56016,7 @@
         <v>1280</v>
       </c>
       <c r="G857" s="9" t="s">
-        <v>1776</v>
+        <v>1773</v>
       </c>
       <c r="H857" s="10" t="n">
         <v>46231</v>
@@ -56011,7 +56074,7 @@
         <v>592</v>
       </c>
       <c r="G858" s="4" t="s">
-        <v>1777</v>
+        <v>1774</v>
       </c>
       <c r="H858" s="5" t="n">
         <v>46230</v>
@@ -56069,7 +56132,7 @@
         <v>1264</v>
       </c>
       <c r="G859" s="9" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
       <c r="H859" s="10" t="n">
         <v>46231</v>
@@ -56124,10 +56187,10 @@
         <v>24</v>
       </c>
       <c r="F860" s="4" t="s">
-        <v>1779</v>
+        <v>1776</v>
       </c>
       <c r="G860" s="4" t="s">
-        <v>1780</v>
+        <v>1777</v>
       </c>
       <c r="H860" s="5" t="n">
         <v>46230</v>
@@ -56179,25 +56242,25 @@
         <v>23</v>
       </c>
       <c r="E861" s="8" t="s">
-        <v>1781</v>
+        <v>1778</v>
       </c>
       <c r="F861" s="9" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
       <c r="G861" s="9" t="s">
-        <v>1783</v>
+        <v>1780</v>
       </c>
       <c r="H861" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I861" s="9" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
       <c r="J861" s="9" t="s">
-        <v>1785</v>
+        <v>1782</v>
       </c>
       <c r="K861" s="9" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
       <c r="L861" s="10"/>
       <c r="M861" s="10"/>
@@ -56211,7 +56274,7 @@
         <v>1455</v>
       </c>
       <c r="Q861" s="9" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="R861" s="12" t="n">
         <v>39446.2</v>
@@ -56220,7 +56283,7 @@
         <v>16215.2</v>
       </c>
       <c r="T861" s="9" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="U861" s="9"/>
       <c r="V861" s="9"/>
@@ -56240,22 +56303,22 @@
         <v>24</v>
       </c>
       <c r="F862" s="4" t="s">
-        <v>1787</v>
+        <v>1784</v>
       </c>
       <c r="G862" s="4" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
       <c r="H862" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="I862" s="4" t="s">
+        <v>1784</v>
+      </c>
+      <c r="J862" s="4" t="s">
+        <v>1786</v>
+      </c>
+      <c r="K862" s="4" t="s">
         <v>1787</v>
-      </c>
-      <c r="J862" s="4" t="s">
-        <v>1789</v>
-      </c>
-      <c r="K862" s="4" t="s">
-        <v>1790</v>
       </c>
       <c r="L862" s="5"/>
       <c r="M862" s="5"/>
@@ -56301,7 +56364,7 @@
         <v>859</v>
       </c>
       <c r="G863" s="9" t="s">
-        <v>1791</v>
+        <v>1788</v>
       </c>
       <c r="H863" s="10" t="n">
         <v>46230</v>
@@ -56359,7 +56422,7 @@
         <v>262</v>
       </c>
       <c r="G864" s="4" t="s">
-        <v>1792</v>
+        <v>1789</v>
       </c>
       <c r="H864" s="5" t="n">
         <v>46230</v>
@@ -56414,22 +56477,22 @@
         <v>24</v>
       </c>
       <c r="F865" s="9" t="s">
-        <v>1793</v>
+        <v>1790</v>
       </c>
       <c r="G865" s="9" t="s">
-        <v>1794</v>
+        <v>1791</v>
       </c>
       <c r="H865" s="10" t="n">
         <v>46230</v>
       </c>
       <c r="I865" s="9" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="J865" s="9" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
       <c r="K865" s="9" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="L865" s="10"/>
       <c r="M865" s="10"/>
@@ -56475,7 +56538,7 @@
         <v>490</v>
       </c>
       <c r="G866" s="4" t="s">
-        <v>1797</v>
+        <v>1794</v>
       </c>
       <c r="H866" s="5" t="n">
         <v>46231</v>
@@ -56533,7 +56596,7 @@
         <v>521</v>
       </c>
       <c r="G867" s="9" t="s">
-        <v>1798</v>
+        <v>1795</v>
       </c>
       <c r="H867" s="10" t="n">
         <v>46232</v>
@@ -56588,10 +56651,10 @@
         <v>24</v>
       </c>
       <c r="F868" s="4" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="G868" s="4" t="s">
-        <v>1799</v>
+        <v>1796</v>
       </c>
       <c r="H868" s="5" t="n">
         <v>46231</v>
@@ -56649,7 +56712,7 @@
         <v>1133</v>
       </c>
       <c r="G869" s="9" t="s">
-        <v>1800</v>
+        <v>1797</v>
       </c>
       <c r="H869" s="10" t="n">
         <v>46233</v>
@@ -56704,10 +56767,10 @@
         <v>24</v>
       </c>
       <c r="F870" s="4" t="s">
-        <v>1801</v>
+        <v>1798</v>
       </c>
       <c r="G870" s="4" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
       <c r="H870" s="5" t="n">
         <v>46232</v>
@@ -56765,7 +56828,7 @@
         <v>355</v>
       </c>
       <c r="G871" s="9" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
       <c r="H871" s="10" t="n">
         <v>46232</v>
@@ -56823,7 +56886,7 @@
         <v>351</v>
       </c>
       <c r="G872" s="4" t="s">
-        <v>1804</v>
+        <v>1801</v>
       </c>
       <c r="H872" s="5" t="n">
         <v>46232</v>
@@ -56881,7 +56944,7 @@
         <v>945</v>
       </c>
       <c r="G873" s="9" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
       <c r="H873" s="10" t="n">
         <v>46232</v>
@@ -56939,7 +57002,7 @@
         <v>262</v>
       </c>
       <c r="G874" s="4" t="s">
-        <v>1806</v>
+        <v>1803</v>
       </c>
       <c r="H874" s="5" t="n">
         <v>46231</v>
@@ -56997,7 +57060,7 @@
         <v>1264</v>
       </c>
       <c r="G875" s="9" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
       <c r="H875" s="10" t="n">
         <v>46232</v>
@@ -57049,13 +57112,13 @@
         <v>23</v>
       </c>
       <c r="E876" s="3" t="s">
-        <v>1808</v>
+        <v>1805</v>
       </c>
       <c r="F876" s="4" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
       <c r="G876" s="4" t="s">
-        <v>1810</v>
+        <v>1807</v>
       </c>
       <c r="H876" s="5" t="n">
         <v>46232</v>
@@ -57113,7 +57176,7 @@
         <v>75</v>
       </c>
       <c r="G877" s="9" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="H877" s="10" t="n">
         <v>46232</v>
@@ -57171,7 +57234,7 @@
         <v>408</v>
       </c>
       <c r="G878" s="4" t="s">
-        <v>1812</v>
+        <v>1809</v>
       </c>
       <c r="H878" s="5" t="n">
         <v>46232</v>
@@ -57188,7 +57251,7 @@
       <c r="L878" s="5"/>
       <c r="M878" s="5"/>
       <c r="N878" s="4" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
       <c r="O878" s="6" t="n">
         <v>46233.675736539</v>
@@ -57229,7 +57292,7 @@
         <v>1473</v>
       </c>
       <c r="G879" s="9" t="s">
-        <v>1814</v>
+        <v>1811</v>
       </c>
       <c r="H879" s="10" t="n">
         <v>46232</v>
@@ -57284,22 +57347,22 @@
         <v>24</v>
       </c>
       <c r="F880" s="4" t="s">
-        <v>1815</v>
+        <v>1812</v>
       </c>
       <c r="G880" s="4" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
       <c r="H880" s="5" t="n">
         <v>46233</v>
       </c>
       <c r="I880" s="4" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
       <c r="J880" s="4" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="K880" s="4" t="s">
-        <v>1819</v>
+        <v>1816</v>
       </c>
       <c r="L880" s="5"/>
       <c r="M880" s="5"/>
@@ -57345,7 +57408,7 @@
         <v>276</v>
       </c>
       <c r="G881" s="9" t="s">
-        <v>1820</v>
+        <v>1817</v>
       </c>
       <c r="H881" s="10" t="n">
         <v>46234</v>
@@ -57403,7 +57466,7 @@
         <v>1298</v>
       </c>
       <c r="G882" s="4" t="s">
-        <v>1821</v>
+        <v>1818</v>
       </c>
       <c r="H882" s="5" t="n">
         <v>46233</v>
@@ -57458,10 +57521,10 @@
         <v>24</v>
       </c>
       <c r="F883" s="9" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="G883" s="9" t="s">
-        <v>1822</v>
+        <v>1819</v>
       </c>
       <c r="H883" s="10" t="n">
         <v>46234</v>
@@ -57513,13 +57576,13 @@
         <v>23</v>
       </c>
       <c r="E884" s="3" t="s">
-        <v>1823</v>
+        <v>1820</v>
       </c>
       <c r="F884" s="4" t="s">
         <v>888</v>
       </c>
       <c r="G884" s="4" t="s">
-        <v>1824</v>
+        <v>1821</v>
       </c>
       <c r="H884" s="5" t="n">
         <v>46234</v>
@@ -57574,10 +57637,10 @@
         <v>24</v>
       </c>
       <c r="F885" s="9" t="s">
-        <v>1801</v>
+        <v>1798</v>
       </c>
       <c r="G885" s="9" t="s">
-        <v>1825</v>
+        <v>1822</v>
       </c>
       <c r="H885" s="10" t="n">
         <v>46234</v>
@@ -57635,7 +57698,7 @@
         <v>1378</v>
       </c>
       <c r="G886" s="4" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
       <c r="H886" s="5" t="n">
         <v>46234</v>
@@ -57690,22 +57753,22 @@
         <v>24</v>
       </c>
       <c r="F887" s="9" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="G887" s="9" t="s">
-        <v>1827</v>
+        <v>1824</v>
       </c>
       <c r="H887" s="10" t="n">
         <v>46233</v>
       </c>
       <c r="I887" s="9" t="s">
+        <v>1603</v>
+      </c>
+      <c r="J887" s="9" t="s">
         <v>1604</v>
       </c>
-      <c r="J887" s="9" t="s">
+      <c r="K887" s="9" t="s">
         <v>1605</v>
-      </c>
-      <c r="K887" s="9" t="s">
-        <v>1606</v>
       </c>
       <c r="L887" s="10"/>
       <c r="M887" s="10"/>
@@ -57748,22 +57811,22 @@
         <v>24</v>
       </c>
       <c r="F888" s="4" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="G888" s="4" t="s">
-        <v>1828</v>
+        <v>1825</v>
       </c>
       <c r="H888" s="5" t="n">
         <v>46234</v>
       </c>
       <c r="I888" s="4" t="s">
+        <v>1729</v>
+      </c>
+      <c r="J888" s="4" t="s">
+        <v>1730</v>
+      </c>
+      <c r="K888" s="4" t="s">
         <v>1731</v>
-      </c>
-      <c r="J888" s="4" t="s">
-        <v>1732</v>
-      </c>
-      <c r="K888" s="4" t="s">
-        <v>1733</v>
       </c>
       <c r="L888" s="5"/>
       <c r="M888" s="5"/>
@@ -57809,7 +57872,7 @@
         <v>143</v>
       </c>
       <c r="G889" s="9" t="s">
-        <v>1829</v>
+        <v>1826</v>
       </c>
       <c r="H889" s="10" t="n">
         <v>46238</v>
@@ -57867,7 +57930,7 @@
         <v>402</v>
       </c>
       <c r="G890" s="4" t="s">
-        <v>1830</v>
+        <v>1827</v>
       </c>
       <c r="H890" s="5" t="n">
         <v>46238</v>
@@ -57925,7 +57988,7 @@
         <v>698</v>
       </c>
       <c r="G891" s="9" t="s">
-        <v>1831</v>
+        <v>1828</v>
       </c>
       <c r="H891" s="10" t="n">
         <v>46238</v>
@@ -57983,7 +58046,7 @@
         <v>328</v>
       </c>
       <c r="G892" s="4" t="s">
-        <v>1832</v>
+        <v>1829</v>
       </c>
       <c r="H892" s="5" t="n">
         <v>46238</v>
@@ -58041,7 +58104,7 @@
         <v>1264</v>
       </c>
       <c r="G893" s="9" t="s">
-        <v>1833</v>
+        <v>1830</v>
       </c>
       <c r="H893" s="10" t="n">
         <v>46240</v>
@@ -58099,7 +58162,7 @@
         <v>203</v>
       </c>
       <c r="G894" s="4" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="H894" s="5" t="n">
         <v>46240</v>
@@ -58157,7 +58220,7 @@
         <v>829</v>
       </c>
       <c r="G895" s="9" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
       <c r="H895" s="10" t="n">
         <v>46240</v>
@@ -58212,22 +58275,22 @@
         <v>24</v>
       </c>
       <c r="F896" s="4" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="G896" s="4" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
       <c r="H896" s="5" t="n">
         <v>46240</v>
       </c>
       <c r="I896" s="4" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
       <c r="J896" s="4" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
       <c r="K896" s="4" t="s">
-        <v>1840</v>
+        <v>1837</v>
       </c>
       <c r="L896" s="5"/>
       <c r="M896" s="5"/>
@@ -58250,7 +58313,7 @@
         <v>7411.2</v>
       </c>
       <c r="T896" s="4" t="s">
-        <v>1841</v>
+        <v>1838</v>
       </c>
       <c r="U896" s="4"/>
       <c r="V896" s="4"/>
@@ -58270,22 +58333,22 @@
         <v>24</v>
       </c>
       <c r="F897" s="9" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="G897" s="9" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
       <c r="H897" s="10" t="n">
         <v>46240</v>
       </c>
       <c r="I897" s="9" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
       <c r="J897" s="9" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
       <c r="K897" s="9" t="s">
-        <v>1840</v>
+        <v>1837</v>
       </c>
       <c r="L897" s="10"/>
       <c r="M897" s="10"/>
@@ -58308,7 +58371,7 @@
         <v>6860.4</v>
       </c>
       <c r="T897" s="9" t="s">
-        <v>1841</v>
+        <v>1838</v>
       </c>
       <c r="U897" s="9"/>
       <c r="V897" s="9"/>
@@ -58331,7 +58394,7 @@
         <v>75</v>
       </c>
       <c r="G898" s="4" t="s">
-        <v>1843</v>
+        <v>1840</v>
       </c>
       <c r="H898" s="5" t="n">
         <v>46241</v>
@@ -58389,7 +58452,7 @@
         <v>1056</v>
       </c>
       <c r="G899" s="9" t="s">
-        <v>1844</v>
+        <v>1841</v>
       </c>
       <c r="H899" s="10" t="n">
         <v>46244</v>
@@ -58447,7 +58510,7 @@
         <v>1488</v>
       </c>
       <c r="G900" s="4" t="s">
-        <v>1845</v>
+        <v>1842</v>
       </c>
       <c r="H900" s="5" t="n">
         <v>46244</v>
@@ -58505,7 +58568,7 @@
         <v>1264</v>
       </c>
       <c r="G901" s="9" t="s">
-        <v>1846</v>
+        <v>1843</v>
       </c>
       <c r="H901" s="11" t="n">
         <v>46244.693715278</v>
@@ -58563,7 +58626,7 @@
         <v>904</v>
       </c>
       <c r="G902" s="4" t="s">
-        <v>1847</v>
+        <v>1844</v>
       </c>
       <c r="H902" s="6" t="n">
         <v>46244.646689815</v>
@@ -58618,22 +58681,22 @@
         <v>24</v>
       </c>
       <c r="F903" s="9" t="s">
-        <v>1848</v>
+        <v>1845</v>
       </c>
       <c r="G903" s="9" t="s">
-        <v>1849</v>
+        <v>1846</v>
       </c>
       <c r="H903" s="11" t="n">
         <v>46244.891539352</v>
       </c>
       <c r="I903" s="9" t="s">
+        <v>1845</v>
+      </c>
+      <c r="J903" s="9" t="s">
+        <v>1847</v>
+      </c>
+      <c r="K903" s="9" t="s">
         <v>1848</v>
-      </c>
-      <c r="J903" s="9" t="s">
-        <v>1850</v>
-      </c>
-      <c r="K903" s="9" t="s">
-        <v>1851</v>
       </c>
       <c r="L903" s="10"/>
       <c r="M903" s="10"/>
@@ -58679,7 +58742,7 @@
         <v>592</v>
       </c>
       <c r="G904" s="4" t="s">
-        <v>1852</v>
+        <v>1849</v>
       </c>
       <c r="H904" s="6" t="n">
         <v>46244.846145833</v>
@@ -58737,7 +58800,7 @@
         <v>75</v>
       </c>
       <c r="G905" s="9" t="s">
-        <v>1853</v>
+        <v>1850</v>
       </c>
       <c r="H905" s="11" t="n">
         <v>46244.704305556</v>
@@ -58795,7 +58858,7 @@
         <v>58</v>
       </c>
       <c r="G906" s="4" t="s">
-        <v>1854</v>
+        <v>1851</v>
       </c>
       <c r="H906" s="6" t="n">
         <v>46245.52099537</v>
@@ -58853,7 +58916,7 @@
         <v>152</v>
       </c>
       <c r="G907" s="9" t="s">
-        <v>1855</v>
+        <v>1852</v>
       </c>
       <c r="H907" s="11" t="n">
         <v>46245.60755787</v>
@@ -58911,7 +58974,7 @@
         <v>295</v>
       </c>
       <c r="G908" s="4" t="s">
-        <v>1856</v>
+        <v>1853</v>
       </c>
       <c r="H908" s="6" t="n">
         <v>46245.672013889</v>
@@ -58969,7 +59032,7 @@
         <v>249</v>
       </c>
       <c r="G909" s="9" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
       <c r="H909" s="10" t="n">
         <v>46247</v>
@@ -59027,7 +59090,7 @@
         <v>249</v>
       </c>
       <c r="G910" s="4" t="s">
-        <v>1858</v>
+        <v>1855</v>
       </c>
       <c r="H910" s="6" t="n">
         <v>46247.371365741</v>
@@ -59085,7 +59148,7 @@
         <v>988</v>
       </c>
       <c r="G911" s="9" t="s">
-        <v>1859</v>
+        <v>1856</v>
       </c>
       <c r="H911" s="11" t="n">
         <v>46247.461736111</v>
@@ -59140,22 +59203,22 @@
         <v>24</v>
       </c>
       <c r="F912" s="4" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="G912" s="4" t="s">
-        <v>1860</v>
+        <v>1857</v>
       </c>
       <c r="H912" s="6" t="n">
         <v>46246.935729167</v>
       </c>
       <c r="I912" s="4" t="s">
+        <v>1670</v>
+      </c>
+      <c r="J912" s="4" t="s">
+        <v>1670</v>
+      </c>
+      <c r="K912" s="4" t="s">
         <v>1671</v>
-      </c>
-      <c r="J912" s="4" t="s">
-        <v>1671</v>
-      </c>
-      <c r="K912" s="4" t="s">
-        <v>1672</v>
       </c>
       <c r="L912" s="5"/>
       <c r="M912" s="5"/>
@@ -59198,22 +59261,22 @@
         <v>24</v>
       </c>
       <c r="F913" s="9" t="s">
-        <v>1861</v>
+        <v>1858</v>
       </c>
       <c r="G913" s="9" t="s">
-        <v>1862</v>
+        <v>1859</v>
       </c>
       <c r="H913" s="11" t="n">
         <v>46246.852106481</v>
       </c>
       <c r="I913" s="9" t="s">
+        <v>1858</v>
+      </c>
+      <c r="J913" s="9" t="s">
+        <v>1860</v>
+      </c>
+      <c r="K913" s="9" t="s">
         <v>1861</v>
-      </c>
-      <c r="J913" s="9" t="s">
-        <v>1863</v>
-      </c>
-      <c r="K913" s="9" t="s">
-        <v>1864</v>
       </c>
       <c r="L913" s="10"/>
       <c r="M913" s="10"/>
@@ -59259,7 +59322,7 @@
         <v>332</v>
       </c>
       <c r="G914" s="4" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
       <c r="H914" s="6" t="n">
         <v>46246.467384259</v>
@@ -59317,7 +59380,7 @@
         <v>328</v>
       </c>
       <c r="G915" s="9" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
       <c r="H915" s="11" t="n">
         <v>46247.693402778</v>
@@ -59372,22 +59435,22 @@
         <v>24</v>
       </c>
       <c r="F916" s="4" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="G916" s="4" t="s">
-        <v>1867</v>
+        <v>1864</v>
       </c>
       <c r="H916" s="6" t="n">
         <v>46247.72962963</v>
       </c>
       <c r="I916" s="4" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="J916" s="4" t="s">
+        <v>1506</v>
+      </c>
+      <c r="K916" s="4" t="s">
         <v>1507</v>
-      </c>
-      <c r="K916" s="4" t="s">
-        <v>1508</v>
       </c>
       <c r="L916" s="5"/>
       <c r="M916" s="5"/>
@@ -59433,7 +59496,7 @@
         <v>1473</v>
       </c>
       <c r="G917" s="9" t="s">
-        <v>1868</v>
+        <v>1865</v>
       </c>
       <c r="H917" s="11" t="n">
         <v>46247.621585648</v>
@@ -59491,7 +59554,7 @@
         <v>75</v>
       </c>
       <c r="G918" s="4" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
       <c r="H918" s="6" t="n">
         <v>46248.419988426</v>
@@ -59549,7 +59612,7 @@
         <v>328</v>
       </c>
       <c r="G919" s="9" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
       <c r="H919" s="11" t="n">
         <v>46248.451365741</v>
@@ -59607,7 +59670,7 @@
         <v>272</v>
       </c>
       <c r="G920" s="4" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
       <c r="H920" s="5" t="n">
         <v>46248</v>
@@ -59665,7 +59728,7 @@
         <v>1060</v>
       </c>
       <c r="G921" s="9" t="s">
-        <v>1872</v>
+        <v>1869</v>
       </c>
       <c r="H921" s="11" t="n">
         <v>46251.721273148</v>
@@ -59723,7 +59786,7 @@
         <v>262</v>
       </c>
       <c r="G922" s="4" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
       <c r="H922" s="6" t="n">
         <v>46251.698263889</v>
@@ -59778,22 +59841,22 @@
         <v>24</v>
       </c>
       <c r="F923" s="9" t="s">
-        <v>1874</v>
+        <v>1871</v>
       </c>
       <c r="G923" s="9" t="s">
-        <v>1875</v>
+        <v>1872</v>
       </c>
       <c r="H923" s="11" t="n">
         <v>46253.493287037</v>
       </c>
       <c r="I923" s="9" t="s">
+        <v>1871</v>
+      </c>
+      <c r="J923" s="9" t="s">
+        <v>1873</v>
+      </c>
+      <c r="K923" s="9" t="s">
         <v>1874</v>
-      </c>
-      <c r="J923" s="9" t="s">
-        <v>1876</v>
-      </c>
-      <c r="K923" s="9" t="s">
-        <v>1877</v>
       </c>
       <c r="L923" s="10"/>
       <c r="M923" s="10"/>
@@ -59839,7 +59902,7 @@
         <v>461</v>
       </c>
       <c r="G924" s="4" t="s">
-        <v>1878</v>
+        <v>1875</v>
       </c>
       <c r="H924" s="6" t="n">
         <v>46252.750821759</v>
@@ -59897,7 +59960,7 @@
         <v>1427</v>
       </c>
       <c r="G925" s="9" t="s">
-        <v>1879</v>
+        <v>1876</v>
       </c>
       <c r="H925" s="11" t="n">
         <v>46252.487453704</v>
@@ -59955,7 +60018,7 @@
         <v>75</v>
       </c>
       <c r="G926" s="4" t="s">
-        <v>1880</v>
+        <v>1877</v>
       </c>
       <c r="H926" s="6" t="n">
         <v>46253.626689815</v>
@@ -60013,7 +60076,7 @@
         <v>589</v>
       </c>
       <c r="G927" s="9" t="s">
-        <v>1881</v>
+        <v>1878</v>
       </c>
       <c r="H927" s="10" t="n">
         <v>46255</v>
@@ -60071,7 +60134,7 @@
         <v>355</v>
       </c>
       <c r="G928" s="4" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
       <c r="H928" s="5" t="n">
         <v>46255</v>
@@ -60126,22 +60189,22 @@
         <v>24</v>
       </c>
       <c r="F929" s="9" t="s">
-        <v>1883</v>
+        <v>1880</v>
       </c>
       <c r="G929" s="9" t="s">
-        <v>1884</v>
+        <v>1881</v>
       </c>
       <c r="H929" s="10" t="n">
         <v>46254</v>
       </c>
       <c r="I929" s="9" t="s">
+        <v>1880</v>
+      </c>
+      <c r="J929" s="9" t="s">
+        <v>1882</v>
+      </c>
+      <c r="K929" s="9" t="s">
         <v>1883</v>
-      </c>
-      <c r="J929" s="9" t="s">
-        <v>1885</v>
-      </c>
-      <c r="K929" s="9" t="s">
-        <v>1886</v>
       </c>
       <c r="L929" s="10"/>
       <c r="M929" s="10"/>
@@ -60155,7 +60218,7 @@
         <v>1455</v>
       </c>
       <c r="Q929" s="9" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="R929" s="12" t="n">
         <v>116127.08</v>
@@ -60187,7 +60250,7 @@
         <v>698</v>
       </c>
       <c r="G930" s="4" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="H930" s="6" t="n">
         <v>46258.645081019</v>
@@ -60245,7 +60308,7 @@
         <v>103</v>
       </c>
       <c r="G931" s="9" t="s">
-        <v>1889</v>
+        <v>1886</v>
       </c>
       <c r="H931" s="11" t="n">
         <v>46258.652638889</v>
@@ -60303,7 +60366,7 @@
         <v>888</v>
       </c>
       <c r="G932" s="4" t="s">
-        <v>1890</v>
+        <v>1887</v>
       </c>
       <c r="H932" s="6" t="n">
         <v>46258.672395833</v>
@@ -60361,7 +60424,7 @@
         <v>1459</v>
       </c>
       <c r="G933" s="9" t="s">
-        <v>1891</v>
+        <v>1888</v>
       </c>
       <c r="H933" s="11" t="n">
         <v>46259.638611111</v>
@@ -60416,22 +60479,22 @@
         <v>24</v>
       </c>
       <c r="F934" s="4" t="s">
-        <v>1892</v>
+        <v>1889</v>
       </c>
       <c r="G934" s="4" t="s">
-        <v>1893</v>
+        <v>1890</v>
       </c>
       <c r="H934" s="6" t="n">
         <v>46259.473958333</v>
       </c>
       <c r="I934" s="4" t="s">
+        <v>1889</v>
+      </c>
+      <c r="J934" s="4" t="s">
+        <v>1891</v>
+      </c>
+      <c r="K934" s="4" t="s">
         <v>1892</v>
-      </c>
-      <c r="J934" s="4" t="s">
-        <v>1894</v>
-      </c>
-      <c r="K934" s="4" t="s">
-        <v>1895</v>
       </c>
       <c r="L934" s="5"/>
       <c r="M934" s="5"/>
@@ -60477,7 +60540,7 @@
         <v>1060</v>
       </c>
       <c r="G935" s="9" t="s">
-        <v>1896</v>
+        <v>1893</v>
       </c>
       <c r="H935" s="11" t="n">
         <v>46259.50275463</v>
@@ -60532,22 +60595,22 @@
         <v>24</v>
       </c>
       <c r="F936" s="4" t="s">
-        <v>1897</v>
+        <v>1894</v>
       </c>
       <c r="G936" s="4" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="H936" s="5" t="n">
         <v>46259</v>
       </c>
       <c r="I936" s="4" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
       <c r="J936" s="4" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
       <c r="K936" s="4" t="s">
-        <v>1901</v>
+        <v>1898</v>
       </c>
       <c r="L936" s="5"/>
       <c r="M936" s="5"/>
@@ -60561,7 +60624,7 @@
         <v>1455</v>
       </c>
       <c r="Q936" s="4" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="R936" s="7" t="n">
         <v>42572</v>
@@ -60593,7 +60656,7 @@
         <v>698</v>
       </c>
       <c r="G937" s="9" t="s">
-        <v>1902</v>
+        <v>1899</v>
       </c>
       <c r="H937" s="11" t="n">
         <v>46259.659039352</v>
@@ -60651,7 +60714,7 @@
         <v>262</v>
       </c>
       <c r="G938" s="4" t="s">
-        <v>1903</v>
+        <v>1900</v>
       </c>
       <c r="H938" s="6" t="n">
         <v>46259.757233796</v>
@@ -60709,7 +60772,7 @@
         <v>945</v>
       </c>
       <c r="G939" s="9" t="s">
-        <v>1904</v>
+        <v>1901</v>
       </c>
       <c r="H939" s="11" t="n">
         <v>46259.670231481</v>
@@ -60761,13 +60824,13 @@
         <v>23</v>
       </c>
       <c r="E940" s="3" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
       <c r="F940" s="4" t="s">
         <v>408</v>
       </c>
       <c r="G940" s="4" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="H940" s="6" t="n">
         <v>46261.456944444</v>
@@ -60822,10 +60885,10 @@
         <v>24</v>
       </c>
       <c r="F941" s="9" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="G941" s="9" t="s">
-        <v>1907</v>
+        <v>1904</v>
       </c>
       <c r="H941" s="11" t="n">
         <v>46260.641412037</v>
@@ -60883,7 +60946,7 @@
         <v>1280</v>
       </c>
       <c r="G942" s="4" t="s">
-        <v>1908</v>
+        <v>1905</v>
       </c>
       <c r="H942" s="6" t="n">
         <v>46261.627002315</v>
@@ -60935,13 +60998,13 @@
         <v>23</v>
       </c>
       <c r="E943" s="8" t="s">
-        <v>1909</v>
+        <v>1906</v>
       </c>
       <c r="F943" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G943" s="9" t="s">
-        <v>1910</v>
+        <v>1907</v>
       </c>
       <c r="H943" s="11" t="n">
         <v>46261.674166667</v>
@@ -60999,7 +61062,7 @@
         <v>211</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1911</v>
+        <v>1908</v>
       </c>
       <c r="H944" s="6" t="n">
         <v>46261.624131944</v>
@@ -61057,7 +61120,7 @@
         <v>521</v>
       </c>
       <c r="G945" s="9" t="s">
-        <v>1912</v>
+        <v>1909</v>
       </c>
       <c r="H945" s="11" t="n">
         <v>46261.626898148</v>
@@ -61115,7 +61178,7 @@
         <v>1056</v>
       </c>
       <c r="G946" s="4" t="s">
-        <v>1913</v>
+        <v>1910</v>
       </c>
       <c r="H946" s="5" t="n">
         <v>46262</v>
@@ -61173,7 +61236,7 @@
         <v>1019</v>
       </c>
       <c r="G947" s="9" t="s">
-        <v>1914</v>
+        <v>1911</v>
       </c>
       <c r="H947" s="10" t="n">
         <v>46261</v>
@@ -61231,7 +61294,7 @@
         <v>38</v>
       </c>
       <c r="G948" s="4" t="s">
-        <v>1915</v>
+        <v>1912</v>
       </c>
       <c r="H948" s="6" t="n">
         <v>46262.683993056</v>
@@ -61283,25 +61346,25 @@
         <v>23</v>
       </c>
       <c r="E949" s="8" t="s">
-        <v>1916</v>
+        <v>1913</v>
       </c>
       <c r="F949" s="9" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="G949" s="9" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
       <c r="H949" s="10" t="n">
         <v>46265</v>
       </c>
       <c r="I949" s="9" t="s">
+        <v>1729</v>
+      </c>
+      <c r="J949" s="9" t="s">
+        <v>1730</v>
+      </c>
+      <c r="K949" s="9" t="s">
         <v>1731</v>
-      </c>
-      <c r="J949" s="9" t="s">
-        <v>1732</v>
-      </c>
-      <c r="K949" s="9" t="s">
-        <v>1733</v>
       </c>
       <c r="L949" s="10"/>
       <c r="M949" s="10"/>
@@ -61341,13 +61404,13 @@
         <v>23</v>
       </c>
       <c r="E950" s="3" t="s">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="F950" s="4" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="G950" s="4" t="s">
-        <v>1919</v>
+        <v>1916</v>
       </c>
       <c r="H950" s="5" t="n">
         <v>46265</v>
@@ -61405,7 +61468,7 @@
         <v>619</v>
       </c>
       <c r="G951" s="9" t="s">
-        <v>1920</v>
+        <v>1917</v>
       </c>
       <c r="H951" s="11" t="n">
         <v>46265.756805556</v>
@@ -61463,7 +61526,7 @@
         <v>103</v>
       </c>
       <c r="G952" s="4" t="s">
-        <v>1921</v>
+        <v>1918</v>
       </c>
       <c r="H952" s="6" t="n">
         <v>46262.6721875</v>
@@ -61521,7 +61584,7 @@
         <v>814</v>
       </c>
       <c r="G953" s="9" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
       <c r="H953" s="11" t="n">
         <v>46265.738773148</v>
@@ -61579,7 +61642,7 @@
         <v>484</v>
       </c>
       <c r="G954" s="4" t="s">
-        <v>1923</v>
+        <v>1920</v>
       </c>
       <c r="H954" s="6" t="n">
         <v>46265.406400463</v>
@@ -61637,7 +61700,7 @@
         <v>482</v>
       </c>
       <c r="G955" s="9" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
       <c r="H955" s="11" t="n">
         <v>46262.643506944</v>
@@ -61695,7 +61758,7 @@
         <v>744</v>
       </c>
       <c r="G956" s="4" t="s">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="H956" s="6" t="n">
         <v>46262.644305556</v>
@@ -61753,7 +61816,7 @@
         <v>1179</v>
       </c>
       <c r="G957" s="9" t="s">
-        <v>1926</v>
+        <v>1923</v>
       </c>
       <c r="H957" s="11" t="n">
         <v>46262.617488426</v>
@@ -61808,10 +61871,10 @@
         <v>24</v>
       </c>
       <c r="F958" s="4" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="G958" s="4" t="s">
-        <v>1927</v>
+        <v>1924</v>
       </c>
       <c r="H958" s="6" t="n">
         <v>46262.337835648</v>
@@ -61866,10 +61929,10 @@
         <v>24</v>
       </c>
       <c r="F959" s="9" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="G959" s="9" t="s">
-        <v>1928</v>
+        <v>1925</v>
       </c>
       <c r="H959" s="10" t="n">
         <v>46266</v>
@@ -61924,10 +61987,10 @@
         <v>24</v>
       </c>
       <c r="F960" s="4" t="s">
-        <v>1929</v>
+        <v>1926</v>
       </c>
       <c r="G960" s="4" t="s">
-        <v>1930</v>
+        <v>1927</v>
       </c>
       <c r="H960" s="5" t="n">
         <v>46265</v>
@@ -61982,22 +62045,22 @@
         <v>24</v>
       </c>
       <c r="F961" s="9" t="s">
-        <v>1931</v>
+        <v>1928</v>
       </c>
       <c r="G961" s="9" t="s">
-        <v>1932</v>
+        <v>1929</v>
       </c>
       <c r="H961" s="10" t="n">
         <v>46266</v>
       </c>
       <c r="I961" s="9" t="s">
+        <v>1928</v>
+      </c>
+      <c r="J961" s="9" t="s">
+        <v>1930</v>
+      </c>
+      <c r="K961" s="9" t="s">
         <v>1931</v>
-      </c>
-      <c r="J961" s="9" t="s">
-        <v>1933</v>
-      </c>
-      <c r="K961" s="9" t="s">
-        <v>1934</v>
       </c>
       <c r="L961" s="10"/>
       <c r="M961" s="10"/>
@@ -62011,7 +62074,7 @@
         <v>1455</v>
       </c>
       <c r="Q961" s="9" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="R961" s="12" t="n">
         <v>17437.2</v>
@@ -62040,22 +62103,22 @@
         <v>24</v>
       </c>
       <c r="F962" s="4" t="s">
-        <v>1935</v>
+        <v>1932</v>
       </c>
       <c r="G962" s="4" t="s">
-        <v>1936</v>
+        <v>1933</v>
       </c>
       <c r="H962" s="5" t="n">
         <v>46265</v>
       </c>
       <c r="I962" s="4" t="s">
-        <v>1937</v>
+        <v>1934</v>
       </c>
       <c r="J962" s="4" t="s">
-        <v>1938</v>
+        <v>1935</v>
       </c>
       <c r="K962" s="4" t="s">
-        <v>1939</v>
+        <v>1936</v>
       </c>
       <c r="L962" s="5"/>
       <c r="M962" s="5"/>
@@ -62069,7 +62132,7 @@
         <v>1455</v>
       </c>
       <c r="Q962" s="4" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="R962" s="7" t="n">
         <v>10074</v>
@@ -62101,7 +62164,7 @@
         <v>945</v>
       </c>
       <c r="G963" s="9" t="s">
-        <v>1940</v>
+        <v>1937</v>
       </c>
       <c r="H963" s="11" t="n">
         <v>46267.438217593</v>
@@ -62159,7 +62222,7 @@
         <v>310</v>
       </c>
       <c r="G964" s="4" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
       <c r="H964" s="5" t="n">
         <v>46269</v>
@@ -62217,7 +62280,7 @@
         <v>402</v>
       </c>
       <c r="G965" s="9" t="s">
-        <v>1942</v>
+        <v>1939</v>
       </c>
       <c r="H965" s="11" t="n">
         <v>46269.745752315</v>
@@ -62275,7 +62338,7 @@
         <v>988</v>
       </c>
       <c r="G966" s="4" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="H966" s="6" t="n">
         <v>46269.693969907</v>
@@ -62333,7 +62396,7 @@
         <v>1079</v>
       </c>
       <c r="G967" s="9" t="s">
-        <v>1944</v>
+        <v>1941</v>
       </c>
       <c r="H967" s="11" t="n">
         <v>46269.459189815</v>
@@ -62385,13 +62448,13 @@
         <v>23</v>
       </c>
       <c r="E968" s="3" t="s">
-        <v>1945</v>
+        <v>1915</v>
       </c>
       <c r="F968" s="4" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G968" s="4" t="s">
-        <v>1946</v>
+        <v>1942</v>
       </c>
       <c r="H968" s="6" t="n">
         <v>46268.442615741</v>
@@ -62423,7 +62486,7 @@
         <v>59790</v>
       </c>
       <c r="S968" s="7" t="n">
-        <v>14850</v>
+        <v>20088</v>
       </c>
       <c r="T968" s="4" t="s">
         <v>32</v>
@@ -62443,13 +62506,13 @@
         <v>23</v>
       </c>
       <c r="E969" s="8" t="s">
-        <v>1947</v>
+        <v>24</v>
       </c>
       <c r="F969" s="9" t="s">
         <v>157</v>
       </c>
       <c r="G969" s="9" t="s">
-        <v>1948</v>
+        <v>1943</v>
       </c>
       <c r="H969" s="10" t="n">
         <v>46268</v>
@@ -62466,7 +62529,7 @@
       <c r="L969" s="10"/>
       <c r="M969" s="10"/>
       <c r="N969" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O969" s="11" t="n">
         <v>46274.365774919</v>
@@ -62481,7 +62544,7 @@
         <v>3326.18</v>
       </c>
       <c r="S969" s="12" t="n">
-        <v>1081.68</v>
+        <v>3326.18</v>
       </c>
       <c r="T969" s="9" t="s">
         <v>32</v>
@@ -62507,7 +62570,7 @@
         <v>969</v>
       </c>
       <c r="G970" s="4" t="s">
-        <v>1949</v>
+        <v>1944</v>
       </c>
       <c r="H970" s="5" t="n">
         <v>46268</v>
@@ -62562,10 +62625,10 @@
         <v>24</v>
       </c>
       <c r="F971" s="9" t="s">
-        <v>1950</v>
+        <v>1945</v>
       </c>
       <c r="G971" s="9" t="s">
-        <v>1951</v>
+        <v>1946</v>
       </c>
       <c r="H971" s="10" t="n">
         <v>46273</v>
@@ -62617,13 +62680,13 @@
         <v>23</v>
       </c>
       <c r="E972" s="3" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
       <c r="F972" s="4" t="s">
         <v>1264</v>
       </c>
       <c r="G972" s="4" t="s">
-        <v>1953</v>
+        <v>1948</v>
       </c>
       <c r="H972" s="5" t="n">
         <v>46273</v>
@@ -62681,7 +62744,7 @@
         <v>152</v>
       </c>
       <c r="G973" s="9" t="s">
-        <v>1954</v>
+        <v>1949</v>
       </c>
       <c r="H973" s="11" t="n">
         <v>46273.758136574</v>
@@ -62736,22 +62799,22 @@
         <v>24</v>
       </c>
       <c r="F974" s="4" t="s">
-        <v>1955</v>
+        <v>1950</v>
       </c>
       <c r="G974" s="4" t="s">
-        <v>1956</v>
+        <v>1951</v>
       </c>
       <c r="H974" s="6" t="n">
         <v>46273.740416667</v>
       </c>
       <c r="I974" s="4" t="s">
-        <v>1955</v>
+        <v>1950</v>
       </c>
       <c r="J974" s="4" t="s">
-        <v>1957</v>
+        <v>1952</v>
       </c>
       <c r="K974" s="4" t="s">
-        <v>1958</v>
+        <v>1953</v>
       </c>
       <c r="L974" s="5"/>
       <c r="M974" s="5"/>
@@ -62797,7 +62860,7 @@
         <v>1411</v>
       </c>
       <c r="G975" s="9" t="s">
-        <v>1959</v>
+        <v>1954</v>
       </c>
       <c r="H975" s="11" t="n">
         <v>46273.780162037</v>
@@ -62849,13 +62912,13 @@
         <v>23</v>
       </c>
       <c r="E976" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F976" s="4" t="s">
-        <v>1960</v>
+        <v>1955</v>
       </c>
       <c r="G976" s="4" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="H976" s="6" t="n">
         <v>46274.442685185</v>
@@ -62872,7 +62935,7 @@
       <c r="L976" s="5"/>
       <c r="M976" s="5"/>
       <c r="N976" s="4" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O976" s="6" t="n">
         <v>46274.622029167</v>
@@ -62887,7 +62950,7 @@
         <v>18000</v>
       </c>
       <c r="S976" s="7" t="n">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="T976" s="4" t="s">
         <v>32</v>
@@ -62910,22 +62973,22 @@
         <v>24</v>
       </c>
       <c r="F977" s="9" t="s">
-        <v>1962</v>
+        <v>1957</v>
       </c>
       <c r="G977" s="9" t="s">
-        <v>1963</v>
+        <v>1958</v>
       </c>
       <c r="H977" s="10" t="n">
         <v>46273</v>
       </c>
       <c r="I977" s="9" t="s">
+        <v>1613</v>
+      </c>
+      <c r="J977" s="9" t="s">
         <v>1614</v>
       </c>
-      <c r="J977" s="9" t="s">
+      <c r="K977" s="9" t="s">
         <v>1615</v>
-      </c>
-      <c r="K977" s="9" t="s">
-        <v>1616</v>
       </c>
       <c r="L977" s="10"/>
       <c r="M977" s="10"/>
@@ -62939,7 +63002,7 @@
         <v>1455</v>
       </c>
       <c r="Q977" s="9" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="R977" s="12" t="n">
         <v>12500</v>
@@ -62971,7 +63034,7 @@
         <v>355</v>
       </c>
       <c r="G978" s="4" t="s">
-        <v>1964</v>
+        <v>1959</v>
       </c>
       <c r="H978" s="5" t="n">
         <v>46274</v>
@@ -63029,7 +63092,7 @@
         <v>152</v>
       </c>
       <c r="G979" s="9" t="s">
-        <v>1965</v>
+        <v>1960</v>
       </c>
       <c r="H979" s="10" t="n">
         <v>46273</v>
@@ -63087,7 +63150,7 @@
         <v>1214</v>
       </c>
       <c r="G980" s="4" t="s">
-        <v>1966</v>
+        <v>1961</v>
       </c>
       <c r="H980" s="5" t="n">
         <v>46275</v>
@@ -63145,7 +63208,7 @@
         <v>215</v>
       </c>
       <c r="G981" s="9" t="s">
-        <v>1967</v>
+        <v>1962</v>
       </c>
       <c r="H981" s="10" t="n">
         <v>46275</v>
@@ -63203,7 +63266,7 @@
         <v>1459</v>
       </c>
       <c r="G982" s="4" t="s">
-        <v>1968</v>
+        <v>1963</v>
       </c>
       <c r="H982" s="6" t="n">
         <v>46274.972708333</v>
@@ -63255,13 +63318,13 @@
         <v>23</v>
       </c>
       <c r="E983" s="8" t="s">
-        <v>285</v>
+        <v>1964</v>
       </c>
       <c r="F983" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G983" s="9" t="s">
-        <v>1969</v>
+        <v>1965</v>
       </c>
       <c r="H983" s="11" t="n">
         <v>46274.976979167</v>
@@ -63278,7 +63341,7 @@
       <c r="L983" s="10"/>
       <c r="M983" s="10"/>
       <c r="N983" s="9" t="s">
-        <v>1813</v>
+        <v>1288</v>
       </c>
       <c r="O983" s="11" t="n">
         <v>46275.628351887</v>
@@ -63290,10 +63353,10 @@
         <v>47</v>
       </c>
       <c r="R983" s="12" t="n">
-        <v>94000</v>
+        <v>94188</v>
       </c>
       <c r="S983" s="12" t="n">
-        <v>0</v>
+        <v>56400</v>
       </c>
       <c r="T983" s="9" t="s">
         <v>32</v>
@@ -63319,7 +63382,7 @@
         <v>276</v>
       </c>
       <c r="G984" s="4" t="s">
-        <v>1970</v>
+        <v>1966</v>
       </c>
       <c r="H984" s="6" t="n">
         <v>46274.703055556</v>
@@ -63377,7 +63440,7 @@
         <v>75</v>
       </c>
       <c r="G985" s="9" t="s">
-        <v>1971</v>
+        <v>1967</v>
       </c>
       <c r="H985" s="11" t="n">
         <v>46274.682534722</v>
@@ -63435,7 +63498,7 @@
         <v>1196</v>
       </c>
       <c r="G986" s="4" t="s">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="H986" s="6" t="n">
         <v>46275.472800926</v>
@@ -63487,13 +63550,13 @@
         <v>23</v>
       </c>
       <c r="E987" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F987" s="9" t="s">
         <v>1118</v>
       </c>
       <c r="G987" s="9" t="s">
-        <v>1973</v>
+        <v>1969</v>
       </c>
       <c r="H987" s="11" t="n">
         <v>46276.641041667</v>
@@ -63510,7 +63573,7 @@
       <c r="L987" s="10"/>
       <c r="M987" s="10"/>
       <c r="N987" s="9" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O987" s="11" t="n">
         <v>46279.583453507</v>
@@ -63525,7 +63588,7 @@
         <v>43201</v>
       </c>
       <c r="S987" s="12" t="n">
-        <v>0</v>
+        <v>43201</v>
       </c>
       <c r="T987" s="9" t="s">
         <v>32</v>
@@ -63551,7 +63614,7 @@
         <v>1296</v>
       </c>
       <c r="G988" s="4" t="s">
-        <v>1974</v>
+        <v>1970</v>
       </c>
       <c r="H988" s="6" t="n">
         <v>46276.445613426</v>
@@ -63603,13 +63666,13 @@
         <v>23</v>
       </c>
       <c r="E989" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F989" s="9" t="s">
         <v>478</v>
       </c>
       <c r="G989" s="9" t="s">
-        <v>1975</v>
+        <v>1971</v>
       </c>
       <c r="H989" s="11" t="n">
         <v>46275.859097222</v>
@@ -63626,7 +63689,7 @@
       <c r="L989" s="10"/>
       <c r="M989" s="10"/>
       <c r="N989" s="9" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O989" s="11" t="n">
         <v>46279.583951817</v>
@@ -63641,7 +63704,7 @@
         <v>14826</v>
       </c>
       <c r="S989" s="12" t="n">
-        <v>0</v>
+        <v>14826</v>
       </c>
       <c r="T989" s="9" t="s">
         <v>32</v>
@@ -63667,7 +63730,7 @@
         <v>496</v>
       </c>
       <c r="G990" s="4" t="s">
-        <v>1976</v>
+        <v>1972</v>
       </c>
       <c r="H990" s="6" t="n">
         <v>46276.36244213</v>
@@ -63719,13 +63782,13 @@
         <v>23</v>
       </c>
       <c r="E991" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F991" s="9" t="s">
         <v>1427</v>
       </c>
       <c r="G991" s="9" t="s">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="H991" s="11" t="n">
         <v>46276.780416667</v>
@@ -63742,7 +63805,7 @@
       <c r="L991" s="10"/>
       <c r="M991" s="10"/>
       <c r="N991" s="9" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O991" s="11" t="n">
         <v>46279.584272454</v>
@@ -63757,7 +63820,7 @@
         <v>42000</v>
       </c>
       <c r="S991" s="12" t="n">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="T991" s="9" t="s">
         <v>32</v>
@@ -63783,7 +63846,7 @@
         <v>1292</v>
       </c>
       <c r="G992" s="4" t="s">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="H992" s="6" t="n">
         <v>46276.750868056</v>
@@ -63838,22 +63901,22 @@
         <v>24</v>
       </c>
       <c r="F993" s="9" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="G993" s="9" t="s">
-        <v>1979</v>
+        <v>1975</v>
       </c>
       <c r="H993" s="11" t="n">
         <v>46276.782905093</v>
       </c>
       <c r="I993" s="9" t="s">
+        <v>1670</v>
+      </c>
+      <c r="J993" s="9" t="s">
+        <v>1670</v>
+      </c>
+      <c r="K993" s="9" t="s">
         <v>1671</v>
-      </c>
-      <c r="J993" s="9" t="s">
-        <v>1671</v>
-      </c>
-      <c r="K993" s="9" t="s">
-        <v>1672</v>
       </c>
       <c r="L993" s="10"/>
       <c r="M993" s="10"/>
@@ -63899,24 +63962,24 @@
         <v>1162</v>
       </c>
       <c r="G994" s="4" t="s">
-        <v>1980</v>
+        <v>1976</v>
       </c>
       <c r="H994" s="5" t="n">
         <v>46276</v>
       </c>
       <c r="I994" s="4" t="s">
-        <v>1981</v>
+        <v>1977</v>
       </c>
       <c r="J994" s="4" t="s">
         <v>1165</v>
       </c>
       <c r="K994" s="4" t="s">
-        <v>1982</v>
+        <v>1978</v>
       </c>
       <c r="L994" s="5"/>
       <c r="M994" s="5"/>
       <c r="N994" s="4" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
       <c r="O994" s="6" t="n">
         <v>46279.599731713</v>
@@ -63954,10 +64017,10 @@
         <v>24</v>
       </c>
       <c r="F995" s="9" t="s">
-        <v>1929</v>
+        <v>1926</v>
       </c>
       <c r="G995" s="9" t="s">
-        <v>1983</v>
+        <v>1979</v>
       </c>
       <c r="H995" s="10" t="n">
         <v>46276</v>
@@ -64015,7 +64078,7 @@
         <v>592</v>
       </c>
       <c r="G996" s="4" t="s">
-        <v>1984</v>
+        <v>1980</v>
       </c>
       <c r="H996" s="6" t="n">
         <v>46279.943194444</v>
@@ -64067,13 +64130,13 @@
         <v>23</v>
       </c>
       <c r="E997" s="8" t="s">
-        <v>1985</v>
+        <v>24</v>
       </c>
       <c r="F997" s="9" t="s">
         <v>262</v>
       </c>
       <c r="G997" s="9" t="s">
-        <v>1986</v>
+        <v>1981</v>
       </c>
       <c r="H997" s="11" t="n">
         <v>46280.741736111</v>
@@ -64090,7 +64153,7 @@
       <c r="L997" s="10"/>
       <c r="M997" s="10"/>
       <c r="N997" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O997" s="11" t="n">
         <v>46281.618698843</v>
@@ -64105,7 +64168,7 @@
         <v>49800</v>
       </c>
       <c r="S997" s="12" t="n">
-        <v>27300</v>
+        <v>49800</v>
       </c>
       <c r="T997" s="9" t="s">
         <v>32</v>
@@ -64131,7 +64194,7 @@
         <v>194</v>
       </c>
       <c r="G998" s="4" t="s">
-        <v>1987</v>
+        <v>1982</v>
       </c>
       <c r="H998" s="5" t="n">
         <v>46279</v>
@@ -64189,7 +64252,7 @@
         <v>389</v>
       </c>
       <c r="G999" s="9" t="s">
-        <v>1988</v>
+        <v>1983</v>
       </c>
       <c r="H999" s="11" t="n">
         <v>46280.714386574</v>
@@ -64247,7 +64310,7 @@
         <v>75</v>
       </c>
       <c r="G1000" s="4" t="s">
-        <v>1989</v>
+        <v>1984</v>
       </c>
       <c r="H1000" s="6" t="n">
         <v>46280.693761574</v>
@@ -64264,7 +64327,7 @@
       <c r="L1000" s="5"/>
       <c r="M1000" s="5"/>
       <c r="N1000" s="4" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
       <c r="O1000" s="6" t="n">
         <v>46281.662435336</v>
@@ -64276,7 +64339,7 @@
         <v>31</v>
       </c>
       <c r="R1000" s="7" t="n">
-        <v>882756</v>
+        <v>885906</v>
       </c>
       <c r="S1000" s="7" t="n">
         <v>0</v>
@@ -64305,7 +64368,7 @@
         <v>965</v>
       </c>
       <c r="G1001" s="9" t="s">
-        <v>1990</v>
+        <v>1985</v>
       </c>
       <c r="H1001" s="11" t="n">
         <v>46280.868599537</v>
@@ -64357,13 +64420,13 @@
         <v>23</v>
       </c>
       <c r="E1002" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1002" s="4" t="s">
         <v>366</v>
       </c>
       <c r="G1002" s="4" t="s">
-        <v>1991</v>
+        <v>1986</v>
       </c>
       <c r="H1002" s="5" t="n">
         <v>46280</v>
@@ -64380,7 +64443,7 @@
       <c r="L1002" s="5"/>
       <c r="M1002" s="5"/>
       <c r="N1002" s="4" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O1002" s="6" t="n">
         <v>46281.670784028</v>
@@ -64395,7 +64458,7 @@
         <v>20400</v>
       </c>
       <c r="S1002" s="7" t="n">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="T1002" s="4" t="s">
         <v>32</v>
@@ -64415,30 +64478,30 @@
         <v>23</v>
       </c>
       <c r="E1003" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1003" s="9" t="s">
-        <v>1992</v>
+        <v>1987</v>
       </c>
       <c r="G1003" s="9" t="s">
-        <v>1993</v>
+        <v>1988</v>
       </c>
       <c r="H1003" s="11" t="n">
         <v>46281.483981481</v>
       </c>
       <c r="I1003" s="9" t="s">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="J1003" s="9" t="s">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="K1003" s="9" t="s">
-        <v>1995</v>
+        <v>1990</v>
       </c>
       <c r="L1003" s="10"/>
       <c r="M1003" s="10"/>
       <c r="N1003" s="9" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O1003" s="11" t="n">
         <v>46282.652243715</v>
@@ -64450,10 +64513,10 @@
         <v>37</v>
       </c>
       <c r="R1003" s="12" t="n">
-        <v>13822.8</v>
+        <v>13764.7</v>
       </c>
       <c r="S1003" s="12" t="n">
-        <v>0</v>
+        <v>13764.7</v>
       </c>
       <c r="T1003" s="9" t="s">
         <v>32</v>
@@ -64473,13 +64536,13 @@
         <v>23</v>
       </c>
       <c r="E1004" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1004" s="4" t="s">
         <v>623</v>
       </c>
       <c r="G1004" s="4" t="s">
-        <v>1996</v>
+        <v>1991</v>
       </c>
       <c r="H1004" s="6" t="n">
         <v>46281.591608796</v>
@@ -64496,7 +64559,7 @@
       <c r="L1004" s="5"/>
       <c r="M1004" s="5"/>
       <c r="N1004" s="4" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O1004" s="6" t="n">
         <v>46282.65346184</v>
@@ -64508,10 +64571,10 @@
         <v>31</v>
       </c>
       <c r="R1004" s="7" t="n">
-        <v>23652</v>
+        <v>23538</v>
       </c>
       <c r="S1004" s="7" t="n">
-        <v>0</v>
+        <v>23538</v>
       </c>
       <c r="T1004" s="4" t="s">
         <v>32</v>
@@ -64534,10 +64597,10 @@
         <v>24</v>
       </c>
       <c r="F1005" s="9" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G1005" s="9" t="s">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="H1005" s="10" t="n">
         <v>46282</v>
@@ -64589,13 +64652,13 @@
         <v>23</v>
       </c>
       <c r="E1006" s="3" t="s">
-        <v>1681</v>
+        <v>24</v>
       </c>
       <c r="F1006" s="4" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="G1006" s="4" t="s">
-        <v>1998</v>
+        <v>1993</v>
       </c>
       <c r="H1006" s="5" t="n">
         <v>46282</v>
@@ -64627,7 +64690,7 @@
         <v>29027.712</v>
       </c>
       <c r="S1006" s="7" t="n">
-        <v>22258.992</v>
+        <v>29027.712</v>
       </c>
       <c r="T1006" s="4" t="s">
         <v>32</v>
@@ -64647,13 +64710,13 @@
         <v>23</v>
       </c>
       <c r="E1007" s="8" t="s">
-        <v>285</v>
+        <v>1805</v>
       </c>
       <c r="F1007" s="9" t="s">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="G1007" s="9" t="s">
-        <v>2000</v>
+        <v>1995</v>
       </c>
       <c r="H1007" s="11" t="n">
         <v>46282.690821759</v>
@@ -64670,7 +64733,7 @@
       <c r="L1007" s="10"/>
       <c r="M1007" s="10"/>
       <c r="N1007" s="9" t="s">
-        <v>1813</v>
+        <v>1288</v>
       </c>
       <c r="O1007" s="11" t="n">
         <v>46286.373205243</v>
@@ -64685,7 +64748,7 @@
         <v>89187</v>
       </c>
       <c r="S1007" s="12" t="n">
-        <v>0</v>
+        <v>51375</v>
       </c>
       <c r="T1007" s="9" t="s">
         <v>32</v>
@@ -64702,33 +64765,33 @@
       </c>
       <c r="C1008" s="4"/>
       <c r="D1008" s="4" t="s">
-        <v>284</v>
+        <v>23</v>
       </c>
       <c r="E1008" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1008" s="4" t="s">
-        <v>2001</v>
+        <v>1996</v>
       </c>
       <c r="G1008" s="4" t="s">
-        <v>2002</v>
+        <v>1997</v>
       </c>
       <c r="H1008" s="6" t="n">
         <v>46283.62880787</v>
       </c>
       <c r="I1008" s="4" t="s">
-        <v>2001</v>
+        <v>1996</v>
       </c>
       <c r="J1008" s="4" t="s">
-        <v>2003</v>
+        <v>1998</v>
       </c>
       <c r="K1008" s="4" t="s">
-        <v>2004</v>
+        <v>1999</v>
       </c>
       <c r="L1008" s="5"/>
       <c r="M1008" s="5"/>
       <c r="N1008" s="4" t="s">
-        <v>1813</v>
+        <v>29</v>
       </c>
       <c r="O1008" s="6" t="n">
         <v>46286.37336088</v>
@@ -64743,7 +64806,7 @@
         <v>17281.04</v>
       </c>
       <c r="S1008" s="7" t="n">
-        <v>0</v>
+        <v>17281.04</v>
       </c>
       <c r="T1008" s="4" t="s">
         <v>32</v>
@@ -64756,20 +64819,20 @@
         <v>1078</v>
       </c>
       <c r="B1009" s="9" t="s">
-        <v>2005</v>
+        <v>22</v>
       </c>
       <c r="C1009" s="9"/>
       <c r="D1009" s="9" t="s">
-        <v>284</v>
+        <v>23</v>
       </c>
       <c r="E1009" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1009" s="9" t="s">
-        <v>2006</v>
+        <v>253</v>
       </c>
       <c r="G1009" s="9" t="s">
-        <v>2007</v>
+        <v>2000</v>
       </c>
       <c r="H1009" s="11" t="n">
         <v>46282.73755787</v>
@@ -64786,7 +64849,7 @@
       <c r="L1009" s="10"/>
       <c r="M1009" s="10"/>
       <c r="N1009" s="9" t="s">
-        <v>2008</v>
+        <v>29</v>
       </c>
       <c r="O1009" s="11" t="n">
         <v>46286.373498264</v>
@@ -64801,7 +64864,7 @@
         <v>25800</v>
       </c>
       <c r="S1009" s="12" t="n">
-        <v>0</v>
+        <v>25800</v>
       </c>
       <c r="T1009" s="9" t="s">
         <v>32</v>
@@ -64809,35 +64872,1253 @@
       <c r="U1009" s="9"/>
       <c r="V1009" s="9"/>
     </row>
-    <row r="1010" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A1010" s="13" t="n">
-        <v>1008</v>
-      </c>
-      <c r="B1010" s="14"/>
-      <c r="C1010" s="14"/>
-      <c r="D1010" s="14"/>
-      <c r="E1010" s="14"/>
-      <c r="F1010" s="14"/>
-      <c r="G1010" s="14"/>
-      <c r="H1010" s="14"/>
-      <c r="I1010" s="14"/>
-      <c r="J1010" s="14"/>
-      <c r="K1010" s="14"/>
-      <c r="L1010" s="14"/>
-      <c r="M1010" s="14"/>
-      <c r="N1010" s="14"/>
-      <c r="O1010" s="14"/>
-      <c r="P1010" s="14"/>
-      <c r="Q1010" s="14"/>
-      <c r="R1010" s="15" t="n">
-        <v>60377418.5506</v>
-      </c>
-      <c r="S1010" s="15" t="n">
-        <v>58306509.3306</v>
-      </c>
-      <c r="T1010" s="14"/>
-      <c r="U1010" s="14"/>
-      <c r="V1010" s="16"/>
+    <row r="1010" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1010" s="3" t="n">
+        <v>1079</v>
+      </c>
+      <c r="B1010" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1010" s="4"/>
+      <c r="D1010" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1010" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1010" s="4" t="s">
+        <v>1515</v>
+      </c>
+      <c r="G1010" s="4" t="s">
+        <v>2001</v>
+      </c>
+      <c r="H1010" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="I1010" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="J1010" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="K1010" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="L1010" s="5"/>
+      <c r="M1010" s="5"/>
+      <c r="N1010" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1010" s="6" t="n">
+        <v>46288.337420868</v>
+      </c>
+      <c r="P1010" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1010" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1010" s="7" t="n">
+        <v>8642.72</v>
+      </c>
+      <c r="S1010" s="7" t="n">
+        <v>8642.72</v>
+      </c>
+      <c r="T1010" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1010" s="4"/>
+      <c r="V1010" s="4"/>
+    </row>
+    <row r="1011" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1011" s="8" t="n">
+        <v>1080</v>
+      </c>
+      <c r="B1011" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1011" s="9"/>
+      <c r="D1011" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1011" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1011" s="9" t="s">
+        <v>2002</v>
+      </c>
+      <c r="G1011" s="9" t="s">
+        <v>2003</v>
+      </c>
+      <c r="H1011" s="10" t="n">
+        <v>46286</v>
+      </c>
+      <c r="I1011" s="9" t="s">
+        <v>1613</v>
+      </c>
+      <c r="J1011" s="9" t="s">
+        <v>1614</v>
+      </c>
+      <c r="K1011" s="9" t="s">
+        <v>1615</v>
+      </c>
+      <c r="L1011" s="10"/>
+      <c r="M1011" s="10"/>
+      <c r="N1011" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1011" s="11" t="n">
+        <v>46288.339278241</v>
+      </c>
+      <c r="P1011" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1011" s="9" t="s">
+        <v>1616</v>
+      </c>
+      <c r="R1011" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S1011" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T1011" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1011" s="9"/>
+      <c r="V1011" s="9"/>
+    </row>
+    <row r="1012" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1012" s="3" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B1012" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1012" s="4"/>
+      <c r="D1012" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1012" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1012" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1012" s="4" t="s">
+        <v>2004</v>
+      </c>
+      <c r="H1012" s="6" t="n">
+        <v>46283.945405093</v>
+      </c>
+      <c r="I1012" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1012" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1012" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1012" s="5"/>
+      <c r="M1012" s="5"/>
+      <c r="N1012" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1012" s="6" t="n">
+        <v>46288.340284525</v>
+      </c>
+      <c r="P1012" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1012" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1012" s="7" t="n">
+        <v>3528</v>
+      </c>
+      <c r="S1012" s="7" t="n">
+        <v>3528</v>
+      </c>
+      <c r="T1012" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1012" s="4"/>
+      <c r="V1012" s="4"/>
+    </row>
+    <row r="1013" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1013" s="8" t="n">
+        <v>1082</v>
+      </c>
+      <c r="B1013" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1013" s="9"/>
+      <c r="D1013" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1013" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1013" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1013" s="9" t="s">
+        <v>2005</v>
+      </c>
+      <c r="H1013" s="11" t="n">
+        <v>46283.947222222</v>
+      </c>
+      <c r="I1013" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1013" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1013" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="L1013" s="10"/>
+      <c r="M1013" s="10"/>
+      <c r="N1013" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1013" s="11" t="n">
+        <v>46288.342010104</v>
+      </c>
+      <c r="P1013" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1013" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1013" s="12" t="n">
+        <v>31608</v>
+      </c>
+      <c r="S1013" s="12" t="n">
+        <v>31608</v>
+      </c>
+      <c r="T1013" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1013" s="9"/>
+      <c r="V1013" s="9"/>
+    </row>
+    <row r="1014" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1014" s="3" t="n">
+        <v>1083</v>
+      </c>
+      <c r="B1014" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1014" s="4"/>
+      <c r="D1014" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1014" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1014" s="4" t="s">
+        <v>1630</v>
+      </c>
+      <c r="G1014" s="4" t="s">
+        <v>2006</v>
+      </c>
+      <c r="H1014" s="6" t="n">
+        <v>46286.665289352</v>
+      </c>
+      <c r="I1014" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="J1014" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="K1014" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="L1014" s="5"/>
+      <c r="M1014" s="5"/>
+      <c r="N1014" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1014" s="6" t="n">
+        <v>46288.344906053</v>
+      </c>
+      <c r="P1014" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1014" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1014" s="7" t="n">
+        <v>5612</v>
+      </c>
+      <c r="S1014" s="7" t="n">
+        <v>5612</v>
+      </c>
+      <c r="T1014" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1014" s="4"/>
+      <c r="V1014" s="4"/>
+    </row>
+    <row r="1015" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1015" s="8" t="n">
+        <v>1084</v>
+      </c>
+      <c r="B1015" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1015" s="9"/>
+      <c r="D1015" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1015" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1015" s="9" t="s">
+        <v>892</v>
+      </c>
+      <c r="G1015" s="9" t="s">
+        <v>2007</v>
+      </c>
+      <c r="H1015" s="11" t="n">
+        <v>46286.490671296</v>
+      </c>
+      <c r="I1015" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="J1015" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="K1015" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="L1015" s="10"/>
+      <c r="M1015" s="10"/>
+      <c r="N1015" s="9" t="s">
+        <v>1810</v>
+      </c>
+      <c r="O1015" s="11" t="n">
+        <v>46288.359700694</v>
+      </c>
+      <c r="P1015" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1015" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1015" s="12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="S1015" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1015" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1015" s="9"/>
+      <c r="V1015" s="9"/>
+    </row>
+    <row r="1016" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1016" s="3" t="n">
+        <v>1085</v>
+      </c>
+      <c r="B1016" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1016" s="4"/>
+      <c r="D1016" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1016" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1016" s="4" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G1016" s="4" t="s">
+        <v>2008</v>
+      </c>
+      <c r="H1016" s="6" t="n">
+        <v>46286.636898148</v>
+      </c>
+      <c r="I1016" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="J1016" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="K1016" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="L1016" s="5"/>
+      <c r="M1016" s="5"/>
+      <c r="N1016" s="4" t="s">
+        <v>1810</v>
+      </c>
+      <c r="O1016" s="6" t="n">
+        <v>46288.361034063</v>
+      </c>
+      <c r="P1016" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1016" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1016" s="7" t="n">
+        <v>41328</v>
+      </c>
+      <c r="S1016" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1016" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1016" s="4"/>
+      <c r="V1016" s="4"/>
+    </row>
+    <row r="1017" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1017" s="8" t="n">
+        <v>1086</v>
+      </c>
+      <c r="B1017" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1017" s="9"/>
+      <c r="D1017" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1017" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1017" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="G1017" s="9" t="s">
+        <v>2009</v>
+      </c>
+      <c r="H1017" s="11" t="n">
+        <v>46287.528784722</v>
+      </c>
+      <c r="I1017" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="J1017" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="K1017" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="L1017" s="10"/>
+      <c r="M1017" s="10"/>
+      <c r="N1017" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1017" s="11" t="n">
+        <v>46288.362876389</v>
+      </c>
+      <c r="P1017" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1017" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1017" s="12" t="n">
+        <v>15300</v>
+      </c>
+      <c r="S1017" s="12" t="n">
+        <v>15300</v>
+      </c>
+      <c r="T1017" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1017" s="9"/>
+      <c r="V1017" s="9"/>
+    </row>
+    <row r="1018" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1018" s="3" t="n">
+        <v>1087</v>
+      </c>
+      <c r="B1018" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1018" s="4"/>
+      <c r="D1018" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1018" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1018" s="4" t="s">
+        <v>2010</v>
+      </c>
+      <c r="G1018" s="4" t="s">
+        <v>2011</v>
+      </c>
+      <c r="H1018" s="6" t="n">
+        <v>46287.685717593</v>
+      </c>
+      <c r="I1018" s="4" t="s">
+        <v>2010</v>
+      </c>
+      <c r="J1018" s="4" t="s">
+        <v>2012</v>
+      </c>
+      <c r="K1018" s="4" t="s">
+        <v>2013</v>
+      </c>
+      <c r="L1018" s="5"/>
+      <c r="M1018" s="5"/>
+      <c r="N1018" s="4" t="s">
+        <v>1810</v>
+      </c>
+      <c r="O1018" s="6" t="n">
+        <v>46289.388101852</v>
+      </c>
+      <c r="P1018" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1018" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1018" s="7" t="n">
+        <v>870000</v>
+      </c>
+      <c r="S1018" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1018" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1018" s="4"/>
+      <c r="V1018" s="4"/>
+    </row>
+    <row r="1019" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1019" s="8" t="n">
+        <v>1088</v>
+      </c>
+      <c r="B1019" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1019" s="9"/>
+      <c r="D1019" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1019" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1019" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G1019" s="9" t="s">
+        <v>2014</v>
+      </c>
+      <c r="H1019" s="11" t="n">
+        <v>46287.90775463</v>
+      </c>
+      <c r="I1019" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="J1019" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="K1019" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="L1019" s="10"/>
+      <c r="M1019" s="10"/>
+      <c r="N1019" s="9" t="s">
+        <v>1810</v>
+      </c>
+      <c r="O1019" s="11" t="n">
+        <v>46289.388410069</v>
+      </c>
+      <c r="P1019" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1019" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1019" s="12" t="n">
+        <v>12900</v>
+      </c>
+      <c r="S1019" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1019" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1019" s="9"/>
+      <c r="V1019" s="9"/>
+    </row>
+    <row r="1020" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1020" s="3" t="n">
+        <v>1089</v>
+      </c>
+      <c r="B1020" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1020" s="4"/>
+      <c r="D1020" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1020" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1020" s="4" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G1020" s="4" t="s">
+        <v>2015</v>
+      </c>
+      <c r="H1020" s="6" t="n">
+        <v>46287.518842593</v>
+      </c>
+      <c r="I1020" s="4" t="s">
+        <v>1237</v>
+      </c>
+      <c r="J1020" s="4" t="s">
+        <v>1238</v>
+      </c>
+      <c r="K1020" s="4" t="s">
+        <v>1239</v>
+      </c>
+      <c r="L1020" s="5"/>
+      <c r="M1020" s="5"/>
+      <c r="N1020" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1020" s="6" t="n">
+        <v>46289.38857022</v>
+      </c>
+      <c r="P1020" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1020" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="R1020" s="7" t="n">
+        <v>28914.6</v>
+      </c>
+      <c r="S1020" s="7" t="n">
+        <v>28914.6</v>
+      </c>
+      <c r="T1020" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="U1020" s="4"/>
+      <c r="V1020" s="4"/>
+    </row>
+    <row r="1021" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1021" s="8" t="n">
+        <v>1090</v>
+      </c>
+      <c r="B1021" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1021" s="9"/>
+      <c r="D1021" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1021" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1021" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="G1021" s="9" t="s">
+        <v>2016</v>
+      </c>
+      <c r="H1021" s="11" t="n">
+        <v>46288.409328704</v>
+      </c>
+      <c r="I1021" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="J1021" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="K1021" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="L1021" s="10"/>
+      <c r="M1021" s="10"/>
+      <c r="N1021" s="9" t="s">
+        <v>1810</v>
+      </c>
+      <c r="O1021" s="11" t="n">
+        <v>46289.388875926</v>
+      </c>
+      <c r="P1021" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1021" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1021" s="12" t="n">
+        <v>8375.1</v>
+      </c>
+      <c r="S1021" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1021" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1021" s="9"/>
+      <c r="V1021" s="9"/>
+    </row>
+    <row r="1022" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1022" s="3" t="n">
+        <v>1091</v>
+      </c>
+      <c r="B1022" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1022" s="4"/>
+      <c r="D1022" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1022" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1022" s="4" t="s">
+        <v>1950</v>
+      </c>
+      <c r="G1022" s="4" t="s">
+        <v>2017</v>
+      </c>
+      <c r="H1022" s="6" t="n">
+        <v>46288.63568287</v>
+      </c>
+      <c r="I1022" s="4" t="s">
+        <v>1950</v>
+      </c>
+      <c r="J1022" s="4" t="s">
+        <v>1952</v>
+      </c>
+      <c r="K1022" s="4" t="s">
+        <v>1953</v>
+      </c>
+      <c r="L1022" s="5"/>
+      <c r="M1022" s="5"/>
+      <c r="N1022" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1022" s="6" t="n">
+        <v>46289.389036262</v>
+      </c>
+      <c r="P1022" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1022" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1022" s="7" t="n">
+        <v>4473.7</v>
+      </c>
+      <c r="S1022" s="7" t="n">
+        <v>4473.7</v>
+      </c>
+      <c r="T1022" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1022" s="4"/>
+      <c r="V1022" s="4"/>
+    </row>
+    <row r="1023" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1023" s="8" t="n">
+        <v>1092</v>
+      </c>
+      <c r="B1023" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1023" s="9"/>
+      <c r="D1023" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1023" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1023" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="G1023" s="9" t="s">
+        <v>2018</v>
+      </c>
+      <c r="H1023" s="11" t="n">
+        <v>46288.641435185</v>
+      </c>
+      <c r="I1023" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="J1023" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="K1023" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="L1023" s="10"/>
+      <c r="M1023" s="10"/>
+      <c r="N1023" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1023" s="11" t="n">
+        <v>46289.389215938</v>
+      </c>
+      <c r="P1023" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1023" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1023" s="12" t="n">
+        <v>8934.48</v>
+      </c>
+      <c r="S1023" s="12" t="n">
+        <v>8934.48</v>
+      </c>
+      <c r="T1023" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1023" s="9"/>
+      <c r="V1023" s="9"/>
+    </row>
+    <row r="1024" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1024" s="3" t="n">
+        <v>1093</v>
+      </c>
+      <c r="B1024" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1024" s="4"/>
+      <c r="D1024" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1024" s="3" t="s">
+        <v>2019</v>
+      </c>
+      <c r="F1024" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="G1024" s="4" t="s">
+        <v>2020</v>
+      </c>
+      <c r="H1024" s="6" t="n">
+        <v>46288.645289352</v>
+      </c>
+      <c r="I1024" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1024" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1024" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1024" s="5"/>
+      <c r="M1024" s="5"/>
+      <c r="N1024" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O1024" s="6" t="n">
+        <v>46289.389332639</v>
+      </c>
+      <c r="P1024" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1024" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1024" s="7" t="n">
+        <v>61549.2</v>
+      </c>
+      <c r="S1024" s="7" t="n">
+        <v>30996</v>
+      </c>
+      <c r="T1024" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1024" s="4"/>
+      <c r="V1024" s="4"/>
+    </row>
+    <row r="1025" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1025" s="8" t="n">
+        <v>1094</v>
+      </c>
+      <c r="B1025" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1025" s="9"/>
+      <c r="D1025" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1025" s="8" t="s">
+        <v>2021</v>
+      </c>
+      <c r="F1025" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="G1025" s="9" t="s">
+        <v>2022</v>
+      </c>
+      <c r="H1025" s="10" t="n">
+        <v>46288</v>
+      </c>
+      <c r="I1025" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="J1025" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="K1025" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="L1025" s="10"/>
+      <c r="M1025" s="10"/>
+      <c r="N1025" s="9" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O1025" s="11" t="n">
+        <v>46289.408104514</v>
+      </c>
+      <c r="P1025" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1025" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1025" s="12" t="n">
+        <v>27234</v>
+      </c>
+      <c r="S1025" s="12" t="n">
+        <v>5607</v>
+      </c>
+      <c r="T1025" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1025" s="9"/>
+      <c r="V1025" s="9"/>
+    </row>
+    <row r="1026" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1026" s="3" t="n">
+        <v>1095</v>
+      </c>
+      <c r="B1026" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1026" s="4"/>
+      <c r="D1026" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1026" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1026" s="4" t="s">
+        <v>1264</v>
+      </c>
+      <c r="G1026" s="4" t="s">
+        <v>2023</v>
+      </c>
+      <c r="H1026" s="5" t="n">
+        <v>46288</v>
+      </c>
+      <c r="I1026" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="J1026" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="K1026" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="L1026" s="5"/>
+      <c r="M1026" s="5"/>
+      <c r="N1026" s="4" t="s">
+        <v>1810</v>
+      </c>
+      <c r="O1026" s="6" t="n">
+        <v>46289.410022488</v>
+      </c>
+      <c r="P1026" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1026" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1026" s="7" t="n">
+        <v>119056.5</v>
+      </c>
+      <c r="S1026" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1026" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1026" s="4"/>
+      <c r="V1026" s="4"/>
+    </row>
+    <row r="1027" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1027" s="8" t="n">
+        <v>1096</v>
+      </c>
+      <c r="B1027" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1027" s="9"/>
+      <c r="D1027" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1027" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1027" s="9" t="s">
+        <v>1638</v>
+      </c>
+      <c r="G1027" s="9" t="s">
+        <v>2024</v>
+      </c>
+      <c r="H1027" s="10" t="n">
+        <v>46289</v>
+      </c>
+      <c r="I1027" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1027" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="K1027" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="L1027" s="10"/>
+      <c r="M1027" s="10"/>
+      <c r="N1027" s="9" t="s">
+        <v>1810</v>
+      </c>
+      <c r="O1027" s="11" t="n">
+        <v>46289.617490625</v>
+      </c>
+      <c r="P1027" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1027" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="R1027" s="12" t="n">
+        <v>21290.5</v>
+      </c>
+      <c r="S1027" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1027" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1027" s="9"/>
+      <c r="V1027" s="9"/>
+    </row>
+    <row r="1028" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1028" s="3" t="n">
+        <v>1097</v>
+      </c>
+      <c r="B1028" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1028" s="4"/>
+      <c r="D1028" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1028" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1028" s="4" t="s">
+        <v>2025</v>
+      </c>
+      <c r="G1028" s="4" t="s">
+        <v>2026</v>
+      </c>
+      <c r="H1028" s="6" t="n">
+        <v>46288.697777778</v>
+      </c>
+      <c r="I1028" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="J1028" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1028" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L1028" s="5"/>
+      <c r="M1028" s="5"/>
+      <c r="N1028" s="4" t="s">
+        <v>1810</v>
+      </c>
+      <c r="O1028" s="6" t="n">
+        <v>46289.622865278</v>
+      </c>
+      <c r="P1028" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1028" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1028" s="7" t="n">
+        <v>104654.4</v>
+      </c>
+      <c r="S1028" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1028" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1028" s="4"/>
+      <c r="V1028" s="4"/>
+    </row>
+    <row r="1029" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1029" s="8" t="n">
+        <v>1098</v>
+      </c>
+      <c r="B1029" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1029" s="9"/>
+      <c r="D1029" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1029" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1029" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="G1029" s="9" t="s">
+        <v>2027</v>
+      </c>
+      <c r="H1029" s="11" t="n">
+        <v>46288.708703704</v>
+      </c>
+      <c r="I1029" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="J1029" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="K1029" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="L1029" s="10"/>
+      <c r="M1029" s="10"/>
+      <c r="N1029" s="9" t="s">
+        <v>1810</v>
+      </c>
+      <c r="O1029" s="11" t="n">
+        <v>46289.622969942</v>
+      </c>
+      <c r="P1029" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1029" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1029" s="12" t="n">
+        <v>21000</v>
+      </c>
+      <c r="S1029" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1029" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1029" s="9"/>
+      <c r="V1029" s="9"/>
+    </row>
+    <row r="1030" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1030" s="3" t="n">
+        <v>1099</v>
+      </c>
+      <c r="B1030" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1030" s="4"/>
+      <c r="D1030" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1030" s="3" t="s">
+        <v>2028</v>
+      </c>
+      <c r="F1030" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G1030" s="4" t="s">
+        <v>2029</v>
+      </c>
+      <c r="H1030" s="6" t="n">
+        <v>46288.727013889</v>
+      </c>
+      <c r="I1030" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1030" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="K1030" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="L1030" s="5"/>
+      <c r="M1030" s="5"/>
+      <c r="N1030" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O1030" s="6" t="n">
+        <v>46289.62317581</v>
+      </c>
+      <c r="P1030" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1030" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1030" s="7" t="n">
+        <v>20210.64</v>
+      </c>
+      <c r="S1030" s="7" t="n">
+        <v>8402.64</v>
+      </c>
+      <c r="T1030" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1030" s="4"/>
+      <c r="V1030" s="4"/>
+    </row>
+    <row r="1031" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A1031" s="13" t="n">
+        <v>1029</v>
+      </c>
+      <c r="B1031" s="14"/>
+      <c r="C1031" s="14"/>
+      <c r="D1031" s="14"/>
+      <c r="E1031" s="14"/>
+      <c r="F1031" s="14"/>
+      <c r="G1031" s="14"/>
+      <c r="H1031" s="14"/>
+      <c r="I1031" s="14"/>
+      <c r="J1031" s="14"/>
+      <c r="K1031" s="14"/>
+      <c r="L1031" s="14"/>
+      <c r="M1031" s="14"/>
+      <c r="N1031" s="14"/>
+      <c r="O1031" s="14"/>
+      <c r="P1031" s="14"/>
+      <c r="Q1031" s="14"/>
+      <c r="R1031" s="15" t="n">
+        <v>61800808.5406</v>
+      </c>
+      <c r="S1031" s="15" t="n">
+        <v>59036797.1806</v>
+      </c>
+      <c r="T1031" s="14"/>
+      <c r="U1031" s="14"/>
+      <c r="V1031" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="2030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="2045">
   <si>
     <t>ID</t>
   </si>
@@ -5349,9 +5349,6 @@
     <t>1089</t>
   </si>
   <si>
-    <t>41 %</t>
-  </si>
-  <si>
     <t>C J A PARENTE</t>
   </si>
   <si>
@@ -5430,573 +5427,573 @@
     <t>1104</t>
   </si>
   <si>
+    <t>RC DISTRIBUIDORA DE MED.</t>
+  </si>
+  <si>
+    <t>1105</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>1108</t>
+  </si>
+  <si>
+    <t>LICIMASTER DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LICIMASTER DISTRIBUIDORA DE MEDICAMENTOS E PRODUTOS MEDICO HOSPITALAR </t>
+  </si>
+  <si>
+    <t>LICIMASTER DIST. DE MED. E PRODUTOS MEDICO</t>
+  </si>
+  <si>
+    <t>20.001.049/0001-76</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>1114</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>1119</t>
+  </si>
+  <si>
+    <t>1120</t>
+  </si>
+  <si>
+    <t>1121</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>1123</t>
+  </si>
+  <si>
+    <t>1124</t>
+  </si>
+  <si>
+    <t>1125</t>
+  </si>
+  <si>
+    <t>ARTMED COMERCIAL</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>ARTMED FARMA</t>
+  </si>
+  <si>
+    <t>ARTMED COMERCIAL LTDA</t>
+  </si>
+  <si>
+    <t>04.361.467/0001-18</t>
+  </si>
+  <si>
+    <t>GERAL</t>
+  </si>
+  <si>
+    <t>1127</t>
+  </si>
+  <si>
+    <t>1128</t>
+  </si>
+  <si>
+    <t>1129</t>
+  </si>
+  <si>
+    <t>1130</t>
+  </si>
+  <si>
+    <t>1132</t>
+  </si>
+  <si>
+    <t>1134</t>
+  </si>
+  <si>
+    <t>OMNIELMASTER HEMOMED</t>
+  </si>
+  <si>
+    <t>1135</t>
+  </si>
+  <si>
+    <t>OMNIELMASTER HEMOMED REPRESENTACAO</t>
+  </si>
+  <si>
+    <t>05.578.020/0001-68</t>
+  </si>
+  <si>
+    <t>1136</t>
+  </si>
+  <si>
+    <t>1137</t>
+  </si>
+  <si>
+    <t>1139</t>
+  </si>
+  <si>
+    <t>1140</t>
+  </si>
+  <si>
+    <t>1141</t>
+  </si>
+  <si>
+    <t>1142</t>
+  </si>
+  <si>
+    <t>1143</t>
+  </si>
+  <si>
+    <t>1144</t>
+  </si>
+  <si>
+    <t>1145</t>
+  </si>
+  <si>
+    <t>HRX COMERCIAL</t>
+  </si>
+  <si>
+    <t>1146</t>
+  </si>
+  <si>
+    <t>HRX PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>11.634.742/0002-76</t>
+  </si>
+  <si>
+    <t>1147</t>
+  </si>
+  <si>
+    <t>1148</t>
+  </si>
+  <si>
+    <t>1149</t>
+  </si>
+  <si>
+    <t>1150</t>
+  </si>
+  <si>
+    <t>1151</t>
+  </si>
+  <si>
+    <t>1152</t>
+  </si>
+  <si>
+    <t>1153</t>
+  </si>
+  <si>
+    <t>1154</t>
+  </si>
+  <si>
+    <t>1155</t>
+  </si>
+  <si>
+    <t>MASTER DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1156</t>
+  </si>
+  <si>
+    <t>MASTER DISTRIBUIDORA E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>55.076.740/0001-01</t>
+  </si>
+  <si>
+    <t>1157</t>
+  </si>
+  <si>
+    <t>1158</t>
+  </si>
+  <si>
+    <t>1159</t>
+  </si>
+  <si>
+    <t>1160</t>
+  </si>
+  <si>
+    <t>1161</t>
+  </si>
+  <si>
+    <t>FAMA DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1162</t>
+  </si>
+  <si>
+    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>03.250.803/0001-92</t>
+  </si>
+  <si>
+    <t>FELIPE AQUINO - MT</t>
+  </si>
+  <si>
+    <t>1163</t>
+  </si>
+  <si>
+    <t>1164</t>
+  </si>
+  <si>
+    <t>1165</t>
+  </si>
+  <si>
+    <t>1166</t>
+  </si>
+  <si>
+    <t>MEDKA HOSPITALAR</t>
+  </si>
+  <si>
+    <t>1167</t>
+  </si>
+  <si>
+    <t>MEDKA DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>36.958.637/0001-32</t>
+  </si>
+  <si>
+    <t>1168</t>
+  </si>
+  <si>
+    <t>DAZ MEDIC</t>
+  </si>
+  <si>
+    <t>1169</t>
+  </si>
+  <si>
+    <t>DAZ DISTRIBUIDORA HOSPITALAR</t>
+  </si>
+  <si>
+    <t>DAZ MEDIC DISTRIBUIDOR HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>33.744.332/0001-30</t>
+  </si>
+  <si>
+    <t>1170</t>
+  </si>
+  <si>
+    <t>1171</t>
+  </si>
+  <si>
+    <t>1173</t>
+  </si>
+  <si>
+    <t>1174</t>
+  </si>
+  <si>
+    <t>1175</t>
+  </si>
+  <si>
+    <t>1176</t>
+  </si>
+  <si>
+    <t>88 %</t>
+  </si>
+  <si>
+    <t>1177</t>
+  </si>
+  <si>
+    <t>1178</t>
+  </si>
+  <si>
+    <t>1179</t>
+  </si>
+  <si>
+    <t>1180</t>
+  </si>
+  <si>
+    <t>1181</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>46 %</t>
+  </si>
+  <si>
+    <t>1183</t>
+  </si>
+  <si>
+    <t>48 %</t>
+  </si>
+  <si>
+    <t>1184</t>
+  </si>
+  <si>
+    <t>1185</t>
+  </si>
+  <si>
+    <t>1186</t>
+  </si>
+  <si>
+    <t>1187</t>
+  </si>
+  <si>
+    <t>1188</t>
+  </si>
+  <si>
+    <t>1189</t>
+  </si>
+  <si>
+    <t>1190</t>
+  </si>
+  <si>
+    <t>1191</t>
+  </si>
+  <si>
+    <t>1192</t>
+  </si>
+  <si>
+    <t>1193</t>
+  </si>
+  <si>
+    <t>ODONTOMED COMERCIO</t>
+  </si>
+  <si>
+    <t>1194</t>
+  </si>
+  <si>
+    <t>DENTAL CENTRO OESTE</t>
+  </si>
+  <si>
+    <t>1195</t>
+  </si>
+  <si>
+    <t>DCO COMERCIO DE PRODUTOS PARA SAUDE LTDA</t>
+  </si>
+  <si>
+    <t>36.900.926/0001-80</t>
+  </si>
+  <si>
+    <t>DU BOM DIST.</t>
+  </si>
+  <si>
+    <t>1196</t>
+  </si>
+  <si>
+    <t>DU BOM DISTRIBUICAO DE PRODUTOS MEDICO-HOSPITALAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DU BOM DISTRIBUICAO DE PRODUTOS MEDICO-HOSPITALAR </t>
+  </si>
+  <si>
+    <t>18.483.775/0001-20</t>
+  </si>
+  <si>
+    <t>1197</t>
+  </si>
+  <si>
+    <t>1198</t>
+  </si>
+  <si>
+    <t>1199</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>53 %</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>1204</t>
+  </si>
+  <si>
+    <t>ATECNOMED ASSISTENCIA</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>83 %</t>
+  </si>
+  <si>
+    <t>1206</t>
+  </si>
+  <si>
+    <t>1207</t>
+  </si>
+  <si>
+    <t>CONTROLE MEDLAB</t>
+  </si>
+  <si>
+    <t>1208</t>
+  </si>
+  <si>
+    <t>CONTROLE MEDLAB COMERCIO DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>31.059.333/0001-10</t>
+  </si>
+  <si>
+    <t>1209</t>
+  </si>
+  <si>
+    <t>DISMED DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1210</t>
+  </si>
+  <si>
+    <t>UNI RIM</t>
+  </si>
+  <si>
+    <t>1211</t>
+  </si>
+  <si>
+    <t>1212</t>
+  </si>
+  <si>
+    <t>1213</t>
+  </si>
+  <si>
+    <t>1214</t>
+  </si>
+  <si>
+    <t>1215</t>
+  </si>
+  <si>
+    <t>1216</t>
+  </si>
+  <si>
+    <t>60 %</t>
+  </si>
+  <si>
+    <t>1217</t>
+  </si>
+  <si>
+    <t>1218</t>
+  </si>
+  <si>
+    <t>1219</t>
+  </si>
+  <si>
+    <t>1220</t>
+  </si>
+  <si>
+    <t>1221</t>
+  </si>
+  <si>
+    <t>1222</t>
+  </si>
+  <si>
+    <t>1223</t>
+  </si>
+  <si>
+    <t>1224</t>
+  </si>
+  <si>
+    <t>1225</t>
+  </si>
+  <si>
+    <t>1226</t>
+  </si>
+  <si>
+    <t>1227</t>
+  </si>
+  <si>
+    <t>1228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPECIFARMA COM DE MEDICAMENTOS </t>
+  </si>
+  <si>
+    <t>00.085.822/0001-12</t>
+  </si>
+  <si>
+    <t>A INICIAR</t>
+  </si>
+  <si>
+    <t>1229</t>
+  </si>
+  <si>
+    <t>1230</t>
+  </si>
+  <si>
+    <t>1231</t>
+  </si>
+  <si>
+    <t>1232</t>
+  </si>
+  <si>
+    <t>1233</t>
+  </si>
+  <si>
+    <t>7 %</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>1235</t>
+  </si>
+  <si>
+    <t>1236</t>
+  </si>
+  <si>
+    <t>ZILFARMA PRODUTOS</t>
+  </si>
+  <si>
+    <t>1237</t>
+  </si>
+  <si>
+    <t>ZILFARMA PRODUTOS FARMACEUTICOS E IMPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t>06.046.371/0001-90</t>
+  </si>
+  <si>
+    <t>1238</t>
+  </si>
+  <si>
+    <t>1239</t>
+  </si>
+  <si>
+    <t>1240</t>
+  </si>
+  <si>
     <t>58 %</t>
   </si>
   <si>
-    <t>RC DISTRIBUIDORA DE MED.</t>
-  </si>
-  <si>
-    <t>1105</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
-    <t>A INICIAR</t>
-  </si>
-  <si>
-    <t>1108</t>
-  </si>
-  <si>
-    <t>LICIMASTER DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LICIMASTER DISTRIBUIDORA DE MEDICAMENTOS E PRODUTOS MEDICO HOSPITALAR </t>
-  </si>
-  <si>
-    <t>LICIMASTER DIST. DE MED. E PRODUTOS MEDICO</t>
-  </si>
-  <si>
-    <t>20.001.049/0001-76</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>1112</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>64 %</t>
-  </si>
-  <si>
-    <t>1114</t>
-  </si>
-  <si>
-    <t>1115</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>1117</t>
-  </si>
-  <si>
-    <t>1118</t>
-  </si>
-  <si>
-    <t>1119</t>
-  </si>
-  <si>
-    <t>1120</t>
-  </si>
-  <si>
-    <t>1121</t>
-  </si>
-  <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>1123</t>
-  </si>
-  <si>
-    <t>1124</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>ARTMED COMERCIAL</t>
-  </si>
-  <si>
-    <t>1126</t>
-  </si>
-  <si>
-    <t>ARTMED FARMA</t>
-  </si>
-  <si>
-    <t>ARTMED COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>04.361.467/0001-18</t>
-  </si>
-  <si>
-    <t>GERAL</t>
-  </si>
-  <si>
-    <t>1127</t>
-  </si>
-  <si>
-    <t>1128</t>
-  </si>
-  <si>
-    <t>1129</t>
-  </si>
-  <si>
-    <t>1130</t>
-  </si>
-  <si>
-    <t>1132</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>OMNIELMASTER HEMOMED</t>
-  </si>
-  <si>
-    <t>1135</t>
-  </si>
-  <si>
-    <t>OMNIELMASTER HEMOMED REPRESENTACAO</t>
-  </si>
-  <si>
-    <t>05.578.020/0001-68</t>
-  </si>
-  <si>
-    <t>1136</t>
-  </si>
-  <si>
-    <t>1137</t>
-  </si>
-  <si>
-    <t>1139</t>
-  </si>
-  <si>
-    <t>1140</t>
-  </si>
-  <si>
-    <t>1141</t>
-  </si>
-  <si>
-    <t>1142</t>
-  </si>
-  <si>
-    <t>1143</t>
-  </si>
-  <si>
-    <t>1144</t>
-  </si>
-  <si>
-    <t>1145</t>
-  </si>
-  <si>
-    <t>HRX COMERCIAL</t>
-  </si>
-  <si>
-    <t>1146</t>
-  </si>
-  <si>
-    <t>HRX PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>11.634.742/0002-76</t>
-  </si>
-  <si>
-    <t>1147</t>
-  </si>
-  <si>
-    <t>1148</t>
-  </si>
-  <si>
-    <t>1149</t>
-  </si>
-  <si>
-    <t>1150</t>
-  </si>
-  <si>
-    <t>1151</t>
-  </si>
-  <si>
-    <t>1152</t>
-  </si>
-  <si>
-    <t>1153</t>
-  </si>
-  <si>
-    <t>1154</t>
-  </si>
-  <si>
-    <t>1155</t>
-  </si>
-  <si>
-    <t>MASTER DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1156</t>
-  </si>
-  <si>
-    <t>MASTER DISTRIBUIDORA E SERVICOS LTDA</t>
-  </si>
-  <si>
-    <t>55.076.740/0001-01</t>
-  </si>
-  <si>
-    <t>1157</t>
-  </si>
-  <si>
-    <t>1158</t>
-  </si>
-  <si>
-    <t>1159</t>
-  </si>
-  <si>
-    <t>1160</t>
-  </si>
-  <si>
-    <t>1161</t>
-  </si>
-  <si>
-    <t>FAMA DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1162</t>
-  </si>
-  <si>
-    <t>FAMA DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>03.250.803/0001-92</t>
-  </si>
-  <si>
-    <t>FELIPE AQUINO - MT</t>
-  </si>
-  <si>
-    <t>1163</t>
-  </si>
-  <si>
-    <t>1164</t>
-  </si>
-  <si>
-    <t>1165</t>
-  </si>
-  <si>
-    <t>1166</t>
-  </si>
-  <si>
-    <t>MEDKA HOSPITALAR</t>
-  </si>
-  <si>
-    <t>1167</t>
-  </si>
-  <si>
-    <t>MEDKA DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>36.958.637/0001-32</t>
-  </si>
-  <si>
-    <t>1168</t>
-  </si>
-  <si>
-    <t>DAZ MEDIC</t>
-  </si>
-  <si>
-    <t>1169</t>
-  </si>
-  <si>
-    <t>DAZ DISTRIBUIDORA HOSPITALAR</t>
-  </si>
-  <si>
-    <t>DAZ MEDIC DISTRIBUIDOR HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>33.744.332/0001-30</t>
-  </si>
-  <si>
-    <t>1170</t>
-  </si>
-  <si>
-    <t>1171</t>
-  </si>
-  <si>
-    <t>1173</t>
-  </si>
-  <si>
-    <t>91 %</t>
-  </si>
-  <si>
-    <t>1174</t>
-  </si>
-  <si>
-    <t>1175</t>
-  </si>
-  <si>
-    <t>1176</t>
-  </si>
-  <si>
-    <t>29 %</t>
-  </si>
-  <si>
-    <t>1177</t>
-  </si>
-  <si>
-    <t>1178</t>
-  </si>
-  <si>
-    <t>1179</t>
-  </si>
-  <si>
-    <t>1180</t>
-  </si>
-  <si>
-    <t>1181</t>
-  </si>
-  <si>
-    <t>1182</t>
-  </si>
-  <si>
-    <t>46 %</t>
-  </si>
-  <si>
-    <t>1183</t>
-  </si>
-  <si>
-    <t>34 %</t>
-  </si>
-  <si>
-    <t>1184</t>
-  </si>
-  <si>
-    <t>1185</t>
-  </si>
-  <si>
-    <t>1186</t>
-  </si>
-  <si>
-    <t>1187</t>
-  </si>
-  <si>
-    <t>1188</t>
-  </si>
-  <si>
-    <t>1189</t>
-  </si>
-  <si>
-    <t>1190</t>
-  </si>
-  <si>
-    <t>1191</t>
-  </si>
-  <si>
-    <t>1192</t>
-  </si>
-  <si>
-    <t>1193</t>
-  </si>
-  <si>
-    <t>ODONTOMED COMERCIO</t>
-  </si>
-  <si>
-    <t>1194</t>
-  </si>
-  <si>
-    <t>DENTAL CENTRO OESTE</t>
-  </si>
-  <si>
-    <t>1195</t>
-  </si>
-  <si>
-    <t>DCO COMERCIO DE PRODUTOS PARA SAUDE LTDA</t>
-  </si>
-  <si>
-    <t>36.900.926/0001-80</t>
-  </si>
-  <si>
-    <t>DU BOM DIST.</t>
-  </si>
-  <si>
-    <t>1196</t>
-  </si>
-  <si>
-    <t>DU BOM DISTRIBUICAO DE PRODUTOS MEDICO-HOSPITALAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DU BOM DISTRIBUICAO DE PRODUTOS MEDICO-HOSPITALAR </t>
-  </si>
-  <si>
-    <t>18.483.775/0001-20</t>
-  </si>
-  <si>
-    <t>1197</t>
-  </si>
-  <si>
-    <t>1198</t>
-  </si>
-  <si>
-    <t>1199</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>1202</t>
-  </si>
-  <si>
-    <t>1203</t>
-  </si>
-  <si>
-    <t>1204</t>
-  </si>
-  <si>
-    <t>ATECNOMED ASSISTENCIA</t>
-  </si>
-  <si>
-    <t>1205</t>
-  </si>
-  <si>
-    <t>83 %</t>
-  </si>
-  <si>
-    <t>1206</t>
-  </si>
-  <si>
-    <t>1207</t>
-  </si>
-  <si>
-    <t>CONTROLE MEDLAB</t>
-  </si>
-  <si>
-    <t>1208</t>
-  </si>
-  <si>
-    <t>CONTROLE MEDLAB COMERCIO DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>31.059.333/0001-10</t>
-  </si>
-  <si>
-    <t>1209</t>
-  </si>
-  <si>
-    <t>DISMED DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1210</t>
-  </si>
-  <si>
-    <t>UNI RIM</t>
-  </si>
-  <si>
-    <t>1211</t>
-  </si>
-  <si>
-    <t>1212</t>
-  </si>
-  <si>
-    <t>1213</t>
-  </si>
-  <si>
-    <t>1214</t>
-  </si>
-  <si>
-    <t>1215</t>
-  </si>
-  <si>
-    <t>1216</t>
-  </si>
-  <si>
-    <t>60 %</t>
-  </si>
-  <si>
-    <t>1217</t>
-  </si>
-  <si>
-    <t>1218</t>
-  </si>
-  <si>
-    <t>1219</t>
-  </si>
-  <si>
-    <t>1220</t>
-  </si>
-  <si>
-    <t>1221</t>
-  </si>
-  <si>
-    <t>1222</t>
-  </si>
-  <si>
-    <t>1223</t>
-  </si>
-  <si>
-    <t>1224</t>
-  </si>
-  <si>
-    <t>1225</t>
-  </si>
-  <si>
-    <t>1226</t>
-  </si>
-  <si>
-    <t>1227</t>
-  </si>
-  <si>
-    <t>1228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPECIFARMA COM DE MEDICAMENTOS </t>
-  </si>
-  <si>
-    <t>00.085.822/0001-12</t>
-  </si>
-  <si>
-    <t>1229</t>
-  </si>
-  <si>
-    <t>1230</t>
-  </si>
-  <si>
-    <t>1231</t>
-  </si>
-  <si>
-    <t>1232</t>
-  </si>
-  <si>
-    <t>1233</t>
-  </si>
-  <si>
-    <t>1234</t>
-  </si>
-  <si>
-    <t>1235</t>
-  </si>
-  <si>
-    <t>1236</t>
-  </si>
-  <si>
-    <t>ZILFARMA PRODUTOS</t>
-  </si>
-  <si>
-    <t>1237</t>
-  </si>
-  <si>
-    <t>ZILFARMA PRODUTOS FARMACEUTICOS E IMPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t>06.046.371/0001-90</t>
-  </si>
-  <si>
-    <t>1238</t>
-  </si>
-  <si>
-    <t>1239</t>
-  </si>
-  <si>
-    <t>1240</t>
-  </si>
-  <si>
     <t>MEDCARE DISTRIBUIDORA</t>
   </si>
   <si>
@@ -6039,6 +6036,9 @@
     <t>1249</t>
   </si>
   <si>
+    <t>24 %</t>
+  </si>
+  <si>
     <t>1250</t>
   </si>
   <si>
@@ -6078,9 +6078,6 @@
     <t>1258</t>
   </si>
   <si>
-    <t>21 %</t>
-  </si>
-  <si>
     <t>1259</t>
   </si>
   <si>
@@ -6099,10 +6096,58 @@
     <t>1263</t>
   </si>
   <si>
-    <t>42 %</t>
-  </si>
-  <si>
     <t>1264</t>
+  </si>
+  <si>
+    <t>1265</t>
+  </si>
+  <si>
+    <t>1266</t>
+  </si>
+  <si>
+    <t>1267</t>
+  </si>
+  <si>
+    <t>1268</t>
+  </si>
+  <si>
+    <t>DISTMED</t>
+  </si>
+  <si>
+    <t>1269</t>
+  </si>
+  <si>
+    <t>L N SILVA DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>46.344.793/0001-67</t>
+  </si>
+  <si>
+    <t>35 %</t>
+  </si>
+  <si>
+    <t>1270</t>
+  </si>
+  <si>
+    <t>1271</t>
+  </si>
+  <si>
+    <t>45 %</t>
+  </si>
+  <si>
+    <t>1272</t>
+  </si>
+  <si>
+    <t>CAMPINA SAUDE CENTER</t>
+  </si>
+  <si>
+    <t>1273</t>
+  </si>
+  <si>
+    <t>1274</t>
+  </si>
+  <si>
+    <t>1275</t>
   </si>
 </sst>
 </file>
@@ -6296,7 +6341,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V1031"/>
+  <dimension ref="A1:V1042"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -56242,30 +56287,30 @@
         <v>23</v>
       </c>
       <c r="E861" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F861" s="9" t="s">
         <v>1778</v>
       </c>
-      <c r="F861" s="9" t="s">
+      <c r="G861" s="9" t="s">
         <v>1779</v>
-      </c>
-      <c r="G861" s="9" t="s">
-        <v>1780</v>
       </c>
       <c r="H861" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I861" s="9" t="s">
+        <v>1780</v>
+      </c>
+      <c r="J861" s="9" t="s">
         <v>1781</v>
       </c>
-      <c r="J861" s="9" t="s">
+      <c r="K861" s="9" t="s">
         <v>1782</v>
-      </c>
-      <c r="K861" s="9" t="s">
-        <v>1783</v>
       </c>
       <c r="L861" s="10"/>
       <c r="M861" s="10"/>
       <c r="N861" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O861" s="11" t="n">
         <v>46232.396937037</v>
@@ -56280,7 +56325,7 @@
         <v>39446.2</v>
       </c>
       <c r="S861" s="12" t="n">
-        <v>16215.2</v>
+        <v>39446.2</v>
       </c>
       <c r="T861" s="9" t="s">
         <v>1686</v>
@@ -56303,22 +56348,22 @@
         <v>24</v>
       </c>
       <c r="F862" s="4" t="s">
+        <v>1783</v>
+      </c>
+      <c r="G862" s="4" t="s">
         <v>1784</v>
-      </c>
-      <c r="G862" s="4" t="s">
-        <v>1785</v>
       </c>
       <c r="H862" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="I862" s="4" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="J862" s="4" t="s">
+        <v>1785</v>
+      </c>
+      <c r="K862" s="4" t="s">
         <v>1786</v>
-      </c>
-      <c r="K862" s="4" t="s">
-        <v>1787</v>
       </c>
       <c r="L862" s="5"/>
       <c r="M862" s="5"/>
@@ -56364,7 +56409,7 @@
         <v>859</v>
       </c>
       <c r="G863" s="9" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H863" s="10" t="n">
         <v>46230</v>
@@ -56422,7 +56467,7 @@
         <v>262</v>
       </c>
       <c r="G864" s="4" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H864" s="5" t="n">
         <v>46230</v>
@@ -56477,22 +56522,22 @@
         <v>24</v>
       </c>
       <c r="F865" s="9" t="s">
+        <v>1789</v>
+      </c>
+      <c r="G865" s="9" t="s">
         <v>1790</v>
-      </c>
-      <c r="G865" s="9" t="s">
-        <v>1791</v>
       </c>
       <c r="H865" s="10" t="n">
         <v>46230</v>
       </c>
       <c r="I865" s="9" t="s">
+        <v>1791</v>
+      </c>
+      <c r="J865" s="9" t="s">
+        <v>1791</v>
+      </c>
+      <c r="K865" s="9" t="s">
         <v>1792</v>
-      </c>
-      <c r="J865" s="9" t="s">
-        <v>1792</v>
-      </c>
-      <c r="K865" s="9" t="s">
-        <v>1793</v>
       </c>
       <c r="L865" s="10"/>
       <c r="M865" s="10"/>
@@ -56538,7 +56583,7 @@
         <v>490</v>
       </c>
       <c r="G866" s="4" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H866" s="5" t="n">
         <v>46231</v>
@@ -56596,7 +56641,7 @@
         <v>521</v>
       </c>
       <c r="G867" s="9" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H867" s="10" t="n">
         <v>46232</v>
@@ -56654,7 +56699,7 @@
         <v>1545</v>
       </c>
       <c r="G868" s="4" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H868" s="5" t="n">
         <v>46231</v>
@@ -56712,7 +56757,7 @@
         <v>1133</v>
       </c>
       <c r="G869" s="9" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H869" s="10" t="n">
         <v>46233</v>
@@ -56767,10 +56812,10 @@
         <v>24</v>
       </c>
       <c r="F870" s="4" t="s">
+        <v>1797</v>
+      </c>
+      <c r="G870" s="4" t="s">
         <v>1798</v>
-      </c>
-      <c r="G870" s="4" t="s">
-        <v>1799</v>
       </c>
       <c r="H870" s="5" t="n">
         <v>46232</v>
@@ -56828,7 +56873,7 @@
         <v>355</v>
       </c>
       <c r="G871" s="9" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H871" s="10" t="n">
         <v>46232</v>
@@ -56886,7 +56931,7 @@
         <v>351</v>
       </c>
       <c r="G872" s="4" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H872" s="5" t="n">
         <v>46232</v>
@@ -56944,7 +56989,7 @@
         <v>945</v>
       </c>
       <c r="G873" s="9" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H873" s="10" t="n">
         <v>46232</v>
@@ -57002,7 +57047,7 @@
         <v>262</v>
       </c>
       <c r="G874" s="4" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H874" s="5" t="n">
         <v>46231</v>
@@ -57060,7 +57105,7 @@
         <v>1264</v>
       </c>
       <c r="G875" s="9" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H875" s="10" t="n">
         <v>46232</v>
@@ -57112,13 +57157,13 @@
         <v>23</v>
       </c>
       <c r="E876" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F876" s="4" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G876" s="4" t="s">
         <v>1805</v>
-      </c>
-      <c r="F876" s="4" t="s">
-        <v>1806</v>
-      </c>
-      <c r="G876" s="4" t="s">
-        <v>1807</v>
       </c>
       <c r="H876" s="5" t="n">
         <v>46232</v>
@@ -57135,7 +57180,7 @@
       <c r="L876" s="5"/>
       <c r="M876" s="5"/>
       <c r="N876" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O876" s="6" t="n">
         <v>46233.672459873</v>
@@ -57150,7 +57195,7 @@
         <v>24258.9</v>
       </c>
       <c r="S876" s="7" t="n">
-        <v>14064</v>
+        <v>24258.9</v>
       </c>
       <c r="T876" s="4" t="s">
         <v>32</v>
@@ -57176,7 +57221,7 @@
         <v>75</v>
       </c>
       <c r="G877" s="9" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="H877" s="10" t="n">
         <v>46232</v>
@@ -57228,13 +57273,13 @@
         <v>23</v>
       </c>
       <c r="E878" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F878" s="4" t="s">
         <v>408</v>
       </c>
       <c r="G878" s="4" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="H878" s="5" t="n">
         <v>46232</v>
@@ -57251,7 +57296,7 @@
       <c r="L878" s="5"/>
       <c r="M878" s="5"/>
       <c r="N878" s="4" t="s">
-        <v>1810</v>
+        <v>29</v>
       </c>
       <c r="O878" s="6" t="n">
         <v>46233.675736539</v>
@@ -57266,7 +57311,7 @@
         <v>10603.9</v>
       </c>
       <c r="S878" s="7" t="n">
-        <v>0</v>
+        <v>10603.9</v>
       </c>
       <c r="T878" s="4" t="s">
         <v>32</v>
@@ -57292,7 +57337,7 @@
         <v>1473</v>
       </c>
       <c r="G879" s="9" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="H879" s="10" t="n">
         <v>46232</v>
@@ -57347,22 +57392,22 @@
         <v>24</v>
       </c>
       <c r="F880" s="4" t="s">
-        <v>1812</v>
+        <v>1809</v>
       </c>
       <c r="G880" s="4" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
       <c r="H880" s="5" t="n">
         <v>46233</v>
       </c>
       <c r="I880" s="4" t="s">
-        <v>1814</v>
+        <v>1811</v>
       </c>
       <c r="J880" s="4" t="s">
-        <v>1815</v>
+        <v>1812</v>
       </c>
       <c r="K880" s="4" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
       <c r="L880" s="5"/>
       <c r="M880" s="5"/>
@@ -57408,7 +57453,7 @@
         <v>276</v>
       </c>
       <c r="G881" s="9" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
       <c r="H881" s="10" t="n">
         <v>46234</v>
@@ -57466,7 +57511,7 @@
         <v>1298</v>
       </c>
       <c r="G882" s="4" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="H882" s="5" t="n">
         <v>46233</v>
@@ -57524,7 +57569,7 @@
         <v>1493</v>
       </c>
       <c r="G883" s="9" t="s">
-        <v>1819</v>
+        <v>1816</v>
       </c>
       <c r="H883" s="10" t="n">
         <v>46234</v>
@@ -57576,13 +57621,13 @@
         <v>23</v>
       </c>
       <c r="E884" s="3" t="s">
-        <v>1820</v>
+        <v>24</v>
       </c>
       <c r="F884" s="4" t="s">
         <v>888</v>
       </c>
       <c r="G884" s="4" t="s">
-        <v>1821</v>
+        <v>1817</v>
       </c>
       <c r="H884" s="5" t="n">
         <v>46234</v>
@@ -57599,7 +57644,7 @@
       <c r="L884" s="5"/>
       <c r="M884" s="5"/>
       <c r="N884" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O884" s="6" t="n">
         <v>46237.450804167</v>
@@ -57614,7 +57659,7 @@
         <v>38854.2</v>
       </c>
       <c r="S884" s="7" t="n">
-        <v>24990</v>
+        <v>38854.2</v>
       </c>
       <c r="T884" s="4" t="s">
         <v>32</v>
@@ -57637,10 +57682,10 @@
         <v>24</v>
       </c>
       <c r="F885" s="9" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="G885" s="9" t="s">
-        <v>1822</v>
+        <v>1818</v>
       </c>
       <c r="H885" s="10" t="n">
         <v>46234</v>
@@ -57698,7 +57743,7 @@
         <v>1378</v>
       </c>
       <c r="G886" s="4" t="s">
-        <v>1823</v>
+        <v>1819</v>
       </c>
       <c r="H886" s="5" t="n">
         <v>46234</v>
@@ -57756,7 +57801,7 @@
         <v>1603</v>
       </c>
       <c r="G887" s="9" t="s">
-        <v>1824</v>
+        <v>1820</v>
       </c>
       <c r="H887" s="10" t="n">
         <v>46233</v>
@@ -57814,7 +57859,7 @@
         <v>1729</v>
       </c>
       <c r="G888" s="4" t="s">
-        <v>1825</v>
+        <v>1821</v>
       </c>
       <c r="H888" s="5" t="n">
         <v>46234</v>
@@ -57872,7 +57917,7 @@
         <v>143</v>
       </c>
       <c r="G889" s="9" t="s">
-        <v>1826</v>
+        <v>1822</v>
       </c>
       <c r="H889" s="10" t="n">
         <v>46238</v>
@@ -57930,7 +57975,7 @@
         <v>402</v>
       </c>
       <c r="G890" s="4" t="s">
-        <v>1827</v>
+        <v>1823</v>
       </c>
       <c r="H890" s="5" t="n">
         <v>46238</v>
@@ -57988,7 +58033,7 @@
         <v>698</v>
       </c>
       <c r="G891" s="9" t="s">
-        <v>1828</v>
+        <v>1824</v>
       </c>
       <c r="H891" s="10" t="n">
         <v>46238</v>
@@ -58046,7 +58091,7 @@
         <v>328</v>
       </c>
       <c r="G892" s="4" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="H892" s="5" t="n">
         <v>46238</v>
@@ -58104,7 +58149,7 @@
         <v>1264</v>
       </c>
       <c r="G893" s="9" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
       <c r="H893" s="10" t="n">
         <v>46240</v>
@@ -58162,7 +58207,7 @@
         <v>203</v>
       </c>
       <c r="G894" s="4" t="s">
-        <v>1831</v>
+        <v>1827</v>
       </c>
       <c r="H894" s="5" t="n">
         <v>46240</v>
@@ -58220,7 +58265,7 @@
         <v>829</v>
       </c>
       <c r="G895" s="9" t="s">
-        <v>1832</v>
+        <v>1828</v>
       </c>
       <c r="H895" s="10" t="n">
         <v>46240</v>
@@ -58275,22 +58320,22 @@
         <v>24</v>
       </c>
       <c r="F896" s="4" t="s">
-        <v>1833</v>
+        <v>1829</v>
       </c>
       <c r="G896" s="4" t="s">
-        <v>1834</v>
+        <v>1830</v>
       </c>
       <c r="H896" s="5" t="n">
         <v>46240</v>
       </c>
       <c r="I896" s="4" t="s">
-        <v>1835</v>
+        <v>1831</v>
       </c>
       <c r="J896" s="4" t="s">
-        <v>1836</v>
+        <v>1832</v>
       </c>
       <c r="K896" s="4" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
       <c r="L896" s="5"/>
       <c r="M896" s="5"/>
@@ -58313,7 +58358,7 @@
         <v>7411.2</v>
       </c>
       <c r="T896" s="4" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
       <c r="U896" s="4"/>
       <c r="V896" s="4"/>
@@ -58333,22 +58378,22 @@
         <v>24</v>
       </c>
       <c r="F897" s="9" t="s">
-        <v>1833</v>
+        <v>1829</v>
       </c>
       <c r="G897" s="9" t="s">
-        <v>1839</v>
+        <v>1835</v>
       </c>
       <c r="H897" s="10" t="n">
         <v>46240</v>
       </c>
       <c r="I897" s="9" t="s">
-        <v>1835</v>
+        <v>1831</v>
       </c>
       <c r="J897" s="9" t="s">
-        <v>1836</v>
+        <v>1832</v>
       </c>
       <c r="K897" s="9" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
       <c r="L897" s="10"/>
       <c r="M897" s="10"/>
@@ -58371,7 +58416,7 @@
         <v>6860.4</v>
       </c>
       <c r="T897" s="9" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
       <c r="U897" s="9"/>
       <c r="V897" s="9"/>
@@ -58394,7 +58439,7 @@
         <v>75</v>
       </c>
       <c r="G898" s="4" t="s">
-        <v>1840</v>
+        <v>1836</v>
       </c>
       <c r="H898" s="5" t="n">
         <v>46241</v>
@@ -58452,7 +58497,7 @@
         <v>1056</v>
       </c>
       <c r="G899" s="9" t="s">
-        <v>1841</v>
+        <v>1837</v>
       </c>
       <c r="H899" s="10" t="n">
         <v>46244</v>
@@ -58510,7 +58555,7 @@
         <v>1488</v>
       </c>
       <c r="G900" s="4" t="s">
-        <v>1842</v>
+        <v>1838</v>
       </c>
       <c r="H900" s="5" t="n">
         <v>46244</v>
@@ -58568,7 +58613,7 @@
         <v>1264</v>
       </c>
       <c r="G901" s="9" t="s">
-        <v>1843</v>
+        <v>1839</v>
       </c>
       <c r="H901" s="11" t="n">
         <v>46244.693715278</v>
@@ -58626,7 +58671,7 @@
         <v>904</v>
       </c>
       <c r="G902" s="4" t="s">
-        <v>1844</v>
+        <v>1840</v>
       </c>
       <c r="H902" s="6" t="n">
         <v>46244.646689815</v>
@@ -58681,22 +58726,22 @@
         <v>24</v>
       </c>
       <c r="F903" s="9" t="s">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="G903" s="9" t="s">
-        <v>1846</v>
+        <v>1842</v>
       </c>
       <c r="H903" s="11" t="n">
         <v>46244.891539352</v>
       </c>
       <c r="I903" s="9" t="s">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="J903" s="9" t="s">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="K903" s="9" t="s">
-        <v>1848</v>
+        <v>1844</v>
       </c>
       <c r="L903" s="10"/>
       <c r="M903" s="10"/>
@@ -58742,7 +58787,7 @@
         <v>592</v>
       </c>
       <c r="G904" s="4" t="s">
-        <v>1849</v>
+        <v>1845</v>
       </c>
       <c r="H904" s="6" t="n">
         <v>46244.846145833</v>
@@ -58800,7 +58845,7 @@
         <v>75</v>
       </c>
       <c r="G905" s="9" t="s">
-        <v>1850</v>
+        <v>1846</v>
       </c>
       <c r="H905" s="11" t="n">
         <v>46244.704305556</v>
@@ -58858,7 +58903,7 @@
         <v>58</v>
       </c>
       <c r="G906" s="4" t="s">
-        <v>1851</v>
+        <v>1847</v>
       </c>
       <c r="H906" s="6" t="n">
         <v>46245.52099537</v>
@@ -58916,7 +58961,7 @@
         <v>152</v>
       </c>
       <c r="G907" s="9" t="s">
-        <v>1852</v>
+        <v>1848</v>
       </c>
       <c r="H907" s="11" t="n">
         <v>46245.60755787</v>
@@ -58974,7 +59019,7 @@
         <v>295</v>
       </c>
       <c r="G908" s="4" t="s">
-        <v>1853</v>
+        <v>1849</v>
       </c>
       <c r="H908" s="6" t="n">
         <v>46245.672013889</v>
@@ -59032,7 +59077,7 @@
         <v>249</v>
       </c>
       <c r="G909" s="9" t="s">
-        <v>1854</v>
+        <v>1850</v>
       </c>
       <c r="H909" s="10" t="n">
         <v>46247</v>
@@ -59090,7 +59135,7 @@
         <v>249</v>
       </c>
       <c r="G910" s="4" t="s">
-        <v>1855</v>
+        <v>1851</v>
       </c>
       <c r="H910" s="6" t="n">
         <v>46247.371365741</v>
@@ -59148,7 +59193,7 @@
         <v>988</v>
       </c>
       <c r="G911" s="9" t="s">
-        <v>1856</v>
+        <v>1852</v>
       </c>
       <c r="H911" s="11" t="n">
         <v>46247.461736111</v>
@@ -59206,7 +59251,7 @@
         <v>1668</v>
       </c>
       <c r="G912" s="4" t="s">
-        <v>1857</v>
+        <v>1853</v>
       </c>
       <c r="H912" s="6" t="n">
         <v>46246.935729167</v>
@@ -59261,22 +59306,22 @@
         <v>24</v>
       </c>
       <c r="F913" s="9" t="s">
-        <v>1858</v>
+        <v>1854</v>
       </c>
       <c r="G913" s="9" t="s">
-        <v>1859</v>
+        <v>1855</v>
       </c>
       <c r="H913" s="11" t="n">
         <v>46246.852106481</v>
       </c>
       <c r="I913" s="9" t="s">
-        <v>1858</v>
+        <v>1854</v>
       </c>
       <c r="J913" s="9" t="s">
-        <v>1860</v>
+        <v>1856</v>
       </c>
       <c r="K913" s="9" t="s">
-        <v>1861</v>
+        <v>1857</v>
       </c>
       <c r="L913" s="10"/>
       <c r="M913" s="10"/>
@@ -59322,7 +59367,7 @@
         <v>332</v>
       </c>
       <c r="G914" s="4" t="s">
-        <v>1862</v>
+        <v>1858</v>
       </c>
       <c r="H914" s="6" t="n">
         <v>46246.467384259</v>
@@ -59380,7 +59425,7 @@
         <v>328</v>
       </c>
       <c r="G915" s="9" t="s">
-        <v>1863</v>
+        <v>1859</v>
       </c>
       <c r="H915" s="11" t="n">
         <v>46247.693402778</v>
@@ -59438,7 +59483,7 @@
         <v>1504</v>
       </c>
       <c r="G916" s="4" t="s">
-        <v>1864</v>
+        <v>1860</v>
       </c>
       <c r="H916" s="6" t="n">
         <v>46247.72962963</v>
@@ -59496,7 +59541,7 @@
         <v>1473</v>
       </c>
       <c r="G917" s="9" t="s">
-        <v>1865</v>
+        <v>1861</v>
       </c>
       <c r="H917" s="11" t="n">
         <v>46247.621585648</v>
@@ -59554,7 +59599,7 @@
         <v>75</v>
       </c>
       <c r="G918" s="4" t="s">
-        <v>1866</v>
+        <v>1862</v>
       </c>
       <c r="H918" s="6" t="n">
         <v>46248.419988426</v>
@@ -59612,7 +59657,7 @@
         <v>328</v>
       </c>
       <c r="G919" s="9" t="s">
-        <v>1867</v>
+        <v>1863</v>
       </c>
       <c r="H919" s="11" t="n">
         <v>46248.451365741</v>
@@ -59670,7 +59715,7 @@
         <v>272</v>
       </c>
       <c r="G920" s="4" t="s">
-        <v>1868</v>
+        <v>1864</v>
       </c>
       <c r="H920" s="5" t="n">
         <v>46248</v>
@@ -59728,7 +59773,7 @@
         <v>1060</v>
       </c>
       <c r="G921" s="9" t="s">
-        <v>1869</v>
+        <v>1865</v>
       </c>
       <c r="H921" s="11" t="n">
         <v>46251.721273148</v>
@@ -59786,7 +59831,7 @@
         <v>262</v>
       </c>
       <c r="G922" s="4" t="s">
-        <v>1870</v>
+        <v>1866</v>
       </c>
       <c r="H922" s="6" t="n">
         <v>46251.698263889</v>
@@ -59841,22 +59886,22 @@
         <v>24</v>
       </c>
       <c r="F923" s="9" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="G923" s="9" t="s">
-        <v>1872</v>
+        <v>1868</v>
       </c>
       <c r="H923" s="11" t="n">
         <v>46253.493287037</v>
       </c>
       <c r="I923" s="9" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="J923" s="9" t="s">
-        <v>1873</v>
+        <v>1869</v>
       </c>
       <c r="K923" s="9" t="s">
-        <v>1874</v>
+        <v>1870</v>
       </c>
       <c r="L923" s="10"/>
       <c r="M923" s="10"/>
@@ -59902,7 +59947,7 @@
         <v>461</v>
       </c>
       <c r="G924" s="4" t="s">
-        <v>1875</v>
+        <v>1871</v>
       </c>
       <c r="H924" s="6" t="n">
         <v>46252.750821759</v>
@@ -59960,7 +60005,7 @@
         <v>1427</v>
       </c>
       <c r="G925" s="9" t="s">
-        <v>1876</v>
+        <v>1872</v>
       </c>
       <c r="H925" s="11" t="n">
         <v>46252.487453704</v>
@@ -60018,7 +60063,7 @@
         <v>75</v>
       </c>
       <c r="G926" s="4" t="s">
-        <v>1877</v>
+        <v>1873</v>
       </c>
       <c r="H926" s="6" t="n">
         <v>46253.626689815</v>
@@ -60076,7 +60121,7 @@
         <v>589</v>
       </c>
       <c r="G927" s="9" t="s">
-        <v>1878</v>
+        <v>1874</v>
       </c>
       <c r="H927" s="10" t="n">
         <v>46255</v>
@@ -60134,7 +60179,7 @@
         <v>355</v>
       </c>
       <c r="G928" s="4" t="s">
-        <v>1879</v>
+        <v>1875</v>
       </c>
       <c r="H928" s="5" t="n">
         <v>46255</v>
@@ -60189,22 +60234,22 @@
         <v>24</v>
       </c>
       <c r="F929" s="9" t="s">
-        <v>1880</v>
+        <v>1876</v>
       </c>
       <c r="G929" s="9" t="s">
-        <v>1881</v>
+        <v>1877</v>
       </c>
       <c r="H929" s="10" t="n">
         <v>46254</v>
       </c>
       <c r="I929" s="9" t="s">
-        <v>1880</v>
+        <v>1876</v>
       </c>
       <c r="J929" s="9" t="s">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="K929" s="9" t="s">
-        <v>1883</v>
+        <v>1879</v>
       </c>
       <c r="L929" s="10"/>
       <c r="M929" s="10"/>
@@ -60218,7 +60263,7 @@
         <v>1455</v>
       </c>
       <c r="Q929" s="9" t="s">
-        <v>1884</v>
+        <v>1880</v>
       </c>
       <c r="R929" s="12" t="n">
         <v>116127.08</v>
@@ -60250,7 +60295,7 @@
         <v>698</v>
       </c>
       <c r="G930" s="4" t="s">
-        <v>1885</v>
+        <v>1881</v>
       </c>
       <c r="H930" s="6" t="n">
         <v>46258.645081019</v>
@@ -60308,7 +60353,7 @@
         <v>103</v>
       </c>
       <c r="G931" s="9" t="s">
-        <v>1886</v>
+        <v>1882</v>
       </c>
       <c r="H931" s="11" t="n">
         <v>46258.652638889</v>
@@ -60366,7 +60411,7 @@
         <v>888</v>
       </c>
       <c r="G932" s="4" t="s">
-        <v>1887</v>
+        <v>1883</v>
       </c>
       <c r="H932" s="6" t="n">
         <v>46258.672395833</v>
@@ -60424,7 +60469,7 @@
         <v>1459</v>
       </c>
       <c r="G933" s="9" t="s">
-        <v>1888</v>
+        <v>1884</v>
       </c>
       <c r="H933" s="11" t="n">
         <v>46259.638611111</v>
@@ -60479,22 +60524,22 @@
         <v>24</v>
       </c>
       <c r="F934" s="4" t="s">
-        <v>1889</v>
+        <v>1885</v>
       </c>
       <c r="G934" s="4" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
       <c r="H934" s="6" t="n">
         <v>46259.473958333</v>
       </c>
       <c r="I934" s="4" t="s">
-        <v>1889</v>
+        <v>1885</v>
       </c>
       <c r="J934" s="4" t="s">
-        <v>1891</v>
+        <v>1887</v>
       </c>
       <c r="K934" s="4" t="s">
-        <v>1892</v>
+        <v>1888</v>
       </c>
       <c r="L934" s="5"/>
       <c r="M934" s="5"/>
@@ -60540,7 +60585,7 @@
         <v>1060</v>
       </c>
       <c r="G935" s="9" t="s">
-        <v>1893</v>
+        <v>1889</v>
       </c>
       <c r="H935" s="11" t="n">
         <v>46259.50275463</v>
@@ -60595,22 +60640,22 @@
         <v>24</v>
       </c>
       <c r="F936" s="4" t="s">
-        <v>1894</v>
+        <v>1890</v>
       </c>
       <c r="G936" s="4" t="s">
-        <v>1895</v>
+        <v>1891</v>
       </c>
       <c r="H936" s="5" t="n">
         <v>46259</v>
       </c>
       <c r="I936" s="4" t="s">
-        <v>1896</v>
+        <v>1892</v>
       </c>
       <c r="J936" s="4" t="s">
-        <v>1897</v>
+        <v>1893</v>
       </c>
       <c r="K936" s="4" t="s">
-        <v>1898</v>
+        <v>1894</v>
       </c>
       <c r="L936" s="5"/>
       <c r="M936" s="5"/>
@@ -60624,7 +60669,7 @@
         <v>1455</v>
       </c>
       <c r="Q936" s="4" t="s">
-        <v>1884</v>
+        <v>1880</v>
       </c>
       <c r="R936" s="7" t="n">
         <v>42572</v>
@@ -60656,7 +60701,7 @@
         <v>698</v>
       </c>
       <c r="G937" s="9" t="s">
-        <v>1899</v>
+        <v>1895</v>
       </c>
       <c r="H937" s="11" t="n">
         <v>46259.659039352</v>
@@ -60714,7 +60759,7 @@
         <v>262</v>
       </c>
       <c r="G938" s="4" t="s">
-        <v>1900</v>
+        <v>1896</v>
       </c>
       <c r="H938" s="6" t="n">
         <v>46259.757233796</v>
@@ -60772,7 +60817,7 @@
         <v>945</v>
       </c>
       <c r="G939" s="9" t="s">
-        <v>1901</v>
+        <v>1897</v>
       </c>
       <c r="H939" s="11" t="n">
         <v>46259.670231481</v>
@@ -60824,13 +60869,13 @@
         <v>23</v>
       </c>
       <c r="E940" s="3" t="s">
-        <v>1902</v>
+        <v>24</v>
       </c>
       <c r="F940" s="4" t="s">
         <v>408</v>
       </c>
       <c r="G940" s="4" t="s">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="H940" s="6" t="n">
         <v>46261.456944444</v>
@@ -60847,7 +60892,7 @@
       <c r="L940" s="5"/>
       <c r="M940" s="5"/>
       <c r="N940" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O940" s="6" t="n">
         <v>46261.555533102</v>
@@ -60862,7 +60907,7 @@
         <v>22323.5</v>
       </c>
       <c r="S940" s="7" t="n">
-        <v>20250</v>
+        <v>22323.5</v>
       </c>
       <c r="T940" s="4" t="s">
         <v>32</v>
@@ -60888,7 +60933,7 @@
         <v>1545</v>
       </c>
       <c r="G941" s="9" t="s">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="H941" s="11" t="n">
         <v>46260.641412037</v>
@@ -60946,7 +60991,7 @@
         <v>1280</v>
       </c>
       <c r="G942" s="4" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="H942" s="6" t="n">
         <v>46261.627002315</v>
@@ -60998,13 +61043,13 @@
         <v>23</v>
       </c>
       <c r="E943" s="8" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="F943" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G943" s="9" t="s">
-        <v>1907</v>
+        <v>1902</v>
       </c>
       <c r="H943" s="11" t="n">
         <v>46261.674166667</v>
@@ -61036,7 +61081,7 @@
         <v>42336</v>
       </c>
       <c r="S943" s="12" t="n">
-        <v>12096</v>
+        <v>37296</v>
       </c>
       <c r="T943" s="9" t="s">
         <v>32</v>
@@ -61062,7 +61107,7 @@
         <v>211</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1908</v>
+        <v>1903</v>
       </c>
       <c r="H944" s="6" t="n">
         <v>46261.624131944</v>
@@ -61120,7 +61165,7 @@
         <v>521</v>
       </c>
       <c r="G945" s="9" t="s">
-        <v>1909</v>
+        <v>1904</v>
       </c>
       <c r="H945" s="11" t="n">
         <v>46261.626898148</v>
@@ -61178,7 +61223,7 @@
         <v>1056</v>
       </c>
       <c r="G946" s="4" t="s">
-        <v>1910</v>
+        <v>1905</v>
       </c>
       <c r="H946" s="5" t="n">
         <v>46262</v>
@@ -61236,7 +61281,7 @@
         <v>1019</v>
       </c>
       <c r="G947" s="9" t="s">
-        <v>1911</v>
+        <v>1906</v>
       </c>
       <c r="H947" s="10" t="n">
         <v>46261</v>
@@ -61294,7 +61339,7 @@
         <v>38</v>
       </c>
       <c r="G948" s="4" t="s">
-        <v>1912</v>
+        <v>1907</v>
       </c>
       <c r="H948" s="6" t="n">
         <v>46262.683993056</v>
@@ -61346,13 +61391,13 @@
         <v>23</v>
       </c>
       <c r="E949" s="8" t="s">
-        <v>1913</v>
+        <v>1908</v>
       </c>
       <c r="F949" s="9" t="s">
         <v>1729</v>
       </c>
       <c r="G949" s="9" t="s">
-        <v>1914</v>
+        <v>1909</v>
       </c>
       <c r="H949" s="10" t="n">
         <v>46265</v>
@@ -61404,13 +61449,13 @@
         <v>23</v>
       </c>
       <c r="E950" s="3" t="s">
-        <v>1915</v>
+        <v>1910</v>
       </c>
       <c r="F950" s="4" t="s">
         <v>1638</v>
       </c>
       <c r="G950" s="4" t="s">
-        <v>1916</v>
+        <v>1911</v>
       </c>
       <c r="H950" s="5" t="n">
         <v>46265</v>
@@ -61442,7 +61487,7 @@
         <v>63150.72</v>
       </c>
       <c r="S950" s="7" t="n">
-        <v>21570.72</v>
+        <v>30302.52</v>
       </c>
       <c r="T950" s="4" t="s">
         <v>32</v>
@@ -61468,7 +61513,7 @@
         <v>619</v>
       </c>
       <c r="G951" s="9" t="s">
-        <v>1917</v>
+        <v>1912</v>
       </c>
       <c r="H951" s="11" t="n">
         <v>46265.756805556</v>
@@ -61526,7 +61571,7 @@
         <v>103</v>
       </c>
       <c r="G952" s="4" t="s">
-        <v>1918</v>
+        <v>1913</v>
       </c>
       <c r="H952" s="6" t="n">
         <v>46262.6721875</v>
@@ -61584,7 +61629,7 @@
         <v>814</v>
       </c>
       <c r="G953" s="9" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="H953" s="11" t="n">
         <v>46265.738773148</v>
@@ -61642,7 +61687,7 @@
         <v>484</v>
       </c>
       <c r="G954" s="4" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="H954" s="6" t="n">
         <v>46265.406400463</v>
@@ -61700,7 +61745,7 @@
         <v>482</v>
       </c>
       <c r="G955" s="9" t="s">
-        <v>1921</v>
+        <v>1916</v>
       </c>
       <c r="H955" s="11" t="n">
         <v>46262.643506944</v>
@@ -61758,7 +61803,7 @@
         <v>744</v>
       </c>
       <c r="G956" s="4" t="s">
-        <v>1922</v>
+        <v>1917</v>
       </c>
       <c r="H956" s="6" t="n">
         <v>46262.644305556</v>
@@ -61816,7 +61861,7 @@
         <v>1179</v>
       </c>
       <c r="G957" s="9" t="s">
-        <v>1923</v>
+        <v>1918</v>
       </c>
       <c r="H957" s="11" t="n">
         <v>46262.617488426</v>
@@ -61874,7 +61919,7 @@
         <v>1525</v>
       </c>
       <c r="G958" s="4" t="s">
-        <v>1924</v>
+        <v>1919</v>
       </c>
       <c r="H958" s="6" t="n">
         <v>46262.337835648</v>
@@ -61932,7 +61977,7 @@
         <v>1515</v>
       </c>
       <c r="G959" s="9" t="s">
-        <v>1925</v>
+        <v>1920</v>
       </c>
       <c r="H959" s="10" t="n">
         <v>46266</v>
@@ -61987,10 +62032,10 @@
         <v>24</v>
       </c>
       <c r="F960" s="4" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="G960" s="4" t="s">
-        <v>1927</v>
+        <v>1922</v>
       </c>
       <c r="H960" s="5" t="n">
         <v>46265</v>
@@ -62045,22 +62090,22 @@
         <v>24</v>
       </c>
       <c r="F961" s="9" t="s">
-        <v>1928</v>
+        <v>1923</v>
       </c>
       <c r="G961" s="9" t="s">
-        <v>1929</v>
+        <v>1924</v>
       </c>
       <c r="H961" s="10" t="n">
         <v>46266</v>
       </c>
       <c r="I961" s="9" t="s">
-        <v>1928</v>
+        <v>1923</v>
       </c>
       <c r="J961" s="9" t="s">
-        <v>1930</v>
+        <v>1925</v>
       </c>
       <c r="K961" s="9" t="s">
-        <v>1931</v>
+        <v>1926</v>
       </c>
       <c r="L961" s="10"/>
       <c r="M961" s="10"/>
@@ -62074,7 +62119,7 @@
         <v>1455</v>
       </c>
       <c r="Q961" s="9" t="s">
-        <v>1884</v>
+        <v>1880</v>
       </c>
       <c r="R961" s="12" t="n">
         <v>17437.2</v>
@@ -62103,22 +62148,22 @@
         <v>24</v>
       </c>
       <c r="F962" s="4" t="s">
-        <v>1932</v>
+        <v>1927</v>
       </c>
       <c r="G962" s="4" t="s">
-        <v>1933</v>
+        <v>1928</v>
       </c>
       <c r="H962" s="5" t="n">
         <v>46265</v>
       </c>
       <c r="I962" s="4" t="s">
-        <v>1934</v>
+        <v>1929</v>
       </c>
       <c r="J962" s="4" t="s">
-        <v>1935</v>
+        <v>1930</v>
       </c>
       <c r="K962" s="4" t="s">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="L962" s="5"/>
       <c r="M962" s="5"/>
@@ -62132,7 +62177,7 @@
         <v>1455</v>
       </c>
       <c r="Q962" s="4" t="s">
-        <v>1884</v>
+        <v>1880</v>
       </c>
       <c r="R962" s="7" t="n">
         <v>10074</v>
@@ -62164,7 +62209,7 @@
         <v>945</v>
       </c>
       <c r="G963" s="9" t="s">
-        <v>1937</v>
+        <v>1932</v>
       </c>
       <c r="H963" s="11" t="n">
         <v>46267.438217593</v>
@@ -62222,7 +62267,7 @@
         <v>310</v>
       </c>
       <c r="G964" s="4" t="s">
-        <v>1938</v>
+        <v>1933</v>
       </c>
       <c r="H964" s="5" t="n">
         <v>46269</v>
@@ -62280,7 +62325,7 @@
         <v>402</v>
       </c>
       <c r="G965" s="9" t="s">
-        <v>1939</v>
+        <v>1934</v>
       </c>
       <c r="H965" s="11" t="n">
         <v>46269.745752315</v>
@@ -62338,7 +62383,7 @@
         <v>988</v>
       </c>
       <c r="G966" s="4" t="s">
-        <v>1940</v>
+        <v>1935</v>
       </c>
       <c r="H966" s="6" t="n">
         <v>46269.693969907</v>
@@ -62396,7 +62441,7 @@
         <v>1079</v>
       </c>
       <c r="G967" s="9" t="s">
-        <v>1941</v>
+        <v>1936</v>
       </c>
       <c r="H967" s="11" t="n">
         <v>46269.459189815</v>
@@ -62448,13 +62493,13 @@
         <v>23</v>
       </c>
       <c r="E968" s="3" t="s">
-        <v>1915</v>
+        <v>1937</v>
       </c>
       <c r="F968" s="4" t="s">
         <v>1495</v>
       </c>
       <c r="G968" s="4" t="s">
-        <v>1942</v>
+        <v>1938</v>
       </c>
       <c r="H968" s="6" t="n">
         <v>46268.442615741</v>
@@ -62486,7 +62531,7 @@
         <v>59790</v>
       </c>
       <c r="S968" s="7" t="n">
-        <v>20088</v>
+        <v>31968</v>
       </c>
       <c r="T968" s="4" t="s">
         <v>32</v>
@@ -62512,7 +62557,7 @@
         <v>157</v>
       </c>
       <c r="G969" s="9" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="H969" s="10" t="n">
         <v>46268</v>
@@ -62570,7 +62615,7 @@
         <v>969</v>
       </c>
       <c r="G970" s="4" t="s">
-        <v>1944</v>
+        <v>1940</v>
       </c>
       <c r="H970" s="5" t="n">
         <v>46268</v>
@@ -62625,10 +62670,10 @@
         <v>24</v>
       </c>
       <c r="F971" s="9" t="s">
-        <v>1945</v>
+        <v>1941</v>
       </c>
       <c r="G971" s="9" t="s">
-        <v>1946</v>
+        <v>1942</v>
       </c>
       <c r="H971" s="10" t="n">
         <v>46273</v>
@@ -62680,13 +62725,13 @@
         <v>23</v>
       </c>
       <c r="E972" s="3" t="s">
-        <v>1947</v>
+        <v>1943</v>
       </c>
       <c r="F972" s="4" t="s">
         <v>1264</v>
       </c>
       <c r="G972" s="4" t="s">
-        <v>1948</v>
+        <v>1944</v>
       </c>
       <c r="H972" s="5" t="n">
         <v>46273</v>
@@ -62744,7 +62789,7 @@
         <v>152</v>
       </c>
       <c r="G973" s="9" t="s">
-        <v>1949</v>
+        <v>1945</v>
       </c>
       <c r="H973" s="11" t="n">
         <v>46273.758136574</v>
@@ -62799,22 +62844,22 @@
         <v>24</v>
       </c>
       <c r="F974" s="4" t="s">
-        <v>1950</v>
+        <v>1946</v>
       </c>
       <c r="G974" s="4" t="s">
-        <v>1951</v>
+        <v>1947</v>
       </c>
       <c r="H974" s="6" t="n">
         <v>46273.740416667</v>
       </c>
       <c r="I974" s="4" t="s">
-        <v>1950</v>
+        <v>1946</v>
       </c>
       <c r="J974" s="4" t="s">
-        <v>1952</v>
+        <v>1948</v>
       </c>
       <c r="K974" s="4" t="s">
-        <v>1953</v>
+        <v>1949</v>
       </c>
       <c r="L974" s="5"/>
       <c r="M974" s="5"/>
@@ -62860,7 +62905,7 @@
         <v>1411</v>
       </c>
       <c r="G975" s="9" t="s">
-        <v>1954</v>
+        <v>1950</v>
       </c>
       <c r="H975" s="11" t="n">
         <v>46273.780162037</v>
@@ -62915,10 +62960,10 @@
         <v>24</v>
       </c>
       <c r="F976" s="4" t="s">
-        <v>1955</v>
+        <v>1951</v>
       </c>
       <c r="G976" s="4" t="s">
-        <v>1956</v>
+        <v>1952</v>
       </c>
       <c r="H976" s="6" t="n">
         <v>46274.442685185</v>
@@ -62973,10 +63018,10 @@
         <v>24</v>
       </c>
       <c r="F977" s="9" t="s">
-        <v>1957</v>
+        <v>1953</v>
       </c>
       <c r="G977" s="9" t="s">
-        <v>1958</v>
+        <v>1954</v>
       </c>
       <c r="H977" s="10" t="n">
         <v>46273</v>
@@ -63034,7 +63079,7 @@
         <v>355</v>
       </c>
       <c r="G978" s="4" t="s">
-        <v>1959</v>
+        <v>1955</v>
       </c>
       <c r="H978" s="5" t="n">
         <v>46274</v>
@@ -63092,7 +63137,7 @@
         <v>152</v>
       </c>
       <c r="G979" s="9" t="s">
-        <v>1960</v>
+        <v>1956</v>
       </c>
       <c r="H979" s="10" t="n">
         <v>46273</v>
@@ -63150,7 +63195,7 @@
         <v>1214</v>
       </c>
       <c r="G980" s="4" t="s">
-        <v>1961</v>
+        <v>1957</v>
       </c>
       <c r="H980" s="5" t="n">
         <v>46275</v>
@@ -63208,7 +63253,7 @@
         <v>215</v>
       </c>
       <c r="G981" s="9" t="s">
-        <v>1962</v>
+        <v>1958</v>
       </c>
       <c r="H981" s="10" t="n">
         <v>46275</v>
@@ -63266,7 +63311,7 @@
         <v>1459</v>
       </c>
       <c r="G982" s="4" t="s">
-        <v>1963</v>
+        <v>1959</v>
       </c>
       <c r="H982" s="6" t="n">
         <v>46274.972708333</v>
@@ -63318,13 +63363,13 @@
         <v>23</v>
       </c>
       <c r="E983" s="8" t="s">
-        <v>1964</v>
+        <v>1960</v>
       </c>
       <c r="F983" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G983" s="9" t="s">
-        <v>1965</v>
+        <v>1961</v>
       </c>
       <c r="H983" s="11" t="n">
         <v>46274.976979167</v>
@@ -63382,7 +63427,7 @@
         <v>276</v>
       </c>
       <c r="G984" s="4" t="s">
-        <v>1966</v>
+        <v>1962</v>
       </c>
       <c r="H984" s="6" t="n">
         <v>46274.703055556</v>
@@ -63440,7 +63485,7 @@
         <v>75</v>
       </c>
       <c r="G985" s="9" t="s">
-        <v>1967</v>
+        <v>1963</v>
       </c>
       <c r="H985" s="11" t="n">
         <v>46274.682534722</v>
@@ -63498,7 +63543,7 @@
         <v>1196</v>
       </c>
       <c r="G986" s="4" t="s">
-        <v>1968</v>
+        <v>1964</v>
       </c>
       <c r="H986" s="6" t="n">
         <v>46275.472800926</v>
@@ -63556,7 +63601,7 @@
         <v>1118</v>
       </c>
       <c r="G987" s="9" t="s">
-        <v>1969</v>
+        <v>1965</v>
       </c>
       <c r="H987" s="11" t="n">
         <v>46276.641041667</v>
@@ -63614,7 +63659,7 @@
         <v>1296</v>
       </c>
       <c r="G988" s="4" t="s">
-        <v>1970</v>
+        <v>1966</v>
       </c>
       <c r="H988" s="6" t="n">
         <v>46276.445613426</v>
@@ -63672,7 +63717,7 @@
         <v>478</v>
       </c>
       <c r="G989" s="9" t="s">
-        <v>1971</v>
+        <v>1967</v>
       </c>
       <c r="H989" s="11" t="n">
         <v>46275.859097222</v>
@@ -63730,7 +63775,7 @@
         <v>496</v>
       </c>
       <c r="G990" s="4" t="s">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="H990" s="6" t="n">
         <v>46276.36244213</v>
@@ -63788,7 +63833,7 @@
         <v>1427</v>
       </c>
       <c r="G991" s="9" t="s">
-        <v>1973</v>
+        <v>1969</v>
       </c>
       <c r="H991" s="11" t="n">
         <v>46276.780416667</v>
@@ -63846,7 +63891,7 @@
         <v>1292</v>
       </c>
       <c r="G992" s="4" t="s">
-        <v>1974</v>
+        <v>1970</v>
       </c>
       <c r="H992" s="6" t="n">
         <v>46276.750868056</v>
@@ -63904,7 +63949,7 @@
         <v>1668</v>
       </c>
       <c r="G993" s="9" t="s">
-        <v>1975</v>
+        <v>1971</v>
       </c>
       <c r="H993" s="11" t="n">
         <v>46276.782905093</v>
@@ -63962,24 +64007,24 @@
         <v>1162</v>
       </c>
       <c r="G994" s="4" t="s">
-        <v>1976</v>
+        <v>1972</v>
       </c>
       <c r="H994" s="5" t="n">
         <v>46276</v>
       </c>
       <c r="I994" s="4" t="s">
-        <v>1977</v>
+        <v>1973</v>
       </c>
       <c r="J994" s="4" t="s">
         <v>1165</v>
       </c>
       <c r="K994" s="4" t="s">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="L994" s="5"/>
       <c r="M994" s="5"/>
       <c r="N994" s="4" t="s">
-        <v>1810</v>
+        <v>1975</v>
       </c>
       <c r="O994" s="6" t="n">
         <v>46279.599731713</v>
@@ -64017,10 +64062,10 @@
         <v>24</v>
       </c>
       <c r="F995" s="9" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="G995" s="9" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="H995" s="10" t="n">
         <v>46276</v>
@@ -64078,7 +64123,7 @@
         <v>592</v>
       </c>
       <c r="G996" s="4" t="s">
-        <v>1980</v>
+        <v>1977</v>
       </c>
       <c r="H996" s="6" t="n">
         <v>46279.943194444</v>
@@ -64136,7 +64181,7 @@
         <v>262</v>
       </c>
       <c r="G997" s="9" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
       <c r="H997" s="11" t="n">
         <v>46280.741736111</v>
@@ -64194,7 +64239,7 @@
         <v>194</v>
       </c>
       <c r="G998" s="4" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="H998" s="5" t="n">
         <v>46279</v>
@@ -64252,7 +64297,7 @@
         <v>389</v>
       </c>
       <c r="G999" s="9" t="s">
-        <v>1983</v>
+        <v>1980</v>
       </c>
       <c r="H999" s="11" t="n">
         <v>46280.714386574</v>
@@ -64304,13 +64349,13 @@
         <v>23</v>
       </c>
       <c r="E1000" s="3" t="s">
-        <v>285</v>
+        <v>1981</v>
       </c>
       <c r="F1000" s="4" t="s">
         <v>75</v>
       </c>
       <c r="G1000" s="4" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="H1000" s="6" t="n">
         <v>46280.693761574</v>
@@ -64327,7 +64372,7 @@
       <c r="L1000" s="5"/>
       <c r="M1000" s="5"/>
       <c r="N1000" s="4" t="s">
-        <v>1810</v>
+        <v>1288</v>
       </c>
       <c r="O1000" s="6" t="n">
         <v>46281.662435336</v>
@@ -64342,7 +64387,7 @@
         <v>885906</v>
       </c>
       <c r="S1000" s="7" t="n">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="T1000" s="4" t="s">
         <v>32</v>
@@ -64368,7 +64413,7 @@
         <v>965</v>
       </c>
       <c r="G1001" s="9" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="H1001" s="11" t="n">
         <v>46280.868599537</v>
@@ -64426,7 +64471,7 @@
         <v>366</v>
       </c>
       <c r="G1002" s="4" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="H1002" s="5" t="n">
         <v>46280</v>
@@ -64481,22 +64526,22 @@
         <v>24</v>
       </c>
       <c r="F1003" s="9" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="G1003" s="9" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="H1003" s="11" t="n">
         <v>46281.483981481</v>
       </c>
       <c r="I1003" s="9" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="J1003" s="9" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="K1003" s="9" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="L1003" s="10"/>
       <c r="M1003" s="10"/>
@@ -64542,7 +64587,7 @@
         <v>623</v>
       </c>
       <c r="G1004" s="4" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="H1004" s="6" t="n">
         <v>46281.591608796</v>
@@ -64600,7 +64645,7 @@
         <v>1537</v>
       </c>
       <c r="G1005" s="9" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="H1005" s="10" t="n">
         <v>46282</v>
@@ -64658,7 +64703,7 @@
         <v>1638</v>
       </c>
       <c r="G1006" s="4" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="H1006" s="5" t="n">
         <v>46282</v>
@@ -64710,13 +64755,13 @@
         <v>23</v>
       </c>
       <c r="E1007" s="8" t="s">
-        <v>1805</v>
+        <v>1992</v>
       </c>
       <c r="F1007" s="9" t="s">
+        <v>1993</v>
+      </c>
+      <c r="G1007" s="9" t="s">
         <v>1994</v>
-      </c>
-      <c r="G1007" s="9" t="s">
-        <v>1995</v>
       </c>
       <c r="H1007" s="11" t="n">
         <v>46282.690821759</v>
@@ -64771,22 +64816,22 @@
         <v>24</v>
       </c>
       <c r="F1008" s="4" t="s">
+        <v>1995</v>
+      </c>
+      <c r="G1008" s="4" t="s">
         <v>1996</v>
-      </c>
-      <c r="G1008" s="4" t="s">
-        <v>1997</v>
       </c>
       <c r="H1008" s="6" t="n">
         <v>46283.62880787</v>
       </c>
       <c r="I1008" s="4" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="J1008" s="4" t="s">
+        <v>1997</v>
+      </c>
+      <c r="K1008" s="4" t="s">
         <v>1998</v>
-      </c>
-      <c r="K1008" s="4" t="s">
-        <v>1999</v>
       </c>
       <c r="L1008" s="5"/>
       <c r="M1008" s="5"/>
@@ -64832,7 +64877,7 @@
         <v>253</v>
       </c>
       <c r="G1009" s="9" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H1009" s="11" t="n">
         <v>46282.73755787</v>
@@ -64890,7 +64935,7 @@
         <v>1515</v>
       </c>
       <c r="G1010" s="4" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H1010" s="5" t="n">
         <v>46286</v>
@@ -64945,10 +64990,10 @@
         <v>24</v>
       </c>
       <c r="F1011" s="9" t="s">
+        <v>2001</v>
+      </c>
+      <c r="G1011" s="9" t="s">
         <v>2002</v>
-      </c>
-      <c r="G1011" s="9" t="s">
-        <v>2003</v>
       </c>
       <c r="H1011" s="10" t="n">
         <v>46286</v>
@@ -65006,7 +65051,7 @@
         <v>58</v>
       </c>
       <c r="G1012" s="4" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H1012" s="6" t="n">
         <v>46283.945405093</v>
@@ -65064,7 +65109,7 @@
         <v>152</v>
       </c>
       <c r="G1013" s="9" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H1013" s="11" t="n">
         <v>46283.947222222</v>
@@ -65122,7 +65167,7 @@
         <v>1630</v>
       </c>
       <c r="G1014" s="4" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H1014" s="6" t="n">
         <v>46286.665289352</v>
@@ -65174,13 +65219,13 @@
         <v>23</v>
       </c>
       <c r="E1015" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1015" s="9" t="s">
         <v>892</v>
       </c>
       <c r="G1015" s="9" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H1015" s="11" t="n">
         <v>46286.490671296</v>
@@ -65197,7 +65242,7 @@
       <c r="L1015" s="10"/>
       <c r="M1015" s="10"/>
       <c r="N1015" s="9" t="s">
-        <v>1810</v>
+        <v>29</v>
       </c>
       <c r="O1015" s="11" t="n">
         <v>46288.359700694</v>
@@ -65212,7 +65257,7 @@
         <v>4000</v>
       </c>
       <c r="S1015" s="12" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T1015" s="9" t="s">
         <v>32</v>
@@ -65232,7 +65277,7 @@
         <v>23</v>
       </c>
       <c r="E1016" s="3" t="s">
-        <v>285</v>
+        <v>2007</v>
       </c>
       <c r="F1016" s="4" t="s">
         <v>1628</v>
@@ -65255,7 +65300,7 @@
       <c r="L1016" s="5"/>
       <c r="M1016" s="5"/>
       <c r="N1016" s="4" t="s">
-        <v>1810</v>
+        <v>1288</v>
       </c>
       <c r="O1016" s="6" t="n">
         <v>46288.361034063</v>
@@ -65270,7 +65315,7 @@
         <v>41328</v>
       </c>
       <c r="S1016" s="7" t="n">
-        <v>0</v>
+        <v>9840</v>
       </c>
       <c r="T1016" s="4" t="s">
         <v>32</v>
@@ -65371,7 +65416,7 @@
       <c r="L1018" s="5"/>
       <c r="M1018" s="5"/>
       <c r="N1018" s="4" t="s">
-        <v>1810</v>
+        <v>1975</v>
       </c>
       <c r="O1018" s="6" t="n">
         <v>46289.388101852</v>
@@ -65406,7 +65451,7 @@
         <v>23</v>
       </c>
       <c r="E1019" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1019" s="9" t="s">
         <v>402</v>
@@ -65429,7 +65474,7 @@
       <c r="L1019" s="10"/>
       <c r="M1019" s="10"/>
       <c r="N1019" s="9" t="s">
-        <v>1810</v>
+        <v>29</v>
       </c>
       <c r="O1019" s="11" t="n">
         <v>46289.388410069</v>
@@ -65444,7 +65489,7 @@
         <v>12900</v>
       </c>
       <c r="S1019" s="12" t="n">
-        <v>0</v>
+        <v>12900</v>
       </c>
       <c r="T1019" s="9" t="s">
         <v>32</v>
@@ -65522,7 +65567,7 @@
         <v>23</v>
       </c>
       <c r="E1021" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1021" s="9" t="s">
         <v>347</v>
@@ -65545,7 +65590,7 @@
       <c r="L1021" s="10"/>
       <c r="M1021" s="10"/>
       <c r="N1021" s="9" t="s">
-        <v>1810</v>
+        <v>29</v>
       </c>
       <c r="O1021" s="11" t="n">
         <v>46289.388875926</v>
@@ -65560,7 +65605,7 @@
         <v>8375.1</v>
       </c>
       <c r="S1021" s="12" t="n">
-        <v>0</v>
+        <v>8375.1</v>
       </c>
       <c r="T1021" s="9" t="s">
         <v>32</v>
@@ -65583,7 +65628,7 @@
         <v>24</v>
       </c>
       <c r="F1022" s="4" t="s">
-        <v>1950</v>
+        <v>1946</v>
       </c>
       <c r="G1022" s="4" t="s">
         <v>2017</v>
@@ -65592,13 +65637,13 @@
         <v>46288.63568287</v>
       </c>
       <c r="I1022" s="4" t="s">
-        <v>1950</v>
+        <v>1946</v>
       </c>
       <c r="J1022" s="4" t="s">
-        <v>1952</v>
+        <v>1948</v>
       </c>
       <c r="K1022" s="4" t="s">
-        <v>1953</v>
+        <v>1949</v>
       </c>
       <c r="L1022" s="5"/>
       <c r="M1022" s="5"/>
@@ -65754,13 +65799,13 @@
         <v>23</v>
       </c>
       <c r="E1025" s="8" t="s">
-        <v>2021</v>
+        <v>24</v>
       </c>
       <c r="F1025" s="9" t="s">
         <v>366</v>
       </c>
       <c r="G1025" s="9" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H1025" s="10" t="n">
         <v>46288</v>
@@ -65777,7 +65822,7 @@
       <c r="L1025" s="10"/>
       <c r="M1025" s="10"/>
       <c r="N1025" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O1025" s="11" t="n">
         <v>46289.408104514</v>
@@ -65792,7 +65837,7 @@
         <v>27234</v>
       </c>
       <c r="S1025" s="12" t="n">
-        <v>5607</v>
+        <v>27234</v>
       </c>
       <c r="T1025" s="9" t="s">
         <v>32</v>
@@ -65818,7 +65863,7 @@
         <v>1264</v>
       </c>
       <c r="G1026" s="4" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H1026" s="5" t="n">
         <v>46288</v>
@@ -65835,7 +65880,7 @@
       <c r="L1026" s="5"/>
       <c r="M1026" s="5"/>
       <c r="N1026" s="4" t="s">
-        <v>1810</v>
+        <v>1975</v>
       </c>
       <c r="O1026" s="6" t="n">
         <v>46289.410022488</v>
@@ -65870,13 +65915,13 @@
         <v>23</v>
       </c>
       <c r="E1027" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1027" s="9" t="s">
         <v>1638</v>
       </c>
       <c r="G1027" s="9" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H1027" s="10" t="n">
         <v>46289</v>
@@ -65893,7 +65938,7 @@
       <c r="L1027" s="10"/>
       <c r="M1027" s="10"/>
       <c r="N1027" s="9" t="s">
-        <v>1810</v>
+        <v>29</v>
       </c>
       <c r="O1027" s="11" t="n">
         <v>46289.617490625</v>
@@ -65908,7 +65953,7 @@
         <v>21290.5</v>
       </c>
       <c r="S1027" s="12" t="n">
-        <v>0</v>
+        <v>21290.5</v>
       </c>
       <c r="T1027" s="9" t="s">
         <v>32</v>
@@ -65928,13 +65973,13 @@
         <v>23</v>
       </c>
       <c r="E1028" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1028" s="4" t="s">
+        <v>2024</v>
+      </c>
+      <c r="G1028" s="4" t="s">
         <v>2025</v>
-      </c>
-      <c r="G1028" s="4" t="s">
-        <v>2026</v>
       </c>
       <c r="H1028" s="6" t="n">
         <v>46288.697777778</v>
@@ -65951,7 +65996,7 @@
       <c r="L1028" s="5"/>
       <c r="M1028" s="5"/>
       <c r="N1028" s="4" t="s">
-        <v>1810</v>
+        <v>29</v>
       </c>
       <c r="O1028" s="6" t="n">
         <v>46289.622865278</v>
@@ -65966,7 +66011,7 @@
         <v>104654.4</v>
       </c>
       <c r="S1028" s="7" t="n">
-        <v>0</v>
+        <v>104654.4</v>
       </c>
       <c r="T1028" s="4" t="s">
         <v>32</v>
@@ -65986,13 +66031,13 @@
         <v>23</v>
       </c>
       <c r="E1029" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1029" s="9" t="s">
         <v>490</v>
       </c>
       <c r="G1029" s="9" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="H1029" s="11" t="n">
         <v>46288.708703704</v>
@@ -66009,7 +66054,7 @@
       <c r="L1029" s="10"/>
       <c r="M1029" s="10"/>
       <c r="N1029" s="9" t="s">
-        <v>1810</v>
+        <v>29</v>
       </c>
       <c r="O1029" s="11" t="n">
         <v>46289.622969942</v>
@@ -66024,7 +66069,7 @@
         <v>21000</v>
       </c>
       <c r="S1029" s="12" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="T1029" s="9" t="s">
         <v>32</v>
@@ -66044,13 +66089,13 @@
         <v>23</v>
       </c>
       <c r="E1030" s="3" t="s">
-        <v>2028</v>
+        <v>24</v>
       </c>
       <c r="F1030" s="4" t="s">
         <v>262</v>
       </c>
       <c r="G1030" s="4" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="H1030" s="6" t="n">
         <v>46288.727013889</v>
@@ -66067,7 +66112,7 @@
       <c r="L1030" s="5"/>
       <c r="M1030" s="5"/>
       <c r="N1030" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O1030" s="6" t="n">
         <v>46289.62317581</v>
@@ -66082,7 +66127,7 @@
         <v>20210.64</v>
       </c>
       <c r="S1030" s="7" t="n">
-        <v>8402.64</v>
+        <v>20210.64</v>
       </c>
       <c r="T1030" s="4" t="s">
         <v>32</v>
@@ -66090,35 +66135,673 @@
       <c r="U1030" s="4"/>
       <c r="V1030" s="4"/>
     </row>
-    <row r="1031" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A1031" s="13" t="n">
-        <v>1029</v>
-      </c>
-      <c r="B1031" s="14"/>
-      <c r="C1031" s="14"/>
-      <c r="D1031" s="14"/>
-      <c r="E1031" s="14"/>
-      <c r="F1031" s="14"/>
-      <c r="G1031" s="14"/>
-      <c r="H1031" s="14"/>
-      <c r="I1031" s="14"/>
-      <c r="J1031" s="14"/>
-      <c r="K1031" s="14"/>
-      <c r="L1031" s="14"/>
-      <c r="M1031" s="14"/>
-      <c r="N1031" s="14"/>
-      <c r="O1031" s="14"/>
-      <c r="P1031" s="14"/>
-      <c r="Q1031" s="14"/>
-      <c r="R1031" s="15" t="n">
-        <v>61800808.5406</v>
-      </c>
-      <c r="S1031" s="15" t="n">
-        <v>59036797.1806</v>
-      </c>
-      <c r="T1031" s="14"/>
-      <c r="U1031" s="14"/>
-      <c r="V1031" s="16"/>
+    <row r="1031" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1031" s="8" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B1031" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1031" s="9"/>
+      <c r="D1031" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1031" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1031" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="G1031" s="9" t="s">
+        <v>2028</v>
+      </c>
+      <c r="H1031" s="11" t="n">
+        <v>46293.413449074</v>
+      </c>
+      <c r="I1031" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="J1031" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="K1031" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1031" s="10"/>
+      <c r="M1031" s="10"/>
+      <c r="N1031" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1031" s="11" t="n">
+        <v>46293.621319016</v>
+      </c>
+      <c r="P1031" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1031" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1031" s="12" t="n">
+        <v>12015</v>
+      </c>
+      <c r="S1031" s="12" t="n">
+        <v>12015</v>
+      </c>
+      <c r="T1031" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1031" s="9"/>
+      <c r="V1031" s="9"/>
+    </row>
+    <row r="1032" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1032" s="3" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B1032" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1032" s="4"/>
+      <c r="D1032" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1032" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1032" s="4" t="s">
+        <v>1783</v>
+      </c>
+      <c r="G1032" s="4" t="s">
+        <v>2029</v>
+      </c>
+      <c r="H1032" s="6" t="n">
+        <v>46290.399768519</v>
+      </c>
+      <c r="I1032" s="4" t="s">
+        <v>1783</v>
+      </c>
+      <c r="J1032" s="4" t="s">
+        <v>1785</v>
+      </c>
+      <c r="K1032" s="4" t="s">
+        <v>1786</v>
+      </c>
+      <c r="L1032" s="5"/>
+      <c r="M1032" s="5"/>
+      <c r="N1032" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1032" s="6" t="n">
+        <v>46293.621487616</v>
+      </c>
+      <c r="P1032" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1032" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="R1032" s="7" t="n">
+        <v>8379.56</v>
+      </c>
+      <c r="S1032" s="7" t="n">
+        <v>8379.56</v>
+      </c>
+      <c r="T1032" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="U1032" s="4"/>
+      <c r="V1032" s="4"/>
+    </row>
+    <row r="1033" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1033" s="8" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B1033" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1033" s="9"/>
+      <c r="D1033" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1033" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1033" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1033" s="9" t="s">
+        <v>2030</v>
+      </c>
+      <c r="H1033" s="11" t="n">
+        <v>46293.420972222</v>
+      </c>
+      <c r="I1033" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1033" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1033" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1033" s="10"/>
+      <c r="M1033" s="10"/>
+      <c r="N1033" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1033" s="11" t="n">
+        <v>46293.621619595</v>
+      </c>
+      <c r="P1033" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1033" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1033" s="12" t="n">
+        <v>20145</v>
+      </c>
+      <c r="S1033" s="12" t="n">
+        <v>20145</v>
+      </c>
+      <c r="T1033" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1033" s="9"/>
+      <c r="V1033" s="9"/>
+    </row>
+    <row r="1034" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1034" s="3" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B1034" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1034" s="4"/>
+      <c r="D1034" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1034" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1034" s="4" t="s">
+        <v>1545</v>
+      </c>
+      <c r="G1034" s="4" t="s">
+        <v>2031</v>
+      </c>
+      <c r="H1034" s="6" t="n">
+        <v>46289.403217593</v>
+      </c>
+      <c r="I1034" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1034" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="K1034" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="L1034" s="5"/>
+      <c r="M1034" s="5"/>
+      <c r="N1034" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1034" s="6" t="n">
+        <v>46293.621827083</v>
+      </c>
+      <c r="P1034" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1034" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1034" s="7" t="n">
+        <v>9750</v>
+      </c>
+      <c r="S1034" s="7" t="n">
+        <v>9750</v>
+      </c>
+      <c r="T1034" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1034" s="4"/>
+      <c r="V1034" s="4"/>
+    </row>
+    <row r="1035" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1035" s="8" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B1035" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1035" s="9"/>
+      <c r="D1035" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1035" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1035" s="9" t="s">
+        <v>2032</v>
+      </c>
+      <c r="G1035" s="9" t="s">
+        <v>2033</v>
+      </c>
+      <c r="H1035" s="11" t="n">
+        <v>46289.956689815</v>
+      </c>
+      <c r="I1035" s="9" t="s">
+        <v>2032</v>
+      </c>
+      <c r="J1035" s="9" t="s">
+        <v>2034</v>
+      </c>
+      <c r="K1035" s="9" t="s">
+        <v>2035</v>
+      </c>
+      <c r="L1035" s="10"/>
+      <c r="M1035" s="10"/>
+      <c r="N1035" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1035" s="11" t="n">
+        <v>46293.621978391</v>
+      </c>
+      <c r="P1035" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1035" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1035" s="12" t="n">
+        <v>42000</v>
+      </c>
+      <c r="S1035" s="12" t="n">
+        <v>42000</v>
+      </c>
+      <c r="T1035" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1035" s="9"/>
+      <c r="V1035" s="9"/>
+    </row>
+    <row r="1036" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1036" s="3" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B1036" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1036" s="4"/>
+      <c r="D1036" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1036" s="3" t="s">
+        <v>2036</v>
+      </c>
+      <c r="F1036" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="G1036" s="4" t="s">
+        <v>2037</v>
+      </c>
+      <c r="H1036" s="6" t="n">
+        <v>46293.739594907</v>
+      </c>
+      <c r="I1036" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="J1036" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="K1036" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="L1036" s="5"/>
+      <c r="M1036" s="5"/>
+      <c r="N1036" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O1036" s="6" t="n">
+        <v>46294.385012234</v>
+      </c>
+      <c r="P1036" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1036" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="R1036" s="7" t="n">
+        <v>144576.9</v>
+      </c>
+      <c r="S1036" s="7" t="n">
+        <v>50424</v>
+      </c>
+      <c r="T1036" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1036" s="4"/>
+      <c r="V1036" s="4"/>
+    </row>
+    <row r="1037" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1037" s="8" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B1037" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1037" s="9"/>
+      <c r="D1037" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1037" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1037" s="9" t="s">
+        <v>2032</v>
+      </c>
+      <c r="G1037" s="9" t="s">
+        <v>2038</v>
+      </c>
+      <c r="H1037" s="11" t="n">
+        <v>46293.720231481</v>
+      </c>
+      <c r="I1037" s="9" t="s">
+        <v>2032</v>
+      </c>
+      <c r="J1037" s="9" t="s">
+        <v>2034</v>
+      </c>
+      <c r="K1037" s="9" t="s">
+        <v>2035</v>
+      </c>
+      <c r="L1037" s="10"/>
+      <c r="M1037" s="10"/>
+      <c r="N1037" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1037" s="11" t="n">
+        <v>46294.703747801</v>
+      </c>
+      <c r="P1037" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1037" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1037" s="12" t="n">
+        <v>6300</v>
+      </c>
+      <c r="S1037" s="12" t="n">
+        <v>6300</v>
+      </c>
+      <c r="T1037" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1037" s="9"/>
+      <c r="V1037" s="9"/>
+    </row>
+    <row r="1038" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1038" s="3" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B1038" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1038" s="4"/>
+      <c r="D1038" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1038" s="3" t="s">
+        <v>2039</v>
+      </c>
+      <c r="F1038" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="G1038" s="4" t="s">
+        <v>2040</v>
+      </c>
+      <c r="H1038" s="6" t="n">
+        <v>46294.490601852</v>
+      </c>
+      <c r="I1038" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1038" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1038" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L1038" s="5"/>
+      <c r="M1038" s="5"/>
+      <c r="N1038" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O1038" s="6" t="n">
+        <v>46294.703961343</v>
+      </c>
+      <c r="P1038" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1038" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1038" s="7" t="n">
+        <v>140027.6</v>
+      </c>
+      <c r="S1038" s="7" t="n">
+        <v>62992.2</v>
+      </c>
+      <c r="T1038" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1038" s="4"/>
+      <c r="V1038" s="4"/>
+    </row>
+    <row r="1039" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1039" s="8" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B1039" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1039" s="9"/>
+      <c r="D1039" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1039" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1039" s="9" t="s">
+        <v>2041</v>
+      </c>
+      <c r="G1039" s="9" t="s">
+        <v>2042</v>
+      </c>
+      <c r="H1039" s="10" t="n">
+        <v>46294</v>
+      </c>
+      <c r="I1039" s="9" t="s">
+        <v>1755</v>
+      </c>
+      <c r="J1039" s="9" t="s">
+        <v>1755</v>
+      </c>
+      <c r="K1039" s="9" t="s">
+        <v>1756</v>
+      </c>
+      <c r="L1039" s="10"/>
+      <c r="M1039" s="10"/>
+      <c r="N1039" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1039" s="11" t="n">
+        <v>46294.708252662</v>
+      </c>
+      <c r="P1039" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1039" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1039" s="12" t="n">
+        <v>2700</v>
+      </c>
+      <c r="S1039" s="12" t="n">
+        <v>2700</v>
+      </c>
+      <c r="T1039" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1039" s="9"/>
+      <c r="V1039" s="9"/>
+    </row>
+    <row r="1040" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1040" s="3" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B1040" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1040" s="4"/>
+      <c r="D1040" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1040" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1040" s="4" t="s">
+        <v>1515</v>
+      </c>
+      <c r="G1040" s="4" t="s">
+        <v>2043</v>
+      </c>
+      <c r="H1040" s="5" t="n">
+        <v>46294</v>
+      </c>
+      <c r="I1040" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="J1040" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="K1040" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="L1040" s="5"/>
+      <c r="M1040" s="5"/>
+      <c r="N1040" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1040" s="6" t="n">
+        <v>46294.710484873</v>
+      </c>
+      <c r="P1040" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1040" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1040" s="7" t="n">
+        <v>5508</v>
+      </c>
+      <c r="S1040" s="7" t="n">
+        <v>5508</v>
+      </c>
+      <c r="T1040" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1040" s="4"/>
+      <c r="V1040" s="4"/>
+    </row>
+    <row r="1041" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1041" s="8" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B1041" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1041" s="9"/>
+      <c r="D1041" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1041" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1041" s="9" t="s">
+        <v>969</v>
+      </c>
+      <c r="G1041" s="9" t="s">
+        <v>2044</v>
+      </c>
+      <c r="H1041" s="10" t="n">
+        <v>46290</v>
+      </c>
+      <c r="I1041" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="J1041" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="K1041" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="L1041" s="10"/>
+      <c r="M1041" s="10"/>
+      <c r="N1041" s="9" t="s">
+        <v>1975</v>
+      </c>
+      <c r="O1041" s="11" t="n">
+        <v>46294.712779132</v>
+      </c>
+      <c r="P1041" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1041" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1041" s="12" t="n">
+        <v>6493.6</v>
+      </c>
+      <c r="S1041" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1041" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1041" s="9"/>
+      <c r="V1041" s="9"/>
+    </row>
+    <row r="1042" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A1042" s="13" t="n">
+        <v>1040</v>
+      </c>
+      <c r="B1042" s="14"/>
+      <c r="C1042" s="14"/>
+      <c r="D1042" s="14"/>
+      <c r="E1042" s="14"/>
+      <c r="F1042" s="14"/>
+      <c r="G1042" s="14"/>
+      <c r="H1042" s="14"/>
+      <c r="I1042" s="14"/>
+      <c r="J1042" s="14"/>
+      <c r="K1042" s="14"/>
+      <c r="L1042" s="14"/>
+      <c r="M1042" s="14"/>
+      <c r="N1042" s="14"/>
+      <c r="O1042" s="14"/>
+      <c r="P1042" s="14"/>
+      <c r="Q1042" s="14"/>
+      <c r="R1042" s="15" t="n">
+        <v>62198704.2006</v>
+      </c>
+      <c r="S1042" s="15" t="n">
+        <v>59641285.2406</v>
+      </c>
+      <c r="T1042" s="14"/>
+      <c r="U1042" s="14"/>
+      <c r="V1042" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="2045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="2068">
   <si>
     <t>ID</t>
   </si>
@@ -5826,9 +5826,6 @@
     <t>1201</t>
   </si>
   <si>
-    <t>53 %</t>
-  </si>
-  <si>
     <t>1202</t>
   </si>
   <si>
@@ -5895,9 +5892,6 @@
     <t>1216</t>
   </si>
   <si>
-    <t>60 %</t>
-  </si>
-  <si>
     <t>1217</t>
   </si>
   <si>
@@ -6148,6 +6142,81 @@
   </si>
   <si>
     <t>1275</t>
+  </si>
+  <si>
+    <t>1276</t>
+  </si>
+  <si>
+    <t>1277</t>
+  </si>
+  <si>
+    <t>1278</t>
+  </si>
+  <si>
+    <t>1279</t>
+  </si>
+  <si>
+    <t>1280</t>
+  </si>
+  <si>
+    <t>OBRA PRIVADA - INTERNA</t>
+  </si>
+  <si>
+    <t>1281</t>
+  </si>
+  <si>
+    <t>EM ANDAMENTO</t>
+  </si>
+  <si>
+    <t>DISDROL</t>
+  </si>
+  <si>
+    <t>1282</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA DE DROGAS LTDA</t>
+  </si>
+  <si>
+    <t>06.872.949/0001-68</t>
+  </si>
+  <si>
+    <t>36 %</t>
+  </si>
+  <si>
+    <t>CIRÚRGICA BEZERRA</t>
+  </si>
+  <si>
+    <t>1283</t>
+  </si>
+  <si>
+    <t>1284</t>
+  </si>
+  <si>
+    <t>1285</t>
+  </si>
+  <si>
+    <t>CAMEDIC COMERCIAL</t>
+  </si>
+  <si>
+    <t>1286</t>
+  </si>
+  <si>
+    <t>1287</t>
+  </si>
+  <si>
+    <t>PROVIDA DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1288</t>
+  </si>
+  <si>
+    <t>PROVIDA DISTRIBUIDORA DE MEDICAMENTOS E PRODUTOS H</t>
+  </si>
+  <si>
+    <t>42.259.522/0001-52</t>
+  </si>
+  <si>
+    <t>JULIANO PRIMAVERA</t>
   </si>
 </sst>
 </file>
@@ -6341,7 +6410,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V1042"/>
+  <dimension ref="A1:V1055"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -62493,13 +62562,13 @@
         <v>23</v>
       </c>
       <c r="E968" s="3" t="s">
-        <v>1937</v>
+        <v>24</v>
       </c>
       <c r="F968" s="4" t="s">
         <v>1495</v>
       </c>
       <c r="G968" s="4" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H968" s="6" t="n">
         <v>46268.442615741</v>
@@ -62528,7 +62597,7 @@
         <v>31</v>
       </c>
       <c r="R968" s="7" t="n">
-        <v>59790</v>
+        <v>31968</v>
       </c>
       <c r="S968" s="7" t="n">
         <v>31968</v>
@@ -62557,7 +62626,7 @@
         <v>157</v>
       </c>
       <c r="G969" s="9" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H969" s="10" t="n">
         <v>46268</v>
@@ -62615,7 +62684,7 @@
         <v>969</v>
       </c>
       <c r="G970" s="4" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="H970" s="5" t="n">
         <v>46268</v>
@@ -62670,10 +62739,10 @@
         <v>24</v>
       </c>
       <c r="F971" s="9" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G971" s="9" t="s">
         <v>1941</v>
-      </c>
-      <c r="G971" s="9" t="s">
-        <v>1942</v>
       </c>
       <c r="H971" s="10" t="n">
         <v>46273</v>
@@ -62725,13 +62794,13 @@
         <v>23</v>
       </c>
       <c r="E972" s="3" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="F972" s="4" t="s">
         <v>1264</v>
       </c>
       <c r="G972" s="4" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="H972" s="5" t="n">
         <v>46273</v>
@@ -62789,7 +62858,7 @@
         <v>152</v>
       </c>
       <c r="G973" s="9" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="H973" s="11" t="n">
         <v>46273.758136574</v>
@@ -62844,22 +62913,22 @@
         <v>24</v>
       </c>
       <c r="F974" s="4" t="s">
+        <v>1945</v>
+      </c>
+      <c r="G974" s="4" t="s">
         <v>1946</v>
-      </c>
-      <c r="G974" s="4" t="s">
-        <v>1947</v>
       </c>
       <c r="H974" s="6" t="n">
         <v>46273.740416667</v>
       </c>
       <c r="I974" s="4" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="J974" s="4" t="s">
+        <v>1947</v>
+      </c>
+      <c r="K974" s="4" t="s">
         <v>1948</v>
-      </c>
-      <c r="K974" s="4" t="s">
-        <v>1949</v>
       </c>
       <c r="L974" s="5"/>
       <c r="M974" s="5"/>
@@ -62905,7 +62974,7 @@
         <v>1411</v>
       </c>
       <c r="G975" s="9" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="H975" s="11" t="n">
         <v>46273.780162037</v>
@@ -62960,10 +63029,10 @@
         <v>24</v>
       </c>
       <c r="F976" s="4" t="s">
+        <v>1950</v>
+      </c>
+      <c r="G976" s="4" t="s">
         <v>1951</v>
-      </c>
-      <c r="G976" s="4" t="s">
-        <v>1952</v>
       </c>
       <c r="H976" s="6" t="n">
         <v>46274.442685185</v>
@@ -63018,10 +63087,10 @@
         <v>24</v>
       </c>
       <c r="F977" s="9" t="s">
+        <v>1952</v>
+      </c>
+      <c r="G977" s="9" t="s">
         <v>1953</v>
-      </c>
-      <c r="G977" s="9" t="s">
-        <v>1954</v>
       </c>
       <c r="H977" s="10" t="n">
         <v>46273</v>
@@ -63079,7 +63148,7 @@
         <v>355</v>
       </c>
       <c r="G978" s="4" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="H978" s="5" t="n">
         <v>46274</v>
@@ -63137,7 +63206,7 @@
         <v>152</v>
       </c>
       <c r="G979" s="9" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="H979" s="10" t="n">
         <v>46273</v>
@@ -63195,7 +63264,7 @@
         <v>1214</v>
       </c>
       <c r="G980" s="4" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="H980" s="5" t="n">
         <v>46275</v>
@@ -63253,7 +63322,7 @@
         <v>215</v>
       </c>
       <c r="G981" s="9" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="H981" s="10" t="n">
         <v>46275</v>
@@ -63311,7 +63380,7 @@
         <v>1459</v>
       </c>
       <c r="G982" s="4" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="H982" s="6" t="n">
         <v>46274.972708333</v>
@@ -63363,13 +63432,13 @@
         <v>23</v>
       </c>
       <c r="E983" s="8" t="s">
-        <v>1960</v>
+        <v>24</v>
       </c>
       <c r="F983" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G983" s="9" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="H983" s="11" t="n">
         <v>46274.976979167</v>
@@ -63386,7 +63455,7 @@
       <c r="L983" s="10"/>
       <c r="M983" s="10"/>
       <c r="N983" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O983" s="11" t="n">
         <v>46275.628351887</v>
@@ -63401,7 +63470,7 @@
         <v>94188</v>
       </c>
       <c r="S983" s="12" t="n">
-        <v>56400</v>
+        <v>94188</v>
       </c>
       <c r="T983" s="9" t="s">
         <v>32</v>
@@ -63427,7 +63496,7 @@
         <v>276</v>
       </c>
       <c r="G984" s="4" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="H984" s="6" t="n">
         <v>46274.703055556</v>
@@ -63485,7 +63554,7 @@
         <v>75</v>
       </c>
       <c r="G985" s="9" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="H985" s="11" t="n">
         <v>46274.682534722</v>
@@ -63543,7 +63612,7 @@
         <v>1196</v>
       </c>
       <c r="G986" s="4" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="H986" s="6" t="n">
         <v>46275.472800926</v>
@@ -63601,7 +63670,7 @@
         <v>1118</v>
       </c>
       <c r="G987" s="9" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="H987" s="11" t="n">
         <v>46276.641041667</v>
@@ -63659,7 +63728,7 @@
         <v>1296</v>
       </c>
       <c r="G988" s="4" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="H988" s="6" t="n">
         <v>46276.445613426</v>
@@ -63717,7 +63786,7 @@
         <v>478</v>
       </c>
       <c r="G989" s="9" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="H989" s="11" t="n">
         <v>46275.859097222</v>
@@ -63775,7 +63844,7 @@
         <v>496</v>
       </c>
       <c r="G990" s="4" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="H990" s="6" t="n">
         <v>46276.36244213</v>
@@ -63833,7 +63902,7 @@
         <v>1427</v>
       </c>
       <c r="G991" s="9" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="H991" s="11" t="n">
         <v>46276.780416667</v>
@@ -63891,7 +63960,7 @@
         <v>1292</v>
       </c>
       <c r="G992" s="4" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="H992" s="6" t="n">
         <v>46276.750868056</v>
@@ -63949,7 +64018,7 @@
         <v>1668</v>
       </c>
       <c r="G993" s="9" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="H993" s="11" t="n">
         <v>46276.782905093</v>
@@ -64007,24 +64076,24 @@
         <v>1162</v>
       </c>
       <c r="G994" s="4" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="H994" s="5" t="n">
         <v>46276</v>
       </c>
       <c r="I994" s="4" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="J994" s="4" t="s">
         <v>1165</v>
       </c>
       <c r="K994" s="4" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="L994" s="5"/>
       <c r="M994" s="5"/>
       <c r="N994" s="4" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="O994" s="6" t="n">
         <v>46279.599731713</v>
@@ -64065,7 +64134,7 @@
         <v>1921</v>
       </c>
       <c r="G995" s="9" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="H995" s="10" t="n">
         <v>46276</v>
@@ -64123,7 +64192,7 @@
         <v>592</v>
       </c>
       <c r="G996" s="4" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="H996" s="6" t="n">
         <v>46279.943194444</v>
@@ -64181,7 +64250,7 @@
         <v>262</v>
       </c>
       <c r="G997" s="9" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="H997" s="11" t="n">
         <v>46280.741736111</v>
@@ -64239,7 +64308,7 @@
         <v>194</v>
       </c>
       <c r="G998" s="4" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="H998" s="5" t="n">
         <v>46279</v>
@@ -64297,7 +64366,7 @@
         <v>389</v>
       </c>
       <c r="G999" s="9" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="H999" s="11" t="n">
         <v>46280.714386574</v>
@@ -64349,13 +64418,13 @@
         <v>23</v>
       </c>
       <c r="E1000" s="3" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="F1000" s="4" t="s">
         <v>75</v>
       </c>
       <c r="G1000" s="4" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="H1000" s="6" t="n">
         <v>46280.693761574</v>
@@ -64413,7 +64482,7 @@
         <v>965</v>
       </c>
       <c r="G1001" s="9" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="H1001" s="11" t="n">
         <v>46280.868599537</v>
@@ -64471,7 +64540,7 @@
         <v>366</v>
       </c>
       <c r="G1002" s="4" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="H1002" s="5" t="n">
         <v>46280</v>
@@ -64526,22 +64595,22 @@
         <v>24</v>
       </c>
       <c r="F1003" s="9" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="G1003" s="9" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="H1003" s="11" t="n">
         <v>46281.483981481</v>
       </c>
       <c r="I1003" s="9" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="J1003" s="9" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="K1003" s="9" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="L1003" s="10"/>
       <c r="M1003" s="10"/>
@@ -64587,7 +64656,7 @@
         <v>623</v>
       </c>
       <c r="G1004" s="4" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="H1004" s="6" t="n">
         <v>46281.591608796</v>
@@ -64645,7 +64714,7 @@
         <v>1537</v>
       </c>
       <c r="G1005" s="9" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="H1005" s="10" t="n">
         <v>46282</v>
@@ -64703,7 +64772,7 @@
         <v>1638</v>
       </c>
       <c r="G1006" s="4" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="H1006" s="5" t="n">
         <v>46282</v>
@@ -64755,13 +64824,13 @@
         <v>23</v>
       </c>
       <c r="E1007" s="8" t="s">
+        <v>1990</v>
+      </c>
+      <c r="F1007" s="9" t="s">
+        <v>1991</v>
+      </c>
+      <c r="G1007" s="9" t="s">
         <v>1992</v>
-      </c>
-      <c r="F1007" s="9" t="s">
-        <v>1993</v>
-      </c>
-      <c r="G1007" s="9" t="s">
-        <v>1994</v>
       </c>
       <c r="H1007" s="11" t="n">
         <v>46282.690821759</v>
@@ -64816,22 +64885,22 @@
         <v>24</v>
       </c>
       <c r="F1008" s="4" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="G1008" s="4" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="H1008" s="6" t="n">
         <v>46283.62880787</v>
       </c>
       <c r="I1008" s="4" t="s">
+        <v>1993</v>
+      </c>
+      <c r="J1008" s="4" t="s">
         <v>1995</v>
       </c>
-      <c r="J1008" s="4" t="s">
-        <v>1997</v>
-      </c>
       <c r="K1008" s="4" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="L1008" s="5"/>
       <c r="M1008" s="5"/>
@@ -64877,7 +64946,7 @@
         <v>253</v>
       </c>
       <c r="G1009" s="9" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="H1009" s="11" t="n">
         <v>46282.73755787</v>
@@ -64935,7 +65004,7 @@
         <v>1515</v>
       </c>
       <c r="G1010" s="4" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="H1010" s="5" t="n">
         <v>46286</v>
@@ -64990,10 +65059,10 @@
         <v>24</v>
       </c>
       <c r="F1011" s="9" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="G1011" s="9" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="H1011" s="10" t="n">
         <v>46286</v>
@@ -65051,7 +65120,7 @@
         <v>58</v>
       </c>
       <c r="G1012" s="4" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="H1012" s="6" t="n">
         <v>46283.945405093</v>
@@ -65109,7 +65178,7 @@
         <v>152</v>
       </c>
       <c r="G1013" s="9" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="H1013" s="11" t="n">
         <v>46283.947222222</v>
@@ -65167,7 +65236,7 @@
         <v>1630</v>
       </c>
       <c r="G1014" s="4" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="H1014" s="6" t="n">
         <v>46286.665289352</v>
@@ -65225,7 +65294,7 @@
         <v>892</v>
       </c>
       <c r="G1015" s="9" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="H1015" s="11" t="n">
         <v>46286.490671296</v>
@@ -65277,13 +65346,13 @@
         <v>23</v>
       </c>
       <c r="E1016" s="3" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="F1016" s="4" t="s">
         <v>1628</v>
       </c>
       <c r="G1016" s="4" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="H1016" s="6" t="n">
         <v>46286.636898148</v>
@@ -65341,7 +65410,7 @@
         <v>704</v>
       </c>
       <c r="G1017" s="9" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="H1017" s="11" t="n">
         <v>46287.528784722</v>
@@ -65396,27 +65465,27 @@
         <v>285</v>
       </c>
       <c r="F1018" s="4" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="G1018" s="4" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="H1018" s="6" t="n">
         <v>46287.685717593</v>
       </c>
       <c r="I1018" s="4" t="s">
+        <v>2008</v>
+      </c>
+      <c r="J1018" s="4" t="s">
         <v>2010</v>
       </c>
-      <c r="J1018" s="4" t="s">
-        <v>2012</v>
-      </c>
       <c r="K1018" s="4" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="L1018" s="5"/>
       <c r="M1018" s="5"/>
       <c r="N1018" s="4" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="O1018" s="6" t="n">
         <v>46289.388101852</v>
@@ -65457,7 +65526,7 @@
         <v>402</v>
       </c>
       <c r="G1019" s="9" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H1019" s="11" t="n">
         <v>46287.90775463</v>
@@ -65515,7 +65584,7 @@
         <v>1237</v>
       </c>
       <c r="G1020" s="4" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="H1020" s="6" t="n">
         <v>46287.518842593</v>
@@ -65573,7 +65642,7 @@
         <v>347</v>
       </c>
       <c r="G1021" s="9" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="H1021" s="11" t="n">
         <v>46288.409328704</v>
@@ -65628,22 +65697,22 @@
         <v>24</v>
       </c>
       <c r="F1022" s="4" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="G1022" s="4" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="H1022" s="6" t="n">
         <v>46288.63568287</v>
       </c>
       <c r="I1022" s="4" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="J1022" s="4" t="s">
+        <v>1947</v>
+      </c>
+      <c r="K1022" s="4" t="s">
         <v>1948</v>
-      </c>
-      <c r="K1022" s="4" t="s">
-        <v>1949</v>
       </c>
       <c r="L1022" s="5"/>
       <c r="M1022" s="5"/>
@@ -65689,7 +65758,7 @@
         <v>351</v>
       </c>
       <c r="G1023" s="9" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="H1023" s="11" t="n">
         <v>46288.641435185</v>
@@ -65741,13 +65810,13 @@
         <v>23</v>
       </c>
       <c r="E1024" s="3" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="F1024" s="4" t="s">
         <v>945</v>
       </c>
       <c r="G1024" s="4" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="H1024" s="6" t="n">
         <v>46288.645289352</v>
@@ -65805,7 +65874,7 @@
         <v>366</v>
       </c>
       <c r="G1025" s="9" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="H1025" s="10" t="n">
         <v>46288</v>
@@ -65863,7 +65932,7 @@
         <v>1264</v>
       </c>
       <c r="G1026" s="4" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H1026" s="5" t="n">
         <v>46288</v>
@@ -65880,7 +65949,7 @@
       <c r="L1026" s="5"/>
       <c r="M1026" s="5"/>
       <c r="N1026" s="4" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="O1026" s="6" t="n">
         <v>46289.410022488</v>
@@ -65921,7 +65990,7 @@
         <v>1638</v>
       </c>
       <c r="G1027" s="9" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="H1027" s="10" t="n">
         <v>46289</v>
@@ -65976,10 +66045,10 @@
         <v>24</v>
       </c>
       <c r="F1028" s="4" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="G1028" s="4" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H1028" s="6" t="n">
         <v>46288.697777778</v>
@@ -66037,7 +66106,7 @@
         <v>490</v>
       </c>
       <c r="G1029" s="9" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="H1029" s="11" t="n">
         <v>46288.708703704</v>
@@ -66095,7 +66164,7 @@
         <v>262</v>
       </c>
       <c r="G1030" s="4" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="H1030" s="6" t="n">
         <v>46288.727013889</v>
@@ -66153,7 +66222,7 @@
         <v>521</v>
       </c>
       <c r="G1031" s="9" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="H1031" s="11" t="n">
         <v>46293.413449074</v>
@@ -66211,7 +66280,7 @@
         <v>1783</v>
       </c>
       <c r="G1032" s="4" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="H1032" s="6" t="n">
         <v>46290.399768519</v>
@@ -66269,7 +66338,7 @@
         <v>75</v>
       </c>
       <c r="G1033" s="9" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="H1033" s="11" t="n">
         <v>46293.420972222</v>
@@ -66327,7 +66396,7 @@
         <v>1545</v>
       </c>
       <c r="G1034" s="4" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="H1034" s="6" t="n">
         <v>46289.403217593</v>
@@ -66382,22 +66451,22 @@
         <v>24</v>
       </c>
       <c r="F1035" s="9" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="G1035" s="9" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="H1035" s="11" t="n">
         <v>46289.956689815</v>
       </c>
       <c r="I1035" s="9" t="s">
+        <v>2030</v>
+      </c>
+      <c r="J1035" s="9" t="s">
         <v>2032</v>
       </c>
-      <c r="J1035" s="9" t="s">
-        <v>2034</v>
-      </c>
       <c r="K1035" s="9" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="L1035" s="10"/>
       <c r="M1035" s="10"/>
@@ -66437,13 +66506,13 @@
         <v>23</v>
       </c>
       <c r="E1036" s="3" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="F1036" s="4" t="s">
         <v>801</v>
       </c>
       <c r="G1036" s="4" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="H1036" s="6" t="n">
         <v>46293.739594907</v>
@@ -66498,22 +66567,22 @@
         <v>24</v>
       </c>
       <c r="F1037" s="9" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="G1037" s="9" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="H1037" s="11" t="n">
         <v>46293.720231481</v>
       </c>
       <c r="I1037" s="9" t="s">
+        <v>2030</v>
+      </c>
+      <c r="J1037" s="9" t="s">
         <v>2032</v>
       </c>
-      <c r="J1037" s="9" t="s">
-        <v>2034</v>
-      </c>
       <c r="K1037" s="9" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="L1037" s="10"/>
       <c r="M1037" s="10"/>
@@ -66553,13 +66622,13 @@
         <v>23</v>
       </c>
       <c r="E1038" s="3" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="F1038" s="4" t="s">
         <v>1271</v>
       </c>
       <c r="G1038" s="4" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="H1038" s="6" t="n">
         <v>46294.490601852</v>
@@ -66614,10 +66683,10 @@
         <v>24</v>
       </c>
       <c r="F1039" s="9" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="G1039" s="9" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="H1039" s="10" t="n">
         <v>46294</v>
@@ -66675,7 +66744,7 @@
         <v>1515</v>
       </c>
       <c r="G1040" s="4" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="H1040" s="5" t="n">
         <v>46294</v>
@@ -66733,7 +66802,7 @@
         <v>969</v>
       </c>
       <c r="G1041" s="9" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="H1041" s="10" t="n">
         <v>46290</v>
@@ -66773,35 +66842,789 @@
       <c r="U1041" s="9"/>
       <c r="V1041" s="9"/>
     </row>
-    <row r="1042" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A1042" s="13" t="n">
-        <v>1040</v>
-      </c>
-      <c r="B1042" s="14"/>
-      <c r="C1042" s="14"/>
-      <c r="D1042" s="14"/>
-      <c r="E1042" s="14"/>
-      <c r="F1042" s="14"/>
-      <c r="G1042" s="14"/>
-      <c r="H1042" s="14"/>
-      <c r="I1042" s="14"/>
-      <c r="J1042" s="14"/>
-      <c r="K1042" s="14"/>
-      <c r="L1042" s="14"/>
-      <c r="M1042" s="14"/>
-      <c r="N1042" s="14"/>
-      <c r="O1042" s="14"/>
-      <c r="P1042" s="14"/>
-      <c r="Q1042" s="14"/>
-      <c r="R1042" s="15" t="n">
-        <v>62198704.2006</v>
-      </c>
-      <c r="S1042" s="15" t="n">
-        <v>59663287.3206</v>
-      </c>
-      <c r="T1042" s="14"/>
-      <c r="U1042" s="14"/>
-      <c r="V1042" s="16"/>
+    <row r="1042" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1042" s="3" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B1042" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1042" s="4"/>
+      <c r="D1042" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1042" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1042" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1042" s="4" t="s">
+        <v>2043</v>
+      </c>
+      <c r="H1042" s="6" t="n">
+        <v>46294.604212963</v>
+      </c>
+      <c r="I1042" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="J1042" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="K1042" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L1042" s="5"/>
+      <c r="M1042" s="5"/>
+      <c r="N1042" s="4" t="s">
+        <v>1973</v>
+      </c>
+      <c r="O1042" s="6" t="n">
+        <v>46296.614052928</v>
+      </c>
+      <c r="P1042" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1042" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1042" s="7" t="n">
+        <v>1621.75</v>
+      </c>
+      <c r="S1042" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1042" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1042" s="4"/>
+      <c r="V1042" s="4"/>
+    </row>
+    <row r="1043" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1043" s="8" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B1043" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1043" s="9"/>
+      <c r="D1043" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1043" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1043" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1043" s="9" t="s">
+        <v>2044</v>
+      </c>
+      <c r="H1043" s="11" t="n">
+        <v>46294.585011574</v>
+      </c>
+      <c r="I1043" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="J1043" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="K1043" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="L1043" s="10"/>
+      <c r="M1043" s="10"/>
+      <c r="N1043" s="9" t="s">
+        <v>1973</v>
+      </c>
+      <c r="O1043" s="11" t="n">
+        <v>46296.614185451</v>
+      </c>
+      <c r="P1043" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1043" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1043" s="12" t="n">
+        <v>32824.75</v>
+      </c>
+      <c r="S1043" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1043" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1043" s="9"/>
+      <c r="V1043" s="9"/>
+    </row>
+    <row r="1044" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1044" s="3" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B1044" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1044" s="4"/>
+      <c r="D1044" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1044" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1044" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="G1044" s="4" t="s">
+        <v>2045</v>
+      </c>
+      <c r="H1044" s="6" t="n">
+        <v>46294.608877315</v>
+      </c>
+      <c r="I1044" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="J1044" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="K1044" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="L1044" s="5"/>
+      <c r="M1044" s="5"/>
+      <c r="N1044" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1044" s="6" t="n">
+        <v>46296.614319757</v>
+      </c>
+      <c r="P1044" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1044" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1044" s="7" t="n">
+        <v>10619.1</v>
+      </c>
+      <c r="S1044" s="7" t="n">
+        <v>10619.1</v>
+      </c>
+      <c r="T1044" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1044" s="4"/>
+      <c r="V1044" s="4"/>
+    </row>
+    <row r="1045" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1045" s="8" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B1045" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1045" s="9"/>
+      <c r="D1045" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1045" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1045" s="9" t="s">
+        <v>1649</v>
+      </c>
+      <c r="G1045" s="9" t="s">
+        <v>2046</v>
+      </c>
+      <c r="H1045" s="11" t="n">
+        <v>46294.613831019</v>
+      </c>
+      <c r="I1045" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1045" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="K1045" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="L1045" s="10"/>
+      <c r="M1045" s="10"/>
+      <c r="N1045" s="9" t="s">
+        <v>1973</v>
+      </c>
+      <c r="O1045" s="11" t="n">
+        <v>46296.614460729</v>
+      </c>
+      <c r="P1045" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1045" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1045" s="12" t="n">
+        <v>45906.8</v>
+      </c>
+      <c r="S1045" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1045" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1045" s="9"/>
+      <c r="V1045" s="9"/>
+    </row>
+    <row r="1046" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1046" s="3" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B1046" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1046" s="4"/>
+      <c r="D1046" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1046" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1046" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="G1046" s="4" t="s">
+        <v>2047</v>
+      </c>
+      <c r="H1046" s="6" t="n">
+        <v>46294.707199074</v>
+      </c>
+      <c r="I1046" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="J1046" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="K1046" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="L1046" s="5"/>
+      <c r="M1046" s="5"/>
+      <c r="N1046" s="4" t="s">
+        <v>1973</v>
+      </c>
+      <c r="O1046" s="6" t="n">
+        <v>46296.614563113</v>
+      </c>
+      <c r="P1046" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1046" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1046" s="7" t="n">
+        <v>15200</v>
+      </c>
+      <c r="S1046" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1046" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1046" s="4"/>
+      <c r="V1046" s="4"/>
+    </row>
+    <row r="1047" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1047" s="8" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B1047" s="9" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C1047" s="9"/>
+      <c r="D1047" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1047" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1047" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1047" s="9" t="s">
+        <v>2049</v>
+      </c>
+      <c r="H1047" s="11" t="n">
+        <v>46294.757743056</v>
+      </c>
+      <c r="I1047" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="J1047" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K1047" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="L1047" s="10"/>
+      <c r="M1047" s="10"/>
+      <c r="N1047" s="9" t="s">
+        <v>2050</v>
+      </c>
+      <c r="O1047" s="11" t="n">
+        <v>46296.614756863</v>
+      </c>
+      <c r="P1047" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1047" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1047" s="12" t="n">
+        <v>56400</v>
+      </c>
+      <c r="S1047" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1047" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1047" s="9"/>
+      <c r="V1047" s="9"/>
+    </row>
+    <row r="1048" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1048" s="3" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B1048" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1048" s="4"/>
+      <c r="D1048" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1048" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1048" s="4" t="s">
+        <v>2051</v>
+      </c>
+      <c r="G1048" s="4" t="s">
+        <v>2052</v>
+      </c>
+      <c r="H1048" s="6" t="n">
+        <v>46295.464884259</v>
+      </c>
+      <c r="I1048" s="4" t="s">
+        <v>2051</v>
+      </c>
+      <c r="J1048" s="4" t="s">
+        <v>2053</v>
+      </c>
+      <c r="K1048" s="4" t="s">
+        <v>2054</v>
+      </c>
+      <c r="L1048" s="5"/>
+      <c r="M1048" s="5"/>
+      <c r="N1048" s="4" t="s">
+        <v>1973</v>
+      </c>
+      <c r="O1048" s="6" t="n">
+        <v>46296.614904433</v>
+      </c>
+      <c r="P1048" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1048" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1048" s="7" t="n">
+        <v>10600</v>
+      </c>
+      <c r="S1048" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1048" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1048" s="4"/>
+      <c r="V1048" s="4"/>
+    </row>
+    <row r="1049" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1049" s="8" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B1049" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1049" s="9"/>
+      <c r="D1049" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1049" s="8" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F1049" s="9" t="s">
+        <v>2056</v>
+      </c>
+      <c r="G1049" s="9" t="s">
+        <v>2057</v>
+      </c>
+      <c r="H1049" s="11" t="n">
+        <v>46294.660474537</v>
+      </c>
+      <c r="I1049" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="J1049" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="K1049" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="L1049" s="10"/>
+      <c r="M1049" s="10"/>
+      <c r="N1049" s="9" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O1049" s="11" t="n">
+        <v>46296.615131516</v>
+      </c>
+      <c r="P1049" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1049" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1049" s="12" t="n">
+        <v>26782.3</v>
+      </c>
+      <c r="S1049" s="12" t="n">
+        <v>9760</v>
+      </c>
+      <c r="T1049" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1049" s="9"/>
+      <c r="V1049" s="9"/>
+    </row>
+    <row r="1050" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1050" s="3" t="n">
+        <v>1119</v>
+      </c>
+      <c r="B1050" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1050" s="4"/>
+      <c r="D1050" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1050" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1050" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="G1050" s="4" t="s">
+        <v>2058</v>
+      </c>
+      <c r="H1050" s="6" t="n">
+        <v>46295.603634259</v>
+      </c>
+      <c r="I1050" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1050" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1050" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L1050" s="5"/>
+      <c r="M1050" s="5"/>
+      <c r="N1050" s="4" t="s">
+        <v>1973</v>
+      </c>
+      <c r="O1050" s="6" t="n">
+        <v>46296.61523816</v>
+      </c>
+      <c r="P1050" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1050" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1050" s="7" t="n">
+        <v>1545</v>
+      </c>
+      <c r="S1050" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1050" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1050" s="4"/>
+      <c r="V1050" s="4"/>
+    </row>
+    <row r="1051" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1051" s="8" t="n">
+        <v>1120</v>
+      </c>
+      <c r="B1051" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1051" s="9"/>
+      <c r="D1051" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1051" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1051" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="G1051" s="9" t="s">
+        <v>2059</v>
+      </c>
+      <c r="H1051" s="11" t="n">
+        <v>46295.647060185</v>
+      </c>
+      <c r="I1051" s="9" t="s">
+        <v>906</v>
+      </c>
+      <c r="J1051" s="9" t="s">
+        <v>906</v>
+      </c>
+      <c r="K1051" s="9" t="s">
+        <v>907</v>
+      </c>
+      <c r="L1051" s="10"/>
+      <c r="M1051" s="10"/>
+      <c r="N1051" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1051" s="11" t="n">
+        <v>46296.615454711</v>
+      </c>
+      <c r="P1051" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1051" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1051" s="12" t="n">
+        <v>9760.68</v>
+      </c>
+      <c r="S1051" s="12" t="n">
+        <v>9760.68</v>
+      </c>
+      <c r="T1051" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1051" s="9"/>
+      <c r="V1051" s="9"/>
+    </row>
+    <row r="1052" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1052" s="3" t="n">
+        <v>1121</v>
+      </c>
+      <c r="B1052" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1052" s="4"/>
+      <c r="D1052" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1052" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1052" s="4" t="s">
+        <v>2060</v>
+      </c>
+      <c r="G1052" s="4" t="s">
+        <v>2061</v>
+      </c>
+      <c r="H1052" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="I1052" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="J1052" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="K1052" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="L1052" s="5"/>
+      <c r="M1052" s="5"/>
+      <c r="N1052" s="4" t="s">
+        <v>1973</v>
+      </c>
+      <c r="O1052" s="6" t="n">
+        <v>46296.623752083</v>
+      </c>
+      <c r="P1052" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1052" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1052" s="7" t="n">
+        <v>4510.24</v>
+      </c>
+      <c r="S1052" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1052" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1052" s="4"/>
+      <c r="V1052" s="4"/>
+    </row>
+    <row r="1053" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1053" s="8" t="n">
+        <v>1122</v>
+      </c>
+      <c r="B1053" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1053" s="9"/>
+      <c r="D1053" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1053" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1053" s="9" t="s">
+        <v>1264</v>
+      </c>
+      <c r="G1053" s="9" t="s">
+        <v>2062</v>
+      </c>
+      <c r="H1053" s="10" t="n">
+        <v>46295</v>
+      </c>
+      <c r="I1053" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="J1053" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="K1053" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="L1053" s="10"/>
+      <c r="M1053" s="10"/>
+      <c r="N1053" s="9" t="s">
+        <v>1973</v>
+      </c>
+      <c r="O1053" s="11" t="n">
+        <v>46296.626185336</v>
+      </c>
+      <c r="P1053" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1053" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1053" s="12" t="n">
+        <v>85899</v>
+      </c>
+      <c r="S1053" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1053" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1053" s="9"/>
+      <c r="V1053" s="9"/>
+    </row>
+    <row r="1054" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1054" s="3" t="n">
+        <v>1123</v>
+      </c>
+      <c r="B1054" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1054" s="4"/>
+      <c r="D1054" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1054" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1054" s="4" t="s">
+        <v>2063</v>
+      </c>
+      <c r="G1054" s="4" t="s">
+        <v>2064</v>
+      </c>
+      <c r="H1054" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="I1054" s="4" t="s">
+        <v>2063</v>
+      </c>
+      <c r="J1054" s="4" t="s">
+        <v>2065</v>
+      </c>
+      <c r="K1054" s="4" t="s">
+        <v>2066</v>
+      </c>
+      <c r="L1054" s="5"/>
+      <c r="M1054" s="5"/>
+      <c r="N1054" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1054" s="6" t="n">
+        <v>46296.627580289</v>
+      </c>
+      <c r="P1054" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1054" s="4" t="s">
+        <v>2067</v>
+      </c>
+      <c r="R1054" s="7" t="n">
+        <v>22667.76</v>
+      </c>
+      <c r="S1054" s="7" t="n">
+        <v>22667.76</v>
+      </c>
+      <c r="T1054" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="U1054" s="4"/>
+      <c r="V1054" s="4"/>
+    </row>
+    <row r="1055" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A1055" s="13" t="n">
+        <v>1053</v>
+      </c>
+      <c r="B1055" s="14"/>
+      <c r="C1055" s="14"/>
+      <c r="D1055" s="14"/>
+      <c r="E1055" s="14"/>
+      <c r="F1055" s="14"/>
+      <c r="G1055" s="14"/>
+      <c r="H1055" s="14"/>
+      <c r="I1055" s="14"/>
+      <c r="J1055" s="14"/>
+      <c r="K1055" s="14"/>
+      <c r="L1055" s="14"/>
+      <c r="M1055" s="14"/>
+      <c r="N1055" s="14"/>
+      <c r="O1055" s="14"/>
+      <c r="P1055" s="14"/>
+      <c r="Q1055" s="14"/>
+      <c r="R1055" s="15" t="n">
+        <v>62495219.5806</v>
+      </c>
+      <c r="S1055" s="15" t="n">
+        <v>59753882.8606</v>
+      </c>
+      <c r="T1055" s="14"/>
+      <c r="U1055" s="14"/>
+      <c r="V1055" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="2070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="2074">
   <si>
     <t>ID</t>
   </si>
@@ -3870,7 +3870,7 @@
     <t>703</t>
   </si>
   <si>
-    <t>81 %</t>
+    <t>87 %</t>
   </si>
   <si>
     <t>DBV</t>
@@ -5922,6 +5922,9 @@
     <t>1227</t>
   </si>
   <si>
+    <t>43 %</t>
+  </si>
+  <si>
     <t>1228</t>
   </si>
   <si>
@@ -5931,123 +5934,123 @@
     <t>00.085.822/0001-12</t>
   </si>
   <si>
+    <t>1229</t>
+  </si>
+  <si>
+    <t>1230</t>
+  </si>
+  <si>
+    <t>1231</t>
+  </si>
+  <si>
+    <t>1232</t>
+  </si>
+  <si>
+    <t>1233</t>
+  </si>
+  <si>
+    <t>10 %</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>1235</t>
+  </si>
+  <si>
+    <t>1236</t>
+  </si>
+  <si>
+    <t>ZILFARMA PRODUTOS</t>
+  </si>
+  <si>
+    <t>1237</t>
+  </si>
+  <si>
+    <t>ZILFARMA PRODUTOS FARMACEUTICOS E IMPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t>06.046.371/0001-90</t>
+  </si>
+  <si>
+    <t>1238</t>
+  </si>
+  <si>
+    <t>1239</t>
+  </si>
+  <si>
+    <t>1240</t>
+  </si>
+  <si>
+    <t>58 %</t>
+  </si>
+  <si>
+    <t>MEDCARE DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1241</t>
+  </si>
+  <si>
+    <t>DISNOMED</t>
+  </si>
+  <si>
+    <t>1242</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA NOGUEIRA DE MEDICAMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>03.315.618/0001-39</t>
+  </si>
+  <si>
+    <t>1243</t>
+  </si>
+  <si>
+    <t>1244</t>
+  </si>
+  <si>
+    <t>UNI-RIM</t>
+  </si>
+  <si>
+    <t>1245</t>
+  </si>
+  <si>
+    <t>1246</t>
+  </si>
+  <si>
+    <t>1247</t>
+  </si>
+  <si>
+    <t>1248</t>
+  </si>
+  <si>
+    <t>1249</t>
+  </si>
+  <si>
+    <t>24 %</t>
+  </si>
+  <si>
+    <t>1250</t>
+  </si>
+  <si>
+    <t>1251</t>
+  </si>
+  <si>
+    <t>REC HOSPITALAR</t>
+  </si>
+  <si>
+    <t>1252</t>
+  </si>
+  <si>
+    <t>REC DISTRIBUIDORA HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>39.500.546/0001-47</t>
+  </si>
+  <si>
     <t>A INICIAR</t>
   </si>
   <si>
-    <t>1229</t>
-  </si>
-  <si>
-    <t>1230</t>
-  </si>
-  <si>
-    <t>1231</t>
-  </si>
-  <si>
-    <t>1232</t>
-  </si>
-  <si>
-    <t>1233</t>
-  </si>
-  <si>
-    <t>7 %</t>
-  </si>
-  <si>
-    <t>1234</t>
-  </si>
-  <si>
-    <t>1235</t>
-  </si>
-  <si>
-    <t>1236</t>
-  </si>
-  <si>
-    <t>ZILFARMA PRODUTOS</t>
-  </si>
-  <si>
-    <t>1237</t>
-  </si>
-  <si>
-    <t>ZILFARMA PRODUTOS FARMACEUTICOS E IMPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t>06.046.371/0001-90</t>
-  </si>
-  <si>
-    <t>1238</t>
-  </si>
-  <si>
-    <t>1239</t>
-  </si>
-  <si>
-    <t>1240</t>
-  </si>
-  <si>
-    <t>58 %</t>
-  </si>
-  <si>
-    <t>MEDCARE DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1241</t>
-  </si>
-  <si>
-    <t>DISNOMED</t>
-  </si>
-  <si>
-    <t>1242</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA NOGUEIRA DE MEDICAMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>03.315.618/0001-39</t>
-  </si>
-  <si>
-    <t>1243</t>
-  </si>
-  <si>
-    <t>1244</t>
-  </si>
-  <si>
-    <t>UNI-RIM</t>
-  </si>
-  <si>
-    <t>1245</t>
-  </si>
-  <si>
-    <t>1246</t>
-  </si>
-  <si>
-    <t>1247</t>
-  </si>
-  <si>
-    <t>1248</t>
-  </si>
-  <si>
-    <t>1249</t>
-  </si>
-  <si>
-    <t>24 %</t>
-  </si>
-  <si>
-    <t>1250</t>
-  </si>
-  <si>
-    <t>1251</t>
-  </si>
-  <si>
-    <t>REC HOSPITALAR</t>
-  </si>
-  <si>
-    <t>1252</t>
-  </si>
-  <si>
-    <t>REC DISTRIBUIDORA HOSPITALAR LTDA</t>
-  </si>
-  <si>
-    <t>39.500.546/0001-47</t>
-  </si>
-  <si>
     <t>1253</t>
   </si>
   <si>
@@ -6063,9 +6066,6 @@
     <t>1257</t>
   </si>
   <si>
-    <t>50 %</t>
-  </si>
-  <si>
     <t>1258</t>
   </si>
   <si>
@@ -6177,9 +6177,6 @@
     <t>06.872.949/0001-68</t>
   </si>
   <si>
-    <t>56 %</t>
-  </si>
-  <si>
     <t>CIRÚRGICA BEZERRA</t>
   </si>
   <si>
@@ -6223,6 +6220,21 @@
   </si>
   <si>
     <t>1292</t>
+  </si>
+  <si>
+    <t>1293</t>
+  </si>
+  <si>
+    <t>1294</t>
+  </si>
+  <si>
+    <t>44 %</t>
+  </si>
+  <si>
+    <t>1295</t>
+  </si>
+  <si>
+    <t>1296</t>
   </si>
 </sst>
 </file>
@@ -6416,7 +6428,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V1058"/>
+  <dimension ref="A1:V1062"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -38126,7 +38138,7 @@
         <v>820410</v>
       </c>
       <c r="S546" s="7" t="n">
-        <v>666045</v>
+        <v>716475</v>
       </c>
       <c r="T546" s="4" t="s">
         <v>571</v>
@@ -64076,30 +64088,30 @@
         <v>23</v>
       </c>
       <c r="E994" s="3" t="s">
-        <v>285</v>
+        <v>1969</v>
       </c>
       <c r="F994" s="4" t="s">
         <v>1162</v>
       </c>
       <c r="G994" s="4" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H994" s="5" t="n">
         <v>46276</v>
       </c>
       <c r="I994" s="4" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="J994" s="4" t="s">
         <v>1165</v>
       </c>
       <c r="K994" s="4" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="L994" s="5"/>
       <c r="M994" s="5"/>
       <c r="N994" s="4" t="s">
-        <v>1972</v>
+        <v>1288</v>
       </c>
       <c r="O994" s="6" t="n">
         <v>46279.599731713</v>
@@ -64114,7 +64126,7 @@
         <v>58266</v>
       </c>
       <c r="S994" s="7" t="n">
-        <v>0</v>
+        <v>24900</v>
       </c>
       <c r="T994" s="4" t="s">
         <v>571</v>
@@ -64462,7 +64474,7 @@
         <v>885906</v>
       </c>
       <c r="S1000" s="7" t="n">
-        <v>63000</v>
+        <v>91350</v>
       </c>
       <c r="T1000" s="4" t="s">
         <v>32</v>
@@ -65491,7 +65503,7 @@
       <c r="L1018" s="5"/>
       <c r="M1018" s="5"/>
       <c r="N1018" s="4" t="s">
-        <v>1972</v>
+        <v>2011</v>
       </c>
       <c r="O1018" s="6" t="n">
         <v>46289.388101852</v>
@@ -65532,7 +65544,7 @@
         <v>402</v>
       </c>
       <c r="G1019" s="9" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H1019" s="11" t="n">
         <v>46287.90775463</v>
@@ -65590,7 +65602,7 @@
         <v>1237</v>
       </c>
       <c r="G1020" s="4" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H1020" s="6" t="n">
         <v>46287.518842593</v>
@@ -65648,7 +65660,7 @@
         <v>347</v>
       </c>
       <c r="G1021" s="9" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H1021" s="11" t="n">
         <v>46288.409328704</v>
@@ -65706,7 +65718,7 @@
         <v>1944</v>
       </c>
       <c r="G1022" s="4" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H1022" s="6" t="n">
         <v>46288.63568287</v>
@@ -65764,7 +65776,7 @@
         <v>351</v>
       </c>
       <c r="G1023" s="9" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H1023" s="11" t="n">
         <v>46288.641435185</v>
@@ -65816,7 +65828,7 @@
         <v>23</v>
       </c>
       <c r="E1024" s="3" t="s">
-        <v>2016</v>
+        <v>24</v>
       </c>
       <c r="F1024" s="4" t="s">
         <v>945</v>
@@ -65839,7 +65851,7 @@
       <c r="L1024" s="5"/>
       <c r="M1024" s="5"/>
       <c r="N1024" s="4" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O1024" s="6" t="n">
         <v>46289.389332639</v>
@@ -65854,7 +65866,7 @@
         <v>61549.2</v>
       </c>
       <c r="S1024" s="7" t="n">
-        <v>30996</v>
+        <v>61549.2</v>
       </c>
       <c r="T1024" s="4" t="s">
         <v>32</v>
@@ -65955,7 +65967,7 @@
       <c r="L1026" s="5"/>
       <c r="M1026" s="5"/>
       <c r="N1026" s="4" t="s">
-        <v>1972</v>
+        <v>2011</v>
       </c>
       <c r="O1026" s="6" t="n">
         <v>46289.410022488</v>
@@ -67034,7 +67046,7 @@
         <v>23</v>
       </c>
       <c r="E1045" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1045" s="9" t="s">
         <v>1648</v>
@@ -67057,7 +67069,7 @@
       <c r="L1045" s="10"/>
       <c r="M1045" s="10"/>
       <c r="N1045" s="9" t="s">
-        <v>1972</v>
+        <v>29</v>
       </c>
       <c r="O1045" s="11" t="n">
         <v>46296.614460729</v>
@@ -67072,7 +67084,7 @@
         <v>45906.8</v>
       </c>
       <c r="S1045" s="12" t="n">
-        <v>0</v>
+        <v>45906.8</v>
       </c>
       <c r="T1045" s="9" t="s">
         <v>32</v>
@@ -67231,7 +67243,7 @@
       <c r="L1048" s="5"/>
       <c r="M1048" s="5"/>
       <c r="N1048" s="4" t="s">
-        <v>1972</v>
+        <v>2011</v>
       </c>
       <c r="O1048" s="6" t="n">
         <v>46296.614904433</v>
@@ -67266,13 +67278,13 @@
         <v>23</v>
       </c>
       <c r="E1049" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1049" s="9" t="s">
         <v>2054</v>
       </c>
-      <c r="F1049" s="9" t="s">
+      <c r="G1049" s="9" t="s">
         <v>2055</v>
-      </c>
-      <c r="G1049" s="9" t="s">
-        <v>2056</v>
       </c>
       <c r="H1049" s="11" t="n">
         <v>46294.660474537</v>
@@ -67289,7 +67301,7 @@
       <c r="L1049" s="10"/>
       <c r="M1049" s="10"/>
       <c r="N1049" s="9" t="s">
-        <v>1288</v>
+        <v>29</v>
       </c>
       <c r="O1049" s="11" t="n">
         <v>46296.615131516</v>
@@ -67304,7 +67316,7 @@
         <v>26782.3</v>
       </c>
       <c r="S1049" s="12" t="n">
-        <v>14880</v>
+        <v>26782.3</v>
       </c>
       <c r="T1049" s="9" t="s">
         <v>32</v>
@@ -67330,7 +67342,7 @@
         <v>1271</v>
       </c>
       <c r="G1050" s="4" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="H1050" s="6" t="n">
         <v>46295.603634259</v>
@@ -67347,7 +67359,7 @@
       <c r="L1050" s="5"/>
       <c r="M1050" s="5"/>
       <c r="N1050" s="4" t="s">
-        <v>1972</v>
+        <v>2011</v>
       </c>
       <c r="O1050" s="6" t="n">
         <v>46296.61523816</v>
@@ -67388,7 +67400,7 @@
         <v>904</v>
       </c>
       <c r="G1051" s="9" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="H1051" s="11" t="n">
         <v>46295.647060185</v>
@@ -67443,10 +67455,10 @@
         <v>24</v>
       </c>
       <c r="F1052" s="4" t="s">
+        <v>2058</v>
+      </c>
+      <c r="G1052" s="4" t="s">
         <v>2059</v>
-      </c>
-      <c r="G1052" s="4" t="s">
-        <v>2060</v>
       </c>
       <c r="H1052" s="5" t="n">
         <v>46296</v>
@@ -67504,7 +67516,7 @@
         <v>1264</v>
       </c>
       <c r="G1053" s="9" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="H1053" s="10" t="n">
         <v>46295</v>
@@ -67521,7 +67533,7 @@
       <c r="L1053" s="10"/>
       <c r="M1053" s="10"/>
       <c r="N1053" s="9" t="s">
-        <v>1972</v>
+        <v>2011</v>
       </c>
       <c r="O1053" s="11" t="n">
         <v>46296.626185336</v>
@@ -67559,22 +67571,22 @@
         <v>24</v>
       </c>
       <c r="F1054" s="4" t="s">
+        <v>2061</v>
+      </c>
+      <c r="G1054" s="4" t="s">
         <v>2062</v>
-      </c>
-      <c r="G1054" s="4" t="s">
-        <v>2063</v>
       </c>
       <c r="H1054" s="5" t="n">
         <v>46295</v>
       </c>
       <c r="I1054" s="4" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="J1054" s="4" t="s">
+        <v>2063</v>
+      </c>
+      <c r="K1054" s="4" t="s">
         <v>2064</v>
-      </c>
-      <c r="K1054" s="4" t="s">
-        <v>2065</v>
       </c>
       <c r="L1054" s="5"/>
       <c r="M1054" s="5"/>
@@ -67588,7 +67600,7 @@
         <v>1455</v>
       </c>
       <c r="Q1054" s="4" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="R1054" s="7" t="n">
         <v>22667.76</v>
@@ -67614,13 +67626,13 @@
         <v>23</v>
       </c>
       <c r="E1055" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1055" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="G1055" s="9" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="H1055" s="10" t="n">
         <v>46297</v>
@@ -67637,7 +67649,7 @@
       <c r="L1055" s="10"/>
       <c r="M1055" s="10"/>
       <c r="N1055" s="9" t="s">
-        <v>1972</v>
+        <v>29</v>
       </c>
       <c r="O1055" s="11" t="n">
         <v>46297.642502315</v>
@@ -67652,7 +67664,7 @@
         <v>3891.96</v>
       </c>
       <c r="S1055" s="12" t="n">
-        <v>0</v>
+        <v>3891.96</v>
       </c>
       <c r="T1055" s="9" t="s">
         <v>32</v>
@@ -67672,13 +67684,13 @@
         <v>23</v>
       </c>
       <c r="E1056" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1056" s="4" t="s">
         <v>262</v>
       </c>
       <c r="G1056" s="4" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="H1056" s="6" t="n">
         <v>46296.754675926</v>
@@ -67695,7 +67707,7 @@
       <c r="L1056" s="5"/>
       <c r="M1056" s="5"/>
       <c r="N1056" s="4" t="s">
-        <v>1972</v>
+        <v>29</v>
       </c>
       <c r="O1056" s="6" t="n">
         <v>46297.643961539</v>
@@ -67710,7 +67722,7 @@
         <v>19500</v>
       </c>
       <c r="S1056" s="7" t="n">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="T1056" s="4" t="s">
         <v>32</v>
@@ -67730,13 +67742,13 @@
         <v>23</v>
       </c>
       <c r="E1057" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1057" s="9" t="s">
         <v>194</v>
       </c>
       <c r="G1057" s="9" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="H1057" s="10" t="n">
         <v>46296</v>
@@ -67753,7 +67765,7 @@
       <c r="L1057" s="10"/>
       <c r="M1057" s="10"/>
       <c r="N1057" s="9" t="s">
-        <v>1972</v>
+        <v>29</v>
       </c>
       <c r="O1057" s="11" t="n">
         <v>46297.64512897</v>
@@ -67768,7 +67780,7 @@
         <v>9826.88</v>
       </c>
       <c r="S1057" s="12" t="n">
-        <v>0</v>
+        <v>9826.88</v>
       </c>
       <c r="T1057" s="9" t="s">
         <v>32</v>
@@ -67776,35 +67788,267 @@
       <c r="U1057" s="9"/>
       <c r="V1057" s="9"/>
     </row>
-    <row r="1058" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A1058" s="13" t="n">
-        <v>1056</v>
-      </c>
-      <c r="B1058" s="14"/>
-      <c r="C1058" s="14"/>
-      <c r="D1058" s="14"/>
-      <c r="E1058" s="14"/>
-      <c r="F1058" s="14"/>
-      <c r="G1058" s="14"/>
-      <c r="H1058" s="14"/>
-      <c r="I1058" s="14"/>
-      <c r="J1058" s="14"/>
-      <c r="K1058" s="14"/>
-      <c r="L1058" s="14"/>
-      <c r="M1058" s="14"/>
-      <c r="N1058" s="14"/>
-      <c r="O1058" s="14"/>
-      <c r="P1058" s="14"/>
-      <c r="Q1058" s="14"/>
-      <c r="R1058" s="15" t="n">
-        <v>62527019.3006</v>
-      </c>
-      <c r="S1058" s="15" t="n">
-        <v>59833701.4006</v>
-      </c>
-      <c r="T1058" s="14"/>
-      <c r="U1058" s="14"/>
-      <c r="V1058" s="16"/>
+    <row r="1058" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1058" s="3" t="n">
+        <v>1127</v>
+      </c>
+      <c r="B1058" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1058" s="4"/>
+      <c r="D1058" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1058" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1058" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G1058" s="4" t="s">
+        <v>2069</v>
+      </c>
+      <c r="H1058" s="6" t="n">
+        <v>46300.877766204</v>
+      </c>
+      <c r="I1058" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="J1058" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="K1058" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="L1058" s="5"/>
+      <c r="M1058" s="5"/>
+      <c r="N1058" s="4" t="s">
+        <v>2011</v>
+      </c>
+      <c r="O1058" s="6" t="n">
+        <v>46301.683983449</v>
+      </c>
+      <c r="P1058" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1058" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1058" s="7" t="n">
+        <v>50145.6</v>
+      </c>
+      <c r="S1058" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1058" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1058" s="4"/>
+      <c r="V1058" s="4"/>
+    </row>
+    <row r="1059" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1059" s="8" t="n">
+        <v>1128</v>
+      </c>
+      <c r="B1059" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1059" s="9"/>
+      <c r="D1059" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1059" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1059" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="G1059" s="9" t="s">
+        <v>2070</v>
+      </c>
+      <c r="H1059" s="11" t="n">
+        <v>46300.582071759</v>
+      </c>
+      <c r="I1059" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="J1059" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="K1059" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="L1059" s="10"/>
+      <c r="M1059" s="10"/>
+      <c r="N1059" s="9" t="s">
+        <v>2011</v>
+      </c>
+      <c r="O1059" s="11" t="n">
+        <v>46301.684292095</v>
+      </c>
+      <c r="P1059" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1059" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1059" s="12" t="n">
+        <v>4690.4</v>
+      </c>
+      <c r="S1059" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1059" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1059" s="9"/>
+      <c r="V1059" s="9"/>
+    </row>
+    <row r="1060" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1060" s="3" t="n">
+        <v>1129</v>
+      </c>
+      <c r="B1060" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1060" s="4"/>
+      <c r="D1060" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1060" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="F1060" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="G1060" s="4" t="s">
+        <v>2072</v>
+      </c>
+      <c r="H1060" s="6" t="n">
+        <v>46300.587326389</v>
+      </c>
+      <c r="I1060" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="J1060" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="K1060" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1060" s="5"/>
+      <c r="M1060" s="5"/>
+      <c r="N1060" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="O1060" s="6" t="n">
+        <v>46301.684423148</v>
+      </c>
+      <c r="P1060" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1060" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1060" s="7" t="n">
+        <v>58500</v>
+      </c>
+      <c r="S1060" s="7" t="n">
+        <v>25740</v>
+      </c>
+      <c r="T1060" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1060" s="4"/>
+      <c r="V1060" s="4"/>
+    </row>
+    <row r="1061" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1061" s="8" t="n">
+        <v>1130</v>
+      </c>
+      <c r="B1061" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1061" s="9"/>
+      <c r="D1061" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1061" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1061" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="G1061" s="9" t="s">
+        <v>2073</v>
+      </c>
+      <c r="H1061" s="10" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I1061" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="J1061" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1061" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="L1061" s="10"/>
+      <c r="M1061" s="10"/>
+      <c r="N1061" s="9" t="s">
+        <v>2011</v>
+      </c>
+      <c r="O1061" s="11" t="n">
+        <v>46301.685126701</v>
+      </c>
+      <c r="P1061" s="9" t="s">
+        <v>1455</v>
+      </c>
+      <c r="Q1061" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="R1061" s="12" t="n">
+        <v>1686.72</v>
+      </c>
+      <c r="S1061" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1061" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1061" s="9"/>
+      <c r="V1061" s="9"/>
+    </row>
+    <row r="1062" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A1062" s="13" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B1062" s="14"/>
+      <c r="C1062" s="14"/>
+      <c r="D1062" s="14"/>
+      <c r="E1062" s="14"/>
+      <c r="F1062" s="14"/>
+      <c r="G1062" s="14"/>
+      <c r="H1062" s="14"/>
+      <c r="I1062" s="14"/>
+      <c r="J1062" s="14"/>
+      <c r="K1062" s="14"/>
+      <c r="L1062" s="14"/>
+      <c r="M1062" s="14"/>
+      <c r="N1062" s="14"/>
+      <c r="O1062" s="14"/>
+      <c r="P1062" s="14"/>
+      <c r="Q1062" s="14"/>
+      <c r="R1062" s="15" t="n">
+        <v>62642042.0206</v>
+      </c>
+      <c r="S1062" s="15" t="n">
+        <v>60084702.5406</v>
+      </c>
+      <c r="T1062" s="14"/>
+      <c r="U1062" s="14"/>
+      <c r="V1062" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="2084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="2093">
   <si>
     <t>ID</t>
   </si>
@@ -3861,7 +3861,7 @@
     <t>703</t>
   </si>
   <si>
-    <t>87 %</t>
+    <t>95 %</t>
   </si>
   <si>
     <t>DBV</t>
@@ -4476,9 +4476,6 @@
     <t>879</t>
   </si>
   <si>
-    <t>95 %</t>
-  </si>
-  <si>
     <t>880</t>
   </si>
   <si>
@@ -5940,7 +5937,7 @@
     <t>1233</t>
   </si>
   <si>
-    <t>10 %</t>
+    <t>13 %</t>
   </si>
   <si>
     <t>1234</t>
@@ -6117,9 +6114,6 @@
     <t>1271</t>
   </si>
   <si>
-    <t>94 %</t>
-  </si>
-  <si>
     <t>1272</t>
   </si>
   <si>
@@ -6153,6 +6147,9 @@
     <t>1281</t>
   </si>
   <si>
+    <t>85 %</t>
+  </si>
+  <si>
     <t>DISDROL</t>
   </si>
   <si>
@@ -6213,7 +6210,7 @@
     <t>1292</t>
   </si>
   <si>
-    <t>54 %</t>
+    <t>84 %</t>
   </si>
   <si>
     <t>1293</t>
@@ -6237,15 +6234,9 @@
     <t>1298</t>
   </si>
   <si>
-    <t>52 %</t>
-  </si>
-  <si>
     <t>1299</t>
   </si>
   <si>
-    <t>26 %</t>
-  </si>
-  <si>
     <t>1300</t>
   </si>
   <si>
@@ -6265,6 +6256,42 @@
   </si>
   <si>
     <t>1307</t>
+  </si>
+  <si>
+    <t>12 %</t>
+  </si>
+  <si>
+    <t>1308</t>
+  </si>
+  <si>
+    <t>1309</t>
+  </si>
+  <si>
+    <t>1310</t>
+  </si>
+  <si>
+    <t>1311</t>
+  </si>
+  <si>
+    <t>1312</t>
+  </si>
+  <si>
+    <t>1313</t>
+  </si>
+  <si>
+    <t>1314</t>
+  </si>
+  <si>
+    <t>SISAL MED</t>
+  </si>
+  <si>
+    <t>1315</t>
+  </si>
+  <si>
+    <t>MATOS &amp; OLIVEIRA PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>66.852.326/0001-55</t>
   </si>
 </sst>
 </file>
@@ -6458,7 +6485,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V1072"/>
+  <dimension ref="A1:V1080"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -38168,7 +38195,7 @@
         <v>820410</v>
       </c>
       <c r="S546" s="7" t="n">
-        <v>716475</v>
+        <v>777975</v>
       </c>
       <c r="T546" s="4" t="s">
         <v>571</v>
@@ -45614,13 +45641,13 @@
         <v>23</v>
       </c>
       <c r="E675" s="8" t="s">
-        <v>1487</v>
+        <v>1282</v>
       </c>
       <c r="F675" s="9" t="s">
         <v>944</v>
       </c>
       <c r="G675" s="9" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H675" s="10" t="n">
         <v>46162</v>
@@ -45678,7 +45705,7 @@
         <v>453</v>
       </c>
       <c r="G676" s="4" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H676" s="5" t="n">
         <v>46162</v>
@@ -45736,7 +45763,7 @@
         <v>75</v>
       </c>
       <c r="G677" s="9" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H677" s="10" t="n">
         <v>46163</v>
@@ -45791,10 +45818,10 @@
         <v>24</v>
       </c>
       <c r="F678" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="G678" s="4" t="s">
         <v>1491</v>
-      </c>
-      <c r="G678" s="4" t="s">
-        <v>1492</v>
       </c>
       <c r="H678" s="5" t="n">
         <v>46163</v>
@@ -45849,10 +45876,10 @@
         <v>24</v>
       </c>
       <c r="F679" s="9" t="s">
+        <v>1492</v>
+      </c>
+      <c r="G679" s="9" t="s">
         <v>1493</v>
-      </c>
-      <c r="G679" s="9" t="s">
-        <v>1494</v>
       </c>
       <c r="H679" s="10" t="n">
         <v>46164</v>
@@ -45907,10 +45934,10 @@
         <v>24</v>
       </c>
       <c r="F680" s="4" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="G680" s="4" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H680" s="5" t="n">
         <v>46164</v>
@@ -45968,7 +45995,7 @@
         <v>521</v>
       </c>
       <c r="G681" s="9" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H681" s="10" t="n">
         <v>46164</v>
@@ -46026,7 +46053,7 @@
         <v>619</v>
       </c>
       <c r="G682" s="4" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H682" s="5" t="n">
         <v>46164</v>
@@ -46081,10 +46108,10 @@
         <v>24</v>
       </c>
       <c r="F683" s="9" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G683" s="9" t="s">
         <v>1498</v>
-      </c>
-      <c r="G683" s="9" t="s">
-        <v>1499</v>
       </c>
       <c r="H683" s="10" t="n">
         <v>46164</v>
@@ -46142,7 +46169,7 @@
         <v>276</v>
       </c>
       <c r="G684" s="4" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H684" s="5" t="n">
         <v>46164</v>
@@ -46200,7 +46227,7 @@
         <v>1054</v>
       </c>
       <c r="G685" s="9" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H685" s="10" t="n">
         <v>46164</v>
@@ -46255,22 +46282,22 @@
         <v>24</v>
       </c>
       <c r="F686" s="4" t="s">
+        <v>1501</v>
+      </c>
+      <c r="G686" s="4" t="s">
         <v>1502</v>
-      </c>
-      <c r="G686" s="4" t="s">
-        <v>1503</v>
       </c>
       <c r="H686" s="5" t="n">
         <v>46164</v>
       </c>
       <c r="I686" s="4" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="J686" s="4" t="s">
+        <v>1503</v>
+      </c>
+      <c r="K686" s="4" t="s">
         <v>1504</v>
-      </c>
-      <c r="K686" s="4" t="s">
-        <v>1505</v>
       </c>
       <c r="L686" s="5"/>
       <c r="M686" s="5"/>
@@ -46316,7 +46343,7 @@
         <v>124</v>
       </c>
       <c r="G687" s="9" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H687" s="10" t="n">
         <v>46164</v>
@@ -46374,7 +46401,7 @@
         <v>351</v>
       </c>
       <c r="G688" s="4" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H688" s="5" t="n">
         <v>46164</v>
@@ -46429,10 +46456,10 @@
         <v>24</v>
       </c>
       <c r="F689" s="9" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G689" s="9" t="s">
         <v>1508</v>
-      </c>
-      <c r="G689" s="9" t="s">
-        <v>1509</v>
       </c>
       <c r="H689" s="10" t="n">
         <v>46167</v>
@@ -46490,7 +46517,7 @@
         <v>1470</v>
       </c>
       <c r="G690" s="4" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H690" s="5" t="n">
         <v>46167</v>
@@ -46548,7 +46575,7 @@
         <v>581</v>
       </c>
       <c r="G691" s="9" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H691" s="10" t="n">
         <v>46167</v>
@@ -46606,7 +46633,7 @@
         <v>1014</v>
       </c>
       <c r="G692" s="4" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H692" s="5" t="n">
         <v>46167</v>
@@ -46661,10 +46688,10 @@
         <v>24</v>
       </c>
       <c r="F693" s="9" t="s">
+        <v>1512</v>
+      </c>
+      <c r="G693" s="9" t="s">
         <v>1513</v>
-      </c>
-      <c r="G693" s="9" t="s">
-        <v>1514</v>
       </c>
       <c r="H693" s="10" t="n">
         <v>46167</v>
@@ -46722,7 +46749,7 @@
         <v>75</v>
       </c>
       <c r="G694" s="4" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H694" s="5" t="n">
         <v>46167</v>
@@ -46780,7 +46807,7 @@
         <v>490</v>
       </c>
       <c r="G695" s="9" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H695" s="10" t="n">
         <v>46168</v>
@@ -46835,10 +46862,10 @@
         <v>24</v>
       </c>
       <c r="F696" s="4" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G696" s="4" t="s">
         <v>1517</v>
-      </c>
-      <c r="G696" s="4" t="s">
-        <v>1518</v>
       </c>
       <c r="H696" s="5" t="n">
         <v>46168</v>
@@ -46893,10 +46920,10 @@
         <v>24</v>
       </c>
       <c r="F697" s="9" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="G697" s="9" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H697" s="10" t="n">
         <v>46168</v>
@@ -46954,7 +46981,7 @@
         <v>502</v>
       </c>
       <c r="G698" s="4" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H698" s="5" t="n">
         <v>46169</v>
@@ -47012,7 +47039,7 @@
         <v>75</v>
       </c>
       <c r="G699" s="9" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H699" s="10" t="n">
         <v>46168</v>
@@ -47070,7 +47097,7 @@
         <v>75</v>
       </c>
       <c r="G700" s="4" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H700" s="5" t="n">
         <v>46168</v>
@@ -47125,10 +47152,10 @@
         <v>24</v>
       </c>
       <c r="F701" s="9" t="s">
+        <v>1522</v>
+      </c>
+      <c r="G701" s="9" t="s">
         <v>1523</v>
-      </c>
-      <c r="G701" s="9" t="s">
-        <v>1524</v>
       </c>
       <c r="H701" s="10" t="n">
         <v>46167</v>
@@ -47186,7 +47213,7 @@
         <v>986</v>
       </c>
       <c r="G702" s="4" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H702" s="5" t="n">
         <v>46169</v>
@@ -47244,7 +47271,7 @@
         <v>505</v>
       </c>
       <c r="G703" s="9" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H703" s="10" t="n">
         <v>46168</v>
@@ -47302,7 +47329,7 @@
         <v>592</v>
       </c>
       <c r="G704" s="4" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H704" s="5" t="n">
         <v>46169</v>
@@ -47360,7 +47387,7 @@
         <v>347</v>
       </c>
       <c r="G705" s="9" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H705" s="10" t="n">
         <v>46168</v>
@@ -47418,7 +47445,7 @@
         <v>671</v>
       </c>
       <c r="G706" s="4" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H706" s="5" t="n">
         <v>46168</v>
@@ -47476,7 +47503,7 @@
         <v>203</v>
       </c>
       <c r="G707" s="9" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H707" s="10" t="n">
         <v>46168</v>
@@ -47534,7 +47561,7 @@
         <v>262</v>
       </c>
       <c r="G708" s="4" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H708" s="5" t="n">
         <v>46168</v>
@@ -47592,7 +47619,7 @@
         <v>152</v>
       </c>
       <c r="G709" s="9" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H709" s="10" t="n">
         <v>46167</v>
@@ -47650,7 +47677,7 @@
         <v>58</v>
       </c>
       <c r="G710" s="4" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H710" s="5" t="n">
         <v>46167</v>
@@ -47708,7 +47735,7 @@
         <v>310</v>
       </c>
       <c r="G711" s="9" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H711" s="10" t="n">
         <v>46167</v>
@@ -47763,10 +47790,10 @@
         <v>24</v>
       </c>
       <c r="F712" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="G712" s="4" t="s">
         <v>1535</v>
-      </c>
-      <c r="G712" s="4" t="s">
-        <v>1536</v>
       </c>
       <c r="H712" s="5" t="n">
         <v>46167</v>
@@ -47824,7 +47851,7 @@
         <v>328</v>
       </c>
       <c r="G713" s="9" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H713" s="10" t="n">
         <v>46167</v>
@@ -47879,10 +47906,10 @@
         <v>24</v>
       </c>
       <c r="F714" s="4" t="s">
+        <v>1537</v>
+      </c>
+      <c r="G714" s="4" t="s">
         <v>1538</v>
-      </c>
-      <c r="G714" s="4" t="s">
-        <v>1539</v>
       </c>
       <c r="H714" s="5" t="n">
         <v>46168</v>
@@ -47937,10 +47964,10 @@
         <v>24</v>
       </c>
       <c r="F715" s="9" t="s">
+        <v>1539</v>
+      </c>
+      <c r="G715" s="9" t="s">
         <v>1540</v>
-      </c>
-      <c r="G715" s="9" t="s">
-        <v>1541</v>
       </c>
       <c r="H715" s="10" t="n">
         <v>46169</v>
@@ -47998,7 +48025,7 @@
         <v>675</v>
       </c>
       <c r="G716" s="4" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H716" s="5" t="n">
         <v>46170</v>
@@ -48053,10 +48080,10 @@
         <v>24</v>
       </c>
       <c r="F717" s="9" t="s">
+        <v>1542</v>
+      </c>
+      <c r="G717" s="9" t="s">
         <v>1543</v>
-      </c>
-      <c r="G717" s="9" t="s">
-        <v>1544</v>
       </c>
       <c r="H717" s="10" t="n">
         <v>46169</v>
@@ -48114,7 +48141,7 @@
         <v>909</v>
       </c>
       <c r="G718" s="4" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H718" s="5" t="n">
         <v>46170</v>
@@ -48169,22 +48196,22 @@
         <v>24</v>
       </c>
       <c r="F719" s="9" t="s">
+        <v>1545</v>
+      </c>
+      <c r="G719" s="9" t="s">
         <v>1546</v>
-      </c>
-      <c r="G719" s="9" t="s">
-        <v>1547</v>
       </c>
       <c r="H719" s="10" t="n">
         <v>46174</v>
       </c>
       <c r="I719" s="9" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="J719" s="9" t="s">
+        <v>1547</v>
+      </c>
+      <c r="K719" s="9" t="s">
         <v>1548</v>
-      </c>
-      <c r="K719" s="9" t="s">
-        <v>1549</v>
       </c>
       <c r="L719" s="10"/>
       <c r="M719" s="10"/>
@@ -48230,7 +48257,7 @@
         <v>967</v>
       </c>
       <c r="G720" s="4" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H720" s="5" t="n">
         <v>46170</v>
@@ -48288,7 +48315,7 @@
         <v>1456</v>
       </c>
       <c r="G721" s="9" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H721" s="10" t="n">
         <v>46169</v>
@@ -48346,7 +48373,7 @@
         <v>820</v>
       </c>
       <c r="G722" s="4" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H722" s="5" t="n">
         <v>46169</v>
@@ -48404,7 +48431,7 @@
         <v>1010</v>
       </c>
       <c r="G723" s="9" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H723" s="10" t="n">
         <v>46169</v>
@@ -48459,22 +48486,22 @@
         <v>24</v>
       </c>
       <c r="F724" s="4" t="s">
+        <v>1553</v>
+      </c>
+      <c r="G724" s="4" t="s">
         <v>1554</v>
-      </c>
-      <c r="G724" s="4" t="s">
-        <v>1555</v>
       </c>
       <c r="H724" s="5" t="n">
         <v>46169</v>
       </c>
       <c r="I724" s="4" t="s">
+        <v>1555</v>
+      </c>
+      <c r="J724" s="4" t="s">
         <v>1556</v>
       </c>
-      <c r="J724" s="4" t="s">
+      <c r="K724" s="4" t="s">
         <v>1557</v>
-      </c>
-      <c r="K724" s="4" t="s">
-        <v>1558</v>
       </c>
       <c r="L724" s="5"/>
       <c r="M724" s="5"/>
@@ -48520,7 +48547,7 @@
         <v>1100</v>
       </c>
       <c r="G725" s="9" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H725" s="10" t="n">
         <v>46170</v>
@@ -48578,7 +48605,7 @@
         <v>592</v>
       </c>
       <c r="G726" s="4" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H726" s="5" t="n">
         <v>46170</v>
@@ -48636,7 +48663,7 @@
         <v>461</v>
       </c>
       <c r="G727" s="9" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H727" s="10" t="n">
         <v>46170</v>
@@ -48694,7 +48721,7 @@
         <v>1289</v>
       </c>
       <c r="G728" s="4" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H728" s="5" t="n">
         <v>46171</v>
@@ -48752,7 +48779,7 @@
         <v>1456</v>
       </c>
       <c r="G729" s="9" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H729" s="10" t="n">
         <v>46175</v>
@@ -48810,7 +48837,7 @@
         <v>1060</v>
       </c>
       <c r="G730" s="4" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H730" s="5" t="n">
         <v>46175</v>
@@ -48868,7 +48895,7 @@
         <v>696</v>
       </c>
       <c r="G731" s="9" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H731" s="10" t="n">
         <v>46175</v>
@@ -48923,10 +48950,10 @@
         <v>24</v>
       </c>
       <c r="F732" s="4" t="s">
+        <v>1565</v>
+      </c>
+      <c r="G732" s="4" t="s">
         <v>1566</v>
-      </c>
-      <c r="G732" s="4" t="s">
-        <v>1567</v>
       </c>
       <c r="H732" s="5" t="n">
         <v>46176</v>
@@ -48984,7 +49011,7 @@
         <v>103</v>
       </c>
       <c r="G733" s="9" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H733" s="10" t="n">
         <v>46176</v>
@@ -49039,10 +49066,10 @@
         <v>24</v>
       </c>
       <c r="F734" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G734" s="4" t="s">
         <v>1569</v>
-      </c>
-      <c r="G734" s="4" t="s">
-        <v>1570</v>
       </c>
       <c r="H734" s="5" t="n">
         <v>46176</v>
@@ -49097,10 +49124,10 @@
         <v>24</v>
       </c>
       <c r="F735" s="9" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="G735" s="9" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H735" s="10" t="n">
         <v>46176</v>
@@ -49158,7 +49185,7 @@
         <v>143</v>
       </c>
       <c r="G736" s="4" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H736" s="5" t="n">
         <v>46181</v>
@@ -49216,7 +49243,7 @@
         <v>447</v>
       </c>
       <c r="G737" s="9" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H737" s="10" t="n">
         <v>46182</v>
@@ -49274,7 +49301,7 @@
         <v>143</v>
       </c>
       <c r="G738" s="4" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H738" s="5" t="n">
         <v>46182</v>
@@ -49329,10 +49356,10 @@
         <v>24</v>
       </c>
       <c r="F739" s="9" t="s">
+        <v>1574</v>
+      </c>
+      <c r="G739" s="9" t="s">
         <v>1575</v>
-      </c>
-      <c r="G739" s="9" t="s">
-        <v>1576</v>
       </c>
       <c r="H739" s="10" t="n">
         <v>46182</v>
@@ -49390,7 +49417,7 @@
         <v>1418</v>
       </c>
       <c r="G740" s="4" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H740" s="5" t="n">
         <v>46181</v>
@@ -49445,10 +49472,10 @@
         <v>24</v>
       </c>
       <c r="F741" s="9" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G741" s="9" t="s">
         <v>1578</v>
-      </c>
-      <c r="G741" s="9" t="s">
-        <v>1579</v>
       </c>
       <c r="H741" s="10" t="n">
         <v>46183</v>
@@ -49503,10 +49530,10 @@
         <v>24</v>
       </c>
       <c r="F742" s="4" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G742" s="4" t="s">
         <v>1580</v>
-      </c>
-      <c r="G742" s="4" t="s">
-        <v>1581</v>
       </c>
       <c r="H742" s="5" t="n">
         <v>46184</v>
@@ -49566,7 +49593,7 @@
         <v>1485</v>
       </c>
       <c r="G743" s="9" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H743" s="10" t="n">
         <v>46183</v>
@@ -49621,22 +49648,22 @@
         <v>24</v>
       </c>
       <c r="F744" s="4" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G744" s="4" t="s">
         <v>1583</v>
-      </c>
-      <c r="G744" s="4" t="s">
-        <v>1584</v>
       </c>
       <c r="H744" s="5" t="n">
         <v>46184</v>
       </c>
       <c r="I744" s="4" t="s">
+        <v>1584</v>
+      </c>
+      <c r="J744" s="4" t="s">
         <v>1585</v>
       </c>
-      <c r="J744" s="4" t="s">
+      <c r="K744" s="4" t="s">
         <v>1586</v>
-      </c>
-      <c r="K744" s="4" t="s">
-        <v>1587</v>
       </c>
       <c r="L744" s="5"/>
       <c r="M744" s="5"/>
@@ -49682,7 +49709,7 @@
         <v>272</v>
       </c>
       <c r="G745" s="9" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H745" s="10" t="n">
         <v>46184</v>
@@ -49740,7 +49767,7 @@
         <v>519</v>
       </c>
       <c r="G746" s="4" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H746" s="5" t="n">
         <v>46184</v>
@@ -49795,10 +49822,10 @@
         <v>24</v>
       </c>
       <c r="F747" s="9" t="s">
+        <v>1589</v>
+      </c>
+      <c r="G747" s="9" t="s">
         <v>1590</v>
-      </c>
-      <c r="G747" s="9" t="s">
-        <v>1591</v>
       </c>
       <c r="H747" s="10" t="n">
         <v>46185</v>
@@ -49853,10 +49880,10 @@
         <v>24</v>
       </c>
       <c r="F748" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G748" s="4" t="s">
         <v>1592</v>
-      </c>
-      <c r="G748" s="4" t="s">
-        <v>1593</v>
       </c>
       <c r="H748" s="5" t="n">
         <v>46185</v>
@@ -49914,7 +49941,7 @@
         <v>704</v>
       </c>
       <c r="G749" s="9" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H749" s="10" t="n">
         <v>46188</v>
@@ -49969,10 +49996,10 @@
         <v>24</v>
       </c>
       <c r="F750" s="4" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="G750" s="4" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H750" s="5" t="n">
         <v>46188</v>
@@ -50030,7 +50057,7 @@
         <v>228</v>
       </c>
       <c r="G751" s="9" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H751" s="10" t="n">
         <v>46188</v>
@@ -50088,7 +50115,7 @@
         <v>228</v>
       </c>
       <c r="G752" s="4" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H752" s="5" t="n">
         <v>46188</v>
@@ -50146,7 +50173,7 @@
         <v>589</v>
       </c>
       <c r="G753" s="9" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H753" s="10" t="n">
         <v>46189</v>
@@ -50201,22 +50228,22 @@
         <v>24</v>
       </c>
       <c r="F754" s="4" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G754" s="4" t="s">
         <v>1599</v>
-      </c>
-      <c r="G754" s="4" t="s">
-        <v>1600</v>
       </c>
       <c r="H754" s="5" t="n">
         <v>46188</v>
       </c>
       <c r="I754" s="4" t="s">
+        <v>1600</v>
+      </c>
+      <c r="J754" s="4" t="s">
         <v>1601</v>
       </c>
-      <c r="J754" s="4" t="s">
+      <c r="K754" s="4" t="s">
         <v>1602</v>
-      </c>
-      <c r="K754" s="4" t="s">
-        <v>1603</v>
       </c>
       <c r="L754" s="5"/>
       <c r="M754" s="5"/>
@@ -50262,7 +50289,7 @@
         <v>1295</v>
       </c>
       <c r="G755" s="9" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H755" s="10" t="n">
         <v>46188</v>
@@ -50320,7 +50347,7 @@
         <v>152</v>
       </c>
       <c r="G756" s="4" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H756" s="5" t="n">
         <v>46189</v>
@@ -50378,7 +50405,7 @@
         <v>1293</v>
       </c>
       <c r="G757" s="9" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H757" s="10" t="n">
         <v>46189</v>
@@ -50436,7 +50463,7 @@
         <v>1293</v>
       </c>
       <c r="G758" s="4" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H758" s="5" t="n">
         <v>46189</v>
@@ -50494,7 +50521,7 @@
         <v>402</v>
       </c>
       <c r="G759" s="9" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H759" s="10" t="n">
         <v>46190</v>
@@ -50549,22 +50576,22 @@
         <v>24</v>
       </c>
       <c r="F760" s="4" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G760" s="4" t="s">
         <v>1609</v>
-      </c>
-      <c r="G760" s="4" t="s">
-        <v>1610</v>
       </c>
       <c r="H760" s="5" t="n">
         <v>46189</v>
       </c>
       <c r="I760" s="4" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J760" s="4" t="s">
         <v>1611</v>
       </c>
-      <c r="J760" s="4" t="s">
+      <c r="K760" s="4" t="s">
         <v>1612</v>
-      </c>
-      <c r="K760" s="4" t="s">
-        <v>1613</v>
       </c>
       <c r="L760" s="5"/>
       <c r="M760" s="5"/>
@@ -50578,7 +50605,7 @@
         <v>1452</v>
       </c>
       <c r="Q760" s="4" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="R760" s="7" t="n">
         <v>2230.4</v>
@@ -50610,7 +50637,7 @@
         <v>157</v>
       </c>
       <c r="G761" s="9" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H761" s="10" t="n">
         <v>46189</v>
@@ -50665,22 +50692,22 @@
         <v>24</v>
       </c>
       <c r="F762" s="4" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G762" s="4" t="s">
         <v>1616</v>
-      </c>
-      <c r="G762" s="4" t="s">
-        <v>1617</v>
       </c>
       <c r="H762" s="5" t="n">
         <v>46191</v>
       </c>
       <c r="I762" s="4" t="s">
+        <v>1617</v>
+      </c>
+      <c r="J762" s="4" t="s">
         <v>1618</v>
       </c>
-      <c r="J762" s="4" t="s">
+      <c r="K762" s="4" t="s">
         <v>1619</v>
-      </c>
-      <c r="K762" s="4" t="s">
-        <v>1620</v>
       </c>
       <c r="L762" s="5"/>
       <c r="M762" s="5"/>
@@ -50726,7 +50753,7 @@
         <v>892</v>
       </c>
       <c r="G763" s="9" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H763" s="10" t="n">
         <v>46191</v>
@@ -50784,7 +50811,7 @@
         <v>502</v>
       </c>
       <c r="G764" s="4" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H764" s="5" t="n">
         <v>46190</v>
@@ -50842,7 +50869,7 @@
         <v>322</v>
       </c>
       <c r="G765" s="9" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H765" s="10" t="n">
         <v>46190</v>
@@ -50900,7 +50927,7 @@
         <v>1485</v>
       </c>
       <c r="G766" s="4" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H766" s="5" t="n">
         <v>46192</v>
@@ -50958,7 +50985,7 @@
         <v>249</v>
       </c>
       <c r="G767" s="9" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H767" s="10" t="n">
         <v>46191</v>
@@ -51013,10 +51040,10 @@
         <v>24</v>
       </c>
       <c r="F768" s="4" t="s">
+        <v>1625</v>
+      </c>
+      <c r="G768" s="4" t="s">
         <v>1626</v>
-      </c>
-      <c r="G768" s="4" t="s">
-        <v>1627</v>
       </c>
       <c r="H768" s="5" t="n">
         <v>46191</v>
@@ -51071,10 +51098,10 @@
         <v>24</v>
       </c>
       <c r="F769" s="9" t="s">
+        <v>1627</v>
+      </c>
+      <c r="G769" s="9" t="s">
         <v>1628</v>
-      </c>
-      <c r="G769" s="9" t="s">
-        <v>1629</v>
       </c>
       <c r="H769" s="11" t="n">
         <v>46196.641111111</v>
@@ -51097,7 +51124,7 @@
         <v>46198.434918947</v>
       </c>
       <c r="P769" s="9" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="Q769" s="9" t="s">
         <v>74</v>
@@ -51132,7 +51159,7 @@
         <v>904</v>
       </c>
       <c r="G770" s="4" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H770" s="5" t="n">
         <v>46195</v>
@@ -51190,7 +51217,7 @@
         <v>888</v>
       </c>
       <c r="G771" s="9" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H771" s="10" t="n">
         <v>46192</v>
@@ -51248,7 +51275,7 @@
         <v>995</v>
       </c>
       <c r="G772" s="4" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H772" s="5" t="n">
         <v>46198</v>
@@ -51306,7 +51333,7 @@
         <v>276</v>
       </c>
       <c r="G773" s="9" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H773" s="10" t="n">
         <v>46198</v>
@@ -51361,10 +51388,10 @@
         <v>24</v>
       </c>
       <c r="F774" s="4" t="s">
+        <v>1634</v>
+      </c>
+      <c r="G774" s="4" t="s">
         <v>1635</v>
-      </c>
-      <c r="G774" s="4" t="s">
-        <v>1636</v>
       </c>
       <c r="H774" s="5" t="n">
         <v>46198</v>
@@ -51422,7 +51449,7 @@
         <v>1268</v>
       </c>
       <c r="G775" s="9" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H775" s="10" t="n">
         <v>46196</v>
@@ -51480,7 +51507,7 @@
         <v>1261</v>
       </c>
       <c r="G776" s="4" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H776" s="5" t="n">
         <v>46195</v>
@@ -51538,7 +51565,7 @@
         <v>496</v>
       </c>
       <c r="G777" s="9" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H777" s="10" t="n">
         <v>46198</v>
@@ -51596,7 +51623,7 @@
         <v>1073</v>
       </c>
       <c r="G778" s="4" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H778" s="5" t="n">
         <v>46198</v>
@@ -51654,7 +51681,7 @@
         <v>944</v>
       </c>
       <c r="G779" s="9" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H779" s="10" t="n">
         <v>46198</v>
@@ -51712,7 +51739,7 @@
         <v>1456</v>
       </c>
       <c r="G780" s="4" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H780" s="5" t="n">
         <v>46198</v>
@@ -51767,10 +51794,10 @@
         <v>24</v>
       </c>
       <c r="F781" s="9" t="s">
+        <v>1642</v>
+      </c>
+      <c r="G781" s="9" t="s">
         <v>1643</v>
-      </c>
-      <c r="G781" s="9" t="s">
-        <v>1644</v>
       </c>
       <c r="H781" s="10" t="n">
         <v>46198</v>
@@ -51828,7 +51855,7 @@
         <v>191</v>
       </c>
       <c r="G782" s="4" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H782" s="5" t="n">
         <v>46198</v>
@@ -51883,10 +51910,10 @@
         <v>24</v>
       </c>
       <c r="F783" s="9" t="s">
+        <v>1645</v>
+      </c>
+      <c r="G783" s="9" t="s">
         <v>1646</v>
-      </c>
-      <c r="G783" s="9" t="s">
-        <v>1647</v>
       </c>
       <c r="H783" s="10" t="n">
         <v>46197</v>
@@ -51944,7 +51971,7 @@
         <v>124</v>
       </c>
       <c r="G784" s="4" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H784" s="5" t="n">
         <v>46198</v>
@@ -52002,7 +52029,7 @@
         <v>75</v>
       </c>
       <c r="G785" s="9" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H785" s="10" t="n">
         <v>46199</v>
@@ -52060,7 +52087,7 @@
         <v>332</v>
       </c>
       <c r="G786" s="4" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H786" s="5" t="n">
         <v>46199</v>
@@ -52118,7 +52145,7 @@
         <v>1470</v>
       </c>
       <c r="G787" s="9" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="H787" s="11" t="n">
         <v>46202.697662037</v>
@@ -52176,7 +52203,7 @@
         <v>249</v>
       </c>
       <c r="G788" s="4" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H788" s="6" t="n">
         <v>46203.350740741</v>
@@ -52234,7 +52261,7 @@
         <v>1100</v>
       </c>
       <c r="G789" s="9" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H789" s="11" t="n">
         <v>46203.360023148</v>
@@ -52292,7 +52319,7 @@
         <v>295</v>
       </c>
       <c r="G790" s="4" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H790" s="6" t="n">
         <v>46199.437291667</v>
@@ -52350,7 +52377,7 @@
         <v>262</v>
       </c>
       <c r="G791" s="9" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H791" s="11" t="n">
         <v>46199.61</v>
@@ -52408,7 +52435,7 @@
         <v>58</v>
       </c>
       <c r="G792" s="4" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H792" s="5" t="n">
         <v>46203</v>
@@ -52466,7 +52493,7 @@
         <v>1097</v>
       </c>
       <c r="G793" s="9" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H793" s="10" t="n">
         <v>46199</v>
@@ -52521,10 +52548,10 @@
         <v>24</v>
       </c>
       <c r="F794" s="4" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="G794" s="4" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H794" s="5" t="n">
         <v>46203</v>
@@ -52579,10 +52606,10 @@
         <v>24</v>
       </c>
       <c r="F795" s="9" t="s">
+        <v>1658</v>
+      </c>
+      <c r="G795" s="9" t="s">
         <v>1659</v>
-      </c>
-      <c r="G795" s="9" t="s">
-        <v>1660</v>
       </c>
       <c r="H795" s="11" t="n">
         <v>46203.499918981</v>
@@ -52640,7 +52667,7 @@
         <v>357</v>
       </c>
       <c r="G796" s="4" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H796" s="5" t="n">
         <v>46203</v>
@@ -52698,7 +52725,7 @@
         <v>953</v>
       </c>
       <c r="G797" s="9" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H797" s="11" t="n">
         <v>46204.462268519</v>
@@ -52756,7 +52783,7 @@
         <v>1295</v>
       </c>
       <c r="G798" s="4" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H798" s="5" t="n">
         <v>46205</v>
@@ -52811,22 +52838,22 @@
         <v>24</v>
       </c>
       <c r="F799" s="9" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="G799" s="9" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H799" s="10" t="n">
         <v>46205</v>
       </c>
       <c r="I799" s="9" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J799" s="9" t="s">
         <v>1611</v>
       </c>
-      <c r="J799" s="9" t="s">
+      <c r="K799" s="9" t="s">
         <v>1612</v>
-      </c>
-      <c r="K799" s="9" t="s">
-        <v>1613</v>
       </c>
       <c r="L799" s="10"/>
       <c r="M799" s="10"/>
@@ -52840,7 +52867,7 @@
         <v>1452</v>
       </c>
       <c r="Q799" s="9" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="R799" s="12" t="n">
         <v>5000</v>
@@ -52869,22 +52896,22 @@
         <v>24</v>
       </c>
       <c r="F800" s="4" t="s">
+        <v>1664</v>
+      </c>
+      <c r="G800" s="4" t="s">
         <v>1665</v>
-      </c>
-      <c r="G800" s="4" t="s">
-        <v>1666</v>
       </c>
       <c r="H800" s="6" t="n">
         <v>46205.688020833</v>
       </c>
       <c r="I800" s="4" t="s">
+        <v>1666</v>
+      </c>
+      <c r="J800" s="4" t="s">
+        <v>1666</v>
+      </c>
+      <c r="K800" s="4" t="s">
         <v>1667</v>
-      </c>
-      <c r="J800" s="4" t="s">
-        <v>1667</v>
-      </c>
-      <c r="K800" s="4" t="s">
-        <v>1668</v>
       </c>
       <c r="L800" s="5"/>
       <c r="M800" s="5"/>
@@ -52930,7 +52957,7 @@
         <v>1424</v>
       </c>
       <c r="G801" s="9" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H801" s="11" t="n">
         <v>46205.676435185</v>
@@ -52985,10 +53012,10 @@
         <v>24</v>
       </c>
       <c r="F802" s="4" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G802" s="4" t="s">
         <v>1670</v>
-      </c>
-      <c r="G802" s="4" t="s">
-        <v>1671</v>
       </c>
       <c r="H802" s="5" t="n">
         <v>46206</v>
@@ -53043,10 +53070,10 @@
         <v>24</v>
       </c>
       <c r="F803" s="9" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="G803" s="9" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H803" s="10" t="n">
         <v>46206</v>
@@ -53104,7 +53131,7 @@
         <v>366</v>
       </c>
       <c r="G804" s="4" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H804" s="5" t="n">
         <v>46209</v>
@@ -53162,7 +53189,7 @@
         <v>829</v>
       </c>
       <c r="G805" s="9" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="H805" s="11" t="n">
         <v>46210.393460648</v>
@@ -53217,10 +53244,10 @@
         <v>24</v>
       </c>
       <c r="F806" s="4" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G806" s="4" t="s">
         <v>1675</v>
-      </c>
-      <c r="G806" s="4" t="s">
-        <v>1676</v>
       </c>
       <c r="H806" s="5" t="n">
         <v>46210</v>
@@ -53275,22 +53302,22 @@
         <v>24</v>
       </c>
       <c r="F807" s="9" t="s">
+        <v>1676</v>
+      </c>
+      <c r="G807" s="9" t="s">
         <v>1677</v>
-      </c>
-      <c r="G807" s="9" t="s">
-        <v>1678</v>
       </c>
       <c r="H807" s="10" t="n">
         <v>46209</v>
       </c>
       <c r="I807" s="9" t="s">
+        <v>1678</v>
+      </c>
+      <c r="J807" s="9" t="s">
         <v>1679</v>
       </c>
-      <c r="J807" s="9" t="s">
+      <c r="K807" s="9" t="s">
         <v>1680</v>
-      </c>
-      <c r="K807" s="9" t="s">
-        <v>1681</v>
       </c>
       <c r="L807" s="10"/>
       <c r="M807" s="10"/>
@@ -53304,7 +53331,7 @@
         <v>1452</v>
       </c>
       <c r="Q807" s="9" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="R807" s="12" t="n">
         <v>57832.4</v>
@@ -53313,7 +53340,7 @@
         <v>57832.4</v>
       </c>
       <c r="T807" s="9" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="U807" s="9"/>
       <c r="V807" s="9"/>
@@ -53333,10 +53360,10 @@
         <v>24</v>
       </c>
       <c r="F808" s="4" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="G808" s="4" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H808" s="5" t="n">
         <v>46212</v>
@@ -53391,22 +53418,22 @@
         <v>24</v>
       </c>
       <c r="F809" s="9" t="s">
+        <v>1684</v>
+      </c>
+      <c r="G809" s="9" t="s">
         <v>1685</v>
-      </c>
-      <c r="G809" s="9" t="s">
-        <v>1686</v>
       </c>
       <c r="H809" s="10" t="n">
         <v>46209</v>
       </c>
       <c r="I809" s="9" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="J809" s="9" t="s">
+        <v>1686</v>
+      </c>
+      <c r="K809" s="9" t="s">
         <v>1687</v>
-      </c>
-      <c r="K809" s="9" t="s">
-        <v>1688</v>
       </c>
       <c r="L809" s="10"/>
       <c r="M809" s="10"/>
@@ -53420,7 +53447,7 @@
         <v>1452</v>
       </c>
       <c r="Q809" s="9" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="R809" s="12" t="n">
         <v>12246.14</v>
@@ -53429,7 +53456,7 @@
         <v>12246.14</v>
       </c>
       <c r="T809" s="9" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="U809" s="9"/>
       <c r="V809" s="9"/>
@@ -53449,22 +53476,22 @@
         <v>24</v>
       </c>
       <c r="F810" s="4" t="s">
+        <v>1688</v>
+      </c>
+      <c r="G810" s="4" t="s">
         <v>1689</v>
-      </c>
-      <c r="G810" s="4" t="s">
-        <v>1690</v>
       </c>
       <c r="H810" s="5" t="n">
         <v>46209</v>
       </c>
       <c r="I810" s="4" t="s">
+        <v>1690</v>
+      </c>
+      <c r="J810" s="4" t="s">
         <v>1691</v>
       </c>
-      <c r="J810" s="4" t="s">
+      <c r="K810" s="4" t="s">
         <v>1692</v>
-      </c>
-      <c r="K810" s="4" t="s">
-        <v>1693</v>
       </c>
       <c r="L810" s="5"/>
       <c r="M810" s="5"/>
@@ -53478,7 +53505,7 @@
         <v>1452</v>
       </c>
       <c r="Q810" s="4" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="R810" s="7" t="n">
         <v>12246.14</v>
@@ -53487,7 +53514,7 @@
         <v>12246.14</v>
       </c>
       <c r="T810" s="4" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="U810" s="4"/>
       <c r="V810" s="4"/>
@@ -53507,22 +53534,22 @@
         <v>24</v>
       </c>
       <c r="F811" s="9" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G811" s="9" t="s">
         <v>1694</v>
-      </c>
-      <c r="G811" s="9" t="s">
-        <v>1695</v>
       </c>
       <c r="H811" s="10" t="n">
         <v>46212</v>
       </c>
       <c r="I811" s="9" t="s">
+        <v>1695</v>
+      </c>
+      <c r="J811" s="9" t="s">
         <v>1696</v>
       </c>
-      <c r="J811" s="9" t="s">
+      <c r="K811" s="9" t="s">
         <v>1697</v>
-      </c>
-      <c r="K811" s="9" t="s">
-        <v>1698</v>
       </c>
       <c r="L811" s="10"/>
       <c r="M811" s="10"/>
@@ -53536,7 +53563,7 @@
         <v>1452</v>
       </c>
       <c r="Q811" s="9" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="R811" s="12" t="n">
         <v>46556.88</v>
@@ -53545,7 +53572,7 @@
         <v>46556.88</v>
       </c>
       <c r="T811" s="9" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="U811" s="9"/>
       <c r="V811" s="9"/>
@@ -53565,10 +53592,10 @@
         <v>24</v>
       </c>
       <c r="F812" s="4" t="s">
+        <v>1698</v>
+      </c>
+      <c r="G812" s="4" t="s">
         <v>1699</v>
-      </c>
-      <c r="G812" s="4" t="s">
-        <v>1700</v>
       </c>
       <c r="H812" s="6" t="n">
         <v>46212.609872685</v>
@@ -53623,10 +53650,10 @@
         <v>24</v>
       </c>
       <c r="F813" s="9" t="s">
+        <v>1700</v>
+      </c>
+      <c r="G813" s="9" t="s">
         <v>1701</v>
-      </c>
-      <c r="G813" s="9" t="s">
-        <v>1702</v>
       </c>
       <c r="H813" s="11" t="n">
         <v>46212.603854167</v>
@@ -53684,7 +53711,7 @@
         <v>328</v>
       </c>
       <c r="G814" s="4" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H814" s="6" t="n">
         <v>46212.706458333</v>
@@ -53742,7 +53769,7 @@
         <v>75</v>
       </c>
       <c r="G815" s="9" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H815" s="11" t="n">
         <v>46216.38931713</v>
@@ -53800,7 +53827,7 @@
         <v>389</v>
       </c>
       <c r="G816" s="4" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H816" s="6" t="n">
         <v>46213.494444444</v>
@@ -53858,7 +53885,7 @@
         <v>249</v>
       </c>
       <c r="G817" s="9" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H817" s="11" t="n">
         <v>46216.315104167</v>
@@ -53913,10 +53940,10 @@
         <v>24</v>
       </c>
       <c r="F818" s="4" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="G818" s="4" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H818" s="6" t="n">
         <v>46216.636458333</v>
@@ -53974,7 +54001,7 @@
         <v>1408</v>
       </c>
       <c r="G819" s="9" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H819" s="11" t="n">
         <v>46216.752118056</v>
@@ -54032,7 +54059,7 @@
         <v>164</v>
       </c>
       <c r="G820" s="4" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H820" s="6" t="n">
         <v>46216.772175926</v>
@@ -54090,7 +54117,7 @@
         <v>1485</v>
       </c>
       <c r="G821" s="9" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H821" s="10" t="n">
         <v>46217</v>
@@ -54145,10 +54172,10 @@
         <v>24</v>
       </c>
       <c r="F822" s="4" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="G822" s="4" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H822" s="6" t="n">
         <v>46217.426458333</v>
@@ -54206,7 +54233,7 @@
         <v>1370</v>
       </c>
       <c r="G823" s="9" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H823" s="10" t="n">
         <v>46217</v>
@@ -54261,10 +54288,10 @@
         <v>24</v>
       </c>
       <c r="F824" s="4" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="G824" s="4" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H824" s="5" t="n">
         <v>46219</v>
@@ -54319,10 +54346,10 @@
         <v>24</v>
       </c>
       <c r="F825" s="9" t="s">
+        <v>1713</v>
+      </c>
+      <c r="G825" s="9" t="s">
         <v>1714</v>
-      </c>
-      <c r="G825" s="9" t="s">
-        <v>1715</v>
       </c>
       <c r="H825" s="10" t="n">
         <v>46219</v>
@@ -54380,7 +54407,7 @@
         <v>1468</v>
       </c>
       <c r="G826" s="4" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H826" s="5" t="n">
         <v>46219</v>
@@ -54438,7 +54465,7 @@
         <v>332</v>
       </c>
       <c r="G827" s="9" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H827" s="11" t="n">
         <v>46218.657847222</v>
@@ -54493,10 +54520,10 @@
         <v>24</v>
       </c>
       <c r="F828" s="4" t="s">
+        <v>1717</v>
+      </c>
+      <c r="G828" s="4" t="s">
         <v>1718</v>
-      </c>
-      <c r="G828" s="4" t="s">
-        <v>1719</v>
       </c>
       <c r="H828" s="6" t="n">
         <v>46218.558854167</v>
@@ -54554,7 +54581,7 @@
         <v>484</v>
       </c>
       <c r="G829" s="9" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H829" s="11" t="n">
         <v>46218.501886574</v>
@@ -54612,7 +54639,7 @@
         <v>1261</v>
       </c>
       <c r="G830" s="4" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H830" s="5" t="n">
         <v>46219</v>
@@ -54670,7 +54697,7 @@
         <v>310</v>
       </c>
       <c r="G831" s="9" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H831" s="10" t="n">
         <v>46219</v>
@@ -54728,7 +54755,7 @@
         <v>967</v>
       </c>
       <c r="G832" s="4" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H832" s="5" t="n">
         <v>46219</v>
@@ -54783,22 +54810,22 @@
         <v>24</v>
       </c>
       <c r="F833" s="9" t="s">
+        <v>1723</v>
+      </c>
+      <c r="G833" s="9" t="s">
         <v>1724</v>
-      </c>
-      <c r="G833" s="9" t="s">
-        <v>1725</v>
       </c>
       <c r="H833" s="11" t="n">
         <v>46219.727233796</v>
       </c>
       <c r="I833" s="9" t="s">
+        <v>1725</v>
+      </c>
+      <c r="J833" s="9" t="s">
         <v>1726</v>
       </c>
-      <c r="J833" s="9" t="s">
+      <c r="K833" s="9" t="s">
         <v>1727</v>
-      </c>
-      <c r="K833" s="9" t="s">
-        <v>1728</v>
       </c>
       <c r="L833" s="10"/>
       <c r="M833" s="10"/>
@@ -54844,7 +54871,7 @@
         <v>1325</v>
       </c>
       <c r="G834" s="4" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H834" s="5" t="n">
         <v>46220</v>
@@ -54899,10 +54926,10 @@
         <v>24</v>
       </c>
       <c r="F835" s="9" t="s">
+        <v>1729</v>
+      </c>
+      <c r="G835" s="9" t="s">
         <v>1730</v>
-      </c>
-      <c r="G835" s="9" t="s">
-        <v>1731</v>
       </c>
       <c r="H835" s="10" t="n">
         <v>46223</v>
@@ -54957,10 +54984,10 @@
         <v>24</v>
       </c>
       <c r="F836" s="4" t="s">
+        <v>1731</v>
+      </c>
+      <c r="G836" s="4" t="s">
         <v>1732</v>
-      </c>
-      <c r="G836" s="4" t="s">
-        <v>1733</v>
       </c>
       <c r="H836" s="5" t="n">
         <v>46224</v>
@@ -55015,10 +55042,10 @@
         <v>24</v>
       </c>
       <c r="F837" s="9" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="G837" s="9" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H837" s="10" t="n">
         <v>46225</v>
@@ -55076,7 +55103,7 @@
         <v>1261</v>
       </c>
       <c r="G838" s="4" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H838" s="5" t="n">
         <v>46224</v>
@@ -55134,7 +55161,7 @@
         <v>203</v>
       </c>
       <c r="G839" s="9" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H839" s="10" t="n">
         <v>46224</v>
@@ -55192,7 +55219,7 @@
         <v>310</v>
       </c>
       <c r="G840" s="4" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H840" s="5" t="n">
         <v>46224</v>
@@ -55247,10 +55274,10 @@
         <v>24</v>
       </c>
       <c r="F841" s="9" t="s">
+        <v>1737</v>
+      </c>
+      <c r="G841" s="9" t="s">
         <v>1738</v>
-      </c>
-      <c r="G841" s="9" t="s">
-        <v>1739</v>
       </c>
       <c r="H841" s="10" t="n">
         <v>46224</v>
@@ -55305,10 +55332,10 @@
         <v>24</v>
       </c>
       <c r="F842" s="4" t="s">
+        <v>1739</v>
+      </c>
+      <c r="G842" s="4" t="s">
         <v>1740</v>
-      </c>
-      <c r="G842" s="4" t="s">
-        <v>1741</v>
       </c>
       <c r="H842" s="5" t="n">
         <v>46224</v>
@@ -55363,10 +55390,10 @@
         <v>24</v>
       </c>
       <c r="F843" s="9" t="s">
+        <v>1741</v>
+      </c>
+      <c r="G843" s="9" t="s">
         <v>1742</v>
-      </c>
-      <c r="G843" s="9" t="s">
-        <v>1743</v>
       </c>
       <c r="H843" s="10" t="n">
         <v>46224</v>
@@ -55421,10 +55448,10 @@
         <v>24</v>
       </c>
       <c r="F844" s="4" t="s">
+        <v>1743</v>
+      </c>
+      <c r="G844" s="4" t="s">
         <v>1744</v>
-      </c>
-      <c r="G844" s="4" t="s">
-        <v>1745</v>
       </c>
       <c r="H844" s="5" t="n">
         <v>46225</v>
@@ -55479,22 +55506,22 @@
         <v>24</v>
       </c>
       <c r="F845" s="9" t="s">
+        <v>1745</v>
+      </c>
+      <c r="G845" s="9" t="s">
         <v>1746</v>
-      </c>
-      <c r="G845" s="9" t="s">
-        <v>1747</v>
       </c>
       <c r="H845" s="10" t="n">
         <v>46225</v>
       </c>
       <c r="I845" s="9" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="J845" s="9" t="s">
+        <v>1747</v>
+      </c>
+      <c r="K845" s="9" t="s">
         <v>1748</v>
-      </c>
-      <c r="K845" s="9" t="s">
-        <v>1749</v>
       </c>
       <c r="L845" s="10"/>
       <c r="M845" s="10"/>
@@ -55537,22 +55564,22 @@
         <v>24</v>
       </c>
       <c r="F846" s="4" t="s">
+        <v>1749</v>
+      </c>
+      <c r="G846" s="4" t="s">
         <v>1750</v>
-      </c>
-      <c r="G846" s="4" t="s">
-        <v>1751</v>
       </c>
       <c r="H846" s="5" t="n">
         <v>46226</v>
       </c>
       <c r="I846" s="4" t="s">
+        <v>1751</v>
+      </c>
+      <c r="J846" s="4" t="s">
+        <v>1751</v>
+      </c>
+      <c r="K846" s="4" t="s">
         <v>1752</v>
-      </c>
-      <c r="J846" s="4" t="s">
-        <v>1752</v>
-      </c>
-      <c r="K846" s="4" t="s">
-        <v>1753</v>
       </c>
       <c r="L846" s="5"/>
       <c r="M846" s="5"/>
@@ -55598,7 +55625,7 @@
         <v>592</v>
       </c>
       <c r="G847" s="9" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H847" s="10" t="n">
         <v>46226</v>
@@ -55656,7 +55683,7 @@
         <v>1176</v>
       </c>
       <c r="G848" s="4" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H848" s="5" t="n">
         <v>46227</v>
@@ -55714,7 +55741,7 @@
         <v>623</v>
       </c>
       <c r="G849" s="9" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H849" s="10" t="n">
         <v>46225</v>
@@ -55772,7 +55799,7 @@
         <v>310</v>
       </c>
       <c r="G850" s="4" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H850" s="5" t="n">
         <v>46226</v>
@@ -55827,10 +55854,10 @@
         <v>24</v>
       </c>
       <c r="F851" s="9" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="G851" s="9" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H851" s="10" t="n">
         <v>46225</v>
@@ -55888,7 +55915,7 @@
         <v>581</v>
       </c>
       <c r="G852" s="4" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H852" s="5" t="n">
         <v>46224</v>
@@ -55943,10 +55970,10 @@
         <v>24</v>
       </c>
       <c r="F853" s="9" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="G853" s="9" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H853" s="10" t="n">
         <v>46230</v>
@@ -56001,22 +56028,22 @@
         <v>24</v>
       </c>
       <c r="F854" s="4" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G854" s="4" t="s">
         <v>1761</v>
-      </c>
-      <c r="G854" s="4" t="s">
-        <v>1762</v>
       </c>
       <c r="H854" s="5" t="n">
         <v>46227</v>
       </c>
       <c r="I854" s="4" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="J854" s="4" t="s">
+        <v>1762</v>
+      </c>
+      <c r="K854" s="4" t="s">
         <v>1763</v>
-      </c>
-      <c r="K854" s="4" t="s">
-        <v>1764</v>
       </c>
       <c r="L854" s="5"/>
       <c r="M854" s="5"/>
@@ -56059,22 +56086,22 @@
         <v>24</v>
       </c>
       <c r="F855" s="9" t="s">
+        <v>1764</v>
+      </c>
+      <c r="G855" s="9" t="s">
         <v>1765</v>
-      </c>
-      <c r="G855" s="9" t="s">
-        <v>1766</v>
       </c>
       <c r="H855" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I855" s="9" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="J855" s="9" t="s">
+        <v>1766</v>
+      </c>
+      <c r="K855" s="9" t="s">
         <v>1767</v>
-      </c>
-      <c r="K855" s="9" t="s">
-        <v>1768</v>
       </c>
       <c r="L855" s="10"/>
       <c r="M855" s="10"/>
@@ -56088,7 +56115,7 @@
         <v>1452</v>
       </c>
       <c r="Q855" s="9" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="R855" s="12" t="n">
         <v>176352</v>
@@ -56120,7 +56147,7 @@
         <v>276</v>
       </c>
       <c r="G856" s="4" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H856" s="5" t="n">
         <v>46230</v>
@@ -56178,7 +56205,7 @@
         <v>1277</v>
       </c>
       <c r="G857" s="9" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H857" s="10" t="n">
         <v>46231</v>
@@ -56236,7 +56263,7 @@
         <v>592</v>
       </c>
       <c r="G858" s="4" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H858" s="5" t="n">
         <v>46230</v>
@@ -56294,7 +56321,7 @@
         <v>1261</v>
       </c>
       <c r="G859" s="9" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H859" s="10" t="n">
         <v>46231</v>
@@ -56349,10 +56376,10 @@
         <v>24</v>
       </c>
       <c r="F860" s="4" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G860" s="4" t="s">
         <v>1773</v>
-      </c>
-      <c r="G860" s="4" t="s">
-        <v>1774</v>
       </c>
       <c r="H860" s="5" t="n">
         <v>46230</v>
@@ -56407,22 +56434,22 @@
         <v>24</v>
       </c>
       <c r="F861" s="9" t="s">
+        <v>1774</v>
+      </c>
+      <c r="G861" s="9" t="s">
         <v>1775</v>
-      </c>
-      <c r="G861" s="9" t="s">
-        <v>1776</v>
       </c>
       <c r="H861" s="10" t="n">
         <v>46231</v>
       </c>
       <c r="I861" s="9" t="s">
+        <v>1776</v>
+      </c>
+      <c r="J861" s="9" t="s">
         <v>1777</v>
       </c>
-      <c r="J861" s="9" t="s">
+      <c r="K861" s="9" t="s">
         <v>1778</v>
-      </c>
-      <c r="K861" s="9" t="s">
-        <v>1779</v>
       </c>
       <c r="L861" s="10"/>
       <c r="M861" s="10"/>
@@ -56436,7 +56463,7 @@
         <v>1452</v>
       </c>
       <c r="Q861" s="9" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="R861" s="12" t="n">
         <v>38027.08</v>
@@ -56445,7 +56472,7 @@
         <v>38027.08</v>
       </c>
       <c r="T861" s="9" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="U861" s="9"/>
       <c r="V861" s="9"/>
@@ -56465,22 +56492,22 @@
         <v>24</v>
       </c>
       <c r="F862" s="4" t="s">
+        <v>1779</v>
+      </c>
+      <c r="G862" s="4" t="s">
         <v>1780</v>
-      </c>
-      <c r="G862" s="4" t="s">
-        <v>1781</v>
       </c>
       <c r="H862" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="I862" s="4" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="J862" s="4" t="s">
+        <v>1781</v>
+      </c>
+      <c r="K862" s="4" t="s">
         <v>1782</v>
-      </c>
-      <c r="K862" s="4" t="s">
-        <v>1783</v>
       </c>
       <c r="L862" s="5"/>
       <c r="M862" s="5"/>
@@ -56526,7 +56553,7 @@
         <v>859</v>
       </c>
       <c r="G863" s="9" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H863" s="10" t="n">
         <v>46230</v>
@@ -56584,7 +56611,7 @@
         <v>262</v>
       </c>
       <c r="G864" s="4" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H864" s="5" t="n">
         <v>46230</v>
@@ -56639,22 +56666,22 @@
         <v>24</v>
       </c>
       <c r="F865" s="9" t="s">
+        <v>1785</v>
+      </c>
+      <c r="G865" s="9" t="s">
         <v>1786</v>
-      </c>
-      <c r="G865" s="9" t="s">
-        <v>1787</v>
       </c>
       <c r="H865" s="10" t="n">
         <v>46230</v>
       </c>
       <c r="I865" s="9" t="s">
+        <v>1787</v>
+      </c>
+      <c r="J865" s="9" t="s">
+        <v>1787</v>
+      </c>
+      <c r="K865" s="9" t="s">
         <v>1788</v>
-      </c>
-      <c r="J865" s="9" t="s">
-        <v>1788</v>
-      </c>
-      <c r="K865" s="9" t="s">
-        <v>1789</v>
       </c>
       <c r="L865" s="10"/>
       <c r="M865" s="10"/>
@@ -56700,7 +56727,7 @@
         <v>490</v>
       </c>
       <c r="G866" s="4" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H866" s="5" t="n">
         <v>46231</v>
@@ -56758,7 +56785,7 @@
         <v>521</v>
       </c>
       <c r="G867" s="9" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H867" s="10" t="n">
         <v>46232</v>
@@ -56813,10 +56840,10 @@
         <v>24</v>
       </c>
       <c r="F868" s="4" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="G868" s="4" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H868" s="5" t="n">
         <v>46231</v>
@@ -56874,7 +56901,7 @@
         <v>1130</v>
       </c>
       <c r="G869" s="9" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H869" s="10" t="n">
         <v>46233</v>
@@ -56929,10 +56956,10 @@
         <v>24</v>
       </c>
       <c r="F870" s="4" t="s">
+        <v>1793</v>
+      </c>
+      <c r="G870" s="4" t="s">
         <v>1794</v>
-      </c>
-      <c r="G870" s="4" t="s">
-        <v>1795</v>
       </c>
       <c r="H870" s="5" t="n">
         <v>46232</v>
@@ -56990,7 +57017,7 @@
         <v>355</v>
       </c>
       <c r="G871" s="9" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H871" s="10" t="n">
         <v>46232</v>
@@ -57048,7 +57075,7 @@
         <v>351</v>
       </c>
       <c r="G872" s="4" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H872" s="5" t="n">
         <v>46232</v>
@@ -57106,7 +57133,7 @@
         <v>944</v>
       </c>
       <c r="G873" s="9" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H873" s="10" t="n">
         <v>46232</v>
@@ -57164,7 +57191,7 @@
         <v>262</v>
       </c>
       <c r="G874" s="4" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H874" s="5" t="n">
         <v>46231</v>
@@ -57222,7 +57249,7 @@
         <v>1261</v>
       </c>
       <c r="G875" s="9" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H875" s="10" t="n">
         <v>46232</v>
@@ -57277,10 +57304,10 @@
         <v>24</v>
       </c>
       <c r="F876" s="4" t="s">
+        <v>1800</v>
+      </c>
+      <c r="G876" s="4" t="s">
         <v>1801</v>
-      </c>
-      <c r="G876" s="4" t="s">
-        <v>1802</v>
       </c>
       <c r="H876" s="5" t="n">
         <v>46232</v>
@@ -57338,7 +57365,7 @@
         <v>75</v>
       </c>
       <c r="G877" s="9" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H877" s="10" t="n">
         <v>46232</v>
@@ -57396,7 +57423,7 @@
         <v>408</v>
       </c>
       <c r="G878" s="4" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H878" s="5" t="n">
         <v>46232</v>
@@ -57454,7 +57481,7 @@
         <v>1470</v>
       </c>
       <c r="G879" s="9" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="H879" s="10" t="n">
         <v>46232</v>
@@ -57509,22 +57536,22 @@
         <v>24</v>
       </c>
       <c r="F880" s="4" t="s">
+        <v>1805</v>
+      </c>
+      <c r="G880" s="4" t="s">
         <v>1806</v>
-      </c>
-      <c r="G880" s="4" t="s">
-        <v>1807</v>
       </c>
       <c r="H880" s="5" t="n">
         <v>46233</v>
       </c>
       <c r="I880" s="4" t="s">
+        <v>1807</v>
+      </c>
+      <c r="J880" s="4" t="s">
         <v>1808</v>
       </c>
-      <c r="J880" s="4" t="s">
+      <c r="K880" s="4" t="s">
         <v>1809</v>
-      </c>
-      <c r="K880" s="4" t="s">
-        <v>1810</v>
       </c>
       <c r="L880" s="5"/>
       <c r="M880" s="5"/>
@@ -57570,7 +57597,7 @@
         <v>276</v>
       </c>
       <c r="G881" s="9" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H881" s="10" t="n">
         <v>46234</v>
@@ -57628,7 +57655,7 @@
         <v>1295</v>
       </c>
       <c r="G882" s="4" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H882" s="5" t="n">
         <v>46233</v>
@@ -57683,10 +57710,10 @@
         <v>24</v>
       </c>
       <c r="F883" s="9" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="G883" s="9" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H883" s="10" t="n">
         <v>46234</v>
@@ -57744,7 +57771,7 @@
         <v>888</v>
       </c>
       <c r="G884" s="4" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="H884" s="5" t="n">
         <v>46234</v>
@@ -57799,10 +57826,10 @@
         <v>24</v>
       </c>
       <c r="F885" s="9" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="G885" s="9" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H885" s="10" t="n">
         <v>46234</v>
@@ -57860,7 +57887,7 @@
         <v>1375</v>
       </c>
       <c r="G886" s="4" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="H886" s="5" t="n">
         <v>46234</v>
@@ -57915,22 +57942,22 @@
         <v>24</v>
       </c>
       <c r="F887" s="9" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="G887" s="9" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H887" s="10" t="n">
         <v>46233</v>
       </c>
       <c r="I887" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="J887" s="9" t="s">
         <v>1601</v>
       </c>
-      <c r="J887" s="9" t="s">
+      <c r="K887" s="9" t="s">
         <v>1602</v>
-      </c>
-      <c r="K887" s="9" t="s">
-        <v>1603</v>
       </c>
       <c r="L887" s="10"/>
       <c r="M887" s="10"/>
@@ -57973,22 +58000,22 @@
         <v>24</v>
       </c>
       <c r="F888" s="4" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="G888" s="4" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="H888" s="5" t="n">
         <v>46234</v>
       </c>
       <c r="I888" s="4" t="s">
+        <v>1725</v>
+      </c>
+      <c r="J888" s="4" t="s">
         <v>1726</v>
       </c>
-      <c r="J888" s="4" t="s">
+      <c r="K888" s="4" t="s">
         <v>1727</v>
-      </c>
-      <c r="K888" s="4" t="s">
-        <v>1728</v>
       </c>
       <c r="L888" s="5"/>
       <c r="M888" s="5"/>
@@ -58034,7 +58061,7 @@
         <v>143</v>
       </c>
       <c r="G889" s="9" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="H889" s="10" t="n">
         <v>46238</v>
@@ -58092,7 +58119,7 @@
         <v>402</v>
       </c>
       <c r="G890" s="4" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="H890" s="5" t="n">
         <v>46238</v>
@@ -58150,7 +58177,7 @@
         <v>698</v>
       </c>
       <c r="G891" s="9" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H891" s="10" t="n">
         <v>46238</v>
@@ -58208,7 +58235,7 @@
         <v>328</v>
       </c>
       <c r="G892" s="4" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H892" s="5" t="n">
         <v>46238</v>
@@ -58266,7 +58293,7 @@
         <v>1261</v>
       </c>
       <c r="G893" s="9" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="H893" s="10" t="n">
         <v>46240</v>
@@ -58324,7 +58351,7 @@
         <v>203</v>
       </c>
       <c r="G894" s="4" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="H894" s="5" t="n">
         <v>46240</v>
@@ -58382,7 +58409,7 @@
         <v>829</v>
       </c>
       <c r="G895" s="9" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="H895" s="10" t="n">
         <v>46240</v>
@@ -58437,22 +58464,22 @@
         <v>24</v>
       </c>
       <c r="F896" s="4" t="s">
+        <v>1825</v>
+      </c>
+      <c r="G896" s="4" t="s">
         <v>1826</v>
-      </c>
-      <c r="G896" s="4" t="s">
-        <v>1827</v>
       </c>
       <c r="H896" s="5" t="n">
         <v>46240</v>
       </c>
       <c r="I896" s="4" t="s">
+        <v>1827</v>
+      </c>
+      <c r="J896" s="4" t="s">
         <v>1828</v>
       </c>
-      <c r="J896" s="4" t="s">
+      <c r="K896" s="4" t="s">
         <v>1829</v>
-      </c>
-      <c r="K896" s="4" t="s">
-        <v>1830</v>
       </c>
       <c r="L896" s="5"/>
       <c r="M896" s="5"/>
@@ -58475,7 +58502,7 @@
         <v>7411.2</v>
       </c>
       <c r="T896" s="4" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="U896" s="4"/>
       <c r="V896" s="4"/>
@@ -58495,22 +58522,22 @@
         <v>24</v>
       </c>
       <c r="F897" s="9" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="G897" s="9" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="H897" s="10" t="n">
         <v>46240</v>
       </c>
       <c r="I897" s="9" t="s">
+        <v>1827</v>
+      </c>
+      <c r="J897" s="9" t="s">
         <v>1828</v>
       </c>
-      <c r="J897" s="9" t="s">
+      <c r="K897" s="9" t="s">
         <v>1829</v>
-      </c>
-      <c r="K897" s="9" t="s">
-        <v>1830</v>
       </c>
       <c r="L897" s="10"/>
       <c r="M897" s="10"/>
@@ -58533,7 +58560,7 @@
         <v>6860.4</v>
       </c>
       <c r="T897" s="9" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="U897" s="9"/>
       <c r="V897" s="9"/>
@@ -58556,7 +58583,7 @@
         <v>75</v>
       </c>
       <c r="G898" s="4" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H898" s="5" t="n">
         <v>46241</v>
@@ -58614,7 +58641,7 @@
         <v>1054</v>
       </c>
       <c r="G899" s="9" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H899" s="10" t="n">
         <v>46244</v>
@@ -58672,7 +58699,7 @@
         <v>1485</v>
       </c>
       <c r="G900" s="4" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H900" s="5" t="n">
         <v>46244</v>
@@ -58730,7 +58757,7 @@
         <v>1261</v>
       </c>
       <c r="G901" s="9" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H901" s="11" t="n">
         <v>46244.693715278</v>
@@ -58788,7 +58815,7 @@
         <v>904</v>
       </c>
       <c r="G902" s="4" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="H902" s="6" t="n">
         <v>46244.646689815</v>
@@ -58843,22 +58870,22 @@
         <v>24</v>
       </c>
       <c r="F903" s="9" t="s">
+        <v>1837</v>
+      </c>
+      <c r="G903" s="9" t="s">
         <v>1838</v>
-      </c>
-      <c r="G903" s="9" t="s">
-        <v>1839</v>
       </c>
       <c r="H903" s="11" t="n">
         <v>46244.891539352</v>
       </c>
       <c r="I903" s="9" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="J903" s="9" t="s">
+        <v>1839</v>
+      </c>
+      <c r="K903" s="9" t="s">
         <v>1840</v>
-      </c>
-      <c r="K903" s="9" t="s">
-        <v>1841</v>
       </c>
       <c r="L903" s="10"/>
       <c r="M903" s="10"/>
@@ -58904,7 +58931,7 @@
         <v>592</v>
       </c>
       <c r="G904" s="4" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H904" s="6" t="n">
         <v>46244.846145833</v>
@@ -58962,7 +58989,7 @@
         <v>75</v>
       </c>
       <c r="G905" s="9" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H905" s="11" t="n">
         <v>46244.704305556</v>
@@ -59020,7 +59047,7 @@
         <v>58</v>
       </c>
       <c r="G906" s="4" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="H906" s="6" t="n">
         <v>46245.52099537</v>
@@ -59078,7 +59105,7 @@
         <v>152</v>
       </c>
       <c r="G907" s="9" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H907" s="11" t="n">
         <v>46245.60755787</v>
@@ -59136,7 +59163,7 @@
         <v>295</v>
       </c>
       <c r="G908" s="4" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="H908" s="6" t="n">
         <v>46245.672013889</v>
@@ -59194,7 +59221,7 @@
         <v>249</v>
       </c>
       <c r="G909" s="9" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="H909" s="10" t="n">
         <v>46247</v>
@@ -59252,7 +59279,7 @@
         <v>249</v>
       </c>
       <c r="G910" s="4" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="H910" s="6" t="n">
         <v>46247.371365741</v>
@@ -59310,7 +59337,7 @@
         <v>986</v>
       </c>
       <c r="G911" s="9" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H911" s="11" t="n">
         <v>46247.461736111</v>
@@ -59365,22 +59392,22 @@
         <v>24</v>
       </c>
       <c r="F912" s="4" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="G912" s="4" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="H912" s="6" t="n">
         <v>46246.935729167</v>
       </c>
       <c r="I912" s="4" t="s">
+        <v>1666</v>
+      </c>
+      <c r="J912" s="4" t="s">
+        <v>1666</v>
+      </c>
+      <c r="K912" s="4" t="s">
         <v>1667</v>
-      </c>
-      <c r="J912" s="4" t="s">
-        <v>1667</v>
-      </c>
-      <c r="K912" s="4" t="s">
-        <v>1668</v>
       </c>
       <c r="L912" s="5"/>
       <c r="M912" s="5"/>
@@ -59423,22 +59450,22 @@
         <v>24</v>
       </c>
       <c r="F913" s="9" t="s">
+        <v>1850</v>
+      </c>
+      <c r="G913" s="9" t="s">
         <v>1851</v>
-      </c>
-      <c r="G913" s="9" t="s">
-        <v>1852</v>
       </c>
       <c r="H913" s="11" t="n">
         <v>46246.852106481</v>
       </c>
       <c r="I913" s="9" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="J913" s="9" t="s">
+        <v>1852</v>
+      </c>
+      <c r="K913" s="9" t="s">
         <v>1853</v>
-      </c>
-      <c r="K913" s="9" t="s">
-        <v>1854</v>
       </c>
       <c r="L913" s="10"/>
       <c r="M913" s="10"/>
@@ -59484,7 +59511,7 @@
         <v>332</v>
       </c>
       <c r="G914" s="4" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H914" s="6" t="n">
         <v>46246.467384259</v>
@@ -59542,7 +59569,7 @@
         <v>328</v>
       </c>
       <c r="G915" s="9" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H915" s="11" t="n">
         <v>46247.693402778</v>
@@ -59597,22 +59624,22 @@
         <v>24</v>
       </c>
       <c r="F916" s="4" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="G916" s="4" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H916" s="6" t="n">
         <v>46247.72962963</v>
       </c>
       <c r="I916" s="4" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="J916" s="4" t="s">
+        <v>1503</v>
+      </c>
+      <c r="K916" s="4" t="s">
         <v>1504</v>
-      </c>
-      <c r="K916" s="4" t="s">
-        <v>1505</v>
       </c>
       <c r="L916" s="5"/>
       <c r="M916" s="5"/>
@@ -59658,7 +59685,7 @@
         <v>1470</v>
       </c>
       <c r="G917" s="9" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H917" s="11" t="n">
         <v>46247.621585648</v>
@@ -59716,7 +59743,7 @@
         <v>75</v>
       </c>
       <c r="G918" s="4" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H918" s="6" t="n">
         <v>46248.419988426</v>
@@ -59774,7 +59801,7 @@
         <v>328</v>
       </c>
       <c r="G919" s="9" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="H919" s="11" t="n">
         <v>46248.451365741</v>
@@ -59832,7 +59859,7 @@
         <v>272</v>
       </c>
       <c r="G920" s="4" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H920" s="5" t="n">
         <v>46248</v>
@@ -59890,7 +59917,7 @@
         <v>1058</v>
       </c>
       <c r="G921" s="9" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H921" s="11" t="n">
         <v>46251.721273148</v>
@@ -59948,7 +59975,7 @@
         <v>262</v>
       </c>
       <c r="G922" s="4" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H922" s="6" t="n">
         <v>46251.698263889</v>
@@ -60003,22 +60030,22 @@
         <v>24</v>
       </c>
       <c r="F923" s="9" t="s">
+        <v>1863</v>
+      </c>
+      <c r="G923" s="9" t="s">
         <v>1864</v>
-      </c>
-      <c r="G923" s="9" t="s">
-        <v>1865</v>
       </c>
       <c r="H923" s="11" t="n">
         <v>46253.493287037</v>
       </c>
       <c r="I923" s="9" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="J923" s="9" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K923" s="9" t="s">
         <v>1866</v>
-      </c>
-      <c r="K923" s="9" t="s">
-        <v>1867</v>
       </c>
       <c r="L923" s="10"/>
       <c r="M923" s="10"/>
@@ -60064,7 +60091,7 @@
         <v>461</v>
       </c>
       <c r="G924" s="4" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H924" s="6" t="n">
         <v>46252.750821759</v>
@@ -60122,7 +60149,7 @@
         <v>1424</v>
       </c>
       <c r="G925" s="9" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H925" s="11" t="n">
         <v>46252.487453704</v>
@@ -60180,7 +60207,7 @@
         <v>75</v>
       </c>
       <c r="G926" s="4" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H926" s="6" t="n">
         <v>46253.626689815</v>
@@ -60238,7 +60265,7 @@
         <v>589</v>
       </c>
       <c r="G927" s="9" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H927" s="10" t="n">
         <v>46255</v>
@@ -60296,7 +60323,7 @@
         <v>355</v>
       </c>
       <c r="G928" s="4" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H928" s="5" t="n">
         <v>46255</v>
@@ -60351,22 +60378,22 @@
         <v>24</v>
       </c>
       <c r="F929" s="9" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G929" s="9" t="s">
         <v>1873</v>
-      </c>
-      <c r="G929" s="9" t="s">
-        <v>1874</v>
       </c>
       <c r="H929" s="10" t="n">
         <v>46254</v>
       </c>
       <c r="I929" s="9" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="J929" s="9" t="s">
+        <v>1874</v>
+      </c>
+      <c r="K929" s="9" t="s">
         <v>1875</v>
-      </c>
-      <c r="K929" s="9" t="s">
-        <v>1876</v>
       </c>
       <c r="L929" s="10"/>
       <c r="M929" s="10"/>
@@ -60380,7 +60407,7 @@
         <v>1452</v>
       </c>
       <c r="Q929" s="9" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="R929" s="12" t="n">
         <v>116127.08</v>
@@ -60412,7 +60439,7 @@
         <v>698</v>
       </c>
       <c r="G930" s="4" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H930" s="6" t="n">
         <v>46258.645081019</v>
@@ -60470,7 +60497,7 @@
         <v>103</v>
       </c>
       <c r="G931" s="9" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H931" s="11" t="n">
         <v>46258.652638889</v>
@@ -60528,7 +60555,7 @@
         <v>888</v>
       </c>
       <c r="G932" s="4" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H932" s="6" t="n">
         <v>46258.672395833</v>
@@ -60586,7 +60613,7 @@
         <v>1456</v>
       </c>
       <c r="G933" s="9" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H933" s="11" t="n">
         <v>46259.638611111</v>
@@ -60641,22 +60668,22 @@
         <v>24</v>
       </c>
       <c r="F934" s="4" t="s">
+        <v>1881</v>
+      </c>
+      <c r="G934" s="4" t="s">
         <v>1882</v>
-      </c>
-      <c r="G934" s="4" t="s">
-        <v>1883</v>
       </c>
       <c r="H934" s="6" t="n">
         <v>46259.473958333</v>
       </c>
       <c r="I934" s="4" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="J934" s="4" t="s">
+        <v>1883</v>
+      </c>
+      <c r="K934" s="4" t="s">
         <v>1884</v>
-      </c>
-      <c r="K934" s="4" t="s">
-        <v>1885</v>
       </c>
       <c r="L934" s="5"/>
       <c r="M934" s="5"/>
@@ -60702,7 +60729,7 @@
         <v>1058</v>
       </c>
       <c r="G935" s="9" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="H935" s="11" t="n">
         <v>46259.50275463</v>
@@ -60757,22 +60784,22 @@
         <v>24</v>
       </c>
       <c r="F936" s="4" t="s">
+        <v>1886</v>
+      </c>
+      <c r="G936" s="4" t="s">
         <v>1887</v>
-      </c>
-      <c r="G936" s="4" t="s">
-        <v>1888</v>
       </c>
       <c r="H936" s="5" t="n">
         <v>46259</v>
       </c>
       <c r="I936" s="4" t="s">
+        <v>1888</v>
+      </c>
+      <c r="J936" s="4" t="s">
         <v>1889</v>
       </c>
-      <c r="J936" s="4" t="s">
+      <c r="K936" s="4" t="s">
         <v>1890</v>
-      </c>
-      <c r="K936" s="4" t="s">
-        <v>1891</v>
       </c>
       <c r="L936" s="5"/>
       <c r="M936" s="5"/>
@@ -60786,7 +60813,7 @@
         <v>1452</v>
       </c>
       <c r="Q936" s="4" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="R936" s="7" t="n">
         <v>42572</v>
@@ -60818,7 +60845,7 @@
         <v>698</v>
       </c>
       <c r="G937" s="9" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H937" s="11" t="n">
         <v>46259.659039352</v>
@@ -60876,7 +60903,7 @@
         <v>262</v>
       </c>
       <c r="G938" s="4" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H938" s="6" t="n">
         <v>46259.757233796</v>
@@ -60934,7 +60961,7 @@
         <v>944</v>
       </c>
       <c r="G939" s="9" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="H939" s="11" t="n">
         <v>46259.670231481</v>
@@ -60992,7 +61019,7 @@
         <v>408</v>
       </c>
       <c r="G940" s="4" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H940" s="6" t="n">
         <v>46261.456944444</v>
@@ -61047,10 +61074,10 @@
         <v>24</v>
       </c>
       <c r="F941" s="9" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="G941" s="9" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="H941" s="11" t="n">
         <v>46260.641412037</v>
@@ -61108,7 +61135,7 @@
         <v>1277</v>
       </c>
       <c r="G942" s="4" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H942" s="6" t="n">
         <v>46261.627002315</v>
@@ -61160,13 +61187,13 @@
         <v>23</v>
       </c>
       <c r="E943" s="8" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="F943" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G943" s="9" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H943" s="11" t="n">
         <v>46261.674166667</v>
@@ -61224,7 +61251,7 @@
         <v>211</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H944" s="6" t="n">
         <v>46261.624131944</v>
@@ -61282,7 +61309,7 @@
         <v>521</v>
       </c>
       <c r="G945" s="9" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H945" s="11" t="n">
         <v>46261.626898148</v>
@@ -61340,7 +61367,7 @@
         <v>1054</v>
       </c>
       <c r="G946" s="4" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H946" s="5" t="n">
         <v>46262</v>
@@ -61398,7 +61425,7 @@
         <v>1017</v>
       </c>
       <c r="G947" s="9" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H947" s="10" t="n">
         <v>46261</v>
@@ -61456,7 +61483,7 @@
         <v>38</v>
       </c>
       <c r="G948" s="4" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="H948" s="6" t="n">
         <v>46262.683993056</v>
@@ -61508,25 +61535,25 @@
         <v>23</v>
       </c>
       <c r="E949" s="8" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F949" s="9" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G949" s="9" t="s">
         <v>1905</v>
-      </c>
-      <c r="F949" s="9" t="s">
-        <v>1726</v>
-      </c>
-      <c r="G949" s="9" t="s">
-        <v>1906</v>
       </c>
       <c r="H949" s="10" t="n">
         <v>46265</v>
       </c>
       <c r="I949" s="9" t="s">
+        <v>1725</v>
+      </c>
+      <c r="J949" s="9" t="s">
         <v>1726</v>
       </c>
-      <c r="J949" s="9" t="s">
+      <c r="K949" s="9" t="s">
         <v>1727</v>
-      </c>
-      <c r="K949" s="9" t="s">
-        <v>1728</v>
       </c>
       <c r="L949" s="10"/>
       <c r="M949" s="10"/>
@@ -61566,13 +61593,13 @@
         <v>23</v>
       </c>
       <c r="E950" s="3" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F950" s="4" t="s">
+        <v>1634</v>
+      </c>
+      <c r="G950" s="4" t="s">
         <v>1907</v>
-      </c>
-      <c r="F950" s="4" t="s">
-        <v>1635</v>
-      </c>
-      <c r="G950" s="4" t="s">
-        <v>1908</v>
       </c>
       <c r="H950" s="5" t="n">
         <v>46265</v>
@@ -61630,7 +61657,7 @@
         <v>619</v>
       </c>
       <c r="G951" s="9" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H951" s="11" t="n">
         <v>46265.756805556</v>
@@ -61688,7 +61715,7 @@
         <v>103</v>
       </c>
       <c r="G952" s="4" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="H952" s="6" t="n">
         <v>46262.6721875</v>
@@ -61746,7 +61773,7 @@
         <v>814</v>
       </c>
       <c r="G953" s="9" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H953" s="11" t="n">
         <v>46265.738773148</v>
@@ -61804,7 +61831,7 @@
         <v>484</v>
       </c>
       <c r="G954" s="4" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H954" s="6" t="n">
         <v>46265.406400463</v>
@@ -61862,7 +61889,7 @@
         <v>482</v>
       </c>
       <c r="G955" s="9" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H955" s="11" t="n">
         <v>46262.643506944</v>
@@ -61920,7 +61947,7 @@
         <v>744</v>
       </c>
       <c r="G956" s="4" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="H956" s="6" t="n">
         <v>46262.644305556</v>
@@ -61978,7 +62005,7 @@
         <v>1176</v>
       </c>
       <c r="G957" s="9" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H957" s="11" t="n">
         <v>46262.617488426</v>
@@ -62033,10 +62060,10 @@
         <v>24</v>
       </c>
       <c r="F958" s="4" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G958" s="4" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H958" s="6" t="n">
         <v>46262.337835648</v>
@@ -62091,10 +62118,10 @@
         <v>24</v>
       </c>
       <c r="F959" s="9" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="G959" s="9" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H959" s="10" t="n">
         <v>46266</v>
@@ -62149,10 +62176,10 @@
         <v>24</v>
       </c>
       <c r="F960" s="4" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G960" s="4" t="s">
         <v>1918</v>
-      </c>
-      <c r="G960" s="4" t="s">
-        <v>1919</v>
       </c>
       <c r="H960" s="5" t="n">
         <v>46265</v>
@@ -62207,22 +62234,22 @@
         <v>24</v>
       </c>
       <c r="F961" s="9" t="s">
+        <v>1919</v>
+      </c>
+      <c r="G961" s="9" t="s">
         <v>1920</v>
-      </c>
-      <c r="G961" s="9" t="s">
-        <v>1921</v>
       </c>
       <c r="H961" s="10" t="n">
         <v>46266</v>
       </c>
       <c r="I961" s="9" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="J961" s="9" t="s">
+        <v>1921</v>
+      </c>
+      <c r="K961" s="9" t="s">
         <v>1922</v>
-      </c>
-      <c r="K961" s="9" t="s">
-        <v>1923</v>
       </c>
       <c r="L961" s="10"/>
       <c r="M961" s="10"/>
@@ -62236,7 +62263,7 @@
         <v>1452</v>
       </c>
       <c r="Q961" s="9" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="R961" s="12" t="n">
         <v>17437.2</v>
@@ -62265,22 +62292,22 @@
         <v>24</v>
       </c>
       <c r="F962" s="4" t="s">
+        <v>1923</v>
+      </c>
+      <c r="G962" s="4" t="s">
         <v>1924</v>
-      </c>
-      <c r="G962" s="4" t="s">
-        <v>1925</v>
       </c>
       <c r="H962" s="5" t="n">
         <v>46265</v>
       </c>
       <c r="I962" s="4" t="s">
+        <v>1925</v>
+      </c>
+      <c r="J962" s="4" t="s">
         <v>1926</v>
       </c>
-      <c r="J962" s="4" t="s">
+      <c r="K962" s="4" t="s">
         <v>1927</v>
-      </c>
-      <c r="K962" s="4" t="s">
-        <v>1928</v>
       </c>
       <c r="L962" s="5"/>
       <c r="M962" s="5"/>
@@ -62294,7 +62321,7 @@
         <v>1452</v>
       </c>
       <c r="Q962" s="4" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="R962" s="7" t="n">
         <v>10074</v>
@@ -62326,7 +62353,7 @@
         <v>944</v>
       </c>
       <c r="G963" s="9" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H963" s="11" t="n">
         <v>46267.438217593</v>
@@ -62384,7 +62411,7 @@
         <v>310</v>
       </c>
       <c r="G964" s="4" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H964" s="5" t="n">
         <v>46269</v>
@@ -62442,7 +62469,7 @@
         <v>402</v>
       </c>
       <c r="G965" s="9" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H965" s="11" t="n">
         <v>46269.745752315</v>
@@ -62500,7 +62527,7 @@
         <v>986</v>
       </c>
       <c r="G966" s="4" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="H966" s="6" t="n">
         <v>46269.693969907</v>
@@ -62558,7 +62585,7 @@
         <v>1077</v>
       </c>
       <c r="G967" s="9" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="H967" s="11" t="n">
         <v>46269.459189815</v>
@@ -62613,10 +62640,10 @@
         <v>24</v>
       </c>
       <c r="F968" s="4" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="G968" s="4" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="H968" s="6" t="n">
         <v>46268.442615741</v>
@@ -62674,7 +62701,7 @@
         <v>157</v>
       </c>
       <c r="G969" s="9" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="H969" s="10" t="n">
         <v>46268</v>
@@ -62732,7 +62759,7 @@
         <v>967</v>
       </c>
       <c r="G970" s="4" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="H970" s="5" t="n">
         <v>46268</v>
@@ -62787,10 +62814,10 @@
         <v>24</v>
       </c>
       <c r="F971" s="9" t="s">
+        <v>1936</v>
+      </c>
+      <c r="G971" s="9" t="s">
         <v>1937</v>
-      </c>
-      <c r="G971" s="9" t="s">
-        <v>1938</v>
       </c>
       <c r="H971" s="10" t="n">
         <v>46273</v>
@@ -62848,7 +62875,7 @@
         <v>1261</v>
       </c>
       <c r="G972" s="4" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H972" s="5" t="n">
         <v>46273</v>
@@ -62906,7 +62933,7 @@
         <v>152</v>
       </c>
       <c r="G973" s="9" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="H973" s="11" t="n">
         <v>46273.758136574</v>
@@ -62961,22 +62988,22 @@
         <v>24</v>
       </c>
       <c r="F974" s="4" t="s">
+        <v>1940</v>
+      </c>
+      <c r="G974" s="4" t="s">
         <v>1941</v>
-      </c>
-      <c r="G974" s="4" t="s">
-        <v>1942</v>
       </c>
       <c r="H974" s="6" t="n">
         <v>46273.740416667</v>
       </c>
       <c r="I974" s="4" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="J974" s="4" t="s">
+        <v>1942</v>
+      </c>
+      <c r="K974" s="4" t="s">
         <v>1943</v>
-      </c>
-      <c r="K974" s="4" t="s">
-        <v>1944</v>
       </c>
       <c r="L974" s="5"/>
       <c r="M974" s="5"/>
@@ -63022,7 +63049,7 @@
         <v>1408</v>
       </c>
       <c r="G975" s="9" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="H975" s="11" t="n">
         <v>46273.780162037</v>
@@ -63077,10 +63104,10 @@
         <v>24</v>
       </c>
       <c r="F976" s="4" t="s">
+        <v>1945</v>
+      </c>
+      <c r="G976" s="4" t="s">
         <v>1946</v>
-      </c>
-      <c r="G976" s="4" t="s">
-        <v>1947</v>
       </c>
       <c r="H976" s="6" t="n">
         <v>46274.442685185</v>
@@ -63135,22 +63162,22 @@
         <v>24</v>
       </c>
       <c r="F977" s="9" t="s">
+        <v>1947</v>
+      </c>
+      <c r="G977" s="9" t="s">
         <v>1948</v>
-      </c>
-      <c r="G977" s="9" t="s">
-        <v>1949</v>
       </c>
       <c r="H977" s="10" t="n">
         <v>46273</v>
       </c>
       <c r="I977" s="9" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J977" s="9" t="s">
         <v>1611</v>
       </c>
-      <c r="J977" s="9" t="s">
+      <c r="K977" s="9" t="s">
         <v>1612</v>
-      </c>
-      <c r="K977" s="9" t="s">
-        <v>1613</v>
       </c>
       <c r="L977" s="10"/>
       <c r="M977" s="10"/>
@@ -63164,7 +63191,7 @@
         <v>1452</v>
       </c>
       <c r="Q977" s="9" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="R977" s="12" t="n">
         <v>12500</v>
@@ -63196,7 +63223,7 @@
         <v>355</v>
       </c>
       <c r="G978" s="4" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="H978" s="5" t="n">
         <v>46274</v>
@@ -63254,7 +63281,7 @@
         <v>152</v>
       </c>
       <c r="G979" s="9" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="H979" s="10" t="n">
         <v>46273</v>
@@ -63312,7 +63339,7 @@
         <v>1211</v>
       </c>
       <c r="G980" s="4" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="H980" s="5" t="n">
         <v>46275</v>
@@ -63370,7 +63397,7 @@
         <v>215</v>
       </c>
       <c r="G981" s="9" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="H981" s="10" t="n">
         <v>46275</v>
@@ -63428,7 +63455,7 @@
         <v>1456</v>
       </c>
       <c r="G982" s="4" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="H982" s="6" t="n">
         <v>46274.972708333</v>
@@ -63486,7 +63513,7 @@
         <v>103</v>
       </c>
       <c r="G983" s="9" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="H983" s="11" t="n">
         <v>46274.976979167</v>
@@ -63544,7 +63571,7 @@
         <v>276</v>
       </c>
       <c r="G984" s="4" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="H984" s="6" t="n">
         <v>46274.703055556</v>
@@ -63602,7 +63629,7 @@
         <v>75</v>
       </c>
       <c r="G985" s="9" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="H985" s="11" t="n">
         <v>46274.682534722</v>
@@ -63660,7 +63687,7 @@
         <v>1193</v>
       </c>
       <c r="G986" s="4" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="H986" s="6" t="n">
         <v>46275.472800926</v>
@@ -63718,7 +63745,7 @@
         <v>1116</v>
       </c>
       <c r="G987" s="9" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="H987" s="11" t="n">
         <v>46276.641041667</v>
@@ -63776,7 +63803,7 @@
         <v>1293</v>
       </c>
       <c r="G988" s="4" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="H988" s="6" t="n">
         <v>46276.445613426</v>
@@ -63834,7 +63861,7 @@
         <v>478</v>
       </c>
       <c r="G989" s="9" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H989" s="11" t="n">
         <v>46275.859097222</v>
@@ -63892,7 +63919,7 @@
         <v>496</v>
       </c>
       <c r="G990" s="4" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H990" s="6" t="n">
         <v>46276.36244213</v>
@@ -63950,7 +63977,7 @@
         <v>1424</v>
       </c>
       <c r="G991" s="9" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H991" s="11" t="n">
         <v>46276.780416667</v>
@@ -64008,7 +64035,7 @@
         <v>1289</v>
       </c>
       <c r="G992" s="4" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H992" s="6" t="n">
         <v>46276.750868056</v>
@@ -64063,22 +64090,22 @@
         <v>24</v>
       </c>
       <c r="F993" s="9" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="G993" s="9" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H993" s="11" t="n">
         <v>46276.782905093</v>
       </c>
       <c r="I993" s="9" t="s">
+        <v>1666</v>
+      </c>
+      <c r="J993" s="9" t="s">
+        <v>1666</v>
+      </c>
+      <c r="K993" s="9" t="s">
         <v>1667</v>
-      </c>
-      <c r="J993" s="9" t="s">
-        <v>1667</v>
-      </c>
-      <c r="K993" s="9" t="s">
-        <v>1668</v>
       </c>
       <c r="L993" s="10"/>
       <c r="M993" s="10"/>
@@ -64118,25 +64145,25 @@
         <v>23</v>
       </c>
       <c r="E994" s="3" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="F994" s="4" t="s">
         <v>1159</v>
       </c>
       <c r="G994" s="4" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H994" s="5" t="n">
         <v>46276</v>
       </c>
       <c r="I994" s="4" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="J994" s="4" t="s">
         <v>1162</v>
       </c>
       <c r="K994" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="L994" s="5"/>
       <c r="M994" s="5"/>
@@ -64179,10 +64206,10 @@
         <v>24</v>
       </c>
       <c r="F995" s="9" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="G995" s="9" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H995" s="10" t="n">
         <v>46276</v>
@@ -64240,7 +64267,7 @@
         <v>592</v>
       </c>
       <c r="G996" s="4" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H996" s="6" t="n">
         <v>46279.943194444</v>
@@ -64298,7 +64325,7 @@
         <v>262</v>
       </c>
       <c r="G997" s="9" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H997" s="11" t="n">
         <v>46280.741736111</v>
@@ -64356,7 +64383,7 @@
         <v>194</v>
       </c>
       <c r="G998" s="4" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H998" s="5" t="n">
         <v>46279</v>
@@ -64414,7 +64441,7 @@
         <v>389</v>
       </c>
       <c r="G999" s="9" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H999" s="11" t="n">
         <v>46280.714386574</v>
@@ -64466,13 +64493,13 @@
         <v>23</v>
       </c>
       <c r="E1000" s="3" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="F1000" s="4" t="s">
         <v>75</v>
       </c>
       <c r="G1000" s="4" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H1000" s="6" t="n">
         <v>46280.693761574</v>
@@ -64504,7 +64531,7 @@
         <v>885906</v>
       </c>
       <c r="S1000" s="7" t="n">
-        <v>91350</v>
+        <v>116550</v>
       </c>
       <c r="T1000" s="4" t="s">
         <v>32</v>
@@ -64530,7 +64557,7 @@
         <v>963</v>
       </c>
       <c r="G1001" s="9" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H1001" s="11" t="n">
         <v>46280.868599537</v>
@@ -64588,7 +64615,7 @@
         <v>366</v>
       </c>
       <c r="G1002" s="4" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H1002" s="5" t="n">
         <v>46280</v>
@@ -64643,22 +64670,22 @@
         <v>24</v>
       </c>
       <c r="F1003" s="9" t="s">
+        <v>1978</v>
+      </c>
+      <c r="G1003" s="9" t="s">
         <v>1979</v>
-      </c>
-      <c r="G1003" s="9" t="s">
-        <v>1980</v>
       </c>
       <c r="H1003" s="11" t="n">
         <v>46281.483981481</v>
       </c>
       <c r="I1003" s="9" t="s">
+        <v>1980</v>
+      </c>
+      <c r="J1003" s="9" t="s">
+        <v>1980</v>
+      </c>
+      <c r="K1003" s="9" t="s">
         <v>1981</v>
-      </c>
-      <c r="J1003" s="9" t="s">
-        <v>1981</v>
-      </c>
-      <c r="K1003" s="9" t="s">
-        <v>1982</v>
       </c>
       <c r="L1003" s="10"/>
       <c r="M1003" s="10"/>
@@ -64704,7 +64731,7 @@
         <v>623</v>
       </c>
       <c r="G1004" s="4" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H1004" s="6" t="n">
         <v>46281.591608796</v>
@@ -64759,10 +64786,10 @@
         <v>24</v>
       </c>
       <c r="F1005" s="9" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G1005" s="9" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H1005" s="10" t="n">
         <v>46282</v>
@@ -64817,10 +64844,10 @@
         <v>24</v>
       </c>
       <c r="F1006" s="4" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="G1006" s="4" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H1006" s="5" t="n">
         <v>46282</v>
@@ -64872,13 +64899,13 @@
         <v>23</v>
       </c>
       <c r="E1007" s="8" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F1007" s="9" t="s">
         <v>1986</v>
       </c>
-      <c r="F1007" s="9" t="s">
+      <c r="G1007" s="9" t="s">
         <v>1987</v>
-      </c>
-      <c r="G1007" s="9" t="s">
-        <v>1988</v>
       </c>
       <c r="H1007" s="11" t="n">
         <v>46282.690821759</v>
@@ -64933,22 +64960,22 @@
         <v>24</v>
       </c>
       <c r="F1008" s="4" t="s">
+        <v>1988</v>
+      </c>
+      <c r="G1008" s="4" t="s">
         <v>1989</v>
-      </c>
-      <c r="G1008" s="4" t="s">
-        <v>1990</v>
       </c>
       <c r="H1008" s="6" t="n">
         <v>46283.62880787</v>
       </c>
       <c r="I1008" s="4" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="J1008" s="4" t="s">
+        <v>1990</v>
+      </c>
+      <c r="K1008" s="4" t="s">
         <v>1991</v>
-      </c>
-      <c r="K1008" s="4" t="s">
-        <v>1992</v>
       </c>
       <c r="L1008" s="5"/>
       <c r="M1008" s="5"/>
@@ -64994,7 +65021,7 @@
         <v>253</v>
       </c>
       <c r="G1009" s="9" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H1009" s="11" t="n">
         <v>46282.73755787</v>
@@ -65049,10 +65076,10 @@
         <v>24</v>
       </c>
       <c r="F1010" s="4" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="G1010" s="4" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H1010" s="5" t="n">
         <v>46286</v>
@@ -65107,22 +65134,22 @@
         <v>24</v>
       </c>
       <c r="F1011" s="9" t="s">
+        <v>1994</v>
+      </c>
+      <c r="G1011" s="9" t="s">
         <v>1995</v>
-      </c>
-      <c r="G1011" s="9" t="s">
-        <v>1996</v>
       </c>
       <c r="H1011" s="10" t="n">
         <v>46286</v>
       </c>
       <c r="I1011" s="9" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J1011" s="9" t="s">
         <v>1611</v>
       </c>
-      <c r="J1011" s="9" t="s">
+      <c r="K1011" s="9" t="s">
         <v>1612</v>
-      </c>
-      <c r="K1011" s="9" t="s">
-        <v>1613</v>
       </c>
       <c r="L1011" s="10"/>
       <c r="M1011" s="10"/>
@@ -65136,7 +65163,7 @@
         <v>1452</v>
       </c>
       <c r="Q1011" s="9" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="R1011" s="12" t="n">
         <v>5000</v>
@@ -65168,7 +65195,7 @@
         <v>58</v>
       </c>
       <c r="G1012" s="4" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H1012" s="6" t="n">
         <v>46283.945405093</v>
@@ -65226,7 +65253,7 @@
         <v>152</v>
       </c>
       <c r="G1013" s="9" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H1013" s="11" t="n">
         <v>46283.947222222</v>
@@ -65281,10 +65308,10 @@
         <v>24</v>
       </c>
       <c r="F1014" s="4" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="G1014" s="4" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H1014" s="6" t="n">
         <v>46286.665289352</v>
@@ -65342,7 +65369,7 @@
         <v>892</v>
       </c>
       <c r="G1015" s="9" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H1015" s="11" t="n">
         <v>46286.490671296</v>
@@ -65394,13 +65421,13 @@
         <v>23</v>
       </c>
       <c r="E1016" s="3" t="s">
+        <v>2000</v>
+      </c>
+      <c r="F1016" s="4" t="s">
+        <v>1625</v>
+      </c>
+      <c r="G1016" s="4" t="s">
         <v>2001</v>
-      </c>
-      <c r="F1016" s="4" t="s">
-        <v>1626</v>
-      </c>
-      <c r="G1016" s="4" t="s">
-        <v>2002</v>
       </c>
       <c r="H1016" s="6" t="n">
         <v>46286.636898148</v>
@@ -65458,7 +65485,7 @@
         <v>704</v>
       </c>
       <c r="G1017" s="9" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H1017" s="11" t="n">
         <v>46287.528784722</v>
@@ -65513,27 +65540,27 @@
         <v>285</v>
       </c>
       <c r="F1018" s="4" t="s">
+        <v>2003</v>
+      </c>
+      <c r="G1018" s="4" t="s">
         <v>2004</v>
-      </c>
-      <c r="G1018" s="4" t="s">
-        <v>2005</v>
       </c>
       <c r="H1018" s="6" t="n">
         <v>46287.685717593</v>
       </c>
       <c r="I1018" s="4" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="J1018" s="4" t="s">
+        <v>2005</v>
+      </c>
+      <c r="K1018" s="4" t="s">
         <v>2006</v>
-      </c>
-      <c r="K1018" s="4" t="s">
-        <v>2007</v>
       </c>
       <c r="L1018" s="5"/>
       <c r="M1018" s="5"/>
       <c r="N1018" s="4" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="O1018" s="6" t="n">
         <v>46289.388101852</v>
@@ -65574,7 +65601,7 @@
         <v>402</v>
       </c>
       <c r="G1019" s="9" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H1019" s="11" t="n">
         <v>46287.90775463</v>
@@ -65632,7 +65659,7 @@
         <v>1234</v>
       </c>
       <c r="G1020" s="4" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H1020" s="6" t="n">
         <v>46287.518842593</v>
@@ -65690,7 +65717,7 @@
         <v>347</v>
       </c>
       <c r="G1021" s="9" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H1021" s="11" t="n">
         <v>46288.409328704</v>
@@ -65745,22 +65772,22 @@
         <v>24</v>
       </c>
       <c r="F1022" s="4" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="G1022" s="4" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H1022" s="6" t="n">
         <v>46288.63568287</v>
       </c>
       <c r="I1022" s="4" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="J1022" s="4" t="s">
+        <v>1942</v>
+      </c>
+      <c r="K1022" s="4" t="s">
         <v>1943</v>
-      </c>
-      <c r="K1022" s="4" t="s">
-        <v>1944</v>
       </c>
       <c r="L1022" s="5"/>
       <c r="M1022" s="5"/>
@@ -65806,7 +65833,7 @@
         <v>351</v>
       </c>
       <c r="G1023" s="9" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H1023" s="11" t="n">
         <v>46288.641435185</v>
@@ -65864,7 +65891,7 @@
         <v>944</v>
       </c>
       <c r="G1024" s="4" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H1024" s="6" t="n">
         <v>46288.645289352</v>
@@ -65922,7 +65949,7 @@
         <v>366</v>
       </c>
       <c r="G1025" s="9" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H1025" s="10" t="n">
         <v>46288</v>
@@ -65974,13 +66001,13 @@
         <v>23</v>
       </c>
       <c r="E1026" s="3" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F1026" s="4" t="s">
         <v>1261</v>
       </c>
       <c r="G1026" s="4" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H1026" s="5" t="n">
         <v>46288</v>
@@ -66035,10 +66062,10 @@
         <v>24</v>
       </c>
       <c r="F1027" s="9" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="G1027" s="9" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H1027" s="10" t="n">
         <v>46289</v>
@@ -66093,10 +66120,10 @@
         <v>24</v>
       </c>
       <c r="F1028" s="4" t="s">
+        <v>2018</v>
+      </c>
+      <c r="G1028" s="4" t="s">
         <v>2019</v>
-      </c>
-      <c r="G1028" s="4" t="s">
-        <v>2020</v>
       </c>
       <c r="H1028" s="6" t="n">
         <v>46288.697777778</v>
@@ -66154,7 +66181,7 @@
         <v>490</v>
       </c>
       <c r="G1029" s="9" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H1029" s="11" t="n">
         <v>46288.708703704</v>
@@ -66212,7 +66239,7 @@
         <v>262</v>
       </c>
       <c r="G1030" s="4" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H1030" s="6" t="n">
         <v>46288.727013889</v>
@@ -66270,7 +66297,7 @@
         <v>521</v>
       </c>
       <c r="G1031" s="9" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H1031" s="11" t="n">
         <v>46293.413449074</v>
@@ -66325,22 +66352,22 @@
         <v>24</v>
       </c>
       <c r="F1032" s="4" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="G1032" s="4" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H1032" s="6" t="n">
         <v>46290.399768519</v>
       </c>
       <c r="I1032" s="4" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="J1032" s="4" t="s">
+        <v>1781</v>
+      </c>
+      <c r="K1032" s="4" t="s">
         <v>1782</v>
-      </c>
-      <c r="K1032" s="4" t="s">
-        <v>1783</v>
       </c>
       <c r="L1032" s="5"/>
       <c r="M1032" s="5"/>
@@ -66386,7 +66413,7 @@
         <v>75</v>
       </c>
       <c r="G1033" s="9" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H1033" s="11" t="n">
         <v>46293.420972222</v>
@@ -66441,10 +66468,10 @@
         <v>24</v>
       </c>
       <c r="F1034" s="4" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="G1034" s="4" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H1034" s="6" t="n">
         <v>46289.403217593</v>
@@ -66499,22 +66526,22 @@
         <v>24</v>
       </c>
       <c r="F1035" s="9" t="s">
+        <v>2026</v>
+      </c>
+      <c r="G1035" s="9" t="s">
         <v>2027</v>
-      </c>
-      <c r="G1035" s="9" t="s">
-        <v>2028</v>
       </c>
       <c r="H1035" s="11" t="n">
         <v>46289.956689815</v>
       </c>
       <c r="I1035" s="9" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="J1035" s="9" t="s">
+        <v>2028</v>
+      </c>
+      <c r="K1035" s="9" t="s">
         <v>2029</v>
-      </c>
-      <c r="K1035" s="9" t="s">
-        <v>2030</v>
       </c>
       <c r="L1035" s="10"/>
       <c r="M1035" s="10"/>
@@ -66554,13 +66581,13 @@
         <v>23</v>
       </c>
       <c r="E1036" s="3" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="F1036" s="4" t="s">
         <v>801</v>
       </c>
       <c r="G1036" s="4" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="H1036" s="6" t="n">
         <v>46293.739594907</v>
@@ -66615,22 +66642,22 @@
         <v>24</v>
       </c>
       <c r="F1037" s="9" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="G1037" s="9" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="H1037" s="11" t="n">
         <v>46293.720231481</v>
       </c>
       <c r="I1037" s="9" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="J1037" s="9" t="s">
+        <v>2028</v>
+      </c>
+      <c r="K1037" s="9" t="s">
         <v>2029</v>
-      </c>
-      <c r="K1037" s="9" t="s">
-        <v>2030</v>
       </c>
       <c r="L1037" s="10"/>
       <c r="M1037" s="10"/>
@@ -66670,13 +66697,13 @@
         <v>23</v>
       </c>
       <c r="E1038" s="3" t="s">
-        <v>2034</v>
+        <v>24</v>
       </c>
       <c r="F1038" s="4" t="s">
         <v>1268</v>
       </c>
       <c r="G1038" s="4" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="H1038" s="6" t="n">
         <v>46294.490601852</v>
@@ -66708,7 +66735,7 @@
         <v>140027.6</v>
       </c>
       <c r="S1038" s="7" t="n">
-        <v>131387.6</v>
+        <v>140027.6</v>
       </c>
       <c r="T1038" s="4" t="s">
         <v>32</v>
@@ -66731,22 +66758,22 @@
         <v>24</v>
       </c>
       <c r="F1039" s="9" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="G1039" s="9" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="H1039" s="10" t="n">
         <v>46294</v>
       </c>
       <c r="I1039" s="9" t="s">
+        <v>1751</v>
+      </c>
+      <c r="J1039" s="9" t="s">
+        <v>1751</v>
+      </c>
+      <c r="K1039" s="9" t="s">
         <v>1752</v>
-      </c>
-      <c r="J1039" s="9" t="s">
-        <v>1752</v>
-      </c>
-      <c r="K1039" s="9" t="s">
-        <v>1753</v>
       </c>
       <c r="L1039" s="10"/>
       <c r="M1039" s="10"/>
@@ -66789,10 +66816,10 @@
         <v>24</v>
       </c>
       <c r="F1040" s="4" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="G1040" s="4" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="H1040" s="5" t="n">
         <v>46294</v>
@@ -66850,7 +66877,7 @@
         <v>967</v>
       </c>
       <c r="G1041" s="9" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="H1041" s="10" t="n">
         <v>46290</v>
@@ -66908,7 +66935,7 @@
         <v>230</v>
       </c>
       <c r="G1042" s="4" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="H1042" s="6" t="n">
         <v>46294.604212963</v>
@@ -66966,7 +66993,7 @@
         <v>230</v>
       </c>
       <c r="G1043" s="9" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="H1043" s="11" t="n">
         <v>46294.585011574</v>
@@ -67024,7 +67051,7 @@
         <v>324</v>
       </c>
       <c r="G1044" s="4" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="H1044" s="6" t="n">
         <v>46294.608877315</v>
@@ -67079,10 +67106,10 @@
         <v>24</v>
       </c>
       <c r="F1045" s="9" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="G1045" s="9" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="H1045" s="11" t="n">
         <v>46294.613831019</v>
@@ -67140,7 +67167,7 @@
         <v>461</v>
       </c>
       <c r="G1046" s="4" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="H1046" s="6" t="n">
         <v>46294.707199074</v>
@@ -67198,7 +67225,7 @@
         <v>103</v>
       </c>
       <c r="G1047" s="9" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="H1047" s="11" t="n">
         <v>46294.757743056</v>
@@ -67215,7 +67242,7 @@
       <c r="L1047" s="10"/>
       <c r="M1047" s="10"/>
       <c r="N1047" s="9" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="O1047" s="11" t="n">
         <v>46296.614756863</v>
@@ -67250,30 +67277,30 @@
         <v>23</v>
       </c>
       <c r="E1048" s="3" t="s">
-        <v>285</v>
+        <v>2044</v>
       </c>
       <c r="F1048" s="4" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G1048" s="4" t="s">
         <v>2046</v>
-      </c>
-      <c r="G1048" s="4" t="s">
-        <v>2047</v>
       </c>
       <c r="H1048" s="6" t="n">
         <v>46295.464884259</v>
       </c>
       <c r="I1048" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="J1048" s="4" t="s">
+        <v>2047</v>
+      </c>
+      <c r="K1048" s="4" t="s">
         <v>2048</v>
-      </c>
-      <c r="K1048" s="4" t="s">
-        <v>2049</v>
       </c>
       <c r="L1048" s="5"/>
       <c r="M1048" s="5"/>
       <c r="N1048" s="4" t="s">
-        <v>2008</v>
+        <v>1285</v>
       </c>
       <c r="O1048" s="6" t="n">
         <v>46296.614904433</v>
@@ -67288,7 +67315,7 @@
         <v>10600</v>
       </c>
       <c r="S1048" s="7" t="n">
-        <v>0</v>
+        <v>9010</v>
       </c>
       <c r="T1048" s="4" t="s">
         <v>32</v>
@@ -67311,10 +67338,10 @@
         <v>24</v>
       </c>
       <c r="F1049" s="9" t="s">
+        <v>2049</v>
+      </c>
+      <c r="G1049" s="9" t="s">
         <v>2050</v>
-      </c>
-      <c r="G1049" s="9" t="s">
-        <v>2051</v>
       </c>
       <c r="H1049" s="11" t="n">
         <v>46294.660474537</v>
@@ -67372,7 +67399,7 @@
         <v>1268</v>
       </c>
       <c r="G1050" s="4" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="H1050" s="6" t="n">
         <v>46295.603634259</v>
@@ -67430,7 +67457,7 @@
         <v>904</v>
       </c>
       <c r="G1051" s="9" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="H1051" s="11" t="n">
         <v>46295.647060185</v>
@@ -67485,10 +67512,10 @@
         <v>24</v>
       </c>
       <c r="F1052" s="4" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G1052" s="4" t="s">
         <v>2054</v>
-      </c>
-      <c r="G1052" s="4" t="s">
-        <v>2055</v>
       </c>
       <c r="H1052" s="5" t="n">
         <v>46296</v>
@@ -67540,13 +67567,13 @@
         <v>23</v>
       </c>
       <c r="E1053" s="8" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="F1053" s="9" t="s">
         <v>1261</v>
       </c>
       <c r="G1053" s="9" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="H1053" s="10" t="n">
         <v>46295</v>
@@ -67601,22 +67628,22 @@
         <v>24</v>
       </c>
       <c r="F1054" s="4" t="s">
+        <v>2057</v>
+      </c>
+      <c r="G1054" s="4" t="s">
         <v>2058</v>
-      </c>
-      <c r="G1054" s="4" t="s">
-        <v>2059</v>
       </c>
       <c r="H1054" s="5" t="n">
         <v>46295</v>
       </c>
       <c r="I1054" s="4" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="J1054" s="4" t="s">
+        <v>2059</v>
+      </c>
+      <c r="K1054" s="4" t="s">
         <v>2060</v>
-      </c>
-      <c r="K1054" s="4" t="s">
-        <v>2061</v>
       </c>
       <c r="L1054" s="5"/>
       <c r="M1054" s="5"/>
@@ -67630,7 +67657,7 @@
         <v>1452</v>
       </c>
       <c r="Q1054" s="4" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="R1054" s="7" t="n">
         <v>22667.76</v>
@@ -67662,7 +67689,7 @@
         <v>1017</v>
       </c>
       <c r="G1055" s="9" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="H1055" s="10" t="n">
         <v>46297</v>
@@ -67720,7 +67747,7 @@
         <v>262</v>
       </c>
       <c r="G1056" s="4" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="H1056" s="6" t="n">
         <v>46296.754675926</v>
@@ -67778,7 +67805,7 @@
         <v>194</v>
       </c>
       <c r="G1057" s="9" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="H1057" s="10" t="n">
         <v>46296</v>
@@ -67830,13 +67857,13 @@
         <v>23</v>
       </c>
       <c r="E1058" s="3" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="F1058" s="4" t="s">
         <v>453</v>
       </c>
       <c r="G1058" s="4" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="H1058" s="6" t="n">
         <v>46300.877766204</v>
@@ -67868,7 +67895,7 @@
         <v>50145.6</v>
       </c>
       <c r="S1058" s="7" t="n">
-        <v>27012</v>
+        <v>41883.6</v>
       </c>
       <c r="T1058" s="4" t="s">
         <v>32</v>
@@ -67894,7 +67921,7 @@
         <v>436</v>
       </c>
       <c r="G1059" s="9" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="H1059" s="11" t="n">
         <v>46300.582071759</v>
@@ -67952,7 +67979,7 @@
         <v>698</v>
       </c>
       <c r="G1060" s="4" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="H1060" s="6" t="n">
         <v>46300.587326389</v>
@@ -68010,7 +68037,7 @@
         <v>981</v>
       </c>
       <c r="G1061" s="9" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="H1061" s="10" t="n">
         <v>46301</v>
@@ -68065,10 +68092,10 @@
         <v>24</v>
       </c>
       <c r="F1062" s="4" t="s">
+        <v>2070</v>
+      </c>
+      <c r="G1062" s="4" t="s">
         <v>2071</v>
-      </c>
-      <c r="G1062" s="4" t="s">
-        <v>2072</v>
       </c>
       <c r="H1062" s="6" t="n">
         <v>46301.750358796</v>
@@ -68120,13 +68147,13 @@
         <v>23</v>
       </c>
       <c r="E1063" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1063" s="9" t="s">
         <v>698</v>
       </c>
       <c r="G1063" s="9" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="H1063" s="11" t="n">
         <v>46301.972430556</v>
@@ -68143,7 +68170,7 @@
       <c r="L1063" s="10"/>
       <c r="M1063" s="10"/>
       <c r="N1063" s="9" t="s">
-        <v>2008</v>
+        <v>29</v>
       </c>
       <c r="O1063" s="11" t="n">
         <v>46302.6779625</v>
@@ -68158,7 +68185,7 @@
         <v>10500</v>
       </c>
       <c r="S1063" s="12" t="n">
-        <v>0</v>
+        <v>10500</v>
       </c>
       <c r="T1063" s="9" t="s">
         <v>32</v>
@@ -68178,13 +68205,13 @@
         <v>23</v>
       </c>
       <c r="E1064" s="3" t="s">
-        <v>2074</v>
+        <v>24</v>
       </c>
       <c r="F1064" s="4" t="s">
         <v>953</v>
       </c>
       <c r="G1064" s="4" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="H1064" s="6" t="n">
         <v>46302.362025463</v>
@@ -68201,7 +68228,7 @@
       <c r="L1064" s="5"/>
       <c r="M1064" s="5"/>
       <c r="N1064" s="4" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O1064" s="6" t="n">
         <v>46302.678099421</v>
@@ -68216,7 +68243,7 @@
         <v>122892</v>
       </c>
       <c r="S1064" s="7" t="n">
-        <v>64014</v>
+        <v>122892</v>
       </c>
       <c r="T1064" s="4" t="s">
         <v>32</v>
@@ -68236,13 +68263,13 @@
         <v>23</v>
       </c>
       <c r="E1065" s="8" t="s">
-        <v>2076</v>
+        <v>24</v>
       </c>
       <c r="F1065" s="9" t="s">
         <v>765</v>
       </c>
       <c r="G1065" s="9" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
       <c r="H1065" s="10" t="n">
         <v>46302</v>
@@ -68259,7 +68286,7 @@
       <c r="L1065" s="10"/>
       <c r="M1065" s="10"/>
       <c r="N1065" s="9" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O1065" s="11" t="n">
         <v>46302.678656794</v>
@@ -68271,10 +68298,10 @@
         <v>134</v>
       </c>
       <c r="R1065" s="12" t="n">
-        <v>12797.94</v>
+        <v>12777.38</v>
       </c>
       <c r="S1065" s="12" t="n">
-        <v>3335.04</v>
+        <v>12777.38</v>
       </c>
       <c r="T1065" s="9" t="s">
         <v>32</v>
@@ -68294,13 +68321,13 @@
         <v>23</v>
       </c>
       <c r="E1066" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1066" s="4" t="s">
         <v>332</v>
       </c>
       <c r="G1066" s="4" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="H1066" s="6" t="n">
         <v>46303.385266204</v>
@@ -68317,7 +68344,7 @@
       <c r="L1066" s="5"/>
       <c r="M1066" s="5"/>
       <c r="N1066" s="4" t="s">
-        <v>2008</v>
+        <v>29</v>
       </c>
       <c r="O1066" s="6" t="n">
         <v>46304.461355984</v>
@@ -68332,7 +68359,7 @@
         <v>20709.6</v>
       </c>
       <c r="S1066" s="7" t="n">
-        <v>0</v>
+        <v>20709.6</v>
       </c>
       <c r="T1066" s="4" t="s">
         <v>32</v>
@@ -68352,13 +68379,13 @@
         <v>23</v>
       </c>
       <c r="E1067" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1067" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G1067" s="9" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
       <c r="H1067" s="11" t="n">
         <v>46302.730069444</v>
@@ -68375,7 +68402,7 @@
       <c r="L1067" s="10"/>
       <c r="M1067" s="10"/>
       <c r="N1067" s="9" t="s">
-        <v>2008</v>
+        <v>29</v>
       </c>
       <c r="O1067" s="11" t="n">
         <v>46304.461507176</v>
@@ -68390,7 +68417,7 @@
         <v>5040</v>
       </c>
       <c r="S1067" s="12" t="n">
-        <v>0</v>
+        <v>5040</v>
       </c>
       <c r="T1067" s="9" t="s">
         <v>32</v>
@@ -68410,13 +68437,13 @@
         <v>23</v>
       </c>
       <c r="E1068" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1068" s="4" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="G1068" s="4" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
       <c r="H1068" s="5" t="n">
         <v>46302</v>
@@ -68433,7 +68460,7 @@
       <c r="L1068" s="5"/>
       <c r="M1068" s="5"/>
       <c r="N1068" s="4" t="s">
-        <v>2008</v>
+        <v>29</v>
       </c>
       <c r="O1068" s="6" t="n">
         <v>46304.462336146</v>
@@ -68448,7 +68475,7 @@
         <v>2250</v>
       </c>
       <c r="S1068" s="7" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="T1068" s="4" t="s">
         <v>32</v>
@@ -68468,13 +68495,13 @@
         <v>23</v>
       </c>
       <c r="E1069" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1069" s="9" t="s">
         <v>967</v>
       </c>
       <c r="G1069" s="9" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="H1069" s="10" t="n">
         <v>46304</v>
@@ -68491,7 +68518,7 @@
       <c r="L1069" s="10"/>
       <c r="M1069" s="10"/>
       <c r="N1069" s="9" t="s">
-        <v>2008</v>
+        <v>29</v>
       </c>
       <c r="O1069" s="11" t="n">
         <v>46308.322246215</v>
@@ -68506,7 +68533,7 @@
         <v>3019.68</v>
       </c>
       <c r="S1069" s="12" t="n">
-        <v>0</v>
+        <v>3019.68</v>
       </c>
       <c r="T1069" s="9" t="s">
         <v>32</v>
@@ -68526,13 +68553,13 @@
         <v>23</v>
       </c>
       <c r="E1070" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1070" s="4" t="s">
         <v>295</v>
       </c>
       <c r="G1070" s="4" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
       <c r="H1070" s="6" t="n">
         <v>46304.355324074</v>
@@ -68549,7 +68576,7 @@
       <c r="L1070" s="5"/>
       <c r="M1070" s="5"/>
       <c r="N1070" s="4" t="s">
-        <v>2008</v>
+        <v>29</v>
       </c>
       <c r="O1070" s="6" t="n">
         <v>46308.322793634</v>
@@ -68564,7 +68591,7 @@
         <v>23400</v>
       </c>
       <c r="S1070" s="7" t="n">
-        <v>0</v>
+        <v>23400</v>
       </c>
       <c r="T1070" s="4" t="s">
         <v>32</v>
@@ -68584,30 +68611,30 @@
         <v>23</v>
       </c>
       <c r="E1071" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1071" s="9" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="G1071" s="9" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
       <c r="H1071" s="11" t="n">
         <v>46304.483865741</v>
       </c>
       <c r="I1071" s="9" t="s">
+        <v>1827</v>
+      </c>
+      <c r="J1071" s="9" t="s">
         <v>1828</v>
       </c>
-      <c r="J1071" s="9" t="s">
+      <c r="K1071" s="9" t="s">
         <v>1829</v>
-      </c>
-      <c r="K1071" s="9" t="s">
-        <v>1830</v>
       </c>
       <c r="L1071" s="10"/>
       <c r="M1071" s="10"/>
       <c r="N1071" s="9" t="s">
-        <v>2008</v>
+        <v>29</v>
       </c>
       <c r="O1071" s="11" t="n">
         <v>46308.322972604</v>
@@ -68619,46 +68646,510 @@
         <v>31</v>
       </c>
       <c r="R1071" s="12" t="n">
-        <v>6063.3</v>
+        <v>5916.9</v>
       </c>
       <c r="S1071" s="12" t="n">
-        <v>0</v>
+        <v>5916.9</v>
       </c>
       <c r="T1071" s="9" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="U1071" s="9"/>
       <c r="V1071" s="9"/>
     </row>
-    <row r="1072" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A1072" s="13" t="n">
-        <v>1070</v>
-      </c>
-      <c r="B1072" s="14"/>
-      <c r="C1072" s="14"/>
-      <c r="D1072" s="14"/>
-      <c r="E1072" s="14"/>
-      <c r="F1072" s="14"/>
-      <c r="G1072" s="14"/>
-      <c r="H1072" s="14"/>
-      <c r="I1072" s="14"/>
-      <c r="J1072" s="14"/>
-      <c r="K1072" s="14"/>
-      <c r="L1072" s="14"/>
-      <c r="M1072" s="14"/>
-      <c r="N1072" s="14"/>
-      <c r="O1072" s="14"/>
-      <c r="P1072" s="14"/>
-      <c r="Q1072" s="14"/>
-      <c r="R1072" s="15" t="n">
-        <v>62854012.5206</v>
-      </c>
-      <c r="S1072" s="15" t="n">
-        <v>60495456.4406</v>
-      </c>
-      <c r="T1072" s="14"/>
-      <c r="U1072" s="14"/>
-      <c r="V1072" s="16"/>
+    <row r="1072" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1072" s="3" t="n">
+        <v>1141</v>
+      </c>
+      <c r="B1072" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1072" s="4"/>
+      <c r="D1072" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1072" s="3" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1072" s="4" t="s">
+        <v>1634</v>
+      </c>
+      <c r="G1072" s="4" t="s">
+        <v>2082</v>
+      </c>
+      <c r="H1072" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I1072" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1072" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K1072" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="L1072" s="5"/>
+      <c r="M1072" s="5"/>
+      <c r="N1072" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O1072" s="6" t="n">
+        <v>46308.671253704</v>
+      </c>
+      <c r="P1072" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1072" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="R1072" s="7" t="n">
+        <v>18778.66</v>
+      </c>
+      <c r="S1072" s="7" t="n">
+        <v>2197.3</v>
+      </c>
+      <c r="T1072" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1072" s="4"/>
+      <c r="V1072" s="4"/>
+    </row>
+    <row r="1073" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1073" s="8" t="n">
+        <v>1142</v>
+      </c>
+      <c r="B1073" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1073" s="9"/>
+      <c r="D1073" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1073" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1073" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1073" s="9" t="s">
+        <v>2083</v>
+      </c>
+      <c r="H1073" s="11" t="n">
+        <v>46308.484027778</v>
+      </c>
+      <c r="I1073" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1073" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K1073" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="L1073" s="10"/>
+      <c r="M1073" s="10"/>
+      <c r="N1073" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1073" s="11" t="n">
+        <v>46308.672965127</v>
+      </c>
+      <c r="P1073" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1073" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1073" s="12" t="n">
+        <v>4041</v>
+      </c>
+      <c r="S1073" s="12" t="n">
+        <v>4041</v>
+      </c>
+      <c r="T1073" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1073" s="9"/>
+      <c r="V1073" s="9"/>
+    </row>
+    <row r="1074" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1074" s="3" t="n">
+        <v>1143</v>
+      </c>
+      <c r="B1074" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1074" s="4"/>
+      <c r="D1074" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1074" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1074" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1074" s="4" t="s">
+        <v>2084</v>
+      </c>
+      <c r="H1074" s="6" t="n">
+        <v>46308.475208333</v>
+      </c>
+      <c r="I1074" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1074" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K1074" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="L1074" s="5"/>
+      <c r="M1074" s="5"/>
+      <c r="N1074" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O1074" s="6" t="n">
+        <v>46308.673458252</v>
+      </c>
+      <c r="P1074" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1074" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1074" s="7" t="n">
+        <v>387000</v>
+      </c>
+      <c r="S1074" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1074" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1074" s="4"/>
+      <c r="V1074" s="4"/>
+    </row>
+    <row r="1075" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1075" s="8" t="n">
+        <v>1144</v>
+      </c>
+      <c r="B1075" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1075" s="9"/>
+      <c r="D1075" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1075" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1075" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="G1075" s="9" t="s">
+        <v>2085</v>
+      </c>
+      <c r="H1075" s="10" t="n">
+        <v>46308</v>
+      </c>
+      <c r="I1075" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="J1075" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="K1075" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="L1075" s="10"/>
+      <c r="M1075" s="10"/>
+      <c r="N1075" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1075" s="11" t="n">
+        <v>46309.334198148</v>
+      </c>
+      <c r="P1075" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1075" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1075" s="12" t="n">
+        <v>3480</v>
+      </c>
+      <c r="S1075" s="12" t="n">
+        <v>3480</v>
+      </c>
+      <c r="T1075" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1075" s="9"/>
+      <c r="V1075" s="9"/>
+    </row>
+    <row r="1076" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1076" s="3" t="n">
+        <v>1145</v>
+      </c>
+      <c r="B1076" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1076" s="4"/>
+      <c r="D1076" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1076" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1076" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="G1076" s="4" t="s">
+        <v>2086</v>
+      </c>
+      <c r="H1076" s="6" t="n">
+        <v>46308.757569444</v>
+      </c>
+      <c r="I1076" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="J1076" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="K1076" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="L1076" s="5"/>
+      <c r="M1076" s="5"/>
+      <c r="N1076" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1076" s="6" t="n">
+        <v>46309.377516204</v>
+      </c>
+      <c r="P1076" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1076" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="R1076" s="7" t="n">
+        <v>15707.22</v>
+      </c>
+      <c r="S1076" s="7" t="n">
+        <v>15707.22</v>
+      </c>
+      <c r="T1076" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1076" s="4"/>
+      <c r="V1076" s="4"/>
+    </row>
+    <row r="1077" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1077" s="8" t="n">
+        <v>1146</v>
+      </c>
+      <c r="B1077" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1077" s="9"/>
+      <c r="D1077" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1077" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1077" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="G1077" s="9" t="s">
+        <v>2087</v>
+      </c>
+      <c r="H1077" s="11" t="n">
+        <v>46308.7390625</v>
+      </c>
+      <c r="I1077" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="J1077" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="K1077" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="L1077" s="10"/>
+      <c r="M1077" s="10"/>
+      <c r="N1077" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1077" s="11" t="n">
+        <v>46309.595986377</v>
+      </c>
+      <c r="P1077" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1077" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1077" s="12" t="n">
+        <v>19804.8</v>
+      </c>
+      <c r="S1077" s="12" t="n">
+        <v>19804.8</v>
+      </c>
+      <c r="T1077" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1077" s="9"/>
+      <c r="V1077" s="9"/>
+    </row>
+    <row r="1078" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1078" s="3" t="n">
+        <v>1147</v>
+      </c>
+      <c r="B1078" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1078" s="4"/>
+      <c r="D1078" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1078" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1078" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G1078" s="4" t="s">
+        <v>2088</v>
+      </c>
+      <c r="H1078" s="6" t="n">
+        <v>46308.730625</v>
+      </c>
+      <c r="I1078" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="J1078" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="K1078" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="L1078" s="5"/>
+      <c r="M1078" s="5"/>
+      <c r="N1078" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1078" s="6" t="n">
+        <v>46309.596155706</v>
+      </c>
+      <c r="P1078" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1078" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1078" s="7" t="n">
+        <v>19804.8</v>
+      </c>
+      <c r="S1078" s="7" t="n">
+        <v>19804.8</v>
+      </c>
+      <c r="T1078" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1078" s="4"/>
+      <c r="V1078" s="4"/>
+    </row>
+    <row r="1079" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1079" s="8" t="n">
+        <v>1148</v>
+      </c>
+      <c r="B1079" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1079" s="9"/>
+      <c r="D1079" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1079" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1079" s="9" t="s">
+        <v>2089</v>
+      </c>
+      <c r="G1079" s="9" t="s">
+        <v>2090</v>
+      </c>
+      <c r="H1079" s="10" t="n">
+        <v>46309</v>
+      </c>
+      <c r="I1079" s="9" t="s">
+        <v>2089</v>
+      </c>
+      <c r="J1079" s="9" t="s">
+        <v>2091</v>
+      </c>
+      <c r="K1079" s="9" t="s">
+        <v>2092</v>
+      </c>
+      <c r="L1079" s="10"/>
+      <c r="M1079" s="10"/>
+      <c r="N1079" s="9" t="s">
+        <v>2007</v>
+      </c>
+      <c r="O1079" s="11" t="n">
+        <v>46310.579741169</v>
+      </c>
+      <c r="P1079" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1079" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1079" s="12" t="n">
+        <v>3915.34</v>
+      </c>
+      <c r="S1079" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1079" s="9" t="s">
+        <v>1830</v>
+      </c>
+      <c r="U1079" s="9"/>
+      <c r="V1079" s="9"/>
+    </row>
+    <row r="1080" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A1080" s="13" t="n">
+        <v>1078</v>
+      </c>
+      <c r="B1080" s="14"/>
+      <c r="C1080" s="14"/>
+      <c r="D1080" s="14"/>
+      <c r="E1080" s="14"/>
+      <c r="F1080" s="14"/>
+      <c r="G1080" s="14"/>
+      <c r="H1080" s="14"/>
+      <c r="I1080" s="14"/>
+      <c r="J1080" s="14"/>
+      <c r="K1080" s="14"/>
+      <c r="L1080" s="14"/>
+      <c r="M1080" s="14"/>
+      <c r="N1080" s="14"/>
+      <c r="O1080" s="14"/>
+      <c r="P1080" s="14"/>
+      <c r="Q1080" s="14"/>
+      <c r="R1080" s="15" t="n">
+        <v>63326377.3806</v>
+      </c>
+      <c r="S1080" s="15" t="n">
+        <v>60818869.6806</v>
+      </c>
+      <c r="T1080" s="14"/>
+      <c r="U1080" s="14"/>
+      <c r="V1080" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="2093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="2097">
   <si>
     <t>ID</t>
   </si>
@@ -5910,9 +5910,6 @@
     <t>1227</t>
   </si>
   <si>
-    <t>43 %</t>
-  </si>
-  <si>
     <t>1228</t>
   </si>
   <si>
@@ -5970,9 +5967,6 @@
     <t>1240</t>
   </si>
   <si>
-    <t>90 %</t>
-  </si>
-  <si>
     <t>MEDCARE DISTRIBUIDORA</t>
   </si>
   <si>
@@ -6024,6 +6018,9 @@
     <t>1251</t>
   </si>
   <si>
+    <t>7 %</t>
+  </si>
+  <si>
     <t>REC HOSPITALAR</t>
   </si>
   <si>
@@ -6036,262 +6033,277 @@
     <t>39.500.546/0001-47</t>
   </si>
   <si>
+    <t>1253</t>
+  </si>
+  <si>
+    <t>1254</t>
+  </si>
+  <si>
+    <t>1255</t>
+  </si>
+  <si>
+    <t>1256</t>
+  </si>
+  <si>
+    <t>1257</t>
+  </si>
+  <si>
+    <t>1258</t>
+  </si>
+  <si>
+    <t>1259</t>
+  </si>
+  <si>
+    <t>68 %</t>
+  </si>
+  <si>
+    <t>1260</t>
+  </si>
+  <si>
+    <t>1261</t>
+  </si>
+  <si>
+    <t>MEDFASP SERVICOS</t>
+  </si>
+  <si>
+    <t>1262</t>
+  </si>
+  <si>
+    <t>1263</t>
+  </si>
+  <si>
+    <t>1264</t>
+  </si>
+  <si>
+    <t>1265</t>
+  </si>
+  <si>
+    <t>1266</t>
+  </si>
+  <si>
+    <t>1267</t>
+  </si>
+  <si>
+    <t>1268</t>
+  </si>
+  <si>
+    <t>DISTMED</t>
+  </si>
+  <si>
+    <t>1269</t>
+  </si>
+  <si>
+    <t>L N SILVA DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t>46.344.793/0001-67</t>
+  </si>
+  <si>
+    <t>1270</t>
+  </si>
+  <si>
+    <t>1271</t>
+  </si>
+  <si>
+    <t>1272</t>
+  </si>
+  <si>
+    <t>CAMPINA SAUDE CENTER</t>
+  </si>
+  <si>
+    <t>1273</t>
+  </si>
+  <si>
+    <t>1274</t>
+  </si>
+  <si>
+    <t>1275</t>
+  </si>
+  <si>
+    <t>1276</t>
+  </si>
+  <si>
+    <t>1277</t>
+  </si>
+  <si>
+    <t>1278</t>
+  </si>
+  <si>
+    <t>1279</t>
+  </si>
+  <si>
+    <t>1280</t>
+  </si>
+  <si>
+    <t>50 %</t>
+  </si>
+  <si>
+    <t>1281</t>
+  </si>
+  <si>
+    <t>85 %</t>
+  </si>
+  <si>
+    <t>DISDROL</t>
+  </si>
+  <si>
+    <t>1282</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA DE DROGAS LTDA</t>
+  </si>
+  <si>
+    <t>06.872.949/0001-68</t>
+  </si>
+  <si>
+    <t>CIRÚRGICA BEZERRA</t>
+  </si>
+  <si>
+    <t>1283</t>
+  </si>
+  <si>
+    <t>1284</t>
+  </si>
+  <si>
+    <t>1285</t>
+  </si>
+  <si>
+    <t>CAMEDIC COMERCIAL</t>
+  </si>
+  <si>
+    <t>1286</t>
+  </si>
+  <si>
+    <t>16 %</t>
+  </si>
+  <si>
+    <t>1287</t>
+  </si>
+  <si>
+    <t>1289</t>
+  </si>
+  <si>
+    <t>1291</t>
+  </si>
+  <si>
+    <t>1292</t>
+  </si>
+  <si>
+    <t>84 %</t>
+  </si>
+  <si>
+    <t>1293</t>
+  </si>
+  <si>
+    <t>1294</t>
+  </si>
+  <si>
+    <t>1295</t>
+  </si>
+  <si>
+    <t>1296</t>
+  </si>
+  <si>
+    <t>D E A FARMA</t>
+  </si>
+  <si>
+    <t>1297</t>
+  </si>
+  <si>
+    <t>1298</t>
+  </si>
+  <si>
+    <t>1299</t>
+  </si>
+  <si>
+    <t>1300</t>
+  </si>
+  <si>
+    <t>1301</t>
+  </si>
+  <si>
+    <t>1302</t>
+  </si>
+  <si>
+    <t>1303</t>
+  </si>
+  <si>
+    <t>1304</t>
+  </si>
+  <si>
+    <t>1306</t>
+  </si>
+  <si>
+    <t>1307</t>
+  </si>
+  <si>
+    <t>75 %</t>
+  </si>
+  <si>
+    <t>1308</t>
+  </si>
+  <si>
+    <t>1309</t>
+  </si>
+  <si>
+    <t>1310</t>
+  </si>
+  <si>
+    <t>1311</t>
+  </si>
+  <si>
+    <t>1312</t>
+  </si>
+  <si>
+    <t>1313</t>
+  </si>
+  <si>
+    <t>1314</t>
+  </si>
+  <si>
+    <t>60 %</t>
+  </si>
+  <si>
+    <t>SISAL MED</t>
+  </si>
+  <si>
+    <t>1315</t>
+  </si>
+  <si>
+    <t>MATOS &amp; OLIVEIRA PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>66.852.326/0001-55</t>
+  </si>
+  <si>
+    <t>1317</t>
+  </si>
+  <si>
     <t>A INICIAR</t>
   </si>
   <si>
-    <t>1253</t>
-  </si>
-  <si>
-    <t>1254</t>
-  </si>
-  <si>
-    <t>1255</t>
-  </si>
-  <si>
-    <t>1256</t>
-  </si>
-  <si>
-    <t>1257</t>
-  </si>
-  <si>
-    <t>1258</t>
-  </si>
-  <si>
-    <t>1259</t>
-  </si>
-  <si>
-    <t>68 %</t>
-  </si>
-  <si>
-    <t>1260</t>
-  </si>
-  <si>
-    <t>1261</t>
-  </si>
-  <si>
-    <t>MEDFASP SERVICOS</t>
-  </si>
-  <si>
-    <t>1262</t>
-  </si>
-  <si>
-    <t>1263</t>
-  </si>
-  <si>
-    <t>1264</t>
-  </si>
-  <si>
-    <t>1265</t>
-  </si>
-  <si>
-    <t>1266</t>
-  </si>
-  <si>
-    <t>1267</t>
-  </si>
-  <si>
-    <t>1268</t>
-  </si>
-  <si>
-    <t>DISTMED</t>
-  </si>
-  <si>
-    <t>1269</t>
-  </si>
-  <si>
-    <t>L N SILVA DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>46.344.793/0001-67</t>
-  </si>
-  <si>
-    <t>82 %</t>
-  </si>
-  <si>
-    <t>1270</t>
-  </si>
-  <si>
-    <t>1271</t>
-  </si>
-  <si>
-    <t>1272</t>
-  </si>
-  <si>
-    <t>CAMPINA SAUDE CENTER</t>
-  </si>
-  <si>
-    <t>1273</t>
-  </si>
-  <si>
-    <t>1274</t>
-  </si>
-  <si>
-    <t>1275</t>
-  </si>
-  <si>
-    <t>1276</t>
-  </si>
-  <si>
-    <t>1277</t>
-  </si>
-  <si>
-    <t>1278</t>
-  </si>
-  <si>
-    <t>1279</t>
-  </si>
-  <si>
-    <t>1280</t>
-  </si>
-  <si>
-    <t>1281</t>
-  </si>
-  <si>
-    <t>85 %</t>
-  </si>
-  <si>
-    <t>DISDROL</t>
-  </si>
-  <si>
-    <t>1282</t>
-  </si>
-  <si>
-    <t>DISTRIBUIDORA DE DROGAS LTDA</t>
-  </si>
-  <si>
-    <t>06.872.949/0001-68</t>
-  </si>
-  <si>
-    <t>CIRÚRGICA BEZERRA</t>
-  </si>
-  <si>
-    <t>1283</t>
-  </si>
-  <si>
-    <t>1284</t>
-  </si>
-  <si>
-    <t>1285</t>
-  </si>
-  <si>
-    <t>CAMEDIC COMERCIAL</t>
-  </si>
-  <si>
-    <t>1286</t>
-  </si>
-  <si>
-    <t>16 %</t>
-  </si>
-  <si>
-    <t>1287</t>
-  </si>
-  <si>
-    <t>PROVIDA DISTRIBUIDORA</t>
-  </si>
-  <si>
-    <t>1288</t>
-  </si>
-  <si>
-    <t>PROVIDA DISTRIBUIDORA DE MEDICAMENTOS E PRODUTOS H</t>
-  </si>
-  <si>
-    <t>42.259.522/0001-52</t>
-  </si>
-  <si>
-    <t>JULIANO PRIMAVERA</t>
-  </si>
-  <si>
-    <t>1289</t>
-  </si>
-  <si>
-    <t>1291</t>
-  </si>
-  <si>
-    <t>1292</t>
-  </si>
-  <si>
-    <t>84 %</t>
-  </si>
-  <si>
-    <t>1293</t>
-  </si>
-  <si>
-    <t>1294</t>
-  </si>
-  <si>
-    <t>1295</t>
-  </si>
-  <si>
-    <t>1296</t>
-  </si>
-  <si>
-    <t>D E A FARMA</t>
-  </si>
-  <si>
-    <t>1297</t>
-  </si>
-  <si>
-    <t>1298</t>
-  </si>
-  <si>
-    <t>1299</t>
-  </si>
-  <si>
-    <t>1300</t>
-  </si>
-  <si>
-    <t>1301</t>
-  </si>
-  <si>
-    <t>1302</t>
-  </si>
-  <si>
-    <t>1303</t>
-  </si>
-  <si>
-    <t>1304</t>
-  </si>
-  <si>
-    <t>1306</t>
-  </si>
-  <si>
-    <t>1307</t>
-  </si>
-  <si>
-    <t>12 %</t>
-  </si>
-  <si>
-    <t>1308</t>
-  </si>
-  <si>
-    <t>1309</t>
-  </si>
-  <si>
-    <t>1310</t>
-  </si>
-  <si>
-    <t>1311</t>
-  </si>
-  <si>
-    <t>1312</t>
-  </si>
-  <si>
-    <t>1313</t>
-  </si>
-  <si>
-    <t>1314</t>
-  </si>
-  <si>
-    <t>SISAL MED</t>
-  </si>
-  <si>
-    <t>1315</t>
-  </si>
-  <si>
-    <t>MATOS &amp; OLIVEIRA PRODUTOS HOSPITALARES LTDA</t>
-  </si>
-  <si>
-    <t>66.852.326/0001-55</t>
+    <t>1318</t>
+  </si>
+  <si>
+    <t>1319</t>
+  </si>
+  <si>
+    <t>1320</t>
+  </si>
+  <si>
+    <t>1321</t>
+  </si>
+  <si>
+    <t>1322</t>
+  </si>
+  <si>
+    <t>1323</t>
+  </si>
+  <si>
+    <t>1324</t>
+  </si>
+  <si>
+    <t>1325</t>
   </si>
 </sst>
 </file>
@@ -6485,7 +6497,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V1080"/>
+  <dimension ref="A1:V1088"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -64145,30 +64157,30 @@
         <v>23</v>
       </c>
       <c r="E994" s="3" t="s">
-        <v>1965</v>
+        <v>24</v>
       </c>
       <c r="F994" s="4" t="s">
         <v>1159</v>
       </c>
       <c r="G994" s="4" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H994" s="5" t="n">
         <v>46276</v>
       </c>
       <c r="I994" s="4" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="J994" s="4" t="s">
         <v>1162</v>
       </c>
       <c r="K994" s="4" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="L994" s="5"/>
       <c r="M994" s="5"/>
       <c r="N994" s="4" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O994" s="6" t="n">
         <v>46279.599731713</v>
@@ -64183,7 +64195,7 @@
         <v>58266</v>
       </c>
       <c r="S994" s="7" t="n">
-        <v>24900</v>
+        <v>58266</v>
       </c>
       <c r="T994" s="4" t="s">
         <v>571</v>
@@ -64209,7 +64221,7 @@
         <v>1917</v>
       </c>
       <c r="G995" s="9" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H995" s="10" t="n">
         <v>46276</v>
@@ -64267,7 +64279,7 @@
         <v>592</v>
       </c>
       <c r="G996" s="4" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H996" s="6" t="n">
         <v>46279.943194444</v>
@@ -64325,7 +64337,7 @@
         <v>262</v>
       </c>
       <c r="G997" s="9" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H997" s="11" t="n">
         <v>46280.741736111</v>
@@ -64383,7 +64395,7 @@
         <v>194</v>
       </c>
       <c r="G998" s="4" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H998" s="5" t="n">
         <v>46279</v>
@@ -64441,7 +64453,7 @@
         <v>389</v>
       </c>
       <c r="G999" s="9" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H999" s="11" t="n">
         <v>46280.714386574</v>
@@ -64493,13 +64505,13 @@
         <v>23</v>
       </c>
       <c r="E1000" s="3" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="F1000" s="4" t="s">
         <v>75</v>
       </c>
       <c r="G1000" s="4" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H1000" s="6" t="n">
         <v>46280.693761574</v>
@@ -64557,7 +64569,7 @@
         <v>963</v>
       </c>
       <c r="G1001" s="9" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H1001" s="11" t="n">
         <v>46280.868599537</v>
@@ -64615,7 +64627,7 @@
         <v>366</v>
       </c>
       <c r="G1002" s="4" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H1002" s="5" t="n">
         <v>46280</v>
@@ -64670,22 +64682,22 @@
         <v>24</v>
       </c>
       <c r="F1003" s="9" t="s">
+        <v>1977</v>
+      </c>
+      <c r="G1003" s="9" t="s">
         <v>1978</v>
-      </c>
-      <c r="G1003" s="9" t="s">
-        <v>1979</v>
       </c>
       <c r="H1003" s="11" t="n">
         <v>46281.483981481</v>
       </c>
       <c r="I1003" s="9" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J1003" s="9" t="s">
+        <v>1979</v>
+      </c>
+      <c r="K1003" s="9" t="s">
         <v>1980</v>
-      </c>
-      <c r="J1003" s="9" t="s">
-        <v>1980</v>
-      </c>
-      <c r="K1003" s="9" t="s">
-        <v>1981</v>
       </c>
       <c r="L1003" s="10"/>
       <c r="M1003" s="10"/>
@@ -64731,7 +64743,7 @@
         <v>623</v>
       </c>
       <c r="G1004" s="4" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H1004" s="6" t="n">
         <v>46281.591608796</v>
@@ -64789,7 +64801,7 @@
         <v>1534</v>
       </c>
       <c r="G1005" s="9" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H1005" s="10" t="n">
         <v>46282</v>
@@ -64847,7 +64859,7 @@
         <v>1634</v>
       </c>
       <c r="G1006" s="4" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H1006" s="5" t="n">
         <v>46282</v>
@@ -64899,13 +64911,13 @@
         <v>23</v>
       </c>
       <c r="E1007" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1007" s="9" t="s">
+        <v>1984</v>
+      </c>
+      <c r="G1007" s="9" t="s">
         <v>1985</v>
-      </c>
-      <c r="F1007" s="9" t="s">
-        <v>1986</v>
-      </c>
-      <c r="G1007" s="9" t="s">
-        <v>1987</v>
       </c>
       <c r="H1007" s="11" t="n">
         <v>46282.690821759</v>
@@ -64922,7 +64934,7 @@
       <c r="L1007" s="10"/>
       <c r="M1007" s="10"/>
       <c r="N1007" s="9" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O1007" s="11" t="n">
         <v>46286.373205243</v>
@@ -64937,7 +64949,7 @@
         <v>89187</v>
       </c>
       <c r="S1007" s="12" t="n">
-        <v>80145</v>
+        <v>89187</v>
       </c>
       <c r="T1007" s="9" t="s">
         <v>32</v>
@@ -64960,22 +64972,22 @@
         <v>24</v>
       </c>
       <c r="F1008" s="4" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="G1008" s="4" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="H1008" s="6" t="n">
         <v>46283.62880787</v>
       </c>
       <c r="I1008" s="4" t="s">
+        <v>1986</v>
+      </c>
+      <c r="J1008" s="4" t="s">
         <v>1988</v>
       </c>
-      <c r="J1008" s="4" t="s">
-        <v>1990</v>
-      </c>
       <c r="K1008" s="4" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="L1008" s="5"/>
       <c r="M1008" s="5"/>
@@ -65021,7 +65033,7 @@
         <v>253</v>
       </c>
       <c r="G1009" s="9" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="H1009" s="11" t="n">
         <v>46282.73755787</v>
@@ -65079,7 +65091,7 @@
         <v>1512</v>
       </c>
       <c r="G1010" s="4" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="H1010" s="5" t="n">
         <v>46286</v>
@@ -65134,10 +65146,10 @@
         <v>24</v>
       </c>
       <c r="F1011" s="9" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="G1011" s="9" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="H1011" s="10" t="n">
         <v>46286</v>
@@ -65195,7 +65207,7 @@
         <v>58</v>
       </c>
       <c r="G1012" s="4" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="H1012" s="6" t="n">
         <v>46283.945405093</v>
@@ -65253,7 +65265,7 @@
         <v>152</v>
       </c>
       <c r="G1013" s="9" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="H1013" s="11" t="n">
         <v>46283.947222222</v>
@@ -65311,7 +65323,7 @@
         <v>1627</v>
       </c>
       <c r="G1014" s="4" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="H1014" s="6" t="n">
         <v>46286.665289352</v>
@@ -65369,7 +65381,7 @@
         <v>892</v>
       </c>
       <c r="G1015" s="9" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="H1015" s="11" t="n">
         <v>46286.490671296</v>
@@ -65421,13 +65433,13 @@
         <v>23</v>
       </c>
       <c r="E1016" s="3" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="F1016" s="4" t="s">
         <v>1625</v>
       </c>
       <c r="G1016" s="4" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="H1016" s="6" t="n">
         <v>46286.636898148</v>
@@ -65485,7 +65497,7 @@
         <v>704</v>
       </c>
       <c r="G1017" s="9" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="H1017" s="11" t="n">
         <v>46287.528784722</v>
@@ -65537,30 +65549,30 @@
         <v>23</v>
       </c>
       <c r="E1018" s="3" t="s">
-        <v>285</v>
+        <v>2001</v>
       </c>
       <c r="F1018" s="4" t="s">
+        <v>2002</v>
+      </c>
+      <c r="G1018" s="4" t="s">
         <v>2003</v>
-      </c>
-      <c r="G1018" s="4" t="s">
-        <v>2004</v>
       </c>
       <c r="H1018" s="6" t="n">
         <v>46287.685717593</v>
       </c>
       <c r="I1018" s="4" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="J1018" s="4" t="s">
+        <v>2004</v>
+      </c>
+      <c r="K1018" s="4" t="s">
         <v>2005</v>
-      </c>
-      <c r="K1018" s="4" t="s">
-        <v>2006</v>
       </c>
       <c r="L1018" s="5"/>
       <c r="M1018" s="5"/>
       <c r="N1018" s="4" t="s">
-        <v>2007</v>
+        <v>1285</v>
       </c>
       <c r="O1018" s="6" t="n">
         <v>46289.388101852</v>
@@ -65575,7 +65587,7 @@
         <v>870435</v>
       </c>
       <c r="S1018" s="7" t="n">
-        <v>0</v>
+        <v>65250</v>
       </c>
       <c r="T1018" s="4" t="s">
         <v>32</v>
@@ -65601,7 +65613,7 @@
         <v>402</v>
       </c>
       <c r="G1019" s="9" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="H1019" s="11" t="n">
         <v>46287.90775463</v>
@@ -65659,7 +65671,7 @@
         <v>1234</v>
       </c>
       <c r="G1020" s="4" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="H1020" s="6" t="n">
         <v>46287.518842593</v>
@@ -65717,7 +65729,7 @@
         <v>347</v>
       </c>
       <c r="G1021" s="9" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="H1021" s="11" t="n">
         <v>46288.409328704</v>
@@ -65775,7 +65787,7 @@
         <v>1940</v>
       </c>
       <c r="G1022" s="4" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="H1022" s="6" t="n">
         <v>46288.63568287</v>
@@ -65833,7 +65845,7 @@
         <v>351</v>
       </c>
       <c r="G1023" s="9" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="H1023" s="11" t="n">
         <v>46288.641435185</v>
@@ -65891,7 +65903,7 @@
         <v>944</v>
       </c>
       <c r="G1024" s="4" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="H1024" s="6" t="n">
         <v>46288.645289352</v>
@@ -65949,7 +65961,7 @@
         <v>366</v>
       </c>
       <c r="G1025" s="9" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H1025" s="10" t="n">
         <v>46288</v>
@@ -66001,13 +66013,13 @@
         <v>23</v>
       </c>
       <c r="E1026" s="3" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="F1026" s="4" t="s">
         <v>1261</v>
       </c>
       <c r="G1026" s="4" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="H1026" s="5" t="n">
         <v>46288</v>
@@ -66065,7 +66077,7 @@
         <v>1634</v>
       </c>
       <c r="G1027" s="9" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="H1027" s="10" t="n">
         <v>46289</v>
@@ -66120,10 +66132,10 @@
         <v>24</v>
       </c>
       <c r="F1028" s="4" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="G1028" s="4" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="H1028" s="6" t="n">
         <v>46288.697777778</v>
@@ -66181,7 +66193,7 @@
         <v>490</v>
       </c>
       <c r="G1029" s="9" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="H1029" s="11" t="n">
         <v>46288.708703704</v>
@@ -66239,7 +66251,7 @@
         <v>262</v>
       </c>
       <c r="G1030" s="4" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="H1030" s="6" t="n">
         <v>46288.727013889</v>
@@ -66297,7 +66309,7 @@
         <v>521</v>
       </c>
       <c r="G1031" s="9" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H1031" s="11" t="n">
         <v>46293.413449074</v>
@@ -66355,7 +66367,7 @@
         <v>1779</v>
       </c>
       <c r="G1032" s="4" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="H1032" s="6" t="n">
         <v>46290.399768519</v>
@@ -66413,7 +66425,7 @@
         <v>75</v>
       </c>
       <c r="G1033" s="9" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="H1033" s="11" t="n">
         <v>46293.420972222</v>
@@ -66471,7 +66483,7 @@
         <v>1542</v>
       </c>
       <c r="G1034" s="4" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H1034" s="6" t="n">
         <v>46289.403217593</v>
@@ -66526,22 +66538,22 @@
         <v>24</v>
       </c>
       <c r="F1035" s="9" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="G1035" s="9" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="H1035" s="11" t="n">
         <v>46289.956689815</v>
       </c>
       <c r="I1035" s="9" t="s">
+        <v>2024</v>
+      </c>
+      <c r="J1035" s="9" t="s">
         <v>2026</v>
       </c>
-      <c r="J1035" s="9" t="s">
-        <v>2028</v>
-      </c>
       <c r="K1035" s="9" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="L1035" s="10"/>
       <c r="M1035" s="10"/>
@@ -66581,13 +66593,13 @@
         <v>23</v>
       </c>
       <c r="E1036" s="3" t="s">
-        <v>2030</v>
+        <v>24</v>
       </c>
       <c r="F1036" s="4" t="s">
         <v>801</v>
       </c>
       <c r="G1036" s="4" t="s">
-        <v>2031</v>
+        <v>2028</v>
       </c>
       <c r="H1036" s="6" t="n">
         <v>46293.739594907</v>
@@ -66604,7 +66616,7 @@
       <c r="L1036" s="5"/>
       <c r="M1036" s="5"/>
       <c r="N1036" s="4" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O1036" s="6" t="n">
         <v>46294.385012234</v>
@@ -66619,7 +66631,7 @@
         <v>144576.9</v>
       </c>
       <c r="S1036" s="7" t="n">
-        <v>118308</v>
+        <v>144576.9</v>
       </c>
       <c r="T1036" s="4" t="s">
         <v>32</v>
@@ -66642,22 +66654,22 @@
         <v>24</v>
       </c>
       <c r="F1037" s="9" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="G1037" s="9" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
       <c r="H1037" s="11" t="n">
         <v>46293.720231481</v>
       </c>
       <c r="I1037" s="9" t="s">
+        <v>2024</v>
+      </c>
+      <c r="J1037" s="9" t="s">
         <v>2026</v>
       </c>
-      <c r="J1037" s="9" t="s">
-        <v>2028</v>
-      </c>
       <c r="K1037" s="9" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="L1037" s="10"/>
       <c r="M1037" s="10"/>
@@ -66703,7 +66715,7 @@
         <v>1268</v>
       </c>
       <c r="G1038" s="4" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
       <c r="H1038" s="6" t="n">
         <v>46294.490601852</v>
@@ -66758,10 +66770,10 @@
         <v>24</v>
       </c>
       <c r="F1039" s="9" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
       <c r="G1039" s="9" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
       <c r="H1039" s="10" t="n">
         <v>46294</v>
@@ -66819,7 +66831,7 @@
         <v>1512</v>
       </c>
       <c r="G1040" s="4" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
       <c r="H1040" s="5" t="n">
         <v>46294</v>
@@ -66877,7 +66889,7 @@
         <v>967</v>
       </c>
       <c r="G1041" s="9" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
       <c r="H1041" s="10" t="n">
         <v>46290</v>
@@ -66935,7 +66947,7 @@
         <v>230</v>
       </c>
       <c r="G1042" s="4" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="H1042" s="6" t="n">
         <v>46294.604212963</v>
@@ -66993,7 +67005,7 @@
         <v>230</v>
       </c>
       <c r="G1043" s="9" t="s">
-        <v>2039</v>
+        <v>2036</v>
       </c>
       <c r="H1043" s="11" t="n">
         <v>46294.585011574</v>
@@ -67051,7 +67063,7 @@
         <v>324</v>
       </c>
       <c r="G1044" s="4" t="s">
-        <v>2040</v>
+        <v>2037</v>
       </c>
       <c r="H1044" s="6" t="n">
         <v>46294.608877315</v>
@@ -67109,7 +67121,7 @@
         <v>1645</v>
       </c>
       <c r="G1045" s="9" t="s">
-        <v>2041</v>
+        <v>2038</v>
       </c>
       <c r="H1045" s="11" t="n">
         <v>46294.613831019</v>
@@ -67167,7 +67179,7 @@
         <v>461</v>
       </c>
       <c r="G1046" s="4" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
       <c r="H1046" s="6" t="n">
         <v>46294.707199074</v>
@@ -67219,13 +67231,13 @@
         <v>23</v>
       </c>
       <c r="E1047" s="8" t="s">
-        <v>285</v>
+        <v>2040</v>
       </c>
       <c r="F1047" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G1047" s="9" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="H1047" s="11" t="n">
         <v>46294.757743056</v>
@@ -67242,7 +67254,7 @@
       <c r="L1047" s="10"/>
       <c r="M1047" s="10"/>
       <c r="N1047" s="9" t="s">
-        <v>2007</v>
+        <v>1285</v>
       </c>
       <c r="O1047" s="11" t="n">
         <v>46296.614756863</v>
@@ -67257,7 +67269,7 @@
         <v>56400</v>
       </c>
       <c r="S1047" s="12" t="n">
-        <v>0</v>
+        <v>28200</v>
       </c>
       <c r="T1047" s="9" t="s">
         <v>32</v>
@@ -67277,25 +67289,25 @@
         <v>23</v>
       </c>
       <c r="E1048" s="3" t="s">
+        <v>2042</v>
+      </c>
+      <c r="F1048" s="4" t="s">
+        <v>2043</v>
+      </c>
+      <c r="G1048" s="4" t="s">
         <v>2044</v>
-      </c>
-      <c r="F1048" s="4" t="s">
-        <v>2045</v>
-      </c>
-      <c r="G1048" s="4" t="s">
-        <v>2046</v>
       </c>
       <c r="H1048" s="6" t="n">
         <v>46295.464884259</v>
       </c>
       <c r="I1048" s="4" t="s">
+        <v>2043</v>
+      </c>
+      <c r="J1048" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="J1048" s="4" t="s">
-        <v>2047</v>
-      </c>
       <c r="K1048" s="4" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="L1048" s="5"/>
       <c r="M1048" s="5"/>
@@ -67338,10 +67350,10 @@
         <v>24</v>
       </c>
       <c r="F1049" s="9" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="G1049" s="9" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="H1049" s="11" t="n">
         <v>46294.660474537</v>
@@ -67399,7 +67411,7 @@
         <v>1268</v>
       </c>
       <c r="G1050" s="4" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="H1050" s="6" t="n">
         <v>46295.603634259</v>
@@ -67457,7 +67469,7 @@
         <v>904</v>
       </c>
       <c r="G1051" s="9" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="H1051" s="11" t="n">
         <v>46295.647060185</v>
@@ -67512,10 +67524,10 @@
         <v>24</v>
       </c>
       <c r="F1052" s="4" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="G1052" s="4" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="H1052" s="5" t="n">
         <v>46296</v>
@@ -67567,13 +67579,13 @@
         <v>23</v>
       </c>
       <c r="E1053" s="8" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="F1053" s="9" t="s">
         <v>1261</v>
       </c>
       <c r="G1053" s="9" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="H1053" s="10" t="n">
         <v>46295</v>
@@ -67615,7 +67627,7 @@
     </row>
     <row r="1054" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1054" s="3" t="n">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B1054" s="4" t="s">
         <v>22</v>
@@ -67628,22 +67640,22 @@
         <v>24</v>
       </c>
       <c r="F1054" s="4" t="s">
-        <v>2057</v>
+        <v>1017</v>
       </c>
       <c r="G1054" s="4" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
       <c r="H1054" s="5" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="I1054" s="4" t="s">
-        <v>2057</v>
+        <v>1019</v>
       </c>
       <c r="J1054" s="4" t="s">
-        <v>2059</v>
+        <v>1020</v>
       </c>
       <c r="K1054" s="4" t="s">
-        <v>2060</v>
+        <v>1021</v>
       </c>
       <c r="L1054" s="5"/>
       <c r="M1054" s="5"/>
@@ -67651,29 +67663,29 @@
         <v>29</v>
       </c>
       <c r="O1054" s="6" t="n">
-        <v>46296.627580289</v>
+        <v>46297.642502315</v>
       </c>
       <c r="P1054" s="4" t="s">
         <v>1452</v>
       </c>
       <c r="Q1054" s="4" t="s">
-        <v>2061</v>
+        <v>134</v>
       </c>
       <c r="R1054" s="7" t="n">
-        <v>22667.76</v>
+        <v>3891.96</v>
       </c>
       <c r="S1054" s="7" t="n">
-        <v>22667.76</v>
+        <v>3891.96</v>
       </c>
       <c r="T1054" s="4" t="s">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="U1054" s="4"/>
       <c r="V1054" s="4"/>
     </row>
     <row r="1055" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1055" s="8" t="n">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B1055" s="9" t="s">
         <v>22</v>
@@ -67686,22 +67698,22 @@
         <v>24</v>
       </c>
       <c r="F1055" s="9" t="s">
-        <v>1017</v>
+        <v>262</v>
       </c>
       <c r="G1055" s="9" t="s">
-        <v>2062</v>
-      </c>
-      <c r="H1055" s="10" t="n">
-        <v>46297</v>
+        <v>2056</v>
+      </c>
+      <c r="H1055" s="11" t="n">
+        <v>46296.754675926</v>
       </c>
       <c r="I1055" s="9" t="s">
-        <v>1019</v>
+        <v>122</v>
       </c>
       <c r="J1055" s="9" t="s">
-        <v>1020</v>
+        <v>122</v>
       </c>
       <c r="K1055" s="9" t="s">
-        <v>1021</v>
+        <v>123</v>
       </c>
       <c r="L1055" s="10"/>
       <c r="M1055" s="10"/>
@@ -67709,19 +67721,19 @@
         <v>29</v>
       </c>
       <c r="O1055" s="11" t="n">
-        <v>46297.642502315</v>
+        <v>46297.643961539</v>
       </c>
       <c r="P1055" s="9" t="s">
         <v>1452</v>
       </c>
       <c r="Q1055" s="9" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="R1055" s="12" t="n">
-        <v>3891.96</v>
+        <v>19500</v>
       </c>
       <c r="S1055" s="12" t="n">
-        <v>3891.96</v>
+        <v>19500</v>
       </c>
       <c r="T1055" s="9" t="s">
         <v>32</v>
@@ -67731,7 +67743,7 @@
     </row>
     <row r="1056" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1056" s="3" t="n">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B1056" s="4" t="s">
         <v>22</v>
@@ -67744,22 +67756,22 @@
         <v>24</v>
       </c>
       <c r="F1056" s="4" t="s">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="G1056" s="4" t="s">
-        <v>2063</v>
-      </c>
-      <c r="H1056" s="6" t="n">
-        <v>46296.754675926</v>
+        <v>2057</v>
+      </c>
+      <c r="H1056" s="5" t="n">
+        <v>46296</v>
       </c>
       <c r="I1056" s="4" t="s">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="J1056" s="4" t="s">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="K1056" s="4" t="s">
-        <v>123</v>
+        <v>197</v>
       </c>
       <c r="L1056" s="5"/>
       <c r="M1056" s="5"/>
@@ -67767,19 +67779,19 @@
         <v>29</v>
       </c>
       <c r="O1056" s="6" t="n">
-        <v>46297.643961539</v>
+        <v>46297.64512897</v>
       </c>
       <c r="P1056" s="4" t="s">
         <v>1452</v>
       </c>
       <c r="Q1056" s="4" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="R1056" s="7" t="n">
-        <v>19500</v>
+        <v>9826.88</v>
       </c>
       <c r="S1056" s="7" t="n">
-        <v>19500</v>
+        <v>9826.88</v>
       </c>
       <c r="T1056" s="4" t="s">
         <v>32</v>
@@ -67789,7 +67801,7 @@
     </row>
     <row r="1057" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1057" s="8" t="n">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B1057" s="9" t="s">
         <v>22</v>
@@ -67799,45 +67811,45 @@
         <v>23</v>
       </c>
       <c r="E1057" s="8" t="s">
-        <v>24</v>
+        <v>2058</v>
       </c>
       <c r="F1057" s="9" t="s">
-        <v>194</v>
+        <v>453</v>
       </c>
       <c r="G1057" s="9" t="s">
-        <v>2064</v>
-      </c>
-      <c r="H1057" s="10" t="n">
-        <v>46296</v>
+        <v>2059</v>
+      </c>
+      <c r="H1057" s="11" t="n">
+        <v>46300.877766204</v>
       </c>
       <c r="I1057" s="9" t="s">
-        <v>196</v>
+        <v>453</v>
       </c>
       <c r="J1057" s="9" t="s">
-        <v>196</v>
+        <v>454</v>
       </c>
       <c r="K1057" s="9" t="s">
-        <v>197</v>
+        <v>455</v>
       </c>
       <c r="L1057" s="10"/>
       <c r="M1057" s="10"/>
       <c r="N1057" s="9" t="s">
-        <v>29</v>
+        <v>1285</v>
       </c>
       <c r="O1057" s="11" t="n">
-        <v>46297.64512897</v>
+        <v>46301.683983449</v>
       </c>
       <c r="P1057" s="9" t="s">
         <v>1452</v>
       </c>
       <c r="Q1057" s="9" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="R1057" s="12" t="n">
-        <v>9826.88</v>
+        <v>50145.6</v>
       </c>
       <c r="S1057" s="12" t="n">
-        <v>9826.88</v>
+        <v>41883.6</v>
       </c>
       <c r="T1057" s="9" t="s">
         <v>32</v>
@@ -67847,7 +67859,7 @@
     </row>
     <row r="1058" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1058" s="3" t="n">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B1058" s="4" t="s">
         <v>22</v>
@@ -67857,45 +67869,45 @@
         <v>23</v>
       </c>
       <c r="E1058" s="3" t="s">
-        <v>2065</v>
+        <v>24</v>
       </c>
       <c r="F1058" s="4" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="G1058" s="4" t="s">
-        <v>2066</v>
+        <v>2060</v>
       </c>
       <c r="H1058" s="6" t="n">
-        <v>46300.877766204</v>
+        <v>46300.582071759</v>
       </c>
       <c r="I1058" s="4" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="J1058" s="4" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="K1058" s="4" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="L1058" s="5"/>
       <c r="M1058" s="5"/>
       <c r="N1058" s="4" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O1058" s="6" t="n">
-        <v>46301.683983449</v>
+        <v>46301.684292095</v>
       </c>
       <c r="P1058" s="4" t="s">
         <v>1452</v>
       </c>
       <c r="Q1058" s="4" t="s">
-        <v>142</v>
+        <v>47</v>
       </c>
       <c r="R1058" s="7" t="n">
-        <v>50145.6</v>
+        <v>4690.4</v>
       </c>
       <c r="S1058" s="7" t="n">
-        <v>41883.6</v>
+        <v>4690.4</v>
       </c>
       <c r="T1058" s="4" t="s">
         <v>32</v>
@@ -67905,7 +67917,7 @@
     </row>
     <row r="1059" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1059" s="8" t="n">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B1059" s="9" t="s">
         <v>22</v>
@@ -67918,22 +67930,22 @@
         <v>24</v>
       </c>
       <c r="F1059" s="9" t="s">
-        <v>436</v>
+        <v>698</v>
       </c>
       <c r="G1059" s="9" t="s">
-        <v>2067</v>
+        <v>2061</v>
       </c>
       <c r="H1059" s="11" t="n">
-        <v>46300.582071759</v>
+        <v>46300.587326389</v>
       </c>
       <c r="I1059" s="9" t="s">
-        <v>438</v>
+        <v>698</v>
       </c>
       <c r="J1059" s="9" t="s">
-        <v>439</v>
+        <v>699</v>
       </c>
       <c r="K1059" s="9" t="s">
-        <v>440</v>
+        <v>700</v>
       </c>
       <c r="L1059" s="10"/>
       <c r="M1059" s="10"/>
@@ -67941,7 +67953,7 @@
         <v>29</v>
       </c>
       <c r="O1059" s="11" t="n">
-        <v>46301.684292095</v>
+        <v>46301.684423148</v>
       </c>
       <c r="P1059" s="9" t="s">
         <v>1452</v>
@@ -67950,10 +67962,10 @@
         <v>47</v>
       </c>
       <c r="R1059" s="12" t="n">
-        <v>4690.4</v>
+        <v>58500</v>
       </c>
       <c r="S1059" s="12" t="n">
-        <v>4690.4</v>
+        <v>58500</v>
       </c>
       <c r="T1059" s="9" t="s">
         <v>32</v>
@@ -67963,7 +67975,7 @@
     </row>
     <row r="1060" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1060" s="3" t="n">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B1060" s="4" t="s">
         <v>22</v>
@@ -67976,22 +67988,22 @@
         <v>24</v>
       </c>
       <c r="F1060" s="4" t="s">
-        <v>698</v>
+        <v>981</v>
       </c>
       <c r="G1060" s="4" t="s">
-        <v>2068</v>
-      </c>
-      <c r="H1060" s="6" t="n">
-        <v>46300.587326389</v>
+        <v>2062</v>
+      </c>
+      <c r="H1060" s="5" t="n">
+        <v>46301</v>
       </c>
       <c r="I1060" s="4" t="s">
-        <v>698</v>
+        <v>527</v>
       </c>
       <c r="J1060" s="4" t="s">
-        <v>699</v>
+        <v>527</v>
       </c>
       <c r="K1060" s="4" t="s">
-        <v>700</v>
+        <v>528</v>
       </c>
       <c r="L1060" s="5"/>
       <c r="M1060" s="5"/>
@@ -67999,19 +68011,19 @@
         <v>29</v>
       </c>
       <c r="O1060" s="6" t="n">
-        <v>46301.684423148</v>
+        <v>46301.685126701</v>
       </c>
       <c r="P1060" s="4" t="s">
         <v>1452</v>
       </c>
       <c r="Q1060" s="4" t="s">
-        <v>47</v>
+        <v>474</v>
       </c>
       <c r="R1060" s="7" t="n">
-        <v>58500</v>
+        <v>2108.4</v>
       </c>
       <c r="S1060" s="7" t="n">
-        <v>58500</v>
+        <v>2108.4</v>
       </c>
       <c r="T1060" s="4" t="s">
         <v>32</v>
@@ -68021,7 +68033,7 @@
     </row>
     <row r="1061" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1061" s="8" t="n">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B1061" s="9" t="s">
         <v>22</v>
@@ -68034,22 +68046,22 @@
         <v>24</v>
       </c>
       <c r="F1061" s="9" t="s">
-        <v>981</v>
+        <v>2063</v>
       </c>
       <c r="G1061" s="9" t="s">
-        <v>2069</v>
-      </c>
-      <c r="H1061" s="10" t="n">
-        <v>46301</v>
+        <v>2064</v>
+      </c>
+      <c r="H1061" s="11" t="n">
+        <v>46301.750358796</v>
       </c>
       <c r="I1061" s="9" t="s">
-        <v>527</v>
+        <v>1069</v>
       </c>
       <c r="J1061" s="9" t="s">
-        <v>527</v>
+        <v>1070</v>
       </c>
       <c r="K1061" s="9" t="s">
-        <v>528</v>
+        <v>1071</v>
       </c>
       <c r="L1061" s="10"/>
       <c r="M1061" s="10"/>
@@ -68057,19 +68069,19 @@
         <v>29</v>
       </c>
       <c r="O1061" s="11" t="n">
-        <v>46301.685126701</v>
+        <v>46302.6776625</v>
       </c>
       <c r="P1061" s="9" t="s">
         <v>1452</v>
       </c>
       <c r="Q1061" s="9" t="s">
-        <v>474</v>
+        <v>47</v>
       </c>
       <c r="R1061" s="12" t="n">
-        <v>2108.4</v>
+        <v>6038.8</v>
       </c>
       <c r="S1061" s="12" t="n">
-        <v>2108.4</v>
+        <v>6038.8</v>
       </c>
       <c r="T1061" s="9" t="s">
         <v>32</v>
@@ -68079,7 +68091,7 @@
     </row>
     <row r="1062" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1062" s="3" t="n">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B1062" s="4" t="s">
         <v>22</v>
@@ -68092,22 +68104,22 @@
         <v>24</v>
       </c>
       <c r="F1062" s="4" t="s">
-        <v>2070</v>
+        <v>698</v>
       </c>
       <c r="G1062" s="4" t="s">
-        <v>2071</v>
+        <v>2065</v>
       </c>
       <c r="H1062" s="6" t="n">
-        <v>46301.750358796</v>
+        <v>46301.972430556</v>
       </c>
       <c r="I1062" s="4" t="s">
-        <v>1069</v>
+        <v>698</v>
       </c>
       <c r="J1062" s="4" t="s">
-        <v>1070</v>
+        <v>699</v>
       </c>
       <c r="K1062" s="4" t="s">
-        <v>1071</v>
+        <v>700</v>
       </c>
       <c r="L1062" s="5"/>
       <c r="M1062" s="5"/>
@@ -68115,7 +68127,7 @@
         <v>29</v>
       </c>
       <c r="O1062" s="6" t="n">
-        <v>46302.6776625</v>
+        <v>46302.6779625</v>
       </c>
       <c r="P1062" s="4" t="s">
         <v>1452</v>
@@ -68124,10 +68136,10 @@
         <v>47</v>
       </c>
       <c r="R1062" s="7" t="n">
-        <v>6722.8</v>
+        <v>10500</v>
       </c>
       <c r="S1062" s="7" t="n">
-        <v>6722.8</v>
+        <v>10500</v>
       </c>
       <c r="T1062" s="4" t="s">
         <v>32</v>
@@ -68137,7 +68149,7 @@
     </row>
     <row r="1063" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1063" s="8" t="n">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B1063" s="9" t="s">
         <v>22</v>
@@ -68150,22 +68162,22 @@
         <v>24</v>
       </c>
       <c r="F1063" s="9" t="s">
-        <v>698</v>
+        <v>953</v>
       </c>
       <c r="G1063" s="9" t="s">
-        <v>2072</v>
+        <v>2066</v>
       </c>
       <c r="H1063" s="11" t="n">
-        <v>46301.972430556</v>
+        <v>46302.362025463</v>
       </c>
       <c r="I1063" s="9" t="s">
-        <v>698</v>
+        <v>953</v>
       </c>
       <c r="J1063" s="9" t="s">
-        <v>699</v>
+        <v>955</v>
       </c>
       <c r="K1063" s="9" t="s">
-        <v>700</v>
+        <v>956</v>
       </c>
       <c r="L1063" s="10"/>
       <c r="M1063" s="10"/>
@@ -68173,19 +68185,19 @@
         <v>29</v>
       </c>
       <c r="O1063" s="11" t="n">
-        <v>46302.6779625</v>
+        <v>46302.678099421</v>
       </c>
       <c r="P1063" s="9" t="s">
         <v>1452</v>
       </c>
       <c r="Q1063" s="9" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="R1063" s="12" t="n">
-        <v>10500</v>
+        <v>122892</v>
       </c>
       <c r="S1063" s="12" t="n">
-        <v>10500</v>
+        <v>122892</v>
       </c>
       <c r="T1063" s="9" t="s">
         <v>32</v>
@@ -68195,7 +68207,7 @@
     </row>
     <row r="1064" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1064" s="3" t="n">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B1064" s="4" t="s">
         <v>22</v>
@@ -68208,22 +68220,22 @@
         <v>24</v>
       </c>
       <c r="F1064" s="4" t="s">
-        <v>953</v>
+        <v>765</v>
       </c>
       <c r="G1064" s="4" t="s">
-        <v>2073</v>
-      </c>
-      <c r="H1064" s="6" t="n">
-        <v>46302.362025463</v>
+        <v>2067</v>
+      </c>
+      <c r="H1064" s="5" t="n">
+        <v>46302</v>
       </c>
       <c r="I1064" s="4" t="s">
-        <v>953</v>
+        <v>765</v>
       </c>
       <c r="J1064" s="4" t="s">
-        <v>955</v>
+        <v>767</v>
       </c>
       <c r="K1064" s="4" t="s">
-        <v>956</v>
+        <v>768</v>
       </c>
       <c r="L1064" s="5"/>
       <c r="M1064" s="5"/>
@@ -68231,19 +68243,19 @@
         <v>29</v>
       </c>
       <c r="O1064" s="6" t="n">
-        <v>46302.678099421</v>
+        <v>46302.678656794</v>
       </c>
       <c r="P1064" s="4" t="s">
         <v>1452</v>
       </c>
       <c r="Q1064" s="4" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="R1064" s="7" t="n">
-        <v>122892</v>
+        <v>12777.38</v>
       </c>
       <c r="S1064" s="7" t="n">
-        <v>122892</v>
+        <v>12777.38</v>
       </c>
       <c r="T1064" s="4" t="s">
         <v>32</v>
@@ -68253,7 +68265,7 @@
     </row>
     <row r="1065" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1065" s="8" t="n">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B1065" s="9" t="s">
         <v>22</v>
@@ -68266,22 +68278,22 @@
         <v>24</v>
       </c>
       <c r="F1065" s="9" t="s">
-        <v>765</v>
+        <v>332</v>
       </c>
       <c r="G1065" s="9" t="s">
-        <v>2074</v>
-      </c>
-      <c r="H1065" s="10" t="n">
-        <v>46302</v>
+        <v>2068</v>
+      </c>
+      <c r="H1065" s="11" t="n">
+        <v>46303.385266204</v>
       </c>
       <c r="I1065" s="9" t="s">
-        <v>765</v>
+        <v>117</v>
       </c>
       <c r="J1065" s="9" t="s">
-        <v>767</v>
+        <v>118</v>
       </c>
       <c r="K1065" s="9" t="s">
-        <v>768</v>
+        <v>119</v>
       </c>
       <c r="L1065" s="10"/>
       <c r="M1065" s="10"/>
@@ -68289,19 +68301,19 @@
         <v>29</v>
       </c>
       <c r="O1065" s="11" t="n">
-        <v>46302.678656794</v>
+        <v>46304.461355984</v>
       </c>
       <c r="P1065" s="9" t="s">
         <v>1452</v>
       </c>
       <c r="Q1065" s="9" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="R1065" s="12" t="n">
-        <v>12777.38</v>
+        <v>20709.6</v>
       </c>
       <c r="S1065" s="12" t="n">
-        <v>12777.38</v>
+        <v>20709.6</v>
       </c>
       <c r="T1065" s="9" t="s">
         <v>32</v>
@@ -68311,7 +68323,7 @@
     </row>
     <row r="1066" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1066" s="3" t="n">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B1066" s="4" t="s">
         <v>22</v>
@@ -68324,22 +68336,22 @@
         <v>24</v>
       </c>
       <c r="F1066" s="4" t="s">
-        <v>332</v>
+        <v>75</v>
       </c>
       <c r="G1066" s="4" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="H1066" s="6" t="n">
-        <v>46303.385266204</v>
+        <v>46302.730069444</v>
       </c>
       <c r="I1066" s="4" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="J1066" s="4" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="K1066" s="4" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="L1066" s="5"/>
       <c r="M1066" s="5"/>
@@ -68347,7 +68359,7 @@
         <v>29</v>
       </c>
       <c r="O1066" s="6" t="n">
-        <v>46304.461355984</v>
+        <v>46304.461507176</v>
       </c>
       <c r="P1066" s="4" t="s">
         <v>1452</v>
@@ -68356,10 +68368,10 @@
         <v>31</v>
       </c>
       <c r="R1066" s="7" t="n">
-        <v>20709.6</v>
+        <v>5040</v>
       </c>
       <c r="S1066" s="7" t="n">
-        <v>20709.6</v>
+        <v>5040</v>
       </c>
       <c r="T1066" s="4" t="s">
         <v>32</v>
@@ -68369,7 +68381,7 @@
     </row>
     <row r="1067" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1067" s="8" t="n">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B1067" s="9" t="s">
         <v>22</v>
@@ -68382,22 +68394,22 @@
         <v>24</v>
       </c>
       <c r="F1067" s="9" t="s">
-        <v>75</v>
+        <v>1917</v>
       </c>
       <c r="G1067" s="9" t="s">
-        <v>2076</v>
-      </c>
-      <c r="H1067" s="11" t="n">
-        <v>46302.730069444</v>
+        <v>2070</v>
+      </c>
+      <c r="H1067" s="10" t="n">
+        <v>46302</v>
       </c>
       <c r="I1067" s="9" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J1067" s="9" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="K1067" s="9" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="L1067" s="10"/>
       <c r="M1067" s="10"/>
@@ -68405,19 +68417,19 @@
         <v>29</v>
       </c>
       <c r="O1067" s="11" t="n">
-        <v>46304.461507176</v>
+        <v>46304.462336146</v>
       </c>
       <c r="P1067" s="9" t="s">
         <v>1452</v>
       </c>
       <c r="Q1067" s="9" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="R1067" s="12" t="n">
-        <v>5040</v>
+        <v>2250</v>
       </c>
       <c r="S1067" s="12" t="n">
-        <v>5040</v>
+        <v>2250</v>
       </c>
       <c r="T1067" s="9" t="s">
         <v>32</v>
@@ -68427,7 +68439,7 @@
     </row>
     <row r="1068" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1068" s="3" t="n">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B1068" s="4" t="s">
         <v>22</v>
@@ -68440,22 +68452,22 @@
         <v>24</v>
       </c>
       <c r="F1068" s="4" t="s">
-        <v>1917</v>
+        <v>967</v>
       </c>
       <c r="G1068" s="4" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="H1068" s="5" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="I1068" s="4" t="s">
-        <v>65</v>
+        <v>221</v>
       </c>
       <c r="J1068" s="4" t="s">
-        <v>66</v>
+        <v>221</v>
       </c>
       <c r="K1068" s="4" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="L1068" s="5"/>
       <c r="M1068" s="5"/>
@@ -68463,7 +68475,7 @@
         <v>29</v>
       </c>
       <c r="O1068" s="6" t="n">
-        <v>46304.462336146</v>
+        <v>46308.322246215</v>
       </c>
       <c r="P1068" s="4" t="s">
         <v>1452</v>
@@ -68472,10 +68484,10 @@
         <v>134</v>
       </c>
       <c r="R1068" s="7" t="n">
-        <v>2250</v>
+        <v>3019.68</v>
       </c>
       <c r="S1068" s="7" t="n">
-        <v>2250</v>
+        <v>3019.68</v>
       </c>
       <c r="T1068" s="4" t="s">
         <v>32</v>
@@ -68485,7 +68497,7 @@
     </row>
     <row r="1069" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1069" s="8" t="n">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B1069" s="9" t="s">
         <v>22</v>
@@ -68498,22 +68510,22 @@
         <v>24</v>
       </c>
       <c r="F1069" s="9" t="s">
-        <v>967</v>
+        <v>295</v>
       </c>
       <c r="G1069" s="9" t="s">
-        <v>2078</v>
-      </c>
-      <c r="H1069" s="10" t="n">
-        <v>46304</v>
+        <v>2072</v>
+      </c>
+      <c r="H1069" s="11" t="n">
+        <v>46304.355324074</v>
       </c>
       <c r="I1069" s="9" t="s">
-        <v>221</v>
+        <v>295</v>
       </c>
       <c r="J1069" s="9" t="s">
-        <v>221</v>
+        <v>297</v>
       </c>
       <c r="K1069" s="9" t="s">
-        <v>222</v>
+        <v>1050</v>
       </c>
       <c r="L1069" s="10"/>
       <c r="M1069" s="10"/>
@@ -68521,19 +68533,19 @@
         <v>29</v>
       </c>
       <c r="O1069" s="11" t="n">
-        <v>46308.322246215</v>
+        <v>46308.322793634</v>
       </c>
       <c r="P1069" s="9" t="s">
         <v>1452</v>
       </c>
       <c r="Q1069" s="9" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="R1069" s="12" t="n">
-        <v>3019.68</v>
+        <v>23400</v>
       </c>
       <c r="S1069" s="12" t="n">
-        <v>3019.68</v>
+        <v>23400</v>
       </c>
       <c r="T1069" s="9" t="s">
         <v>32</v>
@@ -68543,7 +68555,7 @@
     </row>
     <row r="1070" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1070" s="3" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B1070" s="4" t="s">
         <v>22</v>
@@ -68556,22 +68568,22 @@
         <v>24</v>
       </c>
       <c r="F1070" s="4" t="s">
-        <v>295</v>
+        <v>1827</v>
       </c>
       <c r="G1070" s="4" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="H1070" s="6" t="n">
-        <v>46304.355324074</v>
+        <v>46304.483865741</v>
       </c>
       <c r="I1070" s="4" t="s">
-        <v>295</v>
+        <v>1827</v>
       </c>
       <c r="J1070" s="4" t="s">
-        <v>297</v>
+        <v>1828</v>
       </c>
       <c r="K1070" s="4" t="s">
-        <v>1050</v>
+        <v>1829</v>
       </c>
       <c r="L1070" s="5"/>
       <c r="M1070" s="5"/>
@@ -68579,7 +68591,7 @@
         <v>29</v>
       </c>
       <c r="O1070" s="6" t="n">
-        <v>46308.322793634</v>
+        <v>46308.322972604</v>
       </c>
       <c r="P1070" s="4" t="s">
         <v>1452</v>
@@ -68588,20 +68600,20 @@
         <v>31</v>
       </c>
       <c r="R1070" s="7" t="n">
-        <v>23400</v>
+        <v>5916.9</v>
       </c>
       <c r="S1070" s="7" t="n">
-        <v>23400</v>
+        <v>5916.9</v>
       </c>
       <c r="T1070" s="4" t="s">
-        <v>32</v>
+        <v>1830</v>
       </c>
       <c r="U1070" s="4"/>
       <c r="V1070" s="4"/>
     </row>
     <row r="1071" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1071" s="8" t="n">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B1071" s="9" t="s">
         <v>22</v>
@@ -68611,55 +68623,55 @@
         <v>23</v>
       </c>
       <c r="E1071" s="8" t="s">
-        <v>24</v>
+        <v>2074</v>
       </c>
       <c r="F1071" s="9" t="s">
-        <v>1827</v>
+        <v>1634</v>
       </c>
       <c r="G1071" s="9" t="s">
-        <v>2080</v>
-      </c>
-      <c r="H1071" s="11" t="n">
-        <v>46304.483865741</v>
+        <v>2075</v>
+      </c>
+      <c r="H1071" s="10" t="n">
+        <v>46308</v>
       </c>
       <c r="I1071" s="9" t="s">
-        <v>1827</v>
+        <v>290</v>
       </c>
       <c r="J1071" s="9" t="s">
-        <v>1828</v>
+        <v>290</v>
       </c>
       <c r="K1071" s="9" t="s">
-        <v>1829</v>
+        <v>291</v>
       </c>
       <c r="L1071" s="10"/>
       <c r="M1071" s="10"/>
       <c r="N1071" s="9" t="s">
-        <v>29</v>
+        <v>1285</v>
       </c>
       <c r="O1071" s="11" t="n">
-        <v>46308.322972604</v>
+        <v>46308.671253704</v>
       </c>
       <c r="P1071" s="9" t="s">
         <v>1452</v>
       </c>
       <c r="Q1071" s="9" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="R1071" s="12" t="n">
-        <v>5916.9</v>
+        <v>19055.26</v>
       </c>
       <c r="S1071" s="12" t="n">
-        <v>5916.9</v>
+        <v>14366.98</v>
       </c>
       <c r="T1071" s="9" t="s">
-        <v>1830</v>
+        <v>32</v>
       </c>
       <c r="U1071" s="9"/>
       <c r="V1071" s="9"/>
     </row>
     <row r="1072" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1072" s="3" t="n">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B1072" s="4" t="s">
         <v>22</v>
@@ -68669,45 +68681,45 @@
         <v>23</v>
       </c>
       <c r="E1072" s="3" t="s">
-        <v>2081</v>
+        <v>24</v>
       </c>
       <c r="F1072" s="4" t="s">
-        <v>1634</v>
+        <v>276</v>
       </c>
       <c r="G1072" s="4" t="s">
-        <v>2082</v>
-      </c>
-      <c r="H1072" s="5" t="n">
-        <v>46308</v>
+        <v>2076</v>
+      </c>
+      <c r="H1072" s="6" t="n">
+        <v>46308.484027778</v>
       </c>
       <c r="I1072" s="4" t="s">
-        <v>290</v>
+        <v>109</v>
       </c>
       <c r="J1072" s="4" t="s">
-        <v>290</v>
+        <v>109</v>
       </c>
       <c r="K1072" s="4" t="s">
-        <v>291</v>
+        <v>110</v>
       </c>
       <c r="L1072" s="5"/>
       <c r="M1072" s="5"/>
       <c r="N1072" s="4" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O1072" s="6" t="n">
-        <v>46308.671253704</v>
+        <v>46308.672965127</v>
       </c>
       <c r="P1072" s="4" t="s">
         <v>1452</v>
       </c>
       <c r="Q1072" s="4" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="R1072" s="7" t="n">
-        <v>18778.66</v>
+        <v>4041</v>
       </c>
       <c r="S1072" s="7" t="n">
-        <v>2197.3</v>
+        <v>4041</v>
       </c>
       <c r="T1072" s="4" t="s">
         <v>32</v>
@@ -68717,7 +68729,7 @@
     </row>
     <row r="1073" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1073" s="8" t="n">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B1073" s="9" t="s">
         <v>22</v>
@@ -68727,16 +68739,16 @@
         <v>23</v>
       </c>
       <c r="E1073" s="8" t="s">
-        <v>24</v>
+        <v>285</v>
       </c>
       <c r="F1073" s="9" t="s">
         <v>276</v>
       </c>
       <c r="G1073" s="9" t="s">
-        <v>2083</v>
+        <v>2077</v>
       </c>
       <c r="H1073" s="11" t="n">
-        <v>46308.484027778</v>
+        <v>46308.475208333</v>
       </c>
       <c r="I1073" s="9" t="s">
         <v>109</v>
@@ -68750,10 +68762,10 @@
       <c r="L1073" s="10"/>
       <c r="M1073" s="10"/>
       <c r="N1073" s="9" t="s">
-        <v>29</v>
+        <v>1285</v>
       </c>
       <c r="O1073" s="11" t="n">
-        <v>46308.672965127</v>
+        <v>46308.673458252</v>
       </c>
       <c r="P1073" s="9" t="s">
         <v>1452</v>
@@ -68762,10 +68774,10 @@
         <v>31</v>
       </c>
       <c r="R1073" s="12" t="n">
-        <v>4041</v>
+        <v>387000</v>
       </c>
       <c r="S1073" s="12" t="n">
-        <v>4041</v>
+        <v>0</v>
       </c>
       <c r="T1073" s="9" t="s">
         <v>32</v>
@@ -68775,7 +68787,7 @@
     </row>
     <row r="1074" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1074" s="3" t="n">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B1074" s="4" t="s">
         <v>22</v>
@@ -68785,45 +68797,45 @@
         <v>23</v>
       </c>
       <c r="E1074" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1074" s="4" t="s">
-        <v>276</v>
+        <v>366</v>
       </c>
       <c r="G1074" s="4" t="s">
-        <v>2084</v>
-      </c>
-      <c r="H1074" s="6" t="n">
-        <v>46308.475208333</v>
+        <v>2078</v>
+      </c>
+      <c r="H1074" s="5" t="n">
+        <v>46308</v>
       </c>
       <c r="I1074" s="4" t="s">
-        <v>109</v>
+        <v>366</v>
       </c>
       <c r="J1074" s="4" t="s">
-        <v>109</v>
+        <v>368</v>
       </c>
       <c r="K1074" s="4" t="s">
-        <v>110</v>
+        <v>369</v>
       </c>
       <c r="L1074" s="5"/>
       <c r="M1074" s="5"/>
       <c r="N1074" s="4" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O1074" s="6" t="n">
-        <v>46308.673458252</v>
+        <v>46309.334198148</v>
       </c>
       <c r="P1074" s="4" t="s">
         <v>1452</v>
       </c>
       <c r="Q1074" s="4" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="R1074" s="7" t="n">
-        <v>387000</v>
+        <v>3480</v>
       </c>
       <c r="S1074" s="7" t="n">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="T1074" s="4" t="s">
         <v>32</v>
@@ -68833,7 +68845,7 @@
     </row>
     <row r="1075" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1075" s="8" t="n">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B1075" s="9" t="s">
         <v>22</v>
@@ -68846,22 +68858,22 @@
         <v>24</v>
       </c>
       <c r="F1075" s="9" t="s">
-        <v>366</v>
+        <v>837</v>
       </c>
       <c r="G1075" s="9" t="s">
-        <v>2085</v>
-      </c>
-      <c r="H1075" s="10" t="n">
-        <v>46308</v>
+        <v>2079</v>
+      </c>
+      <c r="H1075" s="11" t="n">
+        <v>46308.757569444</v>
       </c>
       <c r="I1075" s="9" t="s">
-        <v>366</v>
+        <v>837</v>
       </c>
       <c r="J1075" s="9" t="s">
-        <v>368</v>
+        <v>838</v>
       </c>
       <c r="K1075" s="9" t="s">
-        <v>369</v>
+        <v>839</v>
       </c>
       <c r="L1075" s="10"/>
       <c r="M1075" s="10"/>
@@ -68869,19 +68881,19 @@
         <v>29</v>
       </c>
       <c r="O1075" s="11" t="n">
-        <v>46309.334198148</v>
+        <v>46309.377516204</v>
       </c>
       <c r="P1075" s="9" t="s">
         <v>1452</v>
       </c>
       <c r="Q1075" s="9" t="s">
-        <v>134</v>
+        <v>747</v>
       </c>
       <c r="R1075" s="12" t="n">
-        <v>3480</v>
+        <v>15707.22</v>
       </c>
       <c r="S1075" s="12" t="n">
-        <v>3480</v>
+        <v>15707.22</v>
       </c>
       <c r="T1075" s="9" t="s">
         <v>32</v>
@@ -68891,7 +68903,7 @@
     </row>
     <row r="1076" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1076" s="3" t="n">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B1076" s="4" t="s">
         <v>22</v>
@@ -68904,22 +68916,22 @@
         <v>24</v>
       </c>
       <c r="F1076" s="4" t="s">
-        <v>837</v>
+        <v>191</v>
       </c>
       <c r="G1076" s="4" t="s">
-        <v>2086</v>
+        <v>2080</v>
       </c>
       <c r="H1076" s="6" t="n">
-        <v>46308.757569444</v>
+        <v>46308.7390625</v>
       </c>
       <c r="I1076" s="4" t="s">
-        <v>837</v>
+        <v>191</v>
       </c>
       <c r="J1076" s="4" t="s">
-        <v>838</v>
+        <v>192</v>
       </c>
       <c r="K1076" s="4" t="s">
-        <v>839</v>
+        <v>193</v>
       </c>
       <c r="L1076" s="5"/>
       <c r="M1076" s="5"/>
@@ -68927,19 +68939,19 @@
         <v>29</v>
       </c>
       <c r="O1076" s="6" t="n">
-        <v>46309.377516204</v>
+        <v>46309.595986377</v>
       </c>
       <c r="P1076" s="4" t="s">
         <v>1452</v>
       </c>
       <c r="Q1076" s="4" t="s">
-        <v>747</v>
+        <v>31</v>
       </c>
       <c r="R1076" s="7" t="n">
-        <v>15707.22</v>
+        <v>19804.8</v>
       </c>
       <c r="S1076" s="7" t="n">
-        <v>15707.22</v>
+        <v>19804.8</v>
       </c>
       <c r="T1076" s="4" t="s">
         <v>32</v>
@@ -68949,7 +68961,7 @@
     </row>
     <row r="1077" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1077" s="8" t="n">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B1077" s="9" t="s">
         <v>22</v>
@@ -68962,22 +68974,22 @@
         <v>24</v>
       </c>
       <c r="F1077" s="9" t="s">
-        <v>191</v>
+        <v>1073</v>
       </c>
       <c r="G1077" s="9" t="s">
-        <v>2087</v>
+        <v>2081</v>
       </c>
       <c r="H1077" s="11" t="n">
-        <v>46308.7390625</v>
+        <v>46308.730625</v>
       </c>
       <c r="I1077" s="9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="J1077" s="9" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="K1077" s="9" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="L1077" s="10"/>
       <c r="M1077" s="10"/>
@@ -68985,7 +68997,7 @@
         <v>29</v>
       </c>
       <c r="O1077" s="11" t="n">
-        <v>46309.595986377</v>
+        <v>46309.596155706</v>
       </c>
       <c r="P1077" s="9" t="s">
         <v>1452</v>
@@ -69007,7 +69019,7 @@
     </row>
     <row r="1078" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1078" s="3" t="n">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B1078" s="4" t="s">
         <v>22</v>
@@ -69017,55 +69029,55 @@
         <v>23</v>
       </c>
       <c r="E1078" s="3" t="s">
-        <v>24</v>
+        <v>2082</v>
       </c>
       <c r="F1078" s="4" t="s">
-        <v>1073</v>
+        <v>2083</v>
       </c>
       <c r="G1078" s="4" t="s">
-        <v>2088</v>
-      </c>
-      <c r="H1078" s="6" t="n">
-        <v>46308.730625</v>
+        <v>2084</v>
+      </c>
+      <c r="H1078" s="5" t="n">
+        <v>46309</v>
       </c>
       <c r="I1078" s="4" t="s">
-        <v>186</v>
+        <v>2083</v>
       </c>
       <c r="J1078" s="4" t="s">
-        <v>187</v>
+        <v>2085</v>
       </c>
       <c r="K1078" s="4" t="s">
-        <v>188</v>
+        <v>2086</v>
       </c>
       <c r="L1078" s="5"/>
       <c r="M1078" s="5"/>
       <c r="N1078" s="4" t="s">
-        <v>29</v>
+        <v>1285</v>
       </c>
       <c r="O1078" s="6" t="n">
-        <v>46309.596155706</v>
+        <v>46310.579741169</v>
       </c>
       <c r="P1078" s="4" t="s">
         <v>1452</v>
       </c>
       <c r="Q1078" s="4" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="R1078" s="7" t="n">
-        <v>19804.8</v>
+        <v>3915.34</v>
       </c>
       <c r="S1078" s="7" t="n">
-        <v>19804.8</v>
+        <v>2336.04</v>
       </c>
       <c r="T1078" s="4" t="s">
-        <v>32</v>
+        <v>1830</v>
       </c>
       <c r="U1078" s="4"/>
       <c r="V1078" s="4"/>
     </row>
     <row r="1079" customHeight="true" ht="16.5" customFormat="true" s="1">
       <c r="A1079" s="8" t="n">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1079" s="9" t="s">
         <v>22</v>
@@ -69078,78 +69090,542 @@
         <v>285</v>
       </c>
       <c r="F1079" s="9" t="s">
-        <v>2089</v>
+        <v>38</v>
       </c>
       <c r="G1079" s="9" t="s">
-        <v>2090</v>
-      </c>
-      <c r="H1079" s="10" t="n">
-        <v>46309</v>
+        <v>2087</v>
+      </c>
+      <c r="H1079" s="11" t="n">
+        <v>46310.747743056</v>
       </c>
       <c r="I1079" s="9" t="s">
-        <v>2089</v>
+        <v>40</v>
       </c>
       <c r="J1079" s="9" t="s">
-        <v>2091</v>
+        <v>41</v>
       </c>
       <c r="K1079" s="9" t="s">
-        <v>2092</v>
+        <v>42</v>
       </c>
       <c r="L1079" s="10"/>
       <c r="M1079" s="10"/>
       <c r="N1079" s="9" t="s">
-        <v>2007</v>
+        <v>2088</v>
       </c>
       <c r="O1079" s="11" t="n">
-        <v>46310.579741169</v>
+        <v>46315.400142743</v>
       </c>
       <c r="P1079" s="9" t="s">
         <v>1452</v>
       </c>
       <c r="Q1079" s="9" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="R1079" s="12" t="n">
-        <v>3915.34</v>
+        <v>34860.08</v>
       </c>
       <c r="S1079" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T1079" s="9" t="s">
-        <v>1830</v>
+        <v>32</v>
       </c>
       <c r="U1079" s="9"/>
       <c r="V1079" s="9"/>
     </row>
-    <row r="1080" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A1080" s="13" t="n">
-        <v>1078</v>
-      </c>
-      <c r="B1080" s="14"/>
-      <c r="C1080" s="14"/>
-      <c r="D1080" s="14"/>
-      <c r="E1080" s="14"/>
-      <c r="F1080" s="14"/>
-      <c r="G1080" s="14"/>
-      <c r="H1080" s="14"/>
-      <c r="I1080" s="14"/>
-      <c r="J1080" s="14"/>
-      <c r="K1080" s="14"/>
-      <c r="L1080" s="14"/>
-      <c r="M1080" s="14"/>
-      <c r="N1080" s="14"/>
-      <c r="O1080" s="14"/>
-      <c r="P1080" s="14"/>
-      <c r="Q1080" s="14"/>
-      <c r="R1080" s="15" t="n">
-        <v>63326377.3806</v>
-      </c>
-      <c r="S1080" s="15" t="n">
-        <v>60818869.6806</v>
-      </c>
-      <c r="T1080" s="14"/>
-      <c r="U1080" s="14"/>
-      <c r="V1080" s="16"/>
+    <row r="1080" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1080" s="3" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B1080" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1080" s="4"/>
+      <c r="D1080" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1080" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F1080" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="G1080" s="4" t="s">
+        <v>2089</v>
+      </c>
+      <c r="H1080" s="6" t="n">
+        <v>46310.770381944</v>
+      </c>
+      <c r="I1080" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1080" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1080" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1080" s="5"/>
+      <c r="M1080" s="5"/>
+      <c r="N1080" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O1080" s="6" t="n">
+        <v>46315.400313576</v>
+      </c>
+      <c r="P1080" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1080" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1080" s="7" t="n">
+        <v>28988.52</v>
+      </c>
+      <c r="S1080" s="7" t="n">
+        <v>20985.12</v>
+      </c>
+      <c r="T1080" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1080" s="4"/>
+      <c r="V1080" s="4"/>
+    </row>
+    <row r="1081" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1081" s="8" t="n">
+        <v>1151</v>
+      </c>
+      <c r="B1081" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1081" s="9"/>
+      <c r="D1081" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1081" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1081" s="9" t="s">
+        <v>1389</v>
+      </c>
+      <c r="G1081" s="9" t="s">
+        <v>2090</v>
+      </c>
+      <c r="H1081" s="11" t="n">
+        <v>46310.691099537</v>
+      </c>
+      <c r="I1081" s="9" t="s">
+        <v>1389</v>
+      </c>
+      <c r="J1081" s="9" t="s">
+        <v>1391</v>
+      </c>
+      <c r="K1081" s="9" t="s">
+        <v>1392</v>
+      </c>
+      <c r="L1081" s="10"/>
+      <c r="M1081" s="10"/>
+      <c r="N1081" s="9" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O1081" s="11" t="n">
+        <v>46315.400447072</v>
+      </c>
+      <c r="P1081" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1081" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1081" s="12" t="n">
+        <v>3058</v>
+      </c>
+      <c r="S1081" s="12" t="n">
+        <v>3058</v>
+      </c>
+      <c r="T1081" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1081" s="9"/>
+      <c r="V1081" s="9"/>
+    </row>
+    <row r="1082" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1082" s="3" t="n">
+        <v>1152</v>
+      </c>
+      <c r="B1082" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1082" s="4"/>
+      <c r="D1082" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1082" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1082" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="G1082" s="4" t="s">
+        <v>2091</v>
+      </c>
+      <c r="H1082" s="6" t="n">
+        <v>46310.736655093</v>
+      </c>
+      <c r="I1082" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="J1082" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="K1082" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="L1082" s="5"/>
+      <c r="M1082" s="5"/>
+      <c r="N1082" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1082" s="6" t="n">
+        <v>46315.400593056</v>
+      </c>
+      <c r="P1082" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1082" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1082" s="7" t="n">
+        <v>50527</v>
+      </c>
+      <c r="S1082" s="7" t="n">
+        <v>50527</v>
+      </c>
+      <c r="T1082" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1082" s="4"/>
+      <c r="V1082" s="4"/>
+    </row>
+    <row r="1083" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1083" s="8" t="n">
+        <v>1153</v>
+      </c>
+      <c r="B1083" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1083" s="9"/>
+      <c r="D1083" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1083" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1083" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="G1083" s="9" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H1083" s="11" t="n">
+        <v>46310.60712963</v>
+      </c>
+      <c r="I1083" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="J1083" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="K1083" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="L1083" s="10"/>
+      <c r="M1083" s="10"/>
+      <c r="N1083" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1083" s="11" t="n">
+        <v>46315.400754248</v>
+      </c>
+      <c r="P1083" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1083" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1083" s="12" t="n">
+        <v>23696</v>
+      </c>
+      <c r="S1083" s="12" t="n">
+        <v>23696</v>
+      </c>
+      <c r="T1083" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1083" s="9"/>
+      <c r="V1083" s="9"/>
+    </row>
+    <row r="1084" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1084" s="3" t="n">
+        <v>1154</v>
+      </c>
+      <c r="B1084" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1084" s="4"/>
+      <c r="D1084" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1084" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1084" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1084" s="4" t="s">
+        <v>2093</v>
+      </c>
+      <c r="H1084" s="6" t="n">
+        <v>46311.671215278</v>
+      </c>
+      <c r="I1084" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1084" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1084" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1084" s="5"/>
+      <c r="M1084" s="5"/>
+      <c r="N1084" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1084" s="6" t="n">
+        <v>46315.400893519</v>
+      </c>
+      <c r="P1084" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1084" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1084" s="7" t="n">
+        <v>7056</v>
+      </c>
+      <c r="S1084" s="7" t="n">
+        <v>7056</v>
+      </c>
+      <c r="T1084" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1084" s="4"/>
+      <c r="V1084" s="4"/>
+    </row>
+    <row r="1085" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1085" s="8" t="n">
+        <v>1155</v>
+      </c>
+      <c r="B1085" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1085" s="9"/>
+      <c r="D1085" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1085" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1085" s="9" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G1085" s="9" t="s">
+        <v>2094</v>
+      </c>
+      <c r="H1085" s="11" t="n">
+        <v>46314.461296296</v>
+      </c>
+      <c r="I1085" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="J1085" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="K1085" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="L1085" s="10"/>
+      <c r="M1085" s="10"/>
+      <c r="N1085" s="9" t="s">
+        <v>2088</v>
+      </c>
+      <c r="O1085" s="11" t="n">
+        <v>46315.681983368</v>
+      </c>
+      <c r="P1085" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1085" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1085" s="12" t="n">
+        <v>55080</v>
+      </c>
+      <c r="S1085" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1085" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1085" s="9"/>
+      <c r="V1085" s="9"/>
+    </row>
+    <row r="1086" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1086" s="3" t="n">
+        <v>1156</v>
+      </c>
+      <c r="B1086" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1086" s="4"/>
+      <c r="D1086" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1086" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1086" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="G1086" s="4" t="s">
+        <v>2095</v>
+      </c>
+      <c r="H1086" s="6" t="n">
+        <v>46314.658842593</v>
+      </c>
+      <c r="I1086" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="J1086" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="K1086" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="L1086" s="5"/>
+      <c r="M1086" s="5"/>
+      <c r="N1086" s="4" t="s">
+        <v>2088</v>
+      </c>
+      <c r="O1086" s="6" t="n">
+        <v>46315.68221875</v>
+      </c>
+      <c r="P1086" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1086" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1086" s="7" t="n">
+        <v>25925.7</v>
+      </c>
+      <c r="S1086" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1086" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1086" s="4"/>
+      <c r="V1086" s="4"/>
+    </row>
+    <row r="1087" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1087" s="8" t="n">
+        <v>1157</v>
+      </c>
+      <c r="B1087" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1087" s="9"/>
+      <c r="D1087" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1087" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1087" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="G1087" s="9" t="s">
+        <v>2096</v>
+      </c>
+      <c r="H1087" s="11" t="n">
+        <v>46314.761377315</v>
+      </c>
+      <c r="I1087" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="J1087" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="K1087" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1087" s="10"/>
+      <c r="M1087" s="10"/>
+      <c r="N1087" s="9" t="s">
+        <v>2088</v>
+      </c>
+      <c r="O1087" s="11" t="n">
+        <v>46315.682364005</v>
+      </c>
+      <c r="P1087" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1087" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1087" s="12" t="n">
+        <v>18560.4</v>
+      </c>
+      <c r="S1087" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1087" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1087" s="9"/>
+      <c r="V1087" s="9"/>
+    </row>
+    <row r="1088" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A1088" s="13" t="n">
+        <v>1086</v>
+      </c>
+      <c r="B1088" s="14"/>
+      <c r="C1088" s="14"/>
+      <c r="D1088" s="14"/>
+      <c r="E1088" s="14"/>
+      <c r="F1088" s="14"/>
+      <c r="G1088" s="14"/>
+      <c r="H1088" s="14"/>
+      <c r="I1088" s="14"/>
+      <c r="J1088" s="14"/>
+      <c r="K1088" s="14"/>
+      <c r="L1088" s="14"/>
+      <c r="M1088" s="14"/>
+      <c r="N1088" s="14"/>
+      <c r="O1088" s="14"/>
+      <c r="P1088" s="14"/>
+      <c r="Q1088" s="14"/>
+      <c r="R1088" s="15" t="n">
+        <v>63551053.9206</v>
+      </c>
+      <c r="S1088" s="15" t="n">
+        <v>61077472.6606</v>
+      </c>
+      <c r="T1088" s="14"/>
+      <c r="U1088" s="14"/>
+      <c r="V1088" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="2097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="2123">
   <si>
     <t>ID</t>
   </si>
@@ -5706,9 +5706,6 @@
     <t>1176</t>
   </si>
   <si>
-    <t>88 %</t>
-  </si>
-  <si>
     <t>1177</t>
   </si>
   <si>
@@ -5934,7 +5931,7 @@
     <t>1233</t>
   </si>
   <si>
-    <t>13 %</t>
+    <t>18 %</t>
   </si>
   <si>
     <t>1234</t>
@@ -6009,9 +6006,6 @@
     <t>1249</t>
   </si>
   <si>
-    <t>24 %</t>
-  </si>
-  <si>
     <t>1250</t>
   </si>
   <si>
@@ -6237,9 +6231,6 @@
     <t>1307</t>
   </si>
   <si>
-    <t>75 %</t>
-  </si>
-  <si>
     <t>1308</t>
   </si>
   <si>
@@ -6261,9 +6252,6 @@
     <t>1314</t>
   </si>
   <si>
-    <t>60 %</t>
-  </si>
-  <si>
     <t>SISAL MED</t>
   </si>
   <si>
@@ -6300,10 +6288,100 @@
     <t>1323</t>
   </si>
   <si>
+    <t>71 %</t>
+  </si>
+  <si>
     <t>1324</t>
   </si>
   <si>
+    <t>36 %</t>
+  </si>
+  <si>
     <t>1325</t>
+  </si>
+  <si>
+    <t>1326</t>
+  </si>
+  <si>
+    <t>1327</t>
+  </si>
+  <si>
+    <t>1328</t>
+  </si>
+  <si>
+    <t>41 %</t>
+  </si>
+  <si>
+    <t>DAZ DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1329</t>
+  </si>
+  <si>
+    <t>1330</t>
+  </si>
+  <si>
+    <t>1331</t>
+  </si>
+  <si>
+    <t>1332</t>
+  </si>
+  <si>
+    <t>1333</t>
+  </si>
+  <si>
+    <t>67 %</t>
+  </si>
+  <si>
+    <t>1334</t>
+  </si>
+  <si>
+    <t>1335</t>
+  </si>
+  <si>
+    <t>1336</t>
+  </si>
+  <si>
+    <t>1337</t>
+  </si>
+  <si>
+    <t>1338</t>
+  </si>
+  <si>
+    <t>ALS DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t>1339</t>
+  </si>
+  <si>
+    <t>LUCINEIDE DE SOUSA CARVALHO LTDA</t>
+  </si>
+  <si>
+    <t>26.697.721/0001-96</t>
+  </si>
+  <si>
+    <t>1340</t>
+  </si>
+  <si>
+    <t>SAFETY&amp;HEALTH</t>
+  </si>
+  <si>
+    <t>1341</t>
+  </si>
+  <si>
+    <t>SAFETY&amp;HEALTH SERVICOS</t>
+  </si>
+  <si>
+    <t>SAFETY E HEALTH SERVICOS E ALUGUEL DE EQUIPAMENTOS</t>
+  </si>
+  <si>
+    <t>36.977.902/0001-20</t>
+  </si>
+  <si>
+    <t>1342</t>
+  </si>
+  <si>
+    <t>1343</t>
   </si>
 </sst>
 </file>
@@ -6497,7 +6575,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V1088"/>
+  <dimension ref="A1:V1106"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -61199,13 +61277,13 @@
         <v>23</v>
       </c>
       <c r="E943" s="8" t="s">
-        <v>1897</v>
+        <v>24</v>
       </c>
       <c r="F943" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G943" s="9" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H943" s="11" t="n">
         <v>46261.674166667</v>
@@ -61222,7 +61300,7 @@
       <c r="L943" s="10"/>
       <c r="M943" s="10"/>
       <c r="N943" s="9" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O943" s="11" t="n">
         <v>46262.58240625</v>
@@ -61237,7 +61315,7 @@
         <v>42336</v>
       </c>
       <c r="S943" s="12" t="n">
-        <v>37296</v>
+        <v>42336</v>
       </c>
       <c r="T943" s="9" t="s">
         <v>32</v>
@@ -61263,7 +61341,7 @@
         <v>211</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H944" s="6" t="n">
         <v>46261.624131944</v>
@@ -61321,7 +61399,7 @@
         <v>521</v>
       </c>
       <c r="G945" s="9" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H945" s="11" t="n">
         <v>46261.626898148</v>
@@ -61379,7 +61457,7 @@
         <v>1054</v>
       </c>
       <c r="G946" s="4" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H946" s="5" t="n">
         <v>46262</v>
@@ -61437,7 +61515,7 @@
         <v>1017</v>
       </c>
       <c r="G947" s="9" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H947" s="10" t="n">
         <v>46261</v>
@@ -61495,7 +61573,7 @@
         <v>38</v>
       </c>
       <c r="G948" s="4" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H948" s="6" t="n">
         <v>46262.683993056</v>
@@ -61547,13 +61625,13 @@
         <v>23</v>
       </c>
       <c r="E949" s="8" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="F949" s="9" t="s">
         <v>1725</v>
       </c>
       <c r="G949" s="9" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="H949" s="10" t="n">
         <v>46265</v>
@@ -61605,13 +61683,13 @@
         <v>23</v>
       </c>
       <c r="E950" s="3" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="F950" s="4" t="s">
         <v>1634</v>
       </c>
       <c r="G950" s="4" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H950" s="5" t="n">
         <v>46265</v>
@@ -61669,7 +61747,7 @@
         <v>619</v>
       </c>
       <c r="G951" s="9" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H951" s="11" t="n">
         <v>46265.756805556</v>
@@ -61727,7 +61805,7 @@
         <v>103</v>
       </c>
       <c r="G952" s="4" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H952" s="6" t="n">
         <v>46262.6721875</v>
@@ -61785,7 +61863,7 @@
         <v>814</v>
       </c>
       <c r="G953" s="9" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="H953" s="11" t="n">
         <v>46265.738773148</v>
@@ -61843,7 +61921,7 @@
         <v>484</v>
       </c>
       <c r="G954" s="4" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H954" s="6" t="n">
         <v>46265.406400463</v>
@@ -61901,7 +61979,7 @@
         <v>482</v>
       </c>
       <c r="G955" s="9" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H955" s="11" t="n">
         <v>46262.643506944</v>
@@ -61959,7 +62037,7 @@
         <v>744</v>
       </c>
       <c r="G956" s="4" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H956" s="6" t="n">
         <v>46262.644305556</v>
@@ -62017,7 +62095,7 @@
         <v>1176</v>
       </c>
       <c r="G957" s="9" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="H957" s="11" t="n">
         <v>46262.617488426</v>
@@ -62075,7 +62153,7 @@
         <v>1522</v>
       </c>
       <c r="G958" s="4" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H958" s="6" t="n">
         <v>46262.337835648</v>
@@ -62133,7 +62211,7 @@
         <v>1512</v>
       </c>
       <c r="G959" s="9" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H959" s="10" t="n">
         <v>46266</v>
@@ -62188,10 +62266,10 @@
         <v>24</v>
       </c>
       <c r="F960" s="4" t="s">
+        <v>1916</v>
+      </c>
+      <c r="G960" s="4" t="s">
         <v>1917</v>
-      </c>
-      <c r="G960" s="4" t="s">
-        <v>1918</v>
       </c>
       <c r="H960" s="5" t="n">
         <v>46265</v>
@@ -62246,22 +62324,22 @@
         <v>24</v>
       </c>
       <c r="F961" s="9" t="s">
+        <v>1918</v>
+      </c>
+      <c r="G961" s="9" t="s">
         <v>1919</v>
-      </c>
-      <c r="G961" s="9" t="s">
-        <v>1920</v>
       </c>
       <c r="H961" s="10" t="n">
         <v>46266</v>
       </c>
       <c r="I961" s="9" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="J961" s="9" t="s">
+        <v>1920</v>
+      </c>
+      <c r="K961" s="9" t="s">
         <v>1921</v>
-      </c>
-      <c r="K961" s="9" t="s">
-        <v>1922</v>
       </c>
       <c r="L961" s="10"/>
       <c r="M961" s="10"/>
@@ -62304,22 +62382,22 @@
         <v>24</v>
       </c>
       <c r="F962" s="4" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G962" s="4" t="s">
         <v>1923</v>
-      </c>
-      <c r="G962" s="4" t="s">
-        <v>1924</v>
       </c>
       <c r="H962" s="5" t="n">
         <v>46265</v>
       </c>
       <c r="I962" s="4" t="s">
+        <v>1924</v>
+      </c>
+      <c r="J962" s="4" t="s">
         <v>1925</v>
       </c>
-      <c r="J962" s="4" t="s">
+      <c r="K962" s="4" t="s">
         <v>1926</v>
-      </c>
-      <c r="K962" s="4" t="s">
-        <v>1927</v>
       </c>
       <c r="L962" s="5"/>
       <c r="M962" s="5"/>
@@ -62365,7 +62443,7 @@
         <v>944</v>
       </c>
       <c r="G963" s="9" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H963" s="11" t="n">
         <v>46267.438217593</v>
@@ -62423,7 +62501,7 @@
         <v>310</v>
       </c>
       <c r="G964" s="4" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H964" s="5" t="n">
         <v>46269</v>
@@ -62481,7 +62559,7 @@
         <v>402</v>
       </c>
       <c r="G965" s="9" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H965" s="11" t="n">
         <v>46269.745752315</v>
@@ -62539,7 +62617,7 @@
         <v>986</v>
       </c>
       <c r="G966" s="4" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H966" s="6" t="n">
         <v>46269.693969907</v>
@@ -62597,7 +62675,7 @@
         <v>1077</v>
       </c>
       <c r="G967" s="9" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="H967" s="11" t="n">
         <v>46269.459189815</v>
@@ -62655,7 +62733,7 @@
         <v>1492</v>
       </c>
       <c r="G968" s="4" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="H968" s="6" t="n">
         <v>46268.442615741</v>
@@ -62713,7 +62791,7 @@
         <v>157</v>
       </c>
       <c r="G969" s="9" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="H969" s="10" t="n">
         <v>46268</v>
@@ -62771,7 +62849,7 @@
         <v>967</v>
       </c>
       <c r="G970" s="4" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="H970" s="5" t="n">
         <v>46268</v>
@@ -62826,10 +62904,10 @@
         <v>24</v>
       </c>
       <c r="F971" s="9" t="s">
+        <v>1935</v>
+      </c>
+      <c r="G971" s="9" t="s">
         <v>1936</v>
-      </c>
-      <c r="G971" s="9" t="s">
-        <v>1937</v>
       </c>
       <c r="H971" s="10" t="n">
         <v>46273</v>
@@ -62887,7 +62965,7 @@
         <v>1261</v>
       </c>
       <c r="G972" s="4" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H972" s="5" t="n">
         <v>46273</v>
@@ -62945,7 +63023,7 @@
         <v>152</v>
       </c>
       <c r="G973" s="9" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H973" s="11" t="n">
         <v>46273.758136574</v>
@@ -63000,22 +63078,22 @@
         <v>24</v>
       </c>
       <c r="F974" s="4" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G974" s="4" t="s">
         <v>1940</v>
-      </c>
-      <c r="G974" s="4" t="s">
-        <v>1941</v>
       </c>
       <c r="H974" s="6" t="n">
         <v>46273.740416667</v>
       </c>
       <c r="I974" s="4" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="J974" s="4" t="s">
+        <v>1941</v>
+      </c>
+      <c r="K974" s="4" t="s">
         <v>1942</v>
-      </c>
-      <c r="K974" s="4" t="s">
-        <v>1943</v>
       </c>
       <c r="L974" s="5"/>
       <c r="M974" s="5"/>
@@ -63061,7 +63139,7 @@
         <v>1408</v>
       </c>
       <c r="G975" s="9" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="H975" s="11" t="n">
         <v>46273.780162037</v>
@@ -63116,10 +63194,10 @@
         <v>24</v>
       </c>
       <c r="F976" s="4" t="s">
+        <v>1944</v>
+      </c>
+      <c r="G976" s="4" t="s">
         <v>1945</v>
-      </c>
-      <c r="G976" s="4" t="s">
-        <v>1946</v>
       </c>
       <c r="H976" s="6" t="n">
         <v>46274.442685185</v>
@@ -63174,10 +63252,10 @@
         <v>24</v>
       </c>
       <c r="F977" s="9" t="s">
+        <v>1946</v>
+      </c>
+      <c r="G977" s="9" t="s">
         <v>1947</v>
-      </c>
-      <c r="G977" s="9" t="s">
-        <v>1948</v>
       </c>
       <c r="H977" s="10" t="n">
         <v>46273</v>
@@ -63235,7 +63313,7 @@
         <v>355</v>
       </c>
       <c r="G978" s="4" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="H978" s="5" t="n">
         <v>46274</v>
@@ -63293,7 +63371,7 @@
         <v>152</v>
       </c>
       <c r="G979" s="9" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="H979" s="10" t="n">
         <v>46273</v>
@@ -63351,7 +63429,7 @@
         <v>1211</v>
       </c>
       <c r="G980" s="4" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="H980" s="5" t="n">
         <v>46275</v>
@@ -63409,7 +63487,7 @@
         <v>215</v>
       </c>
       <c r="G981" s="9" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="H981" s="10" t="n">
         <v>46275</v>
@@ -63467,7 +63545,7 @@
         <v>1456</v>
       </c>
       <c r="G982" s="4" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="H982" s="6" t="n">
         <v>46274.972708333</v>
@@ -63525,7 +63603,7 @@
         <v>103</v>
       </c>
       <c r="G983" s="9" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="H983" s="11" t="n">
         <v>46274.976979167</v>
@@ -63583,7 +63661,7 @@
         <v>276</v>
       </c>
       <c r="G984" s="4" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="H984" s="6" t="n">
         <v>46274.703055556</v>
@@ -63641,7 +63719,7 @@
         <v>75</v>
       </c>
       <c r="G985" s="9" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="H985" s="11" t="n">
         <v>46274.682534722</v>
@@ -63699,7 +63777,7 @@
         <v>1193</v>
       </c>
       <c r="G986" s="4" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="H986" s="6" t="n">
         <v>46275.472800926</v>
@@ -63757,7 +63835,7 @@
         <v>1116</v>
       </c>
       <c r="G987" s="9" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="H987" s="11" t="n">
         <v>46276.641041667</v>
@@ -63815,7 +63893,7 @@
         <v>1293</v>
       </c>
       <c r="G988" s="4" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="H988" s="6" t="n">
         <v>46276.445613426</v>
@@ -63873,7 +63951,7 @@
         <v>478</v>
       </c>
       <c r="G989" s="9" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="H989" s="11" t="n">
         <v>46275.859097222</v>
@@ -63931,7 +64009,7 @@
         <v>496</v>
       </c>
       <c r="G990" s="4" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H990" s="6" t="n">
         <v>46276.36244213</v>
@@ -63989,7 +64067,7 @@
         <v>1424</v>
       </c>
       <c r="G991" s="9" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H991" s="11" t="n">
         <v>46276.780416667</v>
@@ -64047,7 +64125,7 @@
         <v>1289</v>
       </c>
       <c r="G992" s="4" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H992" s="6" t="n">
         <v>46276.750868056</v>
@@ -64105,7 +64183,7 @@
         <v>1664</v>
       </c>
       <c r="G993" s="9" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H993" s="11" t="n">
         <v>46276.782905093</v>
@@ -64163,19 +64241,19 @@
         <v>1159</v>
       </c>
       <c r="G994" s="4" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H994" s="5" t="n">
         <v>46276</v>
       </c>
       <c r="I994" s="4" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="J994" s="4" t="s">
         <v>1162</v>
       </c>
       <c r="K994" s="4" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="L994" s="5"/>
       <c r="M994" s="5"/>
@@ -64218,10 +64296,10 @@
         <v>24</v>
       </c>
       <c r="F995" s="9" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="G995" s="9" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H995" s="10" t="n">
         <v>46276</v>
@@ -64279,7 +64357,7 @@
         <v>592</v>
       </c>
       <c r="G996" s="4" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H996" s="6" t="n">
         <v>46279.943194444</v>
@@ -64337,7 +64415,7 @@
         <v>262</v>
       </c>
       <c r="G997" s="9" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H997" s="11" t="n">
         <v>46280.741736111</v>
@@ -64395,7 +64473,7 @@
         <v>194</v>
       </c>
       <c r="G998" s="4" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H998" s="5" t="n">
         <v>46279</v>
@@ -64453,7 +64531,7 @@
         <v>389</v>
       </c>
       <c r="G999" s="9" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H999" s="11" t="n">
         <v>46280.714386574</v>
@@ -64505,13 +64583,13 @@
         <v>23</v>
       </c>
       <c r="E1000" s="3" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="F1000" s="4" t="s">
         <v>75</v>
       </c>
       <c r="G1000" s="4" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H1000" s="6" t="n">
         <v>46280.693761574</v>
@@ -64543,7 +64621,7 @@
         <v>885906</v>
       </c>
       <c r="S1000" s="7" t="n">
-        <v>116550</v>
+        <v>160650</v>
       </c>
       <c r="T1000" s="4" t="s">
         <v>32</v>
@@ -64569,7 +64647,7 @@
         <v>963</v>
       </c>
       <c r="G1001" s="9" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H1001" s="11" t="n">
         <v>46280.868599537</v>
@@ -64627,7 +64705,7 @@
         <v>366</v>
       </c>
       <c r="G1002" s="4" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H1002" s="5" t="n">
         <v>46280</v>
@@ -64682,22 +64760,22 @@
         <v>24</v>
       </c>
       <c r="F1003" s="9" t="s">
+        <v>1976</v>
+      </c>
+      <c r="G1003" s="9" t="s">
         <v>1977</v>
-      </c>
-      <c r="G1003" s="9" t="s">
-        <v>1978</v>
       </c>
       <c r="H1003" s="11" t="n">
         <v>46281.483981481</v>
       </c>
       <c r="I1003" s="9" t="s">
+        <v>1978</v>
+      </c>
+      <c r="J1003" s="9" t="s">
+        <v>1978</v>
+      </c>
+      <c r="K1003" s="9" t="s">
         <v>1979</v>
-      </c>
-      <c r="J1003" s="9" t="s">
-        <v>1979</v>
-      </c>
-      <c r="K1003" s="9" t="s">
-        <v>1980</v>
       </c>
       <c r="L1003" s="10"/>
       <c r="M1003" s="10"/>
@@ -64743,7 +64821,7 @@
         <v>623</v>
       </c>
       <c r="G1004" s="4" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H1004" s="6" t="n">
         <v>46281.591608796</v>
@@ -64801,7 +64879,7 @@
         <v>1534</v>
       </c>
       <c r="G1005" s="9" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H1005" s="10" t="n">
         <v>46282</v>
@@ -64859,7 +64937,7 @@
         <v>1634</v>
       </c>
       <c r="G1006" s="4" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H1006" s="5" t="n">
         <v>46282</v>
@@ -64914,10 +64992,10 @@
         <v>24</v>
       </c>
       <c r="F1007" s="9" t="s">
+        <v>1983</v>
+      </c>
+      <c r="G1007" s="9" t="s">
         <v>1984</v>
-      </c>
-      <c r="G1007" s="9" t="s">
-        <v>1985</v>
       </c>
       <c r="H1007" s="11" t="n">
         <v>46282.690821759</v>
@@ -64972,22 +65050,22 @@
         <v>24</v>
       </c>
       <c r="F1008" s="4" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G1008" s="4" t="s">
         <v>1986</v>
-      </c>
-      <c r="G1008" s="4" t="s">
-        <v>1987</v>
       </c>
       <c r="H1008" s="6" t="n">
         <v>46283.62880787</v>
       </c>
       <c r="I1008" s="4" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="J1008" s="4" t="s">
+        <v>1987</v>
+      </c>
+      <c r="K1008" s="4" t="s">
         <v>1988</v>
-      </c>
-      <c r="K1008" s="4" t="s">
-        <v>1989</v>
       </c>
       <c r="L1008" s="5"/>
       <c r="M1008" s="5"/>
@@ -65033,7 +65111,7 @@
         <v>253</v>
       </c>
       <c r="G1009" s="9" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H1009" s="11" t="n">
         <v>46282.73755787</v>
@@ -65091,7 +65169,7 @@
         <v>1512</v>
       </c>
       <c r="G1010" s="4" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H1010" s="5" t="n">
         <v>46286</v>
@@ -65146,10 +65224,10 @@
         <v>24</v>
       </c>
       <c r="F1011" s="9" t="s">
+        <v>1991</v>
+      </c>
+      <c r="G1011" s="9" t="s">
         <v>1992</v>
-      </c>
-      <c r="G1011" s="9" t="s">
-        <v>1993</v>
       </c>
       <c r="H1011" s="10" t="n">
         <v>46286</v>
@@ -65207,7 +65285,7 @@
         <v>58</v>
       </c>
       <c r="G1012" s="4" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H1012" s="6" t="n">
         <v>46283.945405093</v>
@@ -65265,7 +65343,7 @@
         <v>152</v>
       </c>
       <c r="G1013" s="9" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H1013" s="11" t="n">
         <v>46283.947222222</v>
@@ -65323,7 +65401,7 @@
         <v>1627</v>
       </c>
       <c r="G1014" s="4" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H1014" s="6" t="n">
         <v>46286.665289352</v>
@@ -65381,7 +65459,7 @@
         <v>892</v>
       </c>
       <c r="G1015" s="9" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H1015" s="11" t="n">
         <v>46286.490671296</v>
@@ -65433,13 +65511,13 @@
         <v>23</v>
       </c>
       <c r="E1016" s="3" t="s">
-        <v>1998</v>
+        <v>24</v>
       </c>
       <c r="F1016" s="4" t="s">
         <v>1625</v>
       </c>
       <c r="G1016" s="4" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="H1016" s="6" t="n">
         <v>46286.636898148</v>
@@ -65471,7 +65549,7 @@
         <v>41328</v>
       </c>
       <c r="S1016" s="7" t="n">
-        <v>9840</v>
+        <v>41328</v>
       </c>
       <c r="T1016" s="4" t="s">
         <v>32</v>
@@ -65497,7 +65575,7 @@
         <v>704</v>
       </c>
       <c r="G1017" s="9" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="H1017" s="11" t="n">
         <v>46287.528784722</v>
@@ -65549,25 +65627,25 @@
         <v>23</v>
       </c>
       <c r="E1018" s="3" t="s">
+        <v>1999</v>
+      </c>
+      <c r="F1018" s="4" t="s">
+        <v>2000</v>
+      </c>
+      <c r="G1018" s="4" t="s">
         <v>2001</v>
-      </c>
-      <c r="F1018" s="4" t="s">
-        <v>2002</v>
-      </c>
-      <c r="G1018" s="4" t="s">
-        <v>2003</v>
       </c>
       <c r="H1018" s="6" t="n">
         <v>46287.685717593</v>
       </c>
       <c r="I1018" s="4" t="s">
+        <v>2000</v>
+      </c>
+      <c r="J1018" s="4" t="s">
         <v>2002</v>
       </c>
-      <c r="J1018" s="4" t="s">
-        <v>2004</v>
-      </c>
       <c r="K1018" s="4" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="L1018" s="5"/>
       <c r="M1018" s="5"/>
@@ -65613,7 +65691,7 @@
         <v>402</v>
       </c>
       <c r="G1019" s="9" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="H1019" s="11" t="n">
         <v>46287.90775463</v>
@@ -65671,7 +65749,7 @@
         <v>1234</v>
       </c>
       <c r="G1020" s="4" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="H1020" s="6" t="n">
         <v>46287.518842593</v>
@@ -65729,7 +65807,7 @@
         <v>347</v>
       </c>
       <c r="G1021" s="9" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="H1021" s="11" t="n">
         <v>46288.409328704</v>
@@ -65784,22 +65862,22 @@
         <v>24</v>
       </c>
       <c r="F1022" s="4" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="G1022" s="4" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="H1022" s="6" t="n">
         <v>46288.63568287</v>
       </c>
       <c r="I1022" s="4" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="J1022" s="4" t="s">
+        <v>1941</v>
+      </c>
+      <c r="K1022" s="4" t="s">
         <v>1942</v>
-      </c>
-      <c r="K1022" s="4" t="s">
-        <v>1943</v>
       </c>
       <c r="L1022" s="5"/>
       <c r="M1022" s="5"/>
@@ -65845,7 +65923,7 @@
         <v>351</v>
       </c>
       <c r="G1023" s="9" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="H1023" s="11" t="n">
         <v>46288.641435185</v>
@@ -65903,7 +65981,7 @@
         <v>944</v>
       </c>
       <c r="G1024" s="4" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="H1024" s="6" t="n">
         <v>46288.645289352</v>
@@ -65961,7 +66039,7 @@
         <v>366</v>
       </c>
       <c r="G1025" s="9" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="H1025" s="10" t="n">
         <v>46288</v>
@@ -66013,13 +66091,13 @@
         <v>23</v>
       </c>
       <c r="E1026" s="3" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="F1026" s="4" t="s">
         <v>1261</v>
       </c>
       <c r="G1026" s="4" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H1026" s="5" t="n">
         <v>46288</v>
@@ -66077,7 +66155,7 @@
         <v>1634</v>
       </c>
       <c r="G1027" s="9" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="H1027" s="10" t="n">
         <v>46289</v>
@@ -66132,10 +66210,10 @@
         <v>24</v>
       </c>
       <c r="F1028" s="4" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="G1028" s="4" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="H1028" s="6" t="n">
         <v>46288.697777778</v>
@@ -66193,7 +66271,7 @@
         <v>490</v>
       </c>
       <c r="G1029" s="9" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="H1029" s="11" t="n">
         <v>46288.708703704</v>
@@ -66251,7 +66329,7 @@
         <v>262</v>
       </c>
       <c r="G1030" s="4" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="H1030" s="6" t="n">
         <v>46288.727013889</v>
@@ -66309,7 +66387,7 @@
         <v>521</v>
       </c>
       <c r="G1031" s="9" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="H1031" s="11" t="n">
         <v>46293.413449074</v>
@@ -66367,7 +66445,7 @@
         <v>1779</v>
       </c>
       <c r="G1032" s="4" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="H1032" s="6" t="n">
         <v>46290.399768519</v>
@@ -66425,7 +66503,7 @@
         <v>75</v>
       </c>
       <c r="G1033" s="9" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H1033" s="11" t="n">
         <v>46293.420972222</v>
@@ -66483,7 +66561,7 @@
         <v>1542</v>
       </c>
       <c r="G1034" s="4" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="H1034" s="6" t="n">
         <v>46289.403217593</v>
@@ -66538,22 +66616,22 @@
         <v>24</v>
       </c>
       <c r="F1035" s="9" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="G1035" s="9" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H1035" s="11" t="n">
         <v>46289.956689815</v>
       </c>
       <c r="I1035" s="9" t="s">
+        <v>2022</v>
+      </c>
+      <c r="J1035" s="9" t="s">
         <v>2024</v>
       </c>
-      <c r="J1035" s="9" t="s">
-        <v>2026</v>
-      </c>
       <c r="K1035" s="9" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="L1035" s="10"/>
       <c r="M1035" s="10"/>
@@ -66599,7 +66677,7 @@
         <v>801</v>
       </c>
       <c r="G1036" s="4" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="H1036" s="6" t="n">
         <v>46293.739594907</v>
@@ -66654,22 +66732,22 @@
         <v>24</v>
       </c>
       <c r="F1037" s="9" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="G1037" s="9" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="H1037" s="11" t="n">
         <v>46293.720231481</v>
       </c>
       <c r="I1037" s="9" t="s">
+        <v>2022</v>
+      </c>
+      <c r="J1037" s="9" t="s">
         <v>2024</v>
       </c>
-      <c r="J1037" s="9" t="s">
-        <v>2026</v>
-      </c>
       <c r="K1037" s="9" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="L1037" s="10"/>
       <c r="M1037" s="10"/>
@@ -66715,7 +66793,7 @@
         <v>1268</v>
       </c>
       <c r="G1038" s="4" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="H1038" s="6" t="n">
         <v>46294.490601852</v>
@@ -66770,10 +66848,10 @@
         <v>24</v>
       </c>
       <c r="F1039" s="9" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="G1039" s="9" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="H1039" s="10" t="n">
         <v>46294</v>
@@ -66831,7 +66909,7 @@
         <v>1512</v>
       </c>
       <c r="G1040" s="4" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="H1040" s="5" t="n">
         <v>46294</v>
@@ -66889,7 +66967,7 @@
         <v>967</v>
       </c>
       <c r="G1041" s="9" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="H1041" s="10" t="n">
         <v>46290</v>
@@ -66947,7 +67025,7 @@
         <v>230</v>
       </c>
       <c r="G1042" s="4" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="H1042" s="6" t="n">
         <v>46294.604212963</v>
@@ -67005,7 +67083,7 @@
         <v>230</v>
       </c>
       <c r="G1043" s="9" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="H1043" s="11" t="n">
         <v>46294.585011574</v>
@@ -67063,7 +67141,7 @@
         <v>324</v>
       </c>
       <c r="G1044" s="4" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="H1044" s="6" t="n">
         <v>46294.608877315</v>
@@ -67121,7 +67199,7 @@
         <v>1645</v>
       </c>
       <c r="G1045" s="9" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="H1045" s="11" t="n">
         <v>46294.613831019</v>
@@ -67179,7 +67257,7 @@
         <v>461</v>
       </c>
       <c r="G1046" s="4" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="H1046" s="6" t="n">
         <v>46294.707199074</v>
@@ -67231,13 +67309,13 @@
         <v>23</v>
       </c>
       <c r="E1047" s="8" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="F1047" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G1047" s="9" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="H1047" s="11" t="n">
         <v>46294.757743056</v>
@@ -67289,25 +67367,25 @@
         <v>23</v>
       </c>
       <c r="E1048" s="3" t="s">
+        <v>2040</v>
+      </c>
+      <c r="F1048" s="4" t="s">
+        <v>2041</v>
+      </c>
+      <c r="G1048" s="4" t="s">
         <v>2042</v>
-      </c>
-      <c r="F1048" s="4" t="s">
-        <v>2043</v>
-      </c>
-      <c r="G1048" s="4" t="s">
-        <v>2044</v>
       </c>
       <c r="H1048" s="6" t="n">
         <v>46295.464884259</v>
       </c>
       <c r="I1048" s="4" t="s">
+        <v>2041</v>
+      </c>
+      <c r="J1048" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="J1048" s="4" t="s">
-        <v>2045</v>
-      </c>
       <c r="K1048" s="4" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="L1048" s="5"/>
       <c r="M1048" s="5"/>
@@ -67350,10 +67428,10 @@
         <v>24</v>
       </c>
       <c r="F1049" s="9" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="G1049" s="9" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="H1049" s="11" t="n">
         <v>46294.660474537</v>
@@ -67411,7 +67489,7 @@
         <v>1268</v>
       </c>
       <c r="G1050" s="4" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="H1050" s="6" t="n">
         <v>46295.603634259</v>
@@ -67469,7 +67547,7 @@
         <v>904</v>
       </c>
       <c r="G1051" s="9" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="H1051" s="11" t="n">
         <v>46295.647060185</v>
@@ -67524,10 +67602,10 @@
         <v>24</v>
       </c>
       <c r="F1052" s="4" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="G1052" s="4" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="H1052" s="5" t="n">
         <v>46296</v>
@@ -67579,13 +67657,13 @@
         <v>23</v>
       </c>
       <c r="E1053" s="8" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="F1053" s="9" t="s">
         <v>1261</v>
       </c>
       <c r="G1053" s="9" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="H1053" s="10" t="n">
         <v>46295</v>
@@ -67643,7 +67721,7 @@
         <v>1017</v>
       </c>
       <c r="G1054" s="4" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="H1054" s="5" t="n">
         <v>46297</v>
@@ -67701,7 +67779,7 @@
         <v>262</v>
       </c>
       <c r="G1055" s="9" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="H1055" s="11" t="n">
         <v>46296.754675926</v>
@@ -67759,7 +67837,7 @@
         <v>194</v>
       </c>
       <c r="G1056" s="4" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="H1056" s="5" t="n">
         <v>46296</v>
@@ -67811,13 +67889,13 @@
         <v>23</v>
       </c>
       <c r="E1057" s="8" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="F1057" s="9" t="s">
         <v>453</v>
       </c>
       <c r="G1057" s="9" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="H1057" s="11" t="n">
         <v>46300.877766204</v>
@@ -67875,7 +67953,7 @@
         <v>436</v>
       </c>
       <c r="G1058" s="4" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="H1058" s="6" t="n">
         <v>46300.582071759</v>
@@ -67933,7 +68011,7 @@
         <v>698</v>
       </c>
       <c r="G1059" s="9" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="H1059" s="11" t="n">
         <v>46300.587326389</v>
@@ -67991,7 +68069,7 @@
         <v>981</v>
       </c>
       <c r="G1060" s="4" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="H1060" s="5" t="n">
         <v>46301</v>
@@ -68046,10 +68124,10 @@
         <v>24</v>
       </c>
       <c r="F1061" s="9" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="G1061" s="9" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="H1061" s="11" t="n">
         <v>46301.750358796</v>
@@ -68107,7 +68185,7 @@
         <v>698</v>
       </c>
       <c r="G1062" s="4" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="H1062" s="6" t="n">
         <v>46301.972430556</v>
@@ -68165,7 +68243,7 @@
         <v>953</v>
       </c>
       <c r="G1063" s="9" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="H1063" s="11" t="n">
         <v>46302.362025463</v>
@@ -68223,7 +68301,7 @@
         <v>765</v>
       </c>
       <c r="G1064" s="4" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="H1064" s="5" t="n">
         <v>46302</v>
@@ -68281,7 +68359,7 @@
         <v>332</v>
       </c>
       <c r="G1065" s="9" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="H1065" s="11" t="n">
         <v>46303.385266204</v>
@@ -68339,7 +68417,7 @@
         <v>75</v>
       </c>
       <c r="G1066" s="4" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="H1066" s="6" t="n">
         <v>46302.730069444</v>
@@ -68394,10 +68472,10 @@
         <v>24</v>
       </c>
       <c r="F1067" s="9" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="G1067" s="9" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="H1067" s="10" t="n">
         <v>46302</v>
@@ -68455,7 +68533,7 @@
         <v>967</v>
       </c>
       <c r="G1068" s="4" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="H1068" s="5" t="n">
         <v>46304</v>
@@ -68513,7 +68591,7 @@
         <v>295</v>
       </c>
       <c r="G1069" s="9" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="H1069" s="11" t="n">
         <v>46304.355324074</v>
@@ -68571,7 +68649,7 @@
         <v>1827</v>
       </c>
       <c r="G1070" s="4" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="H1070" s="6" t="n">
         <v>46304.483865741</v>
@@ -68623,13 +68701,13 @@
         <v>23</v>
       </c>
       <c r="E1071" s="8" t="s">
-        <v>2074</v>
+        <v>24</v>
       </c>
       <c r="F1071" s="9" t="s">
         <v>1634</v>
       </c>
       <c r="G1071" s="9" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
       <c r="H1071" s="10" t="n">
         <v>46308</v>
@@ -68646,7 +68724,7 @@
       <c r="L1071" s="10"/>
       <c r="M1071" s="10"/>
       <c r="N1071" s="9" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O1071" s="11" t="n">
         <v>46308.671253704</v>
@@ -68661,7 +68739,7 @@
         <v>19055.26</v>
       </c>
       <c r="S1071" s="12" t="n">
-        <v>14366.98</v>
+        <v>19055.26</v>
       </c>
       <c r="T1071" s="9" t="s">
         <v>32</v>
@@ -68687,7 +68765,7 @@
         <v>276</v>
       </c>
       <c r="G1072" s="4" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
       <c r="H1072" s="6" t="n">
         <v>46308.484027778</v>
@@ -68745,7 +68823,7 @@
         <v>276</v>
       </c>
       <c r="G1073" s="9" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
       <c r="H1073" s="11" t="n">
         <v>46308.475208333</v>
@@ -68803,7 +68881,7 @@
         <v>366</v>
       </c>
       <c r="G1074" s="4" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="H1074" s="5" t="n">
         <v>46308</v>
@@ -68861,7 +68939,7 @@
         <v>837</v>
       </c>
       <c r="G1075" s="9" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
       <c r="H1075" s="11" t="n">
         <v>46308.757569444</v>
@@ -68919,7 +68997,7 @@
         <v>191</v>
       </c>
       <c r="G1076" s="4" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
       <c r="H1076" s="6" t="n">
         <v>46308.7390625</v>
@@ -68977,7 +69055,7 @@
         <v>1073</v>
       </c>
       <c r="G1077" s="9" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="H1077" s="11" t="n">
         <v>46308.730625</v>
@@ -69029,30 +69107,30 @@
         <v>23</v>
       </c>
       <c r="E1078" s="3" t="s">
-        <v>2082</v>
+        <v>24</v>
       </c>
       <c r="F1078" s="4" t="s">
-        <v>2083</v>
+        <v>2079</v>
       </c>
       <c r="G1078" s="4" t="s">
-        <v>2084</v>
+        <v>2080</v>
       </c>
       <c r="H1078" s="5" t="n">
         <v>46309</v>
       </c>
       <c r="I1078" s="4" t="s">
-        <v>2083</v>
+        <v>2079</v>
       </c>
       <c r="J1078" s="4" t="s">
-        <v>2085</v>
+        <v>2081</v>
       </c>
       <c r="K1078" s="4" t="s">
-        <v>2086</v>
+        <v>2082</v>
       </c>
       <c r="L1078" s="5"/>
       <c r="M1078" s="5"/>
       <c r="N1078" s="4" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O1078" s="6" t="n">
         <v>46310.579741169</v>
@@ -69067,7 +69145,7 @@
         <v>3915.34</v>
       </c>
       <c r="S1078" s="7" t="n">
-        <v>2336.04</v>
+        <v>3915.34</v>
       </c>
       <c r="T1078" s="4" t="s">
         <v>1830</v>
@@ -69093,7 +69171,7 @@
         <v>38</v>
       </c>
       <c r="G1079" s="9" t="s">
-        <v>2087</v>
+        <v>2083</v>
       </c>
       <c r="H1079" s="11" t="n">
         <v>46310.747743056</v>
@@ -69110,7 +69188,7 @@
       <c r="L1079" s="10"/>
       <c r="M1079" s="10"/>
       <c r="N1079" s="9" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
       <c r="O1079" s="11" t="n">
         <v>46315.400142743</v>
@@ -69145,13 +69223,13 @@
         <v>23</v>
       </c>
       <c r="E1080" s="3" t="s">
-        <v>1216</v>
+        <v>24</v>
       </c>
       <c r="F1080" s="4" t="s">
         <v>482</v>
       </c>
       <c r="G1080" s="4" t="s">
-        <v>2089</v>
+        <v>2085</v>
       </c>
       <c r="H1080" s="6" t="n">
         <v>46310.770381944</v>
@@ -69168,7 +69246,7 @@
       <c r="L1080" s="5"/>
       <c r="M1080" s="5"/>
       <c r="N1080" s="4" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O1080" s="6" t="n">
         <v>46315.400313576</v>
@@ -69183,7 +69261,7 @@
         <v>28988.52</v>
       </c>
       <c r="S1080" s="7" t="n">
-        <v>20985.12</v>
+        <v>28988.52</v>
       </c>
       <c r="T1080" s="4" t="s">
         <v>32</v>
@@ -69209,7 +69287,7 @@
         <v>1389</v>
       </c>
       <c r="G1081" s="9" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
       <c r="H1081" s="11" t="n">
         <v>46310.691099537</v>
@@ -69267,7 +69345,7 @@
         <v>402</v>
       </c>
       <c r="G1082" s="4" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
       <c r="H1082" s="6" t="n">
         <v>46310.736655093</v>
@@ -69325,7 +69403,7 @@
         <v>490</v>
       </c>
       <c r="G1083" s="9" t="s">
-        <v>2092</v>
+        <v>2088</v>
       </c>
       <c r="H1083" s="11" t="n">
         <v>46310.60712963</v>
@@ -69383,7 +69461,7 @@
         <v>58</v>
       </c>
       <c r="G1084" s="4" t="s">
-        <v>2093</v>
+        <v>2089</v>
       </c>
       <c r="H1084" s="6" t="n">
         <v>46311.671215278</v>
@@ -69441,7 +69519,7 @@
         <v>1058</v>
       </c>
       <c r="G1085" s="9" t="s">
-        <v>2094</v>
+        <v>2090</v>
       </c>
       <c r="H1085" s="11" t="n">
         <v>46314.461296296</v>
@@ -69458,7 +69536,7 @@
       <c r="L1085" s="10"/>
       <c r="M1085" s="10"/>
       <c r="N1085" s="9" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
       <c r="O1085" s="11" t="n">
         <v>46315.681983368</v>
@@ -69493,13 +69571,13 @@
         <v>23</v>
       </c>
       <c r="E1086" s="3" t="s">
-        <v>285</v>
+        <v>2091</v>
       </c>
       <c r="F1086" s="4" t="s">
         <v>328</v>
       </c>
       <c r="G1086" s="4" t="s">
-        <v>2095</v>
+        <v>2092</v>
       </c>
       <c r="H1086" s="6" t="n">
         <v>46314.658842593</v>
@@ -69516,7 +69594,7 @@
       <c r="L1086" s="5"/>
       <c r="M1086" s="5"/>
       <c r="N1086" s="4" t="s">
-        <v>2088</v>
+        <v>1285</v>
       </c>
       <c r="O1086" s="6" t="n">
         <v>46315.68221875</v>
@@ -69531,7 +69609,7 @@
         <v>25925.7</v>
       </c>
       <c r="S1086" s="7" t="n">
-        <v>0</v>
+        <v>18406.5</v>
       </c>
       <c r="T1086" s="4" t="s">
         <v>32</v>
@@ -69551,13 +69629,13 @@
         <v>23</v>
       </c>
       <c r="E1087" s="8" t="s">
-        <v>285</v>
+        <v>2093</v>
       </c>
       <c r="F1087" s="9" t="s">
         <v>521</v>
       </c>
       <c r="G1087" s="9" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="H1087" s="11" t="n">
         <v>46314.761377315</v>
@@ -69574,7 +69652,7 @@
       <c r="L1087" s="10"/>
       <c r="M1087" s="10"/>
       <c r="N1087" s="9" t="s">
-        <v>2088</v>
+        <v>1285</v>
       </c>
       <c r="O1087" s="11" t="n">
         <v>46315.682364005</v>
@@ -69589,7 +69667,7 @@
         <v>18560.4</v>
       </c>
       <c r="S1087" s="12" t="n">
-        <v>0</v>
+        <v>6720</v>
       </c>
       <c r="T1087" s="9" t="s">
         <v>32</v>
@@ -69597,35 +69675,1079 @@
       <c r="U1087" s="9"/>
       <c r="V1087" s="9"/>
     </row>
-    <row r="1088" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A1088" s="13" t="n">
-        <v>1086</v>
-      </c>
-      <c r="B1088" s="14"/>
-      <c r="C1088" s="14"/>
-      <c r="D1088" s="14"/>
-      <c r="E1088" s="14"/>
-      <c r="F1088" s="14"/>
-      <c r="G1088" s="14"/>
-      <c r="H1088" s="14"/>
-      <c r="I1088" s="14"/>
-      <c r="J1088" s="14"/>
-      <c r="K1088" s="14"/>
-      <c r="L1088" s="14"/>
-      <c r="M1088" s="14"/>
-      <c r="N1088" s="14"/>
-      <c r="O1088" s="14"/>
-      <c r="P1088" s="14"/>
-      <c r="Q1088" s="14"/>
-      <c r="R1088" s="15" t="n">
-        <v>63551053.9206</v>
-      </c>
-      <c r="S1088" s="15" t="n">
-        <v>61077472.6606</v>
-      </c>
-      <c r="T1088" s="14"/>
-      <c r="U1088" s="14"/>
-      <c r="V1088" s="16"/>
+    <row r="1088" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1088" s="3" t="n">
+        <v>1158</v>
+      </c>
+      <c r="B1088" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1088" s="4"/>
+      <c r="D1088" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1088" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1088" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G1088" s="4" t="s">
+        <v>2095</v>
+      </c>
+      <c r="H1088" s="6" t="n">
+        <v>46315.573032407</v>
+      </c>
+      <c r="I1088" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="J1088" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="K1088" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="L1088" s="5"/>
+      <c r="M1088" s="5"/>
+      <c r="N1088" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1088" s="6" t="n">
+        <v>46316.48828125</v>
+      </c>
+      <c r="P1088" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1088" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1088" s="7" t="n">
+        <v>8400</v>
+      </c>
+      <c r="S1088" s="7" t="n">
+        <v>8400</v>
+      </c>
+      <c r="T1088" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1088" s="4"/>
+      <c r="V1088" s="4"/>
+    </row>
+    <row r="1089" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1089" s="8" t="n">
+        <v>1159</v>
+      </c>
+      <c r="B1089" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1089" s="9"/>
+      <c r="D1089" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1089" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1089" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="G1089" s="9" t="s">
+        <v>2096</v>
+      </c>
+      <c r="H1089" s="11" t="n">
+        <v>46315.867488426</v>
+      </c>
+      <c r="I1089" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="J1089" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="K1089" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="L1089" s="10"/>
+      <c r="M1089" s="10"/>
+      <c r="N1089" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1089" s="11" t="n">
+        <v>46316.488401586</v>
+      </c>
+      <c r="P1089" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1089" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="R1089" s="12" t="n">
+        <v>32800</v>
+      </c>
+      <c r="S1089" s="12" t="n">
+        <v>32800</v>
+      </c>
+      <c r="T1089" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1089" s="9"/>
+      <c r="V1089" s="9"/>
+    </row>
+    <row r="1090" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1090" s="3" t="n">
+        <v>1160</v>
+      </c>
+      <c r="B1090" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1090" s="4"/>
+      <c r="D1090" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1090" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1090" s="4" t="s">
+        <v>1634</v>
+      </c>
+      <c r="G1090" s="4" t="s">
+        <v>2097</v>
+      </c>
+      <c r="H1090" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="I1090" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1090" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="K1090" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="L1090" s="5"/>
+      <c r="M1090" s="5"/>
+      <c r="N1090" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1090" s="6" t="n">
+        <v>46316.63331331</v>
+      </c>
+      <c r="P1090" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1090" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="R1090" s="7" t="n">
+        <v>16064</v>
+      </c>
+      <c r="S1090" s="7" t="n">
+        <v>16064</v>
+      </c>
+      <c r="T1090" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1090" s="4"/>
+      <c r="V1090" s="4"/>
+    </row>
+    <row r="1091" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1091" s="8" t="n">
+        <v>1161</v>
+      </c>
+      <c r="B1091" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1091" s="9"/>
+      <c r="D1091" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1091" s="8" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F1091" s="9" t="s">
+        <v>2099</v>
+      </c>
+      <c r="G1091" s="9" t="s">
+        <v>2100</v>
+      </c>
+      <c r="H1091" s="11" t="n">
+        <v>46316.363946759</v>
+      </c>
+      <c r="I1091" s="9" t="s">
+        <v>1888</v>
+      </c>
+      <c r="J1091" s="9" t="s">
+        <v>1889</v>
+      </c>
+      <c r="K1091" s="9" t="s">
+        <v>1890</v>
+      </c>
+      <c r="L1091" s="10"/>
+      <c r="M1091" s="10"/>
+      <c r="N1091" s="9" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O1091" s="11" t="n">
+        <v>46317.347029479</v>
+      </c>
+      <c r="P1091" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1091" s="9" t="s">
+        <v>1876</v>
+      </c>
+      <c r="R1091" s="12" t="n">
+        <v>76614.64</v>
+      </c>
+      <c r="S1091" s="12" t="n">
+        <v>31720.28</v>
+      </c>
+      <c r="T1091" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="U1091" s="9"/>
+      <c r="V1091" s="9"/>
+    </row>
+    <row r="1092" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1092" s="3" t="n">
+        <v>1162</v>
+      </c>
+      <c r="B1092" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1092" s="4"/>
+      <c r="D1092" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1092" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1092" s="4" t="s">
+        <v>1512</v>
+      </c>
+      <c r="G1092" s="4" t="s">
+        <v>2101</v>
+      </c>
+      <c r="H1092" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="I1092" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="J1092" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="K1092" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="L1092" s="5"/>
+      <c r="M1092" s="5"/>
+      <c r="N1092" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1092" s="6" t="n">
+        <v>46317.347515081</v>
+      </c>
+      <c r="P1092" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1092" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="R1092" s="7" t="n">
+        <v>5508</v>
+      </c>
+      <c r="S1092" s="7" t="n">
+        <v>5508</v>
+      </c>
+      <c r="T1092" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1092" s="4"/>
+      <c r="V1092" s="4"/>
+    </row>
+    <row r="1093" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1093" s="8" t="n">
+        <v>1163</v>
+      </c>
+      <c r="B1093" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1093" s="9"/>
+      <c r="D1093" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1093" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1093" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="G1093" s="9" t="s">
+        <v>2102</v>
+      </c>
+      <c r="H1093" s="11" t="n">
+        <v>46316.659548611</v>
+      </c>
+      <c r="I1093" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1093" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="K1093" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="L1093" s="10"/>
+      <c r="M1093" s="10"/>
+      <c r="N1093" s="9" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O1093" s="11" t="n">
+        <v>46317.392973692</v>
+      </c>
+      <c r="P1093" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1093" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1093" s="12" t="n">
+        <v>31410</v>
+      </c>
+      <c r="S1093" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1093" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1093" s="9"/>
+      <c r="V1093" s="9"/>
+    </row>
+    <row r="1094" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1094" s="3" t="n">
+        <v>1164</v>
+      </c>
+      <c r="B1094" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1094" s="4"/>
+      <c r="D1094" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1094" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1094" s="4" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G1094" s="4" t="s">
+        <v>2103</v>
+      </c>
+      <c r="H1094" s="6" t="n">
+        <v>46317.534155093</v>
+      </c>
+      <c r="I1094" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J1094" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="K1094" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="L1094" s="5"/>
+      <c r="M1094" s="5"/>
+      <c r="N1094" s="4" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O1094" s="6" t="n">
+        <v>46317.688584109</v>
+      </c>
+      <c r="P1094" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1094" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1094" s="7" t="n">
+        <v>69093.25</v>
+      </c>
+      <c r="S1094" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1094" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1094" s="4"/>
+      <c r="V1094" s="4"/>
+    </row>
+    <row r="1095" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1095" s="8" t="n">
+        <v>1165</v>
+      </c>
+      <c r="B1095" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1095" s="9"/>
+      <c r="D1095" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1095" s="8" t="s">
+        <v>2091</v>
+      </c>
+      <c r="F1095" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="G1095" s="9" t="s">
+        <v>2104</v>
+      </c>
+      <c r="H1095" s="11" t="n">
+        <v>46317.685185185</v>
+      </c>
+      <c r="I1095" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1095" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1095" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1095" s="10"/>
+      <c r="M1095" s="10"/>
+      <c r="N1095" s="9" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O1095" s="11" t="n">
+        <v>46318.324940127</v>
+      </c>
+      <c r="P1095" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1095" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1095" s="12" t="n">
+        <v>24480</v>
+      </c>
+      <c r="S1095" s="12" t="n">
+        <v>17280</v>
+      </c>
+      <c r="T1095" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1095" s="9"/>
+      <c r="V1095" s="9"/>
+    </row>
+    <row r="1096" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1096" s="3" t="n">
+        <v>1166</v>
+      </c>
+      <c r="B1096" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1096" s="4"/>
+      <c r="D1096" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1096" s="3" t="s">
+        <v>2105</v>
+      </c>
+      <c r="F1096" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="G1096" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="H1096" s="6" t="n">
+        <v>46317.686666667</v>
+      </c>
+      <c r="I1096" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1096" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1096" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1096" s="5"/>
+      <c r="M1096" s="5"/>
+      <c r="N1096" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O1096" s="6" t="n">
+        <v>46318.325082095</v>
+      </c>
+      <c r="P1096" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1096" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1096" s="7" t="n">
+        <v>2160</v>
+      </c>
+      <c r="S1096" s="7" t="n">
+        <v>1440</v>
+      </c>
+      <c r="T1096" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1096" s="4"/>
+      <c r="V1096" s="4"/>
+    </row>
+    <row r="1097" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1097" s="8" t="n">
+        <v>1167</v>
+      </c>
+      <c r="B1097" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1097" s="9"/>
+      <c r="D1097" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1097" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1097" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1097" s="9" t="s">
+        <v>2107</v>
+      </c>
+      <c r="H1097" s="11" t="n">
+        <v>46318.373217593</v>
+      </c>
+      <c r="I1097" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1097" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1097" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1097" s="10"/>
+      <c r="M1097" s="10"/>
+      <c r="N1097" s="9" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O1097" s="11" t="n">
+        <v>46318.594988542</v>
+      </c>
+      <c r="P1097" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1097" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1097" s="12" t="n">
+        <v>8190</v>
+      </c>
+      <c r="S1097" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1097" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1097" s="9"/>
+      <c r="V1097" s="9"/>
+    </row>
+    <row r="1098" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1098" s="3" t="n">
+        <v>1168</v>
+      </c>
+      <c r="B1098" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1098" s="4"/>
+      <c r="D1098" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1098" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1098" s="4" t="s">
+        <v>1625</v>
+      </c>
+      <c r="G1098" s="4" t="s">
+        <v>2108</v>
+      </c>
+      <c r="H1098" s="6" t="n">
+        <v>46318.378171296</v>
+      </c>
+      <c r="I1098" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="J1098" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="K1098" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="L1098" s="5"/>
+      <c r="M1098" s="5"/>
+      <c r="N1098" s="4" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O1098" s="6" t="n">
+        <v>46318.595172303</v>
+      </c>
+      <c r="P1098" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1098" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1098" s="7" t="n">
+        <v>41328</v>
+      </c>
+      <c r="S1098" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1098" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1098" s="4"/>
+      <c r="V1098" s="4"/>
+    </row>
+    <row r="1099" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1099" s="8" t="n">
+        <v>1169</v>
+      </c>
+      <c r="B1099" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1099" s="9"/>
+      <c r="D1099" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1099" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1099" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="G1099" s="9" t="s">
+        <v>2109</v>
+      </c>
+      <c r="H1099" s="11" t="n">
+        <v>46304.397569444</v>
+      </c>
+      <c r="I1099" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="J1099" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="K1099" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="L1099" s="10"/>
+      <c r="M1099" s="10"/>
+      <c r="N1099" s="9" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O1099" s="11" t="n">
+        <v>46318.595291319</v>
+      </c>
+      <c r="P1099" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1099" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1099" s="12" t="n">
+        <v>13668.48</v>
+      </c>
+      <c r="S1099" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1099" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1099" s="9"/>
+      <c r="V1099" s="9"/>
+    </row>
+    <row r="1100" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1100" s="3" t="n">
+        <v>1170</v>
+      </c>
+      <c r="B1100" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1100" s="4"/>
+      <c r="D1100" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1100" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1100" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G1100" s="4" t="s">
+        <v>2110</v>
+      </c>
+      <c r="H1100" s="6" t="n">
+        <v>46304.402835648</v>
+      </c>
+      <c r="I1100" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1100" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1100" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L1100" s="5"/>
+      <c r="M1100" s="5"/>
+      <c r="N1100" s="4" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O1100" s="6" t="n">
+        <v>46318.595518171</v>
+      </c>
+      <c r="P1100" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1100" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1100" s="7" t="n">
+        <v>20502.72</v>
+      </c>
+      <c r="S1100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1100" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1100" s="4"/>
+      <c r="V1100" s="4"/>
+    </row>
+    <row r="1101" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1101" s="8" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B1101" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1101" s="9"/>
+      <c r="D1101" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1101" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1101" s="9" t="s">
+        <v>2111</v>
+      </c>
+      <c r="G1101" s="9" t="s">
+        <v>2112</v>
+      </c>
+      <c r="H1101" s="11" t="n">
+        <v>46304.405694444</v>
+      </c>
+      <c r="I1101" s="9" t="s">
+        <v>2111</v>
+      </c>
+      <c r="J1101" s="9" t="s">
+        <v>2113</v>
+      </c>
+      <c r="K1101" s="9" t="s">
+        <v>2114</v>
+      </c>
+      <c r="L1101" s="10"/>
+      <c r="M1101" s="10"/>
+      <c r="N1101" s="9" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O1101" s="11" t="n">
+        <v>46318.59570228</v>
+      </c>
+      <c r="P1101" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1101" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1101" s="12" t="n">
+        <v>6834.24</v>
+      </c>
+      <c r="S1101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1101" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1101" s="9"/>
+      <c r="V1101" s="9"/>
+    </row>
+    <row r="1102" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1102" s="3" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B1102" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1102" s="4"/>
+      <c r="D1102" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1102" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1102" s="4" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G1102" s="4" t="s">
+        <v>2115</v>
+      </c>
+      <c r="H1102" s="6" t="n">
+        <v>46317.755613426</v>
+      </c>
+      <c r="I1102" s="4" t="s">
+        <v>1234</v>
+      </c>
+      <c r="J1102" s="4" t="s">
+        <v>1235</v>
+      </c>
+      <c r="K1102" s="4" t="s">
+        <v>1236</v>
+      </c>
+      <c r="L1102" s="5"/>
+      <c r="M1102" s="5"/>
+      <c r="N1102" s="4" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O1102" s="6" t="n">
+        <v>46318.595873993</v>
+      </c>
+      <c r="P1102" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1102" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="R1102" s="7" t="n">
+        <v>53434.08</v>
+      </c>
+      <c r="S1102" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1102" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="U1102" s="4"/>
+      <c r="V1102" s="4"/>
+    </row>
+    <row r="1103" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1103" s="8" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B1103" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1103" s="9"/>
+      <c r="D1103" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1103" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1103" s="9" t="s">
+        <v>2116</v>
+      </c>
+      <c r="G1103" s="9" t="s">
+        <v>2117</v>
+      </c>
+      <c r="H1103" s="11" t="n">
+        <v>46317.680625</v>
+      </c>
+      <c r="I1103" s="9" t="s">
+        <v>2118</v>
+      </c>
+      <c r="J1103" s="9" t="s">
+        <v>2119</v>
+      </c>
+      <c r="K1103" s="9" t="s">
+        <v>2120</v>
+      </c>
+      <c r="L1103" s="10"/>
+      <c r="M1103" s="10"/>
+      <c r="N1103" s="9" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O1103" s="11" t="n">
+        <v>46318.596058681</v>
+      </c>
+      <c r="P1103" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1103" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1103" s="12" t="n">
+        <v>2560.2</v>
+      </c>
+      <c r="S1103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1103" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1103" s="9"/>
+      <c r="V1103" s="9"/>
+    </row>
+    <row r="1104" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1104" s="3" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B1104" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1104" s="4"/>
+      <c r="D1104" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1104" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1104" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G1104" s="4" t="s">
+        <v>2121</v>
+      </c>
+      <c r="H1104" s="6" t="n">
+        <v>46317.683101852</v>
+      </c>
+      <c r="I1104" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1104" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="K1104" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="L1104" s="5"/>
+      <c r="M1104" s="5"/>
+      <c r="N1104" s="4" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O1104" s="6" t="n">
+        <v>46318.596295104</v>
+      </c>
+      <c r="P1104" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1104" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1104" s="7" t="n">
+        <v>19500</v>
+      </c>
+      <c r="S1104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1104" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1104" s="4"/>
+      <c r="V1104" s="4"/>
+    </row>
+    <row r="1105" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1105" s="8" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B1105" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1105" s="9"/>
+      <c r="D1105" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1105" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1105" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1105" s="9" t="s">
+        <v>2122</v>
+      </c>
+      <c r="H1105" s="11" t="n">
+        <v>46318.486377315</v>
+      </c>
+      <c r="I1105" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1105" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1105" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1105" s="10"/>
+      <c r="M1105" s="10"/>
+      <c r="N1105" s="9" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O1105" s="11" t="n">
+        <v>46318.602708993</v>
+      </c>
+      <c r="P1105" s="9" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1105" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1105" s="12" t="n">
+        <v>42336</v>
+      </c>
+      <c r="S1105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1105" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1105" s="9"/>
+      <c r="V1105" s="9"/>
+    </row>
+    <row r="1106" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A1106" s="13" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B1106" s="14"/>
+      <c r="C1106" s="14"/>
+      <c r="D1106" s="14"/>
+      <c r="E1106" s="14"/>
+      <c r="F1106" s="14"/>
+      <c r="G1106" s="14"/>
+      <c r="H1106" s="14"/>
+      <c r="I1106" s="14"/>
+      <c r="J1106" s="14"/>
+      <c r="K1106" s="14"/>
+      <c r="L1106" s="14"/>
+      <c r="M1106" s="14"/>
+      <c r="N1106" s="14"/>
+      <c r="O1106" s="14"/>
+      <c r="P1106" s="14"/>
+      <c r="Q1106" s="14"/>
+      <c r="R1106" s="15" t="n">
+        <v>64025937.5306</v>
+      </c>
+      <c r="S1106" s="15" t="n">
+        <v>61310710.4206</v>
+      </c>
+      <c r="T1106" s="14"/>
+      <c r="U1106" s="14"/>
+      <c r="V1106" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="2123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="2126">
   <si>
     <t>ID</t>
   </si>
@@ -5730,7 +5730,7 @@
     <t>1183</t>
   </si>
   <si>
-    <t>48 %</t>
+    <t>58 %</t>
   </si>
   <si>
     <t>1184</t>
@@ -5931,7 +5931,7 @@
     <t>1233</t>
   </si>
   <si>
-    <t>18 %</t>
+    <t>22 %</t>
   </si>
   <si>
     <t>1234</t>
@@ -6012,7 +6012,7 @@
     <t>1251</t>
   </si>
   <si>
-    <t>7 %</t>
+    <t>11 %</t>
   </si>
   <si>
     <t>REC HOSPITALAR</t>
@@ -6285,6 +6285,9 @@
     <t>1322</t>
   </si>
   <si>
+    <t>20 %</t>
+  </si>
+  <si>
     <t>1323</t>
   </si>
   <si>
@@ -6294,7 +6297,7 @@
     <t>1324</t>
   </si>
   <si>
-    <t>36 %</t>
+    <t>79 %</t>
   </si>
   <si>
     <t>1325</t>
@@ -6321,6 +6324,9 @@
     <t>1330</t>
   </si>
   <si>
+    <t>62 %</t>
+  </si>
+  <si>
     <t>1331</t>
   </si>
   <si>
@@ -6330,9 +6336,6 @@
     <t>1333</t>
   </si>
   <si>
-    <t>67 %</t>
-  </si>
-  <si>
     <t>1334</t>
   </si>
   <si>
@@ -6372,7 +6375,7 @@
     <t>SAFETY&amp;HEALTH SERVICOS</t>
   </si>
   <si>
-    <t>SAFETY E HEALTH SERVICOS E ALUGUEL DE EQUIPAMENTOS</t>
+    <t>SAFETY E HEALTH SERV E ALUG DE EQUIP HOSP LTDA</t>
   </si>
   <si>
     <t>36.977.902/0001-20</t>
@@ -6381,7 +6384,13 @@
     <t>1342</t>
   </si>
   <si>
+    <t>40 %</t>
+  </si>
+  <si>
     <t>1343</t>
+  </si>
+  <si>
+    <t>1344</t>
   </si>
 </sst>
 </file>
@@ -6575,7 +6584,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V1106"/>
+  <dimension ref="A1:V1107"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
     <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
@@ -61721,7 +61730,7 @@
         <v>63150.72</v>
       </c>
       <c r="S950" s="7" t="n">
-        <v>30302.52</v>
+        <v>36539.52</v>
       </c>
       <c r="T950" s="4" t="s">
         <v>32</v>
@@ -64621,7 +64630,7 @@
         <v>885906</v>
       </c>
       <c r="S1000" s="7" t="n">
-        <v>160650</v>
+        <v>192150</v>
       </c>
       <c r="T1000" s="4" t="s">
         <v>32</v>
@@ -65665,7 +65674,7 @@
         <v>870435</v>
       </c>
       <c r="S1018" s="7" t="n">
-        <v>65250</v>
+        <v>92655</v>
       </c>
       <c r="T1018" s="4" t="s">
         <v>32</v>
@@ -69513,13 +69522,13 @@
         <v>23</v>
       </c>
       <c r="E1085" s="8" t="s">
-        <v>285</v>
+        <v>2090</v>
       </c>
       <c r="F1085" s="9" t="s">
         <v>1058</v>
       </c>
       <c r="G1085" s="9" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="H1085" s="11" t="n">
         <v>46314.461296296</v>
@@ -69536,7 +69545,7 @@
       <c r="L1085" s="10"/>
       <c r="M1085" s="10"/>
       <c r="N1085" s="9" t="s">
-        <v>2084</v>
+        <v>1285</v>
       </c>
       <c r="O1085" s="11" t="n">
         <v>46315.681983368</v>
@@ -69551,7 +69560,7 @@
         <v>55080</v>
       </c>
       <c r="S1085" s="12" t="n">
-        <v>0</v>
+        <v>11016</v>
       </c>
       <c r="T1085" s="9" t="s">
         <v>32</v>
@@ -69571,13 +69580,13 @@
         <v>23</v>
       </c>
       <c r="E1086" s="3" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="F1086" s="4" t="s">
         <v>328</v>
       </c>
       <c r="G1086" s="4" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="H1086" s="6" t="n">
         <v>46314.658842593</v>
@@ -69629,13 +69638,13 @@
         <v>23</v>
       </c>
       <c r="E1087" s="8" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="F1087" s="9" t="s">
         <v>521</v>
       </c>
       <c r="G1087" s="9" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="H1087" s="11" t="n">
         <v>46314.761377315</v>
@@ -69667,7 +69676,7 @@
         <v>18560.4</v>
       </c>
       <c r="S1087" s="12" t="n">
-        <v>6720</v>
+        <v>14730</v>
       </c>
       <c r="T1087" s="9" t="s">
         <v>32</v>
@@ -69693,7 +69702,7 @@
         <v>1100</v>
       </c>
       <c r="G1088" s="4" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="H1088" s="6" t="n">
         <v>46315.573032407</v>
@@ -69751,7 +69760,7 @@
         <v>744</v>
       </c>
       <c r="G1089" s="9" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="H1089" s="11" t="n">
         <v>46315.867488426</v>
@@ -69809,7 +69818,7 @@
         <v>1634</v>
       </c>
       <c r="G1090" s="4" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="H1090" s="5" t="n">
         <v>46315</v>
@@ -69861,13 +69870,13 @@
         <v>23</v>
       </c>
       <c r="E1091" s="8" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="F1091" s="9" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="G1091" s="9" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="H1091" s="11" t="n">
         <v>46316.363946759</v>
@@ -69925,7 +69934,7 @@
         <v>1512</v>
       </c>
       <c r="G1092" s="4" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="H1092" s="5" t="n">
         <v>46316</v>
@@ -69977,13 +69986,13 @@
         <v>23</v>
       </c>
       <c r="E1093" s="8" t="s">
-        <v>285</v>
+        <v>2103</v>
       </c>
       <c r="F1093" s="9" t="s">
         <v>262</v>
       </c>
       <c r="G1093" s="9" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="H1093" s="11" t="n">
         <v>46316.659548611</v>
@@ -70000,7 +70009,7 @@
       <c r="L1093" s="10"/>
       <c r="M1093" s="10"/>
       <c r="N1093" s="9" t="s">
-        <v>2084</v>
+        <v>1285</v>
       </c>
       <c r="O1093" s="11" t="n">
         <v>46317.392973692</v>
@@ -70015,7 +70024,7 @@
         <v>31410</v>
       </c>
       <c r="S1093" s="12" t="n">
-        <v>0</v>
+        <v>19530</v>
       </c>
       <c r="T1093" s="9" t="s">
         <v>32</v>
@@ -70041,7 +70050,7 @@
         <v>1424</v>
       </c>
       <c r="G1094" s="4" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="H1094" s="6" t="n">
         <v>46317.534155093</v>
@@ -70093,13 +70102,13 @@
         <v>23</v>
       </c>
       <c r="E1095" s="8" t="s">
-        <v>2091</v>
+        <v>24</v>
       </c>
       <c r="F1095" s="9" t="s">
         <v>944</v>
       </c>
       <c r="G1095" s="9" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="H1095" s="11" t="n">
         <v>46317.685185185</v>
@@ -70116,7 +70125,7 @@
       <c r="L1095" s="10"/>
       <c r="M1095" s="10"/>
       <c r="N1095" s="9" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O1095" s="11" t="n">
         <v>46318.324940127</v>
@@ -70131,7 +70140,7 @@
         <v>24480</v>
       </c>
       <c r="S1095" s="12" t="n">
-        <v>17280</v>
+        <v>24480</v>
       </c>
       <c r="T1095" s="9" t="s">
         <v>32</v>
@@ -70151,13 +70160,13 @@
         <v>23</v>
       </c>
       <c r="E1096" s="3" t="s">
-        <v>2105</v>
+        <v>24</v>
       </c>
       <c r="F1096" s="4" t="s">
         <v>944</v>
       </c>
       <c r="G1096" s="4" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="H1096" s="6" t="n">
         <v>46317.686666667</v>
@@ -70174,7 +70183,7 @@
       <c r="L1096" s="5"/>
       <c r="M1096" s="5"/>
       <c r="N1096" s="4" t="s">
-        <v>1285</v>
+        <v>29</v>
       </c>
       <c r="O1096" s="6" t="n">
         <v>46318.325082095</v>
@@ -70189,7 +70198,7 @@
         <v>2160</v>
       </c>
       <c r="S1096" s="7" t="n">
-        <v>1440</v>
+        <v>2160</v>
       </c>
       <c r="T1096" s="4" t="s">
         <v>32</v>
@@ -70209,13 +70218,13 @@
         <v>23</v>
       </c>
       <c r="E1097" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1097" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G1097" s="9" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="H1097" s="11" t="n">
         <v>46318.373217593</v>
@@ -70232,7 +70241,7 @@
       <c r="L1097" s="10"/>
       <c r="M1097" s="10"/>
       <c r="N1097" s="9" t="s">
-        <v>2084</v>
+        <v>29</v>
       </c>
       <c r="O1097" s="11" t="n">
         <v>46318.594988542</v>
@@ -70247,7 +70256,7 @@
         <v>8190</v>
       </c>
       <c r="S1097" s="12" t="n">
-        <v>0</v>
+        <v>8190</v>
       </c>
       <c r="T1097" s="9" t="s">
         <v>32</v>
@@ -70273,7 +70282,7 @@
         <v>1625</v>
       </c>
       <c r="G1098" s="4" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="H1098" s="6" t="n">
         <v>46318.378171296</v>
@@ -70325,13 +70334,13 @@
         <v>23</v>
       </c>
       <c r="E1099" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1099" s="9" t="s">
         <v>347</v>
       </c>
       <c r="G1099" s="9" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="H1099" s="11" t="n">
         <v>46304.397569444</v>
@@ -70348,7 +70357,7 @@
       <c r="L1099" s="10"/>
       <c r="M1099" s="10"/>
       <c r="N1099" s="9" t="s">
-        <v>2084</v>
+        <v>29</v>
       </c>
       <c r="O1099" s="11" t="n">
         <v>46318.595291319</v>
@@ -70363,7 +70372,7 @@
         <v>13668.48</v>
       </c>
       <c r="S1099" s="12" t="n">
-        <v>0</v>
+        <v>13668.48</v>
       </c>
       <c r="T1099" s="9" t="s">
         <v>32</v>
@@ -70383,13 +70392,13 @@
         <v>23</v>
       </c>
       <c r="E1100" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1100" s="4" t="s">
         <v>1060</v>
       </c>
       <c r="G1100" s="4" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="H1100" s="6" t="n">
         <v>46304.402835648</v>
@@ -70406,7 +70415,7 @@
       <c r="L1100" s="5"/>
       <c r="M1100" s="5"/>
       <c r="N1100" s="4" t="s">
-        <v>2084</v>
+        <v>29</v>
       </c>
       <c r="O1100" s="6" t="n">
         <v>46318.595518171</v>
@@ -70421,7 +70430,7 @@
         <v>20502.72</v>
       </c>
       <c r="S1100" s="7" t="n">
-        <v>0</v>
+        <v>20502.72</v>
       </c>
       <c r="T1100" s="4" t="s">
         <v>32</v>
@@ -70441,30 +70450,30 @@
         <v>23</v>
       </c>
       <c r="E1101" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1101" s="9" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="G1101" s="9" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="H1101" s="11" t="n">
         <v>46304.405694444</v>
       </c>
       <c r="I1101" s="9" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="J1101" s="9" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="K1101" s="9" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="L1101" s="10"/>
       <c r="M1101" s="10"/>
       <c r="N1101" s="9" t="s">
-        <v>2084</v>
+        <v>29</v>
       </c>
       <c r="O1101" s="11" t="n">
         <v>46318.59570228</v>
@@ -70479,7 +70488,7 @@
         <v>6834.24</v>
       </c>
       <c r="S1101" s="12" t="n">
-        <v>0</v>
+        <v>6834.24</v>
       </c>
       <c r="T1101" s="9" t="s">
         <v>32</v>
@@ -70505,7 +70514,7 @@
         <v>1234</v>
       </c>
       <c r="G1102" s="4" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="H1102" s="6" t="n">
         <v>46317.755613426</v>
@@ -70557,30 +70566,30 @@
         <v>23</v>
       </c>
       <c r="E1103" s="8" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1103" s="9" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="G1103" s="9" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="H1103" s="11" t="n">
         <v>46317.680625</v>
       </c>
       <c r="I1103" s="9" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="J1103" s="9" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="K1103" s="9" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="L1103" s="10"/>
       <c r="M1103" s="10"/>
       <c r="N1103" s="9" t="s">
-        <v>2084</v>
+        <v>29</v>
       </c>
       <c r="O1103" s="11" t="n">
         <v>46318.596058681</v>
@@ -70595,7 +70604,7 @@
         <v>2560.2</v>
       </c>
       <c r="S1103" s="12" t="n">
-        <v>0</v>
+        <v>2560.2</v>
       </c>
       <c r="T1103" s="9" t="s">
         <v>32</v>
@@ -70615,13 +70624,13 @@
         <v>23</v>
       </c>
       <c r="E1104" s="3" t="s">
-        <v>285</v>
+        <v>24</v>
       </c>
       <c r="F1104" s="4" t="s">
         <v>262</v>
       </c>
       <c r="G1104" s="4" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="H1104" s="6" t="n">
         <v>46317.683101852</v>
@@ -70638,7 +70647,7 @@
       <c r="L1104" s="5"/>
       <c r="M1104" s="5"/>
       <c r="N1104" s="4" t="s">
-        <v>2084</v>
+        <v>29</v>
       </c>
       <c r="O1104" s="6" t="n">
         <v>46318.596295104</v>
@@ -70653,7 +70662,7 @@
         <v>19500</v>
       </c>
       <c r="S1104" s="7" t="n">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="T1104" s="4" t="s">
         <v>32</v>
@@ -70673,13 +70682,13 @@
         <v>23</v>
       </c>
       <c r="E1105" s="8" t="s">
-        <v>285</v>
+        <v>2123</v>
       </c>
       <c r="F1105" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G1105" s="9" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="H1105" s="11" t="n">
         <v>46318.486377315</v>
@@ -70711,7 +70720,7 @@
         <v>42336</v>
       </c>
       <c r="S1105" s="12" t="n">
-        <v>0</v>
+        <v>17136</v>
       </c>
       <c r="T1105" s="9" t="s">
         <v>32</v>
@@ -70719,35 +70728,93 @@
       <c r="U1105" s="9"/>
       <c r="V1105" s="9"/>
     </row>
-    <row r="1106" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A1106" s="13" t="n">
-        <v>1104</v>
-      </c>
-      <c r="B1106" s="14"/>
-      <c r="C1106" s="14"/>
-      <c r="D1106" s="14"/>
-      <c r="E1106" s="14"/>
-      <c r="F1106" s="14"/>
-      <c r="G1106" s="14"/>
-      <c r="H1106" s="14"/>
-      <c r="I1106" s="14"/>
-      <c r="J1106" s="14"/>
-      <c r="K1106" s="14"/>
-      <c r="L1106" s="14"/>
-      <c r="M1106" s="14"/>
-      <c r="N1106" s="14"/>
-      <c r="O1106" s="14"/>
-      <c r="P1106" s="14"/>
-      <c r="Q1106" s="14"/>
-      <c r="R1106" s="15" t="n">
-        <v>64025937.5306</v>
-      </c>
-      <c r="S1106" s="15" t="n">
-        <v>61310710.4206</v>
-      </c>
-      <c r="T1106" s="14"/>
-      <c r="U1106" s="14"/>
-      <c r="V1106" s="16"/>
+    <row r="1106" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1106" s="3" t="n">
+        <v>1176</v>
+      </c>
+      <c r="B1106" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1106" s="4"/>
+      <c r="D1106" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1106" s="3" t="s">
+        <v>2090</v>
+      </c>
+      <c r="F1106" s="4" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G1106" s="4" t="s">
+        <v>2125</v>
+      </c>
+      <c r="H1106" s="6" t="n">
+        <v>46321.424699074</v>
+      </c>
+      <c r="I1106" s="4" t="s">
+        <v>1258</v>
+      </c>
+      <c r="J1106" s="4" t="s">
+        <v>1258</v>
+      </c>
+      <c r="K1106" s="4" t="s">
+        <v>1259</v>
+      </c>
+      <c r="L1106" s="5"/>
+      <c r="M1106" s="5"/>
+      <c r="N1106" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="O1106" s="6" t="n">
+        <v>46321.579363113</v>
+      </c>
+      <c r="P1106" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="Q1106" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="R1106" s="7" t="n">
+        <v>129000</v>
+      </c>
+      <c r="S1106" s="7" t="n">
+        <v>25800</v>
+      </c>
+      <c r="T1106" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1106" s="4"/>
+      <c r="V1106" s="4"/>
+    </row>
+    <row r="1107" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A1107" s="13" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B1107" s="14"/>
+      <c r="C1107" s="14"/>
+      <c r="D1107" s="14"/>
+      <c r="E1107" s="14"/>
+      <c r="F1107" s="14"/>
+      <c r="G1107" s="14"/>
+      <c r="H1107" s="14"/>
+      <c r="I1107" s="14"/>
+      <c r="J1107" s="14"/>
+      <c r="K1107" s="14"/>
+      <c r="L1107" s="14"/>
+      <c r="M1107" s="14"/>
+      <c r="N1107" s="14"/>
+      <c r="O1107" s="14"/>
+      <c r="P1107" s="14"/>
+      <c r="Q1107" s="14"/>
+      <c r="R1107" s="15" t="n">
+        <v>64154937.5306</v>
+      </c>
+      <c r="S1107" s="15" t="n">
+        <v>61536520.0606</v>
+      </c>
+      <c r="T1107" s="14"/>
+      <c r="U1107" s="14"/>
+      <c r="V1107" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>

--- a/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
+++ b/dados/XLSX_Grid_CONTRATO CONSULTA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="2146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="2156">
   <si>
     <t>ID</t>
   </si>
@@ -6255,7 +6255,7 @@
     <t>66.852.326/0001-55</t>
   </si>
   <si>
-    <t>68 %</t>
+    <t>90 %</t>
   </si>
   <si>
     <t>1317</t>
@@ -6451,6 +6451,36 @@
   </si>
   <si>
     <t>55.397.585/0001-17</t>
+  </si>
+  <si>
+    <t>1361</t>
+  </si>
+  <si>
+    <t>OBRA PRIVADA - INTERNA</t>
+  </si>
+  <si>
+    <t>1362</t>
+  </si>
+  <si>
+    <t>EM ANDAMENTO</t>
+  </si>
+  <si>
+    <t>Orçamento 363</t>
+  </si>
+  <si>
+    <t>1363</t>
+  </si>
+  <si>
+    <t>Orçamento 371</t>
+  </si>
+  <si>
+    <t>1364</t>
+  </si>
+  <si>
+    <t>Orçamento 370</t>
+  </si>
+  <si>
+    <t>1365</t>
   </si>
 </sst>
 </file>
@@ -6644,31 +6674,31 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:V1122"/>
+  <dimension ref="A1:V1127"/>
   <sheetFormatPr defaultColWidth="12.140625" customHeight="true" defaultRowHeight="15"/>
   <cols>
-    <col max="1" min="1" style="1" width="4.28515625" customWidth="true"/>
-    <col max="2" min="2" style="1" width="13.7109375" customWidth="true"/>
+    <col max="1" min="1" style="1" width="2.85546875" customWidth="true"/>
+    <col max="2" min="2" style="1" width="9.140625" customWidth="true"/>
     <col max="3" min="3" style="1" width="2.85546875" customWidth="true"/>
-    <col max="4" min="4" style="1" width="7.85546875" customWidth="true"/>
-    <col max="5" min="5" style="1" width="9.28515625" customWidth="true"/>
-    <col max="6" min="6" style="1" width="19.85546875" customWidth="true"/>
-    <col max="7" min="7" style="1" width="6.7109375" customWidth="true"/>
-    <col max="8" min="8" style="1" width="8.85546875" customWidth="true"/>
-    <col max="9" min="9" style="1" width="10.7109375" customWidth="true"/>
-    <col max="10" min="10" style="1" width="39.99609375" customWidth="true"/>
-    <col max="11" min="11" style="1" width="14.7109375" customWidth="true"/>
-    <col max="12" min="12" style="1" width="9" customWidth="true"/>
-    <col max="13" min="13" style="1" width="13.42578125" customWidth="true"/>
-    <col max="14" min="14" style="1" width="9.5703125" customWidth="true"/>
-    <col max="15" min="15" style="1" width="15" customWidth="true"/>
-    <col max="16" min="16" style="1" width="7.42578125" customWidth="true"/>
-    <col max="17" min="17" style="1" width="16" customWidth="true"/>
-    <col max="18" min="18" style="1" width="14.7109375" customWidth="true"/>
-    <col max="19" min="19" style="1" width="15.140625" customWidth="true"/>
-    <col max="20" min="20" style="1" width="7.28515625" customWidth="true"/>
-    <col max="21" min="21" style="1" width="10" customWidth="true"/>
-    <col max="22" min="22" style="1" width="14" customWidth="true"/>
+    <col max="4" min="4" style="1" width="5.42578125" customWidth="true"/>
+    <col max="5" min="5" style="1" width="6.28515625" customWidth="true"/>
+    <col max="6" min="6" style="1" width="13.85546875" customWidth="true"/>
+    <col max="7" min="7" style="1" width="4.5703125" customWidth="true"/>
+    <col max="8" min="8" style="1" width="5.99609375" customWidth="true"/>
+    <col max="9" min="9" style="1" width="35.42578125" customWidth="true"/>
+    <col max="10" min="10" style="1" width="30.5703125" customWidth="true"/>
+    <col max="11" min="11" style="1" width="9.85546875" customWidth="true"/>
+    <col max="12" min="12" style="1" width="5.99609375" customWidth="true"/>
+    <col max="13" min="13" style="1" width="9.42578125" customWidth="true"/>
+    <col max="14" min="14" style="1" width="7.140625" customWidth="true"/>
+    <col max="15" min="15" style="1" width="11.28515625" customWidth="true"/>
+    <col max="16" min="16" style="1" width="6.42578125" customWidth="true"/>
+    <col max="17" min="17" style="1" width="11.42578125" customWidth="true"/>
+    <col max="18" min="18" style="1" width="12.85546875" customWidth="true"/>
+    <col max="19" min="19" style="1" width="14" customWidth="true"/>
+    <col max="20" min="20" style="1" width="6.28515625" customWidth="true"/>
+    <col max="21" min="21" style="1" width="26.28515625" customWidth="true"/>
+    <col max="22" min="22" style="1" width="43.42578125" customWidth="true"/>
     <col max="16384" min="23" style="1" width="12.140625"/>
   </cols>
   <sheetData>
@@ -69272,7 +69302,7 @@
         <v>36014.7</v>
       </c>
       <c r="S1079" s="12" t="n">
-        <v>24637.8</v>
+        <v>32292.3</v>
       </c>
       <c r="T1079" s="9" t="s">
         <v>32</v>
@@ -71264,7 +71294,7 @@
         <v>23</v>
       </c>
       <c r="E1114" s="3" t="s">
-        <v>24</v>
+        <v>285</v>
       </c>
       <c r="F1114" s="4" t="s">
         <v>276</v>
@@ -71287,7 +71317,7 @@
       <c r="L1114" s="5"/>
       <c r="M1114" s="5"/>
       <c r="N1114" s="4" t="s">
-        <v>29</v>
+        <v>2106</v>
       </c>
       <c r="O1114" s="6" t="n">
         <v>46324.355512813</v>
@@ -71302,7 +71332,7 @@
         <v>4785</v>
       </c>
       <c r="S1114" s="7" t="n">
-        <v>4785</v>
+        <v>0</v>
       </c>
       <c r="T1114" s="4" t="s">
         <v>32</v>
@@ -71716,35 +71746,325 @@
       <c r="U1121" s="9"/>
       <c r="V1121" s="9"/>
     </row>
-    <row r="1122" customHeight="true" ht="13.5" customFormat="true" s="1">
-      <c r="A1122" s="13" t="n">
-        <v>1120</v>
-      </c>
-      <c r="B1122" s="14"/>
-      <c r="C1122" s="14"/>
-      <c r="D1122" s="14"/>
-      <c r="E1122" s="14"/>
-      <c r="F1122" s="14"/>
-      <c r="G1122" s="14"/>
-      <c r="H1122" s="14"/>
-      <c r="I1122" s="14"/>
-      <c r="J1122" s="14"/>
-      <c r="K1122" s="14"/>
-      <c r="L1122" s="14"/>
-      <c r="M1122" s="14"/>
-      <c r="N1122" s="14"/>
-      <c r="O1122" s="14"/>
-      <c r="P1122" s="14"/>
-      <c r="Q1122" s="14"/>
-      <c r="R1122" s="15" t="n">
-        <v>64650030.1506</v>
-      </c>
-      <c r="S1122" s="15" t="n">
-        <v>62222683.8606</v>
-      </c>
-      <c r="T1122" s="14"/>
-      <c r="U1122" s="14"/>
-      <c r="V1122" s="16"/>
+    <row r="1122" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1122" s="3" t="n">
+        <v>1193</v>
+      </c>
+      <c r="B1122" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1122" s="4"/>
+      <c r="D1122" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1122" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1122" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1122" s="4" t="s">
+        <v>2146</v>
+      </c>
+      <c r="H1122" s="6" t="n">
+        <v>46324.824409722</v>
+      </c>
+      <c r="I1122" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="J1122" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="K1122" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L1122" s="5"/>
+      <c r="M1122" s="5"/>
+      <c r="N1122" s="4" t="s">
+        <v>2106</v>
+      </c>
+      <c r="O1122" s="6" t="n">
+        <v>46325.623301887</v>
+      </c>
+      <c r="P1122" s="4" t="s">
+        <v>1451</v>
+      </c>
+      <c r="Q1122" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1122" s="7" t="n">
+        <v>37565.75</v>
+      </c>
+      <c r="S1122" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1122" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1122" s="4"/>
+      <c r="V1122" s="4"/>
+    </row>
+    <row r="1123" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1123" s="8" t="n">
+        <v>1194</v>
+      </c>
+      <c r="B1123" s="9" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C1123" s="9"/>
+      <c r="D1123" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1123" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1123" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1123" s="9" t="s">
+        <v>2148</v>
+      </c>
+      <c r="H1123" s="11" t="n">
+        <v>46324.832465278</v>
+      </c>
+      <c r="I1123" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="J1123" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="K1123" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="L1123" s="10"/>
+      <c r="M1123" s="10"/>
+      <c r="N1123" s="9" t="s">
+        <v>2149</v>
+      </c>
+      <c r="O1123" s="11" t="n">
+        <v>46325.623442049</v>
+      </c>
+      <c r="P1123" s="9" t="s">
+        <v>1451</v>
+      </c>
+      <c r="Q1123" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="R1123" s="12" t="n">
+        <v>1860</v>
+      </c>
+      <c r="S1123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1123" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1123" s="9"/>
+      <c r="V1123" s="9"/>
+    </row>
+    <row r="1124" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1124" s="3" t="n">
+        <v>1195</v>
+      </c>
+      <c r="B1124" s="4" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C1124" s="4"/>
+      <c r="D1124" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E1124" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1124" s="4" t="s">
+        <v>2150</v>
+      </c>
+      <c r="G1124" s="4" t="s">
+        <v>2151</v>
+      </c>
+      <c r="H1124" s="6" t="n">
+        <v>46308.632453704</v>
+      </c>
+      <c r="I1124" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="J1124" s="4" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K1124" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L1124" s="5"/>
+      <c r="M1124" s="5"/>
+      <c r="N1124" s="4" t="s">
+        <v>2149</v>
+      </c>
+      <c r="O1124" s="6" t="n">
+        <v>46325.623651771</v>
+      </c>
+      <c r="P1124" s="4" t="s">
+        <v>1451</v>
+      </c>
+      <c r="Q1124" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="R1124" s="7" t="n">
+        <v>11037.36</v>
+      </c>
+      <c r="S1124" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1124" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="U1124" s="4"/>
+      <c r="V1124" s="4"/>
+    </row>
+    <row r="1125" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1125" s="8" t="n">
+        <v>1196</v>
+      </c>
+      <c r="B1125" s="9" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C1125" s="9"/>
+      <c r="D1125" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="E1125" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1125" s="9" t="s">
+        <v>2152</v>
+      </c>
+      <c r="G1125" s="9" t="s">
+        <v>2153</v>
+      </c>
+      <c r="H1125" s="11" t="n">
+        <v>46324.683263889</v>
+      </c>
+      <c r="I1125" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1125" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K1125" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="L1125" s="10"/>
+      <c r="M1125" s="10"/>
+      <c r="N1125" s="9" t="s">
+        <v>2149</v>
+      </c>
+      <c r="O1125" s="11" t="n">
+        <v>46325.623781285</v>
+      </c>
+      <c r="P1125" s="9" t="s">
+        <v>1451</v>
+      </c>
+      <c r="Q1125" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1125" s="12" t="n">
+        <v>8473</v>
+      </c>
+      <c r="S1125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1125" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1125" s="9"/>
+      <c r="V1125" s="9"/>
+    </row>
+    <row r="1126" customHeight="true" ht="16.5" customFormat="true" s="1">
+      <c r="A1126" s="3" t="n">
+        <v>1197</v>
+      </c>
+      <c r="B1126" s="4" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C1126" s="4"/>
+      <c r="D1126" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E1126" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1126" s="4" t="s">
+        <v>2154</v>
+      </c>
+      <c r="G1126" s="4" t="s">
+        <v>2155</v>
+      </c>
+      <c r="H1126" s="6" t="n">
+        <v>46324.625023148</v>
+      </c>
+      <c r="I1126" s="4" t="s">
+        <v>1234</v>
+      </c>
+      <c r="J1126" s="4" t="s">
+        <v>1235</v>
+      </c>
+      <c r="K1126" s="4" t="s">
+        <v>1236</v>
+      </c>
+      <c r="L1126" s="5"/>
+      <c r="M1126" s="5"/>
+      <c r="N1126" s="4" t="s">
+        <v>2149</v>
+      </c>
+      <c r="O1126" s="6" t="n">
+        <v>46325.623909225</v>
+      </c>
+      <c r="P1126" s="4" t="s">
+        <v>1451</v>
+      </c>
+      <c r="Q1126" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="R1126" s="7" t="n">
+        <v>27675</v>
+      </c>
+      <c r="S1126" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1126" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="U1126" s="4"/>
+      <c r="V1126" s="4"/>
+    </row>
+    <row r="1127" customHeight="true" ht="13.5" customFormat="true" s="1">
+      <c r="A1127" s="13" t="n">
+        <v>1125</v>
+      </c>
+      <c r="B1127" s="14"/>
+      <c r="C1127" s="14"/>
+      <c r="D1127" s="14"/>
+      <c r="E1127" s="14"/>
+      <c r="F1127" s="14"/>
+      <c r="G1127" s="14"/>
+      <c r="H1127" s="14"/>
+      <c r="I1127" s="14"/>
+      <c r="J1127" s="14"/>
+      <c r="K1127" s="14"/>
+      <c r="L1127" s="14"/>
+      <c r="M1127" s="14"/>
+      <c r="N1127" s="14"/>
+      <c r="O1127" s="14"/>
+      <c r="P1127" s="14"/>
+      <c r="Q1127" s="14"/>
+      <c r="R1127" s="15" t="n">
+        <v>64736641.2606</v>
+      </c>
+      <c r="S1127" s="15" t="n">
+        <v>62225553.3606</v>
+      </c>
+      <c r="T1127" s="14"/>
+      <c r="U1127" s="14"/>
+      <c r="V1127" s="16"/>
     </row>
   </sheetData>
   <pageSetup orientation="default" cellComments="none"/>
